--- a/data/latest.xlsx
+++ b/data/latest.xlsx
@@ -59,31 +59,6 @@
     <t>CAD($)</t>
   </si>
   <si>
-    <t>ENGINEERINGCPR      </t>
-  </si>
-  <si>
-    <t>12/05/2025</t>
-  </si>
-  <si>
-    <t>02/26/2026</t>
-  </si>
-  <si>
-    <t>PAST DUE</t>
-  </si>
-  <si>
-    <t>SMX-TC0479-8AEXXX                 </t>
-  </si>
-  <si>
-    <t>
-    </t>
-  </si>
-  <si>
-    <t>OASYS Extension Arm, 950mm w/LCH Spring Arm, Custom End, Stops, Extra keys,9003 </t>
-  </si>
-  <si>
-    <t>SHIP DATES: AS NOTED</t>
-  </si>
-  <si>
     <t>LOC                 </t>
   </si>
   <si>
@@ -93,25 +68,20 @@
     <t>03/16/2026</t>
   </si>
   <si>
+    <t>PAST DUE</t>
+  </si>
+  <si>
     <t>F-0-XD-XX                         </t>
+  </si>
+  <si>
+    <t>
+    </t>
   </si>
   <si>
     <t>Floor Roll Cart, with vesa mount, White                                         </t>
   </si>
   <si>
     <t>SHIP DATE - TBD</t>
-  </si>
-  <si>
-    <t>MONTH:</t>
-  </si>
-  <si>
-    <t>February, 2026</t>
-  </si>
-  <si>
-    <t>Hours available = 600. Hours remaining = 600</t>
-  </si>
-  <si>
-    <t>TOTAL:</t>
   </si>
   <si>
     <t>MAXIMMED            </t>
@@ -123,9 +93,6 @@
     <t>03/18/2026</t>
   </si>
   <si>
-    <t>OKAY</t>
-  </si>
-  <si>
     <t>EMM-30SVL-SX-0G                   </t>
   </si>
   <si>
@@ -135,40 +102,22 @@
     <t>SHIP DATE - MARCH 18, 2026</t>
   </si>
   <si>
+    <t>TOTAL:</t>
+  </si>
+  <si>
     <t>SM-S391-0GR-3                     </t>
   </si>
   <si>
     <t>Spring arm, Med Duty, 910mm, 3075 w/2075 device end, STP, RAL 9002              </t>
   </si>
   <si>
-    <t>BURTONMEDICALLLC    </t>
+    <t>ENGINEERINGCPR      </t>
   </si>
   <si>
-    <t>03/13/2026</t>
+    <t>12/10/2025</t>
   </si>
   <si>
     <t>03/20/2026</t>
-  </si>
-  <si>
-    <t>SA-L-LCK-F-KT                     </t>
-  </si>
-  <si>
-    <t>Locking Collar with Screw                                                       </t>
-  </si>
-  <si>
-    <t>SHIP DATE - ASAP</t>
-  </si>
-  <si>
-    <t>SR-3P-M-ASSY                      </t>
-  </si>
-  <si>
-    <t>3P SLIP RING - MALE                                                             </t>
-  </si>
-  <si>
-    <t>DOCK DATE - MARCH 27, 2026</t>
-  </si>
-  <si>
-    <t>12/10/2025</t>
   </si>
   <si>
     <t>SMX-TC0179-8AEXXX                 </t>
@@ -180,59 +129,16 @@
     <t>SHIP DATES - AS NOTED</t>
   </si>
   <si>
-    <t>03/23/2026</t>
-  </si>
-  <si>
-    <t>EMA-10024-XX-0B                   </t>
-  </si>
-  <si>
-    <t>Monitor mount adaptor, up to 24" monitor, 10kg, RAL 7035                        </t>
-  </si>
-  <si>
-    <t>HM-30100-0SR                      </t>
-  </si>
-  <si>
-    <t>Extension Arm, 1000mm, 30kg, Stop, reverse, RAL 7035                            </t>
-  </si>
-  <si>
-    <t>HRNS-CAT6-ASSY                    </t>
-  </si>
-  <si>
-    <t>Harness Assembly (CAT6) for arm systems                                         </t>
-  </si>
-  <si>
-    <t>MMW-300-SS-XXX-X                  </t>
-  </si>
-  <si>
-    <t>Wall mount, RAL 7035                                                            </t>
-  </si>
-  <si>
-    <t>SM-C491-0SJ-X                     </t>
-  </si>
-  <si>
-    <t>Spring Arm, Med Duty, 2075, Stop, 3-8kg, 7035                                   </t>
-  </si>
-  <si>
-    <t>KRWOLFE             </t>
-  </si>
-  <si>
-    <t>03/25/2026</t>
-  </si>
-  <si>
-    <t>SM-L391-0WT-X                     </t>
-  </si>
-  <si>
-    <t>Spring Arm, Med Duty, TM3001, 910mm, Stop w/2001 end, RAL 9010                  </t>
-  </si>
-  <si>
-    <t>SHIP DATE - ASAP
-REPLACEMENTS</t>
+    <t>BURTONMEDICALLLC    </t>
   </si>
   <si>
     <t>12/03/2025</t>
   </si>
   <si>
     <t>03/30/2026</t>
+  </si>
+  <si>
+    <t>OKAY</t>
   </si>
   <si>
     <t>SLW-068055-3WG                    </t>
@@ -281,6 +187,9 @@
   </si>
   <si>
     <t>DOCK DATE - APRIL 9, 2026</t>
+  </si>
+  <si>
+    <t>MONTH:</t>
   </si>
   <si>
     <t>March, 2026</t>
@@ -352,6 +261,30 @@
     <t>DOCK DATE - MAY 6, 2026</t>
   </si>
   <si>
+    <t>OASYS               </t>
+  </si>
+  <si>
+    <t>SL-0655-2WG-S                     </t>
+  </si>
+  <si>
+    <t>Light Duty Straight Spring Arm, 3 Contacts/1 Commutators, White                 </t>
+  </si>
+  <si>
+    <t>TESTING FOR BURTON, BRANDON AND DERUNGS ARMS</t>
+  </si>
+  <si>
+    <t>SL-0772-6B-N                      </t>
+  </si>
+  <si>
+    <t>Light Duty Spring Arm, 7kg, 3C/1SR, Curved, Bottom, w/Post, RAL9010, Brandon Med</t>
+  </si>
+  <si>
+    <t>SL-0773-3E-K                      </t>
+  </si>
+  <si>
+    <t>Light Duty Spring arm, 730mm arm, TM, RAL 9010                                  </t>
+  </si>
+  <si>
     <t>SIMEONMEDICALGMBH   </t>
   </si>
   <si>
@@ -364,13 +297,49 @@
     <t>3P SLIP RING - FEMALE, 1.100" OD (28mm)                                         </t>
   </si>
   <si>
+    <t>SR-3P-M-ASSY                      </t>
+  </si>
+  <si>
+    <t>3P SLIP RING - MALE                                                             </t>
+  </si>
+  <si>
     <t>11/10/2025</t>
   </si>
   <si>
     <t>04/10/2026</t>
   </si>
   <si>
+    <t>EMA-10024-XX-0B                   </t>
+  </si>
+  <si>
+    <t>Monitor mount adaptor, up to 24" monitor, 10kg, RAL 7035                        </t>
+  </si>
+  <si>
     <t>SHIP DATE - April 10, 2026</t>
+  </si>
+  <si>
+    <t>HM-30100-0SR                      </t>
+  </si>
+  <si>
+    <t>Extension Arm, 1000mm, 30kg, Stop, reverse, RAL 7035                            </t>
+  </si>
+  <si>
+    <t>HRNS-CAT6-ASSY                    </t>
+  </si>
+  <si>
+    <t>Harness Assembly (CAT6) for arm systems                                         </t>
+  </si>
+  <si>
+    <t>MMW-300-SS-XXX-X                  </t>
+  </si>
+  <si>
+    <t>Wall mount, RAL 7035                                                            </t>
+  </si>
+  <si>
+    <t>SM-C491-0SJ-X                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 2075, Stop, 3-8kg, 7035                                   </t>
   </si>
   <si>
     <t>04/13/2026</t>
@@ -516,6 +485,9 @@
     <t>Light Duty Straight Spring Arm, 3 Contacts/1 Comm, White (Burton), UNI Groove   </t>
   </si>
   <si>
+    <t>SHIP DATE - ASAP</t>
+  </si>
+  <si>
     <t>April, 2026</t>
   </si>
   <si>
@@ -550,6 +522,51 @@
   </si>
   <si>
     <t>DOCK DATE - JUNE 19, 2026</t>
+  </si>
+  <si>
+    <t>NEXORMEDICAL        </t>
+  </si>
+  <si>
+    <t>03/19/2026</t>
+  </si>
+  <si>
+    <t>05/08/2026</t>
+  </si>
+  <si>
+    <t>C-0-XW-X4                         </t>
+  </si>
+  <si>
+    <t>SHIP DATE - MAY 8, 2026</t>
+  </si>
+  <si>
+    <t>C-2-AW-P4                         </t>
+  </si>
+  <si>
+    <t>Ceiling mount, Drop Tube, 3P Slip Ring and Harness, 900mm, RAL 9010             </t>
+  </si>
+  <si>
+    <t>F-1-XW-X4                         </t>
+  </si>
+  <si>
+    <t>Floor stand base, 110v/3/Standard, white, no base harness, no switch            </t>
+  </si>
+  <si>
+    <t>MMW-301-WX-XXX-G                  </t>
+  </si>
+  <si>
+    <t>Wall mount with 3P harness                                                      </t>
+  </si>
+  <si>
+    <t>SA-L-C-DCV4-CLR-KT                </t>
+  </si>
+  <si>
+    <t>Dome Cover with collar Kit                                                      </t>
+  </si>
+  <si>
+    <t>SL-0373-2B-2                      </t>
+  </si>
+  <si>
+    <t>Light Duty Spring arm, 3kg, 720mm straight, 3P, Bottom mount (FS), RAL 9010,N300</t>
   </si>
   <si>
     <t>05/11/2026</t>
@@ -651,6 +668,9 @@
     <t>August, 2026</t>
   </si>
   <si>
+    <t>Hours available = 600. Hours remaining = 600</t>
+  </si>
+  <si>
     <t>10/16/2026</t>
   </si>
   <si>
@@ -664,6 +684,9 @@
   </si>
   <si>
     <t>BARRFAB             </t>
+  </si>
+  <si>
+    <t>02/26/2026</t>
   </si>
   <si>
     <t>TBD</t>
@@ -1683,7 +1706,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="45">
-        <v>0000106773</v>
+        <v>0000106837</v>
       </c>
       <c r="C7" s="46" t="s">
         <v>14</v>
@@ -1698,10 +1721,10 @@
         <v>17</v>
       </c>
       <c r="G7" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7" s="52">
-        <v>2365</v>
+        <v>975</v>
       </c>
       <c r="I7" s="53" t="s">
         <v>18</v>
@@ -1720,46 +1743,52 @@
       <c r="C8" s="46"/>
       <c r="D8" s="46"/>
       <c r="E8" s="47"/>
-      <c r="F8" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F8" s="44"/>
       <c r="G8" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H8" s="52">
-        <v>4730</v>
-      </c>
-      <c r="I8" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>4875</v>
+      </c>
+      <c r="I8" s="53"/>
+      <c r="J8" s="48"/>
       <c r="K8" s="49"/>
       <c r="L8" s="0"/>
     </row>
     <row r="9">
-      <c r="A9" s="44"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" t="s" s="51">
-        <v>27</v>
+      <c r="A9" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B9" s="45">
+        <v>0000106752</v>
+      </c>
+      <c r="C9" t="s" s="46">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s" s="46">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s" s="44">
+        <v>24</v>
+      </c>
+      <c r="G9" s="51">
+        <v>24</v>
       </c>
       <c r="H9" s="52">
-        <v>4730</v>
-      </c>
-      <c r="I9" s="53">
-        <v>0</v>
-      </c>
-      <c r="J9" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="49"/>
+        <v>1141.98</v>
+      </c>
+      <c r="I9" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s" s="48">
+        <v>25</v>
+      </c>
+      <c r="K9" t="s" s="49">
+        <v>26</v>
+      </c>
       <c r="L9" s="0"/>
     </row>
     <row r="10">
@@ -1767,7 +1796,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="45">
-        <v>0000106837</v>
+        <v>0000106752</v>
       </c>
       <c r="C10" t="s" s="46">
         <v>22</v>
@@ -1779,19 +1808,19 @@
         <v>16</v>
       </c>
       <c r="F10" t="s" s="44">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G10" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H10" s="52">
-        <v>975</v>
+        <v>1060.82</v>
       </c>
       <c r="I10" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J10" t="s" s="48">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K10" t="s" s="49">
         <v>26</v>
@@ -1806,10 +1835,10 @@
       <c r="E11" s="47"/>
       <c r="F11" s="44"/>
       <c r="G11" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H11" s="52">
-        <v>4875</v>
+        <v>38015.72</v>
       </c>
       <c r="I11" s="53"/>
       <c r="J11" s="48"/>
@@ -1818,236 +1847,224 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="44">
+        <v>30</v>
+      </c>
+      <c r="B12" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C12" t="s" s="46">
         <v>31</v>
       </c>
-      <c r="B12" s="45">
-        <v>0000106752</v>
-      </c>
-      <c r="C12" t="s" s="46">
+      <c r="D12" t="s" s="46">
         <v>32</v>
       </c>
-      <c r="D12" t="s" s="46">
+      <c r="E12" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s" s="44">
         <v>33</v>
       </c>
-      <c r="E12" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F12" t="s" s="44">
-        <v>35</v>
-      </c>
       <c r="G12" s="51">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H12" s="52">
-        <v>1141.98</v>
+        <v>2250</v>
       </c>
       <c r="I12" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J12" t="s" s="48">
+        <v>34</v>
+      </c>
+      <c r="K12" t="s" s="49">
+        <v>35</v>
+      </c>
+      <c r="L12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="44"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="44"/>
+      <c r="G13" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H13" s="52">
+        <v>11250</v>
+      </c>
+      <c r="I13" s="53"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="44">
         <v>36</v>
       </c>
-      <c r="K12" t="s" s="49">
+      <c r="B14" s="45">
+        <v>0000106769</v>
+      </c>
+      <c r="C14" t="s" s="46">
         <v>37</v>
       </c>
-      <c r="L12" s="0"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="44">
-        <v>31</v>
-      </c>
-      <c r="B13" s="45">
-        <v>0000106752</v>
-      </c>
-      <c r="C13" t="s" s="46">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="46">
-        <v>33</v>
-      </c>
-      <c r="E13" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F13" t="s" s="44">
+      <c r="D14" t="s" s="46">
         <v>38</v>
       </c>
-      <c r="G13" s="51">
-        <v>10</v>
-      </c>
-      <c r="H13" s="52">
-        <v>1060.82</v>
-      </c>
-      <c r="I13" t="s" s="53">
+      <c r="E14" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s" s="44">
+        <v>40</v>
+      </c>
+      <c r="G14" s="51">
+        <v>70</v>
+      </c>
+      <c r="H14" s="52">
+        <v>377.62</v>
+      </c>
+      <c r="I14" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J14" t="s" s="48">
+        <v>41</v>
+      </c>
+      <c r="K14" t="s" s="49">
+        <v>42</v>
+      </c>
+      <c r="L14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="44"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="44"/>
+      <c r="G15" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H15" s="52">
+        <v>26433.4</v>
+      </c>
+      <c r="I15" s="53"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="44">
+        <v>43</v>
+      </c>
+      <c r="B16" s="45">
+        <v>0000106832</v>
+      </c>
+      <c r="C16" t="s" s="46">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s" s="46">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s" s="44">
+        <v>46</v>
+      </c>
+      <c r="G16" s="51">
+        <v>52</v>
+      </c>
+      <c r="H16" s="52">
+        <v>473.26</v>
+      </c>
+      <c r="I16" s="53">
+        <v>52</v>
+      </c>
+      <c r="J16" t="s" s="48">
+        <v>47</v>
+      </c>
+      <c r="K16" t="s" s="49">
+        <v>48</v>
+      </c>
+      <c r="L16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="44"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="44"/>
+      <c r="G17" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H17" s="52">
+        <v>24609.52</v>
+      </c>
+      <c r="I17" s="53"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="44">
+        <v>43</v>
+      </c>
+      <c r="B18" s="45">
+        <v>0000106833</v>
+      </c>
+      <c r="C18" t="s" s="46">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s" s="46">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s" s="44">
+        <v>49</v>
+      </c>
+      <c r="G18" s="51">
+        <v>156</v>
+      </c>
+      <c r="H18" s="52">
+        <v>367.69</v>
+      </c>
+      <c r="I18" s="53">
+        <v>156</v>
+      </c>
+      <c r="J18" t="s" s="48">
+        <v>50</v>
+      </c>
+      <c r="K18" t="s" s="49">
+        <v>48</v>
+      </c>
+      <c r="L18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="44"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="47"/>
+      <c r="F19" t="s" s="44">
         <v>18</v>
       </c>
-      <c r="J13" t="s" s="48">
-        <v>39</v>
-      </c>
-      <c r="K13" t="s" s="49">
-        <v>37</v>
-      </c>
-      <c r="L13" s="0"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="44"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="44"/>
-      <c r="G14" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H14" s="52">
-        <v>38015.72</v>
-      </c>
-      <c r="I14" s="53"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="0"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B15" s="45">
-        <v>0000106878</v>
-      </c>
-      <c r="C15" t="s" s="46">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s" s="46">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F15" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="G15" s="51">
-        <v>50</v>
-      </c>
-      <c r="H15" s="52">
-        <v>20.42</v>
-      </c>
-      <c r="I15" t="s" s="53">
+      <c r="G19" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H19" s="52">
+        <v>57359.64</v>
+      </c>
+      <c r="I19" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="J15" t="s" s="48">
-        <v>44</v>
-      </c>
-      <c r="K15" t="s" s="49">
-        <v>45</v>
-      </c>
-      <c r="L15" s="0"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="44"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="44"/>
-      <c r="G16" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H16" s="52">
-        <v>1021</v>
-      </c>
-      <c r="I16" s="53"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="49"/>
-      <c r="L16" s="0"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B17" s="45">
-        <v>0000106885</v>
-      </c>
-      <c r="C17" t="s" s="46">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s" s="46">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F17" t="s" s="44">
-        <v>46</v>
-      </c>
-      <c r="G17" s="51">
-        <v>25</v>
-      </c>
-      <c r="H17" s="52">
-        <v>14.70</v>
-      </c>
-      <c r="I17" t="s" s="53">
+      <c r="J19" t="s" s="48">
         <v>18</v>
       </c>
-      <c r="J17" t="s" s="48">
-        <v>47</v>
-      </c>
-      <c r="K17" t="s" s="49">
-        <v>48</v>
-      </c>
-      <c r="L17" s="0"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="44"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="44"/>
-      <c r="G18" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H18" s="52">
-        <v>367.5</v>
-      </c>
-      <c r="I18" s="53"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="0"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B19" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C19" t="s" s="46">
-        <v>49</v>
-      </c>
-      <c r="D19" t="s" s="46">
-        <v>42</v>
-      </c>
-      <c r="E19" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F19" t="s" s="44">
-        <v>50</v>
-      </c>
-      <c r="G19" s="51">
-        <v>5</v>
-      </c>
-      <c r="H19" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I19" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s" s="48">
-        <v>51</v>
-      </c>
-      <c r="K19" t="s" s="49">
-        <v>52</v>
-      </c>
+      <c r="K19" s="49"/>
       <c r="L19" s="0"/>
     </row>
     <row r="20">
@@ -2056,195 +2073,165 @@
       <c r="C20" s="46"/>
       <c r="D20" s="46"/>
       <c r="E20" s="47"/>
-      <c r="F20" s="44"/>
+      <c r="F20" s="44" t="s">
+        <v>57</v>
+      </c>
       <c r="G20" t="s" s="51">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H20" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I20" s="53"/>
-      <c r="J20" s="48"/>
+        <v>162543.28</v>
+      </c>
+      <c r="I20" s="53">
+        <v>295.5</v>
+      </c>
+      <c r="J20" s="48" t="s">
+        <v>58</v>
+      </c>
       <c r="K20" s="49"/>
       <c r="L20" s="0"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B21" s="45">
-        <v>0000106879</v>
+        <v>0000106806</v>
       </c>
       <c r="C21" t="s" s="46">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s" s="46">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F21" t="s" s="44">
         <v>53</v>
       </c>
-      <c r="E21" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F21" t="s" s="44">
+      <c r="G21" s="51">
+        <v>10</v>
+      </c>
+      <c r="H21" s="52">
+        <v>572.10</v>
+      </c>
+      <c r="I21" s="53">
+        <v>30</v>
+      </c>
+      <c r="J21" t="s" s="48">
         <v>54</v>
       </c>
-      <c r="G21" s="51">
-        <v>2</v>
-      </c>
-      <c r="H21" s="52">
-        <v>75</v>
-      </c>
-      <c r="I21" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J21" t="s" s="48">
+      <c r="K21" t="s" s="49">
         <v>55</v>
       </c>
-      <c r="K21" t="s" s="49">
-        <v>45</v>
-      </c>
       <c r="L21" s="0"/>
     </row>
     <row r="22">
-      <c r="A22" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B22" s="45">
-        <v>0000106879</v>
-      </c>
-      <c r="C22" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="D22" t="s" s="46">
-        <v>53</v>
-      </c>
-      <c r="E22" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F22" t="s" s="44">
-        <v>56</v>
-      </c>
-      <c r="G22" s="51">
-        <v>2</v>
+      <c r="A22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="44"/>
+      <c r="G22" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H22" s="52">
-        <v>225</v>
-      </c>
-      <c r="I22" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s" s="48">
-        <v>57</v>
-      </c>
-      <c r="K22" t="s" s="49">
-        <v>45</v>
-      </c>
+        <v>5721</v>
+      </c>
+      <c r="I22" s="53"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="49"/>
       <c r="L22" s="0"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B23" s="45">
-        <v>0000106879</v>
+        <v>0000106807</v>
       </c>
       <c r="C23" t="s" s="46">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s" s="46">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s" s="44">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G23" s="51">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H23" s="52">
-        <v>0</v>
-      </c>
-      <c r="I23" t="s" s="53">
-        <v>18</v>
+        <v>319.37</v>
+      </c>
+      <c r="I23" s="53">
+        <v>72</v>
       </c>
       <c r="J23" t="s" s="48">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K23" t="s" s="49">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="L23" s="0"/>
     </row>
     <row r="24">
-      <c r="A24" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B24" s="45">
-        <v>0000106879</v>
-      </c>
-      <c r="C24" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="D24" t="s" s="46">
-        <v>53</v>
-      </c>
-      <c r="E24" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F24" t="s" s="44">
-        <v>60</v>
-      </c>
-      <c r="G24" s="51">
-        <v>2</v>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="44"/>
+      <c r="G24" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H24" s="52">
-        <v>100</v>
-      </c>
-      <c r="I24" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s" s="48">
-        <v>61</v>
-      </c>
-      <c r="K24" t="s" s="49">
-        <v>45</v>
-      </c>
+        <v>15329.76</v>
+      </c>
+      <c r="I24" s="53"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="49"/>
       <c r="L24" s="0"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B25" s="45">
-        <v>0000106879</v>
+        <v>0000106808</v>
       </c>
       <c r="C25" t="s" s="46">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s" s="46">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s" s="44">
+        <v>61</v>
+      </c>
+      <c r="G25" s="51">
+        <v>16</v>
+      </c>
+      <c r="H25" s="52">
+        <v>659.52</v>
+      </c>
+      <c r="I25" s="53">
+        <v>48</v>
+      </c>
+      <c r="J25" t="s" s="48">
         <v>62</v>
       </c>
-      <c r="G25" s="51">
-        <v>2</v>
-      </c>
-      <c r="H25" s="52">
-        <v>495</v>
-      </c>
-      <c r="I25" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J25" t="s" s="48">
-        <v>63</v>
-      </c>
       <c r="K25" t="s" s="49">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="L25" s="0"/>
     </row>
@@ -2256,10 +2243,10 @@
       <c r="E26" s="47"/>
       <c r="F26" s="44"/>
       <c r="G26" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H26" s="52">
-        <v>1790</v>
+        <v>10552.32</v>
       </c>
       <c r="I26" s="53"/>
       <c r="J26" s="48"/>
@@ -2268,37 +2255,37 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B27" s="45">
+        <v>0000106849</v>
+      </c>
+      <c r="C27" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s" s="46">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F27" t="s" s="44">
         <v>64</v>
       </c>
-      <c r="B27" s="45">
-        <v>0000106886</v>
-      </c>
-      <c r="C27" t="s" s="46">
-        <v>33</v>
-      </c>
-      <c r="D27" t="s" s="46">
+      <c r="G27" s="51">
+        <v>5</v>
+      </c>
+      <c r="H27" s="52">
+        <v>400.69</v>
+      </c>
+      <c r="I27" s="53">
+        <v>6.25</v>
+      </c>
+      <c r="J27" t="s" s="48">
         <v>65</v>
       </c>
-      <c r="E27" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F27" t="s" s="44">
+      <c r="K27" t="s" s="49">
         <v>66</v>
-      </c>
-      <c r="G27" s="51">
-        <v>1</v>
-      </c>
-      <c r="H27" s="52">
-        <v>0</v>
-      </c>
-      <c r="I27" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J27" t="s" s="48">
-        <v>67</v>
-      </c>
-      <c r="K27" t="s" s="49">
-        <v>68</v>
       </c>
       <c r="L27" s="0"/>
     </row>
@@ -2310,10 +2297,10 @@
       <c r="E28" s="47"/>
       <c r="F28" s="44"/>
       <c r="G28" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H28" s="52">
-        <v>0</v>
+        <v>2003.45</v>
       </c>
       <c r="I28" s="53"/>
       <c r="J28" s="48"/>
@@ -2322,37 +2309,37 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="44">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B29" s="45">
-        <v>0000106769</v>
+        <v>0000106798</v>
       </c>
       <c r="C29" t="s" s="46">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s" s="46">
         <v>69</v>
       </c>
-      <c r="D29" t="s" s="46">
+      <c r="E29" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F29" t="s" s="44">
         <v>70</v>
       </c>
-      <c r="E29" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F29" t="s" s="44">
+      <c r="G29" s="51">
+        <v>504</v>
+      </c>
+      <c r="H29" s="52">
+        <v>22.71</v>
+      </c>
+      <c r="I29" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s" s="48">
         <v>71</v>
       </c>
-      <c r="G29" s="51">
-        <v>70</v>
-      </c>
-      <c r="H29" s="52">
-        <v>377.62</v>
-      </c>
-      <c r="I29" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J29" t="s" s="48">
+      <c r="K29" t="s" s="49">
         <v>72</v>
-      </c>
-      <c r="K29" t="s" s="49">
-        <v>73</v>
       </c>
       <c r="L29" s="0"/>
     </row>
@@ -2364,10 +2351,10 @@
       <c r="E30" s="47"/>
       <c r="F30" s="44"/>
       <c r="G30" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H30" s="52">
-        <v>26433.4</v>
+        <v>11445.84</v>
       </c>
       <c r="I30" s="53"/>
       <c r="J30" s="48"/>
@@ -2376,37 +2363,37 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B31" s="45">
+        <v>0000106851</v>
+      </c>
+      <c r="C31" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s" s="46">
+        <v>73</v>
+      </c>
+      <c r="E31" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F31" t="s" s="44">
         <v>74</v>
       </c>
-      <c r="B31" s="45">
-        <v>0000106832</v>
-      </c>
-      <c r="C31" t="s" s="46">
+      <c r="G31" s="51">
+        <v>50</v>
+      </c>
+      <c r="H31" s="52">
+        <v>228.58</v>
+      </c>
+      <c r="I31" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="48">
         <v>75</v>
       </c>
-      <c r="D31" t="s" s="46">
-        <v>76</v>
-      </c>
-      <c r="E31" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F31" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G31" s="51">
-        <v>52</v>
-      </c>
-      <c r="H31" s="52">
-        <v>473.26</v>
-      </c>
-      <c r="I31" s="53">
-        <v>52</v>
-      </c>
-      <c r="J31" t="s" s="48">
-        <v>78</v>
-      </c>
       <c r="K31" t="s" s="49">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="L31" s="0"/>
     </row>
@@ -2418,10 +2405,10 @@
       <c r="E32" s="47"/>
       <c r="F32" s="44"/>
       <c r="G32" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H32" s="52">
-        <v>24609.52</v>
+        <v>11429</v>
       </c>
       <c r="I32" s="53"/>
       <c r="J32" s="48"/>
@@ -2430,34 +2417,34 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="44">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B33" s="45">
-        <v>0000106833</v>
+        <v>0000106799</v>
       </c>
       <c r="C33" t="s" s="46">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s" s="46">
         <v>76</v>
       </c>
       <c r="E33" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s" s="44">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G33" s="51">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="H33" s="52">
-        <v>367.69</v>
+        <v>288.01</v>
       </c>
       <c r="I33" s="53">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="J33" t="s" s="48">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K33" t="s" s="49">
         <v>79</v>
@@ -2470,189 +2457,213 @@
       <c r="C34" s="46"/>
       <c r="D34" s="46"/>
       <c r="E34" s="47"/>
-      <c r="F34" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F34" s="44"/>
       <c r="G34" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H34" s="52">
-        <v>57359.64</v>
-      </c>
-      <c r="I34" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>51841.8</v>
+      </c>
+      <c r="I34" s="53"/>
+      <c r="J34" s="48"/>
       <c r="K34" s="49"/>
       <c r="L34" s="0"/>
     </row>
     <row r="35">
-      <c r="A35" s="44"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="G35" t="s" s="51">
-        <v>27</v>
+      <c r="A35" t="s" s="44">
+        <v>80</v>
+      </c>
+      <c r="B35" s="45">
+        <v>0000106889</v>
+      </c>
+      <c r="C35" t="s" s="46">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s" s="46">
+        <v>76</v>
+      </c>
+      <c r="E35" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F35" t="s" s="44">
+        <v>81</v>
+      </c>
+      <c r="G35" s="51">
+        <v>1</v>
       </c>
       <c r="H35" s="52">
-        <v>165721.78</v>
-      </c>
-      <c r="I35" s="53">
-        <v>295.5</v>
-      </c>
-      <c r="J35" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="K35" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="I35" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s" s="48">
+        <v>82</v>
+      </c>
+      <c r="K35" t="s" s="49">
+        <v>83</v>
+      </c>
       <c r="L35" s="0"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="44">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="B36" s="45">
-        <v>0000106806</v>
+        <v>0000106889</v>
       </c>
       <c r="C36" t="s" s="46">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s" s="46">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s" s="44">
         <v>84</v>
       </c>
       <c r="G36" s="51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H36" s="52">
-        <v>572.10</v>
-      </c>
-      <c r="I36" s="53">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="I36" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J36" t="s" s="48">
         <v>85</v>
       </c>
       <c r="K36" t="s" s="49">
+        <v>83</v>
+      </c>
+      <c r="L36" s="0"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="44">
+        <v>80</v>
+      </c>
+      <c r="B37" s="45">
+        <v>0000106889</v>
+      </c>
+      <c r="C37" t="s" s="46">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s" s="46">
+        <v>76</v>
+      </c>
+      <c r="E37" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F37" t="s" s="44">
         <v>86</v>
       </c>
-      <c r="L36" s="0"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="44"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="44"/>
-      <c r="G37" t="s" s="51">
-        <v>30</v>
+      <c r="G37" s="51">
+        <v>1</v>
       </c>
       <c r="H37" s="52">
-        <v>5721</v>
-      </c>
-      <c r="I37" s="53"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="I37" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J37" t="s" s="48">
+        <v>87</v>
+      </c>
+      <c r="K37" t="s" s="49">
+        <v>83</v>
+      </c>
       <c r="L37" s="0"/>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B38" s="45">
-        <v>0000106807</v>
-      </c>
-      <c r="C38" t="s" s="46">
-        <v>82</v>
-      </c>
-      <c r="D38" t="s" s="46">
-        <v>83</v>
-      </c>
-      <c r="E38" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F38" t="s" s="44">
+      <c r="A38" s="44"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="44"/>
+      <c r="G38" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H38" s="52">
+        <v>0</v>
+      </c>
+      <c r="I38" s="53"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="44">
+        <v>88</v>
+      </c>
+      <c r="B39" s="45">
+        <v>0000106873</v>
+      </c>
+      <c r="C39" t="s" s="46">
         <v>89</v>
       </c>
-      <c r="G38" s="51">
-        <v>48</v>
-      </c>
-      <c r="H38" s="52">
-        <v>319.37</v>
-      </c>
-      <c r="I38" s="53">
+      <c r="D39" t="s" s="46">
+        <v>76</v>
+      </c>
+      <c r="E39" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F39" t="s" s="44">
+        <v>90</v>
+      </c>
+      <c r="G39" s="51">
+        <v>300</v>
+      </c>
+      <c r="H39" s="52">
+        <v>9.47</v>
+      </c>
+      <c r="I39" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s" s="48">
+        <v>91</v>
+      </c>
+      <c r="K39" t="s" s="49">
         <v>72</v>
       </c>
-      <c r="J38" t="s" s="48">
-        <v>90</v>
-      </c>
-      <c r="K38" t="s" s="49">
-        <v>86</v>
-      </c>
-      <c r="L38" s="0"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="44"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="44"/>
-      <c r="G39" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H39" s="52">
-        <v>15329.76</v>
-      </c>
-      <c r="I39" s="53"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="49"/>
       <c r="L39" s="0"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="44">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="B40" s="45">
-        <v>0000106808</v>
+        <v>0000106873</v>
       </c>
       <c r="C40" t="s" s="46">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s" s="46">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E40" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F40" t="s" s="44">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G40" s="51">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="H40" s="52">
-        <v>659.52</v>
-      </c>
-      <c r="I40" s="53">
-        <v>48</v>
+        <v>10.42</v>
+      </c>
+      <c r="I40" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J40" t="s" s="48">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K40" t="s" s="49">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L40" s="0"/>
     </row>
@@ -2664,10 +2675,10 @@
       <c r="E41" s="47"/>
       <c r="F41" s="44"/>
       <c r="G41" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H41" s="52">
-        <v>10552.32</v>
+        <v>8051</v>
       </c>
       <c r="I41" s="53"/>
       <c r="J41" s="48"/>
@@ -2676,145 +2687,181 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="44">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B42" s="45">
-        <v>0000106849</v>
+        <v>0000106731</v>
       </c>
       <c r="C42" t="s" s="46">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D42" t="s" s="46">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F42" t="s" s="44">
+        <v>96</v>
+      </c>
+      <c r="G42" s="51">
+        <v>100</v>
+      </c>
+      <c r="H42" s="52">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J42" t="s" s="48">
+        <v>97</v>
+      </c>
+      <c r="K42" t="s" s="49">
+        <v>98</v>
+      </c>
+      <c r="L42" s="0"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B43" s="45">
+        <v>0000106731</v>
+      </c>
+      <c r="C43" t="s" s="46">
         <v>94</v>
       </c>
-      <c r="G42" s="51">
-        <v>5</v>
-      </c>
-      <c r="H42" s="52">
-        <v>400.69</v>
-      </c>
-      <c r="I42" s="53">
-        <v>6.25</v>
-      </c>
-      <c r="J42" t="s" s="48">
+      <c r="D43" t="s" s="46">
         <v>95</v>
       </c>
-      <c r="K42" t="s" s="49">
-        <v>96</v>
-      </c>
-      <c r="L42" s="0"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="44"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="44"/>
-      <c r="G43" t="s" s="51">
-        <v>30</v>
+      <c r="E43" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F43" t="s" s="44">
+        <v>99</v>
+      </c>
+      <c r="G43" s="51">
+        <v>100</v>
       </c>
       <c r="H43" s="52">
-        <v>2003.45</v>
-      </c>
-      <c r="I43" s="53"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="49"/>
+        <v>225</v>
+      </c>
+      <c r="I43" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J43" t="s" s="48">
+        <v>100</v>
+      </c>
+      <c r="K43" t="s" s="49">
+        <v>98</v>
+      </c>
       <c r="L43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="44">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B44" s="45">
-        <v>0000106798</v>
+        <v>0000106731</v>
       </c>
       <c r="C44" t="s" s="46">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s" s="46">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E44" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F44" t="s" s="44">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G44" s="51">
-        <v>504</v>
+        <v>200</v>
       </c>
       <c r="H44" s="52">
-        <v>22.71</v>
+        <v>0</v>
       </c>
       <c r="I44" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J44" t="s" s="48">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K44" t="s" s="49">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="L44" s="0"/>
     </row>
     <row r="45">
-      <c r="A45" s="44"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="44"/>
-      <c r="G45" t="s" s="51">
-        <v>30</v>
+      <c r="A45" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B45" s="45">
+        <v>0000106731</v>
+      </c>
+      <c r="C45" t="s" s="46">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E45" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F45" t="s" s="44">
+        <v>103</v>
+      </c>
+      <c r="G45" s="51">
+        <v>100</v>
       </c>
       <c r="H45" s="52">
-        <v>11445.84</v>
-      </c>
-      <c r="I45" s="53"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="49"/>
+        <v>100</v>
+      </c>
+      <c r="I45" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J45" t="s" s="48">
+        <v>104</v>
+      </c>
+      <c r="K45" t="s" s="49">
+        <v>98</v>
+      </c>
       <c r="L45" s="0"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="44">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B46" s="45">
-        <v>0000106851</v>
+        <v>0000106731</v>
       </c>
       <c r="C46" t="s" s="46">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s" s="46">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E46" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s" s="44">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G46" s="51">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H46" s="52">
-        <v>228.58</v>
+        <v>495</v>
       </c>
       <c r="I46" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J46" t="s" s="48">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K46" t="s" s="49">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L46" s="0"/>
     </row>
@@ -2826,10 +2873,10 @@
       <c r="E47" s="47"/>
       <c r="F47" s="44"/>
       <c r="G47" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H47" s="52">
-        <v>11429</v>
+        <v>89500</v>
       </c>
       <c r="I47" s="53"/>
       <c r="J47" s="48"/>
@@ -2838,415 +2885,397 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="44">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="B48" s="45">
-        <v>0000106799</v>
+        <v>0000106874</v>
       </c>
       <c r="C48" t="s" s="46">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D48" t="s" s="46">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E48" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F48" t="s" s="44">
+        <v>108</v>
+      </c>
+      <c r="G48" s="51">
+        <v>2</v>
+      </c>
+      <c r="H48" s="52">
+        <v>125.57</v>
+      </c>
+      <c r="I48" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J48" t="s" s="48">
+        <v>109</v>
+      </c>
+      <c r="K48" t="s" s="49">
+        <v>110</v>
+      </c>
+      <c r="L48" s="0"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B49" s="45">
+        <v>0000106874</v>
+      </c>
+      <c r="C49" t="s" s="46">
+        <v>89</v>
+      </c>
+      <c r="D49" t="s" s="46">
         <v>107</v>
       </c>
-      <c r="G48" s="51">
-        <v>180</v>
-      </c>
-      <c r="H48" s="52">
-        <v>288.01</v>
-      </c>
-      <c r="I48" s="53">
-        <v>225</v>
-      </c>
-      <c r="J48" t="s" s="48">
-        <v>108</v>
-      </c>
-      <c r="K48" t="s" s="49">
-        <v>109</v>
-      </c>
-      <c r="L48" s="0"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="44"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="44"/>
-      <c r="G49" t="s" s="51">
-        <v>30</v>
+      <c r="E49" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F49" t="s" s="44">
+        <v>111</v>
+      </c>
+      <c r="G49" s="51">
+        <v>5</v>
       </c>
       <c r="H49" s="52">
-        <v>51841.8</v>
-      </c>
-      <c r="I49" s="53"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="49"/>
+        <v>712.26</v>
+      </c>
+      <c r="I49" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s" s="48">
+        <v>112</v>
+      </c>
+      <c r="K49" t="s" s="49">
+        <v>110</v>
+      </c>
       <c r="L49" s="0"/>
     </row>
     <row r="50">
-      <c r="A50" t="s" s="44">
-        <v>110</v>
-      </c>
-      <c r="B50" s="45">
-        <v>0000106873</v>
-      </c>
-      <c r="C50" t="s" s="46">
-        <v>111</v>
-      </c>
-      <c r="D50" t="s" s="46">
-        <v>106</v>
-      </c>
-      <c r="E50" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F50" t="s" s="44">
-        <v>112</v>
-      </c>
-      <c r="G50" s="51">
-        <v>300</v>
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="44"/>
+      <c r="G50" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H50" s="52">
-        <v>9.47</v>
-      </c>
-      <c r="I50" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J50" t="s" s="48">
-        <v>113</v>
-      </c>
-      <c r="K50" t="s" s="49">
-        <v>102</v>
-      </c>
+        <v>3812.44</v>
+      </c>
+      <c r="I50" s="53"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="49"/>
       <c r="L50" s="0"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="44">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="B51" s="45">
-        <v>0000106873</v>
+        <v>0000106877</v>
       </c>
       <c r="C51" t="s" s="46">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D51" t="s" s="46">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E51" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F51" t="s" s="44">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="G51" s="51">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="H51" s="52">
-        <v>10.42</v>
-      </c>
-      <c r="I51" t="s" s="53">
+        <v>11.79</v>
+      </c>
+      <c r="I51" s="53">
+        <v>10</v>
+      </c>
+      <c r="J51" t="s" s="48">
+        <v>115</v>
+      </c>
+      <c r="K51" t="s" s="49">
+        <v>116</v>
+      </c>
+      <c r="L51" s="0"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="44">
+        <v>67</v>
+      </c>
+      <c r="B52" s="45">
+        <v>0000106877</v>
+      </c>
+      <c r="C52" t="s" s="46">
+        <v>113</v>
+      </c>
+      <c r="D52" t="s" s="46">
+        <v>107</v>
+      </c>
+      <c r="E52" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F52" t="s" s="44">
+        <v>117</v>
+      </c>
+      <c r="G52" s="51">
+        <v>10</v>
+      </c>
+      <c r="H52" s="52">
+        <v>15.33</v>
+      </c>
+      <c r="I52" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J51" t="s" s="48">
-        <v>47</v>
-      </c>
-      <c r="K51" t="s" s="49">
-        <v>102</v>
-      </c>
-      <c r="L51" s="0"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="44"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="44"/>
-      <c r="G52" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H52" s="52">
-        <v>8051</v>
-      </c>
-      <c r="I52" s="53"/>
-      <c r="J52" s="48"/>
-      <c r="K52" s="49"/>
+      <c r="J52" t="s" s="48">
+        <v>118</v>
+      </c>
+      <c r="K52" t="s" s="49">
+        <v>116</v>
+      </c>
       <c r="L52" s="0"/>
     </row>
     <row r="53">
-      <c r="A53" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B53" s="45">
-        <v>0000106731</v>
-      </c>
-      <c r="C53" t="s" s="46">
-        <v>114</v>
-      </c>
-      <c r="D53" t="s" s="46">
-        <v>115</v>
-      </c>
-      <c r="E53" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F53" t="s" s="44">
-        <v>54</v>
-      </c>
-      <c r="G53" s="51">
-        <v>100</v>
+      <c r="A53" s="44"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="44"/>
+      <c r="G53" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H53" s="52">
-        <v>75</v>
-      </c>
-      <c r="I53" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J53" t="s" s="48">
-        <v>55</v>
-      </c>
-      <c r="K53" t="s" s="49">
-        <v>116</v>
-      </c>
+        <v>624.9</v>
+      </c>
+      <c r="I53" s="53"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="49"/>
       <c r="L53" s="0"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B54" s="45">
-        <v>0000106731</v>
+        <v>0000106854</v>
       </c>
       <c r="C54" t="s" s="46">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s" s="46">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E54" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F54" t="s" s="44">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="G54" s="51">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H54" s="52">
-        <v>225</v>
+        <v>923.88</v>
       </c>
       <c r="I54" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J54" t="s" s="48">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="K54" t="s" s="49">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L54" s="0"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B55" s="45">
-        <v>0000106731</v>
+        <v>0000106854</v>
       </c>
       <c r="C55" t="s" s="46">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s" s="46">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E55" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F55" t="s" s="44">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="G55" s="51">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="H55" s="52">
-        <v>0</v>
-      </c>
-      <c r="I55" t="s" s="53">
-        <v>18</v>
+        <v>747.36</v>
+      </c>
+      <c r="I55" s="53">
+        <v>0.5</v>
       </c>
       <c r="J55" t="s" s="48">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="K55" t="s" s="49">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L55" s="0"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B56" s="45">
-        <v>0000106731</v>
+        <v>0000106854</v>
       </c>
       <c r="C56" t="s" s="46">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s" s="46">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E56" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F56" t="s" s="44">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="G56" s="51">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H56" s="52">
-        <v>100</v>
+        <v>126.69</v>
       </c>
       <c r="I56" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J56" t="s" s="48">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K56" t="s" s="49">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="L56" s="0"/>
     </row>
     <row r="57">
-      <c r="A57" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B57" s="45">
-        <v>0000106731</v>
-      </c>
-      <c r="C57" t="s" s="46">
-        <v>114</v>
-      </c>
-      <c r="D57" t="s" s="46">
-        <v>115</v>
-      </c>
-      <c r="E57" t="s" s="47">
+      <c r="A57" s="44"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="44"/>
+      <c r="G57" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H57" s="52">
+        <v>3595.86</v>
+      </c>
+      <c r="I57" s="53"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="0"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="44">
+        <v>30</v>
+      </c>
+      <c r="B58" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C58" t="s" s="46">
+        <v>31</v>
+      </c>
+      <c r="D58" t="s" s="46">
+        <v>120</v>
+      </c>
+      <c r="E58" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F58" t="s" s="44">
+        <v>33</v>
+      </c>
+      <c r="G58" s="51">
+        <v>5</v>
+      </c>
+      <c r="H58" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I58" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J58" t="s" s="48">
         <v>34</v>
       </c>
-      <c r="F57" t="s" s="44">
-        <v>62</v>
-      </c>
-      <c r="G57" s="51">
-        <v>100</v>
-      </c>
-      <c r="H57" s="52">
-        <v>495</v>
-      </c>
-      <c r="I57" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J57" t="s" s="48">
-        <v>63</v>
-      </c>
-      <c r="K57" t="s" s="49">
-        <v>116</v>
-      </c>
-      <c r="L57" s="0"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="44"/>
-      <c r="B58" s="45"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="44"/>
-      <c r="G58" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H58" s="52">
-        <v>89500</v>
-      </c>
-      <c r="I58" s="53"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="49"/>
+      <c r="K58" t="s" s="49">
+        <v>35</v>
+      </c>
       <c r="L58" s="0"/>
     </row>
     <row r="59">
-      <c r="A59" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B59" s="45">
-        <v>0000106874</v>
-      </c>
-      <c r="C59" t="s" s="46">
-        <v>111</v>
-      </c>
-      <c r="D59" t="s" s="46">
-        <v>117</v>
-      </c>
-      <c r="E59" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F59" t="s" s="44">
-        <v>118</v>
-      </c>
-      <c r="G59" s="51">
-        <v>2</v>
+      <c r="A59" s="44"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="44"/>
+      <c r="G59" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H59" s="52">
-        <v>125.57</v>
-      </c>
-      <c r="I59" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J59" t="s" s="48">
-        <v>119</v>
-      </c>
-      <c r="K59" t="s" s="49">
-        <v>120</v>
-      </c>
+        <v>11250</v>
+      </c>
+      <c r="I59" s="53"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="49"/>
       <c r="L59" s="0"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="44">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="B60" s="45">
-        <v>0000106874</v>
+        <v>0000106846</v>
       </c>
       <c r="C60" t="s" s="46">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D60" t="s" s="46">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E60" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F60" t="s" s="44">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G60" s="51">
-        <v>5</v>
+        <v>235</v>
       </c>
       <c r="H60" s="52">
-        <v>712.26</v>
+        <v>255.27</v>
       </c>
       <c r="I60" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J60" t="s" s="48">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K60" t="s" s="49">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="L60" s="0"/>
     </row>
@@ -3258,10 +3287,10 @@
       <c r="E61" s="47"/>
       <c r="F61" s="44"/>
       <c r="G61" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H61" s="52">
-        <v>3812.44</v>
+        <v>59988.45</v>
       </c>
       <c r="I61" s="53"/>
       <c r="J61" s="48"/>
@@ -3270,667 +3299,669 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="44">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="B62" s="45">
-        <v>0000106877</v>
+        <v>0000106821</v>
       </c>
       <c r="C62" t="s" s="46">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D62" t="s" s="46">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E62" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F62" t="s" s="44">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="G62" s="51">
+        <v>16</v>
+      </c>
+      <c r="H62" s="52">
+        <v>652.21</v>
+      </c>
+      <c r="I62" s="53">
+        <v>48</v>
+      </c>
+      <c r="J62" t="s" s="48">
+        <v>62</v>
+      </c>
+      <c r="K62" t="s" s="49">
+        <v>79</v>
+      </c>
+      <c r="L62" s="0"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="44"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="44"/>
+      <c r="G63" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H63" s="52">
+        <v>10435.36</v>
+      </c>
+      <c r="I63" s="53"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="49"/>
+      <c r="L63" s="0"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B64" s="45">
+        <v>0000106822</v>
+      </c>
+      <c r="C64" t="s" s="46">
+        <v>132</v>
+      </c>
+      <c r="D64" t="s" s="46">
+        <v>133</v>
+      </c>
+      <c r="E64" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F64" t="s" s="44">
         <v>40</v>
       </c>
-      <c r="H62" s="52">
-        <v>11.79</v>
-      </c>
-      <c r="I62" s="53">
-        <v>10</v>
-      </c>
-      <c r="J62" t="s" s="48">
-        <v>125</v>
-      </c>
-      <c r="K62" t="s" s="49">
-        <v>126</v>
-      </c>
-      <c r="L62" s="0"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="44">
-        <v>97</v>
-      </c>
-      <c r="B63" s="45">
-        <v>0000106877</v>
-      </c>
-      <c r="C63" t="s" s="46">
-        <v>123</v>
-      </c>
-      <c r="D63" t="s" s="46">
-        <v>117</v>
-      </c>
-      <c r="E63" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F63" t="s" s="44">
-        <v>127</v>
-      </c>
-      <c r="G63" s="51">
-        <v>10</v>
-      </c>
-      <c r="H63" s="52">
-        <v>15.33</v>
-      </c>
-      <c r="I63" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J63" t="s" s="48">
-        <v>128</v>
-      </c>
-      <c r="K63" t="s" s="49">
-        <v>126</v>
-      </c>
-      <c r="L63" s="0"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="44"/>
-      <c r="B64" s="45"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="46"/>
-      <c r="E64" s="47"/>
-      <c r="F64" s="44"/>
-      <c r="G64" t="s" s="51">
-        <v>30</v>
+      <c r="G64" s="51">
+        <v>70</v>
       </c>
       <c r="H64" s="52">
-        <v>624.9</v>
-      </c>
-      <c r="I64" s="53"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="49"/>
+        <v>370.76</v>
+      </c>
+      <c r="I64" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J64" t="s" s="48">
+        <v>41</v>
+      </c>
+      <c r="K64" t="s" s="49">
+        <v>79</v>
+      </c>
       <c r="L64" s="0"/>
     </row>
     <row r="65">
-      <c r="A65" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B65" s="45">
-        <v>0000106854</v>
-      </c>
-      <c r="C65" t="s" s="46">
-        <v>129</v>
-      </c>
-      <c r="D65" t="s" s="46">
-        <v>130</v>
-      </c>
-      <c r="E65" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F65" t="s" s="44">
-        <v>131</v>
-      </c>
-      <c r="G65" s="51">
-        <v>2</v>
+      <c r="A65" s="44"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="44"/>
+      <c r="G65" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H65" s="52">
-        <v>923.88</v>
-      </c>
-      <c r="I65" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J65" t="s" s="48">
-        <v>132</v>
-      </c>
-      <c r="K65" t="s" s="49">
-        <v>133</v>
-      </c>
+        <v>25953.2</v>
+      </c>
+      <c r="I65" s="53"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="49"/>
       <c r="L65" s="0"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B66" s="45">
+        <v>0000106823</v>
+      </c>
+      <c r="C66" t="s" s="46">
+        <v>132</v>
+      </c>
+      <c r="D66" t="s" s="46">
+        <v>133</v>
+      </c>
+      <c r="E66" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F66" t="s" s="44">
+        <v>53</v>
+      </c>
+      <c r="G66" s="51">
+        <v>10</v>
+      </c>
+      <c r="H66" s="52">
+        <v>565.75</v>
+      </c>
+      <c r="I66" s="53">
+        <v>30</v>
+      </c>
+      <c r="J66" t="s" s="48">
+        <v>54</v>
+      </c>
+      <c r="K66" t="s" s="49">
+        <v>48</v>
+      </c>
+      <c r="L66" s="0"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="44"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="44"/>
+      <c r="G67" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H67" s="52">
+        <v>5657.5</v>
+      </c>
+      <c r="I67" s="53"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="49"/>
+      <c r="L67" s="0"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="44">
+        <v>134</v>
+      </c>
+      <c r="B68" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C68" t="s" s="46">
+        <v>135</v>
+      </c>
+      <c r="D68" t="s" s="46">
+        <v>136</v>
+      </c>
+      <c r="E68" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F68" t="s" s="44">
+        <v>137</v>
+      </c>
+      <c r="G68" s="51">
         <v>40</v>
       </c>
-      <c r="B66" s="45">
-        <v>0000106854</v>
-      </c>
-      <c r="C66" t="s" s="46">
-        <v>129</v>
-      </c>
-      <c r="D66" t="s" s="46">
-        <v>130</v>
-      </c>
-      <c r="E66" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F66" t="s" s="44">
-        <v>134</v>
-      </c>
-      <c r="G66" s="51">
-        <v>2</v>
-      </c>
-      <c r="H66" s="52">
-        <v>747.36</v>
-      </c>
-      <c r="I66" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="J66" t="s" s="48">
-        <v>135</v>
-      </c>
-      <c r="K66" t="s" s="49">
-        <v>133</v>
-      </c>
-      <c r="L66" s="0"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B67" s="45">
-        <v>0000106854</v>
-      </c>
-      <c r="C67" t="s" s="46">
-        <v>129</v>
-      </c>
-      <c r="D67" t="s" s="46">
-        <v>130</v>
-      </c>
-      <c r="E67" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F67" t="s" s="44">
-        <v>118</v>
-      </c>
-      <c r="G67" s="51">
-        <v>2</v>
-      </c>
-      <c r="H67" s="52">
-        <v>126.69</v>
-      </c>
-      <c r="I67" t="s" s="53">
+      <c r="H68" s="52">
+        <v>943.26</v>
+      </c>
+      <c r="I68" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J67" t="s" s="48">
-        <v>119</v>
-      </c>
-      <c r="K67" t="s" s="49">
-        <v>133</v>
-      </c>
-      <c r="L67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="44"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="44"/>
-      <c r="G68" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H68" s="52">
-        <v>3595.86</v>
-      </c>
-      <c r="I68" s="53"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="49"/>
+      <c r="J68" t="s" s="48">
+        <v>138</v>
+      </c>
+      <c r="K68" t="s" s="49">
+        <v>20</v>
+      </c>
       <c r="L68" s="0"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="44">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="B69" s="45">
-        <v>0000106778</v>
+        <v>0000106869</v>
       </c>
       <c r="C69" t="s" s="46">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="D69" t="s" s="46">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E69" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F69" t="s" s="44">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="G69" s="51">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H69" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I69" t="s" s="53">
+        <v>275.11</v>
+      </c>
+      <c r="I69" s="53">
+        <v>6.25</v>
+      </c>
+      <c r="J69" t="s" s="48">
+        <v>140</v>
+      </c>
+      <c r="K69" t="s" s="49">
+        <v>20</v>
+      </c>
+      <c r="L69" s="0"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="44">
+        <v>134</v>
+      </c>
+      <c r="B70" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C70" t="s" s="46">
+        <v>135</v>
+      </c>
+      <c r="D70" t="s" s="46">
+        <v>136</v>
+      </c>
+      <c r="E70" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F70" t="s" s="44">
+        <v>141</v>
+      </c>
+      <c r="G70" s="51">
+        <v>15</v>
+      </c>
+      <c r="H70" s="52">
+        <v>361.58</v>
+      </c>
+      <c r="I70" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J69" t="s" s="48">
-        <v>51</v>
-      </c>
-      <c r="K69" t="s" s="49">
-        <v>52</v>
-      </c>
-      <c r="L69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="44"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="44"/>
-      <c r="G70" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H70" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I70" s="53"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="49"/>
+      <c r="J70" t="s" s="48">
+        <v>142</v>
+      </c>
+      <c r="K70" t="s" s="49">
+        <v>20</v>
+      </c>
       <c r="L70" s="0"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="44">
+        <v>134</v>
+      </c>
+      <c r="B71" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C71" t="s" s="46">
+        <v>135</v>
+      </c>
+      <c r="D71" t="s" s="46">
         <v>136</v>
       </c>
-      <c r="B71" s="45">
-        <v>0000106846</v>
-      </c>
-      <c r="C71" t="s" s="46">
-        <v>137</v>
-      </c>
-      <c r="D71" t="s" s="46">
-        <v>138</v>
-      </c>
       <c r="E71" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F71" t="s" s="44">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G71" s="51">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="H71" s="52">
-        <v>255.27</v>
+        <v>275.11</v>
       </c>
       <c r="I71" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J71" t="s" s="48">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K71" t="s" s="49">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="L71" s="0"/>
     </row>
     <row r="72">
-      <c r="A72" s="44"/>
-      <c r="B72" s="45"/>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="47"/>
-      <c r="F72" s="44"/>
-      <c r="G72" t="s" s="51">
-        <v>30</v>
+      <c r="A72" t="s" s="44">
+        <v>134</v>
+      </c>
+      <c r="B72" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C72" t="s" s="46">
+        <v>135</v>
+      </c>
+      <c r="D72" t="s" s="46">
+        <v>136</v>
+      </c>
+      <c r="E72" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F72" t="s" s="44">
+        <v>145</v>
+      </c>
+      <c r="G72" s="51">
+        <v>2</v>
       </c>
       <c r="H72" s="52">
-        <v>59988.45</v>
-      </c>
-      <c r="I72" s="53"/>
-      <c r="J72" s="48"/>
-      <c r="K72" s="49"/>
+        <v>361.58</v>
+      </c>
+      <c r="I72" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s" s="48">
+        <v>146</v>
+      </c>
+      <c r="K72" t="s" s="49">
+        <v>20</v>
+      </c>
       <c r="L72" s="0"/>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B73" s="45">
-        <v>0000106821</v>
-      </c>
-      <c r="C73" t="s" s="46">
-        <v>142</v>
-      </c>
-      <c r="D73" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="E73" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F73" t="s" s="44">
-        <v>91</v>
-      </c>
-      <c r="G73" s="51">
-        <v>16</v>
+      <c r="A73" s="44"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="46"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="44"/>
+      <c r="G73" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H73" s="52">
-        <v>652.21</v>
-      </c>
-      <c r="I73" s="53">
-        <v>48</v>
-      </c>
-      <c r="J73" t="s" s="48">
-        <v>92</v>
-      </c>
-      <c r="K73" t="s" s="49">
-        <v>109</v>
-      </c>
+        <v>72763.81</v>
+      </c>
+      <c r="I73" s="53"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="49"/>
       <c r="L73" s="0"/>
     </row>
     <row r="74">
-      <c r="A74" s="44"/>
-      <c r="B74" s="45"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="47"/>
-      <c r="F74" s="44"/>
-      <c r="G74" t="s" s="51">
-        <v>30</v>
+      <c r="A74" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B74" s="45">
+        <v>0000106815</v>
+      </c>
+      <c r="C74" t="s" s="46">
+        <v>147</v>
+      </c>
+      <c r="D74" t="s" s="46">
+        <v>136</v>
+      </c>
+      <c r="E74" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F74" t="s" s="44">
+        <v>96</v>
+      </c>
+      <c r="G74" s="51">
+        <v>200</v>
       </c>
       <c r="H74" s="52">
-        <v>10435.36</v>
-      </c>
-      <c r="I74" s="53"/>
-      <c r="J74" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I74" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J74" t="s" s="48">
+        <v>97</v>
+      </c>
       <c r="K74" s="49"/>
       <c r="L74" s="0"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="44">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B75" s="45">
-        <v>0000106822</v>
+        <v>0000106815</v>
       </c>
       <c r="C75" t="s" s="46">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D75" t="s" s="46">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E75" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F75" t="s" s="44">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="G75" s="51">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="H75" s="52">
-        <v>370.76</v>
-      </c>
-      <c r="I75" s="53">
-        <v>87.5</v>
+        <v>0</v>
+      </c>
+      <c r="I75" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J75" t="s" s="48">
-        <v>72</v>
-      </c>
-      <c r="K75" t="s" s="49">
-        <v>109</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K75" s="49"/>
       <c r="L75" s="0"/>
     </row>
     <row r="76">
-      <c r="A76" s="44"/>
-      <c r="B76" s="45"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="44"/>
-      <c r="G76" t="s" s="51">
-        <v>30</v>
+      <c r="A76" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B76" s="45">
+        <v>0000106815</v>
+      </c>
+      <c r="C76" t="s" s="46">
+        <v>147</v>
+      </c>
+      <c r="D76" t="s" s="46">
+        <v>136</v>
+      </c>
+      <c r="E76" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F76" t="s" s="44">
+        <v>101</v>
+      </c>
+      <c r="G76" s="51">
+        <v>400</v>
       </c>
       <c r="H76" s="52">
-        <v>25953.2</v>
-      </c>
-      <c r="I76" s="53"/>
-      <c r="J76" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I76" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J76" t="s" s="48">
+        <v>102</v>
+      </c>
       <c r="K76" s="49"/>
       <c r="L76" s="0"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="44">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B77" s="45">
-        <v>0000106823</v>
+        <v>0000106815</v>
       </c>
       <c r="C77" t="s" s="46">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D77" t="s" s="46">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E77" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F77" t="s" s="44">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="G77" s="51">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="H77" s="52">
-        <v>565.75</v>
-      </c>
-      <c r="I77" s="53">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="I77" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J77" t="s" s="48">
-        <v>85</v>
-      </c>
-      <c r="K77" t="s" s="49">
-        <v>79</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="K77" s="49"/>
       <c r="L77" s="0"/>
     </row>
     <row r="78">
-      <c r="A78" s="44"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="46"/>
-      <c r="D78" s="46"/>
-      <c r="E78" s="47"/>
-      <c r="F78" s="44"/>
-      <c r="G78" t="s" s="51">
-        <v>30</v>
+      <c r="A78" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B78" s="45">
+        <v>0000106815</v>
+      </c>
+      <c r="C78" t="s" s="46">
+        <v>147</v>
+      </c>
+      <c r="D78" t="s" s="46">
+        <v>136</v>
+      </c>
+      <c r="E78" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F78" t="s" s="44">
+        <v>105</v>
+      </c>
+      <c r="G78" s="51">
+        <v>200</v>
       </c>
       <c r="H78" s="52">
-        <v>5657.5</v>
-      </c>
-      <c r="I78" s="53"/>
-      <c r="J78" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I78" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J78" t="s" s="48">
+        <v>106</v>
+      </c>
       <c r="K78" s="49"/>
       <c r="L78" s="0"/>
     </row>
     <row r="79">
-      <c r="A79" t="s" s="44">
-        <v>144</v>
-      </c>
-      <c r="B79" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C79" t="s" s="46">
-        <v>145</v>
-      </c>
-      <c r="D79" t="s" s="46">
-        <v>146</v>
-      </c>
-      <c r="E79" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F79" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="G79" s="51">
-        <v>40</v>
+      <c r="A79" s="44"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="47"/>
+      <c r="F79" s="44"/>
+      <c r="G79" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H79" s="52">
-        <v>943.26</v>
-      </c>
-      <c r="I79" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J79" t="s" s="48">
-        <v>148</v>
-      </c>
-      <c r="K79" t="s" s="49">
-        <v>26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I79" s="53"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="49"/>
       <c r="L79" s="0"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="44">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="B80" s="45">
-        <v>0000106869</v>
+        <v>0000106867</v>
       </c>
       <c r="C80" t="s" s="46">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D80" t="s" s="46">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E80" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F80" t="s" s="44">
+        <v>46</v>
+      </c>
+      <c r="G80" s="51">
+        <v>52</v>
+      </c>
+      <c r="H80" s="52">
+        <v>470.12</v>
+      </c>
+      <c r="I80" s="53">
+        <v>52</v>
+      </c>
+      <c r="J80" t="s" s="48">
+        <v>47</v>
+      </c>
+      <c r="K80" t="s" s="49">
         <v>149</v>
       </c>
-      <c r="G80" s="51">
-        <v>25</v>
-      </c>
-      <c r="H80" s="52">
-        <v>275.11</v>
-      </c>
-      <c r="I80" s="53">
-        <v>6.25</v>
-      </c>
-      <c r="J80" t="s" s="48">
-        <v>150</v>
-      </c>
-      <c r="K80" t="s" s="49">
-        <v>26</v>
-      </c>
       <c r="L80" s="0"/>
     </row>
     <row r="81">
-      <c r="A81" t="s" s="44">
-        <v>144</v>
-      </c>
-      <c r="B81" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C81" t="s" s="46">
-        <v>145</v>
-      </c>
-      <c r="D81" t="s" s="46">
-        <v>146</v>
-      </c>
-      <c r="E81" t="s" s="47">
-        <v>34</v>
-      </c>
+      <c r="A81" s="44"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="46"/>
+      <c r="D81" s="46"/>
+      <c r="E81" s="47"/>
       <c r="F81" t="s" s="44">
-        <v>151</v>
-      </c>
-      <c r="G81" s="51">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="G81" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H81" s="52">
-        <v>361.58</v>
-      </c>
-      <c r="I81" t="s" s="53">
+        <v>24446.24</v>
+      </c>
+      <c r="I81" s="53" t="s">
         <v>18</v>
       </c>
       <c r="J81" t="s" s="48">
-        <v>152</v>
-      </c>
-      <c r="K81" t="s" s="49">
-        <v>26</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K81" s="49"/>
       <c r="L81" s="0"/>
     </row>
     <row r="82">
-      <c r="A82" t="s" s="44">
-        <v>144</v>
-      </c>
-      <c r="B82" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C82" t="s" s="46">
-        <v>145</v>
-      </c>
-      <c r="D82" t="s" s="46">
-        <v>146</v>
-      </c>
-      <c r="E82" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F82" t="s" s="44">
-        <v>153</v>
-      </c>
-      <c r="G82" s="51">
-        <v>80</v>
+      <c r="A82" s="44"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="47"/>
+      <c r="F82" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="G82" t="s" s="51">
+        <v>56</v>
       </c>
       <c r="H82" s="52">
-        <v>275.11</v>
-      </c>
-      <c r="I82" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J82" t="s" s="48">
-        <v>154</v>
-      </c>
-      <c r="K82" t="s" s="49">
-        <v>26</v>
-      </c>
+        <v>424401.93</v>
+      </c>
+      <c r="I82" s="53">
+        <v>615.5</v>
+      </c>
+      <c r="J82" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="K82" s="49"/>
       <c r="L82" s="0"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="44">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="B83" s="45">
-        <v>0000106869</v>
+        <v>0000106623</v>
       </c>
       <c r="C83" t="s" s="46">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D83" t="s" s="46">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E83" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F83" t="s" s="44">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G83" s="51">
         <v>2</v>
       </c>
       <c r="H83" s="52">
-        <v>361.58</v>
+        <v>265.45</v>
       </c>
       <c r="I83" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J83" t="s" s="48">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K83" t="s" s="49">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="L83" s="0"/>
     </row>
@@ -3942,10 +3973,10 @@
       <c r="E84" s="47"/>
       <c r="F84" s="44"/>
       <c r="G84" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H84" s="52">
-        <v>72763.81</v>
+        <v>530.9</v>
       </c>
       <c r="I84" s="53"/>
       <c r="J84" s="48"/>
@@ -3954,172 +3985,146 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B85" s="45">
-        <v>0000106815</v>
+        <v>0000106852</v>
       </c>
       <c r="C85" t="s" s="46">
-        <v>157</v>
+        <v>63</v>
       </c>
       <c r="D85" t="s" s="46">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E85" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F85" t="s" s="44">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G85" s="51">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H85" s="52">
-        <v>0</v>
+        <v>228.24</v>
       </c>
       <c r="I85" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J85" t="s" s="48">
-        <v>55</v>
-      </c>
-      <c r="K85" s="49"/>
+        <v>75</v>
+      </c>
+      <c r="K85" t="s" s="49">
+        <v>157</v>
+      </c>
       <c r="L85" s="0"/>
     </row>
     <row r="86">
-      <c r="A86" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B86" s="45">
-        <v>0000106815</v>
-      </c>
-      <c r="C86" t="s" s="46">
-        <v>157</v>
-      </c>
-      <c r="D86" t="s" s="46">
-        <v>146</v>
-      </c>
-      <c r="E86" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F86" t="s" s="44">
-        <v>56</v>
-      </c>
-      <c r="G86" s="51">
-        <v>200</v>
+      <c r="A86" s="44"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="46"/>
+      <c r="D86" s="46"/>
+      <c r="E86" s="47"/>
+      <c r="F86" s="44"/>
+      <c r="G86" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H86" s="52">
-        <v>0</v>
-      </c>
-      <c r="I86" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J86" t="s" s="48">
-        <v>57</v>
-      </c>
+        <v>11412</v>
+      </c>
+      <c r="I86" s="53"/>
+      <c r="J86" s="48"/>
       <c r="K86" s="49"/>
       <c r="L86" s="0"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B87" s="45">
-        <v>0000106815</v>
+        <v>0000106818</v>
       </c>
       <c r="C87" t="s" s="46">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D87" t="s" s="46">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E87" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F87" t="s" s="44">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="G87" s="51">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="H87" s="52">
-        <v>0</v>
-      </c>
-      <c r="I87" t="s" s="53">
-        <v>18</v>
+        <v>214.85</v>
+      </c>
+      <c r="I87" s="53">
+        <v>25</v>
       </c>
       <c r="J87" t="s" s="48">
-        <v>59</v>
-      </c>
-      <c r="K87" s="49"/>
+        <v>160</v>
+      </c>
+      <c r="K87" t="s" s="49">
+        <v>161</v>
+      </c>
       <c r="L87" s="0"/>
     </row>
     <row r="88">
-      <c r="A88" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B88" s="45">
-        <v>0000106815</v>
-      </c>
-      <c r="C88" t="s" s="46">
-        <v>157</v>
-      </c>
-      <c r="D88" t="s" s="46">
-        <v>146</v>
-      </c>
-      <c r="E88" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F88" t="s" s="44">
-        <v>60</v>
-      </c>
-      <c r="G88" s="51">
-        <v>200</v>
+      <c r="A88" s="44"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="46"/>
+      <c r="D88" s="46"/>
+      <c r="E88" s="47"/>
+      <c r="F88" s="44"/>
+      <c r="G88" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H88" s="52">
-        <v>0</v>
-      </c>
-      <c r="I88" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J88" t="s" s="48">
-        <v>61</v>
-      </c>
+        <v>10742.5</v>
+      </c>
+      <c r="I88" s="53"/>
+      <c r="J88" s="48"/>
       <c r="K88" s="49"/>
       <c r="L88" s="0"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="44">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B89" s="45">
-        <v>0000106815</v>
+        <v>0000106825</v>
       </c>
       <c r="C89" t="s" s="46">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s" s="46">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E89" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F89" t="s" s="44">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G89" s="51">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="H89" s="52">
-        <v>0</v>
-      </c>
-      <c r="I89" t="s" s="53">
-        <v>18</v>
+        <v>316.89</v>
+      </c>
+      <c r="I89" s="53">
+        <v>72</v>
       </c>
       <c r="J89" t="s" s="48">
-        <v>63</v>
-      </c>
-      <c r="K89" s="49"/>
+        <v>60</v>
+      </c>
+      <c r="K89" t="s" s="49">
+        <v>161</v>
+      </c>
       <c r="L89" s="0"/>
     </row>
     <row r="90">
@@ -4130,10 +4135,10 @@
       <c r="E90" s="47"/>
       <c r="F90" s="44"/>
       <c r="G90" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H90" s="52">
-        <v>0</v>
+        <v>15210.72</v>
       </c>
       <c r="I90" s="53"/>
       <c r="J90" s="48"/>
@@ -4142,37 +4147,37 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="44">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="B91" s="45">
-        <v>0000106867</v>
+        <v>0000106880</v>
       </c>
       <c r="C91" t="s" s="46">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s" s="46">
         <v>158</v>
       </c>
-      <c r="D91" t="s" s="46">
-        <v>146</v>
-      </c>
       <c r="E91" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F91" t="s" s="44">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="G91" s="51">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H91" s="52">
-        <v>470.12</v>
+        <v>30.72</v>
       </c>
       <c r="I91" s="53">
-        <v>52</v>
+        <v>3.35</v>
       </c>
       <c r="J91" t="s" s="48">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="K91" t="s" s="49">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="L91" s="0"/>
     </row>
@@ -4182,243 +4187,285 @@
       <c r="C92" s="46"/>
       <c r="D92" s="46"/>
       <c r="E92" s="47"/>
-      <c r="F92" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F92" s="44"/>
       <c r="G92" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H92" s="52">
-        <v>24446.24</v>
-      </c>
-      <c r="I92" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J92" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>1536</v>
+      </c>
+      <c r="I92" s="53"/>
+      <c r="J92" s="48"/>
       <c r="K92" s="49"/>
       <c r="L92" s="0"/>
     </row>
     <row r="93">
-      <c r="A93" s="44"/>
-      <c r="B93" s="45"/>
-      <c r="C93" s="46"/>
-      <c r="D93" s="46"/>
-      <c r="E93" s="47"/>
-      <c r="F93" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="G93" t="s" s="51">
+      <c r="A93" t="s" s="44">
+        <v>67</v>
+      </c>
+      <c r="B93" s="45">
+        <v>0000106848</v>
+      </c>
+      <c r="C93" t="s" s="46">
+        <v>165</v>
+      </c>
+      <c r="D93" t="s" s="46">
+        <v>158</v>
+      </c>
+      <c r="E93" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F93" t="s" s="44">
+        <v>77</v>
+      </c>
+      <c r="G93" s="51">
+        <v>180</v>
+      </c>
+      <c r="H93" s="52">
+        <v>287.44</v>
+      </c>
+      <c r="I93" s="53">
+        <v>225</v>
+      </c>
+      <c r="J93" t="s" s="48">
+        <v>78</v>
+      </c>
+      <c r="K93" t="s" s="49">
+        <v>166</v>
+      </c>
+      <c r="L93" s="0"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="44"/>
+      <c r="B94" s="45"/>
+      <c r="C94" s="46"/>
+      <c r="D94" s="46"/>
+      <c r="E94" s="47"/>
+      <c r="F94" s="44"/>
+      <c r="G94" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H93" s="52">
-        <v>424401.93</v>
-      </c>
-      <c r="I93" s="53">
-        <v>615.5</v>
-      </c>
-      <c r="J93" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="K93" s="49"/>
-      <c r="L93" s="0"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B94" s="45">
-        <v>0000106623</v>
-      </c>
-      <c r="C94" t="s" s="46">
-        <v>160</v>
-      </c>
-      <c r="D94" t="s" s="46">
-        <v>161</v>
-      </c>
-      <c r="E94" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F94" t="s" s="44">
-        <v>162</v>
-      </c>
-      <c r="G94" s="51">
-        <v>2</v>
-      </c>
       <c r="H94" s="52">
-        <v>265.45</v>
-      </c>
-      <c r="I94" t="s" s="53">
+        <v>51739.2</v>
+      </c>
+      <c r="I94" s="53"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="49"/>
+      <c r="L94" s="0"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="44">
+        <v>167</v>
+      </c>
+      <c r="B95" s="45">
+        <v>0000106887</v>
+      </c>
+      <c r="C95" t="s" s="46">
+        <v>168</v>
+      </c>
+      <c r="D95" t="s" s="46">
+        <v>169</v>
+      </c>
+      <c r="E95" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F95" t="s" s="44">
+        <v>170</v>
+      </c>
+      <c r="G95" s="51">
+        <v>25</v>
+      </c>
+      <c r="H95" s="52">
+        <v>213.19</v>
+      </c>
+      <c r="I95" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J94" t="s" s="48">
-        <v>163</v>
-      </c>
-      <c r="K94" t="s" s="49">
-        <v>45</v>
-      </c>
-      <c r="L94" s="0"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="44"/>
-      <c r="B95" s="45"/>
-      <c r="C95" s="46"/>
-      <c r="D95" s="46"/>
-      <c r="E95" s="47"/>
-      <c r="F95" s="44"/>
-      <c r="G95" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H95" s="52">
-        <v>530.9</v>
-      </c>
-      <c r="I95" s="53"/>
-      <c r="J95" s="48"/>
-      <c r="K95" s="49"/>
+      <c r="J95" t="s" s="48">
+        <v>75</v>
+      </c>
+      <c r="K95" t="s" s="49">
+        <v>171</v>
+      </c>
       <c r="L95" s="0"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="44">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="B96" s="45">
-        <v>0000106852</v>
+        <v>0000106887</v>
       </c>
       <c r="C96" t="s" s="46">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="D96" t="s" s="46">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E96" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F96" t="s" s="44">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="G96" s="51">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H96" s="52">
-        <v>228.24</v>
+        <v>230.96</v>
       </c>
       <c r="I96" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J96" t="s" s="48">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="K96" t="s" s="49">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="L96" s="0"/>
     </row>
     <row r="97">
-      <c r="A97" s="44"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="46"/>
-      <c r="D97" s="46"/>
-      <c r="E97" s="47"/>
-      <c r="F97" s="44"/>
-      <c r="G97" t="s" s="51">
-        <v>30</v>
+      <c r="A97" t="s" s="44">
+        <v>167</v>
+      </c>
+      <c r="B97" s="45">
+        <v>0000106887</v>
+      </c>
+      <c r="C97" t="s" s="46">
+        <v>168</v>
+      </c>
+      <c r="D97" t="s" s="46">
+        <v>169</v>
+      </c>
+      <c r="E97" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F97" t="s" s="44">
+        <v>174</v>
+      </c>
+      <c r="G97" s="51">
+        <v>14</v>
       </c>
       <c r="H97" s="52">
-        <v>11412</v>
-      </c>
-      <c r="I97" s="53"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="49"/>
+        <v>401.58</v>
+      </c>
+      <c r="I97" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J97" t="s" s="48">
+        <v>175</v>
+      </c>
+      <c r="K97" t="s" s="49">
+        <v>171</v>
+      </c>
       <c r="L97" s="0"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="44">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="B98" s="45">
-        <v>0000106818</v>
+        <v>0000106887</v>
       </c>
       <c r="C98" t="s" s="46">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="D98" t="s" s="46">
+        <v>169</v>
+      </c>
+      <c r="E98" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F98" t="s" s="44">
+        <v>176</v>
+      </c>
+      <c r="G98" s="51">
+        <v>2</v>
+      </c>
+      <c r="H98" s="52">
+        <v>159.24</v>
+      </c>
+      <c r="I98" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J98" t="s" s="48">
+        <v>177</v>
+      </c>
+      <c r="K98" t="s" s="49">
+        <v>171</v>
+      </c>
+      <c r="L98" s="0"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="44">
         <v>167</v>
       </c>
-      <c r="E98" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F98" t="s" s="44">
+      <c r="B99" s="45">
+        <v>0000106887</v>
+      </c>
+      <c r="C99" t="s" s="46">
         <v>168</v>
       </c>
-      <c r="G98" s="51">
-        <v>50</v>
-      </c>
-      <c r="H98" s="52">
-        <v>214.85</v>
-      </c>
-      <c r="I98" s="53">
-        <v>25</v>
-      </c>
-      <c r="J98" t="s" s="48">
+      <c r="D99" t="s" s="46">
         <v>169</v>
       </c>
-      <c r="K98" t="s" s="49">
-        <v>170</v>
-      </c>
-      <c r="L98" s="0"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="44"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="46"/>
-      <c r="D99" s="46"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="44"/>
-      <c r="G99" t="s" s="51">
-        <v>30</v>
+      <c r="E99" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F99" t="s" s="44">
+        <v>178</v>
+      </c>
+      <c r="G99" s="51">
+        <v>15</v>
       </c>
       <c r="H99" s="52">
-        <v>10742.5</v>
-      </c>
-      <c r="I99" s="53"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="49"/>
+        <v>105.76</v>
+      </c>
+      <c r="I99" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J99" t="s" s="48">
+        <v>179</v>
+      </c>
+      <c r="K99" t="s" s="49">
+        <v>171</v>
+      </c>
       <c r="L99" s="0"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="44">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="B100" s="45">
-        <v>0000106825</v>
+        <v>0000106887</v>
       </c>
       <c r="C100" t="s" s="46">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="D100" t="s" s="46">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E100" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F100" t="s" s="44">
-        <v>89</v>
+        <v>180</v>
       </c>
       <c r="G100" s="51">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H100" s="52">
-        <v>316.89</v>
-      </c>
-      <c r="I100" s="53">
-        <v>72</v>
+        <v>310.11</v>
+      </c>
+      <c r="I100" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J100" t="s" s="48">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="K100" t="s" s="49">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L100" s="0"/>
     </row>
@@ -4430,10 +4477,10 @@
       <c r="E101" s="47"/>
       <c r="F101" s="44"/>
       <c r="G101" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H101" s="52">
-        <v>15210.72</v>
+        <v>22972.29</v>
       </c>
       <c r="I101" s="53"/>
       <c r="J101" s="48"/>
@@ -4442,37 +4489,37 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="44">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B102" s="45">
-        <v>0000106880</v>
+        <v>0000106877</v>
       </c>
       <c r="C102" t="s" s="46">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="D102" t="s" s="46">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="E102" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F102" t="s" s="44">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G102" s="51">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="H102" s="52">
-        <v>30.72</v>
+        <v>8.40</v>
       </c>
       <c r="I102" s="53">
-        <v>3.35</v>
+        <v>33</v>
       </c>
       <c r="J102" t="s" s="48">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="K102" t="s" s="49">
-        <v>173</v>
+        <v>116</v>
       </c>
       <c r="L102" s="0"/>
     </row>
@@ -4484,10 +4531,10 @@
       <c r="E103" s="47"/>
       <c r="F103" s="44"/>
       <c r="G103" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H103" s="52">
-        <v>1536</v>
+        <v>8400</v>
       </c>
       <c r="I103" s="53"/>
       <c r="J103" s="48"/>
@@ -4496,37 +4543,37 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="44">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="B104" s="45">
-        <v>0000106848</v>
+        <v>0000106778</v>
       </c>
       <c r="C104" t="s" s="46">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="D104" t="s" s="46">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E104" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F104" t="s" s="44">
+        <v>33</v>
+      </c>
+      <c r="G104" s="51">
+        <v>5</v>
+      </c>
+      <c r="H104" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I104" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J104" t="s" s="48">
         <v>34</v>
       </c>
-      <c r="F104" t="s" s="44">
-        <v>107</v>
-      </c>
-      <c r="G104" s="51">
-        <v>180</v>
-      </c>
-      <c r="H104" s="52">
-        <v>287.44</v>
-      </c>
-      <c r="I104" s="53">
-        <v>225</v>
-      </c>
-      <c r="J104" t="s" s="48">
-        <v>108</v>
-      </c>
       <c r="K104" t="s" s="49">
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="L104" s="0"/>
     </row>
@@ -4538,10 +4585,10 @@
       <c r="E105" s="47"/>
       <c r="F105" s="44"/>
       <c r="G105" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H105" s="52">
-        <v>51739.2</v>
+        <v>11250</v>
       </c>
       <c r="I105" s="53"/>
       <c r="J105" s="48"/>
@@ -4550,37 +4597,37 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="44">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B106" s="45">
-        <v>0000106877</v>
+        <v>0000106884</v>
       </c>
       <c r="C106" t="s" s="46">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="D106" t="s" s="46">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E106" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F106" t="s" s="44">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="G106" s="51">
-        <v>1000</v>
+        <v>504</v>
       </c>
       <c r="H106" s="52">
-        <v>8.40</v>
-      </c>
-      <c r="I106" s="53">
-        <v>33</v>
+        <v>22.10</v>
+      </c>
+      <c r="I106" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J106" t="s" s="48">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="K106" t="s" s="49">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="L106" s="0"/>
     </row>
@@ -4592,10 +4639,10 @@
       <c r="E107" s="47"/>
       <c r="F107" s="44"/>
       <c r="G107" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H107" s="52">
-        <v>8400</v>
+        <v>11138.4</v>
       </c>
       <c r="I107" s="53"/>
       <c r="J107" s="48"/>
@@ -4604,37 +4651,37 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="44">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B108" s="45">
-        <v>0000106778</v>
+        <v>0000106850</v>
       </c>
       <c r="C108" t="s" s="46">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D108" t="s" s="46">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E108" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F108" t="s" s="44">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G108" s="51">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H108" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I108" t="s" s="53">
-        <v>18</v>
+        <v>651.07</v>
+      </c>
+      <c r="I108" s="53">
+        <v>48</v>
       </c>
       <c r="J108" t="s" s="48">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K108" t="s" s="49">
-        <v>52</v>
+        <v>189</v>
       </c>
       <c r="L108" s="0"/>
     </row>
@@ -4646,10 +4693,10 @@
       <c r="E109" s="47"/>
       <c r="F109" s="44"/>
       <c r="G109" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H109" s="52">
-        <v>11250</v>
+        <v>10417.12</v>
       </c>
       <c r="I109" s="53"/>
       <c r="J109" s="48"/>
@@ -4658,37 +4705,37 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="44">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B110" s="45">
-        <v>0000106884</v>
+        <v>0000106876</v>
       </c>
       <c r="C110" t="s" s="46">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D110" t="s" s="46">
+        <v>188</v>
+      </c>
+      <c r="E110" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F110" t="s" s="44">
+        <v>77</v>
+      </c>
+      <c r="G110" s="51">
         <v>180</v>
       </c>
-      <c r="E110" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F110" t="s" s="44">
-        <v>100</v>
-      </c>
-      <c r="G110" s="51">
-        <v>504</v>
-      </c>
       <c r="H110" s="52">
-        <v>22.10</v>
-      </c>
-      <c r="I110" t="s" s="53">
-        <v>18</v>
+        <v>280.45</v>
+      </c>
+      <c r="I110" s="53">
+        <v>225</v>
       </c>
       <c r="J110" t="s" s="48">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="K110" t="s" s="49">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="L110" s="0"/>
     </row>
@@ -4700,10 +4747,10 @@
       <c r="E111" s="47"/>
       <c r="F111" s="44"/>
       <c r="G111" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H111" s="52">
-        <v>11138.4</v>
+        <v>50481</v>
       </c>
       <c r="I111" s="53"/>
       <c r="J111" s="48"/>
@@ -4712,92 +4759,104 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="44">
-        <v>40</v>
+        <v>191</v>
       </c>
       <c r="B112" s="45">
-        <v>0000106850</v>
+        <v>0000106325</v>
       </c>
       <c r="C112" t="s" s="46">
-        <v>93</v>
+        <v>192</v>
       </c>
       <c r="D112" t="s" s="46">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E112" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F112" t="s" s="44">
-        <v>91</v>
+        <v>193</v>
       </c>
       <c r="G112" s="51">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H112" s="52">
-        <v>651.07</v>
-      </c>
-      <c r="I112" s="53">
-        <v>48</v>
+        <v>88.67</v>
+      </c>
+      <c r="I112" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J112" t="s" s="48">
-        <v>92</v>
-      </c>
-      <c r="K112" t="s" s="49">
-        <v>183</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="K112" s="49"/>
       <c r="L112" s="0"/>
     </row>
     <row r="113">
-      <c r="A113" s="44"/>
-      <c r="B113" s="45"/>
-      <c r="C113" s="46"/>
-      <c r="D113" s="46"/>
-      <c r="E113" s="47"/>
-      <c r="F113" s="44"/>
-      <c r="G113" t="s" s="51">
-        <v>30</v>
+      <c r="A113" t="s" s="44">
+        <v>191</v>
+      </c>
+      <c r="B113" s="45">
+        <v>0000106325</v>
+      </c>
+      <c r="C113" t="s" s="46">
+        <v>192</v>
+      </c>
+      <c r="D113" t="s" s="46">
+        <v>188</v>
+      </c>
+      <c r="E113" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F113" t="s" s="44">
+        <v>195</v>
+      </c>
+      <c r="G113" s="51">
+        <v>1</v>
       </c>
       <c r="H113" s="52">
-        <v>10417.12</v>
-      </c>
-      <c r="I113" s="53"/>
-      <c r="J113" s="48"/>
+        <v>507.87</v>
+      </c>
+      <c r="I113" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J113" t="s" s="48">
+        <v>196</v>
+      </c>
       <c r="K113" s="49"/>
       <c r="L113" s="0"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="44">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="B114" s="45">
-        <v>0000106876</v>
+        <v>0000106325</v>
       </c>
       <c r="C114" t="s" s="46">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="D114" t="s" s="46">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E114" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F114" t="s" s="44">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="G114" s="51">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H114" s="52">
-        <v>280.45</v>
-      </c>
-      <c r="I114" s="53">
-        <v>225</v>
+        <v>0</v>
+      </c>
+      <c r="I114" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J114" t="s" s="48">
-        <v>108</v>
-      </c>
-      <c r="K114" t="s" s="49">
-        <v>184</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="K114" s="49"/>
       <c r="L114" s="0"/>
     </row>
     <row r="115">
@@ -4806,142 +4865,136 @@
       <c r="C115" s="46"/>
       <c r="D115" s="46"/>
       <c r="E115" s="47"/>
-      <c r="F115" s="44"/>
+      <c r="F115" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G115" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H115" s="52">
-        <v>50481</v>
-      </c>
-      <c r="I115" s="53"/>
-      <c r="J115" s="48"/>
+        <v>596.54</v>
+      </c>
+      <c r="I115" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K115" s="49"/>
       <c r="L115" s="0"/>
     </row>
     <row r="116">
-      <c r="A116" t="s" s="44">
-        <v>185</v>
-      </c>
-      <c r="B116" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C116" t="s" s="46">
-        <v>186</v>
-      </c>
-      <c r="D116" t="s" s="46">
-        <v>182</v>
-      </c>
-      <c r="E116" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F116" t="s" s="44">
-        <v>187</v>
-      </c>
-      <c r="G116" s="51">
-        <v>1</v>
+      <c r="A116" s="44"/>
+      <c r="B116" s="45"/>
+      <c r="C116" s="46"/>
+      <c r="D116" s="46"/>
+      <c r="E116" s="47"/>
+      <c r="F116" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="G116" t="s" s="51">
+        <v>56</v>
       </c>
       <c r="H116" s="52">
-        <v>88.67</v>
-      </c>
-      <c r="I116" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J116" t="s" s="48">
-        <v>188</v>
+        <v>206426.67</v>
+      </c>
+      <c r="I116" s="53">
+        <v>631.35</v>
+      </c>
+      <c r="J116" s="48" t="s">
+        <v>202</v>
       </c>
       <c r="K116" s="49"/>
       <c r="L116" s="0"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="44">
-        <v>185</v>
+        <v>36</v>
       </c>
       <c r="B117" s="45">
-        <v>0000106325</v>
+        <v>0000106805</v>
       </c>
       <c r="C117" t="s" s="46">
-        <v>186</v>
+        <v>51</v>
       </c>
       <c r="D117" t="s" s="46">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="E117" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F117" t="s" s="44">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G117" s="51">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H117" s="52">
-        <v>507.87</v>
-      </c>
-      <c r="I117" t="s" s="53">
-        <v>18</v>
+        <v>11.24</v>
+      </c>
+      <c r="I117" s="53">
+        <v>3.3</v>
       </c>
       <c r="J117" t="s" s="48">
-        <v>190</v>
-      </c>
-      <c r="K117" s="49"/>
+        <v>184</v>
+      </c>
+      <c r="K117" t="s" s="49">
+        <v>200</v>
+      </c>
       <c r="L117" s="0"/>
     </row>
     <row r="118">
-      <c r="A118" t="s" s="44">
-        <v>185</v>
-      </c>
-      <c r="B118" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C118" t="s" s="46">
-        <v>186</v>
-      </c>
-      <c r="D118" t="s" s="46">
-        <v>182</v>
-      </c>
-      <c r="E118" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F118" t="s" s="44">
-        <v>191</v>
-      </c>
-      <c r="G118" s="51">
-        <v>1</v>
+      <c r="A118" s="44"/>
+      <c r="B118" s="45"/>
+      <c r="C118" s="46"/>
+      <c r="D118" s="46"/>
+      <c r="E118" s="47"/>
+      <c r="F118" s="44"/>
+      <c r="G118" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H118" s="52">
-        <v>0</v>
-      </c>
-      <c r="I118" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J118" t="s" s="48">
-        <v>192</v>
-      </c>
+        <v>1124</v>
+      </c>
+      <c r="I118" s="53"/>
+      <c r="J118" s="48"/>
       <c r="K118" s="49"/>
       <c r="L118" s="0"/>
     </row>
     <row r="119">
-      <c r="A119" s="44"/>
-      <c r="B119" s="45"/>
-      <c r="C119" s="46"/>
-      <c r="D119" s="46"/>
-      <c r="E119" s="47"/>
+      <c r="A119" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B119" s="45">
+        <v>0000106824</v>
+      </c>
+      <c r="C119" t="s" s="46">
+        <v>132</v>
+      </c>
+      <c r="D119" t="s" s="46">
+        <v>199</v>
+      </c>
+      <c r="E119" t="s" s="47">
+        <v>39</v>
+      </c>
       <c r="F119" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G119" t="s" s="51">
-        <v>30</v>
+        <v>59</v>
+      </c>
+      <c r="G119" s="51">
+        <v>48</v>
       </c>
       <c r="H119" s="52">
-        <v>596.54</v>
-      </c>
-      <c r="I119" s="53" t="s">
-        <v>18</v>
+        <v>316.89</v>
+      </c>
+      <c r="I119" s="53">
+        <v>72</v>
       </c>
       <c r="J119" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K119" s="49"/>
+        <v>60</v>
+      </c>
+      <c r="K119" t="s" s="49">
+        <v>200</v>
+      </c>
       <c r="L119" s="0"/>
     </row>
     <row r="120">
@@ -4950,57 +5003,51 @@
       <c r="C120" s="46"/>
       <c r="D120" s="46"/>
       <c r="E120" s="47"/>
-      <c r="F120" s="44" t="s">
-        <v>195</v>
-      </c>
+      <c r="F120" s="44"/>
       <c r="G120" t="s" s="51">
         <v>27</v>
       </c>
       <c r="H120" s="52">
-        <v>183454.38</v>
-      </c>
-      <c r="I120" s="53">
-        <v>631.35</v>
-      </c>
-      <c r="J120" s="48" t="s">
-        <v>196</v>
-      </c>
+        <v>15210.72</v>
+      </c>
+      <c r="I120" s="53"/>
+      <c r="J120" s="48"/>
       <c r="K120" s="49"/>
       <c r="L120" s="0"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B121" s="45">
+        <v>0000106881</v>
+      </c>
+      <c r="C121" t="s" s="46">
+        <v>15</v>
+      </c>
+      <c r="D121" t="s" s="46">
+        <v>199</v>
+      </c>
+      <c r="E121" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F121" t="s" s="44">
         <v>40</v>
       </c>
-      <c r="B121" s="45">
-        <v>0000106805</v>
-      </c>
-      <c r="C121" t="s" s="46">
-        <v>82</v>
-      </c>
-      <c r="D121" t="s" s="46">
-        <v>193</v>
-      </c>
-      <c r="E121" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F121" t="s" s="44">
-        <v>177</v>
-      </c>
       <c r="G121" s="51">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H121" s="52">
-        <v>11.24</v>
+        <v>370.33</v>
       </c>
       <c r="I121" s="53">
-        <v>3.3</v>
+        <v>87.5</v>
       </c>
       <c r="J121" t="s" s="48">
-        <v>178</v>
+        <v>41</v>
       </c>
       <c r="K121" t="s" s="49">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="L121" s="0"/>
     </row>
@@ -5012,10 +5059,10 @@
       <c r="E122" s="47"/>
       <c r="F122" s="44"/>
       <c r="G122" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H122" s="52">
-        <v>1124</v>
+        <v>25923.1</v>
       </c>
       <c r="I122" s="53"/>
       <c r="J122" s="48"/>
@@ -5024,37 +5071,37 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="44">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B123" s="45">
-        <v>0000106824</v>
+        <v>0000106778</v>
       </c>
       <c r="C123" t="s" s="46">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="D123" t="s" s="46">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E123" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F123" t="s" s="44">
+        <v>33</v>
+      </c>
+      <c r="G123" s="51">
+        <v>5</v>
+      </c>
+      <c r="H123" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I123" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J123" t="s" s="48">
         <v>34</v>
       </c>
-      <c r="F123" t="s" s="44">
-        <v>89</v>
-      </c>
-      <c r="G123" s="51">
-        <v>48</v>
-      </c>
-      <c r="H123" s="52">
-        <v>316.89</v>
-      </c>
-      <c r="I123" s="53">
-        <v>72</v>
-      </c>
-      <c r="J123" t="s" s="48">
-        <v>90</v>
-      </c>
       <c r="K123" t="s" s="49">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="L123" s="0"/>
     </row>
@@ -5066,10 +5113,10 @@
       <c r="E124" s="47"/>
       <c r="F124" s="44"/>
       <c r="G124" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H124" s="52">
-        <v>15210.72</v>
+        <v>11250</v>
       </c>
       <c r="I124" s="53"/>
       <c r="J124" s="48"/>
@@ -5078,37 +5125,37 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="44">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B125" s="45">
-        <v>0000106881</v>
+        <v>0000106884</v>
       </c>
       <c r="C125" t="s" s="46">
         <v>23</v>
       </c>
       <c r="D125" t="s" s="46">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E125" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F125" t="s" s="44">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G125" s="51">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="H125" s="52">
-        <v>370.33</v>
+        <v>280.25</v>
       </c>
       <c r="I125" s="53">
-        <v>87.5</v>
+        <v>225</v>
       </c>
       <c r="J125" t="s" s="48">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K125" t="s" s="49">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L125" s="0"/>
     </row>
@@ -5118,130 +5165,136 @@
       <c r="C126" s="46"/>
       <c r="D126" s="46"/>
       <c r="E126" s="47"/>
-      <c r="F126" s="44"/>
+      <c r="F126" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G126" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H126" s="52">
-        <v>25923.1</v>
-      </c>
-      <c r="I126" s="53"/>
-      <c r="J126" s="48"/>
+        <v>50445</v>
+      </c>
+      <c r="I126" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K126" s="49"/>
       <c r="L126" s="0"/>
     </row>
     <row r="127">
-      <c r="A127" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B127" s="45">
+      <c r="A127" s="44"/>
+      <c r="B127" s="45"/>
+      <c r="C127" s="46"/>
+      <c r="D127" s="46"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="G127" t="s" s="51">
+        <v>56</v>
+      </c>
+      <c r="H127" s="52">
+        <v>103952.82</v>
+      </c>
+      <c r="I127" s="53">
+        <v>387.8</v>
+      </c>
+      <c r="J127" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="K127" s="49"/>
+      <c r="L127" s="0"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B128" s="45">
+        <v>0000106882</v>
+      </c>
+      <c r="C128" t="s" s="46">
+        <v>15</v>
+      </c>
+      <c r="D128" t="s" s="46">
+        <v>205</v>
+      </c>
+      <c r="E128" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F128" t="s" s="44">
+        <v>59</v>
+      </c>
+      <c r="G128" s="51">
+        <v>48</v>
+      </c>
+      <c r="H128" s="52">
+        <v>315.46</v>
+      </c>
+      <c r="I128" s="53">
+        <v>72</v>
+      </c>
+      <c r="J128" t="s" s="48">
+        <v>60</v>
+      </c>
+      <c r="K128" t="s" s="49">
+        <v>206</v>
+      </c>
+      <c r="L128" s="0"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="44"/>
+      <c r="B129" s="45"/>
+      <c r="C129" s="46"/>
+      <c r="D129" s="46"/>
+      <c r="E129" s="47"/>
+      <c r="F129" s="44"/>
+      <c r="G129" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H129" s="52">
+        <v>15142.08</v>
+      </c>
+      <c r="I129" s="53"/>
+      <c r="J129" s="48"/>
+      <c r="K129" s="49"/>
+      <c r="L129" s="0"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="44">
+        <v>30</v>
+      </c>
+      <c r="B130" s="45">
         <v>0000106778</v>
       </c>
-      <c r="C127" t="s" s="46">
-        <v>49</v>
-      </c>
-      <c r="D127" t="s" s="46">
-        <v>197</v>
-      </c>
-      <c r="E127" t="s" s="47">
+      <c r="C130" t="s" s="46">
+        <v>31</v>
+      </c>
+      <c r="D130" t="s" s="46">
+        <v>209</v>
+      </c>
+      <c r="E130" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F130" t="s" s="44">
+        <v>33</v>
+      </c>
+      <c r="G130" s="51">
+        <v>5</v>
+      </c>
+      <c r="H130" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I130" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J130" t="s" s="48">
         <v>34</v>
       </c>
-      <c r="F127" t="s" s="44">
-        <v>50</v>
-      </c>
-      <c r="G127" s="51">
-        <v>5</v>
-      </c>
-      <c r="H127" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I127" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J127" t="s" s="48">
-        <v>51</v>
-      </c>
-      <c r="K127" t="s" s="49">
-        <v>52</v>
-      </c>
-      <c r="L127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="44"/>
-      <c r="B128" s="45"/>
-      <c r="C128" s="46"/>
-      <c r="D128" s="46"/>
-      <c r="E128" s="47"/>
-      <c r="F128" s="44"/>
-      <c r="G128" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H128" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I128" s="53"/>
-      <c r="J128" s="48"/>
-      <c r="K128" s="49"/>
-      <c r="L128" s="0"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="44">
-        <v>97</v>
-      </c>
-      <c r="B129" s="45">
-        <v>0000106884</v>
-      </c>
-      <c r="C129" t="s" s="46">
-        <v>33</v>
-      </c>
-      <c r="D129" t="s" s="46">
-        <v>198</v>
-      </c>
-      <c r="E129" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F129" t="s" s="44">
-        <v>107</v>
-      </c>
-      <c r="G129" s="51">
-        <v>180</v>
-      </c>
-      <c r="H129" s="52">
-        <v>280.25</v>
-      </c>
-      <c r="I129" s="53">
-        <v>225</v>
-      </c>
-      <c r="J129" t="s" s="48">
-        <v>108</v>
-      </c>
-      <c r="K129" t="s" s="49">
-        <v>181</v>
-      </c>
-      <c r="L129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="44"/>
-      <c r="B130" s="45"/>
-      <c r="C130" s="46"/>
-      <c r="D130" s="46"/>
-      <c r="E130" s="47"/>
-      <c r="F130" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G130" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H130" s="52">
-        <v>50445</v>
-      </c>
-      <c r="I130" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J130" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K130" s="49"/>
+      <c r="K130" t="s" s="49">
+        <v>35</v>
+      </c>
       <c r="L130" s="0"/>
     </row>
     <row r="131">
@@ -5250,57 +5303,57 @@
       <c r="C131" s="46"/>
       <c r="D131" s="46"/>
       <c r="E131" s="47"/>
-      <c r="F131" s="44" t="s">
-        <v>201</v>
+      <c r="F131" t="s" s="44">
+        <v>211</v>
       </c>
       <c r="G131" t="s" s="51">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H131" s="52">
-        <v>103952.82</v>
+        <v>26392.08</v>
       </c>
       <c r="I131" s="53">
-        <v>387.8</v>
-      </c>
-      <c r="J131" s="48" t="s">
-        <v>202</v>
+        <v>72</v>
+      </c>
+      <c r="J131" t="s" s="48">
+        <v>212</v>
       </c>
       <c r="K131" s="49"/>
       <c r="L131" s="0"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="44">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B132" s="45">
-        <v>0000106882</v>
+        <v>0000106778</v>
       </c>
       <c r="C132" t="s" s="46">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D132" t="s" s="46">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E132" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F132" t="s" s="44">
+        <v>33</v>
+      </c>
+      <c r="G132" s="51">
+        <v>5</v>
+      </c>
+      <c r="H132" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I132" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J132" t="s" s="48">
         <v>34</v>
       </c>
-      <c r="F132" t="s" s="44">
-        <v>89</v>
-      </c>
-      <c r="G132" s="51">
-        <v>48</v>
-      </c>
-      <c r="H132" s="52">
-        <v>315.46</v>
-      </c>
-      <c r="I132" s="53">
-        <v>72</v>
-      </c>
-      <c r="J132" t="s" s="48">
-        <v>90</v>
-      </c>
       <c r="K132" t="s" s="49">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="L132" s="0"/>
     </row>
@@ -5310,36 +5363,42 @@
       <c r="C133" s="46"/>
       <c r="D133" s="46"/>
       <c r="E133" s="47"/>
-      <c r="F133" s="44"/>
+      <c r="F133" t="s" s="44">
+        <v>214</v>
+      </c>
       <c r="G133" t="s" s="51">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H133" s="52">
-        <v>15142.08</v>
-      </c>
-      <c r="I133" s="53"/>
-      <c r="J133" s="48"/>
+        <v>11250</v>
+      </c>
+      <c r="I133" s="53">
+        <v>0</v>
+      </c>
+      <c r="J133" t="s" s="48">
+        <v>215</v>
+      </c>
       <c r="K133" s="49"/>
       <c r="L133" s="0"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="44">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B134" s="45">
         <v>0000106778</v>
       </c>
       <c r="C134" t="s" s="46">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s" s="46">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E134" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F134" t="s" s="44">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G134" s="51">
         <v>5</v>
@@ -5351,10 +5410,10 @@
         <v>18</v>
       </c>
       <c r="J134" t="s" s="48">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="K134" t="s" s="49">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="L134" s="0"/>
     </row>
@@ -5365,41 +5424,41 @@
       <c r="D135" s="46"/>
       <c r="E135" s="47"/>
       <c r="F135" t="s" s="44">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G135" t="s" s="51">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H135" s="52">
-        <v>26392.08</v>
+        <v>11250</v>
       </c>
       <c r="I135" s="53">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J135" t="s" s="48">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="K135" s="49"/>
       <c r="L135" s="0"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="44">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B136" s="45">
         <v>0000106778</v>
       </c>
       <c r="C136" t="s" s="46">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D136" t="s" s="46">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E136" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F136" t="s" s="44">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G136" s="51">
         <v>5</v>
@@ -5411,10 +5470,10 @@
         <v>18</v>
       </c>
       <c r="J136" t="s" s="48">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="K136" t="s" s="49">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="L136" s="0"/>
     </row>
@@ -5425,10 +5484,10 @@
       <c r="D137" s="46"/>
       <c r="E137" s="47"/>
       <c r="F137" t="s" s="44">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G137" t="s" s="51">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="H137" s="52">
         <v>11250</v>
@@ -5437,32 +5496,32 @@
         <v>0</v>
       </c>
       <c r="J137" t="s" s="48">
-        <v>29</v>
+        <v>215</v>
       </c>
       <c r="K137" s="49"/>
       <c r="L137" s="0"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="44">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B138" s="45">
         <v>0000106778</v>
       </c>
       <c r="C138" t="s" s="46">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D138" t="s" s="46">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E138" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F138" t="s" s="44">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G138" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H138" s="52">
         <v>2250</v>
@@ -5471,10 +5530,10 @@
         <v>18</v>
       </c>
       <c r="J138" t="s" s="48">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="K138" t="s" s="49">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="L138" s="0"/>
     </row>
@@ -5485,116 +5544,116 @@
       <c r="D139" s="46"/>
       <c r="E139" s="47"/>
       <c r="F139" t="s" s="44">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="G139" t="s" s="51">
         <v>27</v>
       </c>
       <c r="H139" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I139" s="53">
-        <v>0</v>
+        <v>49500</v>
+      </c>
+      <c r="I139" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J139" t="s" s="48">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K139" s="49"/>
       <c r="L139" s="0"/>
     </row>
     <row r="140">
-      <c r="A140" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B140" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C140" t="s" s="46">
-        <v>49</v>
-      </c>
-      <c r="D140" t="s" s="46">
-        <v>209</v>
-      </c>
-      <c r="E140" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F140" t="s" s="44">
-        <v>50</v>
-      </c>
-      <c r="G140" s="51">
-        <v>5</v>
+      <c r="A140" s="44"/>
+      <c r="B140" s="45"/>
+      <c r="C140" s="46"/>
+      <c r="D140" s="46"/>
+      <c r="E140" s="47"/>
+      <c r="F140" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="G140" t="s" s="51">
+        <v>56</v>
       </c>
       <c r="H140" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I140" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J140" t="s" s="48">
-        <v>51</v>
-      </c>
-      <c r="K140" t="s" s="49">
-        <v>52</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="I140" s="53">
+        <v>0</v>
+      </c>
+      <c r="J140" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="K140" s="49"/>
       <c r="L140" s="0"/>
     </row>
     <row r="141">
-      <c r="A141" s="44"/>
-      <c r="B141" s="45"/>
-      <c r="C141" s="46"/>
-      <c r="D141" s="46"/>
-      <c r="E141" s="47"/>
+      <c r="A141" t="s" s="44">
+        <v>220</v>
+      </c>
+      <c r="B141" s="45">
+        <v>0000106853</v>
+      </c>
+      <c r="C141" t="s" s="46">
+        <v>221</v>
+      </c>
+      <c r="D141" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E141" t="s" s="47">
+        <v>39</v>
+      </c>
       <c r="F141" t="s" s="44">
-        <v>212</v>
-      </c>
-      <c r="G141" t="s" s="51">
-        <v>27</v>
+        <v>183</v>
+      </c>
+      <c r="G141" s="51">
+        <v>500</v>
       </c>
       <c r="H141" s="52">
-        <v>11250</v>
+        <v>11.60</v>
       </c>
       <c r="I141" s="53">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="J141" t="s" s="48">
-        <v>29</v>
-      </c>
-      <c r="K141" s="49"/>
+        <v>184</v>
+      </c>
+      <c r="K141" t="s" s="49">
+        <v>20</v>
+      </c>
       <c r="L141" s="0"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="44">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="B142" s="45">
-        <v>0000106778</v>
+        <v>0000106853</v>
       </c>
       <c r="C142" t="s" s="46">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="D142" t="s" s="46">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E142" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F142" t="s" s="44">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G142" s="51">
-        <v>2</v>
+        <v>800</v>
       </c>
       <c r="H142" s="52">
-        <v>2250</v>
+        <v>10.84</v>
       </c>
       <c r="I142" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J142" t="s" s="48">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="K142" t="s" s="49">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="L142" s="0"/>
     </row>
@@ -5604,118 +5663,102 @@
       <c r="C143" s="46"/>
       <c r="D143" s="46"/>
       <c r="E143" s="47"/>
-      <c r="F143" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F143" s="44"/>
       <c r="G143" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H143" s="52">
-        <v>49500</v>
-      </c>
-      <c r="I143" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J143" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>14472</v>
+      </c>
+      <c r="I143" s="53"/>
+      <c r="J143" s="48"/>
       <c r="K143" s="49"/>
       <c r="L143" s="0"/>
     </row>
     <row r="144">
-      <c r="A144" s="44"/>
-      <c r="B144" s="45"/>
-      <c r="C144" s="46"/>
-      <c r="D144" s="46"/>
-      <c r="E144" s="47"/>
-      <c r="F144" s="44" t="s">
-        <v>215</v>
-      </c>
-      <c r="G144" t="s" s="51">
-        <v>27</v>
+      <c r="A144" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B144" s="45">
+        <v>0000106170</v>
+      </c>
+      <c r="C144" t="s" s="46">
+        <v>224</v>
+      </c>
+      <c r="D144" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E144" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F144" t="s" s="44">
+        <v>59</v>
+      </c>
+      <c r="G144" s="51">
+        <v>48</v>
       </c>
       <c r="H144" s="52">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="I144" s="53">
-        <v>0</v>
-      </c>
-      <c r="J144" s="48" t="s">
-        <v>29</v>
+        <v>72</v>
+      </c>
+      <c r="J144" t="s" s="48">
+        <v>60</v>
       </c>
       <c r="K144" s="49"/>
       <c r="L144" s="0"/>
     </row>
     <row r="145">
-      <c r="A145" t="s" s="44">
-        <v>213</v>
-      </c>
-      <c r="B145" s="45">
-        <v>0000106853</v>
-      </c>
-      <c r="C145" t="s" s="46">
-        <v>15</v>
-      </c>
-      <c r="D145" t="s" s="46">
-        <v>214</v>
-      </c>
-      <c r="E145" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F145" t="s" s="44">
-        <v>177</v>
-      </c>
-      <c r="G145" s="51">
-        <v>500</v>
+      <c r="A145" s="44"/>
+      <c r="B145" s="45"/>
+      <c r="C145" s="46"/>
+      <c r="D145" s="46"/>
+      <c r="E145" s="47"/>
+      <c r="F145" s="44"/>
+      <c r="G145" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H145" s="52">
-        <v>11.60</v>
-      </c>
-      <c r="I145" s="53">
-        <v>16.5</v>
-      </c>
-      <c r="J145" t="s" s="48">
-        <v>178</v>
-      </c>
-      <c r="K145" t="s" s="49">
-        <v>26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I145" s="53"/>
+      <c r="J145" s="48"/>
+      <c r="K145" s="49"/>
       <c r="L145" s="0"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="44">
-        <v>213</v>
+        <v>36</v>
       </c>
       <c r="B146" s="45">
-        <v>0000106853</v>
+        <v>0000106171</v>
       </c>
       <c r="C146" t="s" s="46">
-        <v>15</v>
+        <v>224</v>
       </c>
       <c r="D146" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E146" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F146" t="s" s="44">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G146" s="51">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="H146" s="52">
-        <v>10.84</v>
-      </c>
-      <c r="I146" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I146" s="53">
+        <v>87.5</v>
       </c>
       <c r="J146" t="s" s="48">
-        <v>47</v>
-      </c>
-      <c r="K146" t="s" s="49">
-        <v>26</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K146" s="49"/>
       <c r="L146" s="0"/>
     </row>
     <row r="147">
@@ -5726,10 +5769,10 @@
       <c r="E147" s="47"/>
       <c r="F147" s="44"/>
       <c r="G147" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H147" s="52">
-        <v>14472</v>
+        <v>0</v>
       </c>
       <c r="I147" s="53"/>
       <c r="J147" s="48"/>
@@ -5738,34 +5781,34 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B148" s="45">
+        <v>0000106172</v>
+      </c>
+      <c r="C148" t="s" s="46">
+        <v>224</v>
+      </c>
+      <c r="D148" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E148" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F148" t="s" s="44">
         <v>40</v>
       </c>
-      <c r="B148" s="45">
-        <v>0000106170</v>
-      </c>
-      <c r="C148" t="s" s="46">
-        <v>216</v>
-      </c>
-      <c r="D148" t="s" s="46">
-        <v>214</v>
-      </c>
-      <c r="E148" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F148" t="s" s="44">
-        <v>89</v>
-      </c>
       <c r="G148" s="51">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H148" s="52">
         <v>0</v>
       </c>
       <c r="I148" s="53">
-        <v>72</v>
+        <v>87.5</v>
       </c>
       <c r="J148" t="s" s="48">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="K148" s="49"/>
       <c r="L148" s="0"/>
@@ -5778,7 +5821,7 @@
       <c r="E149" s="47"/>
       <c r="F149" s="44"/>
       <c r="G149" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H149" s="52">
         <v>0</v>
@@ -5790,339 +5833,343 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="44">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B150" s="45">
-        <v>0000106171</v>
+        <v>0000106234</v>
       </c>
       <c r="C150" t="s" s="46">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D150" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E150" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F150" t="s" s="44">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="G150" s="51">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="H150" s="52">
         <v>0</v>
       </c>
-      <c r="I150" s="53">
-        <v>87.5</v>
+      <c r="I150" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J150" t="s" s="48">
-        <v>72</v>
-      </c>
-      <c r="K150" s="49"/>
+        <v>122</v>
+      </c>
+      <c r="K150" t="s" s="49">
+        <v>226</v>
+      </c>
       <c r="L150" s="0"/>
     </row>
     <row r="151">
-      <c r="A151" s="44"/>
-      <c r="B151" s="45"/>
-      <c r="C151" s="46"/>
-      <c r="D151" s="46"/>
-      <c r="E151" s="47"/>
-      <c r="F151" s="44"/>
-      <c r="G151" t="s" s="51">
-        <v>30</v>
+      <c r="A151" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B151" s="45">
+        <v>0000106234</v>
+      </c>
+      <c r="C151" t="s" s="46">
+        <v>225</v>
+      </c>
+      <c r="D151" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E151" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F151" t="s" s="44">
+        <v>227</v>
+      </c>
+      <c r="G151" s="51">
+        <v>5</v>
       </c>
       <c r="H151" s="52">
         <v>0</v>
       </c>
-      <c r="I151" s="53"/>
-      <c r="J151" s="48"/>
-      <c r="K151" s="49"/>
+      <c r="I151" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J151" t="s" s="48">
+        <v>228</v>
+      </c>
+      <c r="K151" t="s" s="49">
+        <v>226</v>
+      </c>
       <c r="L151" s="0"/>
     </row>
     <row r="152">
-      <c r="A152" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B152" s="45">
-        <v>0000106172</v>
-      </c>
-      <c r="C152" t="s" s="46">
-        <v>216</v>
-      </c>
-      <c r="D152" t="s" s="46">
-        <v>214</v>
-      </c>
-      <c r="E152" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F152" t="s" s="44">
-        <v>71</v>
-      </c>
-      <c r="G152" s="51">
-        <v>70</v>
+      <c r="A152" s="44"/>
+      <c r="B152" s="45"/>
+      <c r="C152" s="46"/>
+      <c r="D152" s="46"/>
+      <c r="E152" s="47"/>
+      <c r="F152" s="44"/>
+      <c r="G152" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H152" s="52">
         <v>0</v>
       </c>
-      <c r="I152" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J152" t="s" s="48">
-        <v>72</v>
-      </c>
+      <c r="I152" s="53"/>
+      <c r="J152" s="48"/>
       <c r="K152" s="49"/>
       <c r="L152" s="0"/>
     </row>
     <row r="153">
-      <c r="A153" s="44"/>
-      <c r="B153" s="45"/>
-      <c r="C153" s="46"/>
-      <c r="D153" s="46"/>
-      <c r="E153" s="47"/>
-      <c r="F153" s="44"/>
-      <c r="G153" t="s" s="51">
-        <v>30</v>
+      <c r="A153" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B153" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C153" t="s" s="46">
+        <v>229</v>
+      </c>
+      <c r="D153" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E153" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F153" t="s" s="44">
+        <v>230</v>
+      </c>
+      <c r="G153" s="51">
+        <v>1</v>
       </c>
       <c r="H153" s="52">
-        <v>0</v>
-      </c>
-      <c r="I153" s="53"/>
-      <c r="J153" s="48"/>
-      <c r="K153" s="49"/>
+        <v>2132.20</v>
+      </c>
+      <c r="I153" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J153" t="s" s="48">
+        <v>231</v>
+      </c>
+      <c r="K153" t="s" s="49">
+        <v>232</v>
+      </c>
       <c r="L153" s="0"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="44">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B154" s="45">
-        <v>0000106234</v>
+        <v>0000106644</v>
       </c>
       <c r="C154" t="s" s="46">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D154" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E154" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F154" t="s" s="44">
-        <v>131</v>
+        <v>233</v>
       </c>
       <c r="G154" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H154" s="52">
-        <v>0</v>
+        <v>1359.96</v>
       </c>
       <c r="I154" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J154" t="s" s="48">
-        <v>132</v>
+        <v>234</v>
       </c>
       <c r="K154" t="s" s="49">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="L154" s="0"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="44">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B155" s="45">
-        <v>0000106234</v>
+        <v>0000106644</v>
       </c>
       <c r="C155" t="s" s="46">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D155" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E155" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F155" t="s" s="44">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G155" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H155" s="52">
-        <v>0</v>
+        <v>949.92</v>
       </c>
       <c r="I155" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J155" t="s" s="48">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="K155" t="s" s="49">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="L155" s="0"/>
     </row>
     <row r="156">
-      <c r="A156" s="44"/>
-      <c r="B156" s="45"/>
-      <c r="C156" s="46"/>
-      <c r="D156" s="46"/>
-      <c r="E156" s="47"/>
-      <c r="F156" s="44"/>
-      <c r="G156" t="s" s="51">
-        <v>30</v>
+      <c r="A156" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B156" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C156" t="s" s="46">
+        <v>229</v>
+      </c>
+      <c r="D156" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E156" t="s" s="47">
+        <v>39</v>
+      </c>
+      <c r="F156" t="s" s="44">
+        <v>237</v>
+      </c>
+      <c r="G156" s="51">
+        <v>1</v>
       </c>
       <c r="H156" s="52">
-        <v>0</v>
-      </c>
-      <c r="I156" s="53"/>
-      <c r="J156" s="48"/>
-      <c r="K156" s="49"/>
+        <v>531.68</v>
+      </c>
+      <c r="I156" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J156" t="s" s="48">
+        <v>238</v>
+      </c>
+      <c r="K156" t="s" s="49">
+        <v>232</v>
+      </c>
       <c r="L156" s="0"/>
     </row>
     <row r="157">
-      <c r="A157" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B157" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C157" t="s" s="46">
-        <v>221</v>
-      </c>
-      <c r="D157" t="s" s="46">
-        <v>214</v>
-      </c>
-      <c r="E157" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F157" t="s" s="44">
-        <v>222</v>
-      </c>
-      <c r="G157" s="51">
-        <v>1</v>
+      <c r="A157" s="44"/>
+      <c r="B157" s="45"/>
+      <c r="C157" s="46"/>
+      <c r="D157" s="46"/>
+      <c r="E157" s="47"/>
+      <c r="F157" s="44"/>
+      <c r="G157" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H157" s="52">
-        <v>2132.20</v>
-      </c>
-      <c r="I157" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J157" t="s" s="48">
-        <v>223</v>
-      </c>
-      <c r="K157" t="s" s="49">
-        <v>224</v>
-      </c>
+        <v>4973.76</v>
+      </c>
+      <c r="I157" s="53"/>
+      <c r="J157" s="48"/>
+      <c r="K157" s="49"/>
       <c r="L157" s="0"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="44">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B158" s="45">
-        <v>0000106644</v>
+        <v>0000106745</v>
       </c>
       <c r="C158" t="s" s="46">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="D158" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E158" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F158" t="s" s="44">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="G158" s="51">
         <v>1</v>
       </c>
       <c r="H158" s="52">
-        <v>1359.96</v>
+        <v>905.99</v>
       </c>
       <c r="I158" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J158" t="s" s="48">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="K158" t="s" s="49">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="L158" s="0"/>
     </row>
     <row r="159">
-      <c r="A159" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="B159" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C159" t="s" s="46">
-        <v>221</v>
-      </c>
-      <c r="D159" t="s" s="46">
-        <v>214</v>
-      </c>
-      <c r="E159" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F159" t="s" s="44">
-        <v>227</v>
-      </c>
-      <c r="G159" s="51">
-        <v>1</v>
+      <c r="A159" s="44"/>
+      <c r="B159" s="45"/>
+      <c r="C159" s="46"/>
+      <c r="D159" s="46"/>
+      <c r="E159" s="47"/>
+      <c r="F159" s="44"/>
+      <c r="G159" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H159" s="52">
-        <v>949.92</v>
-      </c>
-      <c r="I159" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J159" t="s" s="48">
-        <v>228</v>
-      </c>
-      <c r="K159" t="s" s="49">
-        <v>224</v>
-      </c>
+        <v>905.99</v>
+      </c>
+      <c r="I159" s="53"/>
+      <c r="J159" s="48"/>
+      <c r="K159" s="49"/>
       <c r="L159" s="0"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="44">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="B160" s="45">
-        <v>0000106644</v>
+        <v>0000106764</v>
       </c>
       <c r="C160" t="s" s="46">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="D160" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E160" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F160" t="s" s="44">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G160" s="51">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H160" s="52">
-        <v>531.68</v>
+        <v>15</v>
       </c>
       <c r="I160" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J160" t="s" s="48">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="K160" t="s" s="49">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="L160" s="0"/>
     </row>
@@ -6134,10 +6181,10 @@
       <c r="E161" s="47"/>
       <c r="F161" s="44"/>
       <c r="G161" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H161" s="52">
-        <v>4973.76</v>
+        <v>360</v>
       </c>
       <c r="I161" s="53"/>
       <c r="J161" s="48"/>
@@ -6146,38 +6193,36 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="44">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B162" s="45">
-        <v>0000106745</v>
+        <v>0000106173</v>
       </c>
       <c r="C162" t="s" s="46">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D162" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E162" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F162" t="s" s="44">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="G162" s="51">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="H162" s="52">
-        <v>905.99</v>
-      </c>
-      <c r="I162" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I162" s="53">
+        <v>225</v>
       </c>
       <c r="J162" t="s" s="48">
-        <v>228</v>
-      </c>
-      <c r="K162" t="s" s="49">
-        <v>232</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="K162" s="49"/>
       <c r="L162" s="0"/>
     </row>
     <row r="163">
@@ -6188,10 +6233,10 @@
       <c r="E163" s="47"/>
       <c r="F163" s="44"/>
       <c r="G163" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H163" s="52">
-        <v>905.99</v>
+        <v>0</v>
       </c>
       <c r="I163" s="53"/>
       <c r="J163" s="48"/>
@@ -6200,38 +6245,36 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="44">
-        <v>233</v>
+        <v>67</v>
       </c>
       <c r="B164" s="45">
-        <v>0000106764</v>
+        <v>0000106174</v>
       </c>
       <c r="C164" t="s" s="46">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="D164" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E164" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F164" t="s" s="44">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="G164" s="51">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="H164" s="52">
-        <v>15</v>
-      </c>
-      <c r="I164" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I164" s="53">
+        <v>225</v>
       </c>
       <c r="J164" t="s" s="48">
-        <v>236</v>
-      </c>
-      <c r="K164" t="s" s="49">
-        <v>237</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="K164" s="49"/>
       <c r="L164" s="0"/>
     </row>
     <row r="165">
@@ -6242,10 +6285,10 @@
       <c r="E165" s="47"/>
       <c r="F165" s="44"/>
       <c r="G165" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H165" s="52">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="I165" s="53"/>
       <c r="J165" s="48"/>
@@ -6254,36 +6297,38 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="44">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="B166" s="45">
-        <v>0000106173</v>
+        <v>0000106235</v>
       </c>
       <c r="C166" t="s" s="46">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D166" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E166" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F166" t="s" s="44">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="G166" s="51">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="H166" s="52">
         <v>0</v>
       </c>
-      <c r="I166" s="53">
-        <v>225</v>
+      <c r="I166" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J166" t="s" s="48">
-        <v>108</v>
-      </c>
-      <c r="K166" s="49"/>
+        <v>248</v>
+      </c>
+      <c r="K166" t="s" s="49">
+        <v>226</v>
+      </c>
       <c r="L166" s="0"/>
     </row>
     <row r="167">
@@ -6294,7 +6339,7 @@
       <c r="E167" s="47"/>
       <c r="F167" s="44"/>
       <c r="G167" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H167" s="52">
         <v>0</v>
@@ -6306,36 +6351,38 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="44">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="B168" s="45">
-        <v>0000106174</v>
+        <v>0000106100</v>
       </c>
       <c r="C168" t="s" s="46">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="D168" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E168" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F168" t="s" s="44">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="G168" s="51">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="H168" s="52">
         <v>0</v>
       </c>
       <c r="I168" s="53">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="J168" t="s" s="48">
-        <v>108</v>
-      </c>
-      <c r="K168" s="49"/>
+        <v>47</v>
+      </c>
+      <c r="K168" t="s" s="49">
+        <v>250</v>
+      </c>
       <c r="L168" s="0"/>
     </row>
     <row r="169">
@@ -6346,7 +6393,7 @@
       <c r="E169" s="47"/>
       <c r="F169" s="44"/>
       <c r="G169" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H169" s="52">
         <v>0</v>
@@ -6358,25 +6405,25 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="44">
-        <v>238</v>
+        <v>43</v>
       </c>
       <c r="B170" s="45">
-        <v>0000106235</v>
+        <v>0000106102</v>
       </c>
       <c r="C170" t="s" s="46">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="D170" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E170" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F170" t="s" s="44">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G170" s="51">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="H170" s="52">
         <v>0</v>
@@ -6385,10 +6432,10 @@
         <v>18</v>
       </c>
       <c r="J170" t="s" s="48">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="K170" t="s" s="49">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="L170" s="0"/>
     </row>
@@ -6400,7 +6447,7 @@
       <c r="E171" s="47"/>
       <c r="F171" s="44"/>
       <c r="G171" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H171" s="52">
         <v>0</v>
@@ -6412,37 +6459,37 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B172" s="45">
-        <v>0000106100</v>
+        <v>0000106103</v>
       </c>
       <c r="C172" t="s" s="46">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D172" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E172" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F172" t="s" s="44">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="G172" s="51">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="H172" s="52">
         <v>0</v>
       </c>
-      <c r="I172" s="53">
-        <v>104</v>
+      <c r="I172" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J172" t="s" s="48">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="K172" t="s" s="49">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="L172" s="0"/>
     </row>
@@ -6454,7 +6501,7 @@
       <c r="E173" s="47"/>
       <c r="F173" s="44"/>
       <c r="G173" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H173" s="52">
         <v>0</v>
@@ -6466,22 +6513,22 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B174" s="45">
-        <v>0000106102</v>
+        <v>0000106104</v>
       </c>
       <c r="C174" t="s" s="46">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D174" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E174" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F174" t="s" s="44">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="G174" s="51">
         <v>52</v>
@@ -6493,10 +6540,10 @@
         <v>18</v>
       </c>
       <c r="J174" t="s" s="48">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="K174" t="s" s="49">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="L174" s="0"/>
     </row>
@@ -6508,7 +6555,7 @@
       <c r="E175" s="47"/>
       <c r="F175" s="44"/>
       <c r="G175" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H175" s="52">
         <v>0</v>
@@ -6520,37 +6567,37 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B176" s="45">
-        <v>0000106103</v>
+        <v>0000106132</v>
       </c>
       <c r="C176" t="s" s="46">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D176" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E176" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F176" t="s" s="44">
-        <v>245</v>
+        <v>49</v>
       </c>
       <c r="G176" s="51">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="H176" s="52">
         <v>0</v>
       </c>
-      <c r="I176" t="s" s="53">
-        <v>18</v>
+      <c r="I176" s="53">
+        <v>208</v>
       </c>
       <c r="J176" t="s" s="48">
-        <v>246</v>
+        <v>50</v>
       </c>
       <c r="K176" t="s" s="49">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="L176" s="0"/>
     </row>
@@ -6562,7 +6609,7 @@
       <c r="E177" s="47"/>
       <c r="F177" s="44"/>
       <c r="G177" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H177" s="52">
         <v>0</v>
@@ -6574,38 +6621,36 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B178" s="45">
-        <v>0000106104</v>
+        <v>0000106175</v>
       </c>
       <c r="C178" t="s" s="46">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="D178" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E178" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F178" t="s" s="44">
-        <v>247</v>
+        <v>49</v>
       </c>
       <c r="G178" s="51">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="H178" s="52">
-        <v>0</v>
-      </c>
-      <c r="I178" t="s" s="53">
-        <v>18</v>
+        <v>332.67</v>
+      </c>
+      <c r="I178" s="53">
+        <v>208</v>
       </c>
       <c r="J178" t="s" s="48">
-        <v>248</v>
-      </c>
-      <c r="K178" t="s" s="49">
-        <v>242</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="K178" s="49"/>
       <c r="L178" s="0"/>
     </row>
     <row r="179">
@@ -6616,10 +6661,10 @@
       <c r="E179" s="47"/>
       <c r="F179" s="44"/>
       <c r="G179" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H179" s="52">
-        <v>0</v>
+        <v>69195.36</v>
       </c>
       <c r="I179" s="53"/>
       <c r="J179" s="48"/>
@@ -6628,38 +6673,36 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B180" s="45">
-        <v>0000106132</v>
+        <v>0000106176</v>
       </c>
       <c r="C180" t="s" s="46">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D180" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E180" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F180" t="s" s="44">
-        <v>80</v>
+        <v>255</v>
       </c>
       <c r="G180" s="51">
-        <v>208</v>
+        <v>52</v>
       </c>
       <c r="H180" s="52">
-        <v>0</v>
-      </c>
-      <c r="I180" s="53">
-        <v>208</v>
+        <v>509.41</v>
+      </c>
+      <c r="I180" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J180" t="s" s="48">
-        <v>81</v>
-      </c>
-      <c r="K180" t="s" s="49">
-        <v>242</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="K180" s="49"/>
       <c r="L180" s="0"/>
     </row>
     <row r="181">
@@ -6670,10 +6713,10 @@
       <c r="E181" s="47"/>
       <c r="F181" s="44"/>
       <c r="G181" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H181" s="52">
-        <v>0</v>
+        <v>26489.32</v>
       </c>
       <c r="I181" s="53"/>
       <c r="J181" s="48"/>
@@ -6682,34 +6725,34 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B182" s="45">
-        <v>0000106175</v>
+        <v>0000106177</v>
       </c>
       <c r="C182" t="s" s="46">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D182" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E182" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F182" t="s" s="44">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="G182" s="51">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="H182" s="52">
-        <v>332.67</v>
+        <v>471.46</v>
       </c>
       <c r="I182" s="53">
-        <v>208</v>
+        <v>104</v>
       </c>
       <c r="J182" t="s" s="48">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="K182" s="49"/>
       <c r="L182" s="0"/>
@@ -6722,10 +6765,10 @@
       <c r="E183" s="47"/>
       <c r="F183" s="44"/>
       <c r="G183" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H183" s="52">
-        <v>69195.36</v>
+        <v>49031.84</v>
       </c>
       <c r="I183" s="53"/>
       <c r="J183" s="48"/>
@@ -6734,34 +6777,34 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B184" s="45">
-        <v>0000106176</v>
+        <v>0000106178</v>
       </c>
       <c r="C184" t="s" s="46">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D184" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E184" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F184" t="s" s="44">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="G184" s="51">
         <v>52</v>
       </c>
       <c r="H184" s="52">
-        <v>509.41</v>
+        <v>489.76</v>
       </c>
       <c r="I184" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J184" t="s" s="48">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="K184" s="49"/>
       <c r="L184" s="0"/>
@@ -6774,10 +6817,10 @@
       <c r="E185" s="47"/>
       <c r="F185" s="44"/>
       <c r="G185" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H185" s="52">
-        <v>26489.32</v>
+        <v>25467.52</v>
       </c>
       <c r="I185" s="53"/>
       <c r="J185" s="48"/>
@@ -6786,34 +6829,34 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B186" s="45">
-        <v>0000106177</v>
+        <v>0000106179</v>
       </c>
       <c r="C186" t="s" s="46">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D186" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E186" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F186" t="s" s="44">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="G186" s="51">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="H186" s="52">
-        <v>471.46</v>
-      </c>
-      <c r="I186" s="53">
-        <v>104</v>
+        <v>458.18</v>
+      </c>
+      <c r="I186" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J186" t="s" s="48">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="K186" s="49"/>
       <c r="L186" s="0"/>
@@ -6826,10 +6869,10 @@
       <c r="E187" s="47"/>
       <c r="F187" s="44"/>
       <c r="G187" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H187" s="52">
-        <v>49031.84</v>
+        <v>23825.36</v>
       </c>
       <c r="I187" s="53"/>
       <c r="J187" s="48"/>
@@ -6838,34 +6881,34 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="44">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B188" s="45">
-        <v>0000106178</v>
+        <v>0000106180</v>
       </c>
       <c r="C188" t="s" s="46">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D188" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E188" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F188" t="s" s="44">
-        <v>245</v>
+        <v>46</v>
       </c>
       <c r="G188" s="51">
         <v>52</v>
       </c>
       <c r="H188" s="52">
-        <v>489.76</v>
-      </c>
-      <c r="I188" t="s" s="53">
-        <v>18</v>
+        <v>471.46</v>
+      </c>
+      <c r="I188" s="53">
+        <v>52</v>
       </c>
       <c r="J188" t="s" s="48">
-        <v>246</v>
+        <v>47</v>
       </c>
       <c r="K188" s="49"/>
       <c r="L188" s="0"/>
@@ -6878,10 +6921,10 @@
       <c r="E189" s="47"/>
       <c r="F189" s="44"/>
       <c r="G189" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H189" s="52">
-        <v>25467.52</v>
+        <v>24515.92</v>
       </c>
       <c r="I189" s="53"/>
       <c r="J189" s="48"/>
@@ -6890,34 +6933,34 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="44">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="B190" s="45">
-        <v>0000106179</v>
+        <v>0000106883</v>
       </c>
       <c r="C190" t="s" s="46">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D190" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E190" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F190" t="s" s="44">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="G190" s="51">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H190" s="52">
-        <v>458.18</v>
+        <v>2052.84</v>
       </c>
       <c r="I190" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J190" t="s" s="48">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="K190" s="49"/>
       <c r="L190" s="0"/>
@@ -6930,10 +6973,10 @@
       <c r="E191" s="47"/>
       <c r="F191" s="44"/>
       <c r="G191" t="s" s="51">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H191" s="52">
-        <v>23825.36</v>
+        <v>73902.24</v>
       </c>
       <c r="I191" s="53"/>
       <c r="J191" s="48"/>
@@ -6942,34 +6985,34 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="44">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="B192" s="45">
-        <v>0000106180</v>
+        <v>0000106883</v>
       </c>
       <c r="C192" t="s" s="46">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D192" t="s" s="46">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E192" t="s" s="47">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F192" t="s" s="44">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="G192" s="51">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="H192" s="52">
-        <v>471.46</v>
-      </c>
-      <c r="I192" s="53">
-        <v>52</v>
+        <v>1059.81</v>
+      </c>
+      <c r="I192" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J192" t="s" s="48">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="K192" s="49"/>
       <c r="L192" s="0"/>
@@ -6981,150 +7024,98 @@
       <c r="D193" s="46"/>
       <c r="E193" s="47"/>
       <c r="F193" s="44"/>
-      <c r="G193" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H193" s="52">
-        <v>24515.92</v>
-      </c>
+      <c r="G193" s="51"/>
+      <c r="H193" s="52"/>
       <c r="I193" s="53"/>
       <c r="J193" s="48"/>
       <c r="K193" s="49"/>
       <c r="L193" s="0"/>
     </row>
     <row r="194">
-      <c r="A194" t="s" s="44">
-        <v>31</v>
-      </c>
-      <c r="B194" s="45">
-        <v>0000106883</v>
-      </c>
-      <c r="C194" t="s" s="46">
-        <v>252</v>
-      </c>
-      <c r="D194" t="s" s="46">
-        <v>214</v>
-      </c>
-      <c r="E194" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F194" t="s" s="44">
-        <v>253</v>
-      </c>
-      <c r="G194" s="51">
-        <v>36</v>
+      <c r="A194" s="44"/>
+      <c r="B194" s="45"/>
+      <c r="C194" s="46"/>
+      <c r="D194" s="46"/>
+      <c r="E194" s="47"/>
+      <c r="F194" s="44"/>
+      <c r="G194" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H194" s="52">
-        <v>2052.84</v>
-      </c>
-      <c r="I194" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J194" t="s" s="48">
-        <v>254</v>
-      </c>
+        <v>1275106.09</v>
+      </c>
+      <c r="I194" s="53">
+        <v>2002.15</v>
+      </c>
+      <c r="J194" s="48"/>
       <c r="K194" s="49"/>
       <c r="L194" s="0"/>
     </row>
-    <row r="195">
+    <row r="195" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A195" s="44"/>
       <c r="B195" s="45"/>
       <c r="C195" s="46"/>
       <c r="D195" s="46"/>
       <c r="E195" s="47"/>
       <c r="F195" s="44"/>
-      <c r="G195" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H195" s="52">
-        <v>73902.24</v>
-      </c>
+      <c r="G195" s="51"/>
+      <c r="H195" s="52"/>
       <c r="I195" s="53"/>
       <c r="J195" s="48"/>
       <c r="K195" s="49"/>
       <c r="L195" s="0"/>
     </row>
-    <row r="196">
-      <c r="A196" t="s" s="44">
-        <v>31</v>
-      </c>
-      <c r="B196" s="45">
-        <v>0000106883</v>
-      </c>
-      <c r="C196" t="s" s="46">
-        <v>252</v>
-      </c>
-      <c r="D196" t="s" s="46">
-        <v>214</v>
-      </c>
-      <c r="E196" t="s" s="47">
-        <v>34</v>
-      </c>
-      <c r="F196" t="s" s="44">
-        <v>38</v>
-      </c>
-      <c r="G196" s="51">
-        <v>23</v>
-      </c>
-      <c r="H196" s="52">
-        <v>1059.81</v>
-      </c>
-      <c r="I196" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J196" t="s" s="48">
-        <v>39</v>
-      </c>
-      <c r="K196" s="49"/>
-      <c r="L196" s="0"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="44"/>
-      <c r="B197" s="45"/>
-      <c r="C197" s="46"/>
-      <c r="D197" s="46"/>
-      <c r="E197" s="47"/>
-      <c r="F197" s="44"/>
-      <c r="G197" s="51"/>
-      <c r="H197" s="52"/>
-      <c r="I197" s="53"/>
-      <c r="J197" s="48"/>
-      <c r="K197" s="49"/>
-      <c r="L197" s="0"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="44"/>
-      <c r="B198" s="45"/>
-      <c r="C198" s="46"/>
-      <c r="D198" s="46"/>
-      <c r="E198" s="47"/>
-      <c r="F198" s="44"/>
-      <c r="G198" t="s" s="51">
-        <v>30</v>
-      </c>
-      <c r="H198" s="52">
-        <v>1260042.3</v>
-      </c>
-      <c r="I198" s="53">
-        <v>2002.15</v>
-      </c>
-      <c r="J198" s="48"/>
-      <c r="K198" s="49"/>
-      <c r="L198" s="0"/>
+    <row r="196" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="5"/>
+      <c r="B196" s="25"/>
+      <c r="C196" s="19"/>
+      <c r="D196" s="19"/>
+      <c r="E196" s="13"/>
+      <c r="F196" s="5"/>
+      <c r="G196" s="25"/>
+      <c r="H196" s="25"/>
+      <c r="I196" s="25"/>
+      <c r="J196" s="36"/>
+      <c r="K196" s="29"/>
+    </row>
+    <row r="197" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="5"/>
+      <c r="B197" s="25"/>
+      <c r="C197" s="19"/>
+      <c r="D197" s="19"/>
+      <c r="E197" s="13"/>
+      <c r="F197" s="5"/>
+      <c r="G197" s="25"/>
+      <c r="H197" s="25"/>
+      <c r="I197" s="25"/>
+      <c r="J197" s="36"/>
+      <c r="K197" s="29"/>
+    </row>
+    <row r="198" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="5"/>
+      <c r="B198" s="25"/>
+      <c r="C198" s="19"/>
+      <c r="D198" s="19"/>
+      <c r="E198" s="13"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="25"/>
+      <c r="H198" s="25"/>
+      <c r="I198" s="25"/>
+      <c r="J198" s="36"/>
+      <c r="K198" s="29"/>
     </row>
     <row r="199" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="44"/>
-      <c r="B199" s="45"/>
-      <c r="C199" s="46"/>
-      <c r="D199" s="46"/>
-      <c r="E199" s="47"/>
-      <c r="F199" s="44"/>
-      <c r="G199" s="51"/>
-      <c r="H199" s="52"/>
-      <c r="I199" s="53"/>
-      <c r="J199" s="48"/>
-      <c r="K199" s="49"/>
-      <c r="L199" s="0"/>
+      <c r="A199" s="5"/>
+      <c r="B199" s="25"/>
+      <c r="C199" s="19"/>
+      <c r="D199" s="19"/>
+      <c r="E199" s="13"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="25"/>
+      <c r="H199" s="25"/>
+      <c r="I199" s="25"/>
+      <c r="J199" s="36"/>
+      <c r="K199" s="29"/>
     </row>
     <row r="200" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A200" s="5"/>
@@ -7334,7 +7325,7 @@
       <c r="J215" s="36"/>
       <c r="K215" s="29"/>
     </row>
-    <row r="216" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="216" x14ac:dyDescent="0.2">
       <c r="A216" s="5"/>
       <c r="B216" s="25"/>
       <c r="C216" s="19"/>
@@ -7347,7 +7338,7 @@
       <c r="J216" s="36"/>
       <c r="K216" s="29"/>
     </row>
-    <row r="217" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="217" x14ac:dyDescent="0.2">
       <c r="A217" s="5"/>
       <c r="B217" s="25"/>
       <c r="C217" s="19"/>
@@ -7360,7 +7351,7 @@
       <c r="J217" s="36"/>
       <c r="K217" s="29"/>
     </row>
-    <row r="218" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="218" x14ac:dyDescent="0.2">
       <c r="A218" s="5"/>
       <c r="B218" s="25"/>
       <c r="C218" s="19"/>
@@ -7373,7 +7364,7 @@
       <c r="J218" s="36"/>
       <c r="K218" s="29"/>
     </row>
-    <row r="219" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="219" x14ac:dyDescent="0.2">
       <c r="A219" s="5"/>
       <c r="B219" s="25"/>
       <c r="C219" s="19"/>
@@ -7660,56 +7651,56 @@
       <c r="K240" s="29"/>
     </row>
     <row r="241" x14ac:dyDescent="0.2">
-      <c r="A241" s="5"/>
-      <c r="B241" s="25"/>
-      <c r="C241" s="19"/>
-      <c r="D241" s="19"/>
-      <c r="E241" s="13"/>
-      <c r="F241" s="5"/>
+      <c r="A241" s="6"/>
+      <c r="B241" s="33"/>
+      <c r="C241" s="20"/>
+      <c r="D241" s="20"/>
+      <c r="E241" s="14"/>
+      <c r="F241" s="6"/>
       <c r="G241" s="25"/>
       <c r="H241" s="25"/>
       <c r="I241" s="25"/>
       <c r="J241" s="36"/>
-      <c r="K241" s="29"/>
+      <c r="K241" s="30"/>
     </row>
     <row r="242" x14ac:dyDescent="0.2">
-      <c r="A242" s="5"/>
-      <c r="B242" s="25"/>
-      <c r="C242" s="19"/>
-      <c r="D242" s="19"/>
-      <c r="E242" s="13"/>
-      <c r="F242" s="5"/>
+      <c r="A242" s="6"/>
+      <c r="B242" s="33"/>
+      <c r="C242" s="20"/>
+      <c r="D242" s="20"/>
+      <c r="E242" s="14"/>
+      <c r="F242" s="6"/>
       <c r="G242" s="25"/>
       <c r="H242" s="25"/>
       <c r="I242" s="25"/>
       <c r="J242" s="36"/>
-      <c r="K242" s="29"/>
+      <c r="K242" s="30"/>
     </row>
     <row r="243" x14ac:dyDescent="0.2">
-      <c r="A243" s="5"/>
-      <c r="B243" s="25"/>
-      <c r="C243" s="19"/>
-      <c r="D243" s="19"/>
-      <c r="E243" s="13"/>
-      <c r="F243" s="5"/>
+      <c r="A243" s="6"/>
+      <c r="B243" s="33"/>
+      <c r="C243" s="20"/>
+      <c r="D243" s="20"/>
+      <c r="E243" s="14"/>
+      <c r="F243" s="6"/>
       <c r="G243" s="25"/>
       <c r="H243" s="25"/>
       <c r="I243" s="25"/>
       <c r="J243" s="36"/>
-      <c r="K243" s="29"/>
+      <c r="K243" s="30"/>
     </row>
     <row r="244" x14ac:dyDescent="0.2">
-      <c r="A244" s="5"/>
-      <c r="B244" s="25"/>
-      <c r="C244" s="19"/>
-      <c r="D244" s="19"/>
-      <c r="E244" s="13"/>
-      <c r="F244" s="5"/>
+      <c r="A244" s="6"/>
+      <c r="B244" s="33"/>
+      <c r="C244" s="20"/>
+      <c r="D244" s="20"/>
+      <c r="E244" s="14"/>
+      <c r="F244" s="6"/>
       <c r="G244" s="25"/>
       <c r="H244" s="25"/>
       <c r="I244" s="25"/>
       <c r="J244" s="36"/>
-      <c r="K244" s="29"/>
+      <c r="K244" s="30"/>
     </row>
     <row r="245" x14ac:dyDescent="0.2">
       <c r="A245" s="6"/>
@@ -16162,7 +16153,7 @@
       <c r="K894" s="30"/>
     </row>
     <row r="895" x14ac:dyDescent="0.2">
-      <c r="A895" s="6"/>
+      <c r="A895" s="8"/>
       <c r="B895" s="33"/>
       <c r="C895" s="20"/>
       <c r="D895" s="20"/>
@@ -16175,7 +16166,7 @@
       <c r="K895" s="30"/>
     </row>
     <row r="896" x14ac:dyDescent="0.2">
-      <c r="A896" s="6"/>
+      <c r="A896" s="8"/>
       <c r="B896" s="33"/>
       <c r="C896" s="20"/>
       <c r="D896" s="20"/>
@@ -16188,7 +16179,7 @@
       <c r="K896" s="30"/>
     </row>
     <row r="897" x14ac:dyDescent="0.2">
-      <c r="A897" s="6"/>
+      <c r="A897" s="8"/>
       <c r="B897" s="33"/>
       <c r="C897" s="20"/>
       <c r="D897" s="20"/>
@@ -16201,7 +16192,7 @@
       <c r="K897" s="30"/>
     </row>
     <row r="898" x14ac:dyDescent="0.2">
-      <c r="A898" s="6"/>
+      <c r="A898" s="8"/>
       <c r="B898" s="33"/>
       <c r="C898" s="20"/>
       <c r="D898" s="20"/>
@@ -18046,57 +18037,33 @@
       <c r="J1039" s="36"/>
       <c r="K1039" s="30"/>
     </row>
-    <row r="1040" x14ac:dyDescent="0.2">
-      <c r="A1040" s="8"/>
-      <c r="B1040" s="33"/>
-      <c r="C1040" s="20"/>
-      <c r="D1040" s="20"/>
-      <c r="E1040" s="14"/>
-      <c r="F1040" s="6"/>
-      <c r="G1040" s="25"/>
-      <c r="H1040" s="25"/>
-      <c r="I1040" s="25"/>
-      <c r="J1040" s="36"/>
-      <c r="K1040" s="30"/>
-    </row>
-    <row r="1041" x14ac:dyDescent="0.2">
-      <c r="A1041" s="8"/>
-      <c r="B1041" s="33"/>
-      <c r="C1041" s="20"/>
-      <c r="D1041" s="20"/>
-      <c r="E1041" s="14"/>
-      <c r="F1041" s="6"/>
-      <c r="G1041" s="25"/>
-      <c r="H1041" s="25"/>
-      <c r="I1041" s="25"/>
-      <c r="J1041" s="36"/>
-      <c r="K1041" s="30"/>
-    </row>
-    <row r="1042" x14ac:dyDescent="0.2">
-      <c r="A1042" s="8"/>
-      <c r="B1042" s="33"/>
-      <c r="C1042" s="20"/>
-      <c r="D1042" s="20"/>
-      <c r="E1042" s="14"/>
-      <c r="F1042" s="6"/>
-      <c r="G1042" s="25"/>
-      <c r="H1042" s="25"/>
-      <c r="I1042" s="25"/>
-      <c r="J1042" s="36"/>
-      <c r="K1042" s="30"/>
-    </row>
-    <row r="1043" x14ac:dyDescent="0.2">
-      <c r="A1043" s="8"/>
-      <c r="B1043" s="33"/>
-      <c r="C1043" s="20"/>
-      <c r="D1043" s="20"/>
-      <c r="E1043" s="14"/>
-      <c r="F1043" s="6"/>
-      <c r="G1043" s="25"/>
-      <c r="H1043" s="25"/>
-      <c r="I1043" s="25"/>
-      <c r="J1043" s="36"/>
-      <c r="K1043" s="30"/>
+    <row r="1040" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1040" s="4"/>
+      <c r="G1040" s="26"/>
+      <c r="H1040" s="26"/>
+      <c r="I1040" s="26"/>
+      <c r="J1040" s="37"/>
+    </row>
+    <row r="1041" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1041" s="4"/>
+      <c r="G1041" s="26"/>
+      <c r="H1041" s="26"/>
+      <c r="I1041" s="26"/>
+      <c r="J1041" s="37"/>
+    </row>
+    <row r="1042" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1042" s="4"/>
+      <c r="G1042" s="26"/>
+      <c r="H1042" s="26"/>
+      <c r="I1042" s="26"/>
+      <c r="J1042" s="37"/>
+    </row>
+    <row r="1043" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1043" s="4"/>
+      <c r="G1043" s="26"/>
+      <c r="H1043" s="26"/>
+      <c r="I1043" s="26"/>
+      <c r="J1043" s="37"/>
     </row>
     <row r="1044" ht="15" x14ac:dyDescent="0.25">
       <c r="A1044" s="4"/>
@@ -21683,28 +21650,24 @@
       <c r="J1555" s="37"/>
     </row>
     <row r="1556" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1556" s="4"/>
       <c r="G1556" s="26"/>
       <c r="H1556" s="26"/>
       <c r="I1556" s="26"/>
       <c r="J1556" s="37"/>
     </row>
     <row r="1557" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1557" s="4"/>
       <c r="G1557" s="26"/>
       <c r="H1557" s="26"/>
       <c r="I1557" s="26"/>
       <c r="J1557" s="37"/>
     </row>
     <row r="1558" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1558" s="4"/>
       <c r="G1558" s="26"/>
       <c r="H1558" s="26"/>
       <c r="I1558" s="26"/>
       <c r="J1558" s="37"/>
     </row>
     <row r="1559" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1559" s="4"/>
       <c r="G1559" s="26"/>
       <c r="H1559" s="26"/>
       <c r="I1559" s="26"/>
@@ -55627,30 +55590,6 @@
       <c r="H7212" s="26"/>
       <c r="I7212" s="26"/>
       <c r="J7212" s="37"/>
-    </row>
-    <row r="7213" ht="15" x14ac:dyDescent="0.25">
-      <c r="G7213" s="26"/>
-      <c r="H7213" s="26"/>
-      <c r="I7213" s="26"/>
-      <c r="J7213" s="37"/>
-    </row>
-    <row r="7214" ht="15" x14ac:dyDescent="0.25">
-      <c r="G7214" s="26"/>
-      <c r="H7214" s="26"/>
-      <c r="I7214" s="26"/>
-      <c r="J7214" s="37"/>
-    </row>
-    <row r="7215" ht="15" x14ac:dyDescent="0.25">
-      <c r="G7215" s="26"/>
-      <c r="H7215" s="26"/>
-      <c r="I7215" s="26"/>
-      <c r="J7215" s="37"/>
-    </row>
-    <row r="7216" ht="15" x14ac:dyDescent="0.25">
-      <c r="G7216" s="26"/>
-      <c r="H7216" s="26"/>
-      <c r="I7216" s="26"/>
-      <c r="J7216" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/latest.xlsx
+++ b/data/latest.xlsx
@@ -59,185 +59,35 @@
     <t>CAD($)</t>
   </si>
   <si>
-    <t>LOC                 </t>
+    <t>OASYS               </t>
   </si>
   <si>
-    <t>02/05/2026</t>
+    <t>04/01/2026</t>
   </si>
   <si>
-    <t>03/16/2026</t>
+    <t>04/02/2026</t>
   </si>
   <si>
-    <t>PAST DUE</t>
+    <t>OKAY</t>
   </si>
   <si>
-    <t>F-0-XD-XX                         </t>
+    <t>HL-0680-3WG                       </t>
   </si>
   <si>
     <t>
     </t>
   </si>
   <si>
-    <t>Floor Roll Cart, with vesa mount, White                                         </t>
+    <t>Light Duty Horizontal Extension Arm - 800mm                                     </t>
   </si>
   <si>
-    <t>SHIP DATE - TBD</t>
-  </si>
-  <si>
-    <t>MAXIMMED            </t>
-  </si>
-  <si>
-    <t>11/20/2025</t>
-  </si>
-  <si>
-    <t>03/18/2026</t>
-  </si>
-  <si>
-    <t>EMM-30SVL-SX-0G                   </t>
-  </si>
-  <si>
-    <t>Monitor Yoke, 32" OASYS Telescopic for OASYS 2001 arm, RAL 9002, Swivel version </t>
-  </si>
-  <si>
-    <t>SHIP DATE - MARCH 18, 2026</t>
-  </si>
-  <si>
-    <t>TOTAL:</t>
-  </si>
-  <si>
-    <t>SM-S391-0GR-3                     </t>
-  </si>
-  <si>
-    <t>Spring arm, Med Duty, 910mm, 3075 w/2075 device end, STP, RAL 9002              </t>
-  </si>
-  <si>
-    <t>ENGINEERINGCPR      </t>
-  </si>
-  <si>
-    <t>12/10/2025</t>
-  </si>
-  <si>
-    <t>03/20/2026</t>
-  </si>
-  <si>
-    <t>SMX-TC0179-8AEXXX                 </t>
-  </si>
-  <si>
-    <t>OASYS Extension Arm, 1000mm w/LCH Spring Arm, Custom End, Stops, Extra keys,9003</t>
-  </si>
-  <si>
-    <t>SHIP DATES - AS NOTED</t>
+    <t>SHIP DATE - ASAP</t>
   </si>
   <si>
     <t>BURTONMEDICALLLC    </t>
   </si>
   <si>
-    <t>12/03/2025</t>
-  </si>
-  <si>
-    <t>03/30/2026</t>
-  </si>
-  <si>
-    <t>OKAY</t>
-  </si>
-  <si>
-    <t>SLW-068055-3WG                    </t>
-  </si>
-  <si>
-    <t>Light Duty Wall Mount Spring Arm - White                                        </t>
-  </si>
-  <si>
-    <t>DOCK DATE - APRIL 6, 2026</t>
-  </si>
-  <si>
-    <t>MAQUETSAS           </t>
-  </si>
-  <si>
-    <t>02/02/2026</t>
-  </si>
-  <si>
-    <t>03/31/2026</t>
-  </si>
-  <si>
-    <t>SM-E479-3MH-Q                     </t>
-  </si>
-  <si>
-    <t>Spring Arm, Med Duty, LCH, Axial Stop, 3P, (127 - 165Nm), RAL 9016              </t>
-  </si>
-  <si>
-    <t>DOCK DATE - MAY 4, 2026</t>
-  </si>
-  <si>
-    <t>SM-L091-3MS-Q                     </t>
-  </si>
-  <si>
-    <t>Spring Arm, Med Duty, 2001, 3P, (12 - 17kg), RAL 9016                           </t>
-  </si>
-  <si>
-    <t>01/14/2026</t>
-  </si>
-  <si>
-    <t>04/01/2026</t>
-  </si>
-  <si>
-    <t>SLF-55XX-7WT                      </t>
-  </si>
-  <si>
-    <t>Floor Stand, ULD 550mm Spring Arm, 165 in/lbs, RAL9010, with locking molex      </t>
-  </si>
-  <si>
-    <t>DOCK DATE - APRIL 9, 2026</t>
-  </si>
-  <si>
-    <t>MONTH:</t>
-  </si>
-  <si>
-    <t>March, 2026</t>
-  </si>
-  <si>
-    <t>Hours available = 600. Hours remaining = 304.5</t>
-  </si>
-  <si>
-    <t>SLX-5542-7WT                      </t>
-  </si>
-  <si>
-    <t>Ultra Light Duty Arm, 165in.lb, RAL9010 locking                                 </t>
-  </si>
-  <si>
-    <t>SLF-0655-1WG                      </t>
-  </si>
-  <si>
-    <t> Light Duty Spring Arm with Floor Stand                                         </t>
-  </si>
-  <si>
     <t>02/25/2026</t>
-  </si>
-  <si>
-    <t>C-7-DW-HR                         </t>
-  </si>
-  <si>
-    <t>Dual Splitter and Drop Tube, 3P Slip Ring and Harness, 500mm                    </t>
-  </si>
-  <si>
-    <t>DOCK DATE - APRIL 10, 2026</t>
-  </si>
-  <si>
-    <t>DERUNGSLICHT-EUR    </t>
-  </si>
-  <si>
-    <t>01/08/2026</t>
-  </si>
-  <si>
-    <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>SR-3P-M-ASSY-CR-HRNS              </t>
-  </si>
-  <si>
-    <t>3P Slip Ring - Male (with wiring components)                                    </t>
-  </si>
-  <si>
-    <t>DOCK DATE - APRIL 13, 2026</t>
   </si>
   <si>
     <t>04/03/2026</t>
@@ -249,40 +99,10 @@
     <t>Light Duty Ceiling Mount, no Harness, no Drop tube, ULD flange, Dome RAL 9010   </t>
   </si>
   <si>
-    <t>04/06/2026</t>
+    <t>DOCK DATE - APRIL 10, 2026</t>
   </si>
   <si>
-    <t>SLX-7380-7WD                      </t>
-  </si>
-  <si>
-    <t>Spring Arm, 730mm Arm, 800mm Extension (Straight), 23Nm, RAL 9010               </t>
-  </si>
-  <si>
-    <t>DOCK DATE - MAY 6, 2026</t>
-  </si>
-  <si>
-    <t>OASYS               </t>
-  </si>
-  <si>
-    <t>SL-0655-2WG-S                     </t>
-  </si>
-  <si>
-    <t>Light Duty Straight Spring Arm, 3 Contacts/1 Commutators, White                 </t>
-  </si>
-  <si>
-    <t>TESTING FOR BURTON, BRANDON AND DERUNGS ARMS</t>
-  </si>
-  <si>
-    <t>SL-0772-6B-N                      </t>
-  </si>
-  <si>
-    <t>Light Duty Spring Arm, 7kg, 3C/1SR, Curved, Bottom, w/Post, RAL9010, Brandon Med</t>
-  </si>
-  <si>
-    <t>SL-0773-3E-K                      </t>
-  </si>
-  <si>
-    <t>Light Duty Spring arm, 730mm arm, TM, RAL 9010                                  </t>
+    <t>TOTAL:</t>
   </si>
   <si>
     <t>SIMEONMEDICALGMBH   </t>
@@ -291,10 +111,16 @@
     <t>03/11/2026</t>
   </si>
   <si>
+    <t>04/06/2026</t>
+  </si>
+  <si>
     <t>SR-3P-F-ASSY-1.100                </t>
   </si>
   <si>
     <t>3P SLIP RING - FEMALE, 1.100" OD (28mm)                                         </t>
+  </si>
+  <si>
+    <t>DOCK DATE - APRIL 13, 2026</t>
   </si>
   <si>
     <t>SR-3P-M-ASSY                      </t>
@@ -303,10 +129,52 @@
     <t>3P SLIP RING - MALE                                                             </t>
   </si>
   <si>
-    <t>11/10/2025</t>
+    <t>DEWIMED             </t>
+  </si>
+  <si>
+    <t>03/26/2026</t>
   </si>
   <si>
     <t>04/10/2026</t>
+  </si>
+  <si>
+    <t>FS-SCR-SC-M6-1.0-6-KT             </t>
+  </si>
+  <si>
+    <t>Kit for SOCKET HEAD CAP SCREW, M6-1.0 X 6MM, 4pcs                               </t>
+  </si>
+  <si>
+    <t>SHIP DATE - APRIL 10, 2026</t>
+  </si>
+  <si>
+    <t>MA-M-BRK-SCRW-SHRT                </t>
+  </si>
+  <si>
+    <t>M14 BRAKE SCREW-MINI SHORT                                                      </t>
+  </si>
+  <si>
+    <t>SA-M-BP-RNG-2001-KT               </t>
+  </si>
+  <si>
+    <t>Spring Arm Ring Kit - 2001/LCH                                                  </t>
+  </si>
+  <si>
+    <t>SA-M-CV-F                         </t>
+  </si>
+  <si>
+    <t>Flap Cover - Standard Colour RAL 9010                                           </t>
+  </si>
+  <si>
+    <t>SA-M-CV-P2-ASSY                   </t>
+  </si>
+  <si>
+    <t>PLUG COVER 2 ASSEMBLY - RAL9010                                                 </t>
+  </si>
+  <si>
+    <t>LOC                 </t>
+  </si>
+  <si>
+    <t>11/10/2025</t>
   </si>
   <si>
     <t>EMA-10024-XX-0B                   </t>
@@ -360,6 +228,9 @@
     <t>Spring Arm, Med Duty, 2075 LCH, 3P, 60-105Nm, 9010                              </t>
   </si>
   <si>
+    <t>DERUNGSLICHT-EUR    </t>
+  </si>
+  <si>
     <t>03/12/2026</t>
   </si>
   <si>
@@ -379,25 +250,22 @@
     <t>Extension Arm Main Cover Kit, v2                                                </t>
   </si>
   <si>
-    <t>02/27/2026</t>
+    <t>ENGINEERINGCPR      </t>
+  </si>
+  <si>
+    <t>12/10/2025</t>
   </si>
   <si>
     <t>04/17/2026</t>
   </si>
   <si>
-    <t>CA1-02B-01-W0                     </t>
+    <t>SMX-TC0179-8AEXXX                 </t>
   </si>
   <si>
-    <t>Central Axis, Single, 850mm, 3P, RAL 9010                                       </t>
+    <t>OASYS Extension Arm, 1000mm w/LCH Spring Arm, Custom End, Stops, Extra keys,9003</t>
   </si>
   <si>
-    <t>DOCK DATE - APRIL 24, 2026</t>
-  </si>
-  <si>
-    <t>MMC-300-WC-050-X                  </t>
-  </si>
-  <si>
-    <t>20" (500mm) CENTRAL AXIS DROP TUBE                                              </t>
+    <t>SHIP DATES - AS NOTED</t>
   </si>
   <si>
     <t>BRANDONMEDICAL      </t>
@@ -425,6 +293,30 @@
     <t>04/29/2026</t>
   </si>
   <si>
+    <t>SLF-0655-1WG                      </t>
+  </si>
+  <si>
+    <t> Light Duty Spring Arm with Floor Stand                                         </t>
+  </si>
+  <si>
+    <t>DOCK DATE - MAY 6, 2026</t>
+  </si>
+  <si>
+    <t>SLW-068055-3WG                    </t>
+  </si>
+  <si>
+    <t>Light Duty Wall Mount Spring Arm - White                                        </t>
+  </si>
+  <si>
+    <t>SLF-55XX-7WT                      </t>
+  </si>
+  <si>
+    <t>Floor Stand, ULD 550mm Spring Arm, 165 in/lbs, RAL9010, with locking molex      </t>
+  </si>
+  <si>
+    <t>DOCK DATE - MAY 4, 2026</t>
+  </si>
+  <si>
     <t>EMALED              </t>
   </si>
   <si>
@@ -438,6 +330,9 @@
   </si>
   <si>
     <t>Dual Central Axis, 3p/3p, 850mm top/ 700mm bottom, RAL 9010                     </t>
+  </si>
+  <si>
+    <t>SHIP DATE - TBD</t>
   </si>
   <si>
     <t>MMC-300-WC-080-X                  </t>
@@ -464,13 +359,88 @@
     <t>2001 Spring arm, 5 kg, 910mm, 3p, RAL 9010                                      </t>
   </si>
   <si>
-    <t>01/23/2026</t>
+    <t>MAQUETSAS           </t>
   </si>
   <si>
     <t>03/03/2026</t>
   </si>
   <si>
+    <t>SM-E479-3MH-Q                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, LCH, Axial Stop, 3P, (127 - 165Nm), RAL 9016              </t>
+  </si>
+  <si>
     <t>DOCK DATE - June 2, 2026</t>
+  </si>
+  <si>
+    <t>MAXIMMED            </t>
+  </si>
+  <si>
+    <t>11/20/2025</t>
+  </si>
+  <si>
+    <t>SM-S391-0GR-3                     </t>
+  </si>
+  <si>
+    <t>Spring arm, Med Duty, 910mm, 3075 w/2075 device end, STP, RAL 9002              </t>
+  </si>
+  <si>
+    <t>SHIP DATE - APRIL 30, 2026</t>
+  </si>
+  <si>
+    <t>03/17/2026</t>
+  </si>
+  <si>
+    <t>EMM-30SVL-S3-0G                   </t>
+  </si>
+  <si>
+    <t>Monitor Yoke, 32" OASYS Telescopic for 3001 arm, RAL9002, Swivel version        </t>
+  </si>
+  <si>
+    <t>SM-E479-3GJ-J                     </t>
+  </si>
+  <si>
+    <t>SA, 2075 LCH, 3P, 9002                                                          </t>
+  </si>
+  <si>
+    <t>SHIP DATE - April 30, 2026</t>
+  </si>
+  <si>
+    <t>SM-E479-5GJ-J                     </t>
+  </si>
+  <si>
+    <t>SA, 2075 LCH, 5P, 9002                                                          </t>
+  </si>
+  <si>
+    <t>SM-E479-9GJ-J                     </t>
+  </si>
+  <si>
+    <t>SA, 2075, LCH, 9P, 9002                                                         </t>
+  </si>
+  <si>
+    <t>SM-E491-3GJ-J                     </t>
+  </si>
+  <si>
+    <t>SA, 2075, 3P, 10 -20 kg, 9002                                                   </t>
+  </si>
+  <si>
+    <t>SM-E491-5GJ-J                     </t>
+  </si>
+  <si>
+    <t>SA, 2075, 5P, 10 -20 kg, 9002                                                   </t>
+  </si>
+  <si>
+    <t>SM-E279-3GB-J                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 2001 LCH (Floor stand), 3P, RAL 9002                      </t>
+  </si>
+  <si>
+    <t>SA-M-BP-2075-SM-ASSY              </t>
+  </si>
+  <si>
+    <t>2075 BG PT ASSY                                                                 </t>
   </si>
   <si>
     <t>07/25/2025</t>
@@ -485,13 +455,13 @@
     <t>Light Duty Straight Spring Arm, 3 Contacts/1 Comm, White (Burton), UNI Groove   </t>
   </si>
   <si>
-    <t>SHIP DATE - ASAP</t>
+    <t>MONTH:</t>
   </si>
   <si>
     <t>April, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = -15.5</t>
+    <t>Hours available = 600. Hours remaining = 109.25</t>
   </si>
   <si>
     <t>DOCK DATE - MAY 8, 2026</t>
@@ -509,6 +479,15 @@
     <t>DOCK DATE - MAY 14, 2026</t>
   </si>
   <si>
+    <t>SLX-5542-7WT                      </t>
+  </si>
+  <si>
+    <t>Ultra Light Duty Arm, 165in.lb, RAL9010 locking                                 </t>
+  </si>
+  <si>
+    <t>03/16/2026</t>
+  </si>
+  <si>
     <t>SLF-3-WK                          </t>
   </si>
   <si>
@@ -519,6 +498,12 @@
   </si>
   <si>
     <t>02/24/2026</t>
+  </si>
+  <si>
+    <t>SLX-7380-7WD                      </t>
+  </si>
+  <si>
+    <t>Spring Arm, 730mm Arm, 800mm Extension (Straight), 23Nm, RAL 9010               </t>
   </si>
   <si>
     <t>DOCK DATE - JUNE 19, 2026</t>
@@ -581,7 +566,61 @@
     <t>05/15/2026</t>
   </si>
   <si>
+    <t>SLX-7380-7W6                      </t>
+  </si>
+  <si>
+    <t>730mm Spr Arm,  , 800mm Ext (Straight), 3P, Crimp conn, 11 Nm, 3 S/N stickers   </t>
+  </si>
+  <si>
+    <t>DOCK DATE - JUNE 26, 2026</t>
+  </si>
+  <si>
+    <t>IMAGEDIAGNOSTICS    </t>
+  </si>
+  <si>
+    <t>03/27/2026</t>
+  </si>
+  <si>
+    <t>CA1-02D-02-MI                     </t>
+  </si>
+  <si>
+    <t>Central Axis, Single, 1150mm ext arm, Stop, invert (4" tube), 9016              </t>
+  </si>
+  <si>
+    <t>DOCK DATE - SEE NOTES</t>
+  </si>
+  <si>
+    <t>SM-E491-0MQ-X                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 3075/2075, Stop, 10-20kg, 9016                            </t>
+  </si>
+  <si>
+    <t>03/31/2026</t>
+  </si>
+  <si>
+    <t>05/18/2026</t>
+  </si>
+  <si>
+    <t>SA-L-LCK-F-BRK-KT                 </t>
+  </si>
+  <si>
+    <t>Locking Collar with a brake screw                                               </t>
+  </si>
+  <si>
+    <t>DOCK DATE - MAY 29, 2026</t>
+  </si>
+  <si>
+    <t>03/18/2026</t>
+  </si>
+  <si>
     <t>05/22/2026</t>
+  </si>
+  <si>
+    <t>SR-3P-M-ASSY-CR-HRNS              </t>
+  </si>
+  <si>
+    <t>3P Slip Ring - Male (with wiring components)                                    </t>
   </si>
   <si>
     <t>DOCK DATES - AS NOTED</t>
@@ -620,10 +659,10 @@
     <t>Gimbal Yoke, parallel adaptor                                                   </t>
   </si>
   <si>
-    <t>06/05/2026</t>
+    <t>01/23/2026</t>
   </si>
   <si>
-    <t>DOCK DATE - JUNE 15, 2026</t>
+    <t>06/01/2026</t>
   </si>
   <si>
     <t>May, 2026</t>
@@ -632,10 +671,28 @@
     <t>Hours available = 600. Hours remaining = -31.35</t>
   </si>
   <si>
+    <t>01/14/2026</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>DOCK DATE - JUNE 15, 2026</t>
+  </si>
+  <si>
     <t>06/12/2026</t>
   </si>
   <si>
     <t>06/26/2026</t>
+  </si>
+  <si>
+    <t>06/30/2026</t>
+  </si>
+  <si>
+    <t>730mm Spr Arm, 800mm Ext (Straight), 3P, Crimp conn, 11 Nm, 9010, 3 S/N stickers</t>
+  </si>
+  <si>
+    <t>DOCK DATE - AUGUST 14, 2026</t>
   </si>
   <si>
     <t>07/06/2026</t>
@@ -647,19 +704,22 @@
     <t>June, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = 212.2</t>
+    <t>Hours available = 600. Hours remaining = -12.8</t>
   </si>
   <si>
     <t>07/17/2026</t>
   </si>
   <si>
-    <t>08/14/2026</t>
+    <t>08/03/2026</t>
   </si>
   <si>
     <t>July, 2026</t>
   </si>
   <si>
     <t>Hours available = 600. Hours remaining = 528</t>
+  </si>
+  <si>
+    <t>08/14/2026</t>
   </si>
   <si>
     <t>09/18/2026</t>
@@ -699,6 +759,12 @@
   </si>
   <si>
     <t>08/23/2024</t>
+  </si>
+  <si>
+    <t>CA1-02B-01-W0                     </t>
+  </si>
+  <si>
+    <t>Central Axis, Single, 850mm, 3P, RAL 9010                                       </t>
   </si>
   <si>
     <t>FORECAST</t>
@@ -762,9 +828,6 @@
     <t>SHIP DATE - DECEMBER 12, 2025</t>
   </si>
   <si>
-    <t>DEWIMED             </t>
-  </si>
-  <si>
     <t>CA2-06A-03-WG                     </t>
   </si>
   <si>
@@ -798,19 +861,16 @@
     <t>05/31/2024</t>
   </si>
   <si>
+    <t>SM-L091-3MS-Q                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 2001, 3P, (12 - 17kg), RAL 9016                           </t>
+  </si>
+  <si>
     <t>07/05/2024</t>
   </si>
   <si>
     <t>Spring Arm, Med Duty, 2001, 3P, (4.5 - 8kg), custom end cover, RAL 9016         </t>
-  </si>
-  <si>
-    <t>03/17/2026</t>
-  </si>
-  <si>
-    <t>EMM-30SVL-S3-0G                   </t>
-  </si>
-  <si>
-    <t>Monitor Yoke, 32" OASYS Telescopic for 3001 arm, RAL9002, Swivel version        </t>
   </si>
 </sst>
 </file>
@@ -1706,7 +1766,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="45">
-        <v>0000106837</v>
+        <v>0000106900</v>
       </c>
       <c r="C7" s="46" t="s">
         <v>14</v>
@@ -1721,10 +1781,10 @@
         <v>17</v>
       </c>
       <c r="G7" s="51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" s="52">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="I7" s="53" t="s">
         <v>18</v>
@@ -1748,7 +1808,7 @@
         <v>27</v>
       </c>
       <c r="H8" s="52">
-        <v>4875</v>
+        <v>0</v>
       </c>
       <c r="I8" s="53"/>
       <c r="J8" s="48"/>
@@ -1760,7 +1820,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="45">
-        <v>0000106752</v>
+        <v>0000106851</v>
       </c>
       <c r="C9" t="s" s="46">
         <v>22</v>
@@ -1775,10 +1835,10 @@
         <v>24</v>
       </c>
       <c r="G9" s="51">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H9" s="52">
-        <v>1141.98</v>
+        <v>228.58</v>
       </c>
       <c r="I9" t="s" s="53">
         <v>18</v>
@@ -1792,92 +1852,92 @@
       <c r="L9" s="0"/>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B10" s="45">
-        <v>0000106752</v>
-      </c>
-      <c r="C10" t="s" s="46">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s" s="47">
+      <c r="A10" s="44"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="44"/>
+      <c r="G10" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H10" s="52">
+        <v>11429</v>
+      </c>
+      <c r="I10" s="53"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="0"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="44">
+        <v>28</v>
+      </c>
+      <c r="B11" s="45">
+        <v>0000106873</v>
+      </c>
+      <c r="C11" t="s" s="46">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s" s="46">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s" s="47">
         <v>16</v>
       </c>
-      <c r="F10" t="s" s="44">
-        <v>28</v>
-      </c>
-      <c r="G10" s="51">
-        <v>10</v>
-      </c>
-      <c r="H10" s="52">
-        <v>1060.82</v>
-      </c>
-      <c r="I10" t="s" s="53">
+      <c r="F11" t="s" s="44">
+        <v>31</v>
+      </c>
+      <c r="G11" s="51">
+        <v>300</v>
+      </c>
+      <c r="H11" s="52">
+        <v>9.47</v>
+      </c>
+      <c r="I11" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J10" t="s" s="48">
-        <v>29</v>
-      </c>
-      <c r="K10" t="s" s="49">
-        <v>26</v>
-      </c>
-      <c r="L10" s="0"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="44"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="44"/>
-      <c r="G11" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H11" s="52">
-        <v>38015.72</v>
-      </c>
-      <c r="I11" s="53"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="49"/>
+      <c r="J11" t="s" s="48">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s" s="49">
+        <v>33</v>
+      </c>
       <c r="L11" s="0"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="44">
+        <v>28</v>
+      </c>
+      <c r="B12" s="45">
+        <v>0000106873</v>
+      </c>
+      <c r="C12" t="s" s="46">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s" s="46">
         <v>30</v>
-      </c>
-      <c r="B12" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C12" t="s" s="46">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s" s="46">
-        <v>32</v>
       </c>
       <c r="E12" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F12" t="s" s="44">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="51">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="H12" s="52">
-        <v>2250</v>
+        <v>10.42</v>
       </c>
       <c r="I12" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J12" t="s" s="48">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K12" t="s" s="49">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L12" s="0"/>
     </row>
@@ -1892,7 +1952,7 @@
         <v>27</v>
       </c>
       <c r="H13" s="52">
-        <v>11250</v>
+        <v>8051</v>
       </c>
       <c r="I13" s="53"/>
       <c r="J13" s="48"/>
@@ -1904,7 +1964,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="45">
-        <v>0000106769</v>
+        <v>0000106892</v>
       </c>
       <c r="C14" t="s" s="46">
         <v>37</v>
@@ -1913,133 +1973,169 @@
         <v>38</v>
       </c>
       <c r="E14" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s" s="44">
         <v>39</v>
       </c>
-      <c r="F14" t="s" s="44">
+      <c r="G14" s="51">
+        <v>10</v>
+      </c>
+      <c r="H14" s="52">
+        <v>6.90</v>
+      </c>
+      <c r="I14" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s" s="48">
         <v>40</v>
       </c>
-      <c r="G14" s="51">
-        <v>70</v>
-      </c>
-      <c r="H14" s="52">
-        <v>377.62</v>
-      </c>
-      <c r="I14" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J14" t="s" s="48">
+      <c r="K14" t="s" s="49">
         <v>41</v>
       </c>
-      <c r="K14" t="s" s="49">
+      <c r="L14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B15" s="45">
+        <v>0000106892</v>
+      </c>
+      <c r="C15" t="s" s="46">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s" s="46">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s" s="44">
         <v>42</v>
       </c>
-      <c r="L14" s="0"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="44"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="44"/>
-      <c r="G15" t="s" s="51">
-        <v>27</v>
+      <c r="G15" s="51">
+        <v>15</v>
       </c>
       <c r="H15" s="52">
-        <v>26433.4</v>
-      </c>
-      <c r="I15" s="53"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="49"/>
+        <v>22.77</v>
+      </c>
+      <c r="I15" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s" s="48">
+        <v>43</v>
+      </c>
+      <c r="K15" t="s" s="49">
+        <v>41</v>
+      </c>
       <c r="L15" s="0"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="44">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B16" s="45">
-        <v>0000106832</v>
+        <v>0000106892</v>
       </c>
       <c r="C16" t="s" s="46">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s" s="46">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s" s="44">
         <v>44</v>
       </c>
-      <c r="D16" t="s" s="46">
+      <c r="G16" s="51">
+        <v>10</v>
+      </c>
+      <c r="H16" s="52">
+        <v>12.42</v>
+      </c>
+      <c r="I16" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s" s="48">
         <v>45</v>
       </c>
-      <c r="E16" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F16" t="s" s="44">
+      <c r="K16" t="s" s="49">
+        <v>41</v>
+      </c>
+      <c r="L16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B17" s="45">
+        <v>0000106892</v>
+      </c>
+      <c r="C17" t="s" s="46">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s" s="46">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s" s="44">
         <v>46</v>
       </c>
-      <c r="G16" s="51">
-        <v>52</v>
-      </c>
-      <c r="H16" s="52">
-        <v>473.26</v>
-      </c>
-      <c r="I16" s="53">
-        <v>52</v>
-      </c>
-      <c r="J16" t="s" s="48">
+      <c r="G17" s="51">
+        <v>15</v>
+      </c>
+      <c r="H17" s="52">
+        <v>15.87</v>
+      </c>
+      <c r="I17" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s" s="48">
         <v>47</v>
       </c>
-      <c r="K16" t="s" s="49">
-        <v>48</v>
-      </c>
-      <c r="L16" s="0"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="44"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="44"/>
-      <c r="G17" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H17" s="52">
-        <v>24609.52</v>
-      </c>
-      <c r="I17" s="53"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="49"/>
+      <c r="K17" t="s" s="49">
+        <v>41</v>
+      </c>
       <c r="L17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="44">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B18" s="45">
-        <v>0000106833</v>
+        <v>0000106892</v>
       </c>
       <c r="C18" t="s" s="46">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s" s="46">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s" s="44">
+        <v>48</v>
+      </c>
+      <c r="G18" s="51">
+        <v>10</v>
+      </c>
+      <c r="H18" s="52">
+        <v>26.15</v>
+      </c>
+      <c r="I18" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s" s="48">
         <v>49</v>
       </c>
-      <c r="G18" s="51">
-        <v>156</v>
-      </c>
-      <c r="H18" s="52">
-        <v>367.69</v>
-      </c>
-      <c r="I18" s="53">
-        <v>156</v>
-      </c>
-      <c r="J18" t="s" s="48">
-        <v>50</v>
-      </c>
       <c r="K18" t="s" s="49">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L18" s="0"/>
     </row>
@@ -2049,240 +2145,282 @@
       <c r="C19" s="46"/>
       <c r="D19" s="46"/>
       <c r="E19" s="47"/>
-      <c r="F19" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F19" s="44"/>
       <c r="G19" t="s" s="51">
         <v>27</v>
       </c>
       <c r="H19" s="52">
-        <v>57359.64</v>
-      </c>
-      <c r="I19" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>1034.3</v>
+      </c>
+      <c r="I19" s="53"/>
+      <c r="J19" s="48"/>
       <c r="K19" s="49"/>
       <c r="L19" s="0"/>
     </row>
     <row r="20">
-      <c r="A20" s="44"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" t="s" s="51">
-        <v>56</v>
+      <c r="A20" t="s" s="44">
+        <v>50</v>
+      </c>
+      <c r="B20" s="45">
+        <v>0000106731</v>
+      </c>
+      <c r="C20" t="s" s="46">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s" s="46">
+        <v>38</v>
+      </c>
+      <c r="E20" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s" s="44">
+        <v>52</v>
+      </c>
+      <c r="G20" s="51">
+        <v>100</v>
       </c>
       <c r="H20" s="52">
-        <v>162543.28</v>
-      </c>
-      <c r="I20" s="53">
-        <v>295.5</v>
-      </c>
-      <c r="J20" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="K20" s="49"/>
+        <v>75</v>
+      </c>
+      <c r="I20" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s" s="48">
+        <v>53</v>
+      </c>
+      <c r="K20" t="s" s="49">
+        <v>54</v>
+      </c>
       <c r="L20" s="0"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="44">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B21" s="45">
-        <v>0000106806</v>
+        <v>0000106731</v>
       </c>
       <c r="C21" t="s" s="46">
         <v>51</v>
       </c>
       <c r="D21" t="s" s="46">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s" s="44">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G21" s="51">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H21" s="52">
-        <v>572.10</v>
-      </c>
-      <c r="I21" s="53">
-        <v>30</v>
+        <v>225</v>
+      </c>
+      <c r="I21" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J21" t="s" s="48">
+        <v>56</v>
+      </c>
+      <c r="K21" t="s" s="49">
         <v>54</v>
       </c>
-      <c r="K21" t="s" s="49">
-        <v>55</v>
-      </c>
       <c r="L21" s="0"/>
     </row>
     <row r="22">
-      <c r="A22" s="44"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="44"/>
-      <c r="G22" t="s" s="51">
-        <v>27</v>
+      <c r="A22" t="s" s="44">
+        <v>50</v>
+      </c>
+      <c r="B22" s="45">
+        <v>0000106731</v>
+      </c>
+      <c r="C22" t="s" s="46">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s" s="46">
+        <v>38</v>
+      </c>
+      <c r="E22" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s" s="44">
+        <v>57</v>
+      </c>
+      <c r="G22" s="51">
+        <v>200</v>
       </c>
       <c r="H22" s="52">
-        <v>5721</v>
-      </c>
-      <c r="I22" s="53"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="I22" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s" s="48">
+        <v>58</v>
+      </c>
+      <c r="K22" t="s" s="49">
+        <v>54</v>
+      </c>
       <c r="L22" s="0"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="44">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B23" s="45">
-        <v>0000106807</v>
+        <v>0000106731</v>
       </c>
       <c r="C23" t="s" s="46">
         <v>51</v>
       </c>
       <c r="D23" t="s" s="46">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s" s="44">
         <v>59</v>
       </c>
       <c r="G23" s="51">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="H23" s="52">
-        <v>319.37</v>
-      </c>
-      <c r="I23" s="53">
-        <v>72</v>
+        <v>100</v>
+      </c>
+      <c r="I23" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J23" t="s" s="48">
         <v>60</v>
       </c>
       <c r="K23" t="s" s="49">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L23" s="0"/>
     </row>
     <row r="24">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="44"/>
-      <c r="G24" t="s" s="51">
+      <c r="A24" t="s" s="44">
+        <v>50</v>
+      </c>
+      <c r="B24" s="45">
+        <v>0000106731</v>
+      </c>
+      <c r="C24" t="s" s="46">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s" s="46">
+        <v>38</v>
+      </c>
+      <c r="E24" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F24" t="s" s="44">
+        <v>61</v>
+      </c>
+      <c r="G24" s="51">
+        <v>100</v>
+      </c>
+      <c r="H24" s="52">
+        <v>495</v>
+      </c>
+      <c r="I24" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s" s="48">
+        <v>62</v>
+      </c>
+      <c r="K24" t="s" s="49">
+        <v>54</v>
+      </c>
+      <c r="L24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="44"/>
+      <c r="G25" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H24" s="52">
-        <v>15329.76</v>
-      </c>
-      <c r="I24" s="53"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="0"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B25" s="45">
-        <v>0000106808</v>
-      </c>
-      <c r="C25" t="s" s="46">
-        <v>51</v>
-      </c>
-      <c r="D25" t="s" s="46">
-        <v>52</v>
-      </c>
-      <c r="E25" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F25" t="s" s="44">
-        <v>61</v>
-      </c>
-      <c r="G25" s="51">
+      <c r="H25" s="52">
+        <v>89500</v>
+      </c>
+      <c r="I25" s="53"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B26" s="45">
+        <v>0000106874</v>
+      </c>
+      <c r="C26" t="s" s="46">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s" s="47">
         <v>16</v>
       </c>
-      <c r="H25" s="52">
-        <v>659.52</v>
-      </c>
-      <c r="I25" s="53">
-        <v>48</v>
-      </c>
-      <c r="J25" t="s" s="48">
-        <v>62</v>
-      </c>
-      <c r="K25" t="s" s="49">
-        <v>55</v>
-      </c>
-      <c r="L25" s="0"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="44"/>
-      <c r="G26" t="s" s="51">
-        <v>27</v>
+      <c r="F26" t="s" s="44">
+        <v>64</v>
+      </c>
+      <c r="G26" s="51">
+        <v>2</v>
       </c>
       <c r="H26" s="52">
-        <v>10552.32</v>
-      </c>
-      <c r="I26" s="53"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="49"/>
+        <v>127.37</v>
+      </c>
+      <c r="I26" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s" s="48">
+        <v>65</v>
+      </c>
+      <c r="K26" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L26" s="0"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B27" s="45">
-        <v>0000106849</v>
+        <v>0000106874</v>
       </c>
       <c r="C27" t="s" s="46">
+        <v>29</v>
+      </c>
+      <c r="D27" t="s" s="46">
         <v>63</v>
       </c>
-      <c r="D27" t="s" s="46">
-        <v>52</v>
-      </c>
       <c r="E27" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s" s="44">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G27" s="51">
         <v>5</v>
       </c>
       <c r="H27" s="52">
-        <v>400.69</v>
-      </c>
-      <c r="I27" s="53">
-        <v>6.25</v>
+        <v>722.45</v>
+      </c>
+      <c r="I27" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J27" t="s" s="48">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K27" t="s" s="49">
         <v>66</v>
@@ -2300,7 +2438,7 @@
         <v>27</v>
       </c>
       <c r="H28" s="52">
-        <v>2003.45</v>
+        <v>3866.99</v>
       </c>
       <c r="I28" s="53"/>
       <c r="J28" s="48"/>
@@ -2309,361 +2447,343 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="44">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B29" s="45">
-        <v>0000106798</v>
+        <v>0000106877</v>
       </c>
       <c r="C29" t="s" s="46">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="E29" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F29" t="s" s="44">
+        <v>71</v>
+      </c>
+      <c r="G29" s="51">
+        <v>40</v>
+      </c>
+      <c r="H29" s="52">
+        <v>11.79</v>
+      </c>
+      <c r="I29" s="53">
+        <v>10</v>
+      </c>
+      <c r="J29" t="s" s="48">
+        <v>72</v>
+      </c>
+      <c r="K29" t="s" s="49">
+        <v>73</v>
+      </c>
+      <c r="L29" s="0"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="44">
         <v>69</v>
       </c>
-      <c r="E29" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F29" t="s" s="44">
+      <c r="B30" s="45">
+        <v>0000106877</v>
+      </c>
+      <c r="C30" t="s" s="46">
         <v>70</v>
       </c>
-      <c r="G29" s="51">
-        <v>504</v>
-      </c>
-      <c r="H29" s="52">
-        <v>22.71</v>
-      </c>
-      <c r="I29" t="s" s="53">
+      <c r="D30" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="E30" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s" s="44">
+        <v>74</v>
+      </c>
+      <c r="G30" s="51">
+        <v>10</v>
+      </c>
+      <c r="H30" s="52">
+        <v>15.33</v>
+      </c>
+      <c r="I30" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J29" t="s" s="48">
-        <v>71</v>
-      </c>
-      <c r="K29" t="s" s="49">
-        <v>72</v>
-      </c>
-      <c r="L29" s="0"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="44"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="44"/>
-      <c r="G30" t="s" s="51">
+      <c r="J30" t="s" s="48">
+        <v>75</v>
+      </c>
+      <c r="K30" t="s" s="49">
+        <v>73</v>
+      </c>
+      <c r="L30" s="0"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="44"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="44"/>
+      <c r="G31" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H30" s="52">
-        <v>11445.84</v>
-      </c>
-      <c r="I30" s="53"/>
-      <c r="J30" s="48"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="0"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B31" s="45">
-        <v>0000106851</v>
-      </c>
-      <c r="C31" t="s" s="46">
-        <v>63</v>
-      </c>
-      <c r="D31" t="s" s="46">
-        <v>73</v>
-      </c>
-      <c r="E31" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F31" t="s" s="44">
-        <v>74</v>
-      </c>
-      <c r="G31" s="51">
-        <v>50</v>
-      </c>
       <c r="H31" s="52">
-        <v>228.58</v>
-      </c>
-      <c r="I31" t="s" s="53">
+        <v>624.9</v>
+      </c>
+      <c r="I31" s="53"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="0"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="44">
+        <v>76</v>
+      </c>
+      <c r="B32" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C32" t="s" s="46">
+        <v>77</v>
+      </c>
+      <c r="D32" t="s" s="46">
+        <v>78</v>
+      </c>
+      <c r="E32" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s" s="44">
+        <v>79</v>
+      </c>
+      <c r="G32" s="51">
+        <v>5</v>
+      </c>
+      <c r="H32" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I32" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J31" t="s" s="48">
-        <v>75</v>
-      </c>
-      <c r="K31" t="s" s="49">
-        <v>66</v>
-      </c>
-      <c r="L31" s="0"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="44"/>
-      <c r="G32" t="s" s="51">
+      <c r="J32" t="s" s="48">
+        <v>80</v>
+      </c>
+      <c r="K32" t="s" s="49">
+        <v>81</v>
+      </c>
+      <c r="L32" s="0"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="44"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="44"/>
+      <c r="G33" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H32" s="52">
-        <v>11429</v>
-      </c>
-      <c r="I32" s="53"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="0"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="44">
-        <v>67</v>
-      </c>
-      <c r="B33" s="45">
-        <v>0000106799</v>
-      </c>
-      <c r="C33" t="s" s="46">
-        <v>68</v>
-      </c>
-      <c r="D33" t="s" s="46">
-        <v>76</v>
-      </c>
-      <c r="E33" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F33" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G33" s="51">
-        <v>180</v>
-      </c>
       <c r="H33" s="52">
-        <v>288.01</v>
-      </c>
-      <c r="I33" s="53">
-        <v>225</v>
-      </c>
-      <c r="J33" t="s" s="48">
-        <v>78</v>
-      </c>
-      <c r="K33" t="s" s="49">
-        <v>79</v>
-      </c>
+        <v>11250</v>
+      </c>
+      <c r="I33" s="53"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="49"/>
       <c r="L33" s="0"/>
     </row>
     <row r="34">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="44"/>
-      <c r="G34" t="s" s="51">
+      <c r="A34" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B34" s="45">
+        <v>0000106846</v>
+      </c>
+      <c r="C34" t="s" s="46">
+        <v>83</v>
+      </c>
+      <c r="D34" t="s" s="46">
+        <v>84</v>
+      </c>
+      <c r="E34" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F34" t="s" s="44">
+        <v>85</v>
+      </c>
+      <c r="G34" s="51">
+        <v>235</v>
+      </c>
+      <c r="H34" s="52">
+        <v>255.27</v>
+      </c>
+      <c r="I34" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J34" t="s" s="48">
+        <v>86</v>
+      </c>
+      <c r="K34" t="s" s="49">
+        <v>87</v>
+      </c>
+      <c r="L34" s="0"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="44"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="44"/>
+      <c r="G35" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H34" s="52">
-        <v>51841.8</v>
-      </c>
-      <c r="I34" s="53"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="49"/>
-      <c r="L34" s="0"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="44">
-        <v>80</v>
-      </c>
-      <c r="B35" s="45">
-        <v>0000106889</v>
-      </c>
-      <c r="C35" t="s" s="46">
-        <v>32</v>
-      </c>
-      <c r="D35" t="s" s="46">
-        <v>76</v>
-      </c>
-      <c r="E35" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F35" t="s" s="44">
-        <v>81</v>
-      </c>
-      <c r="G35" s="51">
-        <v>1</v>
-      </c>
       <c r="H35" s="52">
-        <v>0</v>
-      </c>
-      <c r="I35" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J35" t="s" s="48">
-        <v>82</v>
-      </c>
-      <c r="K35" t="s" s="49">
-        <v>83</v>
-      </c>
+        <v>59988.45</v>
+      </c>
+      <c r="I35" s="53"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="49"/>
       <c r="L35" s="0"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="44">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="B36" s="45">
-        <v>0000106889</v>
+        <v>0000106821</v>
       </c>
       <c r="C36" t="s" s="46">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s" s="46">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E36" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s" s="44">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G36" s="51">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H36" s="52">
-        <v>0</v>
-      </c>
-      <c r="I36" t="s" s="53">
-        <v>18</v>
+        <v>652.21</v>
+      </c>
+      <c r="I36" s="53">
+        <v>48</v>
       </c>
       <c r="J36" t="s" s="48">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="49">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="L36" s="0"/>
     </row>
     <row r="37">
-      <c r="A37" t="s" s="44">
-        <v>80</v>
-      </c>
-      <c r="B37" s="45">
-        <v>0000106889</v>
-      </c>
-      <c r="C37" t="s" s="46">
-        <v>32</v>
-      </c>
-      <c r="D37" t="s" s="46">
-        <v>76</v>
-      </c>
-      <c r="E37" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F37" t="s" s="44">
-        <v>86</v>
-      </c>
-      <c r="G37" s="51">
-        <v>1</v>
+      <c r="A37" s="44"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="44"/>
+      <c r="G37" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H37" s="52">
-        <v>0</v>
-      </c>
-      <c r="I37" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J37" t="s" s="48">
-        <v>87</v>
-      </c>
-      <c r="K37" t="s" s="49">
-        <v>83</v>
-      </c>
+        <v>10435.36</v>
+      </c>
+      <c r="I37" s="53"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="49"/>
       <c r="L37" s="0"/>
     </row>
     <row r="38">
-      <c r="A38" s="44"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="44"/>
-      <c r="G38" t="s" s="51">
+      <c r="A38" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B38" s="45">
+        <v>0000106822</v>
+      </c>
+      <c r="C38" t="s" s="46">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s" s="46">
+        <v>89</v>
+      </c>
+      <c r="E38" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F38" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="G38" s="51">
+        <v>70</v>
+      </c>
+      <c r="H38" s="52">
+        <v>370.76</v>
+      </c>
+      <c r="I38" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J38" t="s" s="48">
+        <v>94</v>
+      </c>
+      <c r="K38" t="s" s="49">
+        <v>92</v>
+      </c>
+      <c r="L38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="44"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="44"/>
+      <c r="G39" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H38" s="52">
-        <v>0</v>
-      </c>
-      <c r="I38" s="53"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="0"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B39" s="45">
-        <v>0000106873</v>
-      </c>
-      <c r="C39" t="s" s="46">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s" s="46">
-        <v>76</v>
-      </c>
-      <c r="E39" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F39" t="s" s="44">
-        <v>90</v>
-      </c>
-      <c r="G39" s="51">
-        <v>300</v>
-      </c>
       <c r="H39" s="52">
-        <v>9.47</v>
-      </c>
-      <c r="I39" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J39" t="s" s="48">
-        <v>91</v>
-      </c>
-      <c r="K39" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>25953.2</v>
+      </c>
+      <c r="I39" s="53"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="49"/>
       <c r="L39" s="0"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B40" s="45">
+        <v>0000106823</v>
+      </c>
+      <c r="C40" t="s" s="46">
         <v>88</v>
       </c>
-      <c r="B40" s="45">
-        <v>0000106873</v>
-      </c>
-      <c r="C40" t="s" s="46">
+      <c r="D40" t="s" s="46">
         <v>89</v>
       </c>
-      <c r="D40" t="s" s="46">
-        <v>76</v>
-      </c>
       <c r="E40" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s" s="44">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G40" s="51">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="H40" s="52">
-        <v>10.42</v>
-      </c>
-      <c r="I40" t="s" s="53">
-        <v>18</v>
+        <v>565.75</v>
+      </c>
+      <c r="I40" s="53">
+        <v>30</v>
       </c>
       <c r="J40" t="s" s="48">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K40" t="s" s="49">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L40" s="0"/>
     </row>
@@ -2678,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="H41" s="52">
-        <v>8051</v>
+        <v>5657.5</v>
       </c>
       <c r="I41" s="53"/>
       <c r="J41" s="48"/>
@@ -2687,181 +2807,181 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="44">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B42" s="45">
-        <v>0000106731</v>
+        <v>0000106869</v>
       </c>
       <c r="C42" t="s" s="46">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s" s="46">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E42" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s" s="44">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G42" s="51">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H42" s="52">
-        <v>75</v>
+        <v>943.26</v>
       </c>
       <c r="I42" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J42" t="s" s="48">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K42" t="s" s="49">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L42" s="0"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="44">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B43" s="45">
-        <v>0000106731</v>
+        <v>0000106869</v>
       </c>
       <c r="C43" t="s" s="46">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D43" t="s" s="46">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E43" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s" s="44">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G43" s="51">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H43" s="52">
-        <v>225</v>
-      </c>
-      <c r="I43" t="s" s="53">
-        <v>18</v>
+        <v>275.11</v>
+      </c>
+      <c r="I43" s="53">
+        <v>6.25</v>
       </c>
       <c r="J43" t="s" s="48">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K43" t="s" s="49">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="44">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B44" s="45">
-        <v>0000106731</v>
+        <v>0000106869</v>
       </c>
       <c r="C44" t="s" s="46">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s" s="46">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s" s="44">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G44" s="51">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="H44" s="52">
-        <v>0</v>
+        <v>361.58</v>
       </c>
       <c r="I44" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J44" t="s" s="48">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K44" t="s" s="49">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L44" s="0"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="44">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B45" s="45">
-        <v>0000106731</v>
+        <v>0000106869</v>
       </c>
       <c r="C45" t="s" s="46">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s" s="46">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E45" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s" s="44">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G45" s="51">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H45" s="52">
-        <v>100</v>
+        <v>275.11</v>
       </c>
       <c r="I45" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J45" t="s" s="48">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K45" t="s" s="49">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L45" s="0"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="44">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B46" s="45">
-        <v>0000106731</v>
+        <v>0000106869</v>
       </c>
       <c r="C46" t="s" s="46">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s" s="46">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s" s="44">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G46" s="51">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H46" s="52">
-        <v>495</v>
+        <v>361.58</v>
       </c>
       <c r="I46" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J46" t="s" s="48">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K46" t="s" s="49">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L46" s="0"/>
     </row>
@@ -2876,7 +2996,7 @@
         <v>27</v>
       </c>
       <c r="H47" s="52">
-        <v>89500</v>
+        <v>72763.81</v>
       </c>
       <c r="I47" s="53"/>
       <c r="J47" s="48"/>
@@ -2885,506 +3005,512 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="44">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="B48" s="45">
-        <v>0000106874</v>
+        <v>0000106867</v>
       </c>
       <c r="C48" t="s" s="46">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D48" t="s" s="46">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F48" t="s" s="44">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G48" s="51">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="H48" s="52">
-        <v>125.57</v>
-      </c>
-      <c r="I48" t="s" s="53">
+        <v>470.12</v>
+      </c>
+      <c r="I48" s="53">
+        <v>52</v>
+      </c>
+      <c r="J48" t="s" s="48">
+        <v>115</v>
+      </c>
+      <c r="K48" t="s" s="49">
+        <v>116</v>
+      </c>
+      <c r="L48" s="0"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="44"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="44"/>
+      <c r="G49" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H49" s="52">
+        <v>24446.24</v>
+      </c>
+      <c r="I49" s="53"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="49"/>
+      <c r="L49" s="0"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="44">
+        <v>117</v>
+      </c>
+      <c r="B50" s="45">
+        <v>0000106752</v>
+      </c>
+      <c r="C50" t="s" s="46">
+        <v>118</v>
+      </c>
+      <c r="D50" t="s" s="46">
+        <v>100</v>
+      </c>
+      <c r="E50" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F50" t="s" s="44">
+        <v>119</v>
+      </c>
+      <c r="G50" s="51">
+        <v>10</v>
+      </c>
+      <c r="H50" s="52">
+        <v>1079.26</v>
+      </c>
+      <c r="I50" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J48" t="s" s="48">
-        <v>109</v>
-      </c>
-      <c r="K48" t="s" s="49">
-        <v>110</v>
-      </c>
-      <c r="L48" s="0"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B49" s="45">
-        <v>0000106874</v>
-      </c>
-      <c r="C49" t="s" s="46">
-        <v>89</v>
-      </c>
-      <c r="D49" t="s" s="46">
-        <v>107</v>
-      </c>
-      <c r="E49" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F49" t="s" s="44">
-        <v>111</v>
-      </c>
-      <c r="G49" s="51">
-        <v>5</v>
-      </c>
-      <c r="H49" s="52">
-        <v>712.26</v>
-      </c>
-      <c r="I49" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J49" t="s" s="48">
-        <v>112</v>
-      </c>
-      <c r="K49" t="s" s="49">
-        <v>110</v>
-      </c>
-      <c r="L49" s="0"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="44"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="44"/>
-      <c r="G50" t="s" s="51">
+      <c r="J50" t="s" s="48">
+        <v>120</v>
+      </c>
+      <c r="K50" t="s" s="49">
+        <v>121</v>
+      </c>
+      <c r="L50" s="0"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="44"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="44"/>
+      <c r="G51" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H50" s="52">
-        <v>3812.44</v>
-      </c>
-      <c r="I50" s="53"/>
-      <c r="J50" s="48"/>
-      <c r="K50" s="49"/>
-      <c r="L50" s="0"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="44">
-        <v>67</v>
-      </c>
-      <c r="B51" s="45">
-        <v>0000106877</v>
-      </c>
-      <c r="C51" t="s" s="46">
-        <v>113</v>
-      </c>
-      <c r="D51" t="s" s="46">
-        <v>107</v>
-      </c>
-      <c r="E51" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F51" t="s" s="44">
-        <v>114</v>
-      </c>
-      <c r="G51" s="51">
-        <v>40</v>
-      </c>
       <c r="H51" s="52">
-        <v>11.79</v>
-      </c>
-      <c r="I51" s="53">
-        <v>10</v>
-      </c>
-      <c r="J51" t="s" s="48">
-        <v>115</v>
-      </c>
-      <c r="K51" t="s" s="49">
-        <v>116</v>
-      </c>
+        <v>10792.6</v>
+      </c>
+      <c r="I51" s="53"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="49"/>
       <c r="L51" s="0"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="44">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="B52" s="45">
-        <v>0000106877</v>
+        <v>0000106883</v>
       </c>
       <c r="C52" t="s" s="46">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D52" t="s" s="46">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E52" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s" s="44">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G52" s="51">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H52" s="52">
-        <v>15.33</v>
+        <v>2078.21</v>
       </c>
       <c r="I52" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J52" t="s" s="48">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K52" t="s" s="49">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L52" s="0"/>
     </row>
     <row r="53">
-      <c r="A53" s="44"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="44"/>
-      <c r="G53" t="s" s="51">
+      <c r="A53" t="s" s="44">
+        <v>117</v>
+      </c>
+      <c r="B53" s="45">
+        <v>0000106883</v>
+      </c>
+      <c r="C53" t="s" s="46">
+        <v>122</v>
+      </c>
+      <c r="D53" t="s" s="46">
+        <v>100</v>
+      </c>
+      <c r="E53" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F53" t="s" s="44">
+        <v>119</v>
+      </c>
+      <c r="G53" s="51">
+        <v>23</v>
+      </c>
+      <c r="H53" s="52">
+        <v>1072.91</v>
+      </c>
+      <c r="I53" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J53" t="s" s="48">
+        <v>120</v>
+      </c>
+      <c r="K53" t="s" s="49">
+        <v>121</v>
+      </c>
+      <c r="L53" s="0"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="44"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="44"/>
+      <c r="G54" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H53" s="52">
-        <v>624.9</v>
-      </c>
-      <c r="I53" s="53"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="49"/>
-      <c r="L53" s="0"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B54" s="45">
-        <v>0000106854</v>
-      </c>
-      <c r="C54" t="s" s="46">
-        <v>119</v>
-      </c>
-      <c r="D54" t="s" s="46">
-        <v>120</v>
-      </c>
-      <c r="E54" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F54" t="s" s="44">
-        <v>121</v>
-      </c>
-      <c r="G54" s="51">
-        <v>2</v>
-      </c>
       <c r="H54" s="52">
-        <v>923.88</v>
-      </c>
-      <c r="I54" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J54" t="s" s="48">
-        <v>122</v>
-      </c>
-      <c r="K54" t="s" s="49">
-        <v>123</v>
-      </c>
+        <v>99492.49</v>
+      </c>
+      <c r="I54" s="53"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="49"/>
       <c r="L54" s="0"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="44">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B55" s="45">
-        <v>0000106854</v>
+        <v>0000106897</v>
       </c>
       <c r="C55" t="s" s="46">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s" s="46">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E55" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F55" t="s" s="44">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G55" s="51">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="H55" s="52">
-        <v>747.36</v>
+        <v>625.20</v>
       </c>
       <c r="I55" s="53">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="J55" t="s" s="48">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K55" t="s" s="49">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L55" s="0"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="44">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B56" s="45">
-        <v>0000106854</v>
+        <v>0000106897</v>
       </c>
       <c r="C56" t="s" s="46">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s" s="46">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E56" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s" s="44">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="G56" s="51">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H56" s="52">
-        <v>126.69</v>
-      </c>
-      <c r="I56" t="s" s="53">
-        <v>18</v>
+        <v>885.56</v>
+      </c>
+      <c r="I56" s="53">
+        <v>10</v>
       </c>
       <c r="J56" t="s" s="48">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="K56" t="s" s="49">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L56" s="0"/>
     </row>
     <row r="57">
-      <c r="A57" s="44"/>
-      <c r="B57" s="45"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="44"/>
-      <c r="G57" t="s" s="51">
-        <v>27</v>
+      <c r="A57" t="s" s="44">
+        <v>28</v>
+      </c>
+      <c r="B57" s="45">
+        <v>0000106897</v>
+      </c>
+      <c r="C57" t="s" s="46">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s" s="46">
+        <v>100</v>
+      </c>
+      <c r="E57" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F57" t="s" s="44">
+        <v>130</v>
+      </c>
+      <c r="G57" s="51">
+        <v>10</v>
       </c>
       <c r="H57" s="52">
-        <v>3595.86</v>
-      </c>
-      <c r="I57" s="53"/>
-      <c r="J57" s="48"/>
-      <c r="K57" s="49"/>
+        <v>968.33</v>
+      </c>
+      <c r="I57" s="53">
+        <v>30</v>
+      </c>
+      <c r="J57" t="s" s="48">
+        <v>131</v>
+      </c>
+      <c r="K57" t="s" s="49">
+        <v>127</v>
+      </c>
       <c r="L57" s="0"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="44">
+        <v>28</v>
+      </c>
+      <c r="B58" s="45">
+        <v>0000106897</v>
+      </c>
+      <c r="C58" t="s" s="46">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s" s="46">
+        <v>100</v>
+      </c>
+      <c r="E58" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F58" t="s" s="44">
+        <v>132</v>
+      </c>
+      <c r="G58" s="51">
+        <v>94</v>
+      </c>
+      <c r="H58" s="52">
+        <v>407.42</v>
+      </c>
+      <c r="I58" s="53">
+        <v>94</v>
+      </c>
+      <c r="J58" t="s" s="48">
+        <v>133</v>
+      </c>
+      <c r="K58" t="s" s="49">
+        <v>127</v>
+      </c>
+      <c r="L58" s="0"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="44">
+        <v>28</v>
+      </c>
+      <c r="B59" s="45">
+        <v>0000106897</v>
+      </c>
+      <c r="C59" t="s" s="46">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s" s="46">
+        <v>100</v>
+      </c>
+      <c r="E59" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F59" t="s" s="44">
+        <v>134</v>
+      </c>
+      <c r="G59" s="51">
+        <v>63</v>
+      </c>
+      <c r="H59" s="52">
+        <v>482.16</v>
+      </c>
+      <c r="I59" s="53">
+        <v>63</v>
+      </c>
+      <c r="J59" t="s" s="48">
+        <v>135</v>
+      </c>
+      <c r="K59" t="s" s="49">
+        <v>127</v>
+      </c>
+      <c r="L59" s="0"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="44"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="44"/>
+      <c r="G60" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H60" s="52">
+        <v>124724.46</v>
+      </c>
+      <c r="I60" s="53"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="49"/>
+      <c r="L60" s="0"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="44">
+        <v>28</v>
+      </c>
+      <c r="B61" s="45">
+        <v>0000106898</v>
+      </c>
+      <c r="C61" t="s" s="46">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s" s="46">
+        <v>100</v>
+      </c>
+      <c r="E61" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F61" t="s" s="44">
+        <v>136</v>
+      </c>
+      <c r="G61" s="51">
         <v>30</v>
       </c>
-      <c r="B58" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C58" t="s" s="46">
-        <v>31</v>
-      </c>
-      <c r="D58" t="s" s="46">
-        <v>120</v>
-      </c>
-      <c r="E58" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F58" t="s" s="44">
-        <v>33</v>
-      </c>
-      <c r="G58" s="51">
-        <v>5</v>
-      </c>
-      <c r="H58" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I58" t="s" s="53">
+      <c r="H61" s="52">
+        <v>552.87</v>
+      </c>
+      <c r="I61" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J58" t="s" s="48">
-        <v>34</v>
-      </c>
-      <c r="K58" t="s" s="49">
-        <v>35</v>
-      </c>
-      <c r="L58" s="0"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="44"/>
-      <c r="B59" s="45"/>
-      <c r="C59" s="46"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="44"/>
-      <c r="G59" t="s" s="51">
+      <c r="J61" t="s" s="48">
+        <v>137</v>
+      </c>
+      <c r="K61" t="s" s="49">
+        <v>127</v>
+      </c>
+      <c r="L61" s="0"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="44"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="46"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="44"/>
+      <c r="G62" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H59" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I59" s="53"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="49"/>
-      <c r="L59" s="0"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="44">
-        <v>126</v>
-      </c>
-      <c r="B60" s="45">
-        <v>0000106846</v>
-      </c>
-      <c r="C60" t="s" s="46">
+      <c r="H62" s="52">
+        <v>16586.1</v>
+      </c>
+      <c r="I62" s="53"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="49"/>
+      <c r="L62" s="0"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="44">
+        <v>28</v>
+      </c>
+      <c r="B63" s="45">
+        <v>0000106899</v>
+      </c>
+      <c r="C63" t="s" s="46">
+        <v>14</v>
+      </c>
+      <c r="D63" t="s" s="46">
+        <v>100</v>
+      </c>
+      <c r="E63" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F63" t="s" s="44">
+        <v>138</v>
+      </c>
+      <c r="G63" s="51">
+        <v>10</v>
+      </c>
+      <c r="H63" s="52">
+        <v>15.26</v>
+      </c>
+      <c r="I63" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J63" t="s" s="48">
+        <v>139</v>
+      </c>
+      <c r="K63" t="s" s="49">
         <v>127</v>
       </c>
-      <c r="D60" t="s" s="46">
-        <v>128</v>
-      </c>
-      <c r="E60" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F60" t="s" s="44">
-        <v>129</v>
-      </c>
-      <c r="G60" s="51">
-        <v>235</v>
-      </c>
-      <c r="H60" s="52">
-        <v>255.27</v>
-      </c>
-      <c r="I60" t="s" s="53">
+      <c r="L63" s="0"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="44"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="47"/>
+      <c r="F64" t="s" s="44">
         <v>18</v>
       </c>
-      <c r="J60" t="s" s="48">
-        <v>130</v>
-      </c>
-      <c r="K60" t="s" s="49">
-        <v>131</v>
-      </c>
-      <c r="L60" s="0"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="44"/>
-      <c r="B61" s="45"/>
-      <c r="C61" s="46"/>
-      <c r="D61" s="46"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="44"/>
-      <c r="G61" t="s" s="51">
+      <c r="G64" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H61" s="52">
-        <v>59988.45</v>
-      </c>
-      <c r="I61" s="53"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="49"/>
-      <c r="L61" s="0"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B62" s="45">
-        <v>0000106821</v>
-      </c>
-      <c r="C62" t="s" s="46">
-        <v>132</v>
-      </c>
-      <c r="D62" t="s" s="46">
-        <v>133</v>
-      </c>
-      <c r="E62" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F62" t="s" s="44">
-        <v>61</v>
-      </c>
-      <c r="G62" s="51">
-        <v>16</v>
-      </c>
-      <c r="H62" s="52">
-        <v>652.21</v>
-      </c>
-      <c r="I62" s="53">
-        <v>48</v>
-      </c>
-      <c r="J62" t="s" s="48">
-        <v>62</v>
-      </c>
-      <c r="K62" t="s" s="49">
-        <v>79</v>
-      </c>
-      <c r="L62" s="0"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="44"/>
-      <c r="B63" s="45"/>
-      <c r="C63" s="46"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="44"/>
-      <c r="G63" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H63" s="52">
-        <v>10435.36</v>
-      </c>
-      <c r="I63" s="53"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="49"/>
-      <c r="L63" s="0"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B64" s="45">
-        <v>0000106822</v>
-      </c>
-      <c r="C64" t="s" s="46">
-        <v>132</v>
-      </c>
-      <c r="D64" t="s" s="46">
-        <v>133</v>
-      </c>
-      <c r="E64" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F64" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="G64" s="51">
-        <v>70</v>
-      </c>
       <c r="H64" s="52">
-        <v>370.76</v>
-      </c>
-      <c r="I64" s="53">
-        <v>87.5</v>
+        <v>152.6</v>
+      </c>
+      <c r="I64" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J64" t="s" s="48">
-        <v>41</v>
-      </c>
-      <c r="K64" t="s" s="49">
-        <v>79</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K64" s="49"/>
       <c r="L64" s="0"/>
     </row>
     <row r="65">
@@ -3393,51 +3519,57 @@
       <c r="C65" s="46"/>
       <c r="D65" s="46"/>
       <c r="E65" s="47"/>
-      <c r="F65" s="44"/>
+      <c r="F65" s="44" t="s">
+        <v>145</v>
+      </c>
       <c r="G65" t="s" s="51">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="H65" s="52">
-        <v>25953.2</v>
-      </c>
-      <c r="I65" s="53"/>
-      <c r="J65" s="48"/>
+        <v>576749</v>
+      </c>
+      <c r="I65" s="53">
+        <v>490.75</v>
+      </c>
+      <c r="J65" s="48" t="s">
+        <v>146</v>
+      </c>
       <c r="K65" s="49"/>
       <c r="L65" s="0"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B66" s="45">
-        <v>0000106823</v>
+        <v>0000106623</v>
       </c>
       <c r="C66" t="s" s="46">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D66" t="s" s="46">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E66" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s" s="44">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="G66" s="51">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H66" s="52">
-        <v>565.75</v>
-      </c>
-      <c r="I66" s="53">
-        <v>30</v>
+        <v>265.45</v>
+      </c>
+      <c r="I66" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J66" t="s" s="48">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="K66" t="s" s="49">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="L66" s="0"/>
     </row>
@@ -3452,7 +3584,7 @@
         <v>27</v>
       </c>
       <c r="H67" s="52">
-        <v>5657.5</v>
+        <v>530.9</v>
       </c>
       <c r="I67" s="53"/>
       <c r="J67" s="48"/>
@@ -3461,181 +3593,145 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="44">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="B68" s="45">
-        <v>0000106869</v>
+        <v>0000106852</v>
       </c>
       <c r="C68" t="s" s="46">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="D68" t="s" s="46">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F68" t="s" s="44">
-        <v>137</v>
+        <v>24</v>
       </c>
       <c r="G68" s="51">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H68" s="52">
-        <v>943.26</v>
+        <v>228.24</v>
       </c>
       <c r="I68" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J68" t="s" s="48">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="K68" t="s" s="49">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="L68" s="0"/>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="44">
-        <v>134</v>
-      </c>
-      <c r="B69" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C69" t="s" s="46">
-        <v>135</v>
-      </c>
-      <c r="D69" t="s" s="46">
-        <v>136</v>
-      </c>
-      <c r="E69" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F69" t="s" s="44">
-        <v>139</v>
-      </c>
-      <c r="G69" s="51">
-        <v>25</v>
+      <c r="A69" s="44"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="44"/>
+      <c r="G69" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H69" s="52">
-        <v>275.11</v>
-      </c>
-      <c r="I69" s="53">
-        <v>6.25</v>
-      </c>
-      <c r="J69" t="s" s="48">
-        <v>140</v>
-      </c>
-      <c r="K69" t="s" s="49">
-        <v>20</v>
-      </c>
+        <v>11412</v>
+      </c>
+      <c r="I69" s="53"/>
+      <c r="J69" s="48"/>
+      <c r="K69" s="49"/>
       <c r="L69" s="0"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="44">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="B70" s="45">
-        <v>0000106869</v>
+        <v>0000106818</v>
       </c>
       <c r="C70" t="s" s="46">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="D70" t="s" s="46">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E70" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F70" t="s" s="44">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G70" s="51">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H70" s="52">
-        <v>361.58</v>
-      </c>
-      <c r="I70" t="s" s="53">
-        <v>18</v>
+        <v>214.85</v>
+      </c>
+      <c r="I70" s="53">
+        <v>25</v>
       </c>
       <c r="J70" t="s" s="48">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K70" t="s" s="49">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="L70" s="0"/>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="44">
-        <v>134</v>
-      </c>
-      <c r="B71" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C71" t="s" s="46">
-        <v>135</v>
-      </c>
-      <c r="D71" t="s" s="46">
-        <v>136</v>
-      </c>
-      <c r="E71" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F71" t="s" s="44">
-        <v>143</v>
-      </c>
-      <c r="G71" s="51">
-        <v>80</v>
+      <c r="A71" s="44"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="44"/>
+      <c r="G71" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H71" s="52">
-        <v>275.11</v>
-      </c>
-      <c r="I71" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J71" t="s" s="48">
-        <v>144</v>
-      </c>
-      <c r="K71" t="s" s="49">
-        <v>20</v>
-      </c>
+        <v>10742.5</v>
+      </c>
+      <c r="I71" s="53"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="49"/>
       <c r="L71" s="0"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="44">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="B72" s="45">
-        <v>0000106869</v>
+        <v>0000106825</v>
       </c>
       <c r="C72" t="s" s="46">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="D72" t="s" s="46">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E72" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F72" t="s" s="44">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G72" s="51">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="H72" s="52">
-        <v>361.58</v>
-      </c>
-      <c r="I72" t="s" s="53">
-        <v>18</v>
+        <v>316.89</v>
+      </c>
+      <c r="I72" s="53">
+        <v>72</v>
       </c>
       <c r="J72" t="s" s="48">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K72" t="s" s="49">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="L72" s="0"/>
     </row>
@@ -3650,7 +3746,7 @@
         <v>27</v>
       </c>
       <c r="H73" s="52">
-        <v>72763.81</v>
+        <v>15210.72</v>
       </c>
       <c r="I73" s="53"/>
       <c r="J73" s="48"/>
@@ -3659,309 +3755,325 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="44">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B74" s="45">
-        <v>0000106815</v>
+        <v>0000106880</v>
       </c>
       <c r="C74" t="s" s="46">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D74" t="s" s="46">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E74" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F74" t="s" s="44">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="G74" s="51">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H74" s="52">
-        <v>0</v>
-      </c>
-      <c r="I74" t="s" s="53">
-        <v>18</v>
+        <v>30.72</v>
+      </c>
+      <c r="I74" s="53">
+        <v>3.35</v>
       </c>
       <c r="J74" t="s" s="48">
-        <v>97</v>
-      </c>
-      <c r="K74" s="49"/>
+        <v>156</v>
+      </c>
+      <c r="K74" t="s" s="49">
+        <v>157</v>
+      </c>
       <c r="L74" s="0"/>
     </row>
     <row r="75">
-      <c r="A75" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B75" s="45">
-        <v>0000106815</v>
-      </c>
-      <c r="C75" t="s" s="46">
-        <v>147</v>
-      </c>
-      <c r="D75" t="s" s="46">
-        <v>136</v>
-      </c>
-      <c r="E75" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F75" t="s" s="44">
-        <v>99</v>
-      </c>
-      <c r="G75" s="51">
-        <v>200</v>
+      <c r="A75" s="44"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="46"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="47"/>
+      <c r="F75" s="44"/>
+      <c r="G75" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H75" s="52">
-        <v>0</v>
-      </c>
-      <c r="I75" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J75" t="s" s="48">
-        <v>100</v>
-      </c>
+        <v>1536</v>
+      </c>
+      <c r="I75" s="53"/>
+      <c r="J75" s="48"/>
       <c r="K75" s="49"/>
       <c r="L75" s="0"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="44">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B76" s="45">
-        <v>0000106815</v>
+        <v>0000106848</v>
       </c>
       <c r="C76" t="s" s="46">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D76" t="s" s="46">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E76" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F76" t="s" s="44">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="G76" s="51">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="H76" s="52">
-        <v>0</v>
-      </c>
-      <c r="I76" t="s" s="53">
-        <v>18</v>
+        <v>287.44</v>
+      </c>
+      <c r="I76" s="53">
+        <v>225</v>
       </c>
       <c r="J76" t="s" s="48">
-        <v>102</v>
-      </c>
-      <c r="K76" s="49"/>
+        <v>160</v>
+      </c>
+      <c r="K76" t="s" s="49">
+        <v>161</v>
+      </c>
       <c r="L76" s="0"/>
     </row>
     <row r="77">
-      <c r="A77" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B77" s="45">
-        <v>0000106815</v>
-      </c>
-      <c r="C77" t="s" s="46">
-        <v>147</v>
-      </c>
-      <c r="D77" t="s" s="46">
-        <v>136</v>
-      </c>
-      <c r="E77" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F77" t="s" s="44">
-        <v>103</v>
-      </c>
-      <c r="G77" s="51">
-        <v>200</v>
+      <c r="A77" s="44"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="46"/>
+      <c r="D77" s="46"/>
+      <c r="E77" s="47"/>
+      <c r="F77" s="44"/>
+      <c r="G77" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H77" s="52">
-        <v>0</v>
-      </c>
-      <c r="I77" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J77" t="s" s="48">
-        <v>104</v>
-      </c>
+        <v>51739.2</v>
+      </c>
+      <c r="I77" s="53"/>
+      <c r="J77" s="48"/>
       <c r="K77" s="49"/>
       <c r="L77" s="0"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="44">
-        <v>13</v>
+        <v>162</v>
       </c>
       <c r="B78" s="45">
-        <v>0000106815</v>
+        <v>0000106887</v>
       </c>
       <c r="C78" t="s" s="46">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="D78" t="s" s="46">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="E78" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s" s="44">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="G78" s="51">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="H78" s="52">
-        <v>0</v>
+        <v>213.19</v>
       </c>
       <c r="I78" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J78" t="s" s="48">
-        <v>106</v>
-      </c>
-      <c r="K78" s="49"/>
+        <v>25</v>
+      </c>
+      <c r="K78" t="s" s="49">
+        <v>166</v>
+      </c>
       <c r="L78" s="0"/>
     </row>
     <row r="79">
-      <c r="A79" s="44"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="44"/>
-      <c r="G79" t="s" s="51">
-        <v>27</v>
+      <c r="A79" t="s" s="44">
+        <v>162</v>
+      </c>
+      <c r="B79" s="45">
+        <v>0000106887</v>
+      </c>
+      <c r="C79" t="s" s="46">
+        <v>163</v>
+      </c>
+      <c r="D79" t="s" s="46">
+        <v>164</v>
+      </c>
+      <c r="E79" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F79" t="s" s="44">
+        <v>167</v>
+      </c>
+      <c r="G79" s="51">
+        <v>25</v>
       </c>
       <c r="H79" s="52">
-        <v>0</v>
-      </c>
-      <c r="I79" s="53"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="49"/>
+        <v>230.96</v>
+      </c>
+      <c r="I79" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J79" t="s" s="48">
+        <v>168</v>
+      </c>
+      <c r="K79" t="s" s="49">
+        <v>166</v>
+      </c>
       <c r="L79" s="0"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="44">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="B80" s="45">
-        <v>0000106867</v>
+        <v>0000106887</v>
       </c>
       <c r="C80" t="s" s="46">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s" s="46">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s" s="44">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="G80" s="51">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="H80" s="52">
-        <v>470.12</v>
-      </c>
-      <c r="I80" s="53">
-        <v>52</v>
+        <v>401.58</v>
+      </c>
+      <c r="I80" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J80" t="s" s="48">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="K80" t="s" s="49">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="L80" s="0"/>
     </row>
     <row r="81">
-      <c r="A81" s="44"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="46"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="47"/>
+      <c r="A81" t="s" s="44">
+        <v>162</v>
+      </c>
+      <c r="B81" s="45">
+        <v>0000106887</v>
+      </c>
+      <c r="C81" t="s" s="46">
+        <v>163</v>
+      </c>
+      <c r="D81" t="s" s="46">
+        <v>164</v>
+      </c>
+      <c r="E81" t="s" s="47">
+        <v>16</v>
+      </c>
       <c r="F81" t="s" s="44">
+        <v>171</v>
+      </c>
+      <c r="G81" s="51">
+        <v>2</v>
+      </c>
+      <c r="H81" s="52">
+        <v>159.24</v>
+      </c>
+      <c r="I81" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="G81" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H81" s="52">
-        <v>24446.24</v>
-      </c>
-      <c r="I81" s="53" t="s">
+      <c r="J81" t="s" s="48">
+        <v>172</v>
+      </c>
+      <c r="K81" t="s" s="49">
+        <v>166</v>
+      </c>
+      <c r="L81" s="0"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="44">
+        <v>162</v>
+      </c>
+      <c r="B82" s="45">
+        <v>0000106887</v>
+      </c>
+      <c r="C82" t="s" s="46">
+        <v>163</v>
+      </c>
+      <c r="D82" t="s" s="46">
+        <v>164</v>
+      </c>
+      <c r="E82" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F82" t="s" s="44">
+        <v>173</v>
+      </c>
+      <c r="G82" s="51">
+        <v>15</v>
+      </c>
+      <c r="H82" s="52">
+        <v>105.76</v>
+      </c>
+      <c r="I82" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J81" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K81" s="49"/>
-      <c r="L81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="44"/>
-      <c r="B82" s="45"/>
-      <c r="C82" s="46"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="47"/>
-      <c r="F82" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="G82" t="s" s="51">
-        <v>56</v>
-      </c>
-      <c r="H82" s="52">
-        <v>424401.93</v>
-      </c>
-      <c r="I82" s="53">
-        <v>615.5</v>
-      </c>
-      <c r="J82" s="48" t="s">
-        <v>156</v>
-      </c>
-      <c r="K82" s="49"/>
+      <c r="J82" t="s" s="48">
+        <v>174</v>
+      </c>
+      <c r="K82" t="s" s="49">
+        <v>166</v>
+      </c>
       <c r="L82" s="0"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="44">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="B83" s="45">
-        <v>0000106623</v>
+        <v>0000106887</v>
       </c>
       <c r="C83" t="s" s="46">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="D83" t="s" s="46">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="E83" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F83" t="s" s="44">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="G83" s="51">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H83" s="52">
-        <v>265.45</v>
+        <v>310.11</v>
       </c>
       <c r="I83" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J83" t="s" s="48">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="K83" t="s" s="49">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="L83" s="0"/>
     </row>
@@ -3976,7 +4088,7 @@
         <v>27</v>
       </c>
       <c r="H84" s="52">
-        <v>530.9</v>
+        <v>22972.29</v>
       </c>
       <c r="I84" s="53"/>
       <c r="J84" s="48"/>
@@ -3985,37 +4097,37 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="44">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B85" s="45">
-        <v>0000106852</v>
+        <v>0000106877</v>
       </c>
       <c r="C85" t="s" s="46">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D85" t="s" s="46">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="E85" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F85" t="s" s="44">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="G85" s="51">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="H85" s="52">
-        <v>228.24</v>
-      </c>
-      <c r="I85" t="s" s="53">
-        <v>18</v>
+        <v>8.40</v>
+      </c>
+      <c r="I85" s="53">
+        <v>33</v>
       </c>
       <c r="J85" t="s" s="48">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="K85" t="s" s="49">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="L85" s="0"/>
     </row>
@@ -4030,7 +4142,7 @@
         <v>27</v>
       </c>
       <c r="H86" s="52">
-        <v>11412</v>
+        <v>8400</v>
       </c>
       <c r="I86" s="53"/>
       <c r="J86" s="48"/>
@@ -4039,37 +4151,37 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="44">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B87" s="45">
-        <v>0000106818</v>
+        <v>0000106891</v>
       </c>
       <c r="C87" t="s" s="46">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="D87" t="s" s="46">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E87" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F87" t="s" s="44">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="G87" s="51">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="H87" s="52">
-        <v>214.85</v>
-      </c>
-      <c r="I87" s="53">
-        <v>25</v>
+        <v>311.55</v>
+      </c>
+      <c r="I87" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J87" t="s" s="48">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="K87" t="s" s="49">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L87" s="0"/>
     </row>
@@ -4084,7 +4196,7 @@
         <v>27</v>
       </c>
       <c r="H88" s="52">
-        <v>10742.5</v>
+        <v>42059.25</v>
       </c>
       <c r="I88" s="53"/>
       <c r="J88" s="48"/>
@@ -4093,37 +4205,37 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="44">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B89" s="45">
-        <v>0000106825</v>
+        <v>0000106778</v>
       </c>
       <c r="C89" t="s" s="46">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="D89" t="s" s="46">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E89" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s" s="44">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G89" s="51">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H89" s="52">
-        <v>316.89</v>
-      </c>
-      <c r="I89" s="53">
-        <v>72</v>
+        <v>2250</v>
+      </c>
+      <c r="I89" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J89" t="s" s="48">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s" s="49">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="L89" s="0"/>
     </row>
@@ -4138,7 +4250,7 @@
         <v>27</v>
       </c>
       <c r="H90" s="52">
-        <v>15210.72</v>
+        <v>11250</v>
       </c>
       <c r="I90" s="53"/>
       <c r="J90" s="48"/>
@@ -4147,325 +4259,289 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="44">
-        <v>36</v>
+        <v>184</v>
       </c>
       <c r="B91" s="45">
-        <v>0000106880</v>
+        <v>0000106893</v>
       </c>
       <c r="C91" t="s" s="46">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="D91" t="s" s="46">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E91" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F91" t="s" s="44">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="G91" s="51">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H91" s="52">
-        <v>30.72</v>
-      </c>
-      <c r="I91" s="53">
-        <v>3.35</v>
+        <v>3443.62</v>
+      </c>
+      <c r="I91" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J91" t="s" s="48">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="K91" t="s" s="49">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="L91" s="0"/>
     </row>
     <row r="92">
-      <c r="A92" s="44"/>
-      <c r="B92" s="45"/>
-      <c r="C92" s="46"/>
-      <c r="D92" s="46"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="44"/>
-      <c r="G92" t="s" s="51">
+      <c r="A92" t="s" s="44">
+        <v>184</v>
+      </c>
+      <c r="B92" s="45">
+        <v>0000106893</v>
+      </c>
+      <c r="C92" t="s" s="46">
+        <v>185</v>
+      </c>
+      <c r="D92" t="s" s="46">
+        <v>180</v>
+      </c>
+      <c r="E92" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F92" t="s" s="44">
+        <v>189</v>
+      </c>
+      <c r="G92" s="51">
+        <v>10</v>
+      </c>
+      <c r="H92" s="52">
+        <v>1419.01</v>
+      </c>
+      <c r="I92" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J92" t="s" s="48">
+        <v>190</v>
+      </c>
+      <c r="K92" t="s" s="49">
+        <v>188</v>
+      </c>
+      <c r="L92" s="0"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="44"/>
+      <c r="B93" s="45"/>
+      <c r="C93" s="46"/>
+      <c r="D93" s="46"/>
+      <c r="E93" s="47"/>
+      <c r="F93" s="44"/>
+      <c r="G93" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H92" s="52">
-        <v>1536</v>
-      </c>
-      <c r="I92" s="53"/>
-      <c r="J92" s="48"/>
-      <c r="K92" s="49"/>
-      <c r="L92" s="0"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="44">
-        <v>67</v>
-      </c>
-      <c r="B93" s="45">
-        <v>0000106848</v>
-      </c>
-      <c r="C93" t="s" s="46">
-        <v>165</v>
-      </c>
-      <c r="D93" t="s" s="46">
-        <v>158</v>
-      </c>
-      <c r="E93" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F93" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G93" s="51">
-        <v>180</v>
-      </c>
       <c r="H93" s="52">
-        <v>287.44</v>
-      </c>
-      <c r="I93" s="53">
-        <v>225</v>
-      </c>
-      <c r="J93" t="s" s="48">
-        <v>78</v>
-      </c>
-      <c r="K93" t="s" s="49">
-        <v>166</v>
-      </c>
+        <v>48626.3</v>
+      </c>
+      <c r="I93" s="53"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="49"/>
       <c r="L93" s="0"/>
     </row>
     <row r="94">
-      <c r="A94" s="44"/>
-      <c r="B94" s="45"/>
-      <c r="C94" s="46"/>
-      <c r="D94" s="46"/>
-      <c r="E94" s="47"/>
-      <c r="F94" s="44"/>
-      <c r="G94" t="s" s="51">
+      <c r="A94" t="s" s="44">
+        <v>69</v>
+      </c>
+      <c r="B94" s="45">
+        <v>0000106894</v>
+      </c>
+      <c r="C94" t="s" s="46">
+        <v>191</v>
+      </c>
+      <c r="D94" t="s" s="46">
+        <v>192</v>
+      </c>
+      <c r="E94" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F94" t="s" s="44">
+        <v>193</v>
+      </c>
+      <c r="G94" s="51">
+        <v>30</v>
+      </c>
+      <c r="H94" s="52">
+        <v>19.15</v>
+      </c>
+      <c r="I94" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J94" t="s" s="48">
+        <v>194</v>
+      </c>
+      <c r="K94" t="s" s="49">
+        <v>195</v>
+      </c>
+      <c r="L94" s="0"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="44"/>
+      <c r="B95" s="45"/>
+      <c r="C95" s="46"/>
+      <c r="D95" s="46"/>
+      <c r="E95" s="47"/>
+      <c r="F95" s="44"/>
+      <c r="G95" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H94" s="52">
-        <v>51739.2</v>
-      </c>
-      <c r="I94" s="53"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="49"/>
-      <c r="L94" s="0"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="44">
-        <v>167</v>
-      </c>
-      <c r="B95" s="45">
-        <v>0000106887</v>
-      </c>
-      <c r="C95" t="s" s="46">
-        <v>168</v>
-      </c>
-      <c r="D95" t="s" s="46">
-        <v>169</v>
-      </c>
-      <c r="E95" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F95" t="s" s="44">
-        <v>170</v>
-      </c>
-      <c r="G95" s="51">
-        <v>25</v>
-      </c>
       <c r="H95" s="52">
-        <v>213.19</v>
-      </c>
-      <c r="I95" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J95" t="s" s="48">
-        <v>75</v>
-      </c>
-      <c r="K95" t="s" s="49">
-        <v>171</v>
-      </c>
+        <v>574.5</v>
+      </c>
+      <c r="I95" s="53"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="0"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="44">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="B96" s="45">
-        <v>0000106887</v>
+        <v>0000106884</v>
       </c>
       <c r="C96" t="s" s="46">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="D96" t="s" s="46">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="E96" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F96" t="s" s="44">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="G96" s="51">
-        <v>25</v>
+        <v>504</v>
       </c>
       <c r="H96" s="52">
-        <v>230.96</v>
+        <v>22.10</v>
       </c>
       <c r="I96" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J96" t="s" s="48">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="K96" t="s" s="49">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="L96" s="0"/>
     </row>
     <row r="97">
-      <c r="A97" t="s" s="44">
-        <v>167</v>
-      </c>
-      <c r="B97" s="45">
-        <v>0000106887</v>
-      </c>
-      <c r="C97" t="s" s="46">
-        <v>168</v>
-      </c>
-      <c r="D97" t="s" s="46">
-        <v>169</v>
-      </c>
-      <c r="E97" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F97" t="s" s="44">
-        <v>174</v>
-      </c>
-      <c r="G97" s="51">
-        <v>14</v>
+      <c r="A97" s="44"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="46"/>
+      <c r="D97" s="46"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="44"/>
+      <c r="G97" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H97" s="52">
-        <v>401.58</v>
-      </c>
-      <c r="I97" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J97" t="s" s="48">
-        <v>175</v>
-      </c>
-      <c r="K97" t="s" s="49">
-        <v>171</v>
-      </c>
+        <v>11138.4</v>
+      </c>
+      <c r="I97" s="53"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="0"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="44">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="B98" s="45">
-        <v>0000106887</v>
+        <v>0000106850</v>
       </c>
       <c r="C98" t="s" s="46">
-        <v>168</v>
+        <v>22</v>
       </c>
       <c r="D98" t="s" s="46">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="E98" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F98" t="s" s="44">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="G98" s="51">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H98" s="52">
-        <v>159.24</v>
-      </c>
-      <c r="I98" t="s" s="53">
-        <v>18</v>
+        <v>651.07</v>
+      </c>
+      <c r="I98" s="53">
+        <v>48</v>
       </c>
       <c r="J98" t="s" s="48">
-        <v>177</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="49">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="L98" s="0"/>
     </row>
     <row r="99">
-      <c r="A99" t="s" s="44">
-        <v>167</v>
-      </c>
-      <c r="B99" s="45">
-        <v>0000106887</v>
-      </c>
-      <c r="C99" t="s" s="46">
-        <v>168</v>
-      </c>
-      <c r="D99" t="s" s="46">
-        <v>169</v>
-      </c>
-      <c r="E99" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F99" t="s" s="44">
-        <v>178</v>
-      </c>
-      <c r="G99" s="51">
-        <v>15</v>
+      <c r="A99" s="44"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="46"/>
+      <c r="D99" s="46"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="44"/>
+      <c r="G99" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H99" s="52">
-        <v>105.76</v>
-      </c>
-      <c r="I99" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J99" t="s" s="48">
-        <v>179</v>
-      </c>
-      <c r="K99" t="s" s="49">
-        <v>171</v>
-      </c>
+        <v>10417.12</v>
+      </c>
+      <c r="I99" s="53"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="0"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="44">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="B100" s="45">
-        <v>0000106887</v>
+        <v>0000106876</v>
       </c>
       <c r="C100" t="s" s="46">
-        <v>168</v>
+        <v>70</v>
       </c>
       <c r="D100" t="s" s="46">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="E100" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F100" t="s" s="44">
+        <v>159</v>
+      </c>
+      <c r="G100" s="51">
         <v>180</v>
       </c>
-      <c r="G100" s="51">
-        <v>14</v>
-      </c>
       <c r="H100" s="52">
-        <v>310.11</v>
-      </c>
-      <c r="I100" t="s" s="53">
-        <v>18</v>
+        <v>280.45</v>
+      </c>
+      <c r="I100" s="53">
+        <v>225</v>
       </c>
       <c r="J100" t="s" s="48">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="K100" t="s" s="49">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="L100" s="0"/>
     </row>
@@ -4480,7 +4556,7 @@
         <v>27</v>
       </c>
       <c r="H101" s="52">
-        <v>22972.29</v>
+        <v>50481</v>
       </c>
       <c r="I101" s="53"/>
       <c r="J101" s="48"/>
@@ -4489,92 +4565,104 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="44">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="B102" s="45">
-        <v>0000106877</v>
+        <v>0000106325</v>
       </c>
       <c r="C102" t="s" s="46">
-        <v>113</v>
+        <v>205</v>
       </c>
       <c r="D102" t="s" s="46">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="E102" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F102" t="s" s="44">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="G102" s="51">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H102" s="52">
-        <v>8.40</v>
-      </c>
-      <c r="I102" s="53">
-        <v>33</v>
+        <v>88.67</v>
+      </c>
+      <c r="I102" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J102" t="s" s="48">
-        <v>184</v>
-      </c>
-      <c r="K102" t="s" s="49">
-        <v>116</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="K102" s="49"/>
       <c r="L102" s="0"/>
     </row>
     <row r="103">
-      <c r="A103" s="44"/>
-      <c r="B103" s="45"/>
-      <c r="C103" s="46"/>
-      <c r="D103" s="46"/>
-      <c r="E103" s="47"/>
-      <c r="F103" s="44"/>
-      <c r="G103" t="s" s="51">
-        <v>27</v>
+      <c r="A103" t="s" s="44">
+        <v>204</v>
+      </c>
+      <c r="B103" s="45">
+        <v>0000106325</v>
+      </c>
+      <c r="C103" t="s" s="46">
+        <v>205</v>
+      </c>
+      <c r="D103" t="s" s="46">
+        <v>201</v>
+      </c>
+      <c r="E103" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F103" t="s" s="44">
+        <v>208</v>
+      </c>
+      <c r="G103" s="51">
+        <v>1</v>
       </c>
       <c r="H103" s="52">
-        <v>8400</v>
-      </c>
-      <c r="I103" s="53"/>
-      <c r="J103" s="48"/>
+        <v>507.87</v>
+      </c>
+      <c r="I103" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J103" t="s" s="48">
+        <v>209</v>
+      </c>
       <c r="K103" s="49"/>
       <c r="L103" s="0"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="44">
-        <v>30</v>
+        <v>204</v>
       </c>
       <c r="B104" s="45">
-        <v>0000106778</v>
+        <v>0000106325</v>
       </c>
       <c r="C104" t="s" s="46">
-        <v>31</v>
+        <v>205</v>
       </c>
       <c r="D104" t="s" s="46">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E104" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F104" t="s" s="44">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="G104" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H104" s="52">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="I104" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J104" t="s" s="48">
-        <v>34</v>
-      </c>
-      <c r="K104" t="s" s="49">
-        <v>35</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="K104" s="49"/>
       <c r="L104" s="0"/>
     </row>
     <row r="105">
@@ -4583,304 +4671,324 @@
       <c r="C105" s="46"/>
       <c r="D105" s="46"/>
       <c r="E105" s="47"/>
-      <c r="F105" s="44"/>
+      <c r="F105" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G105" t="s" s="51">
         <v>27</v>
       </c>
       <c r="H105" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I105" s="53"/>
-      <c r="J105" s="48"/>
+        <v>596.54</v>
+      </c>
+      <c r="I105" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K105" s="49"/>
       <c r="L105" s="0"/>
     </row>
     <row r="106">
-      <c r="A106" t="s" s="44">
-        <v>67</v>
-      </c>
-      <c r="B106" s="45">
-        <v>0000106884</v>
-      </c>
-      <c r="C106" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="D106" t="s" s="46">
-        <v>186</v>
-      </c>
-      <c r="E106" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F106" t="s" s="44">
-        <v>70</v>
-      </c>
-      <c r="G106" s="51">
-        <v>504</v>
+      <c r="A106" s="44"/>
+      <c r="B106" s="45"/>
+      <c r="C106" s="46"/>
+      <c r="D106" s="46"/>
+      <c r="E106" s="47"/>
+      <c r="F106" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="G106" t="s" s="51">
+        <v>144</v>
       </c>
       <c r="H106" s="52">
-        <v>22.10</v>
-      </c>
-      <c r="I106" t="s" s="53">
+        <v>297686.72</v>
+      </c>
+      <c r="I106" s="53">
+        <v>631.35</v>
+      </c>
+      <c r="J106" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="K106" s="49"/>
+      <c r="L106" s="0"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="44">
+        <v>50</v>
+      </c>
+      <c r="B107" s="45">
+        <v>0000106815</v>
+      </c>
+      <c r="C107" t="s" s="46">
+        <v>212</v>
+      </c>
+      <c r="D107" t="s" s="46">
+        <v>213</v>
+      </c>
+      <c r="E107" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F107" t="s" s="44">
+        <v>52</v>
+      </c>
+      <c r="G107" s="51">
+        <v>200</v>
+      </c>
+      <c r="H107" s="52">
+        <v>0</v>
+      </c>
+      <c r="I107" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J106" t="s" s="48">
-        <v>71</v>
-      </c>
-      <c r="K106" t="s" s="49">
-        <v>187</v>
-      </c>
-      <c r="L106" s="0"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="44"/>
-      <c r="B107" s="45"/>
-      <c r="C107" s="46"/>
-      <c r="D107" s="46"/>
-      <c r="E107" s="47"/>
-      <c r="F107" s="44"/>
-      <c r="G107" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H107" s="52">
-        <v>11138.4</v>
-      </c>
-      <c r="I107" s="53"/>
-      <c r="J107" s="48"/>
+      <c r="J107" t="s" s="48">
+        <v>53</v>
+      </c>
       <c r="K107" s="49"/>
       <c r="L107" s="0"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="44">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B108" s="45">
-        <v>0000106850</v>
+        <v>0000106815</v>
       </c>
       <c r="C108" t="s" s="46">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="D108" t="s" s="46">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="E108" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F108" t="s" s="44">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G108" s="51">
+        <v>200</v>
+      </c>
+      <c r="H108" s="52">
+        <v>0</v>
+      </c>
+      <c r="I108" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J108" t="s" s="48">
+        <v>56</v>
+      </c>
+      <c r="K108" s="49"/>
+      <c r="L108" s="0"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="44">
+        <v>50</v>
+      </c>
+      <c r="B109" s="45">
+        <v>0000106815</v>
+      </c>
+      <c r="C109" t="s" s="46">
+        <v>212</v>
+      </c>
+      <c r="D109" t="s" s="46">
+        <v>213</v>
+      </c>
+      <c r="E109" t="s" s="47">
         <v>16</v>
       </c>
-      <c r="H108" s="52">
-        <v>651.07</v>
-      </c>
-      <c r="I108" s="53">
-        <v>48</v>
-      </c>
-      <c r="J108" t="s" s="48">
-        <v>62</v>
-      </c>
-      <c r="K108" t="s" s="49">
-        <v>189</v>
-      </c>
-      <c r="L108" s="0"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="44"/>
-      <c r="B109" s="45"/>
-      <c r="C109" s="46"/>
-      <c r="D109" s="46"/>
-      <c r="E109" s="47"/>
-      <c r="F109" s="44"/>
-      <c r="G109" t="s" s="51">
-        <v>27</v>
+      <c r="F109" t="s" s="44">
+        <v>57</v>
+      </c>
+      <c r="G109" s="51">
+        <v>400</v>
       </c>
       <c r="H109" s="52">
-        <v>10417.12</v>
-      </c>
-      <c r="I109" s="53"/>
-      <c r="J109" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I109" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J109" t="s" s="48">
+        <v>58</v>
+      </c>
       <c r="K109" s="49"/>
       <c r="L109" s="0"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="44">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B110" s="45">
-        <v>0000106876</v>
+        <v>0000106815</v>
       </c>
       <c r="C110" t="s" s="46">
-        <v>113</v>
+        <v>212</v>
       </c>
       <c r="D110" t="s" s="46">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="E110" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F110" t="s" s="44">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="G110" s="51">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H110" s="52">
-        <v>280.45</v>
-      </c>
-      <c r="I110" s="53">
-        <v>225</v>
+        <v>0</v>
+      </c>
+      <c r="I110" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J110" t="s" s="48">
-        <v>78</v>
-      </c>
-      <c r="K110" t="s" s="49">
-        <v>190</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="K110" s="49"/>
       <c r="L110" s="0"/>
     </row>
     <row r="111">
-      <c r="A111" s="44"/>
-      <c r="B111" s="45"/>
-      <c r="C111" s="46"/>
-      <c r="D111" s="46"/>
-      <c r="E111" s="47"/>
-      <c r="F111" s="44"/>
-      <c r="G111" t="s" s="51">
-        <v>27</v>
+      <c r="A111" t="s" s="44">
+        <v>50</v>
+      </c>
+      <c r="B111" s="45">
+        <v>0000106815</v>
+      </c>
+      <c r="C111" t="s" s="46">
+        <v>212</v>
+      </c>
+      <c r="D111" t="s" s="46">
+        <v>213</v>
+      </c>
+      <c r="E111" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F111" t="s" s="44">
+        <v>61</v>
+      </c>
+      <c r="G111" s="51">
+        <v>200</v>
       </c>
       <c r="H111" s="52">
-        <v>50481</v>
-      </c>
-      <c r="I111" s="53"/>
-      <c r="J111" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I111" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J111" t="s" s="48">
+        <v>62</v>
+      </c>
       <c r="K111" s="49"/>
       <c r="L111" s="0"/>
     </row>
     <row r="112">
-      <c r="A112" t="s" s="44">
-        <v>191</v>
-      </c>
-      <c r="B112" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C112" t="s" s="46">
-        <v>192</v>
-      </c>
-      <c r="D112" t="s" s="46">
-        <v>188</v>
-      </c>
-      <c r="E112" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F112" t="s" s="44">
-        <v>193</v>
-      </c>
-      <c r="G112" s="51">
-        <v>1</v>
+      <c r="A112" s="44"/>
+      <c r="B112" s="45"/>
+      <c r="C112" s="46"/>
+      <c r="D112" s="46"/>
+      <c r="E112" s="47"/>
+      <c r="F112" s="44"/>
+      <c r="G112" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H112" s="52">
-        <v>88.67</v>
-      </c>
-      <c r="I112" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J112" t="s" s="48">
-        <v>194</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I112" s="53"/>
+      <c r="J112" s="48"/>
       <c r="K112" s="49"/>
       <c r="L112" s="0"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="44">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="B113" s="45">
-        <v>0000106325</v>
+        <v>0000106805</v>
       </c>
       <c r="C113" t="s" s="46">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="D113" t="s" s="46">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="E113" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s" s="44">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="G113" s="51">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H113" s="52">
-        <v>507.87</v>
-      </c>
-      <c r="I113" t="s" s="53">
-        <v>18</v>
+        <v>11.24</v>
+      </c>
+      <c r="I113" s="53">
+        <v>3.3</v>
       </c>
       <c r="J113" t="s" s="48">
-        <v>196</v>
-      </c>
-      <c r="K113" s="49"/>
+        <v>179</v>
+      </c>
+      <c r="K113" t="s" s="49">
+        <v>218</v>
+      </c>
       <c r="L113" s="0"/>
     </row>
     <row r="114">
-      <c r="A114" t="s" s="44">
-        <v>191</v>
-      </c>
-      <c r="B114" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C114" t="s" s="46">
-        <v>192</v>
-      </c>
-      <c r="D114" t="s" s="46">
-        <v>188</v>
-      </c>
-      <c r="E114" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F114" t="s" s="44">
-        <v>197</v>
-      </c>
-      <c r="G114" s="51">
-        <v>1</v>
+      <c r="A114" s="44"/>
+      <c r="B114" s="45"/>
+      <c r="C114" s="46"/>
+      <c r="D114" s="46"/>
+      <c r="E114" s="47"/>
+      <c r="F114" s="44"/>
+      <c r="G114" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H114" s="52">
-        <v>0</v>
-      </c>
-      <c r="I114" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J114" t="s" s="48">
-        <v>198</v>
-      </c>
+        <v>1124</v>
+      </c>
+      <c r="I114" s="53"/>
+      <c r="J114" s="48"/>
       <c r="K114" s="49"/>
       <c r="L114" s="0"/>
     </row>
     <row r="115">
-      <c r="A115" s="44"/>
-      <c r="B115" s="45"/>
-      <c r="C115" s="46"/>
-      <c r="D115" s="46"/>
-      <c r="E115" s="47"/>
+      <c r="A115" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B115" s="45">
+        <v>0000106824</v>
+      </c>
+      <c r="C115" t="s" s="46">
+        <v>88</v>
+      </c>
+      <c r="D115" t="s" s="46">
+        <v>217</v>
+      </c>
+      <c r="E115" t="s" s="47">
+        <v>16</v>
+      </c>
       <c r="F115" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G115" t="s" s="51">
-        <v>27</v>
+        <v>152</v>
+      </c>
+      <c r="G115" s="51">
+        <v>48</v>
       </c>
       <c r="H115" s="52">
-        <v>596.54</v>
-      </c>
-      <c r="I115" s="53" t="s">
-        <v>18</v>
+        <v>316.89</v>
+      </c>
+      <c r="I115" s="53">
+        <v>72</v>
       </c>
       <c r="J115" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K115" s="49"/>
+        <v>153</v>
+      </c>
+      <c r="K115" t="s" s="49">
+        <v>218</v>
+      </c>
       <c r="L115" s="0"/>
     </row>
     <row r="116">
@@ -4889,57 +4997,51 @@
       <c r="C116" s="46"/>
       <c r="D116" s="46"/>
       <c r="E116" s="47"/>
-      <c r="F116" s="44" t="s">
-        <v>201</v>
-      </c>
+      <c r="F116" s="44"/>
       <c r="G116" t="s" s="51">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="H116" s="52">
-        <v>206426.67</v>
-      </c>
-      <c r="I116" s="53">
-        <v>631.35</v>
-      </c>
-      <c r="J116" s="48" t="s">
-        <v>202</v>
-      </c>
+        <v>15210.72</v>
+      </c>
+      <c r="I116" s="53"/>
+      <c r="J116" s="48"/>
       <c r="K116" s="49"/>
       <c r="L116" s="0"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B117" s="45">
-        <v>0000106805</v>
+        <v>0000106881</v>
       </c>
       <c r="C117" t="s" s="46">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="D117" t="s" s="46">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="E117" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F117" t="s" s="44">
-        <v>183</v>
+        <v>93</v>
       </c>
       <c r="G117" s="51">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H117" s="52">
-        <v>11.24</v>
+        <v>370.33</v>
       </c>
       <c r="I117" s="53">
-        <v>3.3</v>
+        <v>87.5</v>
       </c>
       <c r="J117" t="s" s="48">
-        <v>184</v>
+        <v>94</v>
       </c>
       <c r="K117" t="s" s="49">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="L117" s="0"/>
     </row>
@@ -4954,7 +5056,7 @@
         <v>27</v>
       </c>
       <c r="H118" s="52">
-        <v>1124</v>
+        <v>25923.1</v>
       </c>
       <c r="I118" s="53"/>
       <c r="J118" s="48"/>
@@ -4963,37 +5065,37 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="44">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B119" s="45">
-        <v>0000106824</v>
+        <v>0000106778</v>
       </c>
       <c r="C119" t="s" s="46">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="D119" t="s" s="46">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="E119" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F119" t="s" s="44">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G119" s="51">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H119" s="52">
-        <v>316.89</v>
-      </c>
-      <c r="I119" s="53">
-        <v>72</v>
+        <v>2250</v>
+      </c>
+      <c r="I119" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J119" t="s" s="48">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K119" t="s" s="49">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="L119" s="0"/>
     </row>
@@ -5008,7 +5110,7 @@
         <v>27</v>
       </c>
       <c r="H120" s="52">
-        <v>15210.72</v>
+        <v>11250</v>
       </c>
       <c r="I120" s="53"/>
       <c r="J120" s="48"/>
@@ -5017,34 +5119,34 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="44">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B121" s="45">
-        <v>0000106881</v>
+        <v>0000106884</v>
       </c>
       <c r="C121" t="s" s="46">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="D121" t="s" s="46">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="E121" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F121" t="s" s="44">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="G121" s="51">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="H121" s="52">
-        <v>370.33</v>
+        <v>280.25</v>
       </c>
       <c r="I121" s="53">
-        <v>87.5</v>
+        <v>225</v>
       </c>
       <c r="J121" t="s" s="48">
-        <v>41</v>
+        <v>160</v>
       </c>
       <c r="K121" t="s" s="49">
         <v>200</v>
@@ -5062,7 +5164,7 @@
         <v>27</v>
       </c>
       <c r="H122" s="52">
-        <v>25923.1</v>
+        <v>50445</v>
       </c>
       <c r="I122" s="53"/>
       <c r="J122" s="48"/>
@@ -5071,92 +5173,98 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="44">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B123" s="45">
-        <v>0000106778</v>
+        <v>0000106895</v>
       </c>
       <c r="C123" t="s" s="46">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="D123" t="s" s="46">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="E123" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F123" t="s" s="44">
-        <v>33</v>
+        <v>181</v>
       </c>
       <c r="G123" s="51">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="H123" s="52">
-        <v>2250</v>
+        <v>311.29</v>
       </c>
       <c r="I123" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J123" t="s" s="48">
-        <v>34</v>
+        <v>222</v>
       </c>
       <c r="K123" t="s" s="49">
-        <v>35</v>
+        <v>223</v>
       </c>
       <c r="L123" s="0"/>
     </row>
     <row r="124">
-      <c r="A124" s="44"/>
-      <c r="B124" s="45"/>
-      <c r="C124" s="46"/>
-      <c r="D124" s="46"/>
-      <c r="E124" s="47"/>
-      <c r="F124" s="44"/>
-      <c r="G124" t="s" s="51">
+      <c r="A124" t="s" s="44">
+        <v>69</v>
+      </c>
+      <c r="B124" s="45">
+        <v>0000106895</v>
+      </c>
+      <c r="C124" t="s" s="46">
+        <v>191</v>
+      </c>
+      <c r="D124" t="s" s="46">
+        <v>221</v>
+      </c>
+      <c r="E124" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F124" t="s" s="44">
+        <v>159</v>
+      </c>
+      <c r="G124" s="51">
+        <v>180</v>
+      </c>
+      <c r="H124" s="52">
+        <v>284.59</v>
+      </c>
+      <c r="I124" s="53">
+        <v>225</v>
+      </c>
+      <c r="J124" t="s" s="48">
+        <v>160</v>
+      </c>
+      <c r="K124" t="s" s="49">
+        <v>223</v>
+      </c>
+      <c r="L124" s="0"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="44"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="46"/>
+      <c r="D125" s="46"/>
+      <c r="E125" s="47"/>
+      <c r="F125" t="s" s="44">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H124" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I124" s="53"/>
-      <c r="J124" s="48"/>
-      <c r="K124" s="49"/>
-      <c r="L124" s="0"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="s" s="44">
-        <v>67</v>
-      </c>
-      <c r="B125" s="45">
-        <v>0000106884</v>
-      </c>
-      <c r="C125" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="D125" t="s" s="46">
-        <v>204</v>
-      </c>
-      <c r="E125" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F125" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G125" s="51">
-        <v>180</v>
-      </c>
       <c r="H125" s="52">
-        <v>280.25</v>
-      </c>
-      <c r="I125" s="53">
-        <v>225</v>
+        <v>93250.35</v>
+      </c>
+      <c r="I125" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J125" t="s" s="48">
-        <v>78</v>
-      </c>
-      <c r="K125" t="s" s="49">
-        <v>187</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K125" s="49"/>
       <c r="L125" s="0"/>
     </row>
     <row r="126">
@@ -5165,136 +5273,136 @@
       <c r="C126" s="46"/>
       <c r="D126" s="46"/>
       <c r="E126" s="47"/>
-      <c r="F126" t="s" s="44">
-        <v>18</v>
+      <c r="F126" s="44" t="s">
+        <v>226</v>
       </c>
       <c r="G126" t="s" s="51">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="H126" s="52">
-        <v>50445</v>
-      </c>
-      <c r="I126" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J126" t="s" s="48">
-        <v>18</v>
+        <v>197203.17</v>
+      </c>
+      <c r="I126" s="53">
+        <v>612.8</v>
+      </c>
+      <c r="J126" s="48" t="s">
+        <v>227</v>
       </c>
       <c r="K126" s="49"/>
       <c r="L126" s="0"/>
     </row>
     <row r="127">
-      <c r="A127" s="44"/>
-      <c r="B127" s="45"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="46"/>
-      <c r="E127" s="47"/>
-      <c r="F127" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="G127" t="s" s="51">
-        <v>56</v>
+      <c r="A127" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B127" s="45">
+        <v>0000106882</v>
+      </c>
+      <c r="C127" t="s" s="46">
+        <v>154</v>
+      </c>
+      <c r="D127" t="s" s="46">
+        <v>224</v>
+      </c>
+      <c r="E127" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F127" t="s" s="44">
+        <v>152</v>
+      </c>
+      <c r="G127" s="51">
+        <v>48</v>
       </c>
       <c r="H127" s="52">
-        <v>103952.82</v>
+        <v>315.46</v>
       </c>
       <c r="I127" s="53">
-        <v>387.8</v>
-      </c>
-      <c r="J127" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="K127" s="49"/>
+        <v>72</v>
+      </c>
+      <c r="J127" t="s" s="48">
+        <v>153</v>
+      </c>
+      <c r="K127" t="s" s="49">
+        <v>225</v>
+      </c>
       <c r="L127" s="0"/>
     </row>
     <row r="128">
-      <c r="A128" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B128" s="45">
-        <v>0000106882</v>
-      </c>
-      <c r="C128" t="s" s="46">
-        <v>15</v>
-      </c>
-      <c r="D128" t="s" s="46">
-        <v>205</v>
-      </c>
-      <c r="E128" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F128" t="s" s="44">
-        <v>59</v>
-      </c>
-      <c r="G128" s="51">
-        <v>48</v>
+      <c r="A128" s="44"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="46"/>
+      <c r="D128" s="46"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="44"/>
+      <c r="G128" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H128" s="52">
-        <v>315.46</v>
-      </c>
-      <c r="I128" s="53">
-        <v>72</v>
-      </c>
-      <c r="J128" t="s" s="48">
-        <v>60</v>
-      </c>
-      <c r="K128" t="s" s="49">
-        <v>206</v>
-      </c>
+        <v>15142.08</v>
+      </c>
+      <c r="I128" s="53"/>
+      <c r="J128" s="48"/>
+      <c r="K128" s="49"/>
       <c r="L128" s="0"/>
     </row>
     <row r="129">
-      <c r="A129" s="44"/>
-      <c r="B129" s="45"/>
-      <c r="C129" s="46"/>
-      <c r="D129" s="46"/>
-      <c r="E129" s="47"/>
-      <c r="F129" s="44"/>
-      <c r="G129" t="s" s="51">
+      <c r="A129" t="s" s="44">
+        <v>76</v>
+      </c>
+      <c r="B129" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C129" t="s" s="46">
+        <v>77</v>
+      </c>
+      <c r="D129" t="s" s="46">
+        <v>228</v>
+      </c>
+      <c r="E129" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F129" t="s" s="44">
+        <v>79</v>
+      </c>
+      <c r="G129" s="51">
+        <v>5</v>
+      </c>
+      <c r="H129" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I129" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J129" t="s" s="48">
+        <v>80</v>
+      </c>
+      <c r="K129" t="s" s="49">
+        <v>81</v>
+      </c>
+      <c r="L129" s="0"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="44"/>
+      <c r="B130" s="45"/>
+      <c r="C130" s="46"/>
+      <c r="D130" s="46"/>
+      <c r="E130" s="47"/>
+      <c r="F130" t="s" s="44">
+        <v>18</v>
+      </c>
+      <c r="G130" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H129" s="52">
-        <v>15142.08</v>
-      </c>
-      <c r="I129" s="53"/>
-      <c r="J129" s="48"/>
-      <c r="K129" s="49"/>
-      <c r="L129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="44">
-        <v>30</v>
-      </c>
-      <c r="B130" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C130" t="s" s="46">
-        <v>31</v>
-      </c>
-      <c r="D130" t="s" s="46">
-        <v>209</v>
-      </c>
-      <c r="E130" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F130" t="s" s="44">
-        <v>33</v>
-      </c>
-      <c r="G130" s="51">
-        <v>5</v>
-      </c>
       <c r="H130" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I130" t="s" s="53">
+        <v>11250</v>
+      </c>
+      <c r="I130" s="53" t="s">
         <v>18</v>
       </c>
       <c r="J130" t="s" s="48">
-        <v>34</v>
-      </c>
-      <c r="K130" t="s" s="49">
-        <v>35</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K130" s="49"/>
       <c r="L130" s="0"/>
     </row>
     <row r="131">
@@ -5303,11 +5411,11 @@
       <c r="C131" s="46"/>
       <c r="D131" s="46"/>
       <c r="E131" s="47"/>
-      <c r="F131" t="s" s="44">
-        <v>211</v>
+      <c r="F131" s="44" t="s">
+        <v>230</v>
       </c>
       <c r="G131" t="s" s="51">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="H131" s="52">
         <v>26392.08</v>
@@ -5315,250 +5423,256 @@
       <c r="I131" s="53">
         <v>72</v>
       </c>
-      <c r="J131" t="s" s="48">
-        <v>212</v>
+      <c r="J131" s="48" t="s">
+        <v>231</v>
       </c>
       <c r="K131" s="49"/>
       <c r="L131" s="0"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="44">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="B132" s="45">
-        <v>0000106778</v>
+        <v>0000106893</v>
       </c>
       <c r="C132" t="s" s="46">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="D132" t="s" s="46">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="E132" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F132" t="s" s="44">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="G132" s="51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H132" s="52">
-        <v>2250</v>
+        <v>3443.62</v>
       </c>
       <c r="I132" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J132" t="s" s="48">
-        <v>34</v>
+        <v>187</v>
       </c>
       <c r="K132" t="s" s="49">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="L132" s="0"/>
     </row>
     <row r="133">
-      <c r="A133" s="44"/>
-      <c r="B133" s="45"/>
-      <c r="C133" s="46"/>
-      <c r="D133" s="46"/>
-      <c r="E133" s="47"/>
+      <c r="A133" t="s" s="44">
+        <v>184</v>
+      </c>
+      <c r="B133" s="45">
+        <v>0000106893</v>
+      </c>
+      <c r="C133" t="s" s="46">
+        <v>185</v>
+      </c>
+      <c r="D133" t="s" s="46">
+        <v>229</v>
+      </c>
+      <c r="E133" t="s" s="47">
+        <v>16</v>
+      </c>
       <c r="F133" t="s" s="44">
-        <v>214</v>
-      </c>
-      <c r="G133" t="s" s="51">
-        <v>56</v>
+        <v>189</v>
+      </c>
+      <c r="G133" s="51">
+        <v>10</v>
       </c>
       <c r="H133" s="52">
+        <v>1419.01</v>
+      </c>
+      <c r="I133" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J133" t="s" s="48">
+        <v>190</v>
+      </c>
+      <c r="K133" t="s" s="49">
+        <v>188</v>
+      </c>
+      <c r="L133" s="0"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="44"/>
+      <c r="B134" s="45"/>
+      <c r="C134" s="46"/>
+      <c r="D134" s="46"/>
+      <c r="E134" s="47"/>
+      <c r="F134" s="44"/>
+      <c r="G134" t="s" s="51">
+        <v>27</v>
+      </c>
+      <c r="H134" s="52">
+        <v>48626.3</v>
+      </c>
+      <c r="I134" s="53"/>
+      <c r="J134" s="48"/>
+      <c r="K134" s="49"/>
+      <c r="L134" s="0"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="44">
+        <v>76</v>
+      </c>
+      <c r="B135" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C135" t="s" s="46">
+        <v>77</v>
+      </c>
+      <c r="D135" t="s" s="46">
+        <v>232</v>
+      </c>
+      <c r="E135" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F135" t="s" s="44">
+        <v>79</v>
+      </c>
+      <c r="G135" s="51">
+        <v>5</v>
+      </c>
+      <c r="H135" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I135" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J135" t="s" s="48">
+        <v>80</v>
+      </c>
+      <c r="K135" t="s" s="49">
+        <v>81</v>
+      </c>
+      <c r="L135" s="0"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="44"/>
+      <c r="B136" s="45"/>
+      <c r="C136" s="46"/>
+      <c r="D136" s="46"/>
+      <c r="E136" s="47"/>
+      <c r="F136" t="s" s="44">
+        <v>234</v>
+      </c>
+      <c r="G136" t="s" s="51">
+        <v>144</v>
+      </c>
+      <c r="H136" s="52">
+        <v>59876.3</v>
+      </c>
+      <c r="I136" s="53">
+        <v>0</v>
+      </c>
+      <c r="J136" t="s" s="48">
+        <v>235</v>
+      </c>
+      <c r="K136" s="49"/>
+      <c r="L136" s="0"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="44">
+        <v>76</v>
+      </c>
+      <c r="B137" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C137" t="s" s="46">
+        <v>77</v>
+      </c>
+      <c r="D137" t="s" s="46">
+        <v>233</v>
+      </c>
+      <c r="E137" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F137" t="s" s="44">
+        <v>79</v>
+      </c>
+      <c r="G137" s="51">
+        <v>5</v>
+      </c>
+      <c r="H137" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I137" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J137" t="s" s="48">
+        <v>80</v>
+      </c>
+      <c r="K137" t="s" s="49">
+        <v>81</v>
+      </c>
+      <c r="L137" s="0"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="44"/>
+      <c r="B138" s="45"/>
+      <c r="C138" s="46"/>
+      <c r="D138" s="46"/>
+      <c r="E138" s="47"/>
+      <c r="F138" t="s" s="44">
+        <v>237</v>
+      </c>
+      <c r="G138" t="s" s="51">
+        <v>144</v>
+      </c>
+      <c r="H138" s="52">
         <v>11250</v>
       </c>
-      <c r="I133" s="53">
+      <c r="I138" s="53">
         <v>0</v>
       </c>
-      <c r="J133" t="s" s="48">
-        <v>215</v>
-      </c>
-      <c r="K133" s="49"/>
-      <c r="L133" s="0"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="44">
-        <v>30</v>
-      </c>
-      <c r="B134" s="45">
+      <c r="J138" t="s" s="48">
+        <v>235</v>
+      </c>
+      <c r="K138" s="49"/>
+      <c r="L138" s="0"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="44">
+        <v>76</v>
+      </c>
+      <c r="B139" s="45">
         <v>0000106778</v>
       </c>
-      <c r="C134" t="s" s="46">
-        <v>31</v>
-      </c>
-      <c r="D134" t="s" s="46">
-        <v>213</v>
-      </c>
-      <c r="E134" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F134" t="s" s="44">
-        <v>33</v>
-      </c>
-      <c r="G134" s="51">
+      <c r="C139" t="s" s="46">
+        <v>77</v>
+      </c>
+      <c r="D139" t="s" s="46">
+        <v>236</v>
+      </c>
+      <c r="E139" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F139" t="s" s="44">
+        <v>79</v>
+      </c>
+      <c r="G139" s="51">
         <v>5</v>
       </c>
-      <c r="H134" s="52">
+      <c r="H139" s="52">
         <v>2250</v>
       </c>
-      <c r="I134" t="s" s="53">
+      <c r="I139" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J134" t="s" s="48">
-        <v>34</v>
-      </c>
-      <c r="K134" t="s" s="49">
-        <v>35</v>
-      </c>
-      <c r="L134" s="0"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="44"/>
-      <c r="B135" s="45"/>
-      <c r="C135" s="46"/>
-      <c r="D135" s="46"/>
-      <c r="E135" s="47"/>
-      <c r="F135" t="s" s="44">
-        <v>217</v>
-      </c>
-      <c r="G135" t="s" s="51">
-        <v>56</v>
-      </c>
-      <c r="H135" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I135" s="53">
-        <v>0</v>
-      </c>
-      <c r="J135" t="s" s="48">
-        <v>215</v>
-      </c>
-      <c r="K135" s="49"/>
-      <c r="L135" s="0"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="44">
-        <v>30</v>
-      </c>
-      <c r="B136" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C136" t="s" s="46">
-        <v>31</v>
-      </c>
-      <c r="D136" t="s" s="46">
-        <v>216</v>
-      </c>
-      <c r="E136" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F136" t="s" s="44">
-        <v>33</v>
-      </c>
-      <c r="G136" s="51">
-        <v>5</v>
-      </c>
-      <c r="H136" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I136" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J136" t="s" s="48">
-        <v>34</v>
-      </c>
-      <c r="K136" t="s" s="49">
-        <v>35</v>
-      </c>
-      <c r="L136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="44"/>
-      <c r="B137" s="45"/>
-      <c r="C137" s="46"/>
-      <c r="D137" s="46"/>
-      <c r="E137" s="47"/>
-      <c r="F137" t="s" s="44">
-        <v>219</v>
-      </c>
-      <c r="G137" t="s" s="51">
-        <v>56</v>
-      </c>
-      <c r="H137" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I137" s="53">
-        <v>0</v>
-      </c>
-      <c r="J137" t="s" s="48">
-        <v>215</v>
-      </c>
-      <c r="K137" s="49"/>
-      <c r="L137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="44">
-        <v>30</v>
-      </c>
-      <c r="B138" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C138" t="s" s="46">
-        <v>31</v>
-      </c>
-      <c r="D138" t="s" s="46">
-        <v>218</v>
-      </c>
-      <c r="E138" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F138" t="s" s="44">
-        <v>33</v>
-      </c>
-      <c r="G138" s="51">
-        <v>2</v>
-      </c>
-      <c r="H138" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I138" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J138" t="s" s="48">
-        <v>34</v>
-      </c>
-      <c r="K138" t="s" s="49">
-        <v>35</v>
-      </c>
-      <c r="L138" s="0"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="44"/>
-      <c r="B139" s="45"/>
-      <c r="C139" s="46"/>
-      <c r="D139" s="46"/>
-      <c r="E139" s="47"/>
-      <c r="F139" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G139" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H139" s="52">
-        <v>49500</v>
-      </c>
-      <c r="I139" s="53" t="s">
-        <v>18</v>
-      </c>
       <c r="J139" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K139" s="49"/>
+        <v>80</v>
+      </c>
+      <c r="K139" t="s" s="49">
+        <v>81</v>
+      </c>
       <c r="L139" s="0"/>
     </row>
     <row r="140">
@@ -5567,94 +5681,82 @@
       <c r="C140" s="46"/>
       <c r="D140" s="46"/>
       <c r="E140" s="47"/>
-      <c r="F140" s="44" t="s">
-        <v>223</v>
+      <c r="F140" t="s" s="44">
+        <v>239</v>
       </c>
       <c r="G140" t="s" s="51">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="H140" s="52">
-        <v>4500</v>
+        <v>11250</v>
       </c>
       <c r="I140" s="53">
         <v>0</v>
       </c>
-      <c r="J140" s="48" t="s">
-        <v>215</v>
+      <c r="J140" t="s" s="48">
+        <v>235</v>
       </c>
       <c r="K140" s="49"/>
       <c r="L140" s="0"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="44">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="B141" s="45">
-        <v>0000106853</v>
+        <v>0000106778</v>
       </c>
       <c r="C141" t="s" s="46">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="D141" t="s" s="46">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="E141" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F141" t="s" s="44">
-        <v>183</v>
+        <v>79</v>
       </c>
       <c r="G141" s="51">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="H141" s="52">
-        <v>11.60</v>
-      </c>
-      <c r="I141" s="53">
-        <v>16.5</v>
+        <v>2250</v>
+      </c>
+      <c r="I141" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J141" t="s" s="48">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="K141" t="s" s="49">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="L141" s="0"/>
     </row>
     <row r="142">
-      <c r="A142" t="s" s="44">
-        <v>220</v>
-      </c>
-      <c r="B142" s="45">
-        <v>0000106853</v>
-      </c>
-      <c r="C142" t="s" s="46">
-        <v>221</v>
-      </c>
-      <c r="D142" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E142" t="s" s="47">
-        <v>39</v>
-      </c>
+      <c r="A142" s="44"/>
+      <c r="B142" s="45"/>
+      <c r="C142" s="46"/>
+      <c r="D142" s="46"/>
+      <c r="E142" s="47"/>
       <c r="F142" t="s" s="44">
-        <v>92</v>
-      </c>
-      <c r="G142" s="51">
-        <v>800</v>
+        <v>18</v>
+      </c>
+      <c r="G142" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H142" s="52">
-        <v>10.84</v>
-      </c>
-      <c r="I142" t="s" s="53">
+        <v>38250</v>
+      </c>
+      <c r="I142" s="53" t="s">
         <v>18</v>
       </c>
       <c r="J142" t="s" s="48">
-        <v>93</v>
-      </c>
-      <c r="K142" t="s" s="49">
-        <v>20</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K142" s="49"/>
       <c r="L142" s="0"/>
     </row>
     <row r="143">
@@ -5663,244 +5765,250 @@
       <c r="C143" s="46"/>
       <c r="D143" s="46"/>
       <c r="E143" s="47"/>
-      <c r="F143" s="44"/>
+      <c r="F143" s="44" t="s">
+        <v>243</v>
+      </c>
       <c r="G143" t="s" s="51">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="H143" s="52">
-        <v>14472</v>
-      </c>
-      <c r="I143" s="53"/>
-      <c r="J143" s="48"/>
+        <v>4500</v>
+      </c>
+      <c r="I143" s="53">
+        <v>0</v>
+      </c>
+      <c r="J143" s="48" t="s">
+        <v>235</v>
+      </c>
       <c r="K143" s="49"/>
       <c r="L143" s="0"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="44">
-        <v>36</v>
+        <v>240</v>
       </c>
       <c r="B144" s="45">
-        <v>0000106170</v>
+        <v>0000106853</v>
       </c>
       <c r="C144" t="s" s="46">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="D144" t="s" s="46">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E144" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F144" t="s" s="44">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="G144" s="51">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="H144" s="52">
-        <v>0</v>
+        <v>11.60</v>
       </c>
       <c r="I144" s="53">
-        <v>72</v>
+        <v>16.5</v>
       </c>
       <c r="J144" t="s" s="48">
-        <v>60</v>
-      </c>
-      <c r="K144" s="49"/>
+        <v>179</v>
+      </c>
+      <c r="K144" t="s" s="49">
+        <v>103</v>
+      </c>
       <c r="L144" s="0"/>
     </row>
     <row r="145">
-      <c r="A145" s="44"/>
-      <c r="B145" s="45"/>
-      <c r="C145" s="46"/>
-      <c r="D145" s="46"/>
-      <c r="E145" s="47"/>
-      <c r="F145" s="44"/>
-      <c r="G145" t="s" s="51">
+      <c r="A145" t="s" s="44">
+        <v>240</v>
+      </c>
+      <c r="B145" s="45">
+        <v>0000106853</v>
+      </c>
+      <c r="C145" t="s" s="46">
+        <v>241</v>
+      </c>
+      <c r="D145" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E145" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F145" t="s" s="44">
+        <v>34</v>
+      </c>
+      <c r="G145" s="51">
+        <v>800</v>
+      </c>
+      <c r="H145" s="52">
+        <v>10.84</v>
+      </c>
+      <c r="I145" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J145" t="s" s="48">
+        <v>35</v>
+      </c>
+      <c r="K145" t="s" s="49">
+        <v>103</v>
+      </c>
+      <c r="L145" s="0"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="44"/>
+      <c r="B146" s="45"/>
+      <c r="C146" s="46"/>
+      <c r="D146" s="46"/>
+      <c r="E146" s="47"/>
+      <c r="F146" s="44"/>
+      <c r="G146" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H145" s="52">
-        <v>0</v>
-      </c>
-      <c r="I145" s="53"/>
-      <c r="J145" s="48"/>
-      <c r="K145" s="49"/>
-      <c r="L145" s="0"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B146" s="45">
-        <v>0000106171</v>
-      </c>
-      <c r="C146" t="s" s="46">
-        <v>224</v>
-      </c>
-      <c r="D146" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E146" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F146" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="G146" s="51">
-        <v>70</v>
-      </c>
       <c r="H146" s="52">
-        <v>0</v>
-      </c>
-      <c r="I146" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J146" t="s" s="48">
-        <v>41</v>
-      </c>
+        <v>14472</v>
+      </c>
+      <c r="I146" s="53"/>
+      <c r="J146" s="48"/>
       <c r="K146" s="49"/>
       <c r="L146" s="0"/>
     </row>
     <row r="147">
-      <c r="A147" s="44"/>
-      <c r="B147" s="45"/>
-      <c r="C147" s="46"/>
-      <c r="D147" s="46"/>
-      <c r="E147" s="47"/>
-      <c r="F147" s="44"/>
-      <c r="G147" t="s" s="51">
-        <v>27</v>
+      <c r="A147" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B147" s="45">
+        <v>0000106170</v>
+      </c>
+      <c r="C147" t="s" s="46">
+        <v>244</v>
+      </c>
+      <c r="D147" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E147" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F147" t="s" s="44">
+        <v>152</v>
+      </c>
+      <c r="G147" s="51">
+        <v>48</v>
       </c>
       <c r="H147" s="52">
         <v>0</v>
       </c>
-      <c r="I147" s="53"/>
-      <c r="J147" s="48"/>
+      <c r="I147" s="53">
+        <v>72</v>
+      </c>
+      <c r="J147" t="s" s="48">
+        <v>153</v>
+      </c>
       <c r="K147" s="49"/>
       <c r="L147" s="0"/>
     </row>
     <row r="148">
-      <c r="A148" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B148" s="45">
-        <v>0000106172</v>
-      </c>
-      <c r="C148" t="s" s="46">
-        <v>224</v>
-      </c>
-      <c r="D148" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E148" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F148" t="s" s="44">
-        <v>40</v>
-      </c>
-      <c r="G148" s="51">
-        <v>70</v>
+      <c r="A148" s="44"/>
+      <c r="B148" s="45"/>
+      <c r="C148" s="46"/>
+      <c r="D148" s="46"/>
+      <c r="E148" s="47"/>
+      <c r="F148" s="44"/>
+      <c r="G148" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H148" s="52">
         <v>0</v>
       </c>
-      <c r="I148" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J148" t="s" s="48">
-        <v>41</v>
-      </c>
+      <c r="I148" s="53"/>
+      <c r="J148" s="48"/>
       <c r="K148" s="49"/>
       <c r="L148" s="0"/>
     </row>
     <row r="149">
-      <c r="A149" s="44"/>
-      <c r="B149" s="45"/>
-      <c r="C149" s="46"/>
-      <c r="D149" s="46"/>
-      <c r="E149" s="47"/>
-      <c r="F149" s="44"/>
-      <c r="G149" t="s" s="51">
-        <v>27</v>
+      <c r="A149" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B149" s="45">
+        <v>0000106171</v>
+      </c>
+      <c r="C149" t="s" s="46">
+        <v>244</v>
+      </c>
+      <c r="D149" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E149" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F149" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="G149" s="51">
+        <v>70</v>
       </c>
       <c r="H149" s="52">
         <v>0</v>
       </c>
-      <c r="I149" s="53"/>
-      <c r="J149" s="48"/>
+      <c r="I149" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J149" t="s" s="48">
+        <v>94</v>
+      </c>
       <c r="K149" s="49"/>
       <c r="L149" s="0"/>
     </row>
     <row r="150">
-      <c r="A150" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B150" s="45">
-        <v>0000106234</v>
-      </c>
-      <c r="C150" t="s" s="46">
-        <v>225</v>
-      </c>
-      <c r="D150" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E150" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F150" t="s" s="44">
-        <v>121</v>
-      </c>
-      <c r="G150" s="51">
-        <v>5</v>
+      <c r="A150" s="44"/>
+      <c r="B150" s="45"/>
+      <c r="C150" s="46"/>
+      <c r="D150" s="46"/>
+      <c r="E150" s="47"/>
+      <c r="F150" s="44"/>
+      <c r="G150" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H150" s="52">
         <v>0</v>
       </c>
-      <c r="I150" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J150" t="s" s="48">
-        <v>122</v>
-      </c>
-      <c r="K150" t="s" s="49">
-        <v>226</v>
-      </c>
+      <c r="I150" s="53"/>
+      <c r="J150" s="48"/>
+      <c r="K150" s="49"/>
       <c r="L150" s="0"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B151" s="45">
-        <v>0000106234</v>
+        <v>0000106172</v>
       </c>
       <c r="C151" t="s" s="46">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="D151" t="s" s="46">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E151" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F151" t="s" s="44">
-        <v>227</v>
+        <v>93</v>
       </c>
       <c r="G151" s="51">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="H151" s="52">
         <v>0</v>
       </c>
-      <c r="I151" t="s" s="53">
-        <v>18</v>
+      <c r="I151" s="53">
+        <v>87.5</v>
       </c>
       <c r="J151" t="s" s="48">
-        <v>228</v>
-      </c>
-      <c r="K151" t="s" s="49">
-        <v>226</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="K151" s="49"/>
       <c r="L151" s="0"/>
     </row>
     <row r="152">
@@ -5923,1097 +6031,1101 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B153" s="45">
-        <v>0000106644</v>
+        <v>0000106234</v>
       </c>
       <c r="C153" t="s" s="46">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="D153" t="s" s="46">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E153" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F153" t="s" s="44">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="G153" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H153" s="52">
-        <v>2132.20</v>
+        <v>0</v>
       </c>
       <c r="I153" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J153" t="s" s="48">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="K153" t="s" s="49">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="L153" s="0"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B154" s="45">
-        <v>0000106644</v>
+        <v>0000106234</v>
       </c>
       <c r="C154" t="s" s="46">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="D154" t="s" s="46">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E154" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F154" t="s" s="44">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="G154" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H154" s="52">
-        <v>1359.96</v>
+        <v>0</v>
       </c>
       <c r="I154" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J154" t="s" s="48">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="K154" t="s" s="49">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="L154" s="0"/>
     </row>
     <row r="155">
-      <c r="A155" t="s" s="44">
-        <v>36</v>
-      </c>
-      <c r="B155" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C155" t="s" s="46">
-        <v>229</v>
-      </c>
-      <c r="D155" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E155" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F155" t="s" s="44">
-        <v>235</v>
-      </c>
-      <c r="G155" s="51">
-        <v>1</v>
+      <c r="A155" s="44"/>
+      <c r="B155" s="45"/>
+      <c r="C155" s="46"/>
+      <c r="D155" s="46"/>
+      <c r="E155" s="47"/>
+      <c r="F155" s="44"/>
+      <c r="G155" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H155" s="52">
-        <v>949.92</v>
-      </c>
-      <c r="I155" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J155" t="s" s="48">
-        <v>236</v>
-      </c>
-      <c r="K155" t="s" s="49">
-        <v>232</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I155" s="53"/>
+      <c r="J155" s="48"/>
+      <c r="K155" s="49"/>
       <c r="L155" s="0"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B156" s="45">
         <v>0000106644</v>
       </c>
       <c r="C156" t="s" s="46">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D156" t="s" s="46">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E156" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F156" t="s" s="44">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="G156" s="51">
         <v>1</v>
       </c>
       <c r="H156" s="52">
-        <v>531.68</v>
+        <v>2132.20</v>
       </c>
       <c r="I156" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J156" t="s" s="48">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="K156" t="s" s="49">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="L156" s="0"/>
     </row>
     <row r="157">
-      <c r="A157" s="44"/>
-      <c r="B157" s="45"/>
-      <c r="C157" s="46"/>
-      <c r="D157" s="46"/>
-      <c r="E157" s="47"/>
-      <c r="F157" s="44"/>
-      <c r="G157" t="s" s="51">
-        <v>27</v>
+      <c r="A157" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B157" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C157" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="D157" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E157" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F157" t="s" s="44">
+        <v>255</v>
+      </c>
+      <c r="G157" s="51">
+        <v>1</v>
       </c>
       <c r="H157" s="52">
-        <v>4973.76</v>
-      </c>
-      <c r="I157" s="53"/>
-      <c r="J157" s="48"/>
-      <c r="K157" s="49"/>
+        <v>1359.96</v>
+      </c>
+      <c r="I157" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J157" t="s" s="48">
+        <v>256</v>
+      </c>
+      <c r="K157" t="s" s="49">
+        <v>254</v>
+      </c>
       <c r="L157" s="0"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="44">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B158" s="45">
-        <v>0000106745</v>
+        <v>0000106644</v>
       </c>
       <c r="C158" t="s" s="46">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D158" t="s" s="46">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E158" t="s" s="47">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F158" t="s" s="44">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="G158" s="51">
         <v>1</v>
       </c>
       <c r="H158" s="52">
-        <v>905.99</v>
+        <v>949.92</v>
       </c>
       <c r="I158" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J158" t="s" s="48">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="K158" t="s" s="49">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="L158" s="0"/>
     </row>
     <row r="159">
-      <c r="A159" s="44"/>
-      <c r="B159" s="45"/>
-      <c r="C159" s="46"/>
-      <c r="D159" s="46"/>
-      <c r="E159" s="47"/>
-      <c r="F159" s="44"/>
-      <c r="G159" t="s" s="51">
+      <c r="A159" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B159" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C159" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="D159" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E159" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F159" t="s" s="44">
+        <v>259</v>
+      </c>
+      <c r="G159" s="51">
+        <v>1</v>
+      </c>
+      <c r="H159" s="52">
+        <v>531.68</v>
+      </c>
+      <c r="I159" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J159" t="s" s="48">
+        <v>260</v>
+      </c>
+      <c r="K159" t="s" s="49">
+        <v>254</v>
+      </c>
+      <c r="L159" s="0"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="44"/>
+      <c r="B160" s="45"/>
+      <c r="C160" s="46"/>
+      <c r="D160" s="46"/>
+      <c r="E160" s="47"/>
+      <c r="F160" s="44"/>
+      <c r="G160" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H159" s="52">
+      <c r="H160" s="52">
+        <v>4973.76</v>
+      </c>
+      <c r="I160" s="53"/>
+      <c r="J160" s="48"/>
+      <c r="K160" s="49"/>
+      <c r="L160" s="0"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="B161" s="45">
+        <v>0000106745</v>
+      </c>
+      <c r="C161" t="s" s="46">
+        <v>261</v>
+      </c>
+      <c r="D161" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E161" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F161" t="s" s="44">
+        <v>257</v>
+      </c>
+      <c r="G161" s="51">
+        <v>1</v>
+      </c>
+      <c r="H161" s="52">
         <v>905.99</v>
       </c>
-      <c r="I159" s="53"/>
-      <c r="J159" s="48"/>
-      <c r="K159" s="49"/>
-      <c r="L159" s="0"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="44">
-        <v>241</v>
-      </c>
-      <c r="B160" s="45">
-        <v>0000106764</v>
-      </c>
-      <c r="C160" t="s" s="46">
-        <v>242</v>
-      </c>
-      <c r="D160" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E160" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F160" t="s" s="44">
-        <v>243</v>
-      </c>
-      <c r="G160" s="51">
-        <v>24</v>
-      </c>
-      <c r="H160" s="52">
-        <v>15</v>
-      </c>
-      <c r="I160" t="s" s="53">
+      <c r="I161" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J160" t="s" s="48">
-        <v>244</v>
-      </c>
-      <c r="K160" t="s" s="49">
-        <v>245</v>
-      </c>
-      <c r="L160" s="0"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="44"/>
-      <c r="B161" s="45"/>
-      <c r="C161" s="46"/>
-      <c r="D161" s="46"/>
-      <c r="E161" s="47"/>
-      <c r="F161" s="44"/>
-      <c r="G161" t="s" s="51">
+      <c r="J161" t="s" s="48">
+        <v>258</v>
+      </c>
+      <c r="K161" t="s" s="49">
+        <v>262</v>
+      </c>
+      <c r="L161" s="0"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="44"/>
+      <c r="B162" s="45"/>
+      <c r="C162" s="46"/>
+      <c r="D162" s="46"/>
+      <c r="E162" s="47"/>
+      <c r="F162" s="44"/>
+      <c r="G162" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H161" s="52">
-        <v>360</v>
-      </c>
-      <c r="I161" s="53"/>
-      <c r="J161" s="48"/>
-      <c r="K161" s="49"/>
-      <c r="L161" s="0"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="44">
-        <v>67</v>
-      </c>
-      <c r="B162" s="45">
-        <v>0000106173</v>
-      </c>
-      <c r="C162" t="s" s="46">
-        <v>224</v>
-      </c>
-      <c r="D162" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E162" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F162" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G162" s="51">
-        <v>180</v>
-      </c>
       <c r="H162" s="52">
-        <v>0</v>
-      </c>
-      <c r="I162" s="53">
-        <v>225</v>
-      </c>
-      <c r="J162" t="s" s="48">
-        <v>78</v>
-      </c>
+        <v>905.99</v>
+      </c>
+      <c r="I162" s="53"/>
+      <c r="J162" s="48"/>
       <c r="K162" s="49"/>
       <c r="L162" s="0"/>
     </row>
     <row r="163">
-      <c r="A163" s="44"/>
-      <c r="B163" s="45"/>
-      <c r="C163" s="46"/>
-      <c r="D163" s="46"/>
-      <c r="E163" s="47"/>
-      <c r="F163" s="44"/>
-      <c r="G163" t="s" s="51">
+      <c r="A163" t="s" s="44">
+        <v>263</v>
+      </c>
+      <c r="B163" s="45">
+        <v>0000106764</v>
+      </c>
+      <c r="C163" t="s" s="46">
+        <v>264</v>
+      </c>
+      <c r="D163" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E163" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F163" t="s" s="44">
+        <v>265</v>
+      </c>
+      <c r="G163" s="51">
+        <v>24</v>
+      </c>
+      <c r="H163" s="52">
+        <v>15</v>
+      </c>
+      <c r="I163" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J163" t="s" s="48">
+        <v>266</v>
+      </c>
+      <c r="K163" t="s" s="49">
+        <v>267</v>
+      </c>
+      <c r="L163" s="0"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="44"/>
+      <c r="B164" s="45"/>
+      <c r="C164" s="46"/>
+      <c r="D164" s="46"/>
+      <c r="E164" s="47"/>
+      <c r="F164" s="44"/>
+      <c r="G164" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H163" s="52">
-        <v>0</v>
-      </c>
-      <c r="I163" s="53"/>
-      <c r="J163" s="48"/>
-      <c r="K163" s="49"/>
-      <c r="L163" s="0"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="44">
-        <v>67</v>
-      </c>
-      <c r="B164" s="45">
-        <v>0000106174</v>
-      </c>
-      <c r="C164" t="s" s="46">
-        <v>224</v>
-      </c>
-      <c r="D164" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E164" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F164" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G164" s="51">
-        <v>180</v>
-      </c>
       <c r="H164" s="52">
-        <v>0</v>
-      </c>
-      <c r="I164" s="53">
-        <v>225</v>
-      </c>
-      <c r="J164" t="s" s="48">
-        <v>78</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="I164" s="53"/>
+      <c r="J164" s="48"/>
       <c r="K164" s="49"/>
       <c r="L164" s="0"/>
     </row>
     <row r="165">
-      <c r="A165" s="44"/>
-      <c r="B165" s="45"/>
-      <c r="C165" s="46"/>
-      <c r="D165" s="46"/>
-      <c r="E165" s="47"/>
-      <c r="F165" s="44"/>
-      <c r="G165" t="s" s="51">
-        <v>27</v>
+      <c r="A165" t="s" s="44">
+        <v>69</v>
+      </c>
+      <c r="B165" s="45">
+        <v>0000106173</v>
+      </c>
+      <c r="C165" t="s" s="46">
+        <v>244</v>
+      </c>
+      <c r="D165" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E165" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F165" t="s" s="44">
+        <v>159</v>
+      </c>
+      <c r="G165" s="51">
+        <v>180</v>
       </c>
       <c r="H165" s="52">
         <v>0</v>
       </c>
-      <c r="I165" s="53"/>
-      <c r="J165" s="48"/>
+      <c r="I165" s="53">
+        <v>225</v>
+      </c>
+      <c r="J165" t="s" s="48">
+        <v>160</v>
+      </c>
       <c r="K165" s="49"/>
       <c r="L165" s="0"/>
     </row>
     <row r="166">
-      <c r="A166" t="s" s="44">
-        <v>246</v>
-      </c>
-      <c r="B166" s="45">
-        <v>0000106235</v>
-      </c>
-      <c r="C166" t="s" s="46">
-        <v>225</v>
-      </c>
-      <c r="D166" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E166" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F166" t="s" s="44">
-        <v>247</v>
-      </c>
-      <c r="G166" s="51">
-        <v>25</v>
+      <c r="A166" s="44"/>
+      <c r="B166" s="45"/>
+      <c r="C166" s="46"/>
+      <c r="D166" s="46"/>
+      <c r="E166" s="47"/>
+      <c r="F166" s="44"/>
+      <c r="G166" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H166" s="52">
         <v>0</v>
       </c>
-      <c r="I166" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J166" t="s" s="48">
-        <v>248</v>
-      </c>
-      <c r="K166" t="s" s="49">
-        <v>226</v>
-      </c>
+      <c r="I166" s="53"/>
+      <c r="J166" s="48"/>
+      <c r="K166" s="49"/>
       <c r="L166" s="0"/>
     </row>
     <row r="167">
-      <c r="A167" s="44"/>
-      <c r="B167" s="45"/>
-      <c r="C167" s="46"/>
-      <c r="D167" s="46"/>
-      <c r="E167" s="47"/>
-      <c r="F167" s="44"/>
-      <c r="G167" t="s" s="51">
-        <v>27</v>
+      <c r="A167" t="s" s="44">
+        <v>69</v>
+      </c>
+      <c r="B167" s="45">
+        <v>0000106174</v>
+      </c>
+      <c r="C167" t="s" s="46">
+        <v>244</v>
+      </c>
+      <c r="D167" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E167" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F167" t="s" s="44">
+        <v>159</v>
+      </c>
+      <c r="G167" s="51">
+        <v>180</v>
       </c>
       <c r="H167" s="52">
         <v>0</v>
       </c>
-      <c r="I167" s="53"/>
-      <c r="J167" s="48"/>
+      <c r="I167" s="53">
+        <v>225</v>
+      </c>
+      <c r="J167" t="s" s="48">
+        <v>160</v>
+      </c>
       <c r="K167" s="49"/>
       <c r="L167" s="0"/>
     </row>
     <row r="168">
-      <c r="A168" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B168" s="45">
-        <v>0000106100</v>
-      </c>
-      <c r="C168" t="s" s="46">
-        <v>249</v>
-      </c>
-      <c r="D168" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E168" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F168" t="s" s="44">
-        <v>46</v>
-      </c>
-      <c r="G168" s="51">
-        <v>104</v>
+      <c r="A168" s="44"/>
+      <c r="B168" s="45"/>
+      <c r="C168" s="46"/>
+      <c r="D168" s="46"/>
+      <c r="E168" s="47"/>
+      <c r="F168" s="44"/>
+      <c r="G168" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H168" s="52">
         <v>0</v>
       </c>
-      <c r="I168" s="53">
-        <v>104</v>
-      </c>
-      <c r="J168" t="s" s="48">
-        <v>47</v>
-      </c>
-      <c r="K168" t="s" s="49">
-        <v>250</v>
-      </c>
+      <c r="I168" s="53"/>
+      <c r="J168" s="48"/>
+      <c r="K168" s="49"/>
       <c r="L168" s="0"/>
     </row>
     <row r="169">
-      <c r="A169" s="44"/>
-      <c r="B169" s="45"/>
-      <c r="C169" s="46"/>
-      <c r="D169" s="46"/>
-      <c r="E169" s="47"/>
-      <c r="F169" s="44"/>
-      <c r="G169" t="s" s="51">
-        <v>27</v>
+      <c r="A169" t="s" s="44">
+        <v>36</v>
+      </c>
+      <c r="B169" s="45">
+        <v>0000106235</v>
+      </c>
+      <c r="C169" t="s" s="46">
+        <v>245</v>
+      </c>
+      <c r="D169" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E169" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F169" t="s" s="44">
+        <v>268</v>
+      </c>
+      <c r="G169" s="51">
+        <v>25</v>
       </c>
       <c r="H169" s="52">
         <v>0</v>
       </c>
-      <c r="I169" s="53"/>
-      <c r="J169" s="48"/>
-      <c r="K169" s="49"/>
+      <c r="I169" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J169" t="s" s="48">
+        <v>269</v>
+      </c>
+      <c r="K169" t="s" s="49">
+        <v>248</v>
+      </c>
       <c r="L169" s="0"/>
     </row>
     <row r="170">
-      <c r="A170" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B170" s="45">
-        <v>0000106102</v>
-      </c>
-      <c r="C170" t="s" s="46">
-        <v>249</v>
-      </c>
-      <c r="D170" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E170" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F170" t="s" s="44">
-        <v>251</v>
-      </c>
-      <c r="G170" s="51">
-        <v>52</v>
+      <c r="A170" s="44"/>
+      <c r="B170" s="45"/>
+      <c r="C170" s="46"/>
+      <c r="D170" s="46"/>
+      <c r="E170" s="47"/>
+      <c r="F170" s="44"/>
+      <c r="G170" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H170" s="52">
         <v>0</v>
       </c>
-      <c r="I170" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J170" t="s" s="48">
-        <v>252</v>
-      </c>
-      <c r="K170" t="s" s="49">
-        <v>250</v>
-      </c>
+      <c r="I170" s="53"/>
+      <c r="J170" s="48"/>
+      <c r="K170" s="49"/>
       <c r="L170" s="0"/>
     </row>
     <row r="171">
-      <c r="A171" s="44"/>
-      <c r="B171" s="45"/>
-      <c r="C171" s="46"/>
-      <c r="D171" s="46"/>
-      <c r="E171" s="47"/>
-      <c r="F171" s="44"/>
-      <c r="G171" t="s" s="51">
-        <v>27</v>
+      <c r="A171" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B171" s="45">
+        <v>0000106100</v>
+      </c>
+      <c r="C171" t="s" s="46">
+        <v>270</v>
+      </c>
+      <c r="D171" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E171" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F171" t="s" s="44">
+        <v>114</v>
+      </c>
+      <c r="G171" s="51">
+        <v>104</v>
       </c>
       <c r="H171" s="52">
         <v>0</v>
       </c>
-      <c r="I171" s="53"/>
-      <c r="J171" s="48"/>
-      <c r="K171" s="49"/>
+      <c r="I171" s="53">
+        <v>104</v>
+      </c>
+      <c r="J171" t="s" s="48">
+        <v>115</v>
+      </c>
+      <c r="K171" t="s" s="49">
+        <v>271</v>
+      </c>
       <c r="L171" s="0"/>
     </row>
     <row r="172">
-      <c r="A172" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B172" s="45">
-        <v>0000106103</v>
-      </c>
-      <c r="C172" t="s" s="46">
-        <v>249</v>
-      </c>
-      <c r="D172" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E172" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F172" t="s" s="44">
-        <v>253</v>
-      </c>
-      <c r="G172" s="51">
-        <v>52</v>
+      <c r="A172" s="44"/>
+      <c r="B172" s="45"/>
+      <c r="C172" s="46"/>
+      <c r="D172" s="46"/>
+      <c r="E172" s="47"/>
+      <c r="F172" s="44"/>
+      <c r="G172" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H172" s="52">
         <v>0</v>
       </c>
-      <c r="I172" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J172" t="s" s="48">
-        <v>254</v>
-      </c>
-      <c r="K172" t="s" s="49">
-        <v>250</v>
-      </c>
+      <c r="I172" s="53"/>
+      <c r="J172" s="48"/>
+      <c r="K172" s="49"/>
       <c r="L172" s="0"/>
     </row>
     <row r="173">
-      <c r="A173" s="44"/>
-      <c r="B173" s="45"/>
-      <c r="C173" s="46"/>
-      <c r="D173" s="46"/>
-      <c r="E173" s="47"/>
-      <c r="F173" s="44"/>
-      <c r="G173" t="s" s="51">
-        <v>27</v>
+      <c r="A173" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B173" s="45">
+        <v>0000106102</v>
+      </c>
+      <c r="C173" t="s" s="46">
+        <v>270</v>
+      </c>
+      <c r="D173" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E173" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F173" t="s" s="44">
+        <v>272</v>
+      </c>
+      <c r="G173" s="51">
+        <v>52</v>
       </c>
       <c r="H173" s="52">
         <v>0</v>
       </c>
-      <c r="I173" s="53"/>
-      <c r="J173" s="48"/>
-      <c r="K173" s="49"/>
+      <c r="I173" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J173" t="s" s="48">
+        <v>273</v>
+      </c>
+      <c r="K173" t="s" s="49">
+        <v>271</v>
+      </c>
       <c r="L173" s="0"/>
     </row>
     <row r="174">
-      <c r="A174" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B174" s="45">
-        <v>0000106104</v>
-      </c>
-      <c r="C174" t="s" s="46">
-        <v>249</v>
-      </c>
-      <c r="D174" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E174" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F174" t="s" s="44">
-        <v>255</v>
-      </c>
-      <c r="G174" s="51">
-        <v>52</v>
+      <c r="A174" s="44"/>
+      <c r="B174" s="45"/>
+      <c r="C174" s="46"/>
+      <c r="D174" s="46"/>
+      <c r="E174" s="47"/>
+      <c r="F174" s="44"/>
+      <c r="G174" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H174" s="52">
         <v>0</v>
       </c>
-      <c r="I174" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J174" t="s" s="48">
-        <v>256</v>
-      </c>
-      <c r="K174" t="s" s="49">
-        <v>250</v>
-      </c>
+      <c r="I174" s="53"/>
+      <c r="J174" s="48"/>
+      <c r="K174" s="49"/>
       <c r="L174" s="0"/>
     </row>
     <row r="175">
-      <c r="A175" s="44"/>
-      <c r="B175" s="45"/>
-      <c r="C175" s="46"/>
-      <c r="D175" s="46"/>
-      <c r="E175" s="47"/>
-      <c r="F175" s="44"/>
-      <c r="G175" t="s" s="51">
-        <v>27</v>
+      <c r="A175" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B175" s="45">
+        <v>0000106103</v>
+      </c>
+      <c r="C175" t="s" s="46">
+        <v>270</v>
+      </c>
+      <c r="D175" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E175" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F175" t="s" s="44">
+        <v>274</v>
+      </c>
+      <c r="G175" s="51">
+        <v>52</v>
       </c>
       <c r="H175" s="52">
         <v>0</v>
       </c>
-      <c r="I175" s="53"/>
-      <c r="J175" s="48"/>
-      <c r="K175" s="49"/>
+      <c r="I175" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J175" t="s" s="48">
+        <v>275</v>
+      </c>
+      <c r="K175" t="s" s="49">
+        <v>271</v>
+      </c>
       <c r="L175" s="0"/>
     </row>
     <row r="176">
-      <c r="A176" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B176" s="45">
-        <v>0000106132</v>
-      </c>
-      <c r="C176" t="s" s="46">
-        <v>257</v>
-      </c>
-      <c r="D176" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E176" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F176" t="s" s="44">
-        <v>49</v>
-      </c>
-      <c r="G176" s="51">
-        <v>208</v>
+      <c r="A176" s="44"/>
+      <c r="B176" s="45"/>
+      <c r="C176" s="46"/>
+      <c r="D176" s="46"/>
+      <c r="E176" s="47"/>
+      <c r="F176" s="44"/>
+      <c r="G176" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H176" s="52">
         <v>0</v>
       </c>
-      <c r="I176" s="53">
-        <v>208</v>
-      </c>
-      <c r="J176" t="s" s="48">
-        <v>50</v>
-      </c>
-      <c r="K176" t="s" s="49">
-        <v>250</v>
-      </c>
+      <c r="I176" s="53"/>
+      <c r="J176" s="48"/>
+      <c r="K176" s="49"/>
       <c r="L176" s="0"/>
     </row>
     <row r="177">
-      <c r="A177" s="44"/>
-      <c r="B177" s="45"/>
-      <c r="C177" s="46"/>
-      <c r="D177" s="46"/>
-      <c r="E177" s="47"/>
-      <c r="F177" s="44"/>
-      <c r="G177" t="s" s="51">
-        <v>27</v>
+      <c r="A177" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B177" s="45">
+        <v>0000106104</v>
+      </c>
+      <c r="C177" t="s" s="46">
+        <v>270</v>
+      </c>
+      <c r="D177" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E177" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F177" t="s" s="44">
+        <v>276</v>
+      </c>
+      <c r="G177" s="51">
+        <v>52</v>
       </c>
       <c r="H177" s="52">
         <v>0</v>
       </c>
-      <c r="I177" s="53"/>
-      <c r="J177" s="48"/>
-      <c r="K177" s="49"/>
+      <c r="I177" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J177" t="s" s="48">
+        <v>277</v>
+      </c>
+      <c r="K177" t="s" s="49">
+        <v>271</v>
+      </c>
       <c r="L177" s="0"/>
     </row>
     <row r="178">
-      <c r="A178" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B178" s="45">
-        <v>0000106175</v>
-      </c>
-      <c r="C178" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="D178" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E178" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F178" t="s" s="44">
-        <v>49</v>
-      </c>
-      <c r="G178" s="51">
-        <v>208</v>
+      <c r="A178" s="44"/>
+      <c r="B178" s="45"/>
+      <c r="C178" s="46"/>
+      <c r="D178" s="46"/>
+      <c r="E178" s="47"/>
+      <c r="F178" s="44"/>
+      <c r="G178" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H178" s="52">
-        <v>332.67</v>
-      </c>
-      <c r="I178" s="53">
-        <v>208</v>
-      </c>
-      <c r="J178" t="s" s="48">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I178" s="53"/>
+      <c r="J178" s="48"/>
       <c r="K178" s="49"/>
       <c r="L178" s="0"/>
     </row>
     <row r="179">
-      <c r="A179" s="44"/>
-      <c r="B179" s="45"/>
-      <c r="C179" s="46"/>
-      <c r="D179" s="46"/>
-      <c r="E179" s="47"/>
-      <c r="F179" s="44"/>
-      <c r="G179" t="s" s="51">
+      <c r="A179" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B179" s="45">
+        <v>0000106132</v>
+      </c>
+      <c r="C179" t="s" s="46">
+        <v>278</v>
+      </c>
+      <c r="D179" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E179" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F179" t="s" s="44">
+        <v>279</v>
+      </c>
+      <c r="G179" s="51">
+        <v>208</v>
+      </c>
+      <c r="H179" s="52">
+        <v>0</v>
+      </c>
+      <c r="I179" s="53">
+        <v>208</v>
+      </c>
+      <c r="J179" t="s" s="48">
+        <v>280</v>
+      </c>
+      <c r="K179" t="s" s="49">
+        <v>271</v>
+      </c>
+      <c r="L179" s="0"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="44"/>
+      <c r="B180" s="45"/>
+      <c r="C180" s="46"/>
+      <c r="D180" s="46"/>
+      <c r="E180" s="47"/>
+      <c r="F180" s="44"/>
+      <c r="G180" t="s" s="51">
         <v>27</v>
       </c>
-      <c r="H179" s="52">
-        <v>69195.36</v>
-      </c>
-      <c r="I179" s="53"/>
-      <c r="J179" s="48"/>
-      <c r="K179" s="49"/>
-      <c r="L179" s="0"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B180" s="45">
-        <v>0000106176</v>
-      </c>
-      <c r="C180" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="D180" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E180" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F180" t="s" s="44">
-        <v>255</v>
-      </c>
-      <c r="G180" s="51">
-        <v>52</v>
-      </c>
       <c r="H180" s="52">
-        <v>509.41</v>
-      </c>
-      <c r="I180" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J180" t="s" s="48">
-        <v>256</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I180" s="53"/>
+      <c r="J180" s="48"/>
       <c r="K180" s="49"/>
       <c r="L180" s="0"/>
     </row>
     <row r="181">
-      <c r="A181" s="44"/>
-      <c r="B181" s="45"/>
-      <c r="C181" s="46"/>
-      <c r="D181" s="46"/>
-      <c r="E181" s="47"/>
-      <c r="F181" s="44"/>
-      <c r="G181" t="s" s="51">
-        <v>27</v>
+      <c r="A181" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B181" s="45">
+        <v>0000106175</v>
+      </c>
+      <c r="C181" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="D181" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E181" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F181" t="s" s="44">
+        <v>279</v>
+      </c>
+      <c r="G181" s="51">
+        <v>208</v>
       </c>
       <c r="H181" s="52">
-        <v>26489.32</v>
-      </c>
-      <c r="I181" s="53"/>
-      <c r="J181" s="48"/>
+        <v>332.67</v>
+      </c>
+      <c r="I181" s="53">
+        <v>208</v>
+      </c>
+      <c r="J181" t="s" s="48">
+        <v>280</v>
+      </c>
       <c r="K181" s="49"/>
       <c r="L181" s="0"/>
     </row>
     <row r="182">
-      <c r="A182" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B182" s="45">
-        <v>0000106177</v>
-      </c>
-      <c r="C182" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="D182" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E182" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F182" t="s" s="44">
-        <v>46</v>
-      </c>
-      <c r="G182" s="51">
-        <v>104</v>
+      <c r="A182" s="44"/>
+      <c r="B182" s="45"/>
+      <c r="C182" s="46"/>
+      <c r="D182" s="46"/>
+      <c r="E182" s="47"/>
+      <c r="F182" s="44"/>
+      <c r="G182" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H182" s="52">
-        <v>471.46</v>
-      </c>
-      <c r="I182" s="53">
-        <v>104</v>
-      </c>
-      <c r="J182" t="s" s="48">
-        <v>47</v>
-      </c>
+        <v>69195.36</v>
+      </c>
+      <c r="I182" s="53"/>
+      <c r="J182" s="48"/>
       <c r="K182" s="49"/>
       <c r="L182" s="0"/>
     </row>
     <row r="183">
-      <c r="A183" s="44"/>
-      <c r="B183" s="45"/>
-      <c r="C183" s="46"/>
-      <c r="D183" s="46"/>
-      <c r="E183" s="47"/>
-      <c r="F183" s="44"/>
-      <c r="G183" t="s" s="51">
-        <v>27</v>
+      <c r="A183" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B183" s="45">
+        <v>0000106176</v>
+      </c>
+      <c r="C183" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="D183" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E183" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F183" t="s" s="44">
+        <v>276</v>
+      </c>
+      <c r="G183" s="51">
+        <v>52</v>
       </c>
       <c r="H183" s="52">
-        <v>49031.84</v>
-      </c>
-      <c r="I183" s="53"/>
-      <c r="J183" s="48"/>
+        <v>509.41</v>
+      </c>
+      <c r="I183" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J183" t="s" s="48">
+        <v>277</v>
+      </c>
       <c r="K183" s="49"/>
       <c r="L183" s="0"/>
     </row>
     <row r="184">
-      <c r="A184" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B184" s="45">
-        <v>0000106178</v>
-      </c>
-      <c r="C184" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="D184" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E184" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F184" t="s" s="44">
-        <v>253</v>
-      </c>
-      <c r="G184" s="51">
-        <v>52</v>
+      <c r="A184" s="44"/>
+      <c r="B184" s="45"/>
+      <c r="C184" s="46"/>
+      <c r="D184" s="46"/>
+      <c r="E184" s="47"/>
+      <c r="F184" s="44"/>
+      <c r="G184" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H184" s="52">
-        <v>489.76</v>
-      </c>
-      <c r="I184" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J184" t="s" s="48">
-        <v>254</v>
-      </c>
+        <v>26489.32</v>
+      </c>
+      <c r="I184" s="53"/>
+      <c r="J184" s="48"/>
       <c r="K184" s="49"/>
       <c r="L184" s="0"/>
     </row>
     <row r="185">
-      <c r="A185" s="44"/>
-      <c r="B185" s="45"/>
-      <c r="C185" s="46"/>
-      <c r="D185" s="46"/>
-      <c r="E185" s="47"/>
-      <c r="F185" s="44"/>
-      <c r="G185" t="s" s="51">
-        <v>27</v>
+      <c r="A185" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B185" s="45">
+        <v>0000106177</v>
+      </c>
+      <c r="C185" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="D185" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E185" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F185" t="s" s="44">
+        <v>114</v>
+      </c>
+      <c r="G185" s="51">
+        <v>104</v>
       </c>
       <c r="H185" s="52">
-        <v>25467.52</v>
-      </c>
-      <c r="I185" s="53"/>
-      <c r="J185" s="48"/>
+        <v>471.46</v>
+      </c>
+      <c r="I185" s="53">
+        <v>104</v>
+      </c>
+      <c r="J185" t="s" s="48">
+        <v>115</v>
+      </c>
       <c r="K185" s="49"/>
       <c r="L185" s="0"/>
     </row>
     <row r="186">
-      <c r="A186" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B186" s="45">
-        <v>0000106179</v>
-      </c>
-      <c r="C186" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="D186" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E186" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F186" t="s" s="44">
-        <v>251</v>
-      </c>
-      <c r="G186" s="51">
-        <v>52</v>
+      <c r="A186" s="44"/>
+      <c r="B186" s="45"/>
+      <c r="C186" s="46"/>
+      <c r="D186" s="46"/>
+      <c r="E186" s="47"/>
+      <c r="F186" s="44"/>
+      <c r="G186" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H186" s="52">
-        <v>458.18</v>
-      </c>
-      <c r="I186" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J186" t="s" s="48">
-        <v>259</v>
-      </c>
+        <v>49031.84</v>
+      </c>
+      <c r="I186" s="53"/>
+      <c r="J186" s="48"/>
       <c r="K186" s="49"/>
       <c r="L186" s="0"/>
     </row>
     <row r="187">
-      <c r="A187" s="44"/>
-      <c r="B187" s="45"/>
-      <c r="C187" s="46"/>
-      <c r="D187" s="46"/>
-      <c r="E187" s="47"/>
-      <c r="F187" s="44"/>
-      <c r="G187" t="s" s="51">
-        <v>27</v>
+      <c r="A187" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B187" s="45">
+        <v>0000106178</v>
+      </c>
+      <c r="C187" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="D187" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E187" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F187" t="s" s="44">
+        <v>274</v>
+      </c>
+      <c r="G187" s="51">
+        <v>52</v>
       </c>
       <c r="H187" s="52">
-        <v>23825.36</v>
-      </c>
-      <c r="I187" s="53"/>
-      <c r="J187" s="48"/>
+        <v>489.76</v>
+      </c>
+      <c r="I187" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J187" t="s" s="48">
+        <v>275</v>
+      </c>
       <c r="K187" s="49"/>
       <c r="L187" s="0"/>
     </row>
     <row r="188">
-      <c r="A188" t="s" s="44">
-        <v>43</v>
-      </c>
-      <c r="B188" s="45">
-        <v>0000106180</v>
-      </c>
-      <c r="C188" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="D188" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E188" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F188" t="s" s="44">
-        <v>46</v>
-      </c>
-      <c r="G188" s="51">
-        <v>52</v>
+      <c r="A188" s="44"/>
+      <c r="B188" s="45"/>
+      <c r="C188" s="46"/>
+      <c r="D188" s="46"/>
+      <c r="E188" s="47"/>
+      <c r="F188" s="44"/>
+      <c r="G188" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H188" s="52">
-        <v>471.46</v>
-      </c>
-      <c r="I188" s="53">
-        <v>52</v>
-      </c>
-      <c r="J188" t="s" s="48">
-        <v>47</v>
-      </c>
+        <v>25467.52</v>
+      </c>
+      <c r="I188" s="53"/>
+      <c r="J188" s="48"/>
       <c r="K188" s="49"/>
       <c r="L188" s="0"/>
     </row>
     <row r="189">
-      <c r="A189" s="44"/>
-      <c r="B189" s="45"/>
-      <c r="C189" s="46"/>
-      <c r="D189" s="46"/>
-      <c r="E189" s="47"/>
-      <c r="F189" s="44"/>
-      <c r="G189" t="s" s="51">
-        <v>27</v>
+      <c r="A189" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B189" s="45">
+        <v>0000106179</v>
+      </c>
+      <c r="C189" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="D189" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E189" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F189" t="s" s="44">
+        <v>272</v>
+      </c>
+      <c r="G189" s="51">
+        <v>52</v>
       </c>
       <c r="H189" s="52">
-        <v>24515.92</v>
-      </c>
-      <c r="I189" s="53"/>
-      <c r="J189" s="48"/>
+        <v>458.18</v>
+      </c>
+      <c r="I189" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J189" t="s" s="48">
+        <v>282</v>
+      </c>
       <c r="K189" s="49"/>
       <c r="L189" s="0"/>
     </row>
     <row r="190">
-      <c r="A190" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B190" s="45">
-        <v>0000106883</v>
-      </c>
-      <c r="C190" t="s" s="46">
-        <v>260</v>
-      </c>
-      <c r="D190" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E190" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F190" t="s" s="44">
-        <v>261</v>
-      </c>
-      <c r="G190" s="51">
-        <v>36</v>
+      <c r="A190" s="44"/>
+      <c r="B190" s="45"/>
+      <c r="C190" s="46"/>
+      <c r="D190" s="46"/>
+      <c r="E190" s="47"/>
+      <c r="F190" s="44"/>
+      <c r="G190" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H190" s="52">
-        <v>2052.84</v>
-      </c>
-      <c r="I190" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J190" t="s" s="48">
-        <v>262</v>
-      </c>
+        <v>23825.36</v>
+      </c>
+      <c r="I190" s="53"/>
+      <c r="J190" s="48"/>
       <c r="K190" s="49"/>
       <c r="L190" s="0"/>
     </row>
     <row r="191">
-      <c r="A191" s="44"/>
-      <c r="B191" s="45"/>
-      <c r="C191" s="46"/>
-      <c r="D191" s="46"/>
-      <c r="E191" s="47"/>
-      <c r="F191" s="44"/>
-      <c r="G191" t="s" s="51">
-        <v>27</v>
+      <c r="A191" t="s" s="44">
+        <v>112</v>
+      </c>
+      <c r="B191" s="45">
+        <v>0000106180</v>
+      </c>
+      <c r="C191" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="D191" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E191" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F191" t="s" s="44">
+        <v>114</v>
+      </c>
+      <c r="G191" s="51">
+        <v>52</v>
       </c>
       <c r="H191" s="52">
-        <v>73902.24</v>
-      </c>
-      <c r="I191" s="53"/>
-      <c r="J191" s="48"/>
+        <v>471.46</v>
+      </c>
+      <c r="I191" s="53">
+        <v>52</v>
+      </c>
+      <c r="J191" t="s" s="48">
+        <v>115</v>
+      </c>
       <c r="K191" s="49"/>
       <c r="L191" s="0"/>
     </row>
     <row r="192">
-      <c r="A192" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B192" s="45">
-        <v>0000106883</v>
-      </c>
-      <c r="C192" t="s" s="46">
-        <v>260</v>
-      </c>
-      <c r="D192" t="s" s="46">
-        <v>222</v>
-      </c>
-      <c r="E192" t="s" s="47">
-        <v>39</v>
-      </c>
-      <c r="F192" t="s" s="44">
-        <v>28</v>
-      </c>
-      <c r="G192" s="51">
-        <v>23</v>
+      <c r="A192" s="44"/>
+      <c r="B192" s="45"/>
+      <c r="C192" s="46"/>
+      <c r="D192" s="46"/>
+      <c r="E192" s="47"/>
+      <c r="F192" s="44"/>
+      <c r="G192" t="s" s="51">
+        <v>27</v>
       </c>
       <c r="H192" s="52">
-        <v>1059.81</v>
-      </c>
-      <c r="I192" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J192" t="s" s="48">
-        <v>29</v>
-      </c>
+        <v>24515.92</v>
+      </c>
+      <c r="I192" s="53"/>
+      <c r="J192" s="48"/>
       <c r="K192" s="49"/>
       <c r="L192" s="0"/>
     </row>
@@ -7042,10 +7154,10 @@
         <v>27</v>
       </c>
       <c r="H194" s="52">
-        <v>1275106.09</v>
+        <v>1424144.34</v>
       </c>
       <c r="I194" s="53">
-        <v>2002.15</v>
+        <v>1806.9</v>
       </c>
       <c r="J194" s="48"/>
       <c r="K194" s="49"/>

--- a/data/latest.xlsx
+++ b/data/latest.xlsx
@@ -59,31 +59,6 @@
     <t>CAD($)</t>
   </si>
   <si>
-    <t>ENGINEERINGCPR      </t>
-  </si>
-  <si>
-    <t>12/10/2025</t>
-  </si>
-  <si>
-    <t>05/15/2026</t>
-  </si>
-  <si>
-    <t>PAST DUE</t>
-  </si>
-  <si>
-    <t>SMX-TC0179-8AEXXX                 </t>
-  </si>
-  <si>
-    <t>
-    </t>
-  </si>
-  <si>
-    <t>OASYS Extension Arm, 1000mm w/LCH Spring Arm, Custom End, Stops, Extra keys,9003</t>
-  </si>
-  <si>
-    <t>SHIP DATES - AS NOTED</t>
-  </si>
-  <si>
     <t>SIMEONMEDICALGMBH   </t>
   </si>
   <si>
@@ -93,7 +68,14 @@
     <t>05/29/2026</t>
   </si>
   <si>
+    <t>PAST DUE</t>
+  </si>
+  <si>
     <t>NS-SM-E479-9GJ-J                  </t>
+  </si>
+  <si>
+    <t>
+    </t>
   </si>
   <si>
     <t>SA, 2075, LCH, 9P, 9002                                                         </t>
@@ -101,9 +83,6 @@
   <si>
     <t>SHIP DATE - ASAP
 Return and Repair of Arms for RGA R25-004</t>
-  </si>
-  <si>
-    <t>TOTAL:</t>
   </si>
   <si>
     <t>NS-SM-E491-0GJ-J                  </t>
@@ -126,6 +105,9 @@
 Return and Repair of Arms for RGA R25-004 SA, 2075, 3P, 10 -20 kg, 9002                                                    SA, 2075, 3P, 10 -20 kg, 9002                                                   </t>
   </si>
   <si>
+    <t>05/15/2026</t>
+  </si>
+  <si>
     <t>NS-SM-E479-5GJ-J                  </t>
   </si>
   <si>
@@ -133,6 +115,9 @@
   </si>
   <si>
     <t>SHIP WITH ORDER 106935</t>
+  </si>
+  <si>
+    <t>TOTAL:</t>
   </si>
   <si>
     <t>SA, 2075, 3P, 10-20kg, 9002                                                     </t>
@@ -165,7 +150,22 @@
     <t>SHIP WITH ORDERS 106935 AND 106948</t>
   </si>
   <si>
+    <t>MAQUETSAS           </t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
     <t>06/12/2026</t>
+  </si>
+  <si>
+    <t>NS-SM-E479-3MH-Q                  </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med duty, LCH, Axial Stop, 3P, (127-165Nm), RAL 9016                </t>
+  </si>
+  <si>
+    <t>R26-006 - Holds weight as intended. Return as is.</t>
   </si>
   <si>
     <t>MONTH:</t>
@@ -175,21 +175,6 @@
   </si>
   <si>
     <t>Hours available = 600. Hours remaining = 600</t>
-  </si>
-  <si>
-    <t>MAQUETSAS           </t>
-  </si>
-  <si>
-    <t>06/05/2026</t>
-  </si>
-  <si>
-    <t>NS-SM-E479-3MH-Q                  </t>
-  </si>
-  <si>
-    <t>Spring Arm, Med duty, LCH, Axial Stop, 3P, (127-165Nm), RAL 9016                </t>
-  </si>
-  <si>
-    <t>R26-006 - Holds weight as intended. Return as is.</t>
   </si>
   <si>
     <t>NS-SM-L091-3MS-Q                  </t>
@@ -208,9 +193,6 @@
   </si>
   <si>
     <t>06/30/2026</t>
-  </si>
-  <si>
-    <t>OKAY</t>
   </si>
   <si>
     <t>SM-B691-9GJ-J                     </t>
@@ -320,18 +302,6 @@
     <t>Light Duty Wall Mount Spring Arm - White                                        </t>
   </si>
   <si>
-    <t>DERUNGSLICHT-EUR    </t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>SR-3P-M-ASSY-CR-HRNS              </t>
-  </si>
-  <si>
-    <t>3P Slip Ring - Male (with wiring components)                                    </t>
-  </si>
-  <si>
     <t>07/08/2026</t>
   </si>
   <si>
@@ -344,10 +314,22 @@
     <t>DOCK DATE - JULY 15, 2026</t>
   </si>
   <si>
-    <t>EGGMED              </t>
+    <t>07/10/2026</t>
   </si>
   <si>
-    <t>07/10/2026</t>
+    <t>OKAY</t>
+  </si>
+  <si>
+    <t>C-2-AW-PN                         </t>
+  </si>
+  <si>
+    <t>Single Ceiling Drop Tube, 3P Slip Ring and Harness, 900mm                       </t>
+  </si>
+  <si>
+    <t>DOCK DATE - JULY 17, 2026</t>
+  </si>
+  <si>
+    <t>EGGMED              </t>
   </si>
   <si>
     <t>SM-BERCH-EXT-ADP-9010             </t>
@@ -363,11 +345,25 @@
 Load 17.5kg, Stop, RAL 9010               </t>
   </si>
   <si>
-    <t>SM-G291-0WT-X                     </t>
+    <t>07/07/2026</t>
   </si>
   <si>
-    <t>Spring arm, Med Duty, 910mm, TM3001 w/2001 device end, Load 17.5
-kg, STP, 9010  </t>
+    <t>SM-C879-3WJ-5                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 2075, LCH, 3P, 46-57Nm, 9010                              </t>
+  </si>
+  <si>
+    <t>NEXORMEDICAL        </t>
+  </si>
+  <si>
+    <t>07/14/2026</t>
+  </si>
+  <si>
+    <t>SA-L-LCK-F-BRK-KT                 </t>
+  </si>
+  <si>
+    <t>Locking Collar with a brake screw                                               </t>
   </si>
   <si>
     <t>REDSHANK            </t>
@@ -401,6 +397,9 @@
   </si>
   <si>
     <t>DOCK DATE - JULY 24, 2026</t>
+  </si>
+  <si>
+    <t>DERUNGSLICHT-EUR    </t>
   </si>
   <si>
     <t>04/23/2026</t>
@@ -454,67 +453,25 @@
     <t>2001 Spring arm, 5 kg, 910mm, 3p, RAL 9010                                      </t>
   </si>
   <si>
+    <t>ENGINEERINGCPR      </t>
+  </si>
+  <si>
+    <t>12/10/2025</t>
+  </si>
+  <si>
+    <t>SMX-TC0179-8AEXXX                 </t>
+  </si>
+  <si>
+    <t>OASYS Extension Arm, 1000mm w/LCH Spring Arm, Custom End, Stops, Extra keys,9003</t>
+  </si>
+  <si>
+    <t>SHIP DATES - AS NOTED</t>
+  </si>
+  <si>
     <t>SCANATRON           </t>
   </si>
   <si>
     <t>06/18/2026</t>
-  </si>
-  <si>
-    <t>07/20/2026</t>
-  </si>
-  <si>
-    <t>CA1-02B-01-W5                     </t>
-  </si>
-  <si>
-    <t>Central Axis, Single, 850mm, 3P, RAL 9010                                       </t>
-  </si>
-  <si>
-    <t>CA1-02B-50-W5                     </t>
-  </si>
-  <si>
-    <t>Central Axis, Single, 850mm, 5P, RAL 9010                                       </t>
-  </si>
-  <si>
-    <t>CA2-06A-03-W5                     </t>
-  </si>
-  <si>
-    <t>Dual Central Axis, 700/850mm, 3P/3P, RAL 9010                                   </t>
-  </si>
-  <si>
-    <t>MMC-300-W2-080-X                  </t>
-  </si>
-  <si>
-    <t>32" (800mm) CENTRAL AXIS DROP TUBE and Flange - RAL 9010                        </t>
-  </si>
-  <si>
-    <t>MMC-300-WC-050-X                  </t>
-  </si>
-  <si>
-    <t>20" (500mm) CENTRAL AXIS DROP TUBE                                              </t>
-  </si>
-  <si>
-    <t>MMW-301-WX-XXX-5                  </t>
-  </si>
-  <si>
-    <t>Wall mount with 3P harness, RAL 9010                                            </t>
-  </si>
-  <si>
-    <t>SA-M-C-CV-DM                      </t>
-  </si>
-  <si>
-    <t>DOME CEILING COVER (Central Axis)                                               </t>
-  </si>
-  <si>
-    <t>SLF-55XX-7WM                      </t>
-  </si>
-  <si>
-    <t>Light Duty Floor Stand, 550mm Spring arm, 7kg max, RAL 9010                     </t>
-  </si>
-  <si>
-    <t>SLX-5580-7WM                      </t>
-  </si>
-  <si>
-    <t>Spring Arm, Light Duty, 550mm arm length, 800mm ext arm, 7kg, 3P, RAL 9010      </t>
   </si>
   <si>
     <t>SM-B179-3WH-5                     </t>
@@ -523,16 +480,19 @@
     <t>Spring Arm, Med Duty, 2001 LCH, 3P, bearing end, RAL 9010                       </t>
   </si>
   <si>
-    <t>SM-C879-3WJ-5                     </t>
+    <t>SHIP DATE - SEE NOTES</t>
   </si>
   <si>
-    <t>Spring Arm, Med Duty, 2075, LCH, 3P, 46-57Nm, 9010                              </t>
+    <t>07/06/2026</t>
   </si>
   <si>
-    <t>SM-E879-5WJ-5                     </t>
+    <t>07/20/2026</t>
   </si>
   <si>
-    <t>Spring Arm, Med Duty, 2075, LCH, 5P, 95-125Nm, 9010                             </t>
+    <t>SR-3P-M-ASSY                      </t>
+  </si>
+  <si>
+    <t>3P SLIP RING - MALE                                                             </t>
   </si>
   <si>
     <t>04/28/2026</t>
@@ -632,6 +592,54 @@
     <t>Weight for Floor Base                                                           </t>
   </si>
   <si>
+    <t>CA1-02B-01-W5                     </t>
+  </si>
+  <si>
+    <t>Central Axis, Single, 850mm, 3P, RAL 9010                                       </t>
+  </si>
+  <si>
+    <t>CA1-02B-50-W5                     </t>
+  </si>
+  <si>
+    <t>Central Axis, Single, 850mm, 5P, RAL 9010                                       </t>
+  </si>
+  <si>
+    <t>CA2-06A-03-W5                     </t>
+  </si>
+  <si>
+    <t>Dual Central Axis, 700/850mm, 3P/3P, RAL 9010                                   </t>
+  </si>
+  <si>
+    <t>MMW-301-WX-XXX-5                  </t>
+  </si>
+  <si>
+    <t>Wall mount with 3P harness, RAL 9010                                            </t>
+  </si>
+  <si>
+    <t>SA-M-C-CV-DM                      </t>
+  </si>
+  <si>
+    <t>DOME CEILING COVER (Central Axis)                                               </t>
+  </si>
+  <si>
+    <t>SLF-55XX-7WM                      </t>
+  </si>
+  <si>
+    <t>Light Duty Floor Stand, 550mm Spring arm, 7kg max, RAL 9010                     </t>
+  </si>
+  <si>
+    <t>SLX-5580-7WM                      </t>
+  </si>
+  <si>
+    <t>Spring Arm, Light Duty, 550mm arm length, 800mm ext arm, 7kg, 3P, RAL 9010      </t>
+  </si>
+  <si>
+    <t>SM-E879-5WJ-5                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 2075, LCH, 5P, 95-125Nm, 9010                             </t>
+  </si>
+  <si>
     <t>IMAGEDIAGNOSTICS    </t>
   </si>
   <si>
@@ -653,7 +661,7 @@
     <t>July, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = -208.2</t>
+    <t>Hours available = 600. Hours remaining = -215.2</t>
   </si>
   <si>
     <t>SM-E491-0MQ-X                     </t>
@@ -748,6 +756,21 @@
     <t>Spring Arm, Med Duty, 2075, Stop, 3-8kg, 9002                                   </t>
   </si>
   <si>
+    <t>08/24/2026</t>
+  </si>
+  <si>
+    <t>MMC-300-W2-080-X                  </t>
+  </si>
+  <si>
+    <t>32" (800mm) CENTRAL AXIS DROP TUBE and Flange - RAL 9010                        </t>
+  </si>
+  <si>
+    <t>MMC-300-WC-050-X                  </t>
+  </si>
+  <si>
+    <t>20" (500mm) CENTRAL AXIS DROP TUBE                                              </t>
+  </si>
+  <si>
     <t>06/26/2026</t>
   </si>
   <si>
@@ -775,6 +798,25 @@
     <t>DOCK DATE - October 14, 2026</t>
   </si>
   <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>DOCK DATE - OCTOBER 16, 2026</t>
+  </si>
+  <si>
+    <t>07/02/2026</t>
+  </si>
+  <si>
+    <t>SMX-TC0479-8AEXXX                 </t>
+  </si>
+  <si>
+    <t>OASYS Extension Arm, 950mm w/LCH Spring Arm, Custom End, Stops, Extra keys,9003 </t>
+  </si>
+  <si>
+    <t>SHIP 2 PCS ASAP
+SHIP DATE FOR REMAINDER SEPTEMBER</t>
+  </si>
+  <si>
     <t>08/31/2026</t>
   </si>
   <si>
@@ -796,7 +838,7 @@
     <t>August, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = 30.5</t>
+    <t>Hours available = 600. Hours remaining = -195</t>
   </si>
   <si>
     <t>EKONTOR             </t>
@@ -838,7 +880,16 @@
     <t>DOCK DATE - OCTOBER 5, 2026</t>
   </si>
   <si>
-    <t>10/16/2026</t>
+    <t>SR-3P-M-ASSY-CR-HRNS              </t>
+  </si>
+  <si>
+    <t>3P Slip Ring - Male (with wiring components)                                    </t>
+  </si>
+  <si>
+    <t>06/29/2026</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
   </si>
   <si>
     <t>September, 2026</t>
@@ -847,10 +898,16 @@
     <t>Hours available = 600. Hours remaining = 392.5</t>
   </si>
   <si>
+    <t>10/16/2026</t>
+  </si>
+  <si>
     <t>11/13/2026</t>
   </si>
   <si>
     <t>October, 2026</t>
+  </si>
+  <si>
+    <t>Hours available = 600. Hours remaining = 528</t>
   </si>
   <si>
     <t>07/04/2024</t>
@@ -920,18 +977,6 @@
     <t>SHIP DATE - DECEMBER 12, 2025</t>
   </si>
   <si>
-    <t>05/06/2024</t>
-  </si>
-  <si>
-    <t>***FORECAST</t>
-  </si>
-  <si>
-    <t>Spring Arm, Med Duty, 2001, 3P, (3.5 - 7kg), custom end cover, RAL 9016         </t>
-  </si>
-  <si>
-    <t>05/31/2024</t>
-  </si>
-  <si>
     <t>07/05/2024</t>
   </si>
   <si>
@@ -945,15 +990,6 @@
   </si>
   <si>
     <t>Spring Arm Med Duty, 910mm, 3P, TM2001, RAL 9016                                </t>
-  </si>
-  <si>
-    <t>SHIP DATE - AUGUST 10, 2026</t>
-  </si>
-  <si>
-    <t>SR-3P-M-ASSY                      </t>
-  </si>
-  <si>
-    <t>3P SLIP RING - MALE                                                             </t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1885,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="45">
-        <v>0000106778</v>
+        <v>0000106935</v>
       </c>
       <c r="C7" s="46" t="s">
         <v>14</v>
@@ -1864,10 +1900,10 @@
         <v>17</v>
       </c>
       <c r="G7" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7" s="52">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="I7" s="53" t="s">
         <v>18</v>
@@ -1881,41 +1917,59 @@
       <c r="L7" s="0"/>
     </row>
     <row r="8">
-      <c r="A8" s="44"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="44"/>
-      <c r="G8" t="s" s="51">
-        <v>27</v>
+      <c r="A8" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B8" s="45">
+        <v>0000106935</v>
+      </c>
+      <c r="C8" t="s" s="46">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s" s="46">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s" s="44">
+        <v>21</v>
+      </c>
+      <c r="G8" s="51">
+        <v>1</v>
       </c>
       <c r="H8" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I8" s="53"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="I8" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s" s="48">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s" s="49">
+        <v>20</v>
+      </c>
       <c r="L8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B9" s="45">
         <v>0000106935</v>
       </c>
       <c r="C9" t="s" s="46">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s" s="46">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F9" t="s" s="44">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" s="51">
         <v>1</v>
@@ -1927,7 +1981,7 @@
         <v>18</v>
       </c>
       <c r="J9" t="s" s="48">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s" s="49">
         <v>26</v>
@@ -1935,59 +1989,41 @@
       <c r="L9" s="0"/>
     </row>
     <row r="10">
-      <c r="A10" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B10" s="45">
-        <v>0000106935</v>
-      </c>
-      <c r="C10" t="s" s="46">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s" s="47">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s" s="44">
-        <v>28</v>
-      </c>
-      <c r="G10" s="51">
-        <v>1</v>
+      <c r="A10" s="44"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="44"/>
+      <c r="G10" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H10" s="52">
         <v>0</v>
       </c>
-      <c r="I10" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s" s="48">
-        <v>29</v>
-      </c>
-      <c r="K10" t="s" s="49">
-        <v>26</v>
-      </c>
+      <c r="I10" s="53"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
       <c r="L10" s="0"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B11" s="45">
-        <v>0000106935</v>
+        <v>0000106947</v>
       </c>
       <c r="C11" t="s" s="46">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s" s="46">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F11" t="s" s="44">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" s="51">
         <v>1</v>
@@ -1999,49 +2035,67 @@
         <v>18</v>
       </c>
       <c r="J11" t="s" s="48">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s" s="49">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L11" s="0"/>
     </row>
     <row r="12">
-      <c r="A12" s="44"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="44"/>
-      <c r="G12" t="s" s="51">
+      <c r="A12" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B12" s="45">
+        <v>0000106947</v>
+      </c>
+      <c r="C12" t="s" s="46">
         <v>27</v>
+      </c>
+      <c r="D12" t="s" s="46">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s" s="44">
+        <v>23</v>
+      </c>
+      <c r="G12" s="51">
+        <v>1</v>
       </c>
       <c r="H12" s="52">
         <v>0</v>
       </c>
-      <c r="I12" s="53"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="49"/>
+      <c r="I12" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s" s="48">
+        <v>32</v>
+      </c>
+      <c r="K12" t="s" s="49">
+        <v>30</v>
+      </c>
       <c r="L12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B13" s="45">
         <v>0000106947</v>
       </c>
       <c r="C13" t="s" s="46">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s" s="46">
         <v>15</v>
-      </c>
-      <c r="D13" t="s" s="46">
-        <v>23</v>
       </c>
       <c r="E13" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F13" t="s" s="44">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="51">
         <v>1</v>
@@ -2053,7 +2107,7 @@
         <v>18</v>
       </c>
       <c r="J13" t="s" s="48">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K13" t="s" s="49">
         <v>36</v>
@@ -2062,22 +2116,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B14" s="45">
         <v>0000106947</v>
       </c>
       <c r="C14" t="s" s="46">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s" s="46">
         <v>15</v>
-      </c>
-      <c r="D14" t="s" s="46">
-        <v>23</v>
       </c>
       <c r="E14" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F14" t="s" s="44">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G14" s="51">
         <v>1</v>
@@ -2089,67 +2143,49 @@
         <v>18</v>
       </c>
       <c r="J14" t="s" s="48">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s" s="49">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L14" s="0"/>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B15" s="45">
-        <v>0000106947</v>
-      </c>
-      <c r="C15" t="s" s="46">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s" s="47">
-        <v>16</v>
-      </c>
-      <c r="F15" t="s" s="44">
-        <v>38</v>
-      </c>
-      <c r="G15" s="51">
-        <v>1</v>
+      <c r="A15" s="44"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="44"/>
+      <c r="G15" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H15" s="52">
         <v>0</v>
       </c>
-      <c r="I15" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s" s="48">
-        <v>39</v>
-      </c>
-      <c r="K15" t="s" s="49">
-        <v>41</v>
-      </c>
+      <c r="I15" s="53"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="49"/>
       <c r="L15" s="0"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B16" s="45">
-        <v>0000106947</v>
+        <v>0000106948</v>
       </c>
       <c r="C16" t="s" s="46">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s" s="46">
         <v>15</v>
-      </c>
-      <c r="D16" t="s" s="46">
-        <v>23</v>
       </c>
       <c r="E16" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F16" t="s" s="44">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" s="51">
         <v>1</v>
@@ -2161,125 +2197,131 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="48">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K16" t="s" s="49">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L16" s="0"/>
     </row>
     <row r="17">
-      <c r="A17" s="44"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="44"/>
-      <c r="G17" t="s" s="51">
+      <c r="A17" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B17" s="45">
+        <v>0000106948</v>
+      </c>
+      <c r="C17" t="s" s="46">
         <v>27</v>
+      </c>
+      <c r="D17" t="s" s="46">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s" s="44">
+        <v>33</v>
+      </c>
+      <c r="G17" s="51">
+        <v>1</v>
       </c>
       <c r="H17" s="52">
         <v>0</v>
       </c>
-      <c r="I17" s="53"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="49"/>
+      <c r="I17" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s" s="48">
+        <v>34</v>
+      </c>
+      <c r="K17" t="s" s="49">
+        <v>41</v>
+      </c>
       <c r="L17" s="0"/>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B18" s="45">
-        <v>0000106948</v>
-      </c>
-      <c r="C18" t="s" s="46">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s" s="47">
-        <v>16</v>
-      </c>
+      <c r="A18" s="44"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="47"/>
       <c r="F18" t="s" s="44">
-        <v>44</v>
-      </c>
-      <c r="G18" s="51">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="G18" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H18" s="52">
         <v>0</v>
       </c>
-      <c r="I18" t="s" s="53">
+      <c r="I18" s="53" t="s">
         <v>18</v>
       </c>
       <c r="J18" t="s" s="48">
-        <v>45</v>
-      </c>
-      <c r="K18" t="s" s="49">
-        <v>46</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K18" s="49"/>
       <c r="L18" s="0"/>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B19" s="45">
-        <v>0000106948</v>
-      </c>
-      <c r="C19" t="s" s="46">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s" s="46">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s" s="47">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s" s="44">
-        <v>38</v>
-      </c>
-      <c r="G19" s="51">
-        <v>1</v>
+      <c r="A19" s="44"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H19" s="52">
         <v>0</v>
       </c>
-      <c r="I19" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J19" t="s" s="48">
-        <v>39</v>
-      </c>
-      <c r="K19" t="s" s="49">
-        <v>46</v>
-      </c>
+      <c r="I19" s="53">
+        <v>0</v>
+      </c>
+      <c r="J19" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" s="49"/>
       <c r="L19" s="0"/>
     </row>
     <row r="20">
-      <c r="A20" s="44"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="47"/>
+      <c r="A20" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B20" s="45">
+        <v>0000106969</v>
+      </c>
+      <c r="C20" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s" s="46">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s" s="47">
+        <v>16</v>
+      </c>
       <c r="F20" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G20" t="s" s="51">
-        <v>27</v>
+        <v>45</v>
+      </c>
+      <c r="G20" s="51">
+        <v>1</v>
       </c>
       <c r="H20" s="52">
         <v>0</v>
       </c>
-      <c r="I20" s="53" t="s">
+      <c r="I20" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J20" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K20" s="49"/>
+        <v>46</v>
+      </c>
+      <c r="K20" t="s" s="49">
+        <v>47</v>
+      </c>
       <c r="L20" s="0"/>
     </row>
     <row r="21">
@@ -2288,57 +2330,51 @@
       <c r="C21" s="46"/>
       <c r="D21" s="46"/>
       <c r="E21" s="47"/>
-      <c r="F21" s="44" t="s">
-        <v>49</v>
-      </c>
+      <c r="F21" s="44"/>
       <c r="G21" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H21" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I21" s="53">
         <v>0</v>
       </c>
-      <c r="J21" s="48" t="s">
-        <v>50</v>
-      </c>
+      <c r="I21" s="53"/>
+      <c r="J21" s="48"/>
       <c r="K21" s="49"/>
       <c r="L21" s="0"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="44">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B22" s="45">
-        <v>0000106778</v>
+        <v>0000106970</v>
       </c>
       <c r="C22" t="s" s="46">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s" s="46">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F22" t="s" s="44">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G22" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" s="52">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="I22" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J22" t="s" s="48">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="K22" t="s" s="49">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="L22" s="0"/>
     </row>
@@ -2350,10 +2386,10 @@
       <c r="E23" s="47"/>
       <c r="F23" s="44"/>
       <c r="G23" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H23" s="52">
-        <v>11250</v>
+        <v>0</v>
       </c>
       <c r="I23" s="53"/>
       <c r="J23" s="48"/>
@@ -2362,92 +2398,104 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="44">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" s="45">
-        <v>0000106969</v>
+        <v>0000106975</v>
       </c>
       <c r="C24" t="s" s="46">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s" s="46">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F24" t="s" s="44">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G24" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="52">
         <v>0</v>
       </c>
-      <c r="I24" t="s" s="53">
-        <v>18</v>
+      <c r="I24" s="53">
+        <v>6</v>
       </c>
       <c r="J24" t="s" s="48">
+        <v>58</v>
+      </c>
+      <c r="K24" s="49"/>
+      <c r="L24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="44">
         <v>54</v>
       </c>
-      <c r="K24" t="s" s="49">
+      <c r="B25" s="45">
+        <v>0000106975</v>
+      </c>
+      <c r="C25" t="s" s="46">
         <v>55</v>
       </c>
-      <c r="L24" s="0"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="44"/>
-      <c r="G25" t="s" s="51">
-        <v>27</v>
+      <c r="D25" t="s" s="46">
+        <v>56</v>
+      </c>
+      <c r="E25" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s" s="44">
+        <v>59</v>
+      </c>
+      <c r="G25" s="51">
+        <v>2</v>
       </c>
       <c r="H25" s="52">
         <v>0</v>
       </c>
-      <c r="I25" s="53"/>
-      <c r="J25" s="48"/>
+      <c r="I25" s="53">
+        <v>6</v>
+      </c>
+      <c r="J25" t="s" s="48">
+        <v>60</v>
+      </c>
       <c r="K25" s="49"/>
       <c r="L25" s="0"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="44">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" s="45">
-        <v>0000106970</v>
+        <v>0000106975</v>
       </c>
       <c r="C26" t="s" s="46">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s" s="46">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F26" t="s" s="44">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G26" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="52">
         <v>0</v>
       </c>
-      <c r="I26" t="s" s="53">
-        <v>18</v>
+      <c r="I26" s="53">
+        <v>6</v>
       </c>
       <c r="J26" t="s" s="48">
-        <v>57</v>
-      </c>
-      <c r="K26" t="s" s="49">
-        <v>58</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="K26" s="49"/>
       <c r="L26" s="0"/>
     </row>
     <row r="27">
@@ -2458,7 +2506,7 @@
       <c r="E27" s="47"/>
       <c r="F27" s="44"/>
       <c r="G27" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H27" s="52">
         <v>0</v>
@@ -2470,56 +2518,58 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="44">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B28" s="45">
-        <v>0000106975</v>
+        <v>0000106936</v>
       </c>
       <c r="C28" t="s" s="46">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s" s="46">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s" s="44">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G28" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="52">
         <v>0</v>
       </c>
-      <c r="I28" s="53">
-        <v>6</v>
+      <c r="I28" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J28" t="s" s="48">
-        <v>64</v>
-      </c>
-      <c r="K28" s="49"/>
+        <v>65</v>
+      </c>
+      <c r="K28" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L28" s="0"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="44">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B29" s="45">
-        <v>0000106975</v>
+        <v>0000106936</v>
       </c>
       <c r="C29" t="s" s="46">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s" s="46">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F29" t="s" s="44">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G29" s="51">
         <v>2</v>
@@ -2527,88 +2577,110 @@
       <c r="H29" s="52">
         <v>0</v>
       </c>
-      <c r="I29" s="53">
-        <v>6</v>
+      <c r="I29" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J29" t="s" s="48">
+        <v>68</v>
+      </c>
+      <c r="K29" t="s" s="49">
         <v>66</v>
       </c>
-      <c r="K29" s="49"/>
       <c r="L29" s="0"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="44">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B30" s="45">
-        <v>0000106975</v>
+        <v>0000106936</v>
       </c>
       <c r="C30" t="s" s="46">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s" s="46">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s" s="44">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G30" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="52">
         <v>0</v>
       </c>
-      <c r="I30" s="53">
-        <v>6</v>
+      <c r="I30" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J30" t="s" s="48">
-        <v>68</v>
-      </c>
-      <c r="K30" s="49"/>
+        <v>70</v>
+      </c>
+      <c r="K30" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L30" s="0"/>
     </row>
     <row r="31">
-      <c r="A31" s="44"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="44"/>
-      <c r="G31" t="s" s="51">
-        <v>27</v>
+      <c r="A31" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B31" s="45">
+        <v>0000106936</v>
+      </c>
+      <c r="C31" t="s" s="46">
+        <v>63</v>
+      </c>
+      <c r="D31" t="s" s="46">
+        <v>56</v>
+      </c>
+      <c r="E31" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s" s="44">
+        <v>71</v>
+      </c>
+      <c r="G31" s="51">
+        <v>2</v>
       </c>
       <c r="H31" s="52">
         <v>0</v>
       </c>
-      <c r="I31" s="53"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="49"/>
+      <c r="I31" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s" s="48">
+        <v>72</v>
+      </c>
+      <c r="K31" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L31" s="0"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B32" s="45">
         <v>0000106936</v>
       </c>
       <c r="C32" t="s" s="46">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D32" t="s" s="46">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s" s="44">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G32" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="52">
         <v>0</v>
@@ -2617,70 +2689,52 @@
         <v>18</v>
       </c>
       <c r="J32" t="s" s="48">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K32" t="s" s="49">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L32" s="0"/>
     </row>
     <row r="33">
-      <c r="A33" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B33" s="45">
-        <v>0000106936</v>
-      </c>
-      <c r="C33" t="s" s="46">
-        <v>69</v>
-      </c>
-      <c r="D33" t="s" s="46">
-        <v>61</v>
-      </c>
-      <c r="E33" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F33" t="s" s="44">
-        <v>73</v>
-      </c>
-      <c r="G33" s="51">
-        <v>2</v>
+      <c r="A33" s="44"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="44"/>
+      <c r="G33" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H33" s="52">
         <v>0</v>
       </c>
-      <c r="I33" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J33" t="s" s="48">
-        <v>74</v>
-      </c>
-      <c r="K33" t="s" s="49">
-        <v>72</v>
-      </c>
+      <c r="I33" s="53"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="49"/>
       <c r="L33" s="0"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B34" s="45">
-        <v>0000106936</v>
+        <v>0000106973</v>
       </c>
       <c r="C34" t="s" s="46">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s" s="46">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E34" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s" s="44">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G34" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="52">
         <v>0</v>
@@ -2689,31 +2743,31 @@
         <v>18</v>
       </c>
       <c r="J34" t="s" s="48">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s" s="49">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L34" s="0"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B35" s="45">
-        <v>0000106936</v>
+        <v>0000106973</v>
       </c>
       <c r="C35" t="s" s="46">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s" s="46">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E35" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s" s="44">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="G35" s="51">
         <v>2</v>
@@ -2725,31 +2779,31 @@
         <v>18</v>
       </c>
       <c r="J35" t="s" s="48">
+        <v>79</v>
+      </c>
+      <c r="K35" t="s" s="49">
         <v>78</v>
-      </c>
-      <c r="K35" t="s" s="49">
-        <v>72</v>
       </c>
       <c r="L35" s="0"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="44">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B36" s="45">
-        <v>0000106936</v>
+        <v>0000106973</v>
       </c>
       <c r="C36" t="s" s="46">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s" s="46">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E36" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s" s="44">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G36" s="51">
         <v>2</v>
@@ -2761,10 +2815,10 @@
         <v>18</v>
       </c>
       <c r="J36" t="s" s="48">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K36" t="s" s="49">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L36" s="0"/>
     </row>
@@ -2774,123 +2828,117 @@
       <c r="C37" s="46"/>
       <c r="D37" s="46"/>
       <c r="E37" s="47"/>
-      <c r="F37" s="44"/>
+      <c r="F37" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G37" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H37" s="52">
         <v>0</v>
       </c>
-      <c r="I37" s="53"/>
-      <c r="J37" s="48"/>
+      <c r="I37" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K37" s="49"/>
       <c r="L37" s="0"/>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="44">
-        <v>21</v>
-      </c>
-      <c r="B38" s="45">
-        <v>0000106973</v>
-      </c>
-      <c r="C38" t="s" s="46">
-        <v>81</v>
-      </c>
-      <c r="D38" t="s" s="46">
-        <v>61</v>
-      </c>
-      <c r="E38" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F38" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="G38" s="51">
-        <v>2</v>
+      <c r="A38" s="44"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H38" s="52">
         <v>0</v>
       </c>
-      <c r="I38" t="s" s="53">
+      <c r="I38" s="53">
         <v>18</v>
       </c>
-      <c r="J38" t="s" s="48">
-        <v>83</v>
-      </c>
-      <c r="K38" t="s" s="49">
-        <v>84</v>
-      </c>
+      <c r="J38" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="K38" s="49"/>
       <c r="L38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="44">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B39" s="45">
-        <v>0000106973</v>
+        <v>0000106939</v>
       </c>
       <c r="C39" t="s" s="46">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s" s="46">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E39" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F39" t="s" s="44">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G39" s="51">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H39" s="52">
-        <v>0</v>
-      </c>
-      <c r="I39" t="s" s="53">
-        <v>18</v>
+        <v>233.81</v>
+      </c>
+      <c r="I39" s="53">
+        <v>12.5</v>
       </c>
       <c r="J39" t="s" s="48">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K39" t="s" s="49">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L39" s="0"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="44">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="B40" s="45">
-        <v>0000106973</v>
+        <v>0000106939</v>
       </c>
       <c r="C40" t="s" s="46">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s" s="46">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E40" t="s" s="47">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s" s="44">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G40" s="51">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="H40" s="52">
-        <v>0</v>
-      </c>
-      <c r="I40" t="s" s="53">
-        <v>18</v>
+        <v>369.52</v>
+      </c>
+      <c r="I40" s="53">
+        <v>87.5</v>
       </c>
       <c r="J40" t="s" s="48">
+        <v>91</v>
+      </c>
+      <c r="K40" t="s" s="49">
         <v>87</v>
-      </c>
-      <c r="K40" t="s" s="49">
-        <v>84</v>
       </c>
       <c r="L40" s="0"/>
     </row>
@@ -2900,117 +2948,105 @@
       <c r="C41" s="46"/>
       <c r="D41" s="46"/>
       <c r="E41" s="47"/>
-      <c r="F41" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F41" s="44"/>
       <c r="G41" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H41" s="52">
-        <v>0</v>
-      </c>
-      <c r="I41" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>31711.65</v>
+      </c>
+      <c r="I41" s="53"/>
+      <c r="J41" s="48"/>
       <c r="K41" s="49"/>
       <c r="L41" s="0"/>
     </row>
     <row r="42">
-      <c r="A42" s="44"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="44" t="s">
+      <c r="A42" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B42" s="45">
+        <v>0000106938</v>
+      </c>
+      <c r="C42" t="s" s="46">
+        <v>83</v>
+      </c>
+      <c r="D42" t="s" s="46">
+        <v>92</v>
+      </c>
+      <c r="E42" t="s" s="47">
+        <v>16</v>
+      </c>
+      <c r="F42" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="G42" s="51">
+        <v>16</v>
+      </c>
+      <c r="H42" s="52">
+        <v>650.03</v>
+      </c>
+      <c r="I42" s="53">
+        <v>48</v>
+      </c>
+      <c r="J42" t="s" s="48">
         <v>94</v>
       </c>
-      <c r="G42" t="s" s="51">
-        <v>48</v>
-      </c>
-      <c r="H42" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I42" s="53">
-        <v>18</v>
-      </c>
-      <c r="J42" s="48" t="s">
+      <c r="K42" t="s" s="49">
         <v>95</v>
       </c>
-      <c r="K42" s="49"/>
       <c r="L42" s="0"/>
     </row>
     <row r="43">
-      <c r="A43" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B43" s="45">
-        <v>0000106939</v>
-      </c>
-      <c r="C43" t="s" s="46">
-        <v>89</v>
-      </c>
-      <c r="D43" t="s" s="46">
-        <v>90</v>
-      </c>
-      <c r="E43" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F43" t="s" s="44">
-        <v>91</v>
-      </c>
-      <c r="G43" s="51">
-        <v>25</v>
+      <c r="A43" s="44"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="44"/>
+      <c r="G43" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H43" s="52">
-        <v>233.81</v>
-      </c>
-      <c r="I43" s="53">
-        <v>12.5</v>
-      </c>
-      <c r="J43" t="s" s="48">
-        <v>92</v>
-      </c>
-      <c r="K43" t="s" s="49">
-        <v>93</v>
-      </c>
+        <v>10400.48</v>
+      </c>
+      <c r="I43" s="53"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="49"/>
       <c r="L43" s="0"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B44" s="45">
-        <v>0000106939</v>
+        <v>0000106988</v>
       </c>
       <c r="C44" t="s" s="46">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="D44" t="s" s="46">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s" s="44">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G44" s="51">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="H44" s="52">
-        <v>369.52</v>
+        <v>255.96</v>
       </c>
       <c r="I44" s="53">
-        <v>87.5</v>
+        <v>7.5</v>
       </c>
       <c r="J44" t="s" s="48">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K44" t="s" s="49">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="L44" s="0"/>
     </row>
@@ -3022,10 +3058,10 @@
       <c r="E45" s="47"/>
       <c r="F45" s="44"/>
       <c r="G45" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H45" s="52">
-        <v>31711.65</v>
+        <v>3839.4</v>
       </c>
       <c r="I45" s="53"/>
       <c r="J45" s="48"/>
@@ -3034,488 +3070,486 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="44">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B46" s="45">
-        <v>0000106913</v>
+        <v>0000106974</v>
       </c>
       <c r="C46" t="s" s="46">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s" s="46">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E46" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s" s="44">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G46" s="51">
-        <v>504</v>
+        <v>9</v>
       </c>
       <c r="H46" s="52">
-        <v>22.54</v>
+        <v>635.00</v>
       </c>
       <c r="I46" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J46" t="s" s="48">
+        <v>103</v>
+      </c>
+      <c r="K46" t="s" s="49">
+        <v>66</v>
+      </c>
+      <c r="L46" s="0"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="44">
         <v>101</v>
       </c>
-      <c r="K46" t="s" s="49">
-        <v>93</v>
-      </c>
-      <c r="L46" s="0"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="44"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="46"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="44"/>
-      <c r="G47" t="s" s="51">
-        <v>27</v>
+      <c r="B47" s="45">
+        <v>0000106974</v>
+      </c>
+      <c r="C47" t="s" s="46">
+        <v>44</v>
+      </c>
+      <c r="D47" t="s" s="46">
+        <v>96</v>
+      </c>
+      <c r="E47" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F47" t="s" s="44">
+        <v>104</v>
+      </c>
+      <c r="G47" s="51">
+        <v>9</v>
       </c>
       <c r="H47" s="52">
-        <v>11360.16</v>
-      </c>
-      <c r="I47" s="53"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="49"/>
+        <v>603.75</v>
+      </c>
+      <c r="I47" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J47" t="s" s="48">
+        <v>105</v>
+      </c>
+      <c r="K47" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L47" s="0"/>
     </row>
     <row r="48">
-      <c r="A48" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B48" s="45">
-        <v>0000106938</v>
-      </c>
-      <c r="C48" t="s" s="46">
-        <v>89</v>
-      </c>
-      <c r="D48" t="s" s="46">
-        <v>102</v>
-      </c>
-      <c r="E48" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F48" t="s" s="44">
-        <v>103</v>
-      </c>
-      <c r="G48" s="51">
-        <v>16</v>
+      <c r="A48" s="44"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="44"/>
+      <c r="G48" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H48" s="52">
-        <v>650.03</v>
-      </c>
-      <c r="I48" s="53">
-        <v>48</v>
-      </c>
-      <c r="J48" t="s" s="48">
-        <v>104</v>
-      </c>
-      <c r="K48" t="s" s="49">
-        <v>105</v>
-      </c>
+        <v>11148.75</v>
+      </c>
+      <c r="I48" s="53"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="49"/>
       <c r="L48" s="0"/>
     </row>
     <row r="49">
-      <c r="A49" s="44"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="44"/>
-      <c r="G49" t="s" s="51">
-        <v>27</v>
+      <c r="A49" t="s" s="44">
+        <v>54</v>
+      </c>
+      <c r="B49" s="45">
+        <v>0000106992</v>
+      </c>
+      <c r="C49" t="s" s="46">
+        <v>106</v>
+      </c>
+      <c r="D49" t="s" s="46">
+        <v>96</v>
+      </c>
+      <c r="E49" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F49" t="s" s="44">
+        <v>107</v>
+      </c>
+      <c r="G49" s="51">
+        <v>1</v>
       </c>
       <c r="H49" s="52">
-        <v>10400.48</v>
-      </c>
-      <c r="I49" s="53"/>
-      <c r="J49" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I49" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s" s="48">
+        <v>108</v>
+      </c>
       <c r="K49" s="49"/>
       <c r="L49" s="0"/>
     </row>
     <row r="50">
-      <c r="A50" t="s" s="44">
-        <v>106</v>
-      </c>
-      <c r="B50" s="45">
-        <v>0000106974</v>
-      </c>
-      <c r="C50" t="s" s="46">
-        <v>47</v>
-      </c>
-      <c r="D50" t="s" s="46">
-        <v>107</v>
-      </c>
-      <c r="E50" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F50" t="s" s="44">
-        <v>108</v>
-      </c>
-      <c r="G50" s="51">
-        <v>9</v>
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="44"/>
+      <c r="G50" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H50" s="52">
-        <v>625.48</v>
-      </c>
-      <c r="I50" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J50" t="s" s="48">
-        <v>109</v>
-      </c>
-      <c r="K50" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I50" s="53"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="49"/>
       <c r="L50" s="0"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="44">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B51" s="45">
-        <v>0000106974</v>
+        <v>0000106987</v>
       </c>
       <c r="C51" t="s" s="46">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D51" t="s" s="46">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E51" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F51" t="s" s="44">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G51" s="51">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="H51" s="52">
-        <v>594.70</v>
+        <v>25.06</v>
       </c>
       <c r="I51" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J51" t="s" s="48">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K51" t="s" s="49">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L51" s="0"/>
     </row>
     <row r="52">
-      <c r="A52" t="s" s="44">
-        <v>106</v>
-      </c>
-      <c r="B52" s="45">
-        <v>0000106974</v>
-      </c>
-      <c r="C52" t="s" s="46">
-        <v>47</v>
-      </c>
-      <c r="D52" t="s" s="46">
-        <v>107</v>
-      </c>
-      <c r="E52" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F52" t="s" s="44">
-        <v>112</v>
-      </c>
-      <c r="G52" s="51">
-        <v>3</v>
+      <c r="A52" s="44"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="44"/>
+      <c r="G52" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H52" s="52">
-        <v>972.51</v>
-      </c>
-      <c r="I52" t="s" s="53">
+        <v>751.8</v>
+      </c>
+      <c r="I52" s="53"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="49"/>
+      <c r="L52" s="0"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="44">
+        <v>113</v>
+      </c>
+      <c r="B53" s="45">
+        <v>0000106976</v>
+      </c>
+      <c r="C53" t="s" s="46">
+        <v>114</v>
+      </c>
+      <c r="D53" t="s" s="46">
+        <v>115</v>
+      </c>
+      <c r="E53" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F53" t="s" s="44">
+        <v>116</v>
+      </c>
+      <c r="G53" s="51">
+        <v>1</v>
+      </c>
+      <c r="H53" s="52">
+        <v>35.08</v>
+      </c>
+      <c r="I53" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J52" t="s" s="48">
-        <v>113</v>
-      </c>
-      <c r="K52" t="s" s="49">
-        <v>72</v>
-      </c>
-      <c r="L52" s="0"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="44"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="44"/>
-      <c r="G53" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H53" s="52">
-        <v>13899.15</v>
-      </c>
-      <c r="I53" s="53"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="49"/>
+      <c r="J53" t="s" s="48">
+        <v>117</v>
+      </c>
+      <c r="K53" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L53" s="0"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="44">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B54" s="45">
         <v>0000106976</v>
       </c>
       <c r="C54" t="s" s="46">
+        <v>114</v>
+      </c>
+      <c r="D54" t="s" s="46">
         <v>115</v>
       </c>
-      <c r="D54" t="s" s="46">
-        <v>116</v>
-      </c>
       <c r="E54" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F54" t="s" s="44">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G54" s="51">
         <v>1</v>
       </c>
       <c r="H54" s="52">
-        <v>35.08</v>
+        <v>624.51</v>
       </c>
       <c r="I54" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J54" t="s" s="48">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K54" t="s" s="49">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L54" s="0"/>
     </row>
     <row r="55">
-      <c r="A55" t="s" s="44">
-        <v>114</v>
-      </c>
-      <c r="B55" s="45">
-        <v>0000106976</v>
-      </c>
-      <c r="C55" t="s" s="46">
-        <v>115</v>
-      </c>
-      <c r="D55" t="s" s="46">
-        <v>116</v>
-      </c>
-      <c r="E55" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F55" t="s" s="44">
-        <v>119</v>
-      </c>
-      <c r="G55" s="51">
-        <v>1</v>
+      <c r="A55" s="44"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="44"/>
+      <c r="G55" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H55" s="52">
-        <v>624.51</v>
-      </c>
-      <c r="I55" t="s" s="53">
+        <v>659.59</v>
+      </c>
+      <c r="I55" s="53"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="0"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B56" s="45">
+        <v>0000106964</v>
+      </c>
+      <c r="C56" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D56" t="s" s="46">
+        <v>120</v>
+      </c>
+      <c r="E56" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F56" t="s" s="44">
+        <v>121</v>
+      </c>
+      <c r="G56" s="51">
+        <v>100</v>
+      </c>
+      <c r="H56" s="52">
+        <v>11.33</v>
+      </c>
+      <c r="I56" s="53">
+        <v>3.3</v>
+      </c>
+      <c r="J56" t="s" s="48">
+        <v>122</v>
+      </c>
+      <c r="K56" t="s" s="49">
+        <v>123</v>
+      </c>
+      <c r="L56" s="0"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="44"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="44"/>
+      <c r="G57" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H57" s="52">
+        <v>1133</v>
+      </c>
+      <c r="I57" s="53"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="0"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B58" s="45">
+        <v>0000106965</v>
+      </c>
+      <c r="C58" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D58" t="s" s="46">
+        <v>120</v>
+      </c>
+      <c r="E58" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F58" t="s" s="44">
+        <v>90</v>
+      </c>
+      <c r="G58" s="51">
+        <v>40</v>
+      </c>
+      <c r="H58" s="52">
+        <v>375.19</v>
+      </c>
+      <c r="I58" s="53">
+        <v>50</v>
+      </c>
+      <c r="J58" t="s" s="48">
+        <v>91</v>
+      </c>
+      <c r="K58" t="s" s="49">
+        <v>123</v>
+      </c>
+      <c r="L58" s="0"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="44"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="44"/>
+      <c r="G59" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H59" s="52">
+        <v>15007.6</v>
+      </c>
+      <c r="I59" s="53"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="0"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="44">
+        <v>124</v>
+      </c>
+      <c r="B60" s="45">
+        <v>0000106923</v>
+      </c>
+      <c r="C60" t="s" s="46">
+        <v>125</v>
+      </c>
+      <c r="D60" t="s" s="46">
+        <v>120</v>
+      </c>
+      <c r="E60" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F60" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="G60" s="51">
+        <v>135</v>
+      </c>
+      <c r="H60" s="52">
+        <v>312.70</v>
+      </c>
+      <c r="I60" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J55" t="s" s="48">
+      <c r="J60" t="s" s="48">
+        <v>127</v>
+      </c>
+      <c r="K60" t="s" s="49">
+        <v>128</v>
+      </c>
+      <c r="L60" s="0"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="44"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="44"/>
+      <c r="G61" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H61" s="52">
+        <v>42214.5</v>
+      </c>
+      <c r="I61" s="53"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="49"/>
+      <c r="L61" s="0"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="44">
+        <v>129</v>
+      </c>
+      <c r="B62" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C62" t="s" s="46">
+        <v>130</v>
+      </c>
+      <c r="D62" t="s" s="46">
         <v>120</v>
       </c>
-      <c r="K55" t="s" s="49">
-        <v>72</v>
-      </c>
-      <c r="L55" s="0"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="44"/>
-      <c r="B56" s="45"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="44"/>
-      <c r="G56" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H56" s="52">
-        <v>659.59</v>
-      </c>
-      <c r="I56" s="53"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="49"/>
-      <c r="L56" s="0"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B57" s="45">
-        <v>0000106964</v>
-      </c>
-      <c r="C57" t="s" s="46">
-        <v>52</v>
-      </c>
-      <c r="D57" t="s" s="46">
-        <v>121</v>
-      </c>
-      <c r="E57" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F57" t="s" s="44">
-        <v>122</v>
-      </c>
-      <c r="G57" s="51">
-        <v>100</v>
-      </c>
-      <c r="H57" s="52">
-        <v>11.33</v>
-      </c>
-      <c r="I57" s="53">
-        <v>3.3</v>
-      </c>
-      <c r="J57" t="s" s="48">
-        <v>123</v>
-      </c>
-      <c r="K57" t="s" s="49">
-        <v>124</v>
-      </c>
-      <c r="L57" s="0"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="44"/>
-      <c r="B58" s="45"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="44"/>
-      <c r="G58" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H58" s="52">
-        <v>1133</v>
-      </c>
-      <c r="I58" s="53"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="49"/>
-      <c r="L58" s="0"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B59" s="45">
-        <v>0000106965</v>
-      </c>
-      <c r="C59" t="s" s="46">
-        <v>52</v>
-      </c>
-      <c r="D59" t="s" s="46">
-        <v>121</v>
-      </c>
-      <c r="E59" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F59" t="s" s="44">
-        <v>96</v>
-      </c>
-      <c r="G59" s="51">
+      <c r="E62" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F62" t="s" s="44">
+        <v>131</v>
+      </c>
+      <c r="G62" s="51">
         <v>40</v>
       </c>
-      <c r="H59" s="52">
-        <v>375.19</v>
-      </c>
-      <c r="I59" s="53">
-        <v>50</v>
-      </c>
-      <c r="J59" t="s" s="48">
-        <v>97</v>
-      </c>
-      <c r="K59" t="s" s="49">
-        <v>124</v>
-      </c>
-      <c r="L59" s="0"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="44"/>
-      <c r="B60" s="45"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="44"/>
-      <c r="G60" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H60" s="52">
-        <v>15007.6</v>
-      </c>
-      <c r="I60" s="53"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="49"/>
-      <c r="L60" s="0"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="44">
-        <v>98</v>
-      </c>
-      <c r="B61" s="45">
-        <v>0000106923</v>
-      </c>
-      <c r="C61" t="s" s="46">
-        <v>125</v>
-      </c>
-      <c r="D61" t="s" s="46">
-        <v>121</v>
-      </c>
-      <c r="E61" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F61" t="s" s="44">
-        <v>126</v>
-      </c>
-      <c r="G61" s="51">
-        <v>135</v>
-      </c>
-      <c r="H61" s="52">
-        <v>312.70</v>
-      </c>
-      <c r="I61" t="s" s="53">
+      <c r="H62" s="52">
+        <v>951.36</v>
+      </c>
+      <c r="I62" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J61" t="s" s="48">
-        <v>127</v>
-      </c>
-      <c r="K61" t="s" s="49">
-        <v>128</v>
-      </c>
-      <c r="L61" s="0"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="44"/>
-      <c r="B62" s="45"/>
-      <c r="C62" s="46"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="44"/>
-      <c r="G62" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H62" s="52">
-        <v>42214.5</v>
-      </c>
-      <c r="I62" s="53"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="49"/>
+      <c r="J62" t="s" s="48">
+        <v>132</v>
+      </c>
+      <c r="K62" t="s" s="49">
+        <v>133</v>
+      </c>
       <c r="L62" s="0"/>
     </row>
     <row r="63">
@@ -3529,25 +3563,25 @@
         <v>130</v>
       </c>
       <c r="D63" t="s" s="46">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E63" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F63" t="s" s="44">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G63" s="51">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H63" s="52">
-        <v>951.36</v>
-      </c>
-      <c r="I63" t="s" s="53">
-        <v>18</v>
+        <v>277.48</v>
+      </c>
+      <c r="I63" s="53">
+        <v>6.25</v>
       </c>
       <c r="J63" t="s" s="48">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K63" t="s" s="49">
         <v>133</v>
@@ -3565,25 +3599,25 @@
         <v>130</v>
       </c>
       <c r="D64" t="s" s="46">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E64" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F64" t="s" s="44">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G64" s="51">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H64" s="52">
-        <v>277.48</v>
-      </c>
-      <c r="I64" s="53">
-        <v>6.25</v>
+        <v>364.68</v>
+      </c>
+      <c r="I64" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J64" t="s" s="48">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K64" t="s" s="49">
         <v>133</v>
@@ -3601,25 +3635,25 @@
         <v>130</v>
       </c>
       <c r="D65" t="s" s="46">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E65" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F65" t="s" s="44">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G65" s="51">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="H65" s="52">
-        <v>364.68</v>
+        <v>277.48</v>
       </c>
       <c r="I65" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J65" t="s" s="48">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K65" t="s" s="49">
         <v>133</v>
@@ -3637,25 +3671,25 @@
         <v>130</v>
       </c>
       <c r="D66" t="s" s="46">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E66" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F66" t="s" s="44">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G66" s="51">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="H66" s="52">
-        <v>277.48</v>
+        <v>364.68</v>
       </c>
       <c r="I66" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J66" t="s" s="48">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K66" t="s" s="49">
         <v>133</v>
@@ -3663,647 +3697,557 @@
       <c r="L66" s="0"/>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="44">
-        <v>129</v>
-      </c>
-      <c r="B67" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C67" t="s" s="46">
-        <v>130</v>
-      </c>
-      <c r="D67" t="s" s="46">
-        <v>121</v>
-      </c>
-      <c r="E67" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F67" t="s" s="44">
-        <v>140</v>
-      </c>
-      <c r="G67" s="51">
+      <c r="A67" s="44"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="46"/>
+      <c r="D67" s="46"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="44"/>
+      <c r="G67" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H67" s="52">
+        <v>73389.36</v>
+      </c>
+      <c r="I67" s="53"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="49"/>
+      <c r="L67" s="0"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="44">
+        <v>142</v>
+      </c>
+      <c r="B68" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C68" t="s" s="46">
+        <v>143</v>
+      </c>
+      <c r="D68" t="s" s="46">
+        <v>120</v>
+      </c>
+      <c r="E68" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F68" t="s" s="44">
+        <v>144</v>
+      </c>
+      <c r="G68" s="51">
+        <v>5</v>
+      </c>
+      <c r="H68" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I68" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J68" t="s" s="48">
+        <v>145</v>
+      </c>
+      <c r="K68" t="s" s="49">
+        <v>146</v>
+      </c>
+      <c r="L68" s="0"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="44"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="46"/>
+      <c r="D69" s="46"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="44"/>
+      <c r="G69" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H69" s="52">
+        <v>11250</v>
+      </c>
+      <c r="I69" s="53"/>
+      <c r="J69" s="48"/>
+      <c r="K69" s="49"/>
+      <c r="L69" s="0"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="44">
+        <v>147</v>
+      </c>
+      <c r="B70" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C70" t="s" s="46">
+        <v>148</v>
+      </c>
+      <c r="D70" t="s" s="46">
+        <v>120</v>
+      </c>
+      <c r="E70" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F70" t="s" s="44">
+        <v>149</v>
+      </c>
+      <c r="G70" s="51">
         <v>2</v>
       </c>
-      <c r="H67" s="52">
-        <v>364.68</v>
-      </c>
-      <c r="I67" t="s" s="53">
+      <c r="H70" s="52">
+        <v>609.3</v>
+      </c>
+      <c r="I70" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J67" t="s" s="48">
-        <v>141</v>
-      </c>
-      <c r="K67" t="s" s="49">
-        <v>133</v>
-      </c>
-      <c r="L67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="44"/>
-      <c r="B68" s="45"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="44"/>
-      <c r="G68" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H68" s="52">
-        <v>73389.36</v>
-      </c>
-      <c r="I68" s="53"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="49"/>
-      <c r="L68" s="0"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B69" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C69" t="s" s="46">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s" s="46">
-        <v>121</v>
-      </c>
-      <c r="E69" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F69" t="s" s="44">
-        <v>17</v>
-      </c>
-      <c r="G69" s="51">
-        <v>5</v>
-      </c>
-      <c r="H69" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I69" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J69" t="s" s="48">
-        <v>19</v>
-      </c>
-      <c r="K69" t="s" s="49">
-        <v>20</v>
-      </c>
-      <c r="L69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="44"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="44"/>
-      <c r="G70" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H70" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I70" s="53"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="49"/>
+      <c r="J70" t="s" s="48">
+        <v>150</v>
+      </c>
+      <c r="K70" t="s" s="49">
+        <v>151</v>
+      </c>
       <c r="L70" s="0"/>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B71" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C71" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D71" t="s" s="46">
-        <v>144</v>
-      </c>
-      <c r="E71" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F71" t="s" s="44">
-        <v>145</v>
-      </c>
-      <c r="G71" s="51">
-        <v>1</v>
+      <c r="A71" s="44"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="46"/>
+      <c r="D71" s="46"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="44"/>
+      <c r="G71" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H71" s="52">
-        <v>1245.24</v>
-      </c>
-      <c r="I71" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J71" t="s" s="48">
-        <v>146</v>
-      </c>
-      <c r="K71" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>1218.6</v>
+      </c>
+      <c r="I71" s="53"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="49"/>
       <c r="L71" s="0"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="44">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B72" s="45">
-        <v>0000106977</v>
+        <v>0000106991</v>
       </c>
       <c r="C72" t="s" s="46">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D72" t="s" s="46">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E72" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F72" t="s" s="44">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G72" s="51">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H72" s="52">
-        <v>1280.82</v>
+        <v>12.99</v>
       </c>
       <c r="I72" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J72" t="s" s="48">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="K72" t="s" s="49">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L72" s="0"/>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B73" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C73" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D73" t="s" s="46">
-        <v>144</v>
-      </c>
-      <c r="E73" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F73" t="s" s="44">
-        <v>149</v>
-      </c>
-      <c r="G73" s="51">
-        <v>1</v>
+      <c r="A73" s="44"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="46"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="44"/>
+      <c r="G73" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H73" s="52">
-        <v>1447.39</v>
-      </c>
-      <c r="I73" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J73" t="s" s="48">
-        <v>150</v>
-      </c>
-      <c r="K73" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>1299</v>
+      </c>
+      <c r="I73" s="53"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="49"/>
       <c r="L73" s="0"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="44">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B74" s="45">
-        <v>0000106977</v>
+        <v>0000106924</v>
       </c>
       <c r="C74" t="s" s="46">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D74" t="s" s="46">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E74" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F74" t="s" s="44">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G74" s="51">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="H74" s="52">
-        <v>566.02</v>
-      </c>
-      <c r="I74" t="s" s="53">
-        <v>18</v>
+        <v>285.87</v>
+      </c>
+      <c r="I74" s="53">
+        <v>225</v>
       </c>
       <c r="J74" t="s" s="48">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="K74" t="s" s="49">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="L74" s="0"/>
     </row>
     <row r="75">
-      <c r="A75" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B75" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C75" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D75" t="s" s="46">
-        <v>144</v>
-      </c>
-      <c r="E75" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F75" t="s" s="44">
-        <v>153</v>
-      </c>
-      <c r="G75" s="51">
-        <v>2</v>
+      <c r="A75" s="44"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="46"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="47"/>
+      <c r="F75" s="44"/>
+      <c r="G75" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H75" s="52">
-        <v>525.59</v>
-      </c>
-      <c r="I75" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="J75" t="s" s="48">
-        <v>154</v>
-      </c>
-      <c r="K75" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>51456.6</v>
+      </c>
+      <c r="I75" s="53"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="49"/>
       <c r="L75" s="0"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="44">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="B76" s="45">
-        <v>0000106977</v>
+        <v>0000106962</v>
       </c>
       <c r="C76" t="s" s="46">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D76" t="s" s="46">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="E76" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F76" t="s" s="44">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G76" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H76" s="52">
-        <v>161.72</v>
+        <v>1691.23</v>
       </c>
       <c r="I76" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J76" t="s" s="48">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="K76" t="s" s="49">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="L76" s="0"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="44">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="B77" s="45">
-        <v>0000106977</v>
+        <v>0000106962</v>
       </c>
       <c r="C77" t="s" s="46">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D77" t="s" s="46">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="E77" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F77" t="s" s="44">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G77" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H77" s="52">
-        <v>143.93</v>
+        <v>636.22</v>
       </c>
       <c r="I77" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J77" t="s" s="48">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="K77" t="s" s="49">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="L77" s="0"/>
     </row>
     <row r="78">
-      <c r="A78" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B78" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C78" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D78" t="s" s="46">
-        <v>144</v>
-      </c>
-      <c r="E78" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F78" t="s" s="44">
-        <v>159</v>
-      </c>
-      <c r="G78" s="51">
-        <v>4</v>
+      <c r="A78" s="44"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="46"/>
+      <c r="D78" s="46"/>
+      <c r="E78" s="47"/>
+      <c r="F78" s="44"/>
+      <c r="G78" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H78" s="52">
-        <v>654.96</v>
-      </c>
-      <c r="I78" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J78" t="s" s="48">
-        <v>160</v>
-      </c>
-      <c r="K78" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>11637.25</v>
+      </c>
+      <c r="I78" s="53"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="49"/>
       <c r="L78" s="0"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="44">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="B79" s="45">
-        <v>0000106977</v>
+        <v>0000106959</v>
       </c>
       <c r="C79" t="s" s="46">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D79" t="s" s="46">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="E79" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s" s="44">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G79" s="51">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="H79" s="52">
-        <v>380.04</v>
-      </c>
-      <c r="I79" t="s" s="53">
-        <v>18</v>
+        <v>472.59</v>
+      </c>
+      <c r="I79" s="53">
+        <v>52</v>
       </c>
       <c r="J79" t="s" s="48">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="K79" t="s" s="49">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="L79" s="0"/>
     </row>
     <row r="80">
-      <c r="A80" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B80" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C80" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D80" t="s" s="46">
-        <v>144</v>
-      </c>
-      <c r="E80" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F80" t="s" s="44">
-        <v>163</v>
-      </c>
-      <c r="G80" s="51">
-        <v>2</v>
+      <c r="A80" s="44"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="46"/>
+      <c r="D80" s="46"/>
+      <c r="E80" s="47"/>
+      <c r="F80" s="44"/>
+      <c r="G80" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H80" s="52">
-        <v>606.45</v>
-      </c>
-      <c r="I80" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J80" t="s" s="48">
-        <v>164</v>
-      </c>
-      <c r="K80" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>24574.68</v>
+      </c>
+      <c r="I80" s="53"/>
+      <c r="J80" s="48"/>
+      <c r="K80" s="49"/>
       <c r="L80" s="0"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="44">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="B81" s="45">
-        <v>0000106977</v>
+        <v>0000106960</v>
       </c>
       <c r="C81" t="s" s="46">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="D81" t="s" s="46">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="E81" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F81" t="s" s="44">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G81" s="51">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="H81" s="52">
-        <v>638.79</v>
-      </c>
-      <c r="I81" t="s" s="53">
+        <v>367.17</v>
+      </c>
+      <c r="I81" s="53">
+        <v>156</v>
+      </c>
+      <c r="J81" t="s" s="48">
+        <v>52</v>
+      </c>
+      <c r="K81" t="s" s="49">
+        <v>172</v>
+      </c>
+      <c r="L81" s="0"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="44"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="47"/>
+      <c r="F82" s="44"/>
+      <c r="G82" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H82" s="52">
+        <v>57278.52</v>
+      </c>
+      <c r="I82" s="53"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="49"/>
+      <c r="L82" s="0"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B83" s="45">
+        <v>0000106961</v>
+      </c>
+      <c r="C83" t="s" s="46">
+        <v>169</v>
+      </c>
+      <c r="D83" t="s" s="46">
+        <v>163</v>
+      </c>
+      <c r="E83" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F83" t="s" s="44">
+        <v>174</v>
+      </c>
+      <c r="G83" s="51">
+        <v>52</v>
+      </c>
+      <c r="H83" s="52">
+        <v>510.62</v>
+      </c>
+      <c r="I83" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J81" t="s" s="48">
-        <v>166</v>
-      </c>
-      <c r="K81" t="s" s="49">
-        <v>72</v>
-      </c>
-      <c r="L81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B82" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C82" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D82" t="s" s="46">
-        <v>144</v>
-      </c>
-      <c r="E82" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F82" t="s" s="44">
-        <v>167</v>
-      </c>
-      <c r="G82" s="51">
-        <v>1</v>
-      </c>
-      <c r="H82" s="52">
-        <v>638.79</v>
-      </c>
-      <c r="I82" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J82" t="s" s="48">
-        <v>168</v>
-      </c>
-      <c r="K82" t="s" s="49">
-        <v>72</v>
-      </c>
-      <c r="L82" s="0"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="44"/>
-      <c r="B83" s="45"/>
-      <c r="C83" s="46"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="44"/>
-      <c r="G83" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H83" s="52">
-        <v>17902.35</v>
-      </c>
-      <c r="I83" s="53"/>
-      <c r="J83" s="48"/>
-      <c r="K83" s="49"/>
+      <c r="J83" t="s" s="48">
+        <v>175</v>
+      </c>
+      <c r="K83" t="s" s="49">
+        <v>172</v>
+      </c>
       <c r="L83" s="0"/>
     </row>
     <row r="84">
-      <c r="A84" t="s" s="44">
-        <v>98</v>
-      </c>
-      <c r="B84" s="45">
-        <v>0000106924</v>
-      </c>
-      <c r="C84" t="s" s="46">
-        <v>169</v>
-      </c>
-      <c r="D84" t="s" s="46">
-        <v>170</v>
-      </c>
-      <c r="E84" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F84" t="s" s="44">
-        <v>171</v>
-      </c>
-      <c r="G84" s="51">
-        <v>180</v>
+      <c r="A84" s="44"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="46"/>
+      <c r="D84" s="46"/>
+      <c r="E84" s="47"/>
+      <c r="F84" s="44"/>
+      <c r="G84" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H84" s="52">
-        <v>285.87</v>
-      </c>
-      <c r="I84" s="53">
-        <v>225</v>
-      </c>
-      <c r="J84" t="s" s="48">
-        <v>172</v>
-      </c>
-      <c r="K84" t="s" s="49">
-        <v>173</v>
-      </c>
+        <v>26552.24</v>
+      </c>
+      <c r="I84" s="53"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="49"/>
       <c r="L84" s="0"/>
     </row>
     <row r="85">
-      <c r="A85" s="44"/>
-      <c r="B85" s="45"/>
-      <c r="C85" s="46"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="44"/>
-      <c r="G85" t="s" s="51">
-        <v>27</v>
+      <c r="A85" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B85" s="45">
+        <v>0000106940</v>
+      </c>
+      <c r="C85" t="s" s="46">
+        <v>83</v>
+      </c>
+      <c r="D85" t="s" s="46">
+        <v>176</v>
+      </c>
+      <c r="E85" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F85" t="s" s="44">
+        <v>177</v>
+      </c>
+      <c r="G85" s="51">
+        <v>16</v>
       </c>
       <c r="H85" s="52">
-        <v>51456.6</v>
-      </c>
-      <c r="I85" s="53"/>
-      <c r="J85" s="48"/>
-      <c r="K85" s="49"/>
+        <v>563.86</v>
+      </c>
+      <c r="I85" s="53">
+        <v>48</v>
+      </c>
+      <c r="J85" t="s" s="48">
+        <v>178</v>
+      </c>
+      <c r="K85" t="s" s="49">
+        <v>179</v>
+      </c>
       <c r="L85" s="0"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="44">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="B86" s="45">
-        <v>0000106962</v>
+        <v>0000106940</v>
       </c>
       <c r="C86" t="s" s="46">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="D86" t="s" s="46">
         <v>176</v>
       </c>
       <c r="E86" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F86" t="s" s="44">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="G86" s="51">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="H86" s="52">
-        <v>1691.23</v>
-      </c>
-      <c r="I86" t="s" s="53">
-        <v>18</v>
+        <v>369.52</v>
+      </c>
+      <c r="I86" s="53">
+        <v>87.5</v>
       </c>
       <c r="J86" t="s" s="48">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="49">
         <v>179</v>
@@ -4311,92 +4255,92 @@
       <c r="L86" s="0"/>
     </row>
     <row r="87">
-      <c r="A87" t="s" s="44">
-        <v>174</v>
-      </c>
-      <c r="B87" s="45">
-        <v>0000106962</v>
-      </c>
-      <c r="C87" t="s" s="46">
-        <v>175</v>
-      </c>
-      <c r="D87" t="s" s="46">
+      <c r="A87" s="44"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="46"/>
+      <c r="D87" s="46"/>
+      <c r="E87" s="47"/>
+      <c r="F87" s="44"/>
+      <c r="G87" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H87" s="52">
+        <v>34888.16</v>
+      </c>
+      <c r="I87" s="53"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="49"/>
+      <c r="L87" s="0"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B88" s="45">
+        <v>0000106941</v>
+      </c>
+      <c r="C88" t="s" s="46">
+        <v>83</v>
+      </c>
+      <c r="D88" t="s" s="46">
         <v>176</v>
       </c>
-      <c r="E87" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F87" t="s" s="44">
+      <c r="E88" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F88" t="s" s="44">
         <v>180</v>
       </c>
-      <c r="G87" s="51">
-        <v>5</v>
-      </c>
-      <c r="H87" s="52">
-        <v>636.22</v>
-      </c>
-      <c r="I87" t="s" s="53">
+      <c r="G88" s="51">
+        <v>50</v>
+      </c>
+      <c r="H88" s="52">
+        <v>4.44</v>
+      </c>
+      <c r="I88" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J87" t="s" s="48">
+      <c r="J88" t="s" s="48">
         <v>181</v>
       </c>
-      <c r="K87" t="s" s="49">
+      <c r="K88" t="s" s="49">
         <v>179</v>
       </c>
-      <c r="L87" s="0"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="44"/>
-      <c r="B88" s="45"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="44"/>
-      <c r="G88" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H88" s="52">
-        <v>11637.25</v>
-      </c>
-      <c r="I88" s="53"/>
-      <c r="J88" s="48"/>
-      <c r="K88" s="49"/>
       <c r="L88" s="0"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="44">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B89" s="45">
-        <v>0000106959</v>
+        <v>0000106941</v>
       </c>
       <c r="C89" t="s" s="46">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="D89" t="s" s="46">
         <v>176</v>
       </c>
       <c r="E89" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F89" t="s" s="44">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="G89" s="51">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="H89" s="52">
-        <v>472.59</v>
+        <v>11.16</v>
       </c>
       <c r="I89" s="53">
-        <v>52</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="s" s="48">
-        <v>184</v>
+        <v>122</v>
       </c>
       <c r="K89" t="s" s="49">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="L89" s="0"/>
     </row>
@@ -4408,10 +4352,10 @@
       <c r="E90" s="47"/>
       <c r="F90" s="44"/>
       <c r="G90" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H90" s="52">
-        <v>24574.68</v>
+        <v>1338</v>
       </c>
       <c r="I90" s="53"/>
       <c r="J90" s="48"/>
@@ -4420,91 +4364,109 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="44">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B91" s="45">
-        <v>0000106960</v>
+        <v>0000106942</v>
       </c>
       <c r="C91" t="s" s="46">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="D91" t="s" s="46">
         <v>176</v>
       </c>
       <c r="E91" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F91" t="s" s="44">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G91" s="51">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="H91" s="52">
-        <v>367.17</v>
-      </c>
-      <c r="I91" s="53">
-        <v>156</v>
+        <v>228.21</v>
+      </c>
+      <c r="I91" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J91" t="s" s="48">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="K91" t="s" s="49">
+        <v>179</v>
+      </c>
+      <c r="L91" s="0"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B92" s="45">
+        <v>0000106942</v>
+      </c>
+      <c r="C92" t="s" s="46">
+        <v>83</v>
+      </c>
+      <c r="D92" t="s" s="46">
+        <v>176</v>
+      </c>
+      <c r="E92" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F92" t="s" s="44">
+        <v>184</v>
+      </c>
+      <c r="G92" s="51">
+        <v>50</v>
+      </c>
+      <c r="H92" s="52">
+        <v>213.41</v>
+      </c>
+      <c r="I92" s="53">
+        <v>25</v>
+      </c>
+      <c r="J92" t="s" s="48">
         <v>185</v>
       </c>
-      <c r="L91" s="0"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="44"/>
-      <c r="B92" s="45"/>
-      <c r="C92" s="46"/>
-      <c r="D92" s="46"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="44"/>
-      <c r="G92" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H92" s="52">
-        <v>57278.52</v>
-      </c>
-      <c r="I92" s="53"/>
-      <c r="J92" s="48"/>
-      <c r="K92" s="49"/>
+      <c r="K92" t="s" s="49">
+        <v>179</v>
+      </c>
       <c r="L92" s="0"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="44">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B93" s="45">
-        <v>0000106961</v>
+        <v>0000106942</v>
       </c>
       <c r="C93" t="s" s="46">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="D93" t="s" s="46">
         <v>176</v>
       </c>
       <c r="E93" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F93" t="s" s="44">
+        <v>186</v>
+      </c>
+      <c r="G93" s="51">
+        <v>50</v>
+      </c>
+      <c r="H93" s="52">
+        <v>30.65</v>
+      </c>
+      <c r="I93" s="53">
+        <v>3.35</v>
+      </c>
+      <c r="J93" t="s" s="48">
         <v>187</v>
       </c>
-      <c r="G93" s="51">
-        <v>52</v>
-      </c>
-      <c r="H93" s="52">
-        <v>510.62</v>
-      </c>
-      <c r="I93" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J93" t="s" s="48">
-        <v>188</v>
-      </c>
       <c r="K93" t="s" s="49">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="L93" s="0"/>
     </row>
@@ -4516,10 +4478,10 @@
       <c r="E94" s="47"/>
       <c r="F94" s="44"/>
       <c r="G94" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H94" s="52">
-        <v>26552.24</v>
+        <v>23613.5</v>
       </c>
       <c r="I94" s="53"/>
       <c r="J94" s="48"/>
@@ -4528,289 +4490,325 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="44">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="B95" s="45">
-        <v>0000106940</v>
+        <v>0000106977</v>
       </c>
       <c r="C95" t="s" s="46">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D95" t="s" s="46">
+        <v>176</v>
+      </c>
+      <c r="E95" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F95" t="s" s="44">
+        <v>188</v>
+      </c>
+      <c r="G95" s="51">
+        <v>1</v>
+      </c>
+      <c r="H95" s="52">
+        <v>1251.09</v>
+      </c>
+      <c r="I95" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J95" t="s" s="48">
         <v>189</v>
       </c>
-      <c r="E95" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F95" t="s" s="44">
-        <v>190</v>
-      </c>
-      <c r="G95" s="51">
-        <v>16</v>
-      </c>
-      <c r="H95" s="52">
-        <v>563.86</v>
-      </c>
-      <c r="I95" s="53">
-        <v>48</v>
-      </c>
-      <c r="J95" t="s" s="48">
-        <v>191</v>
-      </c>
       <c r="K95" t="s" s="49">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L95" s="0"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="44">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="B96" s="45">
-        <v>0000106940</v>
+        <v>0000106977</v>
       </c>
       <c r="C96" t="s" s="46">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D96" t="s" s="46">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E96" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F96" t="s" s="44">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="G96" s="51">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="H96" s="52">
-        <v>369.52</v>
-      </c>
-      <c r="I96" s="53">
-        <v>87.5</v>
+        <v>1286.84</v>
+      </c>
+      <c r="I96" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J96" t="s" s="48">
+        <v>191</v>
+      </c>
+      <c r="K96" t="s" s="49">
+        <v>151</v>
+      </c>
+      <c r="L96" s="0"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="44">
+        <v>147</v>
+      </c>
+      <c r="B97" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C97" t="s" s="46">
+        <v>148</v>
+      </c>
+      <c r="D97" t="s" s="46">
+        <v>176</v>
+      </c>
+      <c r="E97" t="s" s="47">
         <v>97</v>
       </c>
-      <c r="K96" t="s" s="49">
+      <c r="F97" t="s" s="44">
         <v>192</v>
       </c>
-      <c r="L96" s="0"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="44"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="46"/>
-      <c r="D97" s="46"/>
-      <c r="E97" s="47"/>
-      <c r="F97" s="44"/>
-      <c r="G97" t="s" s="51">
-        <v>27</v>
+      <c r="G97" s="51">
+        <v>1</v>
       </c>
       <c r="H97" s="52">
-        <v>34888.16</v>
-      </c>
-      <c r="I97" s="53"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="49"/>
+        <v>1454.19</v>
+      </c>
+      <c r="I97" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J97" t="s" s="48">
+        <v>193</v>
+      </c>
+      <c r="K97" t="s" s="49">
+        <v>151</v>
+      </c>
       <c r="L97" s="0"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="44">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="B98" s="45">
-        <v>0000106941</v>
+        <v>0000106977</v>
       </c>
       <c r="C98" t="s" s="46">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D98" t="s" s="46">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E98" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F98" t="s" s="44">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G98" s="51">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H98" s="52">
-        <v>4.44</v>
+        <v>162.48</v>
       </c>
       <c r="I98" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J98" t="s" s="48">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K98" t="s" s="49">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L98" s="0"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="44">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="B99" s="45">
-        <v>0000106941</v>
+        <v>0000106977</v>
       </c>
       <c r="C99" t="s" s="46">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D99" t="s" s="46">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E99" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F99" t="s" s="44">
-        <v>122</v>
+        <v>196</v>
       </c>
       <c r="G99" s="51">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H99" s="52">
-        <v>11.16</v>
-      </c>
-      <c r="I99" s="53">
-        <v>3.3</v>
+        <v>144.60</v>
+      </c>
+      <c r="I99" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J99" t="s" s="48">
-        <v>123</v>
+        <v>197</v>
       </c>
       <c r="K99" t="s" s="49">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L99" s="0"/>
     </row>
     <row r="100">
-      <c r="A100" s="44"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="44"/>
-      <c r="G100" t="s" s="51">
-        <v>27</v>
+      <c r="A100" t="s" s="44">
+        <v>147</v>
+      </c>
+      <c r="B100" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C100" t="s" s="46">
+        <v>148</v>
+      </c>
+      <c r="D100" t="s" s="46">
+        <v>176</v>
+      </c>
+      <c r="E100" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F100" t="s" s="44">
+        <v>198</v>
+      </c>
+      <c r="G100" s="51">
+        <v>4</v>
       </c>
       <c r="H100" s="52">
-        <v>1338</v>
-      </c>
-      <c r="I100" s="53"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="49"/>
+        <v>658.04</v>
+      </c>
+      <c r="I100" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J100" t="s" s="48">
+        <v>199</v>
+      </c>
+      <c r="K100" t="s" s="49">
+        <v>151</v>
+      </c>
       <c r="L100" s="0"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="44">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="B101" s="45">
-        <v>0000106942</v>
+        <v>0000106977</v>
       </c>
       <c r="C101" t="s" s="46">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D101" t="s" s="46">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E101" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F101" t="s" s="44">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G101" s="51">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H101" s="52">
-        <v>228.21</v>
+        <v>381.82</v>
       </c>
       <c r="I101" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J101" t="s" s="48">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K101" t="s" s="49">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L101" s="0"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="44">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="B102" s="45">
-        <v>0000106942</v>
+        <v>0000106977</v>
       </c>
       <c r="C102" t="s" s="46">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D102" t="s" s="46">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E102" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F102" t="s" s="44">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="G102" s="51">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H102" s="52">
-        <v>213.41</v>
-      </c>
-      <c r="I102" s="53">
-        <v>25</v>
+        <v>641.79</v>
+      </c>
+      <c r="I102" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J102" t="s" s="48">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="K102" t="s" s="49">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L102" s="0"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="44">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="B103" s="45">
-        <v>0000106942</v>
+        <v>0000106977</v>
       </c>
       <c r="C103" t="s" s="46">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="D103" t="s" s="46">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E103" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F103" t="s" s="44">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G103" s="51">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H103" s="52">
-        <v>30.65</v>
-      </c>
-      <c r="I103" s="53">
-        <v>3.35</v>
+        <v>641.79</v>
+      </c>
+      <c r="I103" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J103" t="s" s="48">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K103" t="s" s="49">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L103" s="0"/>
     </row>
@@ -4824,10 +4822,10 @@
         <v>18</v>
       </c>
       <c r="G104" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H104" s="52">
-        <v>23613.5</v>
+        <v>11308.52</v>
       </c>
       <c r="I104" s="53" t="s">
         <v>18</v>
@@ -4845,41 +4843,41 @@
       <c r="D105" s="46"/>
       <c r="E105" s="47"/>
       <c r="F105" s="44" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G105" t="s" s="51">
         <v>48</v>
       </c>
       <c r="H105" s="52">
-        <v>460266.79</v>
+        <v>446671.2</v>
       </c>
       <c r="I105" s="53">
-        <v>808.2</v>
+        <v>815.2</v>
       </c>
       <c r="J105" s="48" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K105" s="49"/>
       <c r="L105" s="0"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="44">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B106" s="45">
         <v>0000106893</v>
       </c>
       <c r="C106" t="s" s="46">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D106" t="s" s="46">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E106" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F106" t="s" s="44">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G106" s="51">
         <v>10</v>
@@ -4891,31 +4889,31 @@
         <v>18</v>
       </c>
       <c r="J106" t="s" s="48">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K106" t="s" s="49">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L106" s="0"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="44">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B107" s="45">
         <v>0000106893</v>
       </c>
       <c r="C107" t="s" s="46">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D107" t="s" s="46">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E107" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F107" t="s" s="44">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G107" s="51">
         <v>10</v>
@@ -4927,10 +4925,10 @@
         <v>18</v>
       </c>
       <c r="J107" t="s" s="48">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K107" t="s" s="49">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L107" s="0"/>
     </row>
@@ -4942,7 +4940,7 @@
       <c r="E108" s="47"/>
       <c r="F108" s="44"/>
       <c r="G108" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H108" s="52">
         <v>48131</v>
@@ -4954,22 +4952,22 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="44">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B109" s="45">
         <v>0000106979</v>
       </c>
       <c r="C109" t="s" s="46">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D109" t="s" s="46">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E109" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F109" t="s" s="44">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G109" s="51">
         <v>133</v>
@@ -4981,10 +4979,10 @@
         <v>18</v>
       </c>
       <c r="J109" t="s" s="48">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K109" t="s" s="49">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L109" s="0"/>
     </row>
@@ -4996,7 +4994,7 @@
       <c r="E110" s="47"/>
       <c r="F110" s="44"/>
       <c r="G110" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H110" s="52">
         <v>42379.12</v>
@@ -5008,22 +5006,22 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B111" s="45">
         <v>0000106623</v>
       </c>
       <c r="C111" t="s" s="46">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D111" t="s" s="46">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E111" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F111" t="s" s="44">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G111" s="51">
         <v>2</v>
@@ -5035,10 +5033,10 @@
         <v>18</v>
       </c>
       <c r="J111" t="s" s="48">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K111" t="s" s="49">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L111" s="0"/>
     </row>
@@ -5050,7 +5048,7 @@
       <c r="E112" s="47"/>
       <c r="F112" s="44"/>
       <c r="G112" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H112" s="52">
         <v>541.94</v>
@@ -5062,22 +5060,22 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B113" s="45">
         <v>0000106824</v>
       </c>
       <c r="C113" t="s" s="46">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D113" t="s" s="46">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E113" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F113" t="s" s="44">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G113" s="51">
         <v>48</v>
@@ -5089,10 +5087,10 @@
         <v>72</v>
       </c>
       <c r="J113" t="s" s="48">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K113" t="s" s="49">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L113" s="0"/>
     </row>
@@ -5104,7 +5102,7 @@
       <c r="E114" s="47"/>
       <c r="F114" s="44"/>
       <c r="G114" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H114" s="52">
         <v>15372</v>
@@ -5116,22 +5114,22 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B115" s="45">
         <v>0000106943</v>
       </c>
       <c r="C115" t="s" s="46">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D115" t="s" s="46">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E115" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F115" t="s" s="44">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G115" s="51">
         <v>16</v>
@@ -5143,10 +5141,10 @@
         <v>48</v>
       </c>
       <c r="J115" t="s" s="48">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="K115" t="s" s="49">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="L115" s="0"/>
     </row>
@@ -5158,7 +5156,7 @@
       <c r="E116" s="47"/>
       <c r="F116" s="44"/>
       <c r="G116" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H116" s="52">
         <v>10400.48</v>
@@ -5170,22 +5168,22 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="44">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="B117" s="45">
         <v>0000106778</v>
       </c>
       <c r="C117" t="s" s="46">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="D117" t="s" s="46">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E117" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F117" t="s" s="44">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="G117" s="51">
         <v>5</v>
@@ -5197,10 +5195,10 @@
         <v>18</v>
       </c>
       <c r="J117" t="s" s="48">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="K117" t="s" s="49">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="L117" s="0"/>
     </row>
@@ -5212,7 +5210,7 @@
       <c r="E118" s="47"/>
       <c r="F118" s="44"/>
       <c r="G118" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H118" s="52">
         <v>11250</v>
@@ -5224,22 +5222,22 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="44">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B119" s="45">
         <v>0000106978</v>
       </c>
       <c r="C119" t="s" s="46">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D119" t="s" s="46">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E119" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F119" t="s" s="44">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G119" s="51">
         <v>144</v>
@@ -5251,31 +5249,31 @@
         <v>18</v>
       </c>
       <c r="J119" t="s" s="48">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K119" t="s" s="49">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L119" s="0"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="44">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B120" s="45">
         <v>0000106978</v>
       </c>
       <c r="C120" t="s" s="46">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D120" t="s" s="46">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E120" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F120" t="s" s="44">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G120" s="51">
         <v>144</v>
@@ -5287,31 +5285,31 @@
         <v>18</v>
       </c>
       <c r="J120" t="s" s="48">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K120" t="s" s="49">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L120" s="0"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="44">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B121" s="45">
         <v>0000106978</v>
       </c>
       <c r="C121" t="s" s="46">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D121" t="s" s="46">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E121" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F121" t="s" s="44">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G121" s="51">
         <v>288</v>
@@ -5323,31 +5321,31 @@
         <v>18</v>
       </c>
       <c r="J121" t="s" s="48">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K121" t="s" s="49">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L121" s="0"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="44">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B122" s="45">
         <v>0000106978</v>
       </c>
       <c r="C122" t="s" s="46">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D122" t="s" s="46">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E122" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F122" t="s" s="44">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G122" s="51">
         <v>144</v>
@@ -5359,31 +5357,31 @@
         <v>18</v>
       </c>
       <c r="J122" t="s" s="48">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="K122" t="s" s="49">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L122" s="0"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="44">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B123" s="45">
         <v>0000106978</v>
       </c>
       <c r="C123" t="s" s="46">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D123" t="s" s="46">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E123" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F123" t="s" s="44">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G123" s="51">
         <v>144</v>
@@ -5395,10 +5393,10 @@
         <v>18</v>
       </c>
       <c r="J123" t="s" s="48">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K123" t="s" s="49">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L123" s="0"/>
     </row>
@@ -5410,7 +5408,7 @@
       <c r="E124" s="47"/>
       <c r="F124" s="44"/>
       <c r="G124" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H124" s="52">
         <v>128880</v>
@@ -5422,440 +5420,452 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="44">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="B125" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C125" t="s" s="46">
+        <v>148</v>
+      </c>
+      <c r="D125" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E125" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F125" t="s" s="44">
+        <v>243</v>
+      </c>
+      <c r="G125" s="51">
+        <v>10</v>
+      </c>
+      <c r="H125" s="52">
+        <v>568.68</v>
+      </c>
+      <c r="I125" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J125" t="s" s="48">
+        <v>244</v>
+      </c>
+      <c r="K125" t="s" s="49">
+        <v>151</v>
+      </c>
+      <c r="L125" s="0"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="44">
+        <v>147</v>
+      </c>
+      <c r="B126" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C126" t="s" s="46">
+        <v>148</v>
+      </c>
+      <c r="D126" t="s" s="46">
+        <v>242</v>
+      </c>
+      <c r="E126" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F126" t="s" s="44">
+        <v>245</v>
+      </c>
+      <c r="G126" s="51">
+        <v>2</v>
+      </c>
+      <c r="H126" s="52">
+        <v>528.06</v>
+      </c>
+      <c r="I126" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="J126" t="s" s="48">
+        <v>246</v>
+      </c>
+      <c r="K126" t="s" s="49">
+        <v>151</v>
+      </c>
+      <c r="L126" s="0"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="44"/>
+      <c r="B127" s="45"/>
+      <c r="C127" s="46"/>
+      <c r="D127" s="46"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="44"/>
+      <c r="G127" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H127" s="52">
+        <v>6742.92</v>
+      </c>
+      <c r="I127" s="53"/>
+      <c r="J127" s="48"/>
+      <c r="K127" s="49"/>
+      <c r="L127" s="0"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B128" s="45">
         <v>0000106981</v>
       </c>
-      <c r="C125" t="s" s="46">
-        <v>239</v>
-      </c>
-      <c r="D125" t="s" s="46">
-        <v>240</v>
-      </c>
-      <c r="E125" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F125" t="s" s="44">
-        <v>183</v>
-      </c>
-      <c r="G125" s="51">
+      <c r="C128" t="s" s="46">
+        <v>247</v>
+      </c>
+      <c r="D128" t="s" s="46">
+        <v>248</v>
+      </c>
+      <c r="E128" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F128" t="s" s="44">
+        <v>170</v>
+      </c>
+      <c r="G128" s="51">
         <v>52</v>
       </c>
-      <c r="H125" s="52">
+      <c r="H128" s="52">
         <v>474.23</v>
       </c>
-      <c r="I125" s="53">
+      <c r="I128" s="53">
         <v>52</v>
       </c>
-      <c r="J125" t="s" s="48">
-        <v>184</v>
-      </c>
-      <c r="K125" t="s" s="49">
-        <v>241</v>
-      </c>
-      <c r="L125" s="0"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="44"/>
-      <c r="B126" s="45"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="46"/>
-      <c r="E126" s="47"/>
-      <c r="F126" s="44"/>
-      <c r="G126" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H126" s="52">
+      <c r="J128" t="s" s="48">
+        <v>171</v>
+      </c>
+      <c r="K128" t="s" s="49">
+        <v>249</v>
+      </c>
+      <c r="L128" s="0"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="44"/>
+      <c r="B129" s="45"/>
+      <c r="C129" s="46"/>
+      <c r="D129" s="46"/>
+      <c r="E129" s="47"/>
+      <c r="F129" s="44"/>
+      <c r="G129" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H129" s="52">
         <v>24659.96</v>
       </c>
-      <c r="I126" s="53"/>
-      <c r="J126" s="48"/>
-      <c r="K126" s="49"/>
-      <c r="L126" s="0"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B127" s="45">
+      <c r="I129" s="53"/>
+      <c r="J129" s="48"/>
+      <c r="K129" s="49"/>
+      <c r="L129" s="0"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B130" s="45">
         <v>0000106982</v>
       </c>
-      <c r="C127" t="s" s="46">
-        <v>239</v>
-      </c>
-      <c r="D127" t="s" s="46">
-        <v>240</v>
-      </c>
-      <c r="E127" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F127" t="s" s="44">
-        <v>186</v>
-      </c>
-      <c r="G127" s="51">
+      <c r="C130" t="s" s="46">
+        <v>247</v>
+      </c>
+      <c r="D130" t="s" s="46">
+        <v>248</v>
+      </c>
+      <c r="E130" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F130" t="s" s="44">
+        <v>173</v>
+      </c>
+      <c r="G130" s="51">
         <v>52</v>
       </c>
-      <c r="H127" s="52">
+      <c r="H130" s="52">
         <v>368.44</v>
       </c>
-      <c r="I127" s="53">
+      <c r="I130" s="53">
         <v>52</v>
       </c>
-      <c r="J127" t="s" s="48">
-        <v>57</v>
-      </c>
-      <c r="K127" t="s" s="49">
-        <v>241</v>
-      </c>
-      <c r="L127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="44"/>
-      <c r="B128" s="45"/>
-      <c r="C128" s="46"/>
-      <c r="D128" s="46"/>
-      <c r="E128" s="47"/>
-      <c r="F128" s="44"/>
-      <c r="G128" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H128" s="52">
+      <c r="J130" t="s" s="48">
+        <v>52</v>
+      </c>
+      <c r="K130" t="s" s="49">
+        <v>249</v>
+      </c>
+      <c r="L130" s="0"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="44"/>
+      <c r="B131" s="45"/>
+      <c r="C131" s="46"/>
+      <c r="D131" s="46"/>
+      <c r="E131" s="47"/>
+      <c r="F131" s="44"/>
+      <c r="G131" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H131" s="52">
         <v>19158.88</v>
       </c>
-      <c r="I128" s="53"/>
-      <c r="J128" s="48"/>
-      <c r="K128" s="49"/>
-      <c r="L128" s="0"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B129" s="45">
+      <c r="I131" s="53"/>
+      <c r="J131" s="48"/>
+      <c r="K131" s="49"/>
+      <c r="L131" s="0"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B132" s="45">
         <v>0000106983</v>
       </c>
-      <c r="C129" t="s" s="46">
-        <v>239</v>
-      </c>
-      <c r="D129" t="s" s="46">
-        <v>240</v>
-      </c>
-      <c r="E129" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F129" t="s" s="44">
-        <v>242</v>
-      </c>
-      <c r="G129" s="51">
+      <c r="C132" t="s" s="46">
+        <v>247</v>
+      </c>
+      <c r="D132" t="s" s="46">
+        <v>248</v>
+      </c>
+      <c r="E132" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F132" t="s" s="44">
+        <v>250</v>
+      </c>
+      <c r="G132" s="51">
         <v>52</v>
       </c>
-      <c r="H129" s="52">
+      <c r="H132" s="52">
         <v>507.46</v>
       </c>
-      <c r="I129" t="s" s="53">
+      <c r="I132" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J129" t="s" s="48">
-        <v>243</v>
-      </c>
-      <c r="K129" t="s" s="49">
-        <v>241</v>
-      </c>
-      <c r="L129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="44"/>
-      <c r="B130" s="45"/>
-      <c r="C130" s="46"/>
-      <c r="D130" s="46"/>
-      <c r="E130" s="47"/>
-      <c r="F130" s="44"/>
-      <c r="G130" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H130" s="52">
+      <c r="J132" t="s" s="48">
+        <v>251</v>
+      </c>
+      <c r="K132" t="s" s="49">
+        <v>249</v>
+      </c>
+      <c r="L132" s="0"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="44"/>
+      <c r="B133" s="45"/>
+      <c r="C133" s="46"/>
+      <c r="D133" s="46"/>
+      <c r="E133" s="47"/>
+      <c r="F133" s="44"/>
+      <c r="G133" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H133" s="52">
         <v>26387.92</v>
       </c>
-      <c r="I130" s="53"/>
-      <c r="J130" s="48"/>
-      <c r="K130" s="49"/>
-      <c r="L130" s="0"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B131" s="45">
+      <c r="I133" s="53"/>
+      <c r="J133" s="48"/>
+      <c r="K133" s="49"/>
+      <c r="L133" s="0"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B134" s="45">
         <v>0000106984</v>
       </c>
-      <c r="C131" t="s" s="46">
-        <v>239</v>
-      </c>
-      <c r="D131" t="s" s="46">
-        <v>240</v>
-      </c>
-      <c r="E131" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F131" t="s" s="44">
-        <v>244</v>
-      </c>
-      <c r="G131" s="51">
+      <c r="C134" t="s" s="46">
+        <v>247</v>
+      </c>
+      <c r="D134" t="s" s="46">
+        <v>248</v>
+      </c>
+      <c r="E134" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F134" t="s" s="44">
+        <v>252</v>
+      </c>
+      <c r="G134" s="51">
         <v>52</v>
       </c>
-      <c r="H131" s="52">
+      <c r="H134" s="52">
         <v>486.04</v>
       </c>
-      <c r="I131" t="s" s="53">
+      <c r="I134" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J131" t="s" s="48">
-        <v>245</v>
-      </c>
-      <c r="K131" t="s" s="49">
-        <v>241</v>
-      </c>
-      <c r="L131" s="0"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="44"/>
-      <c r="B132" s="45"/>
-      <c r="C132" s="46"/>
-      <c r="D132" s="46"/>
-      <c r="E132" s="47"/>
-      <c r="F132" s="44"/>
-      <c r="G132" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H132" s="52">
+      <c r="J134" t="s" s="48">
+        <v>253</v>
+      </c>
+      <c r="K134" t="s" s="49">
+        <v>249</v>
+      </c>
+      <c r="L134" s="0"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="44"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="46"/>
+      <c r="D135" s="46"/>
+      <c r="E135" s="47"/>
+      <c r="F135" s="44"/>
+      <c r="G135" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H135" s="52">
         <v>25274.08</v>
       </c>
-      <c r="I132" s="53"/>
-      <c r="J132" s="48"/>
-      <c r="K132" s="49"/>
-      <c r="L132" s="0"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B133" s="45">
+      <c r="I135" s="53"/>
+      <c r="J135" s="48"/>
+      <c r="K135" s="49"/>
+      <c r="L135" s="0"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B136" s="45">
         <v>0000106985</v>
       </c>
-      <c r="C133" t="s" s="46">
-        <v>239</v>
-      </c>
-      <c r="D133" t="s" s="46">
-        <v>240</v>
-      </c>
-      <c r="E133" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F133" t="s" s="44">
-        <v>187</v>
-      </c>
-      <c r="G133" s="51">
+      <c r="C136" t="s" s="46">
+        <v>247</v>
+      </c>
+      <c r="D136" t="s" s="46">
+        <v>248</v>
+      </c>
+      <c r="E136" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F136" t="s" s="44">
+        <v>174</v>
+      </c>
+      <c r="G136" s="51">
         <v>52</v>
       </c>
-      <c r="H133" s="52">
+      <c r="H136" s="52">
         <v>512.40</v>
       </c>
-      <c r="I133" t="s" s="53">
+      <c r="I136" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J133" t="s" s="48">
-        <v>188</v>
-      </c>
-      <c r="K133" t="s" s="49">
-        <v>241</v>
-      </c>
-      <c r="L133" s="0"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="44"/>
-      <c r="B134" s="45"/>
-      <c r="C134" s="46"/>
-      <c r="D134" s="46"/>
-      <c r="E134" s="47"/>
-      <c r="F134" s="44"/>
-      <c r="G134" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H134" s="52">
+      <c r="J136" t="s" s="48">
+        <v>175</v>
+      </c>
+      <c r="K136" t="s" s="49">
+        <v>249</v>
+      </c>
+      <c r="L136" s="0"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="44"/>
+      <c r="B137" s="45"/>
+      <c r="C137" s="46"/>
+      <c r="D137" s="46"/>
+      <c r="E137" s="47"/>
+      <c r="F137" s="44"/>
+      <c r="G137" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H137" s="52">
         <v>26644.8</v>
       </c>
-      <c r="I134" s="53"/>
-      <c r="J134" s="48"/>
-      <c r="K134" s="49"/>
-      <c r="L134" s="0"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="44">
-        <v>98</v>
-      </c>
-      <c r="B135" s="45">
+      <c r="I137" s="53"/>
+      <c r="J137" s="48"/>
+      <c r="K137" s="49"/>
+      <c r="L137" s="0"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="44">
+        <v>124</v>
+      </c>
+      <c r="B138" s="45">
         <v>0000106958</v>
       </c>
-      <c r="C135" t="s" s="46">
-        <v>182</v>
-      </c>
-      <c r="D135" t="s" s="46">
-        <v>246</v>
-      </c>
-      <c r="E135" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F135" t="s" s="44">
-        <v>171</v>
-      </c>
-      <c r="G135" s="51">
+      <c r="C138" t="s" s="46">
+        <v>169</v>
+      </c>
+      <c r="D138" t="s" s="46">
+        <v>254</v>
+      </c>
+      <c r="E138" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F138" t="s" s="44">
+        <v>158</v>
+      </c>
+      <c r="G138" s="51">
         <v>180</v>
       </c>
-      <c r="H135" s="52">
+      <c r="H138" s="52">
         <v>286.96</v>
       </c>
-      <c r="I135" s="53">
+      <c r="I138" s="53">
         <v>225</v>
       </c>
-      <c r="J135" t="s" s="48">
-        <v>172</v>
-      </c>
-      <c r="K135" t="s" s="49">
-        <v>247</v>
-      </c>
-      <c r="L135" s="0"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="44"/>
-      <c r="B136" s="45"/>
-      <c r="C136" s="46"/>
-      <c r="D136" s="46"/>
-      <c r="E136" s="47"/>
-      <c r="F136" s="44"/>
-      <c r="G136" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H136" s="52">
+      <c r="J138" t="s" s="48">
+        <v>159</v>
+      </c>
+      <c r="K138" t="s" s="49">
+        <v>255</v>
+      </c>
+      <c r="L138" s="0"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="44"/>
+      <c r="B139" s="45"/>
+      <c r="C139" s="46"/>
+      <c r="D139" s="46"/>
+      <c r="E139" s="47"/>
+      <c r="F139" s="44"/>
+      <c r="G139" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H139" s="52">
         <v>51652.8</v>
       </c>
-      <c r="I136" s="53"/>
-      <c r="J136" s="48"/>
-      <c r="K136" s="49"/>
-      <c r="L136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B137" s="45">
-        <v>0000106966</v>
-      </c>
-      <c r="C137" t="s" s="46">
-        <v>52</v>
-      </c>
-      <c r="D137" t="s" s="46">
-        <v>248</v>
-      </c>
-      <c r="E137" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F137" t="s" s="44">
-        <v>96</v>
-      </c>
-      <c r="G137" s="51">
-        <v>70</v>
-      </c>
-      <c r="H137" s="52">
-        <v>375.19</v>
-      </c>
-      <c r="I137" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J137" t="s" s="48">
+      <c r="I139" s="53"/>
+      <c r="J139" s="48"/>
+      <c r="K139" s="49"/>
+      <c r="L139" s="0"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="44">
+        <v>124</v>
+      </c>
+      <c r="B140" s="45">
+        <v>0000106993</v>
+      </c>
+      <c r="C140" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="D140" t="s" s="46">
+        <v>254</v>
+      </c>
+      <c r="E140" t="s" s="47">
         <v>97</v>
       </c>
-      <c r="K137" t="s" s="49">
-        <v>249</v>
-      </c>
-      <c r="L137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="44"/>
-      <c r="B138" s="45"/>
-      <c r="C138" s="46"/>
-      <c r="D138" s="46"/>
-      <c r="E138" s="47"/>
-      <c r="F138" s="44"/>
-      <c r="G138" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H138" s="52">
-        <v>26263.3</v>
-      </c>
-      <c r="I138" s="53"/>
-      <c r="J138" s="48"/>
-      <c r="K138" s="49"/>
-      <c r="L138" s="0"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="44">
-        <v>98</v>
-      </c>
-      <c r="B139" s="45">
-        <v>0000106971</v>
-      </c>
-      <c r="C139" t="s" s="46">
-        <v>250</v>
-      </c>
-      <c r="D139" t="s" s="46">
-        <v>248</v>
-      </c>
-      <c r="E139" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F139" t="s" s="44">
-        <v>122</v>
-      </c>
-      <c r="G139" s="51">
-        <v>1000</v>
-      </c>
-      <c r="H139" s="52">
-        <v>8.58</v>
-      </c>
-      <c r="I139" s="53">
-        <v>33</v>
-      </c>
-      <c r="J139" t="s" s="48">
-        <v>123</v>
-      </c>
-      <c r="K139" t="s" s="49">
-        <v>173</v>
-      </c>
-      <c r="L139" s="0"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="44"/>
-      <c r="B140" s="45"/>
-      <c r="C140" s="46"/>
-      <c r="D140" s="46"/>
-      <c r="E140" s="47"/>
       <c r="F140" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G140" t="s" s="51">
-        <v>27</v>
+        <v>158</v>
+      </c>
+      <c r="G140" s="51">
+        <v>180</v>
       </c>
       <c r="H140" s="52">
-        <v>8580</v>
-      </c>
-      <c r="I140" s="53" t="s">
-        <v>18</v>
+        <v>289.26</v>
+      </c>
+      <c r="I140" s="53">
+        <v>225</v>
       </c>
       <c r="J140" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K140" s="49"/>
+        <v>159</v>
+      </c>
+      <c r="K140" t="s" s="49">
+        <v>257</v>
+      </c>
       <c r="L140" s="0"/>
     </row>
     <row r="141">
@@ -5864,57 +5874,51 @@
       <c r="C141" s="46"/>
       <c r="D141" s="46"/>
       <c r="E141" s="47"/>
-      <c r="F141" s="44" t="s">
-        <v>254</v>
-      </c>
+      <c r="F141" s="44"/>
       <c r="G141" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H141" s="52">
-        <v>465576.28</v>
-      </c>
-      <c r="I141" s="53">
-        <v>569.5</v>
-      </c>
-      <c r="J141" s="48" t="s">
-        <v>255</v>
-      </c>
+        <v>52066.8</v>
+      </c>
+      <c r="I141" s="53"/>
+      <c r="J141" s="48"/>
       <c r="K141" s="49"/>
       <c r="L141" s="0"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="44">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="B142" s="45">
-        <v>0000106882</v>
+        <v>0000106989</v>
       </c>
       <c r="C142" t="s" s="46">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D142" t="s" s="46">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E142" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F142" t="s" s="44">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="G142" s="51">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H142" s="52">
-        <v>315.49</v>
-      </c>
-      <c r="I142" s="53">
-        <v>72</v>
+        <v>2365</v>
+      </c>
+      <c r="I142" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J142" t="s" s="48">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="K142" t="s" s="49">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="L142" s="0"/>
     </row>
@@ -5926,10 +5930,10 @@
       <c r="E143" s="47"/>
       <c r="F143" s="44"/>
       <c r="G143" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H143" s="52">
-        <v>15143.52</v>
+        <v>18920</v>
       </c>
       <c r="I143" s="53"/>
       <c r="J143" s="48"/>
@@ -5938,37 +5942,37 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B144" s="45">
-        <v>0000106967</v>
+        <v>0000106966</v>
       </c>
       <c r="C144" t="s" s="46">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D144" t="s" s="46">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E144" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F144" t="s" s="44">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G144" s="51">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="H144" s="52">
-        <v>660.00</v>
+        <v>375.19</v>
       </c>
       <c r="I144" s="53">
-        <v>48</v>
+        <v>87.5</v>
       </c>
       <c r="J144" t="s" s="48">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="K144" t="s" s="49">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="L144" s="0"/>
     </row>
@@ -5980,10 +5984,10 @@
       <c r="E145" s="47"/>
       <c r="F145" s="44"/>
       <c r="G145" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H145" s="52">
-        <v>10560</v>
+        <v>26263.3</v>
       </c>
       <c r="I145" s="53"/>
       <c r="J145" s="48"/>
@@ -5992,296 +5996,296 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="44">
-        <v>256</v>
+        <v>124</v>
       </c>
       <c r="B146" s="45">
-        <v>0000106325</v>
+        <v>0000106971</v>
       </c>
       <c r="C146" t="s" s="46">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D146" t="s" s="46">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E146" t="s" s="47">
-        <v>259</v>
+        <v>97</v>
       </c>
       <c r="F146" t="s" s="44">
-        <v>260</v>
+        <v>121</v>
       </c>
       <c r="G146" s="51">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H146" s="52">
-        <v>88.19</v>
-      </c>
-      <c r="I146" t="s" s="53">
+        <v>8.58</v>
+      </c>
+      <c r="I146" s="53">
+        <v>33</v>
+      </c>
+      <c r="J146" t="s" s="48">
+        <v>122</v>
+      </c>
+      <c r="K146" t="s" s="49">
+        <v>160</v>
+      </c>
+      <c r="L146" s="0"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="44"/>
+      <c r="B147" s="45"/>
+      <c r="C147" s="46"/>
+      <c r="D147" s="46"/>
+      <c r="E147" s="47"/>
+      <c r="F147" t="s" s="44">
         <v>18</v>
       </c>
-      <c r="J146" t="s" s="48">
-        <v>261</v>
-      </c>
-      <c r="K146" s="49"/>
-      <c r="L146" s="0"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="s" s="44">
-        <v>256</v>
-      </c>
-      <c r="B147" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C147" t="s" s="46">
-        <v>257</v>
-      </c>
-      <c r="D147" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="E147" t="s" s="47">
-        <v>259</v>
-      </c>
-      <c r="F147" t="s" s="44">
-        <v>262</v>
-      </c>
-      <c r="G147" s="51">
-        <v>1</v>
+      <c r="G147" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H147" s="52">
-        <v>505.13</v>
-      </c>
-      <c r="I147" t="s" s="53">
+        <v>8580</v>
+      </c>
+      <c r="I147" s="53" t="s">
         <v>18</v>
       </c>
       <c r="J147" t="s" s="48">
-        <v>263</v>
+        <v>18</v>
       </c>
       <c r="K147" s="49"/>
       <c r="L147" s="0"/>
     </row>
     <row r="148">
-      <c r="A148" t="s" s="44">
-        <v>256</v>
-      </c>
-      <c r="B148" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C148" t="s" s="46">
-        <v>257</v>
-      </c>
-      <c r="D148" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="E148" t="s" s="47">
-        <v>259</v>
-      </c>
-      <c r="F148" t="s" s="44">
-        <v>264</v>
-      </c>
-      <c r="G148" s="51">
-        <v>1</v>
+      <c r="A148" s="44"/>
+      <c r="B148" s="45"/>
+      <c r="C148" s="46"/>
+      <c r="D148" s="46"/>
+      <c r="E148" s="47"/>
+      <c r="F148" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="G148" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H148" s="52">
-        <v>0</v>
-      </c>
-      <c r="I148" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J148" t="s" s="48">
-        <v>265</v>
+        <v>543306</v>
+      </c>
+      <c r="I148" s="53">
+        <v>795</v>
+      </c>
+      <c r="J148" s="48" t="s">
+        <v>269</v>
       </c>
       <c r="K148" s="49"/>
       <c r="L148" s="0"/>
     </row>
     <row r="149">
-      <c r="A149" s="44"/>
-      <c r="B149" s="45"/>
-      <c r="C149" s="46"/>
-      <c r="D149" s="46"/>
-      <c r="E149" s="47"/>
-      <c r="F149" s="44"/>
-      <c r="G149" t="s" s="51">
-        <v>27</v>
+      <c r="A149" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B149" s="45">
+        <v>0000106882</v>
+      </c>
+      <c r="C149" t="s" s="46">
+        <v>265</v>
+      </c>
+      <c r="D149" t="s" s="46">
+        <v>266</v>
+      </c>
+      <c r="E149" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F149" t="s" s="44">
+        <v>224</v>
+      </c>
+      <c r="G149" s="51">
+        <v>48</v>
       </c>
       <c r="H149" s="52">
-        <v>593.32</v>
-      </c>
-      <c r="I149" s="53"/>
-      <c r="J149" s="48"/>
-      <c r="K149" s="49"/>
+        <v>315.49</v>
+      </c>
+      <c r="I149" s="53">
+        <v>72</v>
+      </c>
+      <c r="J149" t="s" s="48">
+        <v>225</v>
+      </c>
+      <c r="K149" t="s" s="49">
+        <v>267</v>
+      </c>
       <c r="L149" s="0"/>
     </row>
     <row r="150">
-      <c r="A150" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B150" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C150" t="s" s="46">
-        <v>14</v>
-      </c>
-      <c r="D150" t="s" s="46">
+      <c r="A150" s="44"/>
+      <c r="B150" s="45"/>
+      <c r="C150" s="46"/>
+      <c r="D150" s="46"/>
+      <c r="E150" s="47"/>
+      <c r="F150" s="44"/>
+      <c r="G150" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H150" s="52">
+        <v>15143.52</v>
+      </c>
+      <c r="I150" s="53"/>
+      <c r="J150" s="48"/>
+      <c r="K150" s="49"/>
+      <c r="L150" s="0"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B151" s="45">
+        <v>0000106967</v>
+      </c>
+      <c r="C151" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D151" t="s" s="46">
         <v>266</v>
       </c>
-      <c r="E150" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F150" t="s" s="44">
-        <v>17</v>
-      </c>
-      <c r="G150" s="51">
-        <v>5</v>
-      </c>
-      <c r="H150" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I150" t="s" s="53">
+      <c r="E151" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F151" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="G151" s="51">
+        <v>16</v>
+      </c>
+      <c r="H151" s="52">
+        <v>660.00</v>
+      </c>
+      <c r="I151" s="53">
+        <v>48</v>
+      </c>
+      <c r="J151" t="s" s="48">
+        <v>94</v>
+      </c>
+      <c r="K151" t="s" s="49">
+        <v>267</v>
+      </c>
+      <c r="L151" s="0"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="44"/>
+      <c r="B152" s="45"/>
+      <c r="C152" s="46"/>
+      <c r="D152" s="46"/>
+      <c r="E152" s="47"/>
+      <c r="F152" s="44"/>
+      <c r="G152" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H152" s="52">
+        <v>10560</v>
+      </c>
+      <c r="I152" s="53"/>
+      <c r="J152" s="48"/>
+      <c r="K152" s="49"/>
+      <c r="L152" s="0"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="44">
+        <v>270</v>
+      </c>
+      <c r="B153" s="45">
+        <v>0000106325</v>
+      </c>
+      <c r="C153" t="s" s="46">
+        <v>271</v>
+      </c>
+      <c r="D153" t="s" s="46">
+        <v>272</v>
+      </c>
+      <c r="E153" t="s" s="47">
+        <v>273</v>
+      </c>
+      <c r="F153" t="s" s="44">
+        <v>274</v>
+      </c>
+      <c r="G153" s="51">
+        <v>1</v>
+      </c>
+      <c r="H153" s="52">
+        <v>88.19</v>
+      </c>
+      <c r="I153" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J150" t="s" s="48">
-        <v>19</v>
-      </c>
-      <c r="K150" t="s" s="49">
-        <v>20</v>
-      </c>
-      <c r="L150" s="0"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="44"/>
-      <c r="B151" s="45"/>
-      <c r="C151" s="46"/>
-      <c r="D151" s="46"/>
-      <c r="E151" s="47"/>
-      <c r="F151" s="44"/>
-      <c r="G151" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H151" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I151" s="53"/>
-      <c r="J151" s="48"/>
-      <c r="K151" s="49"/>
-      <c r="L151" s="0"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B152" s="45">
-        <v>0000106968</v>
-      </c>
-      <c r="C152" t="s" s="46">
-        <v>52</v>
-      </c>
-      <c r="D152" t="s" s="46">
-        <v>267</v>
-      </c>
-      <c r="E152" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F152" t="s" s="44">
-        <v>96</v>
-      </c>
-      <c r="G152" s="51">
-        <v>70</v>
-      </c>
-      <c r="H152" s="52">
-        <v>375.19</v>
-      </c>
-      <c r="I152" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J152" t="s" s="48">
-        <v>97</v>
-      </c>
-      <c r="K152" t="s" s="49">
-        <v>268</v>
-      </c>
-      <c r="L152" s="0"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="44"/>
-      <c r="B153" s="45"/>
-      <c r="C153" s="46"/>
-      <c r="D153" s="46"/>
-      <c r="E153" s="47"/>
-      <c r="F153" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G153" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H153" s="52">
-        <v>26263.3</v>
-      </c>
-      <c r="I153" s="53" t="s">
-        <v>18</v>
-      </c>
       <c r="J153" t="s" s="48">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="K153" s="49"/>
       <c r="L153" s="0"/>
     </row>
     <row r="154">
-      <c r="A154" s="44"/>
-      <c r="B154" s="45"/>
-      <c r="C154" s="46"/>
-      <c r="D154" s="46"/>
-      <c r="E154" s="47"/>
-      <c r="F154" s="44" t="s">
+      <c r="A154" t="s" s="44">
         <v>270</v>
       </c>
-      <c r="G154" t="s" s="51">
-        <v>48</v>
+      <c r="B154" s="45">
+        <v>0000106325</v>
+      </c>
+      <c r="C154" t="s" s="46">
+        <v>271</v>
+      </c>
+      <c r="D154" t="s" s="46">
+        <v>272</v>
+      </c>
+      <c r="E154" t="s" s="47">
+        <v>273</v>
+      </c>
+      <c r="F154" t="s" s="44">
+        <v>276</v>
+      </c>
+      <c r="G154" s="51">
+        <v>1</v>
       </c>
       <c r="H154" s="52">
-        <v>63810.14</v>
-      </c>
-      <c r="I154" s="53">
-        <v>207.5</v>
-      </c>
-      <c r="J154" s="48" t="s">
-        <v>271</v>
+        <v>505.13</v>
+      </c>
+      <c r="I154" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J154" t="s" s="48">
+        <v>277</v>
       </c>
       <c r="K154" s="49"/>
       <c r="L154" s="0"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="44">
-        <v>13</v>
+        <v>270</v>
       </c>
       <c r="B155" s="45">
-        <v>0000106778</v>
+        <v>0000106325</v>
       </c>
       <c r="C155" t="s" s="46">
-        <v>14</v>
+        <v>271</v>
       </c>
       <c r="D155" t="s" s="46">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E155" t="s" s="47">
-        <v>62</v>
+        <v>273</v>
       </c>
       <c r="F155" t="s" s="44">
-        <v>17</v>
+        <v>278</v>
       </c>
       <c r="G155" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H155" s="52">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="I155" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J155" t="s" s="48">
-        <v>19</v>
-      </c>
-      <c r="K155" t="s" s="49">
-        <v>20</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="K155" s="49"/>
       <c r="L155" s="0"/>
     </row>
     <row r="156">
@@ -6290,45 +6294,39 @@
       <c r="C156" s="46"/>
       <c r="D156" s="46"/>
       <c r="E156" s="47"/>
-      <c r="F156" t="s" s="44">
-        <v>273</v>
-      </c>
+      <c r="F156" s="44"/>
       <c r="G156" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H156" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I156" s="53">
-        <v>0</v>
-      </c>
-      <c r="J156" t="s" s="48">
-        <v>50</v>
-      </c>
+        <v>593.32</v>
+      </c>
+      <c r="I156" s="53"/>
+      <c r="J156" s="48"/>
       <c r="K156" s="49"/>
       <c r="L156" s="0"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="44">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="B157" s="45">
         <v>0000106778</v>
       </c>
       <c r="C157" t="s" s="46">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="D157" t="s" s="46">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E157" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F157" t="s" s="44">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="G157" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H157" s="52">
         <v>2250</v>
@@ -6337,10 +6335,10 @@
         <v>18</v>
       </c>
       <c r="J157" t="s" s="48">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="K157" t="s" s="49">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="L157" s="0"/>
     </row>
@@ -6350,130 +6348,128 @@
       <c r="C158" s="46"/>
       <c r="D158" s="46"/>
       <c r="E158" s="47"/>
-      <c r="F158" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F158" s="44"/>
       <c r="G158" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H158" s="52">
-        <v>15750</v>
-      </c>
-      <c r="I158" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J158" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>11250</v>
+      </c>
+      <c r="I158" s="53"/>
+      <c r="J158" s="48"/>
       <c r="K158" s="49"/>
       <c r="L158" s="0"/>
     </row>
     <row r="159">
-      <c r="A159" s="44"/>
-      <c r="B159" s="45"/>
-      <c r="C159" s="46"/>
-      <c r="D159" s="46"/>
-      <c r="E159" s="47"/>
-      <c r="F159" s="44" t="s">
-        <v>276</v>
-      </c>
-      <c r="G159" t="s" s="51">
-        <v>48</v>
+      <c r="A159" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B159" s="45">
+        <v>0000106968</v>
+      </c>
+      <c r="C159" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D159" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="E159" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F159" t="s" s="44">
+        <v>90</v>
+      </c>
+      <c r="G159" s="51">
+        <v>70</v>
       </c>
       <c r="H159" s="52">
-        <v>4500</v>
+        <v>375.19</v>
       </c>
       <c r="I159" s="53">
-        <v>0</v>
-      </c>
-      <c r="J159" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="K159" s="49"/>
+        <v>87.5</v>
+      </c>
+      <c r="J159" t="s" s="48">
+        <v>91</v>
+      </c>
+      <c r="K159" t="s" s="49">
+        <v>282</v>
+      </c>
       <c r="L159" s="0"/>
     </row>
     <row r="160">
-      <c r="A160" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B160" s="45">
-        <v>0000106170</v>
-      </c>
-      <c r="C160" t="s" s="46">
-        <v>274</v>
-      </c>
-      <c r="D160" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E160" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F160" t="s" s="44">
-        <v>221</v>
-      </c>
-      <c r="G160" s="51">
-        <v>48</v>
+      <c r="A160" s="44"/>
+      <c r="B160" s="45"/>
+      <c r="C160" s="46"/>
+      <c r="D160" s="46"/>
+      <c r="E160" s="47"/>
+      <c r="F160" s="44"/>
+      <c r="G160" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H160" s="52">
-        <v>0</v>
-      </c>
-      <c r="I160" s="53">
-        <v>72</v>
-      </c>
-      <c r="J160" t="s" s="48">
-        <v>222</v>
-      </c>
+        <v>26263.3</v>
+      </c>
+      <c r="I160" s="53"/>
+      <c r="J160" s="48"/>
       <c r="K160" s="49"/>
       <c r="L160" s="0"/>
     </row>
     <row r="161">
-      <c r="A161" s="44"/>
-      <c r="B161" s="45"/>
-      <c r="C161" s="46"/>
-      <c r="D161" s="46"/>
-      <c r="E161" s="47"/>
-      <c r="F161" s="44"/>
-      <c r="G161" t="s" s="51">
-        <v>27</v>
+      <c r="A161" t="s" s="44">
+        <v>124</v>
+      </c>
+      <c r="B161" s="45">
+        <v>0000106990</v>
+      </c>
+      <c r="C161" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="D161" t="s" s="46">
+        <v>281</v>
+      </c>
+      <c r="E161" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F161" t="s" s="44">
+        <v>283</v>
+      </c>
+      <c r="G161" s="51">
+        <v>504</v>
       </c>
       <c r="H161" s="52">
-        <v>0</v>
-      </c>
-      <c r="I161" s="53"/>
-      <c r="J161" s="48"/>
-      <c r="K161" s="49"/>
+        <v>22.84</v>
+      </c>
+      <c r="I161" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J161" t="s" s="48">
+        <v>284</v>
+      </c>
+      <c r="K161" t="s" s="49">
+        <v>282</v>
+      </c>
       <c r="L161" s="0"/>
     </row>
     <row r="162">
-      <c r="A162" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B162" s="45">
-        <v>0000106171</v>
-      </c>
-      <c r="C162" t="s" s="46">
-        <v>274</v>
-      </c>
-      <c r="D162" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E162" t="s" s="47">
-        <v>62</v>
-      </c>
+      <c r="A162" s="44"/>
+      <c r="B162" s="45"/>
+      <c r="C162" s="46"/>
+      <c r="D162" s="46"/>
+      <c r="E162" s="47"/>
       <c r="F162" t="s" s="44">
-        <v>96</v>
-      </c>
-      <c r="G162" s="51">
-        <v>70</v>
+        <v>18</v>
+      </c>
+      <c r="G162" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H162" s="52">
-        <v>0</v>
-      </c>
-      <c r="I162" s="53">
-        <v>87.5</v>
+        <v>11511.36</v>
+      </c>
+      <c r="I162" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J162" t="s" s="48">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="K162" s="49"/>
       <c r="L162" s="0"/>
@@ -6484,50 +6480,58 @@
       <c r="C163" s="46"/>
       <c r="D163" s="46"/>
       <c r="E163" s="47"/>
-      <c r="F163" s="44"/>
+      <c r="F163" s="44" t="s">
+        <v>287</v>
+      </c>
       <c r="G163" t="s" s="51">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H163" s="52">
-        <v>0</v>
-      </c>
-      <c r="I163" s="53"/>
-      <c r="J163" s="48"/>
+        <v>75321.5</v>
+      </c>
+      <c r="I163" s="53">
+        <v>207.5</v>
+      </c>
+      <c r="J163" s="48" t="s">
+        <v>288</v>
+      </c>
       <c r="K163" s="49"/>
       <c r="L163" s="0"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B164" s="45">
-        <v>0000106172</v>
+        <v>0000106986</v>
       </c>
       <c r="C164" t="s" s="46">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D164" t="s" s="46">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E164" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F164" t="s" s="44">
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="G164" s="51">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H164" s="52">
-        <v>0</v>
+        <v>326.73</v>
       </c>
       <c r="I164" s="53">
-        <v>87.5</v>
+        <v>72</v>
       </c>
       <c r="J164" t="s" s="48">
-        <v>97</v>
-      </c>
-      <c r="K164" s="49"/>
+        <v>225</v>
+      </c>
+      <c r="K164" t="s" s="49">
+        <v>257</v>
+      </c>
       <c r="L164" s="0"/>
     </row>
     <row r="165">
@@ -6538,10 +6542,10 @@
       <c r="E165" s="47"/>
       <c r="F165" s="44"/>
       <c r="G165" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H165" s="52">
-        <v>0</v>
+        <v>15683.04</v>
       </c>
       <c r="I165" s="53"/>
       <c r="J165" s="48"/>
@@ -6550,394 +6554,374 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="44">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="B166" s="45">
-        <v>0000106234</v>
+        <v>0000106778</v>
       </c>
       <c r="C166" t="s" s="46">
-        <v>277</v>
+        <v>143</v>
       </c>
       <c r="D166" t="s" s="46">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="E166" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F166" t="s" s="44">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="G166" s="51">
         <v>5</v>
       </c>
       <c r="H166" s="52">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="I166" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J166" t="s" s="48">
+        <v>145</v>
+      </c>
+      <c r="K166" t="s" s="49">
         <v>146</v>
       </c>
-      <c r="K166" t="s" s="49">
-        <v>279</v>
-      </c>
       <c r="L166" s="0"/>
     </row>
     <row r="167">
-      <c r="A167" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B167" s="45">
-        <v>0000106234</v>
-      </c>
-      <c r="C167" t="s" s="46">
-        <v>277</v>
-      </c>
-      <c r="D167" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E167" t="s" s="47">
-        <v>62</v>
-      </c>
+      <c r="A167" s="44"/>
+      <c r="B167" s="45"/>
+      <c r="C167" s="46"/>
+      <c r="D167" s="46"/>
+      <c r="E167" s="47"/>
       <c r="F167" t="s" s="44">
-        <v>280</v>
-      </c>
-      <c r="G167" s="51">
-        <v>5</v>
+        <v>291</v>
+      </c>
+      <c r="G167" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H167" s="52">
+        <v>26933.04</v>
+      </c>
+      <c r="I167" s="53">
+        <v>72</v>
+      </c>
+      <c r="J167" t="s" s="48">
+        <v>292</v>
+      </c>
+      <c r="K167" s="49"/>
+      <c r="L167" s="0"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="44">
+        <v>142</v>
+      </c>
+      <c r="B168" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C168" t="s" s="46">
+        <v>143</v>
+      </c>
+      <c r="D168" t="s" s="46">
+        <v>290</v>
+      </c>
+      <c r="E168" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F168" t="s" s="44">
+        <v>144</v>
+      </c>
+      <c r="G168" s="51">
+        <v>2</v>
+      </c>
+      <c r="H168" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I168" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J168" t="s" s="48">
+        <v>145</v>
+      </c>
+      <c r="K168" t="s" s="49">
+        <v>146</v>
+      </c>
+      <c r="L168" s="0"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="44"/>
+      <c r="B169" s="45"/>
+      <c r="C169" s="46"/>
+      <c r="D169" s="46"/>
+      <c r="E169" s="47"/>
+      <c r="F169" t="s" s="44">
+        <v>18</v>
+      </c>
+      <c r="G169" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H169" s="52">
+        <v>15750</v>
+      </c>
+      <c r="I169" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J169" t="s" s="48">
+        <v>18</v>
+      </c>
+      <c r="K169" s="49"/>
+      <c r="L169" s="0"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="44"/>
+      <c r="B170" s="45"/>
+      <c r="C170" s="46"/>
+      <c r="D170" s="46"/>
+      <c r="E170" s="47"/>
+      <c r="F170" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="G170" t="s" s="51">
+        <v>48</v>
+      </c>
+      <c r="H170" s="52">
+        <v>4500</v>
+      </c>
+      <c r="I170" s="53">
         <v>0</v>
       </c>
-      <c r="I167" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J167" t="s" s="48">
-        <v>150</v>
-      </c>
-      <c r="K167" t="s" s="49">
-        <v>279</v>
-      </c>
-      <c r="L167" s="0"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="44"/>
-      <c r="B168" s="45"/>
-      <c r="C168" s="46"/>
-      <c r="D168" s="46"/>
-      <c r="E168" s="47"/>
-      <c r="F168" s="44"/>
-      <c r="G168" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H168" s="52">
-        <v>0</v>
-      </c>
-      <c r="I168" s="53"/>
-      <c r="J168" s="48"/>
-      <c r="K168" s="49"/>
-      <c r="L168" s="0"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B169" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C169" t="s" s="46">
-        <v>281</v>
-      </c>
-      <c r="D169" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E169" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F169" t="s" s="44">
-        <v>282</v>
-      </c>
-      <c r="G169" s="51">
-        <v>1</v>
-      </c>
-      <c r="H169" s="52">
-        <v>2132.20</v>
-      </c>
-      <c r="I169" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J169" t="s" s="48">
-        <v>283</v>
-      </c>
-      <c r="K169" t="s" s="49">
-        <v>284</v>
-      </c>
-      <c r="L169" s="0"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B170" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C170" t="s" s="46">
-        <v>281</v>
-      </c>
-      <c r="D170" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E170" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F170" t="s" s="44">
-        <v>285</v>
-      </c>
-      <c r="G170" s="51">
-        <v>1</v>
-      </c>
-      <c r="H170" s="52">
-        <v>1359.96</v>
-      </c>
-      <c r="I170" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J170" t="s" s="48">
-        <v>286</v>
-      </c>
-      <c r="K170" t="s" s="49">
-        <v>284</v>
-      </c>
+      <c r="J170" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="K170" s="49"/>
       <c r="L170" s="0"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B171" s="45">
-        <v>0000106644</v>
+        <v>0000106170</v>
       </c>
       <c r="C171" t="s" s="46">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D171" t="s" s="46">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E171" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F171" t="s" s="44">
-        <v>287</v>
+        <v>224</v>
       </c>
       <c r="G171" s="51">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H171" s="52">
-        <v>949.92</v>
-      </c>
-      <c r="I171" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I171" s="53">
+        <v>72</v>
       </c>
       <c r="J171" t="s" s="48">
-        <v>288</v>
-      </c>
-      <c r="K171" t="s" s="49">
-        <v>284</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="K171" s="49"/>
       <c r="L171" s="0"/>
     </row>
     <row r="172">
-      <c r="A172" t="s" s="44">
-        <v>88</v>
-      </c>
-      <c r="B172" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C172" t="s" s="46">
-        <v>281</v>
-      </c>
-      <c r="D172" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E172" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F172" t="s" s="44">
-        <v>289</v>
-      </c>
-      <c r="G172" s="51">
-        <v>1</v>
+      <c r="A172" s="44"/>
+      <c r="B172" s="45"/>
+      <c r="C172" s="46"/>
+      <c r="D172" s="46"/>
+      <c r="E172" s="47"/>
+      <c r="F172" s="44"/>
+      <c r="G172" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H172" s="52">
-        <v>531.68</v>
-      </c>
-      <c r="I172" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J172" t="s" s="48">
-        <v>290</v>
-      </c>
-      <c r="K172" t="s" s="49">
-        <v>284</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I172" s="53"/>
+      <c r="J172" s="48"/>
+      <c r="K172" s="49"/>
       <c r="L172" s="0"/>
     </row>
     <row r="173">
-      <c r="A173" s="44"/>
-      <c r="B173" s="45"/>
-      <c r="C173" s="46"/>
-      <c r="D173" s="46"/>
-      <c r="E173" s="47"/>
-      <c r="F173" s="44"/>
-      <c r="G173" t="s" s="51">
-        <v>27</v>
+      <c r="A173" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B173" s="45">
+        <v>0000106171</v>
+      </c>
+      <c r="C173" t="s" s="46">
+        <v>293</v>
+      </c>
+      <c r="D173" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E173" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F173" t="s" s="44">
+        <v>90</v>
+      </c>
+      <c r="G173" s="51">
+        <v>70</v>
       </c>
       <c r="H173" s="52">
-        <v>4973.76</v>
-      </c>
-      <c r="I173" s="53"/>
-      <c r="J173" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I173" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J173" t="s" s="48">
+        <v>91</v>
+      </c>
       <c r="K173" s="49"/>
       <c r="L173" s="0"/>
     </row>
     <row r="174">
-      <c r="A174" t="s" s="44">
-        <v>291</v>
-      </c>
-      <c r="B174" s="45">
-        <v>0000106764</v>
-      </c>
-      <c r="C174" t="s" s="46">
-        <v>292</v>
-      </c>
-      <c r="D174" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E174" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F174" t="s" s="44">
+      <c r="A174" s="44"/>
+      <c r="B174" s="45"/>
+      <c r="C174" s="46"/>
+      <c r="D174" s="46"/>
+      <c r="E174" s="47"/>
+      <c r="F174" s="44"/>
+      <c r="G174" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H174" s="52">
+        <v>0</v>
+      </c>
+      <c r="I174" s="53"/>
+      <c r="J174" s="48"/>
+      <c r="K174" s="49"/>
+      <c r="L174" s="0"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B175" s="45">
+        <v>0000106172</v>
+      </c>
+      <c r="C175" t="s" s="46">
         <v>293</v>
       </c>
-      <c r="G174" s="51">
-        <v>24</v>
-      </c>
-      <c r="H174" s="52">
-        <v>15</v>
-      </c>
-      <c r="I174" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J174" t="s" s="48">
+      <c r="D175" t="s" s="46">
         <v>294</v>
       </c>
-      <c r="K174" t="s" s="49">
-        <v>295</v>
-      </c>
-      <c r="L174" s="0"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="44"/>
-      <c r="B175" s="45"/>
-      <c r="C175" s="46"/>
-      <c r="D175" s="46"/>
-      <c r="E175" s="47"/>
-      <c r="F175" s="44"/>
-      <c r="G175" t="s" s="51">
-        <v>27</v>
+      <c r="E175" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F175" t="s" s="44">
+        <v>90</v>
+      </c>
+      <c r="G175" s="51">
+        <v>70</v>
       </c>
       <c r="H175" s="52">
-        <v>360</v>
-      </c>
-      <c r="I175" s="53"/>
-      <c r="J175" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I175" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J175" t="s" s="48">
+        <v>91</v>
+      </c>
       <c r="K175" s="49"/>
       <c r="L175" s="0"/>
     </row>
     <row r="176">
-      <c r="A176" t="s" s="44">
-        <v>98</v>
-      </c>
-      <c r="B176" s="45">
-        <v>0000106173</v>
-      </c>
-      <c r="C176" t="s" s="46">
-        <v>274</v>
-      </c>
-      <c r="D176" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E176" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F176" t="s" s="44">
-        <v>171</v>
-      </c>
-      <c r="G176" s="51">
-        <v>180</v>
+      <c r="A176" s="44"/>
+      <c r="B176" s="45"/>
+      <c r="C176" s="46"/>
+      <c r="D176" s="46"/>
+      <c r="E176" s="47"/>
+      <c r="F176" s="44"/>
+      <c r="G176" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H176" s="52">
         <v>0</v>
       </c>
-      <c r="I176" s="53">
-        <v>225</v>
-      </c>
-      <c r="J176" t="s" s="48">
-        <v>172</v>
-      </c>
+      <c r="I176" s="53"/>
+      <c r="J176" s="48"/>
       <c r="K176" s="49"/>
       <c r="L176" s="0"/>
     </row>
     <row r="177">
-      <c r="A177" s="44"/>
-      <c r="B177" s="45"/>
-      <c r="C177" s="46"/>
-      <c r="D177" s="46"/>
-      <c r="E177" s="47"/>
-      <c r="F177" s="44"/>
-      <c r="G177" t="s" s="51">
-        <v>27</v>
+      <c r="A177" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B177" s="45">
+        <v>0000106234</v>
+      </c>
+      <c r="C177" t="s" s="46">
+        <v>296</v>
+      </c>
+      <c r="D177" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E177" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F177" t="s" s="44">
+        <v>297</v>
+      </c>
+      <c r="G177" s="51">
+        <v>5</v>
       </c>
       <c r="H177" s="52">
         <v>0</v>
       </c>
-      <c r="I177" s="53"/>
-      <c r="J177" s="48"/>
-      <c r="K177" s="49"/>
+      <c r="I177" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J177" t="s" s="48">
+        <v>189</v>
+      </c>
+      <c r="K177" t="s" s="49">
+        <v>298</v>
+      </c>
       <c r="L177" s="0"/>
     </row>
     <row r="178">
       <c r="A178" t="s" s="44">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B178" s="45">
-        <v>0000106174</v>
+        <v>0000106234</v>
       </c>
       <c r="C178" t="s" s="46">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="D178" t="s" s="46">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E178" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F178" t="s" s="44">
-        <v>171</v>
+        <v>299</v>
       </c>
       <c r="G178" s="51">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="H178" s="52">
         <v>0</v>
       </c>
-      <c r="I178" s="53">
-        <v>225</v>
+      <c r="I178" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J178" t="s" s="48">
-        <v>172</v>
-      </c>
-      <c r="K178" s="49"/>
+        <v>193</v>
+      </c>
+      <c r="K178" t="s" s="49">
+        <v>298</v>
+      </c>
       <c r="L178" s="0"/>
     </row>
     <row r="179">
@@ -6948,7 +6932,7 @@
       <c r="E179" s="47"/>
       <c r="F179" s="44"/>
       <c r="G179" t="s" s="51">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H179" s="52">
         <v>0</v>
@@ -6960,710 +6944,724 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="44">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B180" s="45">
-        <v>0000106100</v>
+        <v>0000106644</v>
       </c>
       <c r="C180" t="s" s="46">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D180" t="s" s="46">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E180" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F180" t="s" s="44">
-        <v>183</v>
+        <v>301</v>
       </c>
       <c r="G180" s="51">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="H180" s="52">
-        <v>0</v>
-      </c>
-      <c r="I180" s="53">
-        <v>104</v>
+        <v>2132.20</v>
+      </c>
+      <c r="I180" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J180" t="s" s="48">
-        <v>184</v>
+        <v>302</v>
       </c>
       <c r="K180" t="s" s="49">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="L180" s="0"/>
     </row>
     <row r="181">
-      <c r="A181" s="44"/>
-      <c r="B181" s="45"/>
-      <c r="C181" s="46"/>
-      <c r="D181" s="46"/>
-      <c r="E181" s="47"/>
-      <c r="F181" s="44"/>
-      <c r="G181" t="s" s="51">
-        <v>27</v>
+      <c r="A181" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B181" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C181" t="s" s="46">
+        <v>300</v>
+      </c>
+      <c r="D181" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E181" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F181" t="s" s="44">
+        <v>304</v>
+      </c>
+      <c r="G181" s="51">
+        <v>1</v>
       </c>
       <c r="H181" s="52">
-        <v>0</v>
-      </c>
-      <c r="I181" s="53"/>
-      <c r="J181" s="48"/>
-      <c r="K181" s="49"/>
+        <v>1359.96</v>
+      </c>
+      <c r="I181" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J181" t="s" s="48">
+        <v>305</v>
+      </c>
+      <c r="K181" t="s" s="49">
+        <v>303</v>
+      </c>
       <c r="L181" s="0"/>
     </row>
     <row r="182">
       <c r="A182" t="s" s="44">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B182" s="45">
-        <v>0000106102</v>
+        <v>0000106644</v>
       </c>
       <c r="C182" t="s" s="46">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D182" t="s" s="46">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E182" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F182" t="s" s="44">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="G182" s="51">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H182" s="52">
-        <v>0</v>
+        <v>949.92</v>
       </c>
       <c r="I182" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J182" t="s" s="48">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="K182" t="s" s="49">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="L182" s="0"/>
     </row>
     <row r="183">
-      <c r="A183" s="44"/>
-      <c r="B183" s="45"/>
-      <c r="C183" s="46"/>
-      <c r="D183" s="46"/>
-      <c r="E183" s="47"/>
-      <c r="F183" s="44"/>
-      <c r="G183" t="s" s="51">
-        <v>27</v>
+      <c r="A183" t="s" s="44">
+        <v>82</v>
+      </c>
+      <c r="B183" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C183" t="s" s="46">
+        <v>300</v>
+      </c>
+      <c r="D183" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E183" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F183" t="s" s="44">
+        <v>308</v>
+      </c>
+      <c r="G183" s="51">
+        <v>1</v>
       </c>
       <c r="H183" s="52">
-        <v>0</v>
-      </c>
-      <c r="I183" s="53"/>
-      <c r="J183" s="48"/>
-      <c r="K183" s="49"/>
+        <v>531.68</v>
+      </c>
+      <c r="I183" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J183" t="s" s="48">
+        <v>309</v>
+      </c>
+      <c r="K183" t="s" s="49">
+        <v>303</v>
+      </c>
       <c r="L183" s="0"/>
     </row>
     <row r="184">
-      <c r="A184" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B184" s="45">
-        <v>0000106103</v>
-      </c>
-      <c r="C184" t="s" s="46">
-        <v>296</v>
-      </c>
-      <c r="D184" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E184" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F184" t="s" s="44">
-        <v>244</v>
-      </c>
-      <c r="G184" s="51">
-        <v>52</v>
+      <c r="A184" s="44"/>
+      <c r="B184" s="45"/>
+      <c r="C184" s="46"/>
+      <c r="D184" s="46"/>
+      <c r="E184" s="47"/>
+      <c r="F184" s="44"/>
+      <c r="G184" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H184" s="52">
-        <v>0</v>
-      </c>
-      <c r="I184" t="s" s="53">
+        <v>4973.76</v>
+      </c>
+      <c r="I184" s="53"/>
+      <c r="J184" s="48"/>
+      <c r="K184" s="49"/>
+      <c r="L184" s="0"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="44">
+        <v>310</v>
+      </c>
+      <c r="B185" s="45">
+        <v>0000106764</v>
+      </c>
+      <c r="C185" t="s" s="46">
+        <v>311</v>
+      </c>
+      <c r="D185" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E185" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F185" t="s" s="44">
+        <v>312</v>
+      </c>
+      <c r="G185" s="51">
+        <v>24</v>
+      </c>
+      <c r="H185" s="52">
+        <v>15</v>
+      </c>
+      <c r="I185" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J184" t="s" s="48">
-        <v>245</v>
-      </c>
-      <c r="K184" t="s" s="49">
-        <v>297</v>
-      </c>
-      <c r="L184" s="0"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="44"/>
-      <c r="B185" s="45"/>
-      <c r="C185" s="46"/>
-      <c r="D185" s="46"/>
-      <c r="E185" s="47"/>
-      <c r="F185" s="44"/>
-      <c r="G185" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H185" s="52">
-        <v>0</v>
-      </c>
-      <c r="I185" s="53"/>
-      <c r="J185" s="48"/>
-      <c r="K185" s="49"/>
+      <c r="J185" t="s" s="48">
+        <v>313</v>
+      </c>
+      <c r="K185" t="s" s="49">
+        <v>314</v>
+      </c>
       <c r="L185" s="0"/>
     </row>
     <row r="186">
-      <c r="A186" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B186" s="45">
-        <v>0000106104</v>
-      </c>
-      <c r="C186" t="s" s="46">
-        <v>296</v>
-      </c>
-      <c r="D186" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E186" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F186" t="s" s="44">
-        <v>187</v>
-      </c>
-      <c r="G186" s="51">
-        <v>52</v>
+      <c r="A186" s="44"/>
+      <c r="B186" s="45"/>
+      <c r="C186" s="46"/>
+      <c r="D186" s="46"/>
+      <c r="E186" s="47"/>
+      <c r="F186" s="44"/>
+      <c r="G186" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H186" s="52">
-        <v>0</v>
-      </c>
-      <c r="I186" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J186" t="s" s="48">
-        <v>188</v>
-      </c>
-      <c r="K186" t="s" s="49">
-        <v>297</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="I186" s="53"/>
+      <c r="J186" s="48"/>
+      <c r="K186" s="49"/>
       <c r="L186" s="0"/>
     </row>
     <row r="187">
-      <c r="A187" s="44"/>
-      <c r="B187" s="45"/>
-      <c r="C187" s="46"/>
-      <c r="D187" s="46"/>
-      <c r="E187" s="47"/>
-      <c r="F187" s="44"/>
-      <c r="G187" t="s" s="51">
-        <v>27</v>
+      <c r="A187" t="s" s="44">
+        <v>124</v>
+      </c>
+      <c r="B187" s="45">
+        <v>0000106173</v>
+      </c>
+      <c r="C187" t="s" s="46">
+        <v>293</v>
+      </c>
+      <c r="D187" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E187" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F187" t="s" s="44">
+        <v>158</v>
+      </c>
+      <c r="G187" s="51">
+        <v>180</v>
       </c>
       <c r="H187" s="52">
         <v>0</v>
       </c>
-      <c r="I187" s="53"/>
-      <c r="J187" s="48"/>
+      <c r="I187" s="53">
+        <v>225</v>
+      </c>
+      <c r="J187" t="s" s="48">
+        <v>159</v>
+      </c>
       <c r="K187" s="49"/>
       <c r="L187" s="0"/>
     </row>
     <row r="188">
-      <c r="A188" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B188" s="45">
-        <v>0000106132</v>
-      </c>
-      <c r="C188" t="s" s="46">
-        <v>299</v>
-      </c>
-      <c r="D188" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E188" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F188" t="s" s="44">
-        <v>186</v>
-      </c>
-      <c r="G188" s="51">
-        <v>208</v>
+      <c r="A188" s="44"/>
+      <c r="B188" s="45"/>
+      <c r="C188" s="46"/>
+      <c r="D188" s="46"/>
+      <c r="E188" s="47"/>
+      <c r="F188" s="44"/>
+      <c r="G188" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H188" s="52">
         <v>0</v>
       </c>
-      <c r="I188" s="53">
-        <v>208</v>
-      </c>
-      <c r="J188" t="s" s="48">
-        <v>57</v>
-      </c>
-      <c r="K188" t="s" s="49">
-        <v>297</v>
-      </c>
+      <c r="I188" s="53"/>
+      <c r="J188" s="48"/>
+      <c r="K188" s="49"/>
       <c r="L188" s="0"/>
     </row>
     <row r="189">
-      <c r="A189" s="44"/>
-      <c r="B189" s="45"/>
-      <c r="C189" s="46"/>
-      <c r="D189" s="46"/>
-      <c r="E189" s="47"/>
-      <c r="F189" s="44"/>
-      <c r="G189" t="s" s="51">
-        <v>27</v>
+      <c r="A189" t="s" s="44">
+        <v>124</v>
+      </c>
+      <c r="B189" s="45">
+        <v>0000106174</v>
+      </c>
+      <c r="C189" t="s" s="46">
+        <v>293</v>
+      </c>
+      <c r="D189" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E189" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F189" t="s" s="44">
+        <v>158</v>
+      </c>
+      <c r="G189" s="51">
+        <v>180</v>
       </c>
       <c r="H189" s="52">
         <v>0</v>
       </c>
-      <c r="I189" s="53"/>
-      <c r="J189" s="48"/>
+      <c r="I189" s="53">
+        <v>225</v>
+      </c>
+      <c r="J189" t="s" s="48">
+        <v>159</v>
+      </c>
       <c r="K189" s="49"/>
       <c r="L189" s="0"/>
     </row>
     <row r="190">
-      <c r="A190" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B190" s="45">
-        <v>0000106175</v>
-      </c>
-      <c r="C190" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D190" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E190" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F190" t="s" s="44">
-        <v>186</v>
-      </c>
-      <c r="G190" s="51">
-        <v>208</v>
+      <c r="A190" s="44"/>
+      <c r="B190" s="45"/>
+      <c r="C190" s="46"/>
+      <c r="D190" s="46"/>
+      <c r="E190" s="47"/>
+      <c r="F190" s="44"/>
+      <c r="G190" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H190" s="52">
-        <v>332.67</v>
-      </c>
-      <c r="I190" s="53">
-        <v>208</v>
-      </c>
-      <c r="J190" t="s" s="48">
-        <v>57</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I190" s="53"/>
+      <c r="J190" s="48"/>
       <c r="K190" s="49"/>
       <c r="L190" s="0"/>
     </row>
     <row r="191">
-      <c r="A191" s="44"/>
-      <c r="B191" s="45"/>
-      <c r="C191" s="46"/>
-      <c r="D191" s="46"/>
-      <c r="E191" s="47"/>
-      <c r="F191" s="44"/>
-      <c r="G191" t="s" s="51">
-        <v>27</v>
+      <c r="A191" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B191" s="45">
+        <v>0000106175</v>
+      </c>
+      <c r="C191" t="s" s="46">
+        <v>315</v>
+      </c>
+      <c r="D191" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E191" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F191" t="s" s="44">
+        <v>173</v>
+      </c>
+      <c r="G191" s="51">
+        <v>208</v>
       </c>
       <c r="H191" s="52">
-        <v>69195.36</v>
-      </c>
-      <c r="I191" s="53"/>
-      <c r="J191" s="48"/>
+        <v>362.68</v>
+      </c>
+      <c r="I191" s="53">
+        <v>208</v>
+      </c>
+      <c r="J191" t="s" s="48">
+        <v>52</v>
+      </c>
       <c r="K191" s="49"/>
       <c r="L191" s="0"/>
     </row>
     <row r="192">
-      <c r="A192" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B192" s="45">
-        <v>0000106176</v>
-      </c>
-      <c r="C192" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D192" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E192" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F192" t="s" s="44">
-        <v>187</v>
-      </c>
-      <c r="G192" s="51">
-        <v>52</v>
+      <c r="A192" s="44"/>
+      <c r="B192" s="45"/>
+      <c r="C192" s="46"/>
+      <c r="D192" s="46"/>
+      <c r="E192" s="47"/>
+      <c r="F192" s="44"/>
+      <c r="G192" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H192" s="52">
-        <v>509.41</v>
-      </c>
-      <c r="I192" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J192" t="s" s="48">
-        <v>188</v>
-      </c>
+        <v>75437.44</v>
+      </c>
+      <c r="I192" s="53"/>
+      <c r="J192" s="48"/>
       <c r="K192" s="49"/>
       <c r="L192" s="0"/>
     </row>
     <row r="193">
-      <c r="A193" s="44"/>
-      <c r="B193" s="45"/>
-      <c r="C193" s="46"/>
-      <c r="D193" s="46"/>
-      <c r="E193" s="47"/>
-      <c r="F193" s="44"/>
-      <c r="G193" t="s" s="51">
-        <v>27</v>
+      <c r="A193" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B193" s="45">
+        <v>0000106176</v>
+      </c>
+      <c r="C193" t="s" s="46">
+        <v>315</v>
+      </c>
+      <c r="D193" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E193" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F193" t="s" s="44">
+        <v>174</v>
+      </c>
+      <c r="G193" s="51">
+        <v>52</v>
       </c>
       <c r="H193" s="52">
-        <v>26489.32</v>
-      </c>
-      <c r="I193" s="53"/>
-      <c r="J193" s="48"/>
+        <v>509.41</v>
+      </c>
+      <c r="I193" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J193" t="s" s="48">
+        <v>175</v>
+      </c>
       <c r="K193" s="49"/>
       <c r="L193" s="0"/>
     </row>
     <row r="194">
-      <c r="A194" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B194" s="45">
-        <v>0000106177</v>
-      </c>
-      <c r="C194" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D194" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E194" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F194" t="s" s="44">
-        <v>183</v>
-      </c>
-      <c r="G194" s="51">
-        <v>104</v>
+      <c r="A194" s="44"/>
+      <c r="B194" s="45"/>
+      <c r="C194" s="46"/>
+      <c r="D194" s="46"/>
+      <c r="E194" s="47"/>
+      <c r="F194" s="44"/>
+      <c r="G194" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H194" s="52">
-        <v>471.46</v>
-      </c>
-      <c r="I194" s="53">
-        <v>104</v>
-      </c>
-      <c r="J194" t="s" s="48">
-        <v>184</v>
-      </c>
+        <v>26489.32</v>
+      </c>
+      <c r="I194" s="53"/>
+      <c r="J194" s="48"/>
       <c r="K194" s="49"/>
       <c r="L194" s="0"/>
     </row>
     <row r="195">
-      <c r="A195" s="44"/>
-      <c r="B195" s="45"/>
-      <c r="C195" s="46"/>
-      <c r="D195" s="46"/>
-      <c r="E195" s="47"/>
-      <c r="F195" s="44"/>
-      <c r="G195" t="s" s="51">
-        <v>27</v>
+      <c r="A195" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B195" s="45">
+        <v>0000106178</v>
+      </c>
+      <c r="C195" t="s" s="46">
+        <v>315</v>
+      </c>
+      <c r="D195" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E195" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F195" t="s" s="44">
+        <v>252</v>
+      </c>
+      <c r="G195" s="51">
+        <v>52</v>
       </c>
       <c r="H195" s="52">
-        <v>49031.84</v>
-      </c>
-      <c r="I195" s="53"/>
-      <c r="J195" s="48"/>
+        <v>489.76</v>
+      </c>
+      <c r="I195" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J195" t="s" s="48">
+        <v>253</v>
+      </c>
       <c r="K195" s="49"/>
       <c r="L195" s="0"/>
     </row>
     <row r="196">
-      <c r="A196" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B196" s="45">
-        <v>0000106178</v>
-      </c>
-      <c r="C196" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D196" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E196" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F196" t="s" s="44">
-        <v>244</v>
-      </c>
-      <c r="G196" s="51">
-        <v>52</v>
+      <c r="A196" s="44"/>
+      <c r="B196" s="45"/>
+      <c r="C196" s="46"/>
+      <c r="D196" s="46"/>
+      <c r="E196" s="47"/>
+      <c r="F196" s="44"/>
+      <c r="G196" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H196" s="52">
-        <v>489.76</v>
-      </c>
-      <c r="I196" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J196" t="s" s="48">
-        <v>245</v>
-      </c>
+        <v>25467.52</v>
+      </c>
+      <c r="I196" s="53"/>
+      <c r="J196" s="48"/>
       <c r="K196" s="49"/>
       <c r="L196" s="0"/>
     </row>
     <row r="197">
-      <c r="A197" s="44"/>
-      <c r="B197" s="45"/>
-      <c r="C197" s="46"/>
-      <c r="D197" s="46"/>
-      <c r="E197" s="47"/>
-      <c r="F197" s="44"/>
-      <c r="G197" t="s" s="51">
-        <v>27</v>
+      <c r="A197" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B197" s="45">
+        <v>0000106179</v>
+      </c>
+      <c r="C197" t="s" s="46">
+        <v>315</v>
+      </c>
+      <c r="D197" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E197" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F197" t="s" s="44">
+        <v>250</v>
+      </c>
+      <c r="G197" s="51">
+        <v>52</v>
       </c>
       <c r="H197" s="52">
-        <v>25467.52</v>
-      </c>
-      <c r="I197" s="53"/>
-      <c r="J197" s="48"/>
+        <v>458.18</v>
+      </c>
+      <c r="I197" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J197" t="s" s="48">
+        <v>251</v>
+      </c>
       <c r="K197" s="49"/>
       <c r="L197" s="0"/>
     </row>
     <row r="198">
-      <c r="A198" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B198" s="45">
-        <v>0000106179</v>
-      </c>
-      <c r="C198" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D198" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E198" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F198" t="s" s="44">
-        <v>242</v>
-      </c>
-      <c r="G198" s="51">
-        <v>52</v>
+      <c r="A198" s="44"/>
+      <c r="B198" s="45"/>
+      <c r="C198" s="46"/>
+      <c r="D198" s="46"/>
+      <c r="E198" s="47"/>
+      <c r="F198" s="44"/>
+      <c r="G198" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H198" s="52">
-        <v>458.18</v>
-      </c>
-      <c r="I198" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J198" t="s" s="48">
-        <v>243</v>
-      </c>
+        <v>23825.36</v>
+      </c>
+      <c r="I198" s="53"/>
+      <c r="J198" s="48"/>
       <c r="K198" s="49"/>
       <c r="L198" s="0"/>
     </row>
     <row r="199">
-      <c r="A199" s="44"/>
-      <c r="B199" s="45"/>
-      <c r="C199" s="46"/>
-      <c r="D199" s="46"/>
-      <c r="E199" s="47"/>
-      <c r="F199" s="44"/>
-      <c r="G199" t="s" s="51">
-        <v>27</v>
+      <c r="A199" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B199" s="45">
+        <v>0000106180</v>
+      </c>
+      <c r="C199" t="s" s="46">
+        <v>315</v>
+      </c>
+      <c r="D199" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E199" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F199" t="s" s="44">
+        <v>170</v>
+      </c>
+      <c r="G199" s="51">
+        <v>104</v>
       </c>
       <c r="H199" s="52">
-        <v>23825.36</v>
-      </c>
-      <c r="I199" s="53"/>
-      <c r="J199" s="48"/>
-      <c r="K199" s="49"/>
+        <v>466.80</v>
+      </c>
+      <c r="I199" s="53">
+        <v>104</v>
+      </c>
+      <c r="J199" t="s" s="48">
+        <v>171</v>
+      </c>
+      <c r="K199" t="s" s="49">
+        <v>298</v>
+      </c>
       <c r="L199" s="0"/>
     </row>
     <row r="200">
-      <c r="A200" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B200" s="45">
-        <v>0000106180</v>
-      </c>
-      <c r="C200" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D200" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E200" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F200" t="s" s="44">
-        <v>183</v>
-      </c>
-      <c r="G200" s="51">
-        <v>52</v>
+      <c r="A200" s="44"/>
+      <c r="B200" s="45"/>
+      <c r="C200" s="46"/>
+      <c r="D200" s="46"/>
+      <c r="E200" s="47"/>
+      <c r="F200" s="44"/>
+      <c r="G200" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H200" s="52">
-        <v>471.46</v>
-      </c>
-      <c r="I200" s="53">
-        <v>52</v>
-      </c>
-      <c r="J200" t="s" s="48">
-        <v>184</v>
-      </c>
+        <v>48547.2</v>
+      </c>
+      <c r="I200" s="53"/>
+      <c r="J200" s="48"/>
       <c r="K200" s="49"/>
       <c r="L200" s="0"/>
     </row>
     <row r="201">
-      <c r="A201" s="44"/>
-      <c r="B201" s="45"/>
-      <c r="C201" s="46"/>
-      <c r="D201" s="46"/>
-      <c r="E201" s="47"/>
-      <c r="F201" s="44"/>
-      <c r="G201" t="s" s="51">
-        <v>27</v>
+      <c r="A201" t="s" s="44">
+        <v>316</v>
+      </c>
+      <c r="B201" s="45">
+        <v>0000106980</v>
+      </c>
+      <c r="C201" t="s" s="46">
+        <v>317</v>
+      </c>
+      <c r="D201" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E201" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F201" t="s" s="44">
+        <v>318</v>
+      </c>
+      <c r="G201" s="51">
+        <v>50</v>
       </c>
       <c r="H201" s="52">
-        <v>24515.92</v>
-      </c>
-      <c r="I201" s="53"/>
-      <c r="J201" s="48"/>
-      <c r="K201" s="49"/>
+        <v>532.72</v>
+      </c>
+      <c r="I201" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J201" t="s" s="48">
+        <v>319</v>
+      </c>
+      <c r="K201" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L201" s="0"/>
     </row>
     <row r="202">
-      <c r="A202" t="s" s="44">
-        <v>301</v>
-      </c>
-      <c r="B202" s="45">
+      <c r="A202" s="44"/>
+      <c r="B202" s="45"/>
+      <c r="C202" s="46"/>
+      <c r="D202" s="46"/>
+      <c r="E202" s="47"/>
+      <c r="F202" s="44"/>
+      <c r="G202" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H202" s="52">
+        <v>26636</v>
+      </c>
+      <c r="I202" s="53"/>
+      <c r="J202" s="48"/>
+      <c r="K202" s="49"/>
+      <c r="L202" s="0"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="44">
+        <v>316</v>
+      </c>
+      <c r="B203" s="45">
         <v>0000106980</v>
       </c>
-      <c r="C202" t="s" s="46">
-        <v>302</v>
-      </c>
-      <c r="D202" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E202" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F202" t="s" s="44">
-        <v>303</v>
-      </c>
-      <c r="G202" s="51">
-        <v>50</v>
-      </c>
-      <c r="H202" s="52">
-        <v>531.97</v>
-      </c>
-      <c r="I202" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J202" t="s" s="48">
-        <v>304</v>
-      </c>
-      <c r="K202" t="s" s="49">
-        <v>305</v>
-      </c>
-      <c r="L202" s="0"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="44"/>
-      <c r="B203" s="45"/>
-      <c r="C203" s="46"/>
-      <c r="D203" s="46"/>
-      <c r="E203" s="47"/>
-      <c r="F203" s="44"/>
-      <c r="G203" t="s" s="51">
-        <v>27</v>
+      <c r="C203" t="s" s="46">
+        <v>317</v>
+      </c>
+      <c r="D203" t="s" s="46">
+        <v>294</v>
+      </c>
+      <c r="E203" t="s" s="47">
+        <v>97</v>
+      </c>
+      <c r="F203" t="s" s="44">
+        <v>121</v>
+      </c>
+      <c r="G203" s="51">
+        <v>200</v>
       </c>
       <c r="H203" s="52">
-        <v>26598.5</v>
-      </c>
-      <c r="I203" s="53"/>
-      <c r="J203" s="48"/>
-      <c r="K203" s="49"/>
+        <v>13.14</v>
+      </c>
+      <c r="I203" s="53">
+        <v>6.6</v>
+      </c>
+      <c r="J203" t="s" s="48">
+        <v>122</v>
+      </c>
+      <c r="K203" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L203" s="0"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="44">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B204" s="45">
         <v>0000106980</v>
       </c>
       <c r="C204" t="s" s="46">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D204" t="s" s="46">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E204" t="s" s="47">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F204" t="s" s="44">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="G204" s="51">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H204" s="52">
-        <v>13.12</v>
-      </c>
-      <c r="I204" s="53">
-        <v>6.6</v>
+        <v>12.78</v>
+      </c>
+      <c r="I204" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J204" t="s" s="48">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="K204" t="s" s="49">
-        <v>305</v>
+        <v>66</v>
       </c>
       <c r="L204" s="0"/>
     </row>
     <row r="205">
-      <c r="A205" t="s" s="44">
-        <v>301</v>
-      </c>
-      <c r="B205" s="45">
-        <v>0000106980</v>
-      </c>
-      <c r="C205" t="s" s="46">
-        <v>302</v>
-      </c>
-      <c r="D205" t="s" s="46">
-        <v>275</v>
-      </c>
-      <c r="E205" t="s" s="47">
-        <v>62</v>
-      </c>
-      <c r="F205" t="s" s="44">
-        <v>306</v>
-      </c>
-      <c r="G205" s="51">
-        <v>300</v>
-      </c>
-      <c r="H205" s="52">
-        <v>12.76</v>
-      </c>
-      <c r="I205" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J205" t="s" s="48">
-        <v>307</v>
-      </c>
-      <c r="K205" t="s" s="49">
-        <v>305</v>
-      </c>
+      <c r="A205" s="44"/>
+      <c r="B205" s="45"/>
+      <c r="C205" s="46"/>
+      <c r="D205" s="46"/>
+      <c r="E205" s="47"/>
+      <c r="F205" s="44"/>
+      <c r="G205" s="51"/>
+      <c r="H205" s="52"/>
+      <c r="I205" s="53"/>
+      <c r="J205" s="48"/>
+      <c r="K205" s="49"/>
       <c r="L205" s="0"/>
     </row>
     <row r="206">
@@ -7673,46 +7671,45 @@
       <c r="D206" s="46"/>
       <c r="E206" s="47"/>
       <c r="F206" s="44"/>
-      <c r="G206" s="51"/>
-      <c r="H206" s="52"/>
-      <c r="I206" s="53"/>
+      <c r="G206" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H206" s="52">
+        <v>1328468.34</v>
+      </c>
+      <c r="I206" s="53">
+        <v>1907.7</v>
+      </c>
       <c r="J206" s="48"/>
       <c r="K206" s="49"/>
       <c r="L206" s="0"/>
     </row>
-    <row r="207">
+    <row r="207" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A207" s="44"/>
       <c r="B207" s="45"/>
       <c r="C207" s="46"/>
       <c r="D207" s="46"/>
       <c r="E207" s="47"/>
       <c r="F207" s="44"/>
-      <c r="G207" t="s" s="51">
-        <v>27</v>
-      </c>
-      <c r="H207" s="52">
-        <v>1278360.79</v>
-      </c>
-      <c r="I207" s="53">
-        <v>1603.2</v>
-      </c>
+      <c r="G207" s="51"/>
+      <c r="H207" s="52"/>
+      <c r="I207" s="53"/>
       <c r="J207" s="48"/>
       <c r="K207" s="49"/>
       <c r="L207" s="0"/>
     </row>
     <row r="208" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="44"/>
-      <c r="B208" s="45"/>
-      <c r="C208" s="46"/>
-      <c r="D208" s="46"/>
-      <c r="E208" s="47"/>
-      <c r="F208" s="44"/>
-      <c r="G208" s="51"/>
-      <c r="H208" s="52"/>
-      <c r="I208" s="53"/>
-      <c r="J208" s="48"/>
-      <c r="K208" s="49"/>
-      <c r="L208" s="0"/>
+      <c r="A208" s="5"/>
+      <c r="B208" s="25"/>
+      <c r="C208" s="19"/>
+      <c r="D208" s="19"/>
+      <c r="E208" s="13"/>
+      <c r="F208" s="5"/>
+      <c r="G208" s="25"/>
+      <c r="H208" s="25"/>
+      <c r="I208" s="25"/>
+      <c r="J208" s="36"/>
+      <c r="K208" s="29"/>
     </row>
     <row r="209" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A209" s="5"/>
@@ -7961,7 +7958,7 @@
       <c r="J227" s="36"/>
       <c r="K227" s="29"/>
     </row>
-    <row r="228" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="228" x14ac:dyDescent="0.2">
       <c r="A228" s="5"/>
       <c r="B228" s="25"/>
       <c r="C228" s="19"/>
@@ -8287,17 +8284,17 @@
       <c r="K252" s="29"/>
     </row>
     <row r="253" x14ac:dyDescent="0.2">
-      <c r="A253" s="5"/>
-      <c r="B253" s="25"/>
-      <c r="C253" s="19"/>
-      <c r="D253" s="19"/>
-      <c r="E253" s="13"/>
-      <c r="F253" s="5"/>
+      <c r="A253" s="6"/>
+      <c r="B253" s="33"/>
+      <c r="C253" s="20"/>
+      <c r="D253" s="20"/>
+      <c r="E253" s="14"/>
+      <c r="F253" s="6"/>
       <c r="G253" s="25"/>
       <c r="H253" s="25"/>
       <c r="I253" s="25"/>
       <c r="J253" s="36"/>
-      <c r="K253" s="29"/>
+      <c r="K253" s="30"/>
     </row>
     <row r="254" x14ac:dyDescent="0.2">
       <c r="A254" s="6"/>
@@ -16789,7 +16786,7 @@
       <c r="K906" s="30"/>
     </row>
     <row r="907" x14ac:dyDescent="0.2">
-      <c r="A907" s="6"/>
+      <c r="A907" s="8"/>
       <c r="B907" s="33"/>
       <c r="C907" s="20"/>
       <c r="D907" s="20"/>
@@ -18673,18 +18670,12 @@
       <c r="J1051" s="36"/>
       <c r="K1051" s="30"/>
     </row>
-    <row r="1052" x14ac:dyDescent="0.2">
-      <c r="A1052" s="8"/>
-      <c r="B1052" s="33"/>
-      <c r="C1052" s="20"/>
-      <c r="D1052" s="20"/>
-      <c r="E1052" s="14"/>
-      <c r="F1052" s="6"/>
-      <c r="G1052" s="25"/>
-      <c r="H1052" s="25"/>
-      <c r="I1052" s="25"/>
-      <c r="J1052" s="36"/>
-      <c r="K1052" s="30"/>
+    <row r="1052" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1052" s="4"/>
+      <c r="G1052" s="26"/>
+      <c r="H1052" s="26"/>
+      <c r="I1052" s="26"/>
+      <c r="J1052" s="37"/>
     </row>
     <row r="1053" ht="15" x14ac:dyDescent="0.25">
       <c r="A1053" s="4"/>
@@ -22292,7 +22283,6 @@
       <c r="J1567" s="37"/>
     </row>
     <row r="1568" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1568" s="4"/>
       <c r="G1568" s="26"/>
       <c r="H1568" s="26"/>
       <c r="I1568" s="26"/>
@@ -56233,12 +56223,6 @@
       <c r="H7224" s="26"/>
       <c r="I7224" s="26"/>
       <c r="J7224" s="37"/>
-    </row>
-    <row r="7225" ht="15" x14ac:dyDescent="0.25">
-      <c r="G7225" s="26"/>
-      <c r="H7225" s="26"/>
-      <c r="I7225" s="26"/>
-      <c r="J7225" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/latest.xlsx
+++ b/data/latest.xlsx
@@ -91,6 +91,10 @@
     <t>SA, 2075, STP, 10 - 20 kg, 9002                                                 </t>
   </si>
   <si>
+    <t>SHIP DATE - ASAP
+Return and Repair of Arms for RGA R25-004 SA, 2075, STP, 10 - 20 kg, 9002                                                 </t>
+  </si>
+  <si>
     <t>NS-SM-E491-3GJ-J                  </t>
   </si>
   <si>
@@ -99,10 +103,6 @@
   <si>
     <t>SHIP DATE - ASAP
 Return and Repair of Arms for RGA R25-004 SA, 2075, 3P, 10 -20 kg, 9002                                                   </t>
-  </si>
-  <si>
-    <t>SHIP DATE - ASAP
-Return and Repair of Arms for RGA R25-004 SA, 2075, 3P, 10 -20 kg, 9002                                                    SA, 2075, 3P, 10 -20 kg, 9002                                                   </t>
   </si>
   <si>
     <t>05/15/2026</t>
@@ -272,70 +272,22 @@
     <t>SA, 2075, 9P, 10 -20 kg, 9002, Harness Change Sample                            </t>
   </si>
   <si>
-    <t>BURTONMEDICALLLC    </t>
+    <t>EGGMED              </t>
   </si>
   <si>
-    <t>05/11/2026</t>
+    <t>07/10/2026</t>
   </si>
   <si>
-    <t>07/03/2026</t>
+    <t>SM-BERCH-EXT-ADP-9010             </t>
   </si>
   <si>
-    <t>C-2-AW-LN                         </t>
-  </si>
-  <si>
-    <t>Single Ceiling Drop Tube, 3P Slip Ring and Harness, 700mm                       </t>
-  </si>
-  <si>
-    <t>DOCK DATE - JULY 10, 2026</t>
+    <t>Berchtold adapter for OASYS 2001 arm to Berchtold extension arm, RAL 9010       </t>
   </si>
   <si>
     <t>June, 2026</t>
   </si>
   <si>
     <t>Hours available = 600. Hours remaining = 582</t>
-  </si>
-  <si>
-    <t>SLW-068055-3WG                    </t>
-  </si>
-  <si>
-    <t>Light Duty Wall Mount Spring Arm - White                                        </t>
-  </si>
-  <si>
-    <t>07/08/2026</t>
-  </si>
-  <si>
-    <t>SLF-0655-1WG                      </t>
-  </si>
-  <si>
-    <t> Light Duty Spring Arm with Floor Stand                                         </t>
-  </si>
-  <si>
-    <t>DOCK DATE - JULY 15, 2026</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t>OKAY</t>
-  </si>
-  <si>
-    <t>C-2-AW-PN                         </t>
-  </si>
-  <si>
-    <t>Single Ceiling Drop Tube, 3P Slip Ring and Harness, 900mm                       </t>
-  </si>
-  <si>
-    <t>DOCK DATE - JULY 17, 2026</t>
-  </si>
-  <si>
-    <t>EGGMED              </t>
-  </si>
-  <si>
-    <t>SM-BERCH-EXT-ADP-9010             </t>
-  </si>
-  <si>
-    <t>Berchtold adapter for OASYS 2001 arm to Berchtold extension arm, RAL 9010       </t>
   </si>
   <si>
     <t>SM-G291-0WS-X                     </t>
@@ -354,55 +306,16 @@
     <t>Spring Arm, Med Duty, 2075, LCH, 3P, 46-57Nm, 9010                              </t>
   </si>
   <si>
-    <t>NEXORMEDICAL        </t>
+    <t>DERUNGSLICHT-EUR    </t>
   </si>
   <si>
-    <t>07/14/2026</t>
-  </si>
-  <si>
-    <t>SA-L-LCK-F-BRK-KT                 </t>
-  </si>
-  <si>
-    <t>Locking Collar with a brake screw                                               </t>
-  </si>
-  <si>
-    <t>REDSHANK            </t>
-  </si>
-  <si>
-    <t>06/17/2026</t>
-  </si>
-  <si>
-    <t>07/15/2026</t>
-  </si>
-  <si>
-    <t>NS-WIREFEE                        </t>
-  </si>
-  <si>
-    <t>Wire Transfer Fee                                                               </t>
-  </si>
-  <si>
-    <t>SA-L-0772-6B-E                    </t>
-  </si>
-  <si>
-    <t>Light Spring Arm Sub Assembly, 3C, 1SR, 40Nm,720mm, Curved, Bottom, Brandon Med </t>
+    <t>04/23/2026</t>
   </si>
   <si>
     <t>07/17/2026</t>
   </si>
   <si>
-    <t>SR-3P-F-ASSY                      </t>
-  </si>
-  <si>
-    <t>3P SLIP RING - FEMALE                                                           </t>
-  </si>
-  <si>
-    <t>DOCK DATE - JULY 24, 2026</t>
-  </si>
-  <si>
-    <t>DERUNGSLICHT-EUR    </t>
-  </si>
-  <si>
-    <t>04/23/2026</t>
+    <t>OKAY</t>
   </si>
   <si>
     <t>SLX-7380-7W6                      </t>
@@ -468,31 +381,43 @@
     <t>SHIP DATES - AS NOTED</t>
   </si>
   <si>
-    <t>SCANATRON           </t>
+    <t>OQTIS               </t>
   </si>
   <si>
-    <t>06/18/2026</t>
+    <t>06/25/2026</t>
   </si>
   <si>
-    <t>SM-B179-3WH-5                     </t>
+    <t>SM-I091-3MS-X                     </t>
   </si>
   <si>
-    <t>Spring Arm, Med Duty, 2001 LCH, 3P, bearing end, RAL 9010                       </t>
+    <t>Spring Arm Med Duty, 910mm, 3P, TM2001, RAL 9016                                </t>
   </si>
   <si>
-    <t>SHIP DATE - SEE NOTES</t>
+    <t>SR-3P-F-ASSY                      </t>
   </si>
   <si>
-    <t>07/06/2026</t>
-  </si>
-  <si>
-    <t>07/20/2026</t>
+    <t>3P SLIP RING - FEMALE                                                           </t>
   </si>
   <si>
     <t>SR-3P-M-ASSY                      </t>
   </si>
   <si>
     <t>3P SLIP RING - MALE                                                             </t>
+  </si>
+  <si>
+    <t>BURTONMEDICALLLC    </t>
+  </si>
+  <si>
+    <t>07/16/2026</t>
+  </si>
+  <si>
+    <t>07/22/2026</t>
+  </si>
+  <si>
+    <t>C-7-DW-HR                         </t>
+  </si>
+  <si>
+    <t>Dual Splitter and Drop Tube, 3P Slip Ring and Harness, 500mm                    </t>
   </si>
   <si>
     <t>04/28/2026</t>
@@ -556,22 +481,29 @@
     <t>Spring Arm, Med Duty, LCH, 3P, (60 - 105Nm), Floor Stand  Bottom mount, RAL 9016</t>
   </si>
   <si>
+    <t>05/11/2026</t>
+  </si>
+  <si>
     <t>07/31/2026</t>
   </si>
   <si>
-    <t>SLF-55XX-7WT                      </t>
+    <t>SLW-068055-3WG                    </t>
   </si>
   <si>
-    <t>Floor Stand, ULD 550mm Spring Arm, 165 in/lbs, RAL9010, with locking molex      </t>
+    <t>Light Duty Wall Mount Spring Arm - White                                        </t>
   </si>
   <si>
-    <t>DOCK DATE - AUGUST 7, 2026</t>
+    <t>DOCK DATE - AUGUST 7, 2026
+Revised date for SLF's - September 7, 2026</t>
   </si>
   <si>
     <t>SA-L-KEY                          </t>
   </si>
   <si>
     <t>*Locking Key                                                                    </t>
+  </si>
+  <si>
+    <t>DOCK DATE - AUGUST 7, 2026</t>
   </si>
   <si>
     <t>C-0-XW-XJ                         </t>
@@ -592,10 +524,19 @@
     <t>Weight for Floor Base                                                           </t>
   </si>
   <si>
+    <t>SCANATRON           </t>
+  </si>
+  <si>
+    <t>06/18/2026</t>
+  </si>
+  <si>
     <t>CA1-02B-01-W5                     </t>
   </si>
   <si>
     <t>Central Axis, Single, 850mm, 3P, RAL 9010                                       </t>
+  </si>
+  <si>
+    <t>SHIP DATE - SEE NOTES</t>
   </si>
   <si>
     <t>CA1-02B-50-W5                     </t>
@@ -640,6 +581,20 @@
     <t>Spring Arm, Med Duty, 2075, LCH, 5P, 95-125Nm, 9010                             </t>
   </si>
   <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>SA-M-CV-P2-ASSY-7011-2-KT         </t>
+  </si>
+  <si>
+    <t>PLUG COVER 2 ASSEMBLY - RAL7011, version 2 - KIT                                </t>
+  </si>
+  <si>
+    <t>SHIP DATE - ASAP
+NO CHARGE ORDER.
+**THERE SHOULD BE NO MORE NO CHARGE ORDER FOR P2'S</t>
+  </si>
+  <si>
     <t>IMAGEDIAGNOSTICS    </t>
   </si>
   <si>
@@ -661,7 +616,7 @@
     <t>July, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = -215.2</t>
+    <t>Hours available = 600. Hours remaining = 28.75</t>
   </si>
   <si>
     <t>SM-E491-0MQ-X                     </t>
@@ -713,6 +668,30 @@
     <t>08/14/2026</t>
   </si>
   <si>
+    <t>07/14/2026</t>
+  </si>
+  <si>
+    <t>EMA-10024-XX-0B                   </t>
+  </si>
+  <si>
+    <t>Monitor mount adaptor, up to 24" monitor, 10kg, RAL 7035                        </t>
+  </si>
+  <si>
+    <t>SHIP DATE - AUGUST 14, 2026</t>
+  </si>
+  <si>
+    <t>MMF-300-G2-XXX-X                  </t>
+  </si>
+  <si>
+    <t>Medium Duty Floor Stand, No Electrical, RAL 9002                                </t>
+  </si>
+  <si>
+    <t>SM-C791-0GB-X                     </t>
+  </si>
+  <si>
+    <t>Med Duty, 2001 Spring Arm (FS), Stop, RAL 9002                                  </t>
+  </si>
+  <si>
     <t>LOC                 </t>
   </si>
   <si>
@@ -720,12 +699,6 @@
   </si>
   <si>
     <t>08/17/2026</t>
-  </si>
-  <si>
-    <t>EMA-10024-XX-0B                   </t>
-  </si>
-  <si>
-    <t>Monitor mount adaptor, up to 24" monitor, 10kg, RAL 7035                        </t>
   </si>
   <si>
     <t>SHIP DATE - ASAP
@@ -798,9 +771,6 @@
     <t>DOCK DATE - October 14, 2026</t>
   </si>
   <si>
-    <t>07/09/2026</t>
-  </si>
-  <si>
     <t>DOCK DATE - OCTOBER 16, 2026</t>
   </si>
   <si>
@@ -820,7 +790,37 @@
     <t>08/31/2026</t>
   </si>
   <si>
+    <t>SLF-55XX-7WT                      </t>
+  </si>
+  <si>
+    <t>Floor Stand, ULD 550mm Spring Arm, 165 in/lbs, RAL9010, with locking molex      </t>
+  </si>
+  <si>
+    <t>SLF-0655-1WG                      </t>
+  </si>
+  <si>
+    <t> Light Duty Spring Arm with Floor Stand                                         </t>
+  </si>
+  <si>
+    <t>REVISED SHIP DATE - AUGUST 31, 2026</t>
+  </si>
+  <si>
     <t>DOCK DATE - SEPTEMBER 8, 2026</t>
+  </si>
+  <si>
+    <t>07/15/2026</t>
+  </si>
+  <si>
+    <t>SA-L-9010-EXTCVR2-KT              </t>
+  </si>
+  <si>
+    <t>Extension Arm Main Cover Kit, v2                                                </t>
+  </si>
+  <si>
+    <t>SA-L-LCK-F-KT                     </t>
+  </si>
+  <si>
+    <t>Locking Collar with Screw                                                       </t>
   </si>
   <si>
     <t>06/09/2026</t>
@@ -838,7 +838,7 @@
     <t>August, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = -195</t>
+    <t>Hours available = 600. Hours remaining = -246.3</t>
   </si>
   <si>
     <t>EKONTOR             </t>
@@ -880,10 +880,37 @@
     <t>DOCK DATE - OCTOBER 5, 2026</t>
   </si>
   <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
     <t>SR-3P-M-ASSY-CR-HRNS              </t>
   </si>
   <si>
     <t>3P Slip Ring - Male (with wiring components)                                    </t>
+  </si>
+  <si>
+    <t>09/29/2026</t>
+  </si>
+  <si>
+    <t>DOCK DATE - OCTOBER 6, 2026</t>
+  </si>
+  <si>
+    <t>C-2-AW-PN                         </t>
+  </si>
+  <si>
+    <t>Single Ceiling Drop Tube, 3P Slip Ring and Harness, 900mm                       </t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>NEW DOCK DATE - OCTOBER 14, 2026</t>
+  </si>
+  <si>
+    <t>September, 2026</t>
+  </si>
+  <si>
+    <t>Hours available = 600. Hours remaining = 433</t>
   </si>
   <si>
     <t>06/29/2026</t>
@@ -892,13 +919,19 @@
     <t>10/09/2026</t>
   </si>
   <si>
-    <t>September, 2026</t>
+    <t>10/16/2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = 392.5</t>
+    <t>10/30/2026</t>
   </si>
   <si>
-    <t>10/16/2026</t>
+    <t>DOCK DATE - NOVEMBER 6, 2026</t>
+  </si>
+  <si>
+    <t>C-2-AW-LN                         </t>
+  </si>
+  <si>
+    <t>Single Ceiling Drop Tube, 3P Slip Ring and Harness, 700mm                       </t>
   </si>
   <si>
     <t>11/13/2026</t>
@@ -907,7 +940,7 @@
     <t>October, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = 528</t>
+    <t>Hours available = 600. Hours remaining = 350</t>
   </si>
   <si>
     <t>07/04/2024</t>
@@ -978,18 +1011,6 @@
   </si>
   <si>
     <t>07/05/2024</t>
-  </si>
-  <si>
-    <t>OQTIS               </t>
-  </si>
-  <si>
-    <t>06/25/2026</t>
-  </si>
-  <si>
-    <t>SM-I091-3MS-X                     </t>
-  </si>
-  <si>
-    <t>Spring Arm Med Duty, 910mm, 3P, TM2001, RAL 9016                                </t>
   </si>
 </sst>
 </file>
@@ -1948,7 +1969,7 @@
         <v>22</v>
       </c>
       <c r="K8" t="s" s="49">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L8" s="0"/>
     </row>
@@ -1969,7 +1990,7 @@
         <v>16</v>
       </c>
       <c r="F9" t="s" s="44">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" s="51">
         <v>1</v>
@@ -1981,7 +2002,7 @@
         <v>18</v>
       </c>
       <c r="J9" t="s" s="48">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s" s="49">
         <v>26</v>
@@ -2059,7 +2080,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="s" s="44">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G12" s="51">
         <v>1</v>
@@ -2853,7 +2874,7 @@
       <c r="D38" s="46"/>
       <c r="E38" s="47"/>
       <c r="F38" s="44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s" s="51">
         <v>48</v>
@@ -2865,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="J38" s="48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K38" s="49"/>
       <c r="L38" s="0"/>
@@ -2875,34 +2896,34 @@
         <v>82</v>
       </c>
       <c r="B39" s="45">
-        <v>0000106939</v>
+        <v>0000106974</v>
       </c>
       <c r="C39" t="s" s="46">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s" s="46">
         <v>83</v>
-      </c>
-      <c r="D39" t="s" s="46">
-        <v>84</v>
       </c>
       <c r="E39" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F39" t="s" s="44">
+        <v>84</v>
+      </c>
+      <c r="G39" s="51">
+        <v>9</v>
+      </c>
+      <c r="H39" s="52">
+        <v>635.00</v>
+      </c>
+      <c r="I39" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s" s="48">
         <v>85</v>
       </c>
-      <c r="G39" s="51">
-        <v>25</v>
-      </c>
-      <c r="H39" s="52">
-        <v>233.81</v>
-      </c>
-      <c r="I39" s="53">
-        <v>12.5</v>
-      </c>
-      <c r="J39" t="s" s="48">
-        <v>86</v>
-      </c>
       <c r="K39" t="s" s="49">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="L39" s="0"/>
     </row>
@@ -2911,34 +2932,34 @@
         <v>82</v>
       </c>
       <c r="B40" s="45">
-        <v>0000106939</v>
+        <v>0000106974</v>
       </c>
       <c r="C40" t="s" s="46">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s" s="46">
         <v>83</v>
-      </c>
-      <c r="D40" t="s" s="46">
-        <v>84</v>
       </c>
       <c r="E40" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F40" t="s" s="44">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G40" s="51">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="H40" s="52">
-        <v>369.52</v>
-      </c>
-      <c r="I40" s="53">
-        <v>87.5</v>
+        <v>603.75</v>
+      </c>
+      <c r="I40" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J40" t="s" s="48">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K40" t="s" s="49">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="L40" s="0"/>
     </row>
@@ -2953,7 +2974,7 @@
         <v>31</v>
       </c>
       <c r="H41" s="52">
-        <v>31711.65</v>
+        <v>11148.75</v>
       </c>
       <c r="I41" s="53"/>
       <c r="J41" s="48"/>
@@ -2962,38 +2983,36 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="44">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="B42" s="45">
-        <v>0000106938</v>
+        <v>0000106992</v>
       </c>
       <c r="C42" t="s" s="46">
+        <v>90</v>
+      </c>
+      <c r="D42" t="s" s="46">
         <v>83</v>
-      </c>
-      <c r="D42" t="s" s="46">
-        <v>92</v>
       </c>
       <c r="E42" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F42" t="s" s="44">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G42" s="51">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H42" s="52">
-        <v>650.03</v>
-      </c>
-      <c r="I42" s="53">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="I42" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J42" t="s" s="48">
-        <v>94</v>
-      </c>
-      <c r="K42" t="s" s="49">
-        <v>95</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="K42" s="49"/>
       <c r="L42" s="0"/>
     </row>
     <row r="43">
@@ -3007,7 +3026,7 @@
         <v>31</v>
       </c>
       <c r="H43" s="52">
-        <v>10400.48</v>
+        <v>0</v>
       </c>
       <c r="I43" s="53"/>
       <c r="J43" s="48"/>
@@ -3016,37 +3035,37 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="44">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B44" s="45">
-        <v>0000106988</v>
+        <v>0000106923</v>
       </c>
       <c r="C44" t="s" s="46">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E44" t="s" s="47">
         <v>96</v>
       </c>
-      <c r="E44" t="s" s="47">
+      <c r="F44" t="s" s="44">
         <v>97</v>
       </c>
-      <c r="F44" t="s" s="44">
+      <c r="G44" s="51">
+        <v>135</v>
+      </c>
+      <c r="H44" s="52">
+        <v>312.70</v>
+      </c>
+      <c r="I44" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J44" t="s" s="48">
         <v>98</v>
       </c>
-      <c r="G44" s="51">
-        <v>15</v>
-      </c>
-      <c r="H44" s="52">
-        <v>255.96</v>
-      </c>
-      <c r="I44" s="53">
-        <v>7.5</v>
-      </c>
-      <c r="J44" t="s" s="48">
+      <c r="K44" t="s" s="49">
         <v>99</v>
-      </c>
-      <c r="K44" t="s" s="49">
-        <v>100</v>
       </c>
       <c r="L44" s="0"/>
     </row>
@@ -3061,7 +3080,7 @@
         <v>31</v>
       </c>
       <c r="H45" s="52">
-        <v>3839.4</v>
+        <v>42214.5</v>
       </c>
       <c r="I45" s="53"/>
       <c r="J45" s="48"/>
@@ -3070,28 +3089,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="44">
+        <v>100</v>
+      </c>
+      <c r="B46" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C46" t="s" s="46">
         <v>101</v>
       </c>
-      <c r="B46" s="45">
-        <v>0000106974</v>
-      </c>
-      <c r="C46" t="s" s="46">
-        <v>44</v>
-      </c>
       <c r="D46" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E46" t="s" s="47">
         <v>96</v>
-      </c>
-      <c r="E46" t="s" s="47">
-        <v>97</v>
       </c>
       <c r="F46" t="s" s="44">
         <v>102</v>
       </c>
       <c r="G46" s="51">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="H46" s="52">
-        <v>635.00</v>
+        <v>964.74</v>
       </c>
       <c r="I46" t="s" s="53">
         <v>18</v>
@@ -3100,236 +3119,256 @@
         <v>103</v>
       </c>
       <c r="K46" t="s" s="49">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="L46" s="0"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="44">
+        <v>100</v>
+      </c>
+      <c r="B47" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C47" t="s" s="46">
         <v>101</v>
       </c>
-      <c r="B47" s="45">
-        <v>0000106974</v>
-      </c>
-      <c r="C47" t="s" s="46">
-        <v>44</v>
-      </c>
       <c r="D47" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E47" t="s" s="47">
         <v>96</v>
       </c>
-      <c r="E47" t="s" s="47">
-        <v>97</v>
-      </c>
       <c r="F47" t="s" s="44">
+        <v>105</v>
+      </c>
+      <c r="G47" s="51">
+        <v>25</v>
+      </c>
+      <c r="H47" s="52">
+        <v>281.38</v>
+      </c>
+      <c r="I47" s="53">
+        <v>6.25</v>
+      </c>
+      <c r="J47" t="s" s="48">
+        <v>106</v>
+      </c>
+      <c r="K47" t="s" s="49">
         <v>104</v>
       </c>
-      <c r="G47" s="51">
-        <v>9</v>
-      </c>
-      <c r="H47" s="52">
-        <v>603.75</v>
-      </c>
-      <c r="I47" t="s" s="53">
+      <c r="L47" s="0"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="44">
+        <v>100</v>
+      </c>
+      <c r="B48" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C48" t="s" s="46">
+        <v>101</v>
+      </c>
+      <c r="D48" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E48" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F48" t="s" s="44">
+        <v>107</v>
+      </c>
+      <c r="G48" s="51">
+        <v>15</v>
+      </c>
+      <c r="H48" s="52">
+        <v>369.81</v>
+      </c>
+      <c r="I48" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J47" t="s" s="48">
-        <v>105</v>
-      </c>
-      <c r="K47" t="s" s="49">
-        <v>66</v>
-      </c>
-      <c r="L47" s="0"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="44"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="44"/>
-      <c r="G48" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H48" s="52">
-        <v>11148.75</v>
-      </c>
-      <c r="I48" s="53"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="49"/>
+      <c r="J48" t="s" s="48">
+        <v>108</v>
+      </c>
+      <c r="K48" t="s" s="49">
+        <v>104</v>
+      </c>
       <c r="L48" s="0"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="44">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="B49" s="45">
-        <v>0000106992</v>
+        <v>0000106869</v>
       </c>
       <c r="C49" t="s" s="46">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E49" t="s" s="47">
         <v>96</v>
       </c>
-      <c r="E49" t="s" s="47">
-        <v>97</v>
-      </c>
       <c r="F49" t="s" s="44">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G49" s="51">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="H49" s="52">
-        <v>0</v>
+        <v>281.38</v>
       </c>
       <c r="I49" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J49" t="s" s="48">
-        <v>108</v>
-      </c>
-      <c r="K49" s="49"/>
+        <v>110</v>
+      </c>
+      <c r="K49" t="s" s="49">
+        <v>104</v>
+      </c>
       <c r="L49" s="0"/>
     </row>
     <row r="50">
-      <c r="A50" s="44"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="44"/>
-      <c r="G50" t="s" s="51">
+      <c r="A50" t="s" s="44">
+        <v>100</v>
+      </c>
+      <c r="B50" s="45">
+        <v>0000106869</v>
+      </c>
+      <c r="C50" t="s" s="46">
+        <v>101</v>
+      </c>
+      <c r="D50" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E50" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s" s="44">
+        <v>111</v>
+      </c>
+      <c r="G50" s="51">
+        <v>2</v>
+      </c>
+      <c r="H50" s="52">
+        <v>369.81</v>
+      </c>
+      <c r="I50" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J50" t="s" s="48">
+        <v>112</v>
+      </c>
+      <c r="K50" t="s" s="49">
+        <v>104</v>
+      </c>
+      <c r="L50" s="0"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="44"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="44"/>
+      <c r="G51" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H50" s="52">
-        <v>0</v>
-      </c>
-      <c r="I50" s="53"/>
-      <c r="J50" s="48"/>
-      <c r="K50" s="49"/>
-      <c r="L50" s="0"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="44">
-        <v>109</v>
-      </c>
-      <c r="B51" s="45">
-        <v>0000106987</v>
-      </c>
-      <c r="C51" t="s" s="46">
-        <v>56</v>
-      </c>
-      <c r="D51" t="s" s="46">
-        <v>110</v>
-      </c>
-      <c r="E51" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F51" t="s" s="44">
-        <v>111</v>
-      </c>
-      <c r="G51" s="51">
-        <v>30</v>
-      </c>
       <c r="H51" s="52">
-        <v>25.06</v>
-      </c>
-      <c r="I51" t="s" s="53">
+        <v>74421.27</v>
+      </c>
+      <c r="I51" s="53"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="49"/>
+      <c r="L51" s="0"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="44">
+        <v>113</v>
+      </c>
+      <c r="B52" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C52" t="s" s="46">
+        <v>114</v>
+      </c>
+      <c r="D52" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E52" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F52" t="s" s="44">
+        <v>115</v>
+      </c>
+      <c r="G52" s="51">
+        <v>5</v>
+      </c>
+      <c r="H52" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I52" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J51" t="s" s="48">
-        <v>112</v>
-      </c>
-      <c r="K51" t="s" s="49">
-        <v>66</v>
-      </c>
-      <c r="L51" s="0"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="44"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="44"/>
-      <c r="G52" t="s" s="51">
+      <c r="J52" t="s" s="48">
+        <v>116</v>
+      </c>
+      <c r="K52" t="s" s="49">
+        <v>117</v>
+      </c>
+      <c r="L52" s="0"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="44"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="44"/>
+      <c r="G53" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H52" s="52">
-        <v>751.8</v>
-      </c>
-      <c r="I52" s="53"/>
-      <c r="J52" s="48"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="0"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="44">
-        <v>113</v>
-      </c>
-      <c r="B53" s="45">
-        <v>0000106976</v>
-      </c>
-      <c r="C53" t="s" s="46">
-        <v>114</v>
-      </c>
-      <c r="D53" t="s" s="46">
-        <v>115</v>
-      </c>
-      <c r="E53" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F53" t="s" s="44">
-        <v>116</v>
-      </c>
-      <c r="G53" s="51">
-        <v>1</v>
-      </c>
       <c r="H53" s="52">
-        <v>35.08</v>
-      </c>
-      <c r="I53" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J53" t="s" s="48">
-        <v>117</v>
-      </c>
-      <c r="K53" t="s" s="49">
-        <v>66</v>
-      </c>
+        <v>11250</v>
+      </c>
+      <c r="I53" s="53"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="49"/>
       <c r="L53" s="0"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="44">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B54" s="45">
-        <v>0000106976</v>
+        <v>0000106980</v>
       </c>
       <c r="C54" t="s" s="46">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s" s="46">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E54" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F54" t="s" s="44">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G54" s="51">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H54" s="52">
-        <v>624.51</v>
+        <v>530.47</v>
       </c>
       <c r="I54" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J54" t="s" s="48">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K54" t="s" s="49">
         <v>66</v>
@@ -3337,56 +3376,74 @@
       <c r="L54" s="0"/>
     </row>
     <row r="55">
-      <c r="A55" s="44"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="44"/>
-      <c r="G55" t="s" s="51">
-        <v>31</v>
+      <c r="A55" t="s" s="44">
+        <v>118</v>
+      </c>
+      <c r="B55" s="45">
+        <v>0000106980</v>
+      </c>
+      <c r="C55" t="s" s="46">
+        <v>119</v>
+      </c>
+      <c r="D55" t="s" s="46">
+        <v>95</v>
+      </c>
+      <c r="E55" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F55" t="s" s="44">
+        <v>122</v>
+      </c>
+      <c r="G55" s="51">
+        <v>200</v>
       </c>
       <c r="H55" s="52">
-        <v>659.59</v>
-      </c>
-      <c r="I55" s="53"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="49"/>
+        <v>13.08</v>
+      </c>
+      <c r="I55" s="53">
+        <v>6.6</v>
+      </c>
+      <c r="J55" t="s" s="48">
+        <v>123</v>
+      </c>
+      <c r="K55" t="s" s="49">
+        <v>66</v>
+      </c>
       <c r="L55" s="0"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="44">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="B56" s="45">
-        <v>0000106964</v>
+        <v>0000106980</v>
       </c>
       <c r="C56" t="s" s="46">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s" s="46">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="E56" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F56" t="s" s="44">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G56" s="51">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H56" s="52">
-        <v>11.33</v>
-      </c>
-      <c r="I56" s="53">
-        <v>3.3</v>
+        <v>12.73</v>
+      </c>
+      <c r="I56" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J56" t="s" s="48">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K56" t="s" s="49">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="L56" s="0"/>
     </row>
@@ -3401,7 +3458,7 @@
         <v>31</v>
       </c>
       <c r="H57" s="52">
-        <v>1133</v>
+        <v>32958.5</v>
       </c>
       <c r="I57" s="53"/>
       <c r="J57" s="48"/>
@@ -3410,37 +3467,37 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="44">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B58" s="45">
-        <v>0000106965</v>
+        <v>0000107000</v>
       </c>
       <c r="C58" t="s" s="46">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="D58" t="s" s="46">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E58" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F58" t="s" s="44">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G58" s="51">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H58" s="52">
-        <v>375.19</v>
+        <v>412.38</v>
       </c>
       <c r="I58" s="53">
-        <v>50</v>
+        <v>6.25</v>
       </c>
       <c r="J58" t="s" s="48">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="K58" t="s" s="49">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="L58" s="0"/>
     </row>
@@ -3455,7 +3512,7 @@
         <v>31</v>
       </c>
       <c r="H59" s="52">
-        <v>15007.6</v>
+        <v>2061.9</v>
       </c>
       <c r="I59" s="53"/>
       <c r="J59" s="48"/>
@@ -3464,37 +3521,37 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="44">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="B60" s="45">
-        <v>0000106923</v>
+        <v>0000106924</v>
       </c>
       <c r="C60" t="s" s="46">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D60" t="s" s="46">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E60" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F60" t="s" s="44">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G60" s="51">
+        <v>180</v>
+      </c>
+      <c r="H60" s="52">
+        <v>285.87</v>
+      </c>
+      <c r="I60" s="53">
+        <v>225</v>
+      </c>
+      <c r="J60" t="s" s="48">
+        <v>134</v>
+      </c>
+      <c r="K60" t="s" s="49">
         <v>135</v>
-      </c>
-      <c r="H60" s="52">
-        <v>312.70</v>
-      </c>
-      <c r="I60" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J60" t="s" s="48">
-        <v>127</v>
-      </c>
-      <c r="K60" t="s" s="49">
-        <v>128</v>
       </c>
       <c r="L60" s="0"/>
     </row>
@@ -3509,7 +3566,7 @@
         <v>31</v>
       </c>
       <c r="H61" s="52">
-        <v>42214.5</v>
+        <v>51456.6</v>
       </c>
       <c r="I61" s="53"/>
       <c r="J61" s="48"/>
@@ -3518,397 +3575,379 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="44">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B62" s="45">
-        <v>0000106869</v>
+        <v>0000106962</v>
       </c>
       <c r="C62" t="s" s="46">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s" s="46">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E62" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F62" t="s" s="44">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G62" s="51">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H62" s="52">
-        <v>951.36</v>
+        <v>1691.23</v>
       </c>
       <c r="I62" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J62" t="s" s="48">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K62" t="s" s="49">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="L62" s="0"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="44">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B63" s="45">
-        <v>0000106869</v>
+        <v>0000106962</v>
       </c>
       <c r="C63" t="s" s="46">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s" s="46">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E63" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F63" t="s" s="44">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G63" s="51">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H63" s="52">
-        <v>277.48</v>
-      </c>
-      <c r="I63" s="53">
-        <v>6.25</v>
+        <v>636.22</v>
+      </c>
+      <c r="I63" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J63" t="s" s="48">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="K63" t="s" s="49">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="L63" s="0"/>
     </row>
     <row r="64">
-      <c r="A64" t="s" s="44">
-        <v>129</v>
-      </c>
-      <c r="B64" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C64" t="s" s="46">
-        <v>130</v>
-      </c>
-      <c r="D64" t="s" s="46">
-        <v>120</v>
-      </c>
-      <c r="E64" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F64" t="s" s="44">
-        <v>136</v>
-      </c>
-      <c r="G64" s="51">
-        <v>15</v>
+      <c r="A64" s="44"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="46"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="44"/>
+      <c r="G64" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H64" s="52">
-        <v>364.68</v>
-      </c>
-      <c r="I64" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J64" t="s" s="48">
-        <v>137</v>
-      </c>
-      <c r="K64" t="s" s="49">
-        <v>133</v>
-      </c>
+        <v>11637.25</v>
+      </c>
+      <c r="I64" s="53"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="49"/>
       <c r="L64" s="0"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="44">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="B65" s="45">
-        <v>0000106869</v>
+        <v>0000106959</v>
       </c>
       <c r="C65" t="s" s="46">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="D65" t="s" s="46">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E65" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F65" t="s" s="44">
+        <v>145</v>
+      </c>
+      <c r="G65" s="51">
+        <v>52</v>
+      </c>
+      <c r="H65" s="52">
+        <v>472.59</v>
+      </c>
+      <c r="I65" s="53">
+        <v>52</v>
+      </c>
+      <c r="J65" t="s" s="48">
+        <v>146</v>
+      </c>
+      <c r="K65" t="s" s="49">
+        <v>147</v>
+      </c>
+      <c r="L65" s="0"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="44"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="46"/>
+      <c r="D66" s="46"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="44"/>
+      <c r="G66" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H66" s="52">
+        <v>24574.68</v>
+      </c>
+      <c r="I66" s="53"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="49"/>
+      <c r="L66" s="0"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B67" s="45">
+        <v>0000106960</v>
+      </c>
+      <c r="C67" t="s" s="46">
+        <v>144</v>
+      </c>
+      <c r="D67" t="s" s="46">
         <v>138</v>
       </c>
-      <c r="G65" s="51">
-        <v>80</v>
-      </c>
-      <c r="H65" s="52">
-        <v>277.48</v>
-      </c>
-      <c r="I65" t="s" s="53">
+      <c r="E67" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F67" t="s" s="44">
+        <v>148</v>
+      </c>
+      <c r="G67" s="51">
+        <v>156</v>
+      </c>
+      <c r="H67" s="52">
+        <v>367.17</v>
+      </c>
+      <c r="I67" s="53">
+        <v>156</v>
+      </c>
+      <c r="J67" t="s" s="48">
+        <v>52</v>
+      </c>
+      <c r="K67" t="s" s="49">
+        <v>147</v>
+      </c>
+      <c r="L67" s="0"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="44"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="44"/>
+      <c r="G68" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H68" s="52">
+        <v>57278.52</v>
+      </c>
+      <c r="I68" s="53"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="49"/>
+      <c r="L68" s="0"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B69" s="45">
+        <v>0000106961</v>
+      </c>
+      <c r="C69" t="s" s="46">
+        <v>144</v>
+      </c>
+      <c r="D69" t="s" s="46">
+        <v>138</v>
+      </c>
+      <c r="E69" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F69" t="s" s="44">
+        <v>149</v>
+      </c>
+      <c r="G69" s="51">
+        <v>52</v>
+      </c>
+      <c r="H69" s="52">
+        <v>510.62</v>
+      </c>
+      <c r="I69" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J65" t="s" s="48">
-        <v>139</v>
-      </c>
-      <c r="K65" t="s" s="49">
-        <v>133</v>
-      </c>
-      <c r="L65" s="0"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="44">
-        <v>129</v>
-      </c>
-      <c r="B66" s="45">
-        <v>0000106869</v>
-      </c>
-      <c r="C66" t="s" s="46">
-        <v>130</v>
-      </c>
-      <c r="D66" t="s" s="46">
-        <v>120</v>
-      </c>
-      <c r="E66" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F66" t="s" s="44">
-        <v>140</v>
-      </c>
-      <c r="G66" s="51">
-        <v>2</v>
-      </c>
-      <c r="H66" s="52">
-        <v>364.68</v>
-      </c>
-      <c r="I66" t="s" s="53">
+      <c r="J69" t="s" s="48">
+        <v>150</v>
+      </c>
+      <c r="K69" t="s" s="49">
+        <v>147</v>
+      </c>
+      <c r="L69" s="0"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="44"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="44"/>
+      <c r="G70" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H70" s="52">
+        <v>26552.24</v>
+      </c>
+      <c r="I70" s="53"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="49"/>
+      <c r="L70" s="0"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B71" s="45">
+        <v>0000106940</v>
+      </c>
+      <c r="C71" t="s" s="46">
+        <v>151</v>
+      </c>
+      <c r="D71" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E71" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F71" t="s" s="44">
+        <v>153</v>
+      </c>
+      <c r="G71" s="51">
+        <v>70</v>
+      </c>
+      <c r="H71" s="52">
+        <v>370.52</v>
+      </c>
+      <c r="I71" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J71" t="s" s="48">
+        <v>154</v>
+      </c>
+      <c r="K71" t="s" s="49">
+        <v>155</v>
+      </c>
+      <c r="L71" s="0"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="44"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="47"/>
+      <c r="F72" s="44"/>
+      <c r="G72" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H72" s="52">
+        <v>25936.4</v>
+      </c>
+      <c r="I72" s="53"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="49"/>
+      <c r="L72" s="0"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B73" s="45">
+        <v>0000106941</v>
+      </c>
+      <c r="C73" t="s" s="46">
+        <v>151</v>
+      </c>
+      <c r="D73" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E73" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F73" t="s" s="44">
+        <v>156</v>
+      </c>
+      <c r="G73" s="51">
+        <v>50</v>
+      </c>
+      <c r="H73" s="52">
+        <v>4.44</v>
+      </c>
+      <c r="I73" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J66" t="s" s="48">
-        <v>141</v>
-      </c>
-      <c r="K66" t="s" s="49">
-        <v>133</v>
-      </c>
-      <c r="L66" s="0"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="44"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="46"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="44"/>
-      <c r="G67" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H67" s="52">
-        <v>73389.36</v>
-      </c>
-      <c r="I67" s="53"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="49"/>
-      <c r="L67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B68" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C68" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D68" t="s" s="46">
-        <v>120</v>
-      </c>
-      <c r="E68" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F68" t="s" s="44">
-        <v>144</v>
-      </c>
-      <c r="G68" s="51">
-        <v>5</v>
-      </c>
-      <c r="H68" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I68" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J68" t="s" s="48">
-        <v>145</v>
-      </c>
-      <c r="K68" t="s" s="49">
-        <v>146</v>
-      </c>
-      <c r="L68" s="0"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="44"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="44"/>
-      <c r="G69" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H69" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I69" s="53"/>
-      <c r="J69" s="48"/>
-      <c r="K69" s="49"/>
-      <c r="L69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B70" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C70" t="s" s="46">
-        <v>148</v>
-      </c>
-      <c r="D70" t="s" s="46">
-        <v>120</v>
-      </c>
-      <c r="E70" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F70" t="s" s="44">
-        <v>149</v>
-      </c>
-      <c r="G70" s="51">
-        <v>2</v>
-      </c>
-      <c r="H70" s="52">
-        <v>609.3</v>
-      </c>
-      <c r="I70" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J70" t="s" s="48">
-        <v>150</v>
-      </c>
-      <c r="K70" t="s" s="49">
-        <v>151</v>
-      </c>
-      <c r="L70" s="0"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="44"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="44"/>
-      <c r="G71" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H71" s="52">
-        <v>1218.6</v>
-      </c>
-      <c r="I71" s="53"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="49"/>
-      <c r="L71" s="0"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B72" s="45">
-        <v>0000106991</v>
-      </c>
-      <c r="C72" t="s" s="46">
-        <v>152</v>
-      </c>
-      <c r="D72" t="s" s="46">
-        <v>153</v>
-      </c>
-      <c r="E72" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F72" t="s" s="44">
-        <v>154</v>
-      </c>
-      <c r="G72" s="51">
-        <v>100</v>
-      </c>
-      <c r="H72" s="52">
-        <v>12.99</v>
-      </c>
-      <c r="I72" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J72" t="s" s="48">
-        <v>155</v>
-      </c>
-      <c r="K72" t="s" s="49">
-        <v>66</v>
-      </c>
-      <c r="L72" s="0"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="44"/>
-      <c r="B73" s="45"/>
-      <c r="C73" s="46"/>
-      <c r="D73" s="46"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="44"/>
-      <c r="G73" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H73" s="52">
-        <v>1299</v>
-      </c>
-      <c r="I73" s="53"/>
-      <c r="J73" s="48"/>
-      <c r="K73" s="49"/>
+      <c r="J73" t="s" s="48">
+        <v>157</v>
+      </c>
+      <c r="K73" t="s" s="49">
+        <v>158</v>
+      </c>
       <c r="L73" s="0"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="44">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" s="45">
-        <v>0000106924</v>
+        <v>0000106941</v>
       </c>
       <c r="C74" t="s" s="46">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s" s="46">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E74" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F74" t="s" s="44">
+        <v>122</v>
+      </c>
+      <c r="G74" s="51">
+        <v>100</v>
+      </c>
+      <c r="H74" s="52">
+        <v>11.16</v>
+      </c>
+      <c r="I74" s="53">
+        <v>3.3</v>
+      </c>
+      <c r="J74" t="s" s="48">
+        <v>123</v>
+      </c>
+      <c r="K74" t="s" s="49">
         <v>158</v>
-      </c>
-      <c r="G74" s="51">
-        <v>180</v>
-      </c>
-      <c r="H74" s="52">
-        <v>285.87</v>
-      </c>
-      <c r="I74" s="53">
-        <v>225</v>
-      </c>
-      <c r="J74" t="s" s="48">
-        <v>159</v>
-      </c>
-      <c r="K74" t="s" s="49">
-        <v>160</v>
       </c>
       <c r="L74" s="0"/>
     </row>
@@ -3923,7 +3962,7 @@
         <v>31</v>
       </c>
       <c r="H75" s="52">
-        <v>51456.6</v>
+        <v>1338</v>
       </c>
       <c r="I75" s="53"/>
       <c r="J75" s="48"/>
@@ -3932,226 +3971,262 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="44">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="B76" s="45">
-        <v>0000106962</v>
+        <v>0000106942</v>
       </c>
       <c r="C76" t="s" s="46">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D76" t="s" s="46">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E76" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F76" t="s" s="44">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G76" s="51">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H76" s="52">
-        <v>1691.23</v>
+        <v>228.21</v>
       </c>
       <c r="I76" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J76" t="s" s="48">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="K76" t="s" s="49">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L76" s="0"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B77" s="45">
+        <v>0000106942</v>
+      </c>
+      <c r="C77" t="s" s="46">
+        <v>151</v>
+      </c>
+      <c r="D77" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E77" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F77" t="s" s="44">
         <v>161</v>
       </c>
-      <c r="B77" s="45">
-        <v>0000106962</v>
-      </c>
-      <c r="C77" t="s" s="46">
+      <c r="G77" s="51">
+        <v>50</v>
+      </c>
+      <c r="H77" s="52">
+        <v>213.41</v>
+      </c>
+      <c r="I77" s="53">
+        <v>25</v>
+      </c>
+      <c r="J77" t="s" s="48">
         <v>162</v>
       </c>
-      <c r="D77" t="s" s="46">
+      <c r="K77" t="s" s="49">
+        <v>158</v>
+      </c>
+      <c r="L77" s="0"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B78" s="45">
+        <v>0000106942</v>
+      </c>
+      <c r="C78" t="s" s="46">
+        <v>151</v>
+      </c>
+      <c r="D78" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E78" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F78" t="s" s="44">
         <v>163</v>
       </c>
-      <c r="E77" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F77" t="s" s="44">
+      <c r="G78" s="51">
+        <v>50</v>
+      </c>
+      <c r="H78" s="52">
+        <v>30.65</v>
+      </c>
+      <c r="I78" s="53">
+        <v>3.35</v>
+      </c>
+      <c r="J78" t="s" s="48">
+        <v>164</v>
+      </c>
+      <c r="K78" t="s" s="49">
+        <v>158</v>
+      </c>
+      <c r="L78" s="0"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="44"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="46"/>
+      <c r="D79" s="46"/>
+      <c r="E79" s="47"/>
+      <c r="F79" s="44"/>
+      <c r="G79" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H79" s="52">
+        <v>23613.5</v>
+      </c>
+      <c r="I79" s="53"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="49"/>
+      <c r="L79" s="0"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="44">
+        <v>165</v>
+      </c>
+      <c r="B80" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C80" t="s" s="46">
+        <v>166</v>
+      </c>
+      <c r="D80" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E80" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F80" t="s" s="44">
         <v>167</v>
       </c>
-      <c r="G77" s="51">
-        <v>5</v>
-      </c>
-      <c r="H77" s="52">
-        <v>636.22</v>
-      </c>
-      <c r="I77" t="s" s="53">
+      <c r="G80" s="51">
+        <v>1</v>
+      </c>
+      <c r="H80" s="52">
+        <v>1245.55</v>
+      </c>
+      <c r="I80" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J77" t="s" s="48">
+      <c r="J80" t="s" s="48">
         <v>168</v>
       </c>
-      <c r="K77" t="s" s="49">
-        <v>166</v>
-      </c>
-      <c r="L77" s="0"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="44"/>
-      <c r="B78" s="45"/>
-      <c r="C78" s="46"/>
-      <c r="D78" s="46"/>
-      <c r="E78" s="47"/>
-      <c r="F78" s="44"/>
-      <c r="G78" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H78" s="52">
-        <v>11637.25</v>
-      </c>
-      <c r="I78" s="53"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="49"/>
-      <c r="L78" s="0"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B79" s="45">
-        <v>0000106959</v>
-      </c>
-      <c r="C79" t="s" s="46">
+      <c r="K80" t="s" s="49">
         <v>169</v>
       </c>
-      <c r="D79" t="s" s="46">
-        <v>163</v>
-      </c>
-      <c r="E79" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F79" t="s" s="44">
-        <v>170</v>
-      </c>
-      <c r="G79" s="51">
-        <v>52</v>
-      </c>
-      <c r="H79" s="52">
-        <v>472.59</v>
-      </c>
-      <c r="I79" s="53">
-        <v>52</v>
-      </c>
-      <c r="J79" t="s" s="48">
-        <v>171</v>
-      </c>
-      <c r="K79" t="s" s="49">
-        <v>172</v>
-      </c>
-      <c r="L79" s="0"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="44"/>
-      <c r="B80" s="45"/>
-      <c r="C80" s="46"/>
-      <c r="D80" s="46"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="44"/>
-      <c r="G80" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H80" s="52">
-        <v>24574.68</v>
-      </c>
-      <c r="I80" s="53"/>
-      <c r="J80" s="48"/>
-      <c r="K80" s="49"/>
       <c r="L80" s="0"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="44">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B81" s="45">
-        <v>0000106960</v>
+        <v>0000106977</v>
       </c>
       <c r="C81" t="s" s="46">
+        <v>166</v>
+      </c>
+      <c r="D81" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E81" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F81" t="s" s="44">
+        <v>170</v>
+      </c>
+      <c r="G81" s="51">
+        <v>1</v>
+      </c>
+      <c r="H81" s="52">
+        <v>1281.13</v>
+      </c>
+      <c r="I81" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J81" t="s" s="48">
+        <v>171</v>
+      </c>
+      <c r="K81" t="s" s="49">
         <v>169</v>
       </c>
-      <c r="D81" t="s" s="46">
-        <v>163</v>
-      </c>
-      <c r="E81" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F81" t="s" s="44">
+      <c r="L81" s="0"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="44">
+        <v>165</v>
+      </c>
+      <c r="B82" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C82" t="s" s="46">
+        <v>166</v>
+      </c>
+      <c r="D82" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E82" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F82" t="s" s="44">
+        <v>172</v>
+      </c>
+      <c r="G82" s="51">
+        <v>1</v>
+      </c>
+      <c r="H82" s="52">
+        <v>1447.75</v>
+      </c>
+      <c r="I82" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J82" t="s" s="48">
         <v>173</v>
       </c>
-      <c r="G81" s="51">
-        <v>156</v>
-      </c>
-      <c r="H81" s="52">
-        <v>367.17</v>
-      </c>
-      <c r="I81" s="53">
-        <v>156</v>
-      </c>
-      <c r="J81" t="s" s="48">
-        <v>52</v>
-      </c>
-      <c r="K81" t="s" s="49">
-        <v>172</v>
-      </c>
-      <c r="L81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="44"/>
-      <c r="B82" s="45"/>
-      <c r="C82" s="46"/>
-      <c r="D82" s="46"/>
-      <c r="E82" s="47"/>
-      <c r="F82" s="44"/>
-      <c r="G82" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H82" s="52">
-        <v>57278.52</v>
-      </c>
-      <c r="I82" s="53"/>
-      <c r="J82" s="48"/>
-      <c r="K82" s="49"/>
+      <c r="K82" t="s" s="49">
+        <v>169</v>
+      </c>
       <c r="L82" s="0"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="44">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B83" s="45">
-        <v>0000106961</v>
+        <v>0000106977</v>
       </c>
       <c r="C83" t="s" s="46">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D83" t="s" s="46">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E83" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F83" t="s" s="44">
         <v>174</v>
       </c>
       <c r="G83" s="51">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="H83" s="52">
-        <v>510.62</v>
+        <v>161.76</v>
       </c>
       <c r="I83" t="s" s="53">
         <v>18</v>
@@ -4160,991 +4235,991 @@
         <v>175</v>
       </c>
       <c r="K83" t="s" s="49">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L83" s="0"/>
     </row>
     <row r="84">
-      <c r="A84" s="44"/>
-      <c r="B84" s="45"/>
-      <c r="C84" s="46"/>
-      <c r="D84" s="46"/>
-      <c r="E84" s="47"/>
-      <c r="F84" s="44"/>
-      <c r="G84" t="s" s="51">
-        <v>31</v>
+      <c r="A84" t="s" s="44">
+        <v>165</v>
+      </c>
+      <c r="B84" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C84" t="s" s="46">
+        <v>166</v>
+      </c>
+      <c r="D84" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E84" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F84" t="s" s="44">
+        <v>176</v>
+      </c>
+      <c r="G84" s="51">
+        <v>2</v>
       </c>
       <c r="H84" s="52">
-        <v>26552.24</v>
-      </c>
-      <c r="I84" s="53"/>
-      <c r="J84" s="48"/>
-      <c r="K84" s="49"/>
+        <v>143.96</v>
+      </c>
+      <c r="I84" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J84" t="s" s="48">
+        <v>177</v>
+      </c>
+      <c r="K84" t="s" s="49">
+        <v>169</v>
+      </c>
       <c r="L84" s="0"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="44">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="B85" s="45">
-        <v>0000106940</v>
+        <v>0000106977</v>
       </c>
       <c r="C85" t="s" s="46">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="D85" t="s" s="46">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E85" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F85" t="s" s="44">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G85" s="51">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H85" s="52">
-        <v>563.86</v>
-      </c>
-      <c r="I85" s="53">
-        <v>48</v>
+        <v>655.12</v>
+      </c>
+      <c r="I85" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J85" t="s" s="48">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K85" t="s" s="49">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="L85" s="0"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="44">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="B86" s="45">
-        <v>0000106940</v>
+        <v>0000106977</v>
       </c>
       <c r="C86" t="s" s="46">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="D86" t="s" s="46">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E86" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F86" t="s" s="44">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G86" s="51">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="H86" s="52">
-        <v>369.52</v>
-      </c>
-      <c r="I86" s="53">
-        <v>87.5</v>
+        <v>380.13</v>
+      </c>
+      <c r="I86" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J86" t="s" s="48">
+        <v>181</v>
+      </c>
+      <c r="K86" t="s" s="49">
+        <v>169</v>
+      </c>
+      <c r="L86" s="0"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="44">
+        <v>165</v>
+      </c>
+      <c r="B87" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C87" t="s" s="46">
+        <v>166</v>
+      </c>
+      <c r="D87" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E87" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F87" t="s" s="44">
         <v>91</v>
       </c>
-      <c r="K86" t="s" s="49">
-        <v>179</v>
-      </c>
-      <c r="L86" s="0"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="44"/>
-      <c r="B87" s="45"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="44"/>
-      <c r="G87" t="s" s="51">
-        <v>31</v>
+      <c r="G87" s="51">
+        <v>5</v>
       </c>
       <c r="H87" s="52">
-        <v>34888.16</v>
-      </c>
-      <c r="I87" s="53"/>
-      <c r="J87" s="48"/>
-      <c r="K87" s="49"/>
+        <v>638.95</v>
+      </c>
+      <c r="I87" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J87" t="s" s="48">
+        <v>92</v>
+      </c>
+      <c r="K87" t="s" s="49">
+        <v>169</v>
+      </c>
       <c r="L87" s="0"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="44">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="B88" s="45">
-        <v>0000106941</v>
+        <v>0000106977</v>
       </c>
       <c r="C88" t="s" s="46">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s" s="46">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="E88" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F88" t="s" s="44">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G88" s="51">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H88" s="52">
-        <v>4.44</v>
+        <v>638.95</v>
       </c>
       <c r="I88" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J88" t="s" s="48">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K88" t="s" s="49">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="L88" s="0"/>
     </row>
     <row r="89">
-      <c r="A89" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B89" s="45">
-        <v>0000106941</v>
-      </c>
-      <c r="C89" t="s" s="46">
-        <v>83</v>
-      </c>
-      <c r="D89" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E89" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F89" t="s" s="44">
-        <v>121</v>
-      </c>
-      <c r="G89" s="51">
-        <v>100</v>
+      <c r="A89" s="44"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="46"/>
+      <c r="D89" s="46"/>
+      <c r="E89" s="47"/>
+      <c r="F89" s="44"/>
+      <c r="G89" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H89" s="52">
-        <v>11.16</v>
-      </c>
-      <c r="I89" s="53">
-        <v>3.3</v>
-      </c>
-      <c r="J89" t="s" s="48">
-        <v>122</v>
-      </c>
-      <c r="K89" t="s" s="49">
-        <v>179</v>
-      </c>
+        <v>11258.42</v>
+      </c>
+      <c r="I89" s="53"/>
+      <c r="J89" s="48"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="0"/>
     </row>
     <row r="90">
-      <c r="A90" s="44"/>
-      <c r="B90" s="45"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="47"/>
-      <c r="F90" s="44"/>
-      <c r="G90" t="s" s="51">
+      <c r="A90" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B90" s="45">
+        <v>0000106994</v>
+      </c>
+      <c r="C90" t="s" s="46">
+        <v>184</v>
+      </c>
+      <c r="D90" t="s" s="46">
+        <v>152</v>
+      </c>
+      <c r="E90" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F90" t="s" s="44">
+        <v>185</v>
+      </c>
+      <c r="G90" s="51">
+        <v>500</v>
+      </c>
+      <c r="H90" s="52">
+        <v>0</v>
+      </c>
+      <c r="I90" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J90" t="s" s="48">
+        <v>186</v>
+      </c>
+      <c r="K90" t="s" s="49">
+        <v>187</v>
+      </c>
+      <c r="L90" s="0"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="44"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="47"/>
+      <c r="F91" t="s" s="44">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H90" s="52">
-        <v>1338</v>
-      </c>
-      <c r="I90" s="53"/>
-      <c r="J90" s="48"/>
-      <c r="K90" s="49"/>
-      <c r="L90" s="0"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B91" s="45">
-        <v>0000106942</v>
-      </c>
-      <c r="C91" t="s" s="46">
-        <v>83</v>
-      </c>
-      <c r="D91" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E91" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F91" t="s" s="44">
-        <v>182</v>
-      </c>
-      <c r="G91" s="51">
-        <v>50</v>
-      </c>
       <c r="H91" s="52">
-        <v>228.21</v>
-      </c>
-      <c r="I91" t="s" s="53">
+        <v>0</v>
+      </c>
+      <c r="I91" s="53" t="s">
         <v>18</v>
       </c>
       <c r="J91" t="s" s="48">
-        <v>183</v>
-      </c>
-      <c r="K91" t="s" s="49">
-        <v>179</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K91" s="49"/>
       <c r="L91" s="0"/>
     </row>
     <row r="92">
-      <c r="A92" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B92" s="45">
-        <v>0000106942</v>
-      </c>
-      <c r="C92" t="s" s="46">
-        <v>83</v>
-      </c>
-      <c r="D92" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E92" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F92" t="s" s="44">
-        <v>184</v>
-      </c>
-      <c r="G92" s="51">
-        <v>50</v>
+      <c r="A92" s="44"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="46"/>
+      <c r="D92" s="46"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="G92" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H92" s="52">
-        <v>213.41</v>
+        <v>407700.53</v>
       </c>
       <c r="I92" s="53">
-        <v>25</v>
-      </c>
-      <c r="J92" t="s" s="48">
-        <v>185</v>
-      </c>
-      <c r="K92" t="s" s="49">
-        <v>179</v>
-      </c>
+        <v>571.25</v>
+      </c>
+      <c r="J92" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="K92" s="49"/>
       <c r="L92" s="0"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="44">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="B93" s="45">
-        <v>0000106942</v>
+        <v>0000106893</v>
       </c>
       <c r="C93" t="s" s="46">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="D93" t="s" s="46">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E93" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F93" t="s" s="44">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G93" s="51">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H93" s="52">
-        <v>30.65</v>
-      </c>
-      <c r="I93" s="53">
-        <v>3.35</v>
+        <v>3408.55</v>
+      </c>
+      <c r="I93" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J93" t="s" s="48">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K93" t="s" s="49">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="L93" s="0"/>
     </row>
     <row r="94">
-      <c r="A94" s="44"/>
-      <c r="B94" s="45"/>
-      <c r="C94" s="46"/>
-      <c r="D94" s="46"/>
-      <c r="E94" s="47"/>
-      <c r="F94" s="44"/>
-      <c r="G94" t="s" s="51">
+      <c r="A94" t="s" s="44">
+        <v>188</v>
+      </c>
+      <c r="B94" s="45">
+        <v>0000106893</v>
+      </c>
+      <c r="C94" t="s" s="46">
+        <v>189</v>
+      </c>
+      <c r="D94" t="s" s="46">
+        <v>190</v>
+      </c>
+      <c r="E94" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F94" t="s" s="44">
+        <v>196</v>
+      </c>
+      <c r="G94" s="51">
+        <v>10</v>
+      </c>
+      <c r="H94" s="52">
+        <v>1404.55</v>
+      </c>
+      <c r="I94" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J94" t="s" s="48">
+        <v>197</v>
+      </c>
+      <c r="K94" t="s" s="49">
+        <v>193</v>
+      </c>
+      <c r="L94" s="0"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="44"/>
+      <c r="B95" s="45"/>
+      <c r="C95" s="46"/>
+      <c r="D95" s="46"/>
+      <c r="E95" s="47"/>
+      <c r="F95" s="44"/>
+      <c r="G95" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H94" s="52">
-        <v>23613.5</v>
-      </c>
-      <c r="I94" s="53"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="49"/>
-      <c r="L94" s="0"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B95" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C95" t="s" s="46">
-        <v>148</v>
-      </c>
-      <c r="D95" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E95" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F95" t="s" s="44">
-        <v>188</v>
-      </c>
-      <c r="G95" s="51">
-        <v>1</v>
-      </c>
       <c r="H95" s="52">
-        <v>1251.09</v>
-      </c>
-      <c r="I95" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J95" t="s" s="48">
-        <v>189</v>
-      </c>
-      <c r="K95" t="s" s="49">
-        <v>151</v>
-      </c>
+        <v>48131</v>
+      </c>
+      <c r="I95" s="53"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="0"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="44">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="B96" s="45">
-        <v>0000106977</v>
+        <v>0000106979</v>
       </c>
       <c r="C96" t="s" s="46">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="D96" t="s" s="46">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E96" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F96" t="s" s="44">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="G96" s="51">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="H96" s="52">
-        <v>1286.84</v>
+        <v>318.64</v>
       </c>
       <c r="I96" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J96" t="s" s="48">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="K96" t="s" s="49">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="L96" s="0"/>
     </row>
     <row r="97">
-      <c r="A97" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B97" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C97" t="s" s="46">
-        <v>148</v>
-      </c>
-      <c r="D97" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E97" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F97" t="s" s="44">
-        <v>192</v>
-      </c>
-      <c r="G97" s="51">
-        <v>1</v>
+      <c r="A97" s="44"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="46"/>
+      <c r="D97" s="46"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="44"/>
+      <c r="G97" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H97" s="52">
-        <v>1454.19</v>
-      </c>
-      <c r="I97" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J97" t="s" s="48">
-        <v>193</v>
-      </c>
-      <c r="K97" t="s" s="49">
-        <v>151</v>
-      </c>
+        <v>42379.12</v>
+      </c>
+      <c r="I97" s="53"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="0"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="44">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="B98" s="45">
-        <v>0000106977</v>
+        <v>0000106623</v>
       </c>
       <c r="C98" t="s" s="46">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="D98" t="s" s="46">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E98" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F98" t="s" s="44">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G98" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="52">
-        <v>162.48</v>
+        <v>270.97</v>
       </c>
       <c r="I98" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J98" t="s" s="48">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K98" t="s" s="49">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="L98" s="0"/>
     </row>
     <row r="99">
-      <c r="A99" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B99" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C99" t="s" s="46">
-        <v>148</v>
-      </c>
-      <c r="D99" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E99" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F99" t="s" s="44">
-        <v>196</v>
-      </c>
-      <c r="G99" s="51">
-        <v>2</v>
+      <c r="A99" s="44"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="46"/>
+      <c r="D99" s="46"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="44"/>
+      <c r="G99" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H99" s="52">
-        <v>144.60</v>
-      </c>
-      <c r="I99" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J99" t="s" s="48">
-        <v>197</v>
-      </c>
-      <c r="K99" t="s" s="49">
-        <v>151</v>
-      </c>
+        <v>541.94</v>
+      </c>
+      <c r="I99" s="53"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="0"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="44">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="B100" s="45">
-        <v>0000106977</v>
+        <v>0000106824</v>
       </c>
       <c r="C100" t="s" s="46">
-        <v>148</v>
+        <v>207</v>
       </c>
       <c r="D100" t="s" s="46">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="E100" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F100" t="s" s="44">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G100" s="51">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H100" s="52">
-        <v>658.04</v>
-      </c>
-      <c r="I100" t="s" s="53">
-        <v>18</v>
+        <v>320.25</v>
+      </c>
+      <c r="I100" s="53">
+        <v>72</v>
       </c>
       <c r="J100" t="s" s="48">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="K100" t="s" s="49">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="L100" s="0"/>
     </row>
     <row r="101">
-      <c r="A101" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B101" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C101" t="s" s="46">
-        <v>148</v>
-      </c>
-      <c r="D101" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E101" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F101" t="s" s="44">
-        <v>200</v>
-      </c>
-      <c r="G101" s="51">
-        <v>1</v>
+      <c r="A101" s="44"/>
+      <c r="B101" s="45"/>
+      <c r="C101" s="46"/>
+      <c r="D101" s="46"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="44"/>
+      <c r="G101" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H101" s="52">
-        <v>381.82</v>
-      </c>
-      <c r="I101" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J101" t="s" s="48">
-        <v>201</v>
-      </c>
-      <c r="K101" t="s" s="49">
-        <v>151</v>
-      </c>
+        <v>15372</v>
+      </c>
+      <c r="I101" s="53"/>
+      <c r="J101" s="48"/>
+      <c r="K101" s="49"/>
       <c r="L101" s="0"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="44">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="B102" s="45">
-        <v>0000106977</v>
+        <v>0000106778</v>
       </c>
       <c r="C102" t="s" s="46">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="D102" t="s" s="46">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="E102" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F102" t="s" s="44">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G102" s="51">
         <v>5</v>
       </c>
       <c r="H102" s="52">
-        <v>641.79</v>
+        <v>2250</v>
       </c>
       <c r="I102" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J102" t="s" s="48">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K102" t="s" s="49">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="L102" s="0"/>
     </row>
     <row r="103">
-      <c r="A103" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B103" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C103" t="s" s="46">
-        <v>148</v>
-      </c>
-      <c r="D103" t="s" s="46">
-        <v>176</v>
-      </c>
-      <c r="E103" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F103" t="s" s="44">
-        <v>202</v>
-      </c>
-      <c r="G103" s="51">
+      <c r="A103" s="44"/>
+      <c r="B103" s="45"/>
+      <c r="C103" s="46"/>
+      <c r="D103" s="46"/>
+      <c r="E103" s="47"/>
+      <c r="F103" s="44"/>
+      <c r="G103" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H103" s="52">
+        <v>11250</v>
+      </c>
+      <c r="I103" s="53"/>
+      <c r="J103" s="48"/>
+      <c r="K103" s="49"/>
+      <c r="L103" s="0"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="44">
+        <v>54</v>
+      </c>
+      <c r="B104" s="45">
+        <v>0000106995</v>
+      </c>
+      <c r="C104" t="s" s="46">
+        <v>212</v>
+      </c>
+      <c r="D104" t="s" s="46">
+        <v>211</v>
+      </c>
+      <c r="E104" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F104" t="s" s="44">
+        <v>213</v>
+      </c>
+      <c r="G104" s="51">
         <v>1</v>
       </c>
-      <c r="H103" s="52">
-        <v>641.79</v>
-      </c>
-      <c r="I103" t="s" s="53">
+      <c r="H104" s="52">
+        <v>0</v>
+      </c>
+      <c r="I104" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J103" t="s" s="48">
-        <v>203</v>
-      </c>
-      <c r="K103" t="s" s="49">
-        <v>151</v>
-      </c>
-      <c r="L103" s="0"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="44"/>
-      <c r="B104" s="45"/>
-      <c r="C104" s="46"/>
-      <c r="D104" s="46"/>
-      <c r="E104" s="47"/>
-      <c r="F104" t="s" s="44">
+      <c r="J104" t="s" s="48">
+        <v>214</v>
+      </c>
+      <c r="K104" t="s" s="49">
+        <v>215</v>
+      </c>
+      <c r="L104" s="0"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="44">
+        <v>54</v>
+      </c>
+      <c r="B105" s="45">
+        <v>0000106995</v>
+      </c>
+      <c r="C105" t="s" s="46">
+        <v>212</v>
+      </c>
+      <c r="D105" t="s" s="46">
+        <v>211</v>
+      </c>
+      <c r="E105" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F105" t="s" s="44">
+        <v>216</v>
+      </c>
+      <c r="G105" s="51">
+        <v>1</v>
+      </c>
+      <c r="H105" s="52">
+        <v>0</v>
+      </c>
+      <c r="I105" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="G104" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H104" s="52">
-        <v>11308.52</v>
-      </c>
-      <c r="I104" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J104" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K104" s="49"/>
-      <c r="L104" s="0"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="44"/>
-      <c r="B105" s="45"/>
-      <c r="C105" s="46"/>
-      <c r="D105" s="46"/>
-      <c r="E105" s="47"/>
-      <c r="F105" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="G105" t="s" s="51">
-        <v>48</v>
-      </c>
-      <c r="H105" s="52">
-        <v>446671.2</v>
-      </c>
-      <c r="I105" s="53">
-        <v>815.2</v>
-      </c>
-      <c r="J105" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="K105" s="49"/>
+      <c r="J105" t="s" s="48">
+        <v>217</v>
+      </c>
+      <c r="K105" t="s" s="49">
+        <v>215</v>
+      </c>
       <c r="L105" s="0"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="44">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="B106" s="45">
-        <v>0000106893</v>
+        <v>0000106995</v>
       </c>
       <c r="C106" t="s" s="46">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D106" t="s" s="46">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E106" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F106" t="s" s="44">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G106" s="51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H106" s="52">
-        <v>3408.55</v>
+        <v>0</v>
       </c>
       <c r="I106" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J106" t="s" s="48">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="K106" t="s" s="49">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="L106" s="0"/>
     </row>
     <row r="107">
-      <c r="A107" t="s" s="44">
-        <v>204</v>
-      </c>
-      <c r="B107" s="45">
-        <v>0000106893</v>
-      </c>
-      <c r="C107" t="s" s="46">
-        <v>205</v>
-      </c>
-      <c r="D107" t="s" s="46">
-        <v>206</v>
-      </c>
-      <c r="E107" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F107" t="s" s="44">
-        <v>212</v>
-      </c>
-      <c r="G107" s="51">
-        <v>10</v>
+      <c r="A107" s="44"/>
+      <c r="B107" s="45"/>
+      <c r="C107" s="46"/>
+      <c r="D107" s="46"/>
+      <c r="E107" s="47"/>
+      <c r="F107" s="44"/>
+      <c r="G107" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H107" s="52">
-        <v>1404.55</v>
-      </c>
-      <c r="I107" t="s" s="53">
+        <v>0</v>
+      </c>
+      <c r="I107" s="53"/>
+      <c r="J107" s="48"/>
+      <c r="K107" s="49"/>
+      <c r="L107" s="0"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="44">
+        <v>220</v>
+      </c>
+      <c r="B108" s="45">
+        <v>0000106978</v>
+      </c>
+      <c r="C108" t="s" s="46">
+        <v>221</v>
+      </c>
+      <c r="D108" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E108" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F108" t="s" s="44">
+        <v>213</v>
+      </c>
+      <c r="G108" s="51">
+        <v>144</v>
+      </c>
+      <c r="H108" s="52">
+        <v>75</v>
+      </c>
+      <c r="I108" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J107" t="s" s="48">
-        <v>213</v>
-      </c>
-      <c r="K107" t="s" s="49">
-        <v>209</v>
-      </c>
-      <c r="L107" s="0"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="44"/>
-      <c r="B108" s="45"/>
-      <c r="C108" s="46"/>
-      <c r="D108" s="46"/>
-      <c r="E108" s="47"/>
-      <c r="F108" s="44"/>
-      <c r="G108" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H108" s="52">
-        <v>48131</v>
-      </c>
-      <c r="I108" s="53"/>
-      <c r="J108" s="48"/>
-      <c r="K108" s="49"/>
+      <c r="J108" t="s" s="48">
+        <v>214</v>
+      </c>
+      <c r="K108" t="s" s="49">
+        <v>223</v>
+      </c>
       <c r="L108" s="0"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="44">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B109" s="45">
-        <v>0000106979</v>
+        <v>0000106978</v>
       </c>
       <c r="C109" t="s" s="46">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D109" t="s" s="46">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E109" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F109" t="s" s="44">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G109" s="51">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H109" s="52">
-        <v>318.64</v>
+        <v>225</v>
       </c>
       <c r="I109" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J109" t="s" s="48">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="K109" t="s" s="49">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="L109" s="0"/>
     </row>
     <row r="110">
-      <c r="A110" s="44"/>
-      <c r="B110" s="45"/>
-      <c r="C110" s="46"/>
-      <c r="D110" s="46"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="44"/>
-      <c r="G110" t="s" s="51">
-        <v>31</v>
+      <c r="A110" t="s" s="44">
+        <v>220</v>
+      </c>
+      <c r="B110" s="45">
+        <v>0000106978</v>
+      </c>
+      <c r="C110" t="s" s="46">
+        <v>221</v>
+      </c>
+      <c r="D110" t="s" s="46">
+        <v>222</v>
+      </c>
+      <c r="E110" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F110" t="s" s="44">
+        <v>226</v>
+      </c>
+      <c r="G110" s="51">
+        <v>288</v>
       </c>
       <c r="H110" s="52">
-        <v>42379.12</v>
-      </c>
-      <c r="I110" s="53"/>
-      <c r="J110" s="48"/>
-      <c r="K110" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="I110" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J110" t="s" s="48">
+        <v>227</v>
+      </c>
+      <c r="K110" t="s" s="49">
+        <v>223</v>
+      </c>
       <c r="L110" s="0"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="44">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="B111" s="45">
-        <v>0000106623</v>
+        <v>0000106978</v>
       </c>
       <c r="C111" t="s" s="46">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D111" t="s" s="46">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E111" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F111" t="s" s="44">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G111" s="51">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="H111" s="52">
-        <v>270.97</v>
+        <v>100</v>
       </c>
       <c r="I111" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J111" t="s" s="48">
+        <v>229</v>
+      </c>
+      <c r="K111" t="s" s="49">
+        <v>223</v>
+      </c>
+      <c r="L111" s="0"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="44">
+        <v>220</v>
+      </c>
+      <c r="B112" s="45">
+        <v>0000106978</v>
+      </c>
+      <c r="C112" t="s" s="46">
+        <v>221</v>
+      </c>
+      <c r="D112" t="s" s="46">
         <v>222</v>
       </c>
-      <c r="K111" t="s" s="49">
-        <v>66</v>
-      </c>
-      <c r="L111" s="0"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="44"/>
-      <c r="B112" s="45"/>
-      <c r="C112" s="46"/>
-      <c r="D112" s="46"/>
-      <c r="E112" s="47"/>
-      <c r="F112" s="44"/>
-      <c r="G112" t="s" s="51">
+      <c r="E112" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F112" t="s" s="44">
+        <v>230</v>
+      </c>
+      <c r="G112" s="51">
+        <v>144</v>
+      </c>
+      <c r="H112" s="52">
+        <v>495</v>
+      </c>
+      <c r="I112" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J112" t="s" s="48">
+        <v>231</v>
+      </c>
+      <c r="K112" t="s" s="49">
+        <v>223</v>
+      </c>
+      <c r="L112" s="0"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="44"/>
+      <c r="B113" s="45"/>
+      <c r="C113" s="46"/>
+      <c r="D113" s="46"/>
+      <c r="E113" s="47"/>
+      <c r="F113" s="44"/>
+      <c r="G113" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H112" s="52">
-        <v>541.94</v>
-      </c>
-      <c r="I112" s="53"/>
-      <c r="J112" s="48"/>
-      <c r="K112" s="49"/>
-      <c r="L112" s="0"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B113" s="45">
-        <v>0000106824</v>
-      </c>
-      <c r="C113" t="s" s="46">
-        <v>223</v>
-      </c>
-      <c r="D113" t="s" s="46">
-        <v>216</v>
-      </c>
-      <c r="E113" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F113" t="s" s="44">
-        <v>224</v>
-      </c>
-      <c r="G113" s="51">
-        <v>48</v>
-      </c>
       <c r="H113" s="52">
-        <v>320.25</v>
-      </c>
-      <c r="I113" s="53">
-        <v>72</v>
-      </c>
-      <c r="J113" t="s" s="48">
-        <v>225</v>
-      </c>
-      <c r="K113" t="s" s="49">
-        <v>226</v>
-      </c>
+        <v>128880</v>
+      </c>
+      <c r="I113" s="53"/>
+      <c r="J113" s="48"/>
+      <c r="K113" s="49"/>
       <c r="L113" s="0"/>
     </row>
     <row r="114">
-      <c r="A114" s="44"/>
-      <c r="B114" s="45"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="46"/>
-      <c r="E114" s="47"/>
-      <c r="F114" s="44"/>
-      <c r="G114" t="s" s="51">
-        <v>31</v>
+      <c r="A114" t="s" s="44">
+        <v>165</v>
+      </c>
+      <c r="B114" s="45">
+        <v>0000106977</v>
+      </c>
+      <c r="C114" t="s" s="46">
+        <v>166</v>
+      </c>
+      <c r="D114" t="s" s="46">
+        <v>232</v>
+      </c>
+      <c r="E114" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F114" t="s" s="44">
+        <v>233</v>
+      </c>
+      <c r="G114" s="51">
+        <v>10</v>
       </c>
       <c r="H114" s="52">
-        <v>15372</v>
-      </c>
-      <c r="I114" s="53"/>
-      <c r="J114" s="48"/>
-      <c r="K114" s="49"/>
+        <v>566.16</v>
+      </c>
+      <c r="I114" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J114" t="s" s="48">
+        <v>234</v>
+      </c>
+      <c r="K114" t="s" s="49">
+        <v>169</v>
+      </c>
       <c r="L114" s="0"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="44">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="B115" s="45">
-        <v>0000106943</v>
+        <v>0000106977</v>
       </c>
       <c r="C115" t="s" s="46">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="D115" t="s" s="46">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E115" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F115" t="s" s="44">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="G115" s="51">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H115" s="52">
-        <v>650.03</v>
+        <v>525.72</v>
       </c>
       <c r="I115" s="53">
-        <v>48</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="s" s="48">
-        <v>94</v>
+        <v>236</v>
       </c>
       <c r="K115" t="s" s="49">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="L115" s="0"/>
     </row>
@@ -5159,7 +5234,7 @@
         <v>31</v>
       </c>
       <c r="H116" s="52">
-        <v>10400.48</v>
+        <v>6713.04</v>
       </c>
       <c r="I116" s="53"/>
       <c r="J116" s="48"/>
@@ -5168,37 +5243,37 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="44">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="B117" s="45">
-        <v>0000106778</v>
+        <v>0000106981</v>
       </c>
       <c r="C117" t="s" s="46">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="D117" t="s" s="46">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E117" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F117" t="s" s="44">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G117" s="51">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="H117" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I117" t="s" s="53">
-        <v>18</v>
+        <v>474.23</v>
+      </c>
+      <c r="I117" s="53">
+        <v>52</v>
       </c>
       <c r="J117" t="s" s="48">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K117" t="s" s="49">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="L117" s="0"/>
     </row>
@@ -5213,7 +5288,7 @@
         <v>31</v>
       </c>
       <c r="H118" s="52">
-        <v>11250</v>
+        <v>24659.96</v>
       </c>
       <c r="I118" s="53"/>
       <c r="J118" s="48"/>
@@ -5222,181 +5297,145 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="44">
-        <v>228</v>
+        <v>42</v>
       </c>
       <c r="B119" s="45">
-        <v>0000106978</v>
+        <v>0000106982</v>
       </c>
       <c r="C119" t="s" s="46">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D119" t="s" s="46">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E119" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F119" t="s" s="44">
-        <v>231</v>
+        <v>148</v>
       </c>
       <c r="G119" s="51">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="H119" s="52">
-        <v>75</v>
-      </c>
-      <c r="I119" t="s" s="53">
-        <v>18</v>
+        <v>368.44</v>
+      </c>
+      <c r="I119" s="53">
+        <v>52</v>
       </c>
       <c r="J119" t="s" s="48">
-        <v>232</v>
+        <v>52</v>
       </c>
       <c r="K119" t="s" s="49">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L119" s="0"/>
     </row>
     <row r="120">
-      <c r="A120" t="s" s="44">
-        <v>228</v>
-      </c>
-      <c r="B120" s="45">
-        <v>0000106978</v>
-      </c>
-      <c r="C120" t="s" s="46">
-        <v>229</v>
-      </c>
-      <c r="D120" t="s" s="46">
-        <v>230</v>
-      </c>
-      <c r="E120" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F120" t="s" s="44">
-        <v>234</v>
-      </c>
-      <c r="G120" s="51">
-        <v>144</v>
+      <c r="A120" s="44"/>
+      <c r="B120" s="45"/>
+      <c r="C120" s="46"/>
+      <c r="D120" s="46"/>
+      <c r="E120" s="47"/>
+      <c r="F120" s="44"/>
+      <c r="G120" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H120" s="52">
-        <v>225</v>
-      </c>
-      <c r="I120" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J120" t="s" s="48">
-        <v>235</v>
-      </c>
-      <c r="K120" t="s" s="49">
-        <v>233</v>
-      </c>
+        <v>19158.88</v>
+      </c>
+      <c r="I120" s="53"/>
+      <c r="J120" s="48"/>
+      <c r="K120" s="49"/>
       <c r="L120" s="0"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="44">
-        <v>228</v>
+        <v>42</v>
       </c>
       <c r="B121" s="45">
-        <v>0000106978</v>
+        <v>0000106983</v>
       </c>
       <c r="C121" t="s" s="46">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D121" t="s" s="46">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E121" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F121" t="s" s="44">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G121" s="51">
-        <v>288</v>
+        <v>52</v>
       </c>
       <c r="H121" s="52">
-        <v>0</v>
+        <v>507.46</v>
       </c>
       <c r="I121" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J121" t="s" s="48">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K121" t="s" s="49">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L121" s="0"/>
     </row>
     <row r="122">
-      <c r="A122" t="s" s="44">
-        <v>228</v>
-      </c>
-      <c r="B122" s="45">
-        <v>0000106978</v>
-      </c>
-      <c r="C122" t="s" s="46">
-        <v>229</v>
-      </c>
-      <c r="D122" t="s" s="46">
-        <v>230</v>
-      </c>
-      <c r="E122" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F122" t="s" s="44">
-        <v>238</v>
-      </c>
-      <c r="G122" s="51">
-        <v>144</v>
+      <c r="A122" s="44"/>
+      <c r="B122" s="45"/>
+      <c r="C122" s="46"/>
+      <c r="D122" s="46"/>
+      <c r="E122" s="47"/>
+      <c r="F122" s="44"/>
+      <c r="G122" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H122" s="52">
-        <v>100</v>
-      </c>
-      <c r="I122" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J122" t="s" s="48">
-        <v>239</v>
-      </c>
-      <c r="K122" t="s" s="49">
-        <v>233</v>
-      </c>
+        <v>26387.92</v>
+      </c>
+      <c r="I122" s="53"/>
+      <c r="J122" s="48"/>
+      <c r="K122" s="49"/>
       <c r="L122" s="0"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="44">
-        <v>228</v>
+        <v>42</v>
       </c>
       <c r="B123" s="45">
-        <v>0000106978</v>
+        <v>0000106984</v>
       </c>
       <c r="C123" t="s" s="46">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D123" t="s" s="46">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E123" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F123" t="s" s="44">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G123" s="51">
-        <v>144</v>
+        <v>52</v>
       </c>
       <c r="H123" s="52">
-        <v>495</v>
+        <v>486.04</v>
       </c>
       <c r="I123" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J123" t="s" s="48">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K123" t="s" s="49">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="L123" s="0"/>
     </row>
@@ -5411,7 +5450,7 @@
         <v>31</v>
       </c>
       <c r="H124" s="52">
-        <v>128880</v>
+        <v>25274.08</v>
       </c>
       <c r="I124" s="53"/>
       <c r="J124" s="48"/>
@@ -5420,448 +5459,448 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="44">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="B125" s="45">
-        <v>0000106977</v>
+        <v>0000106985</v>
       </c>
       <c r="C125" t="s" s="46">
-        <v>148</v>
+        <v>237</v>
       </c>
       <c r="D125" t="s" s="46">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E125" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F125" t="s" s="44">
-        <v>243</v>
+        <v>149</v>
       </c>
       <c r="G125" s="51">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H125" s="52">
-        <v>568.68</v>
+        <v>512.40</v>
       </c>
       <c r="I125" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J125" t="s" s="48">
+        <v>150</v>
+      </c>
+      <c r="K125" t="s" s="49">
+        <v>239</v>
+      </c>
+      <c r="L125" s="0"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="44"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="46"/>
+      <c r="D126" s="46"/>
+      <c r="E126" s="47"/>
+      <c r="F126" s="44"/>
+      <c r="G126" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H126" s="52">
+        <v>26644.8</v>
+      </c>
+      <c r="I126" s="53"/>
+      <c r="J126" s="48"/>
+      <c r="K126" s="49"/>
+      <c r="L126" s="0"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="B127" s="45">
+        <v>0000106958</v>
+      </c>
+      <c r="C127" t="s" s="46">
+        <v>144</v>
+      </c>
+      <c r="D127" t="s" s="46">
         <v>244</v>
       </c>
-      <c r="K125" t="s" s="49">
+      <c r="E127" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F127" t="s" s="44">
+        <v>133</v>
+      </c>
+      <c r="G127" s="51">
+        <v>180</v>
+      </c>
+      <c r="H127" s="52">
+        <v>286.96</v>
+      </c>
+      <c r="I127" s="53">
+        <v>225</v>
+      </c>
+      <c r="J127" t="s" s="48">
+        <v>134</v>
+      </c>
+      <c r="K127" t="s" s="49">
+        <v>245</v>
+      </c>
+      <c r="L127" s="0"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="44"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="46"/>
+      <c r="D128" s="46"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="44"/>
+      <c r="G128" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H128" s="52">
+        <v>51652.8</v>
+      </c>
+      <c r="I128" s="53"/>
+      <c r="J128" s="48"/>
+      <c r="K128" s="49"/>
+      <c r="L128" s="0"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="B129" s="45">
+        <v>0000106993</v>
+      </c>
+      <c r="C129" t="s" s="46">
+        <v>184</v>
+      </c>
+      <c r="D129" t="s" s="46">
+        <v>244</v>
+      </c>
+      <c r="E129" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F129" t="s" s="44">
+        <v>133</v>
+      </c>
+      <c r="G129" s="51">
+        <v>180</v>
+      </c>
+      <c r="H129" s="52">
+        <v>289.26</v>
+      </c>
+      <c r="I129" s="53">
+        <v>225</v>
+      </c>
+      <c r="J129" t="s" s="48">
+        <v>134</v>
+      </c>
+      <c r="K129" t="s" s="49">
+        <v>246</v>
+      </c>
+      <c r="L129" s="0"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="44"/>
+      <c r="B130" s="45"/>
+      <c r="C130" s="46"/>
+      <c r="D130" s="46"/>
+      <c r="E130" s="47"/>
+      <c r="F130" s="44"/>
+      <c r="G130" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H130" s="52">
+        <v>52066.8</v>
+      </c>
+      <c r="I130" s="53"/>
+      <c r="J130" s="48"/>
+      <c r="K130" s="49"/>
+      <c r="L130" s="0"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="44">
+        <v>113</v>
+      </c>
+      <c r="B131" s="45">
+        <v>0000106989</v>
+      </c>
+      <c r="C131" t="s" s="46">
+        <v>247</v>
+      </c>
+      <c r="D131" t="s" s="46">
+        <v>244</v>
+      </c>
+      <c r="E131" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F131" t="s" s="44">
+        <v>248</v>
+      </c>
+      <c r="G131" s="51">
+        <v>8</v>
+      </c>
+      <c r="H131" s="52">
+        <v>2365</v>
+      </c>
+      <c r="I131" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J131" t="s" s="48">
+        <v>249</v>
+      </c>
+      <c r="K131" t="s" s="49">
+        <v>250</v>
+      </c>
+      <c r="L131" s="0"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="44"/>
+      <c r="B132" s="45"/>
+      <c r="C132" s="46"/>
+      <c r="D132" s="46"/>
+      <c r="E132" s="47"/>
+      <c r="F132" s="44"/>
+      <c r="G132" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H132" s="52">
+        <v>18920</v>
+      </c>
+      <c r="I132" s="53"/>
+      <c r="J132" s="48"/>
+      <c r="K132" s="49"/>
+      <c r="L132" s="0"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B133" s="45">
+        <v>0000106940</v>
+      </c>
+      <c r="C133" t="s" s="46">
         <v>151</v>
       </c>
-      <c r="L125" s="0"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="s" s="44">
-        <v>147</v>
-      </c>
-      <c r="B126" s="45">
-        <v>0000106977</v>
-      </c>
-      <c r="C126" t="s" s="46">
-        <v>148</v>
-      </c>
-      <c r="D126" t="s" s="46">
-        <v>242</v>
-      </c>
-      <c r="E126" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F126" t="s" s="44">
-        <v>245</v>
-      </c>
-      <c r="G126" s="51">
-        <v>2</v>
-      </c>
-      <c r="H126" s="52">
-        <v>528.06</v>
-      </c>
-      <c r="I126" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="J126" t="s" s="48">
-        <v>246</v>
-      </c>
-      <c r="K126" t="s" s="49">
+      <c r="D133" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="E133" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F133" t="s" s="44">
+        <v>252</v>
+      </c>
+      <c r="G133" s="51">
+        <v>16</v>
+      </c>
+      <c r="H133" s="52">
+        <v>565.38</v>
+      </c>
+      <c r="I133" s="53">
+        <v>48</v>
+      </c>
+      <c r="J133" t="s" s="48">
+        <v>253</v>
+      </c>
+      <c r="K133" t="s" s="49">
+        <v>155</v>
+      </c>
+      <c r="L133" s="0"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="44"/>
+      <c r="B134" s="45"/>
+      <c r="C134" s="46"/>
+      <c r="D134" s="46"/>
+      <c r="E134" s="47"/>
+      <c r="F134" s="44"/>
+      <c r="G134" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H134" s="52">
+        <v>9046.08</v>
+      </c>
+      <c r="I134" s="53"/>
+      <c r="J134" s="48"/>
+      <c r="K134" s="49"/>
+      <c r="L134" s="0"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B135" s="45">
+        <v>0000106943</v>
+      </c>
+      <c r="C135" t="s" s="46">
         <v>151</v>
       </c>
-      <c r="L126" s="0"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="44"/>
-      <c r="B127" s="45"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="46"/>
-      <c r="E127" s="47"/>
-      <c r="F127" s="44"/>
-      <c r="G127" t="s" s="51">
+      <c r="D135" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="E135" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F135" t="s" s="44">
+        <v>254</v>
+      </c>
+      <c r="G135" s="51">
+        <v>16</v>
+      </c>
+      <c r="H135" s="52">
+        <v>651.78</v>
+      </c>
+      <c r="I135" s="53">
+        <v>48</v>
+      </c>
+      <c r="J135" t="s" s="48">
+        <v>255</v>
+      </c>
+      <c r="K135" t="s" s="49">
+        <v>256</v>
+      </c>
+      <c r="L135" s="0"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="44"/>
+      <c r="B136" s="45"/>
+      <c r="C136" s="46"/>
+      <c r="D136" s="46"/>
+      <c r="E136" s="47"/>
+      <c r="F136" s="44"/>
+      <c r="G136" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H127" s="52">
-        <v>6742.92</v>
-      </c>
-      <c r="I127" s="53"/>
-      <c r="J127" s="48"/>
-      <c r="K127" s="49"/>
-      <c r="L127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B128" s="45">
-        <v>0000106981</v>
-      </c>
-      <c r="C128" t="s" s="46">
-        <v>247</v>
-      </c>
-      <c r="D128" t="s" s="46">
-        <v>248</v>
-      </c>
-      <c r="E128" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F128" t="s" s="44">
-        <v>170</v>
-      </c>
-      <c r="G128" s="51">
-        <v>52</v>
-      </c>
-      <c r="H128" s="52">
-        <v>474.23</v>
-      </c>
-      <c r="I128" s="53">
-        <v>52</v>
-      </c>
-      <c r="J128" t="s" s="48">
-        <v>171</v>
-      </c>
-      <c r="K128" t="s" s="49">
-        <v>249</v>
-      </c>
-      <c r="L128" s="0"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="44"/>
-      <c r="B129" s="45"/>
-      <c r="C129" s="46"/>
-      <c r="D129" s="46"/>
-      <c r="E129" s="47"/>
-      <c r="F129" s="44"/>
-      <c r="G129" t="s" s="51">
+      <c r="H136" s="52">
+        <v>10428.48</v>
+      </c>
+      <c r="I136" s="53"/>
+      <c r="J136" s="48"/>
+      <c r="K136" s="49"/>
+      <c r="L136" s="0"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B137" s="45">
+        <v>0000106966</v>
+      </c>
+      <c r="C137" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D137" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="E137" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F137" t="s" s="44">
+        <v>153</v>
+      </c>
+      <c r="G137" s="51">
+        <v>70</v>
+      </c>
+      <c r="H137" s="52">
+        <v>375.19</v>
+      </c>
+      <c r="I137" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J137" t="s" s="48">
+        <v>154</v>
+      </c>
+      <c r="K137" t="s" s="49">
+        <v>257</v>
+      </c>
+      <c r="L137" s="0"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="44"/>
+      <c r="B138" s="45"/>
+      <c r="C138" s="46"/>
+      <c r="D138" s="46"/>
+      <c r="E138" s="47"/>
+      <c r="F138" s="44"/>
+      <c r="G138" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H129" s="52">
-        <v>24659.96</v>
-      </c>
-      <c r="I129" s="53"/>
-      <c r="J129" s="48"/>
-      <c r="K129" s="49"/>
-      <c r="L129" s="0"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B130" s="45">
-        <v>0000106982</v>
-      </c>
-      <c r="C130" t="s" s="46">
-        <v>247</v>
-      </c>
-      <c r="D130" t="s" s="46">
-        <v>248</v>
-      </c>
-      <c r="E130" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F130" t="s" s="44">
-        <v>173</v>
-      </c>
-      <c r="G130" s="51">
-        <v>52</v>
-      </c>
-      <c r="H130" s="52">
-        <v>368.44</v>
-      </c>
-      <c r="I130" s="53">
-        <v>52</v>
-      </c>
-      <c r="J130" t="s" s="48">
-        <v>52</v>
-      </c>
-      <c r="K130" t="s" s="49">
-        <v>249</v>
-      </c>
-      <c r="L130" s="0"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="44"/>
-      <c r="B131" s="45"/>
-      <c r="C131" s="46"/>
-      <c r="D131" s="46"/>
-      <c r="E131" s="47"/>
-      <c r="F131" s="44"/>
-      <c r="G131" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H131" s="52">
-        <v>19158.88</v>
-      </c>
-      <c r="I131" s="53"/>
-      <c r="J131" s="48"/>
-      <c r="K131" s="49"/>
-      <c r="L131" s="0"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B132" s="45">
-        <v>0000106983</v>
-      </c>
-      <c r="C132" t="s" s="46">
-        <v>247</v>
-      </c>
-      <c r="D132" t="s" s="46">
-        <v>248</v>
-      </c>
-      <c r="E132" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F132" t="s" s="44">
-        <v>250</v>
-      </c>
-      <c r="G132" s="51">
-        <v>52</v>
-      </c>
-      <c r="H132" s="52">
-        <v>507.46</v>
-      </c>
-      <c r="I132" t="s" s="53">
+      <c r="H138" s="52">
+        <v>26263.3</v>
+      </c>
+      <c r="I138" s="53"/>
+      <c r="J138" s="48"/>
+      <c r="K138" s="49"/>
+      <c r="L138" s="0"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B139" s="45">
+        <v>0000106997</v>
+      </c>
+      <c r="C139" t="s" s="46">
+        <v>258</v>
+      </c>
+      <c r="D139" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="E139" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F139" t="s" s="44">
+        <v>259</v>
+      </c>
+      <c r="G139" s="51">
+        <v>50</v>
+      </c>
+      <c r="H139" s="52">
+        <v>4.50</v>
+      </c>
+      <c r="I139" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J132" t="s" s="48">
-        <v>251</v>
-      </c>
-      <c r="K132" t="s" s="49">
-        <v>249</v>
-      </c>
-      <c r="L132" s="0"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="44"/>
-      <c r="B133" s="45"/>
-      <c r="C133" s="46"/>
-      <c r="D133" s="46"/>
-      <c r="E133" s="47"/>
-      <c r="F133" s="44"/>
-      <c r="G133" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H133" s="52">
-        <v>26387.92</v>
-      </c>
-      <c r="I133" s="53"/>
-      <c r="J133" s="48"/>
-      <c r="K133" s="49"/>
-      <c r="L133" s="0"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B134" s="45">
-        <v>0000106984</v>
-      </c>
-      <c r="C134" t="s" s="46">
-        <v>247</v>
-      </c>
-      <c r="D134" t="s" s="46">
-        <v>248</v>
-      </c>
-      <c r="E134" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F134" t="s" s="44">
-        <v>252</v>
-      </c>
-      <c r="G134" s="51">
-        <v>52</v>
-      </c>
-      <c r="H134" s="52">
-        <v>486.04</v>
-      </c>
-      <c r="I134" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J134" t="s" s="48">
-        <v>253</v>
-      </c>
-      <c r="K134" t="s" s="49">
-        <v>249</v>
-      </c>
-      <c r="L134" s="0"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="44"/>
-      <c r="B135" s="45"/>
-      <c r="C135" s="46"/>
-      <c r="D135" s="46"/>
-      <c r="E135" s="47"/>
-      <c r="F135" s="44"/>
-      <c r="G135" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H135" s="52">
-        <v>25274.08</v>
-      </c>
-      <c r="I135" s="53"/>
-      <c r="J135" s="48"/>
-      <c r="K135" s="49"/>
-      <c r="L135" s="0"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B136" s="45">
-        <v>0000106985</v>
-      </c>
-      <c r="C136" t="s" s="46">
-        <v>247</v>
-      </c>
-      <c r="D136" t="s" s="46">
-        <v>248</v>
-      </c>
-      <c r="E136" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F136" t="s" s="44">
-        <v>174</v>
-      </c>
-      <c r="G136" s="51">
-        <v>52</v>
-      </c>
-      <c r="H136" s="52">
-        <v>512.40</v>
-      </c>
-      <c r="I136" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J136" t="s" s="48">
-        <v>175</v>
-      </c>
-      <c r="K136" t="s" s="49">
-        <v>249</v>
-      </c>
-      <c r="L136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="44"/>
-      <c r="B137" s="45"/>
-      <c r="C137" s="46"/>
-      <c r="D137" s="46"/>
-      <c r="E137" s="47"/>
-      <c r="F137" s="44"/>
-      <c r="G137" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H137" s="52">
-        <v>26644.8</v>
-      </c>
-      <c r="I137" s="53"/>
-      <c r="J137" s="48"/>
-      <c r="K137" s="49"/>
-      <c r="L137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="44">
-        <v>124</v>
-      </c>
-      <c r="B138" s="45">
-        <v>0000106958</v>
-      </c>
-      <c r="C138" t="s" s="46">
-        <v>169</v>
-      </c>
-      <c r="D138" t="s" s="46">
-        <v>254</v>
-      </c>
-      <c r="E138" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F138" t="s" s="44">
-        <v>158</v>
-      </c>
-      <c r="G138" s="51">
-        <v>180</v>
-      </c>
-      <c r="H138" s="52">
-        <v>286.96</v>
-      </c>
-      <c r="I138" s="53">
-        <v>225</v>
-      </c>
-      <c r="J138" t="s" s="48">
-        <v>159</v>
-      </c>
-      <c r="K138" t="s" s="49">
-        <v>255</v>
-      </c>
-      <c r="L138" s="0"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="44"/>
-      <c r="B139" s="45"/>
-      <c r="C139" s="46"/>
-      <c r="D139" s="46"/>
-      <c r="E139" s="47"/>
-      <c r="F139" s="44"/>
-      <c r="G139" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H139" s="52">
-        <v>51652.8</v>
-      </c>
-      <c r="I139" s="53"/>
-      <c r="J139" s="48"/>
-      <c r="K139" s="49"/>
+      <c r="J139" t="s" s="48">
+        <v>260</v>
+      </c>
+      <c r="K139" t="s" s="49">
+        <v>257</v>
+      </c>
       <c r="L139" s="0"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="44">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B140" s="45">
-        <v>0000106993</v>
+        <v>0000106997</v>
       </c>
       <c r="C140" t="s" s="46">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D140" t="s" s="46">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E140" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F140" t="s" s="44">
-        <v>158</v>
+        <v>261</v>
       </c>
       <c r="G140" s="51">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="H140" s="52">
-        <v>289.26</v>
-      </c>
-      <c r="I140" s="53">
-        <v>225</v>
+        <v>21.10</v>
+      </c>
+      <c r="I140" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J140" t="s" s="48">
-        <v>159</v>
+        <v>262</v>
       </c>
       <c r="K140" t="s" s="49">
         <v>257</v>
@@ -5869,111 +5908,117 @@
       <c r="L140" s="0"/>
     </row>
     <row r="141">
-      <c r="A141" s="44"/>
-      <c r="B141" s="45"/>
-      <c r="C141" s="46"/>
-      <c r="D141" s="46"/>
-      <c r="E141" s="47"/>
-      <c r="F141" s="44"/>
-      <c r="G141" t="s" s="51">
+      <c r="A141" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B141" s="45">
+        <v>0000106997</v>
+      </c>
+      <c r="C141" t="s" s="46">
+        <v>258</v>
+      </c>
+      <c r="D141" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="E141" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F141" t="s" s="44">
+        <v>122</v>
+      </c>
+      <c r="G141" s="51">
+        <v>100</v>
+      </c>
+      <c r="H141" s="52">
+        <v>11.47</v>
+      </c>
+      <c r="I141" s="53">
+        <v>3.3</v>
+      </c>
+      <c r="J141" t="s" s="48">
+        <v>123</v>
+      </c>
+      <c r="K141" t="s" s="49">
+        <v>257</v>
+      </c>
+      <c r="L141" s="0"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="44"/>
+      <c r="B142" s="45"/>
+      <c r="C142" s="46"/>
+      <c r="D142" s="46"/>
+      <c r="E142" s="47"/>
+      <c r="F142" s="44"/>
+      <c r="G142" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H141" s="52">
-        <v>52066.8</v>
-      </c>
-      <c r="I141" s="53"/>
-      <c r="J141" s="48"/>
-      <c r="K141" s="49"/>
-      <c r="L141" s="0"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B142" s="45">
-        <v>0000106989</v>
-      </c>
-      <c r="C142" t="s" s="46">
-        <v>258</v>
-      </c>
-      <c r="D142" t="s" s="46">
-        <v>254</v>
-      </c>
-      <c r="E142" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F142" t="s" s="44">
-        <v>259</v>
-      </c>
-      <c r="G142" s="51">
-        <v>8</v>
-      </c>
       <c r="H142" s="52">
-        <v>2365</v>
-      </c>
-      <c r="I142" t="s" s="53">
+        <v>2427</v>
+      </c>
+      <c r="I142" s="53"/>
+      <c r="J142" s="48"/>
+      <c r="K142" s="49"/>
+      <c r="L142" s="0"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="B143" s="45">
+        <v>0000106971</v>
+      </c>
+      <c r="C143" t="s" s="46">
+        <v>263</v>
+      </c>
+      <c r="D143" t="s" s="46">
+        <v>251</v>
+      </c>
+      <c r="E143" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F143" t="s" s="44">
+        <v>122</v>
+      </c>
+      <c r="G143" s="51">
+        <v>1000</v>
+      </c>
+      <c r="H143" s="52">
+        <v>8.58</v>
+      </c>
+      <c r="I143" s="53">
+        <v>33</v>
+      </c>
+      <c r="J143" t="s" s="48">
+        <v>123</v>
+      </c>
+      <c r="K143" t="s" s="49">
+        <v>135</v>
+      </c>
+      <c r="L143" s="0"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="44"/>
+      <c r="B144" s="45"/>
+      <c r="C144" s="46"/>
+      <c r="D144" s="46"/>
+      <c r="E144" s="47"/>
+      <c r="F144" t="s" s="44">
         <v>18</v>
       </c>
-      <c r="J142" t="s" s="48">
-        <v>260</v>
-      </c>
-      <c r="K142" t="s" s="49">
-        <v>261</v>
-      </c>
-      <c r="L142" s="0"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="44"/>
-      <c r="B143" s="45"/>
-      <c r="C143" s="46"/>
-      <c r="D143" s="46"/>
-      <c r="E143" s="47"/>
-      <c r="F143" s="44"/>
-      <c r="G143" t="s" s="51">
+      <c r="G144" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H143" s="52">
-        <v>18920</v>
-      </c>
-      <c r="I143" s="53"/>
-      <c r="J143" s="48"/>
-      <c r="K143" s="49"/>
-      <c r="L143" s="0"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B144" s="45">
-        <v>0000106966</v>
-      </c>
-      <c r="C144" t="s" s="46">
-        <v>43</v>
-      </c>
-      <c r="D144" t="s" s="46">
-        <v>262</v>
-      </c>
-      <c r="E144" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F144" t="s" s="44">
-        <v>90</v>
-      </c>
-      <c r="G144" s="51">
-        <v>70</v>
-      </c>
       <c r="H144" s="52">
-        <v>375.19</v>
-      </c>
-      <c r="I144" s="53">
-        <v>87.5</v>
+        <v>8580</v>
+      </c>
+      <c r="I144" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J144" t="s" s="48">
-        <v>91</v>
-      </c>
-      <c r="K144" t="s" s="49">
-        <v>263</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K144" s="49"/>
       <c r="L144" s="0"/>
     </row>
     <row r="145">
@@ -5982,51 +6027,57 @@
       <c r="C145" s="46"/>
       <c r="D145" s="46"/>
       <c r="E145" s="47"/>
-      <c r="F145" s="44"/>
+      <c r="F145" s="44" t="s">
+        <v>267</v>
+      </c>
       <c r="G145" t="s" s="51">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H145" s="52">
-        <v>26263.3</v>
-      </c>
-      <c r="I145" s="53"/>
-      <c r="J145" s="48"/>
+        <v>554777.2</v>
+      </c>
+      <c r="I145" s="53">
+        <v>846.3</v>
+      </c>
+      <c r="J145" s="48" t="s">
+        <v>268</v>
+      </c>
       <c r="K145" s="49"/>
       <c r="L145" s="0"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="44">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B146" s="45">
-        <v>0000106971</v>
+        <v>0000106882</v>
       </c>
       <c r="C146" t="s" s="46">
         <v>264</v>
       </c>
       <c r="D146" t="s" s="46">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E146" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F146" t="s" s="44">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="G146" s="51">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="H146" s="52">
-        <v>8.58</v>
+        <v>315.49</v>
       </c>
       <c r="I146" s="53">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="J146" t="s" s="48">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="K146" t="s" s="49">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="L146" s="0"/>
     </row>
@@ -6036,363 +6087,369 @@
       <c r="C147" s="46"/>
       <c r="D147" s="46"/>
       <c r="E147" s="47"/>
-      <c r="F147" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F147" s="44"/>
       <c r="G147" t="s" s="51">
         <v>31</v>
       </c>
       <c r="H147" s="52">
-        <v>8580</v>
-      </c>
-      <c r="I147" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J147" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>15143.52</v>
+      </c>
+      <c r="I147" s="53"/>
+      <c r="J147" s="48"/>
       <c r="K147" s="49"/>
       <c r="L147" s="0"/>
     </row>
     <row r="148">
-      <c r="A148" s="44"/>
-      <c r="B148" s="45"/>
-      <c r="C148" s="46"/>
-      <c r="D148" s="46"/>
-      <c r="E148" s="47"/>
-      <c r="F148" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="G148" t="s" s="51">
-        <v>48</v>
+      <c r="A148" t="s" s="44">
+        <v>269</v>
+      </c>
+      <c r="B148" s="45">
+        <v>0000106325</v>
+      </c>
+      <c r="C148" t="s" s="46">
+        <v>270</v>
+      </c>
+      <c r="D148" t="s" s="46">
+        <v>271</v>
+      </c>
+      <c r="E148" t="s" s="47">
+        <v>272</v>
+      </c>
+      <c r="F148" t="s" s="44">
+        <v>273</v>
+      </c>
+      <c r="G148" s="51">
+        <v>1</v>
       </c>
       <c r="H148" s="52">
-        <v>543306</v>
-      </c>
-      <c r="I148" s="53">
-        <v>795</v>
-      </c>
-      <c r="J148" s="48" t="s">
-        <v>269</v>
+        <v>88.19</v>
+      </c>
+      <c r="I148" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J148" t="s" s="48">
+        <v>274</v>
       </c>
       <c r="K148" s="49"/>
       <c r="L148" s="0"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="44">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="B149" s="45">
-        <v>0000106882</v>
+        <v>0000106325</v>
       </c>
       <c r="C149" t="s" s="46">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D149" t="s" s="46">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E149" t="s" s="47">
-        <v>97</v>
+        <v>272</v>
       </c>
       <c r="F149" t="s" s="44">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="G149" s="51">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H149" s="52">
-        <v>315.49</v>
-      </c>
-      <c r="I149" s="53">
-        <v>72</v>
+        <v>505.13</v>
+      </c>
+      <c r="I149" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J149" t="s" s="48">
-        <v>225</v>
-      </c>
-      <c r="K149" t="s" s="49">
-        <v>267</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="K149" s="49"/>
       <c r="L149" s="0"/>
     </row>
     <row r="150">
-      <c r="A150" s="44"/>
-      <c r="B150" s="45"/>
-      <c r="C150" s="46"/>
-      <c r="D150" s="46"/>
-      <c r="E150" s="47"/>
-      <c r="F150" s="44"/>
-      <c r="G150" t="s" s="51">
-        <v>31</v>
+      <c r="A150" t="s" s="44">
+        <v>269</v>
+      </c>
+      <c r="B150" s="45">
+        <v>0000106325</v>
+      </c>
+      <c r="C150" t="s" s="46">
+        <v>270</v>
+      </c>
+      <c r="D150" t="s" s="46">
+        <v>271</v>
+      </c>
+      <c r="E150" t="s" s="47">
+        <v>272</v>
+      </c>
+      <c r="F150" t="s" s="44">
+        <v>277</v>
+      </c>
+      <c r="G150" s="51">
+        <v>1</v>
       </c>
       <c r="H150" s="52">
-        <v>15143.52</v>
-      </c>
-      <c r="I150" s="53"/>
-      <c r="J150" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I150" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J150" t="s" s="48">
+        <v>278</v>
+      </c>
       <c r="K150" s="49"/>
       <c r="L150" s="0"/>
     </row>
     <row r="151">
-      <c r="A151" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B151" s="45">
-        <v>0000106967</v>
-      </c>
-      <c r="C151" t="s" s="46">
-        <v>43</v>
-      </c>
-      <c r="D151" t="s" s="46">
-        <v>266</v>
-      </c>
-      <c r="E151" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F151" t="s" s="44">
-        <v>93</v>
-      </c>
-      <c r="G151" s="51">
-        <v>16</v>
+      <c r="A151" s="44"/>
+      <c r="B151" s="45"/>
+      <c r="C151" s="46"/>
+      <c r="D151" s="46"/>
+      <c r="E151" s="47"/>
+      <c r="F151" s="44"/>
+      <c r="G151" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H151" s="52">
-        <v>660.00</v>
-      </c>
-      <c r="I151" s="53">
-        <v>48</v>
-      </c>
-      <c r="J151" t="s" s="48">
-        <v>94</v>
-      </c>
-      <c r="K151" t="s" s="49">
-        <v>267</v>
-      </c>
+        <v>593.32</v>
+      </c>
+      <c r="I151" s="53"/>
+      <c r="J151" s="48"/>
+      <c r="K151" s="49"/>
       <c r="L151" s="0"/>
     </row>
     <row r="152">
-      <c r="A152" s="44"/>
-      <c r="B152" s="45"/>
-      <c r="C152" s="46"/>
-      <c r="D152" s="46"/>
-      <c r="E152" s="47"/>
-      <c r="F152" s="44"/>
-      <c r="G152" t="s" s="51">
+      <c r="A152" t="s" s="44">
+        <v>113</v>
+      </c>
+      <c r="B152" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C152" t="s" s="46">
+        <v>114</v>
+      </c>
+      <c r="D152" t="s" s="46">
+        <v>279</v>
+      </c>
+      <c r="E152" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F152" t="s" s="44">
+        <v>115</v>
+      </c>
+      <c r="G152" s="51">
+        <v>5</v>
+      </c>
+      <c r="H152" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I152" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J152" t="s" s="48">
+        <v>116</v>
+      </c>
+      <c r="K152" t="s" s="49">
+        <v>117</v>
+      </c>
+      <c r="L152" s="0"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="44"/>
+      <c r="B153" s="45"/>
+      <c r="C153" s="46"/>
+      <c r="D153" s="46"/>
+      <c r="E153" s="47"/>
+      <c r="F153" s="44"/>
+      <c r="G153" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H152" s="52">
-        <v>10560</v>
-      </c>
-      <c r="I152" s="53"/>
-      <c r="J152" s="48"/>
-      <c r="K152" s="49"/>
-      <c r="L152" s="0"/>
-    </row>
-    <row r="153">
-      <c r="A153" t="s" s="44">
-        <v>270</v>
-      </c>
-      <c r="B153" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C153" t="s" s="46">
-        <v>271</v>
-      </c>
-      <c r="D153" t="s" s="46">
-        <v>272</v>
-      </c>
-      <c r="E153" t="s" s="47">
-        <v>273</v>
-      </c>
-      <c r="F153" t="s" s="44">
-        <v>274</v>
-      </c>
-      <c r="G153" s="51">
-        <v>1</v>
-      </c>
       <c r="H153" s="52">
-        <v>88.19</v>
-      </c>
-      <c r="I153" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J153" t="s" s="48">
-        <v>275</v>
-      </c>
+        <v>11250</v>
+      </c>
+      <c r="I153" s="53"/>
+      <c r="J153" s="48"/>
       <c r="K153" s="49"/>
       <c r="L153" s="0"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="44">
-        <v>270</v>
+        <v>126</v>
       </c>
       <c r="B154" s="45">
-        <v>0000106325</v>
+        <v>0000106968</v>
       </c>
       <c r="C154" t="s" s="46">
-        <v>271</v>
+        <v>43</v>
       </c>
       <c r="D154" t="s" s="46">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E154" t="s" s="47">
-        <v>273</v>
+        <v>96</v>
       </c>
       <c r="F154" t="s" s="44">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="G154" s="51">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="H154" s="52">
-        <v>505.13</v>
-      </c>
-      <c r="I154" t="s" s="53">
-        <v>18</v>
+        <v>375.19</v>
+      </c>
+      <c r="I154" s="53">
+        <v>87.5</v>
       </c>
       <c r="J154" t="s" s="48">
-        <v>277</v>
-      </c>
-      <c r="K154" s="49"/>
+        <v>154</v>
+      </c>
+      <c r="K154" t="s" s="49">
+        <v>281</v>
+      </c>
       <c r="L154" s="0"/>
     </row>
     <row r="155">
-      <c r="A155" t="s" s="44">
-        <v>270</v>
-      </c>
-      <c r="B155" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C155" t="s" s="46">
-        <v>271</v>
-      </c>
-      <c r="D155" t="s" s="46">
-        <v>272</v>
-      </c>
-      <c r="E155" t="s" s="47">
-        <v>273</v>
-      </c>
-      <c r="F155" t="s" s="44">
-        <v>278</v>
-      </c>
-      <c r="G155" s="51">
-        <v>1</v>
+      <c r="A155" s="44"/>
+      <c r="B155" s="45"/>
+      <c r="C155" s="46"/>
+      <c r="D155" s="46"/>
+      <c r="E155" s="47"/>
+      <c r="F155" s="44"/>
+      <c r="G155" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H155" s="52">
-        <v>0</v>
-      </c>
-      <c r="I155" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J155" t="s" s="48">
-        <v>279</v>
-      </c>
+        <v>26263.3</v>
+      </c>
+      <c r="I155" s="53"/>
+      <c r="J155" s="48"/>
       <c r="K155" s="49"/>
       <c r="L155" s="0"/>
     </row>
     <row r="156">
-      <c r="A156" s="44"/>
-      <c r="B156" s="45"/>
-      <c r="C156" s="46"/>
-      <c r="D156" s="46"/>
-      <c r="E156" s="47"/>
-      <c r="F156" s="44"/>
-      <c r="G156" t="s" s="51">
+      <c r="A156" t="s" s="44">
+        <v>93</v>
+      </c>
+      <c r="B156" s="45">
+        <v>0000106990</v>
+      </c>
+      <c r="C156" t="s" s="46">
+        <v>282</v>
+      </c>
+      <c r="D156" t="s" s="46">
+        <v>280</v>
+      </c>
+      <c r="E156" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F156" t="s" s="44">
+        <v>283</v>
+      </c>
+      <c r="G156" s="51">
+        <v>504</v>
+      </c>
+      <c r="H156" s="52">
+        <v>22.84</v>
+      </c>
+      <c r="I156" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J156" t="s" s="48">
+        <v>284</v>
+      </c>
+      <c r="K156" t="s" s="49">
+        <v>281</v>
+      </c>
+      <c r="L156" s="0"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="44"/>
+      <c r="B157" s="45"/>
+      <c r="C157" s="46"/>
+      <c r="D157" s="46"/>
+      <c r="E157" s="47"/>
+      <c r="F157" s="44"/>
+      <c r="G157" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H156" s="52">
-        <v>593.32</v>
-      </c>
-      <c r="I156" s="53"/>
-      <c r="J156" s="48"/>
-      <c r="K156" s="49"/>
-      <c r="L156" s="0"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="s" s="44">
-        <v>142</v>
-      </c>
-      <c r="B157" s="45">
-        <v>0000106778</v>
-      </c>
-      <c r="C157" t="s" s="46">
-        <v>143</v>
-      </c>
-      <c r="D157" t="s" s="46">
-        <v>280</v>
-      </c>
-      <c r="E157" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F157" t="s" s="44">
-        <v>144</v>
-      </c>
-      <c r="G157" s="51">
-        <v>5</v>
-      </c>
       <c r="H157" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I157" t="s" s="53">
+        <v>11511.36</v>
+      </c>
+      <c r="I157" s="53"/>
+      <c r="J157" s="48"/>
+      <c r="K157" s="49"/>
+      <c r="L157" s="0"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B158" s="45">
+        <v>0000106998</v>
+      </c>
+      <c r="C158" t="s" s="46">
+        <v>258</v>
+      </c>
+      <c r="D158" t="s" s="46">
+        <v>285</v>
+      </c>
+      <c r="E158" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F158" t="s" s="44">
+        <v>159</v>
+      </c>
+      <c r="G158" s="51">
+        <v>50</v>
+      </c>
+      <c r="H158" s="52">
+        <v>234.56</v>
+      </c>
+      <c r="I158" t="s" s="53">
         <v>18</v>
       </c>
-      <c r="J157" t="s" s="48">
-        <v>145</v>
-      </c>
-      <c r="K157" t="s" s="49">
-        <v>146</v>
-      </c>
-      <c r="L157" s="0"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="44"/>
-      <c r="B158" s="45"/>
-      <c r="C158" s="46"/>
-      <c r="D158" s="46"/>
-      <c r="E158" s="47"/>
-      <c r="F158" s="44"/>
-      <c r="G158" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H158" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I158" s="53"/>
-      <c r="J158" s="48"/>
-      <c r="K158" s="49"/>
+      <c r="J158" t="s" s="48">
+        <v>160</v>
+      </c>
+      <c r="K158" t="s" s="49">
+        <v>286</v>
+      </c>
       <c r="L158" s="0"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="44">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B159" s="45">
-        <v>0000106968</v>
+        <v>0000106998</v>
       </c>
       <c r="C159" t="s" s="46">
-        <v>43</v>
+        <v>258</v>
       </c>
       <c r="D159" t="s" s="46">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E159" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F159" t="s" s="44">
-        <v>90</v>
+        <v>287</v>
       </c>
       <c r="G159" s="51">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="H159" s="52">
-        <v>375.19</v>
+        <v>253.45</v>
       </c>
       <c r="I159" s="53">
-        <v>87.5</v>
+        <v>7.5</v>
       </c>
       <c r="J159" t="s" s="48">
-        <v>91</v>
+        <v>288</v>
       </c>
       <c r="K159" t="s" s="49">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="L159" s="0"/>
     </row>
@@ -6402,76 +6459,82 @@
       <c r="C160" s="46"/>
       <c r="D160" s="46"/>
       <c r="E160" s="47"/>
-      <c r="F160" s="44"/>
+      <c r="F160" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G160" t="s" s="51">
         <v>31</v>
       </c>
       <c r="H160" s="52">
-        <v>26263.3</v>
-      </c>
-      <c r="I160" s="53"/>
-      <c r="J160" s="48"/>
+        <v>15529.75</v>
+      </c>
+      <c r="I160" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K160" s="49"/>
       <c r="L160" s="0"/>
     </row>
     <row r="161">
-      <c r="A161" t="s" s="44">
-        <v>124</v>
-      </c>
-      <c r="B161" s="45">
-        <v>0000106990</v>
-      </c>
-      <c r="C161" t="s" s="46">
-        <v>152</v>
-      </c>
-      <c r="D161" t="s" s="46">
-        <v>281</v>
-      </c>
-      <c r="E161" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F161" t="s" s="44">
-        <v>283</v>
-      </c>
-      <c r="G161" s="51">
-        <v>504</v>
+      <c r="A161" s="44"/>
+      <c r="B161" s="45"/>
+      <c r="C161" s="46"/>
+      <c r="D161" s="46"/>
+      <c r="E161" s="47"/>
+      <c r="F161" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="G161" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H161" s="52">
-        <v>22.84</v>
-      </c>
-      <c r="I161" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J161" t="s" s="48">
-        <v>284</v>
-      </c>
-      <c r="K161" t="s" s="49">
-        <v>282</v>
-      </c>
+        <v>80291.25</v>
+      </c>
+      <c r="I161" s="53">
+        <v>167</v>
+      </c>
+      <c r="J161" s="48" t="s">
+        <v>292</v>
+      </c>
+      <c r="K161" s="49"/>
       <c r="L161" s="0"/>
     </row>
     <row r="162">
-      <c r="A162" s="44"/>
-      <c r="B162" s="45"/>
-      <c r="C162" s="46"/>
-      <c r="D162" s="46"/>
-      <c r="E162" s="47"/>
+      <c r="A162" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B162" s="45">
+        <v>0000106967</v>
+      </c>
+      <c r="C162" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D162" t="s" s="46">
+        <v>289</v>
+      </c>
+      <c r="E162" t="s" s="47">
+        <v>96</v>
+      </c>
       <c r="F162" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G162" t="s" s="51">
-        <v>31</v>
+        <v>254</v>
+      </c>
+      <c r="G162" s="51">
+        <v>16</v>
       </c>
       <c r="H162" s="52">
-        <v>11511.36</v>
-      </c>
-      <c r="I162" s="53" t="s">
-        <v>18</v>
+        <v>666.84</v>
+      </c>
+      <c r="I162" s="53">
+        <v>48</v>
       </c>
       <c r="J162" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K162" s="49"/>
+        <v>255</v>
+      </c>
+      <c r="K162" t="s" s="49">
+        <v>290</v>
+      </c>
       <c r="L162" s="0"/>
     </row>
     <row r="163">
@@ -6480,42 +6543,36 @@
       <c r="C163" s="46"/>
       <c r="D163" s="46"/>
       <c r="E163" s="47"/>
-      <c r="F163" s="44" t="s">
-        <v>287</v>
-      </c>
+      <c r="F163" s="44"/>
       <c r="G163" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H163" s="52">
-        <v>75321.5</v>
-      </c>
-      <c r="I163" s="53">
-        <v>207.5</v>
-      </c>
-      <c r="J163" s="48" t="s">
-        <v>288</v>
-      </c>
+        <v>10669.44</v>
+      </c>
+      <c r="I163" s="53"/>
+      <c r="J163" s="48"/>
       <c r="K163" s="49"/>
       <c r="L163" s="0"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="44">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B164" s="45">
         <v>0000106986</v>
       </c>
       <c r="C164" t="s" s="46">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D164" t="s" s="46">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E164" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F164" t="s" s="44">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="G164" s="51">
         <v>48</v>
@@ -6527,10 +6584,10 @@
         <v>72</v>
       </c>
       <c r="J164" t="s" s="48">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="K164" t="s" s="49">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="L164" s="0"/>
     </row>
@@ -6554,22 +6611,22 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="44">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="B166" s="45">
         <v>0000106778</v>
       </c>
       <c r="C166" t="s" s="46">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="D166" t="s" s="46">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E166" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F166" t="s" s="44">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="G166" s="51">
         <v>5</v>
@@ -6581,10 +6638,10 @@
         <v>18</v>
       </c>
       <c r="J166" t="s" s="48">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="K166" t="s" s="49">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="L166" s="0"/>
     </row>
@@ -6594,57 +6651,51 @@
       <c r="C167" s="46"/>
       <c r="D167" s="46"/>
       <c r="E167" s="47"/>
-      <c r="F167" t="s" s="44">
-        <v>291</v>
-      </c>
+      <c r="F167" s="44"/>
       <c r="G167" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H167" s="52">
-        <v>26933.04</v>
-      </c>
-      <c r="I167" s="53">
-        <v>72</v>
-      </c>
-      <c r="J167" t="s" s="48">
-        <v>292</v>
-      </c>
+        <v>11250</v>
+      </c>
+      <c r="I167" s="53"/>
+      <c r="J167" s="48"/>
       <c r="K167" s="49"/>
       <c r="L167" s="0"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="44">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B168" s="45">
-        <v>0000106778</v>
+        <v>0000106996</v>
       </c>
       <c r="C168" t="s" s="46">
-        <v>143</v>
+        <v>258</v>
       </c>
       <c r="D168" t="s" s="46">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E168" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F168" t="s" s="44">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="G168" s="51">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="H168" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I168" t="s" s="53">
-        <v>18</v>
+        <v>379.80</v>
+      </c>
+      <c r="I168" s="53">
+        <v>87.5</v>
       </c>
       <c r="J168" t="s" s="48">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="K168" t="s" s="49">
-        <v>146</v>
+        <v>297</v>
       </c>
       <c r="L168" s="0"/>
     </row>
@@ -6654,80 +6705,88 @@
       <c r="C169" s="46"/>
       <c r="D169" s="46"/>
       <c r="E169" s="47"/>
-      <c r="F169" t="s" s="44">
-        <v>18</v>
-      </c>
+      <c r="F169" s="44"/>
       <c r="G169" t="s" s="51">
         <v>31</v>
       </c>
       <c r="H169" s="52">
-        <v>15750</v>
-      </c>
-      <c r="I169" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J169" t="s" s="48">
-        <v>18</v>
-      </c>
+        <v>26586</v>
+      </c>
+      <c r="I169" s="53"/>
+      <c r="J169" s="48"/>
       <c r="K169" s="49"/>
       <c r="L169" s="0"/>
     </row>
     <row r="170">
-      <c r="A170" s="44"/>
-      <c r="B170" s="45"/>
-      <c r="C170" s="46"/>
-      <c r="D170" s="46"/>
-      <c r="E170" s="47"/>
-      <c r="F170" s="44" t="s">
-        <v>295</v>
-      </c>
-      <c r="G170" t="s" s="51">
-        <v>48</v>
+      <c r="A170" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B170" s="45">
+        <v>0000106999</v>
+      </c>
+      <c r="C170" t="s" s="46">
+        <v>258</v>
+      </c>
+      <c r="D170" t="s" s="46">
+        <v>296</v>
+      </c>
+      <c r="E170" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F170" t="s" s="44">
+        <v>298</v>
+      </c>
+      <c r="G170" s="51">
+        <v>25</v>
       </c>
       <c r="H170" s="52">
-        <v>4500</v>
+        <v>240.32</v>
       </c>
       <c r="I170" s="53">
-        <v>0</v>
-      </c>
-      <c r="J170" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="K170" s="49"/>
+        <v>12.5</v>
+      </c>
+      <c r="J170" t="s" s="48">
+        <v>299</v>
+      </c>
+      <c r="K170" t="s" s="49">
+        <v>297</v>
+      </c>
       <c r="L170" s="0"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="44">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B171" s="45">
-        <v>0000106170</v>
+        <v>0000106999</v>
       </c>
       <c r="C171" t="s" s="46">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="D171" t="s" s="46">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E171" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F171" t="s" s="44">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="G171" s="51">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H171" s="52">
-        <v>0</v>
+        <v>579.56</v>
       </c>
       <c r="I171" s="53">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="J171" t="s" s="48">
-        <v>225</v>
-      </c>
-      <c r="K171" s="49"/>
+        <v>253</v>
+      </c>
+      <c r="K171" t="s" s="49">
+        <v>297</v>
+      </c>
       <c r="L171" s="0"/>
     </row>
     <row r="172">
@@ -6736,100 +6795,104 @@
       <c r="C172" s="46"/>
       <c r="D172" s="46"/>
       <c r="E172" s="47"/>
-      <c r="F172" s="44"/>
+      <c r="F172" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G172" t="s" s="51">
         <v>31</v>
       </c>
       <c r="H172" s="52">
-        <v>0</v>
-      </c>
-      <c r="I172" s="53"/>
-      <c r="J172" s="48"/>
+        <v>11803.6</v>
+      </c>
+      <c r="I172" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J172" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K172" s="49"/>
       <c r="L172" s="0"/>
     </row>
     <row r="173">
-      <c r="A173" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B173" s="45">
-        <v>0000106171</v>
-      </c>
-      <c r="C173" t="s" s="46">
-        <v>293</v>
-      </c>
-      <c r="D173" t="s" s="46">
-        <v>294</v>
-      </c>
-      <c r="E173" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F173" t="s" s="44">
-        <v>90</v>
-      </c>
-      <c r="G173" s="51">
-        <v>70</v>
+      <c r="A173" s="44"/>
+      <c r="B173" s="45"/>
+      <c r="C173" s="46"/>
+      <c r="D173" s="46"/>
+      <c r="E173" s="47"/>
+      <c r="F173" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="G173" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H173" s="52">
-        <v>0</v>
+        <v>75992.08</v>
       </c>
       <c r="I173" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J173" t="s" s="48">
-        <v>91</v>
+        <v>250</v>
+      </c>
+      <c r="J173" s="48" t="s">
+        <v>302</v>
       </c>
       <c r="K173" s="49"/>
       <c r="L173" s="0"/>
     </row>
     <row r="174">
-      <c r="A174" s="44"/>
-      <c r="B174" s="45"/>
-      <c r="C174" s="46"/>
-      <c r="D174" s="46"/>
-      <c r="E174" s="47"/>
-      <c r="F174" s="44"/>
-      <c r="G174" t="s" s="51">
+      <c r="A174" t="s" s="44">
+        <v>113</v>
+      </c>
+      <c r="B174" s="45">
+        <v>0000106778</v>
+      </c>
+      <c r="C174" t="s" s="46">
+        <v>114</v>
+      </c>
+      <c r="D174" t="s" s="46">
+        <v>300</v>
+      </c>
+      <c r="E174" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F174" t="s" s="44">
+        <v>115</v>
+      </c>
+      <c r="G174" s="51">
+        <v>2</v>
+      </c>
+      <c r="H174" s="52">
+        <v>2250</v>
+      </c>
+      <c r="I174" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J174" t="s" s="48">
+        <v>116</v>
+      </c>
+      <c r="K174" t="s" s="49">
+        <v>117</v>
+      </c>
+      <c r="L174" s="0"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="44"/>
+      <c r="B175" s="45"/>
+      <c r="C175" s="46"/>
+      <c r="D175" s="46"/>
+      <c r="E175" s="47"/>
+      <c r="F175" t="s" s="44">
+        <v>18</v>
+      </c>
+      <c r="G175" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H174" s="52">
-        <v>0</v>
-      </c>
-      <c r="I174" s="53"/>
-      <c r="J174" s="48"/>
-      <c r="K174" s="49"/>
-      <c r="L174" s="0"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B175" s="45">
-        <v>0000106172</v>
-      </c>
-      <c r="C175" t="s" s="46">
-        <v>293</v>
-      </c>
-      <c r="D175" t="s" s="46">
-        <v>294</v>
-      </c>
-      <c r="E175" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F175" t="s" s="44">
-        <v>90</v>
-      </c>
-      <c r="G175" s="51">
-        <v>70</v>
-      </c>
       <c r="H175" s="52">
-        <v>0</v>
-      </c>
-      <c r="I175" s="53">
-        <v>87.5</v>
+        <v>4500</v>
+      </c>
+      <c r="I175" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J175" t="s" s="48">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="K175" s="49"/>
       <c r="L175" s="0"/>
@@ -6840,408 +6903,412 @@
       <c r="C176" s="46"/>
       <c r="D176" s="46"/>
       <c r="E176" s="47"/>
-      <c r="F176" s="44"/>
+      <c r="F176" s="44" t="s">
+        <v>305</v>
+      </c>
       <c r="G176" t="s" s="51">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H176" s="52">
+        <v>4500</v>
+      </c>
+      <c r="I176" s="53">
         <v>0</v>
       </c>
-      <c r="I176" s="53"/>
-      <c r="J176" s="48"/>
+      <c r="J176" s="48" t="s">
+        <v>50</v>
+      </c>
       <c r="K176" s="49"/>
       <c r="L176" s="0"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="44">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B177" s="45">
-        <v>0000106234</v>
+        <v>0000106170</v>
       </c>
       <c r="C177" t="s" s="46">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="D177" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E177" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F177" t="s" s="44">
-        <v>297</v>
+        <v>208</v>
       </c>
       <c r="G177" s="51">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="H177" s="52">
         <v>0</v>
       </c>
-      <c r="I177" t="s" s="53">
-        <v>18</v>
+      <c r="I177" s="53">
+        <v>72</v>
       </c>
       <c r="J177" t="s" s="48">
-        <v>189</v>
-      </c>
-      <c r="K177" t="s" s="49">
-        <v>298</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="K177" s="49"/>
       <c r="L177" s="0"/>
     </row>
     <row r="178">
-      <c r="A178" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B178" s="45">
-        <v>0000106234</v>
-      </c>
-      <c r="C178" t="s" s="46">
-        <v>296</v>
-      </c>
-      <c r="D178" t="s" s="46">
-        <v>294</v>
-      </c>
-      <c r="E178" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F178" t="s" s="44">
-        <v>299</v>
-      </c>
-      <c r="G178" s="51">
-        <v>5</v>
+      <c r="A178" s="44"/>
+      <c r="B178" s="45"/>
+      <c r="C178" s="46"/>
+      <c r="D178" s="46"/>
+      <c r="E178" s="47"/>
+      <c r="F178" s="44"/>
+      <c r="G178" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H178" s="52">
         <v>0</v>
       </c>
-      <c r="I178" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J178" t="s" s="48">
-        <v>193</v>
-      </c>
-      <c r="K178" t="s" s="49">
-        <v>298</v>
-      </c>
+      <c r="I178" s="53"/>
+      <c r="J178" s="48"/>
+      <c r="K178" s="49"/>
       <c r="L178" s="0"/>
     </row>
     <row r="179">
-      <c r="A179" s="44"/>
-      <c r="B179" s="45"/>
-      <c r="C179" s="46"/>
-      <c r="D179" s="46"/>
-      <c r="E179" s="47"/>
-      <c r="F179" s="44"/>
-      <c r="G179" t="s" s="51">
-        <v>31</v>
+      <c r="A179" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B179" s="45">
+        <v>0000106171</v>
+      </c>
+      <c r="C179" t="s" s="46">
+        <v>303</v>
+      </c>
+      <c r="D179" t="s" s="46">
+        <v>304</v>
+      </c>
+      <c r="E179" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F179" t="s" s="44">
+        <v>153</v>
+      </c>
+      <c r="G179" s="51">
+        <v>70</v>
       </c>
       <c r="H179" s="52">
         <v>0</v>
       </c>
-      <c r="I179" s="53"/>
-      <c r="J179" s="48"/>
+      <c r="I179" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J179" t="s" s="48">
+        <v>154</v>
+      </c>
       <c r="K179" s="49"/>
       <c r="L179" s="0"/>
     </row>
     <row r="180">
-      <c r="A180" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B180" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C180" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D180" t="s" s="46">
-        <v>294</v>
-      </c>
-      <c r="E180" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F180" t="s" s="44">
-        <v>301</v>
-      </c>
-      <c r="G180" s="51">
-        <v>1</v>
+      <c r="A180" s="44"/>
+      <c r="B180" s="45"/>
+      <c r="C180" s="46"/>
+      <c r="D180" s="46"/>
+      <c r="E180" s="47"/>
+      <c r="F180" s="44"/>
+      <c r="G180" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H180" s="52">
-        <v>2132.20</v>
-      </c>
-      <c r="I180" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J180" t="s" s="48">
-        <v>302</v>
-      </c>
-      <c r="K180" t="s" s="49">
-        <v>303</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I180" s="53"/>
+      <c r="J180" s="48"/>
+      <c r="K180" s="49"/>
       <c r="L180" s="0"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="44">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B181" s="45">
-        <v>0000106644</v>
+        <v>0000106172</v>
       </c>
       <c r="C181" t="s" s="46">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D181" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E181" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F181" t="s" s="44">
-        <v>304</v>
+        <v>153</v>
       </c>
       <c r="G181" s="51">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="H181" s="52">
-        <v>1359.96</v>
-      </c>
-      <c r="I181" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I181" s="53">
+        <v>87.5</v>
       </c>
       <c r="J181" t="s" s="48">
-        <v>305</v>
-      </c>
-      <c r="K181" t="s" s="49">
-        <v>303</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="K181" s="49"/>
       <c r="L181" s="0"/>
     </row>
     <row r="182">
-      <c r="A182" t="s" s="44">
-        <v>82</v>
-      </c>
-      <c r="B182" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C182" t="s" s="46">
-        <v>300</v>
-      </c>
-      <c r="D182" t="s" s="46">
-        <v>294</v>
-      </c>
-      <c r="E182" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F182" t="s" s="44">
-        <v>306</v>
-      </c>
-      <c r="G182" s="51">
-        <v>1</v>
+      <c r="A182" s="44"/>
+      <c r="B182" s="45"/>
+      <c r="C182" s="46"/>
+      <c r="D182" s="46"/>
+      <c r="E182" s="47"/>
+      <c r="F182" s="44"/>
+      <c r="G182" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H182" s="52">
-        <v>949.92</v>
-      </c>
-      <c r="I182" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J182" t="s" s="48">
-        <v>307</v>
-      </c>
-      <c r="K182" t="s" s="49">
-        <v>303</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I182" s="53"/>
+      <c r="J182" s="48"/>
+      <c r="K182" s="49"/>
       <c r="L182" s="0"/>
     </row>
     <row r="183">
       <c r="A183" t="s" s="44">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B183" s="45">
-        <v>0000106644</v>
+        <v>0000106234</v>
       </c>
       <c r="C183" t="s" s="46">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D183" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E183" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F183" t="s" s="44">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G183" s="51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H183" s="52">
-        <v>531.68</v>
+        <v>0</v>
       </c>
       <c r="I183" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J183" t="s" s="48">
+        <v>168</v>
+      </c>
+      <c r="K183" t="s" s="49">
+        <v>308</v>
+      </c>
+      <c r="L183" s="0"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B184" s="45">
+        <v>0000106234</v>
+      </c>
+      <c r="C184" t="s" s="46">
+        <v>306</v>
+      </c>
+      <c r="D184" t="s" s="46">
+        <v>304</v>
+      </c>
+      <c r="E184" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F184" t="s" s="44">
         <v>309</v>
       </c>
-      <c r="K183" t="s" s="49">
-        <v>303</v>
-      </c>
-      <c r="L183" s="0"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="44"/>
-      <c r="B184" s="45"/>
-      <c r="C184" s="46"/>
-      <c r="D184" s="46"/>
-      <c r="E184" s="47"/>
-      <c r="F184" s="44"/>
-      <c r="G184" t="s" s="51">
+      <c r="G184" s="51">
+        <v>5</v>
+      </c>
+      <c r="H184" s="52">
+        <v>0</v>
+      </c>
+      <c r="I184" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J184" t="s" s="48">
+        <v>173</v>
+      </c>
+      <c r="K184" t="s" s="49">
+        <v>308</v>
+      </c>
+      <c r="L184" s="0"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="44"/>
+      <c r="B185" s="45"/>
+      <c r="C185" s="46"/>
+      <c r="D185" s="46"/>
+      <c r="E185" s="47"/>
+      <c r="F185" s="44"/>
+      <c r="G185" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H184" s="52">
-        <v>4973.76</v>
-      </c>
-      <c r="I184" s="53"/>
-      <c r="J184" s="48"/>
-      <c r="K184" s="49"/>
-      <c r="L184" s="0"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="s" s="44">
+      <c r="H185" s="52">
+        <v>0</v>
+      </c>
+      <c r="I185" s="53"/>
+      <c r="J185" s="48"/>
+      <c r="K185" s="49"/>
+      <c r="L185" s="0"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B186" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C186" t="s" s="46">
         <v>310</v>
       </c>
-      <c r="B185" s="45">
-        <v>0000106764</v>
-      </c>
-      <c r="C185" t="s" s="46">
+      <c r="D186" t="s" s="46">
+        <v>304</v>
+      </c>
+      <c r="E186" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F186" t="s" s="44">
         <v>311</v>
       </c>
-      <c r="D185" t="s" s="46">
-        <v>294</v>
-      </c>
-      <c r="E185" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F185" t="s" s="44">
+      <c r="G186" s="51">
+        <v>1</v>
+      </c>
+      <c r="H186" s="52">
+        <v>2132.20</v>
+      </c>
+      <c r="I186" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J186" t="s" s="48">
         <v>312</v>
       </c>
-      <c r="G185" s="51">
-        <v>24</v>
-      </c>
-      <c r="H185" s="52">
-        <v>15</v>
-      </c>
-      <c r="I185" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J185" t="s" s="48">
+      <c r="K186" t="s" s="49">
         <v>313</v>
       </c>
-      <c r="K185" t="s" s="49">
-        <v>314</v>
-      </c>
-      <c r="L185" s="0"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="44"/>
-      <c r="B186" s="45"/>
-      <c r="C186" s="46"/>
-      <c r="D186" s="46"/>
-      <c r="E186" s="47"/>
-      <c r="F186" s="44"/>
-      <c r="G186" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H186" s="52">
-        <v>360</v>
-      </c>
-      <c r="I186" s="53"/>
-      <c r="J186" s="48"/>
-      <c r="K186" s="49"/>
       <c r="L186" s="0"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="44">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B187" s="45">
-        <v>0000106173</v>
+        <v>0000106644</v>
       </c>
       <c r="C187" t="s" s="46">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="D187" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E187" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F187" t="s" s="44">
-        <v>158</v>
+        <v>314</v>
       </c>
       <c r="G187" s="51">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H187" s="52">
-        <v>0</v>
-      </c>
-      <c r="I187" s="53">
-        <v>225</v>
+        <v>1359.96</v>
+      </c>
+      <c r="I187" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J187" t="s" s="48">
-        <v>159</v>
-      </c>
-      <c r="K187" s="49"/>
+        <v>315</v>
+      </c>
+      <c r="K187" t="s" s="49">
+        <v>313</v>
+      </c>
       <c r="L187" s="0"/>
     </row>
     <row r="188">
-      <c r="A188" s="44"/>
-      <c r="B188" s="45"/>
-      <c r="C188" s="46"/>
-      <c r="D188" s="46"/>
-      <c r="E188" s="47"/>
-      <c r="F188" s="44"/>
-      <c r="G188" t="s" s="51">
-        <v>31</v>
+      <c r="A188" t="s" s="44">
+        <v>126</v>
+      </c>
+      <c r="B188" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C188" t="s" s="46">
+        <v>310</v>
+      </c>
+      <c r="D188" t="s" s="46">
+        <v>304</v>
+      </c>
+      <c r="E188" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F188" t="s" s="44">
+        <v>316</v>
+      </c>
+      <c r="G188" s="51">
+        <v>1</v>
       </c>
       <c r="H188" s="52">
-        <v>0</v>
-      </c>
-      <c r="I188" s="53"/>
-      <c r="J188" s="48"/>
-      <c r="K188" s="49"/>
+        <v>949.92</v>
+      </c>
+      <c r="I188" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J188" t="s" s="48">
+        <v>317</v>
+      </c>
+      <c r="K188" t="s" s="49">
+        <v>313</v>
+      </c>
       <c r="L188" s="0"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="44">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B189" s="45">
-        <v>0000106174</v>
+        <v>0000106644</v>
       </c>
       <c r="C189" t="s" s="46">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="D189" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E189" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F189" t="s" s="44">
-        <v>158</v>
+        <v>318</v>
       </c>
       <c r="G189" s="51">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="H189" s="52">
-        <v>0</v>
-      </c>
-      <c r="I189" s="53">
-        <v>225</v>
+        <v>531.68</v>
+      </c>
+      <c r="I189" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J189" t="s" s="48">
-        <v>159</v>
-      </c>
-      <c r="K189" s="49"/>
+        <v>319</v>
+      </c>
+      <c r="K189" t="s" s="49">
+        <v>313</v>
+      </c>
       <c r="L189" s="0"/>
     </row>
     <row r="190">
@@ -7255,7 +7322,7 @@
         <v>31</v>
       </c>
       <c r="H190" s="52">
-        <v>0</v>
+        <v>4973.76</v>
       </c>
       <c r="I190" s="53"/>
       <c r="J190" s="48"/>
@@ -7264,36 +7331,38 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="44">
-        <v>42</v>
+        <v>320</v>
       </c>
       <c r="B191" s="45">
-        <v>0000106175</v>
+        <v>0000106764</v>
       </c>
       <c r="C191" t="s" s="46">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D191" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E191" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F191" t="s" s="44">
-        <v>173</v>
+        <v>322</v>
       </c>
       <c r="G191" s="51">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="H191" s="52">
-        <v>362.68</v>
-      </c>
-      <c r="I191" s="53">
-        <v>208</v>
+        <v>15</v>
+      </c>
+      <c r="I191" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J191" t="s" s="48">
-        <v>52</v>
-      </c>
-      <c r="K191" s="49"/>
+        <v>323</v>
+      </c>
+      <c r="K191" t="s" s="49">
+        <v>324</v>
+      </c>
       <c r="L191" s="0"/>
     </row>
     <row r="192">
@@ -7307,7 +7376,7 @@
         <v>31</v>
       </c>
       <c r="H192" s="52">
-        <v>75437.44</v>
+        <v>360</v>
       </c>
       <c r="I192" s="53"/>
       <c r="J192" s="48"/>
@@ -7316,34 +7385,34 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="44">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="B193" s="45">
-        <v>0000106176</v>
+        <v>0000106173</v>
       </c>
       <c r="C193" t="s" s="46">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D193" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E193" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F193" t="s" s="44">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="G193" s="51">
-        <v>52</v>
+        <v>180</v>
       </c>
       <c r="H193" s="52">
-        <v>509.41</v>
-      </c>
-      <c r="I193" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I193" s="53">
+        <v>225</v>
       </c>
       <c r="J193" t="s" s="48">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="K193" s="49"/>
       <c r="L193" s="0"/>
@@ -7359,7 +7428,7 @@
         <v>31</v>
       </c>
       <c r="H194" s="52">
-        <v>26489.32</v>
+        <v>0</v>
       </c>
       <c r="I194" s="53"/>
       <c r="J194" s="48"/>
@@ -7368,34 +7437,34 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="44">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="B195" s="45">
-        <v>0000106178</v>
+        <v>0000106174</v>
       </c>
       <c r="C195" t="s" s="46">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D195" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E195" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F195" t="s" s="44">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="G195" s="51">
-        <v>52</v>
+        <v>180</v>
       </c>
       <c r="H195" s="52">
-        <v>489.76</v>
-      </c>
-      <c r="I195" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I195" s="53">
+        <v>225</v>
       </c>
       <c r="J195" t="s" s="48">
-        <v>253</v>
+        <v>134</v>
       </c>
       <c r="K195" s="49"/>
       <c r="L195" s="0"/>
@@ -7411,7 +7480,7 @@
         <v>31</v>
       </c>
       <c r="H196" s="52">
-        <v>25467.52</v>
+        <v>0</v>
       </c>
       <c r="I196" s="53"/>
       <c r="J196" s="48"/>
@@ -7423,31 +7492,31 @@
         <v>42</v>
       </c>
       <c r="B197" s="45">
-        <v>0000106179</v>
+        <v>0000106175</v>
       </c>
       <c r="C197" t="s" s="46">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D197" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E197" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F197" t="s" s="44">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="G197" s="51">
+        <v>208</v>
+      </c>
+      <c r="H197" s="52">
+        <v>362.68</v>
+      </c>
+      <c r="I197" s="53">
+        <v>208</v>
+      </c>
+      <c r="J197" t="s" s="48">
         <v>52</v>
-      </c>
-      <c r="H197" s="52">
-        <v>458.18</v>
-      </c>
-      <c r="I197" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J197" t="s" s="48">
-        <v>251</v>
       </c>
       <c r="K197" s="49"/>
       <c r="L197" s="0"/>
@@ -7463,7 +7532,7 @@
         <v>31</v>
       </c>
       <c r="H198" s="52">
-        <v>23825.36</v>
+        <v>75437.44</v>
       </c>
       <c r="I198" s="53"/>
       <c r="J198" s="48"/>
@@ -7475,35 +7544,33 @@
         <v>42</v>
       </c>
       <c r="B199" s="45">
-        <v>0000106180</v>
+        <v>0000106176</v>
       </c>
       <c r="C199" t="s" s="46">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D199" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E199" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F199" t="s" s="44">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="G199" s="51">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="H199" s="52">
-        <v>466.80</v>
-      </c>
-      <c r="I199" s="53">
-        <v>104</v>
+        <v>509.41</v>
+      </c>
+      <c r="I199" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J199" t="s" s="48">
-        <v>171</v>
-      </c>
-      <c r="K199" t="s" s="49">
-        <v>298</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="K199" s="49"/>
       <c r="L199" s="0"/>
     </row>
     <row r="200">
@@ -7517,7 +7584,7 @@
         <v>31</v>
       </c>
       <c r="H200" s="52">
-        <v>48547.2</v>
+        <v>26489.32</v>
       </c>
       <c r="I200" s="53"/>
       <c r="J200" s="48"/>
@@ -7526,38 +7593,36 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="44">
-        <v>316</v>
+        <v>42</v>
       </c>
       <c r="B201" s="45">
-        <v>0000106980</v>
+        <v>0000106178</v>
       </c>
       <c r="C201" t="s" s="46">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D201" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E201" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F201" t="s" s="44">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="G201" s="51">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H201" s="52">
-        <v>532.72</v>
+        <v>489.76</v>
       </c>
       <c r="I201" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J201" t="s" s="48">
-        <v>319</v>
-      </c>
-      <c r="K201" t="s" s="49">
-        <v>66</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="K201" s="49"/>
       <c r="L201" s="0"/>
     </row>
     <row r="202">
@@ -7571,7 +7636,7 @@
         <v>31</v>
       </c>
       <c r="H202" s="52">
-        <v>26636</v>
+        <v>25467.52</v>
       </c>
       <c r="I202" s="53"/>
       <c r="J202" s="48"/>
@@ -7580,88 +7645,90 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="44">
-        <v>316</v>
+        <v>42</v>
       </c>
       <c r="B203" s="45">
-        <v>0000106980</v>
+        <v>0000106179</v>
       </c>
       <c r="C203" t="s" s="46">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D203" t="s" s="46">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E203" t="s" s="47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F203" t="s" s="44">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="G203" s="51">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="H203" s="52">
-        <v>13.14</v>
-      </c>
-      <c r="I203" s="53">
-        <v>6.6</v>
+        <v>458.18</v>
+      </c>
+      <c r="I203" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J203" t="s" s="48">
-        <v>122</v>
-      </c>
-      <c r="K203" t="s" s="49">
-        <v>66</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="K203" s="49"/>
       <c r="L203" s="0"/>
     </row>
     <row r="204">
-      <c r="A204" t="s" s="44">
-        <v>316</v>
-      </c>
-      <c r="B204" s="45">
-        <v>0000106980</v>
-      </c>
-      <c r="C204" t="s" s="46">
-        <v>317</v>
-      </c>
-      <c r="D204" t="s" s="46">
-        <v>294</v>
-      </c>
-      <c r="E204" t="s" s="47">
-        <v>97</v>
-      </c>
-      <c r="F204" t="s" s="44">
-        <v>154</v>
-      </c>
-      <c r="G204" s="51">
-        <v>300</v>
+      <c r="A204" s="44"/>
+      <c r="B204" s="45"/>
+      <c r="C204" s="46"/>
+      <c r="D204" s="46"/>
+      <c r="E204" s="47"/>
+      <c r="F204" s="44"/>
+      <c r="G204" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H204" s="52">
-        <v>12.78</v>
-      </c>
-      <c r="I204" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J204" t="s" s="48">
-        <v>155</v>
-      </c>
-      <c r="K204" t="s" s="49">
-        <v>66</v>
-      </c>
+        <v>23825.36</v>
+      </c>
+      <c r="I204" s="53"/>
+      <c r="J204" s="48"/>
+      <c r="K204" s="49"/>
       <c r="L204" s="0"/>
     </row>
     <row r="205">
-      <c r="A205" s="44"/>
-      <c r="B205" s="45"/>
-      <c r="C205" s="46"/>
-      <c r="D205" s="46"/>
-      <c r="E205" s="47"/>
-      <c r="F205" s="44"/>
-      <c r="G205" s="51"/>
-      <c r="H205" s="52"/>
-      <c r="I205" s="53"/>
-      <c r="J205" s="48"/>
-      <c r="K205" s="49"/>
+      <c r="A205" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B205" s="45">
+        <v>0000106180</v>
+      </c>
+      <c r="C205" t="s" s="46">
+        <v>325</v>
+      </c>
+      <c r="D205" t="s" s="46">
+        <v>304</v>
+      </c>
+      <c r="E205" t="s" s="47">
+        <v>96</v>
+      </c>
+      <c r="F205" t="s" s="44">
+        <v>145</v>
+      </c>
+      <c r="G205" s="51">
+        <v>104</v>
+      </c>
+      <c r="H205" s="52">
+        <v>466.80</v>
+      </c>
+      <c r="I205" s="53">
+        <v>104</v>
+      </c>
+      <c r="J205" t="s" s="48">
+        <v>146</v>
+      </c>
+      <c r="K205" t="s" s="49">
+        <v>308</v>
+      </c>
       <c r="L205" s="0"/>
     </row>
     <row r="206">
@@ -7675,16 +7742,14 @@
         <v>31</v>
       </c>
       <c r="H206" s="52">
-        <v>1328468.34</v>
-      </c>
-      <c r="I206" s="53">
-        <v>1907.7</v>
-      </c>
+        <v>48547.2</v>
+      </c>
+      <c r="I206" s="53"/>
       <c r="J206" s="48"/>
       <c r="K206" s="49"/>
       <c r="L206" s="0"/>
     </row>
-    <row r="207" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="207">
       <c r="A207" s="44"/>
       <c r="B207" s="45"/>
       <c r="C207" s="46"/>
@@ -7698,31 +7763,39 @@
       <c r="K207" s="49"/>
       <c r="L207" s="0"/>
     </row>
-    <row r="208" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="5"/>
-      <c r="B208" s="25"/>
-      <c r="C208" s="19"/>
-      <c r="D208" s="19"/>
-      <c r="E208" s="13"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="25"/>
-      <c r="H208" s="25"/>
-      <c r="I208" s="25"/>
-      <c r="J208" s="36"/>
-      <c r="K208" s="29"/>
+    <row r="208">
+      <c r="A208" s="44"/>
+      <c r="B208" s="45"/>
+      <c r="C208" s="46"/>
+      <c r="D208" s="46"/>
+      <c r="E208" s="47"/>
+      <c r="F208" s="44"/>
+      <c r="G208" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H208" s="52">
+        <v>1328361.66</v>
+      </c>
+      <c r="I208" s="53">
+        <v>1852.55</v>
+      </c>
+      <c r="J208" s="48"/>
+      <c r="K208" s="49"/>
+      <c r="L208" s="0"/>
     </row>
     <row r="209" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="5"/>
-      <c r="B209" s="25"/>
-      <c r="C209" s="19"/>
-      <c r="D209" s="19"/>
-      <c r="E209" s="13"/>
-      <c r="F209" s="5"/>
-      <c r="G209" s="25"/>
-      <c r="H209" s="25"/>
-      <c r="I209" s="25"/>
-      <c r="J209" s="36"/>
-      <c r="K209" s="29"/>
+      <c r="A209" s="44"/>
+      <c r="B209" s="45"/>
+      <c r="C209" s="46"/>
+      <c r="D209" s="46"/>
+      <c r="E209" s="47"/>
+      <c r="F209" s="44"/>
+      <c r="G209" s="51"/>
+      <c r="H209" s="52"/>
+      <c r="I209" s="53"/>
+      <c r="J209" s="48"/>
+      <c r="K209" s="49"/>
+      <c r="L209" s="0"/>
     </row>
     <row r="210" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A210" s="5"/>
@@ -7958,7 +8031,7 @@
       <c r="J227" s="36"/>
       <c r="K227" s="29"/>
     </row>
-    <row r="228" x14ac:dyDescent="0.2">
+    <row r="228" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A228" s="5"/>
       <c r="B228" s="25"/>
       <c r="C228" s="19"/>
@@ -7971,7 +8044,7 @@
       <c r="J228" s="36"/>
       <c r="K228" s="29"/>
     </row>
-    <row r="229" x14ac:dyDescent="0.2">
+    <row r="229" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A229" s="5"/>
       <c r="B229" s="25"/>
       <c r="C229" s="19"/>
@@ -8284,30 +8357,30 @@
       <c r="K252" s="29"/>
     </row>
     <row r="253" x14ac:dyDescent="0.2">
-      <c r="A253" s="6"/>
-      <c r="B253" s="33"/>
-      <c r="C253" s="20"/>
-      <c r="D253" s="20"/>
-      <c r="E253" s="14"/>
-      <c r="F253" s="6"/>
+      <c r="A253" s="5"/>
+      <c r="B253" s="25"/>
+      <c r="C253" s="19"/>
+      <c r="D253" s="19"/>
+      <c r="E253" s="13"/>
+      <c r="F253" s="5"/>
       <c r="G253" s="25"/>
       <c r="H253" s="25"/>
       <c r="I253" s="25"/>
       <c r="J253" s="36"/>
-      <c r="K253" s="30"/>
+      <c r="K253" s="29"/>
     </row>
     <row r="254" x14ac:dyDescent="0.2">
-      <c r="A254" s="6"/>
-      <c r="B254" s="33"/>
-      <c r="C254" s="20"/>
-      <c r="D254" s="20"/>
-      <c r="E254" s="14"/>
-      <c r="F254" s="6"/>
+      <c r="A254" s="5"/>
+      <c r="B254" s="25"/>
+      <c r="C254" s="19"/>
+      <c r="D254" s="19"/>
+      <c r="E254" s="13"/>
+      <c r="F254" s="5"/>
       <c r="G254" s="25"/>
       <c r="H254" s="25"/>
       <c r="I254" s="25"/>
       <c r="J254" s="36"/>
-      <c r="K254" s="30"/>
+      <c r="K254" s="29"/>
     </row>
     <row r="255" x14ac:dyDescent="0.2">
       <c r="A255" s="6"/>
@@ -16786,7 +16859,7 @@
       <c r="K906" s="30"/>
     </row>
     <row r="907" x14ac:dyDescent="0.2">
-      <c r="A907" s="8"/>
+      <c r="A907" s="6"/>
       <c r="B907" s="33"/>
       <c r="C907" s="20"/>
       <c r="D907" s="20"/>
@@ -16799,7 +16872,7 @@
       <c r="K907" s="30"/>
     </row>
     <row r="908" x14ac:dyDescent="0.2">
-      <c r="A908" s="8"/>
+      <c r="A908" s="6"/>
       <c r="B908" s="33"/>
       <c r="C908" s="20"/>
       <c r="D908" s="20"/>
@@ -18670,19 +18743,31 @@
       <c r="J1051" s="36"/>
       <c r="K1051" s="30"/>
     </row>
-    <row r="1052" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1052" s="4"/>
-      <c r="G1052" s="26"/>
-      <c r="H1052" s="26"/>
-      <c r="I1052" s="26"/>
-      <c r="J1052" s="37"/>
-    </row>
-    <row r="1053" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1053" s="4"/>
-      <c r="G1053" s="26"/>
-      <c r="H1053" s="26"/>
-      <c r="I1053" s="26"/>
-      <c r="J1053" s="37"/>
+    <row r="1052" x14ac:dyDescent="0.2">
+      <c r="A1052" s="8"/>
+      <c r="B1052" s="33"/>
+      <c r="C1052" s="20"/>
+      <c r="D1052" s="20"/>
+      <c r="E1052" s="14"/>
+      <c r="F1052" s="6"/>
+      <c r="G1052" s="25"/>
+      <c r="H1052" s="25"/>
+      <c r="I1052" s="25"/>
+      <c r="J1052" s="36"/>
+      <c r="K1052" s="30"/>
+    </row>
+    <row r="1053" x14ac:dyDescent="0.2">
+      <c r="A1053" s="8"/>
+      <c r="B1053" s="33"/>
+      <c r="C1053" s="20"/>
+      <c r="D1053" s="20"/>
+      <c r="E1053" s="14"/>
+      <c r="F1053" s="6"/>
+      <c r="G1053" s="25"/>
+      <c r="H1053" s="25"/>
+      <c r="I1053" s="25"/>
+      <c r="J1053" s="36"/>
+      <c r="K1053" s="30"/>
     </row>
     <row r="1054" ht="15" x14ac:dyDescent="0.25">
       <c r="A1054" s="4"/>
@@ -22283,12 +22368,14 @@
       <c r="J1567" s="37"/>
     </row>
     <row r="1568" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1568" s="4"/>
       <c r="G1568" s="26"/>
       <c r="H1568" s="26"/>
       <c r="I1568" s="26"/>
       <c r="J1568" s="37"/>
     </row>
     <row r="1569" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1569" s="4"/>
       <c r="G1569" s="26"/>
       <c r="H1569" s="26"/>
       <c r="I1569" s="26"/>
@@ -56223,6 +56310,18 @@
       <c r="H7224" s="26"/>
       <c r="I7224" s="26"/>
       <c r="J7224" s="37"/>
+    </row>
+    <row r="7225" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7225" s="26"/>
+      <c r="H7225" s="26"/>
+      <c r="I7225" s="26"/>
+      <c r="J7225" s="37"/>
+    </row>
+    <row r="7226" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7226" s="26"/>
+      <c r="H7226" s="26"/>
+      <c r="I7226" s="26"/>
+      <c r="J7226" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/latest.xlsx
+++ b/data/latest.xlsx
@@ -177,30 +177,6 @@
     <t>Hours available = 600. Hours remaining = 600</t>
   </si>
   <si>
-    <t>MAXIMMED            </t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
-  </si>
-  <si>
-    <t>SM-E591-0GS-3                     </t>
-  </si>
-  <si>
-    <t>Spring Arm, Med Duty, 2001, 910mm, 29-41lbs, Stop, Axial stop, RAL 9002         </t>
-  </si>
-  <si>
-    <t>SM-O291-0GL-3                     </t>
-  </si>
-  <si>
-    <t>Spring Arm, 3075, STP, 20-35 kg, RAL 9002                                       </t>
-  </si>
-  <si>
-    <t>SM-S391-0GR-3                     </t>
-  </si>
-  <si>
-    <t>Spring arm, Med Duty, 910mm, 3075 w/2075 device end, STP, RAL 9002              </t>
-  </si>
-  <si>
     <t>OASYS               </t>
   </si>
   <si>
@@ -229,9 +205,6 @@
   </si>
   <si>
     <t>09/04/2026</t>
-  </si>
-  <si>
-    <t>OKAY</t>
   </si>
   <si>
     <t>SL-0773-AE-K-1                    </t>
@@ -271,10 +244,26 @@
     <t>09/08/2026</t>
   </si>
   <si>
-    <t>08/18/2026</t>
+    <t>OKAY</t>
+  </si>
+  <si>
+    <t>07/15/2026</t>
   </si>
   <si>
     <t>09/11/2026</t>
+  </si>
+  <si>
+    <t>C-2-AW-PN                         </t>
+  </si>
+  <si>
+    <t>Single Ceiling Drop Tube, 3P Slip Ring and Harness, 900mm                       </t>
+  </si>
+  <si>
+    <t>DOCK DATE FOR LINE 1 - SEPTEMBER 18, 2026
+DOCKDATE FOR LINE 2 - OCTOBER 6, 2026</t>
+  </si>
+  <si>
+    <t>08/18/2026</t>
   </si>
   <si>
     <t>CA1-02A-01-W0                     </t>
@@ -284,18 +273,6 @@
   </si>
   <si>
     <t>DOCK DATE - SEPTEMBER 18, 2026</t>
-  </si>
-  <si>
-    <t>08/28/2026</t>
-  </si>
-  <si>
-    <t>09/14/2026</t>
-  </si>
-  <si>
-    <t>SM-B091-0GS-3                     </t>
-  </si>
-  <si>
-    <t>Spring Arm, Med Duty, 910mm length, 2001, 6-12 kg, No electric, RAL 9002        </t>
   </si>
   <si>
     <t>08/20/2026</t>
@@ -410,6 +387,15 @@
     <t>3P SLIP RING - FEMALE                                                           </t>
   </si>
   <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>CA2-06A-03-W0                     </t>
+  </si>
+  <si>
+    <t>Dual Central Axis, 700/850mm, 3P/3P, RAL 9010                                   </t>
+  </si>
+  <si>
     <t>DERUNGSLICHT-EUR    </t>
   </si>
   <si>
@@ -422,9 +408,6 @@
     <t>3P Slip Ring - Male (with wiring components)                                    </t>
   </si>
   <si>
-    <t>07/15/2026</t>
-  </si>
-  <si>
     <t>09/29/2026</t>
   </si>
   <si>
@@ -432,15 +415,6 @@
   </si>
   <si>
     <t>Light Duty Ceiling Mount, no Harness, no Drop tube, ULD flange, Dome RAL 9010   </t>
-  </si>
-  <si>
-    <t>DOCK DATE - OCTOBER 6, 2026</t>
-  </si>
-  <si>
-    <t>C-2-AW-PN                         </t>
-  </si>
-  <si>
-    <t>Single Ceiling Drop Tube, 3P Slip Ring and Harness, 900mm                       </t>
   </si>
   <si>
     <t>08/12/2026</t>
@@ -479,6 +453,12 @@
     <t>Spring Arm, Med Duty, 910mm, TM2001, Load 17.5kg, Stop, RAL 9010                </t>
   </si>
   <si>
+    <t>MAXIMMED            </t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
     <t>EMM-30SVL-SX-0G                   </t>
   </si>
   <si>
@@ -489,6 +469,12 @@
   </si>
   <si>
     <t>Dual Monitor Yoke, 3075 coupler, 9002                                           </t>
+  </si>
+  <si>
+    <t>SM-S391-0GR-3                     </t>
+  </si>
+  <si>
+    <t>Spring arm, Med Duty, 910mm, 3075 w/2075 device end, STP, RAL 9002              </t>
   </si>
   <si>
     <t>SM-B691-9GJ-J                     </t>
@@ -509,6 +495,43 @@
     <t>SA, 2075, 9P, 10 -20 kg, 9002                                                   </t>
   </si>
   <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
+  </si>
+  <si>
+    <t>SM-B691-0GJ-J                     </t>
+  </si>
+  <si>
+    <t>SA, 2075, STP, 3.5 - 13 kg, 9002                                                </t>
+  </si>
+  <si>
+    <t>DOCK DATE - NOVEMBER 1, 2026
+**Ship Door to Door via Ocean Min 4 Pallets**</t>
+  </si>
+  <si>
+    <t>September, 2026</t>
+  </si>
+  <si>
+    <t>Hours available = 600. Hours remaining = -62.3</t>
+  </si>
+  <si>
+    <t>SM-E479-3GJ-J                     </t>
+  </si>
+  <si>
+    <t>SA, 2075 LCH, 3P, 9002                                                          </t>
+  </si>
+  <si>
+    <t>SM-E491-0GJ-J                     </t>
+  </si>
+  <si>
+    <t>SM-O191-0GL-J                     </t>
+  </si>
+  <si>
+    <t>SA, 3075, STP, 20-30 kg, 9002                                                   </t>
+  </si>
+  <si>
     <t>OQTIS               </t>
   </si>
   <si>
@@ -524,12 +547,6 @@
     <t>SHIP DATE - SEPTEMBER 30, 2026</t>
   </si>
   <si>
-    <t>September, 2026</t>
-  </si>
-  <si>
-    <t>Hours available = 600. Hours remaining = -62.3</t>
-  </si>
-  <si>
     <t>10/07/2026</t>
   </si>
   <si>
@@ -540,6 +557,18 @@
   </si>
   <si>
     <t>NEW DOCK DATE - OCTOBER 14, 2026</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t>DOCK DATE - OCTOBER 15, 2026</t>
+  </si>
+  <si>
+    <t>HK-SAL-EXT                        </t>
+  </si>
+  <si>
+    <t>Extension Arm Hardware Kit                                                      </t>
   </si>
   <si>
     <t>06/29/2026</t>
@@ -592,6 +621,10 @@
     <t>C-0-XW-X4                         </t>
   </si>
   <si>
+    <t>SHIP DATE - OCTOBER 13, 2026
+Increased piece price by 9.5 EUR for Door to door shipping.</t>
+  </si>
+  <si>
     <t>C-2-AW-P4                         </t>
   </si>
   <si>
@@ -604,10 +637,55 @@
     <t>Spring Arm, Light Duty, 720mm arm (straight), 800mm ext arm, 7kg, 3P, 9010, N300</t>
   </si>
   <si>
+    <t>MEDSOLUTIONS        </t>
+  </si>
+  <si>
+    <t>10/15/2026</t>
+  </si>
+  <si>
+    <t>MMF-300-G2-XXX-X                  </t>
+  </si>
+  <si>
+    <t>Medium Duty Floor Stand, No Electrical, RAL 9002                                </t>
+  </si>
+  <si>
+    <t>SHIP DATE - OCTOBER 15, 2026</t>
+  </si>
+  <si>
+    <t>NS-WIREFEE                        </t>
+  </si>
+  <si>
+    <t>Wire Transfer Fee                                                               </t>
+  </si>
+  <si>
+    <t>SM-B091-0GB-X                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 2001 (FS w/ Rad Shield), Stop, RAL 9002                   </t>
+  </si>
+  <si>
     <t>10/16/2026</t>
   </si>
   <si>
     <t>DOCK DATE - OCTOBER 23, 2026</t>
+  </si>
+  <si>
+    <t>10/28/2026</t>
+  </si>
+  <si>
+    <t>SHIP DATE -</t>
+  </si>
+  <si>
+    <t>SM-G291-0WR-X                     </t>
+  </si>
+  <si>
+    <t>Spring Arm, Med Duty, 910mm, 3075 BK5/2075 FR5, Load 17.5kg, Stop, RAL 9010     </t>
+  </si>
+  <si>
+    <t>SM-G291-0WT-X                     </t>
+  </si>
+  <si>
+    <t>Spring arm, Med Duty, 910mm, TM3001 w/2001 device end, Load 17.5kg, STP, 9010   </t>
   </si>
   <si>
     <t>10/29/2026</t>
@@ -643,7 +721,7 @@
     <t>October, 2026</t>
   </si>
   <si>
-    <t>Hours available = 600. Hours remaining = 346.7</t>
+    <t>Hours available = 600. Hours remaining = -360.8</t>
   </si>
   <si>
     <t>11/13/2026</t>
@@ -742,12 +820,6 @@
     <t>FORECAST</t>
   </si>
   <si>
-    <t>CA2-06A-03-W0                     </t>
-  </si>
-  <si>
-    <t>Dual Central Axis, 700/850mm, 3P/3P, RAL 9010                                   </t>
-  </si>
-  <si>
     <t>08/18/2025</t>
   </si>
   <si>
@@ -777,21 +849,6 @@
   </si>
   <si>
     <t>Spring Arm, Med Duty, 2075, Stop, 5.9-12kg, 9010                                </t>
-  </si>
-  <si>
-    <t>CIUSSSCN            </t>
-  </si>
-  <si>
-    <t>11/26/2025</t>
-  </si>
-  <si>
-    <t>SA-M-CV-F-WHT                     </t>
-  </si>
-  <si>
-    <t>Flap Cover - Apollo White                                                       </t>
-  </si>
-  <si>
-    <t>SHIP DATE - DECEMBER 12, 2025</t>
   </si>
   <si>
     <t>07/05/2024</t>
@@ -2176,7 +2233,7 @@
         <v>51</v>
       </c>
       <c r="B22" s="45">
-        <v>0000107011</v>
+        <v>0000107009</v>
       </c>
       <c r="C22" t="s" s="46">
         <v>52</v>
@@ -2191,10 +2248,10 @@
         <v>53</v>
       </c>
       <c r="G22" s="51">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H22" s="52">
-        <v>499.25</v>
+        <v>0</v>
       </c>
       <c r="I22" t="s" s="53">
         <v>18</v>
@@ -2202,9 +2259,7 @@
       <c r="J22" t="s" s="48">
         <v>54</v>
       </c>
-      <c r="K22" t="s" s="49">
-        <v>47</v>
-      </c>
+      <c r="K22" s="49"/>
       <c r="L22" s="0"/>
     </row>
     <row r="23">
@@ -2212,7 +2267,7 @@
         <v>51</v>
       </c>
       <c r="B23" s="45">
-        <v>0000107011</v>
+        <v>0000107009</v>
       </c>
       <c r="C23" t="s" s="46">
         <v>52</v>
@@ -2227,20 +2282,18 @@
         <v>55</v>
       </c>
       <c r="G23" s="51">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H23" s="52">
-        <v>1066.4</v>
-      </c>
-      <c r="I23" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="53">
+        <v>1</v>
       </c>
       <c r="J23" t="s" s="48">
-        <v>56</v>
-      </c>
-      <c r="K23" t="s" s="49">
-        <v>47</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="K23" s="49"/>
       <c r="L23" s="0"/>
     </row>
     <row r="24">
@@ -2248,7 +2301,7 @@
         <v>51</v>
       </c>
       <c r="B24" s="45">
-        <v>0000107011</v>
+        <v>0000107009</v>
       </c>
       <c r="C24" t="s" s="46">
         <v>52</v>
@@ -2260,22 +2313,22 @@
         <v>16</v>
       </c>
       <c r="F24" t="s" s="44">
+        <v>56</v>
+      </c>
+      <c r="G24" s="51">
+        <v>1</v>
+      </c>
+      <c r="H24" s="52">
+        <v>0</v>
+      </c>
+      <c r="I24" s="53">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s" s="48">
         <v>57</v>
       </c>
-      <c r="G24" s="51">
-        <v>40</v>
-      </c>
-      <c r="H24" s="52">
-        <v>1066.4</v>
-      </c>
-      <c r="I24" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J24" t="s" s="48">
+      <c r="K24" t="s" s="49">
         <v>58</v>
-      </c>
-      <c r="K24" t="s" s="49">
-        <v>47</v>
       </c>
       <c r="L24" s="0"/>
     </row>
@@ -2285,70 +2338,66 @@
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
       <c r="E25" s="47"/>
-      <c r="F25" s="44"/>
+      <c r="F25" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G25" t="s" s="51">
         <v>31</v>
       </c>
       <c r="H25" s="52">
-        <v>63145.25</v>
-      </c>
-      <c r="I25" s="53"/>
-      <c r="J25" s="48"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K25" s="49"/>
       <c r="L25" s="0"/>
     </row>
     <row r="26">
-      <c r="A26" t="s" s="44">
-        <v>59</v>
-      </c>
-      <c r="B26" s="45">
-        <v>0000107009</v>
-      </c>
-      <c r="C26" t="s" s="46">
-        <v>60</v>
-      </c>
-      <c r="D26" t="s" s="46">
-        <v>44</v>
-      </c>
-      <c r="E26" t="s" s="47">
-        <v>16</v>
-      </c>
-      <c r="F26" t="s" s="44">
-        <v>61</v>
-      </c>
-      <c r="G26" s="51">
-        <v>1</v>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" t="s" s="51">
+        <v>48</v>
       </c>
       <c r="H26" s="52">
         <v>0</v>
       </c>
-      <c r="I26" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J26" t="s" s="48">
-        <v>62</v>
+      <c r="I26" s="53">
+        <v>2</v>
+      </c>
+      <c r="J26" s="48" t="s">
+        <v>65</v>
       </c>
       <c r="K26" s="49"/>
       <c r="L26" s="0"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="44">
+        <v>51</v>
+      </c>
+      <c r="B27" s="45">
+        <v>0000107032</v>
+      </c>
+      <c r="C27" t="s" s="46">
         <v>59</v>
       </c>
-      <c r="B27" s="45">
-        <v>0000107009</v>
-      </c>
-      <c r="C27" t="s" s="46">
+      <c r="D27" t="s" s="46">
         <v>60</v>
-      </c>
-      <c r="D27" t="s" s="46">
-        <v>44</v>
       </c>
       <c r="E27" t="s" s="47">
         <v>16</v>
       </c>
       <c r="F27" t="s" s="44">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G27" s="51">
         <v>1</v>
@@ -2356,73 +2405,69 @@
       <c r="H27" s="52">
         <v>0</v>
       </c>
-      <c r="I27" s="53">
-        <v>1</v>
+      <c r="I27" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J27" t="s" s="48">
-        <v>25</v>
-      </c>
-      <c r="K27" s="49"/>
+        <v>62</v>
+      </c>
+      <c r="K27" t="s" s="49">
+        <v>63</v>
+      </c>
       <c r="L27" s="0"/>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="44">
-        <v>59</v>
-      </c>
-      <c r="B28" s="45">
-        <v>0000107009</v>
-      </c>
-      <c r="C28" t="s" s="46">
-        <v>60</v>
-      </c>
-      <c r="D28" t="s" s="46">
-        <v>44</v>
-      </c>
-      <c r="E28" t="s" s="47">
-        <v>16</v>
-      </c>
-      <c r="F28" t="s" s="44">
-        <v>64</v>
-      </c>
-      <c r="G28" s="51">
-        <v>1</v>
+      <c r="A28" s="44"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="44"/>
+      <c r="G28" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H28" s="52">
         <v>0</v>
       </c>
-      <c r="I28" s="53">
-        <v>1</v>
-      </c>
-      <c r="J28" t="s" s="48">
-        <v>65</v>
-      </c>
-      <c r="K28" t="s" s="49">
+      <c r="I28" s="53"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="0"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B29" s="45">
+        <v>0000106882</v>
+      </c>
+      <c r="C29" t="s" s="46">
         <v>66</v>
       </c>
-      <c r="L28" s="0"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="44"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="47"/>
+      <c r="D29" t="s" s="46">
+        <v>67</v>
+      </c>
+      <c r="E29" t="s" s="47">
+        <v>16</v>
+      </c>
       <c r="F29" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G29" t="s" s="51">
-        <v>31</v>
+        <v>68</v>
+      </c>
+      <c r="G29" s="51">
+        <v>48</v>
       </c>
       <c r="H29" s="52">
-        <v>0</v>
-      </c>
-      <c r="I29" s="53" t="s">
-        <v>18</v>
+        <v>315.49</v>
+      </c>
+      <c r="I29" s="53">
+        <v>72</v>
       </c>
       <c r="J29" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K29" s="49"/>
+        <v>69</v>
+      </c>
+      <c r="K29" t="s" s="49">
+        <v>70</v>
+      </c>
       <c r="L29" s="0"/>
     </row>
     <row r="30">
@@ -2431,42 +2476,36 @@
       <c r="C30" s="46"/>
       <c r="D30" s="46"/>
       <c r="E30" s="47"/>
-      <c r="F30" s="44" t="s">
-        <v>73</v>
-      </c>
+      <c r="F30" s="44"/>
       <c r="G30" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H30" s="52">
-        <v>63145.25</v>
-      </c>
-      <c r="I30" s="53">
-        <v>2</v>
-      </c>
-      <c r="J30" s="48" t="s">
-        <v>74</v>
-      </c>
+        <v>15143.52</v>
+      </c>
+      <c r="I30" s="53"/>
+      <c r="J30" s="48"/>
       <c r="K30" s="49"/>
       <c r="L30" s="0"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="44">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B31" s="45">
-        <v>0000107032</v>
+        <v>0000107035</v>
       </c>
       <c r="C31" t="s" s="46">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s" s="46">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E31" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s" s="44">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G31" s="51">
         <v>1</v>
@@ -2478,11 +2517,9 @@
         <v>18</v>
       </c>
       <c r="J31" t="s" s="48">
-        <v>71</v>
-      </c>
-      <c r="K31" t="s" s="49">
-        <v>72</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="K31" s="49"/>
       <c r="L31" s="0"/>
     </row>
     <row r="32">
@@ -2508,34 +2545,34 @@
         <v>42</v>
       </c>
       <c r="B33" s="45">
-        <v>0000106882</v>
+        <v>0000106998</v>
       </c>
       <c r="C33" t="s" s="46">
+        <v>74</v>
+      </c>
+      <c r="D33" t="s" s="46">
         <v>75</v>
       </c>
-      <c r="D33" t="s" s="46">
+      <c r="E33" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F33" t="s" s="44">
         <v>76</v>
       </c>
-      <c r="E33" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F33" t="s" s="44">
+      <c r="G33" s="51">
+        <v>15</v>
+      </c>
+      <c r="H33" s="52">
+        <v>254.17</v>
+      </c>
+      <c r="I33" s="53">
+        <v>7.5</v>
+      </c>
+      <c r="J33" t="s" s="48">
         <v>77</v>
       </c>
-      <c r="G33" s="51">
-        <v>48</v>
-      </c>
-      <c r="H33" s="52">
-        <v>315.49</v>
-      </c>
-      <c r="I33" s="53">
-        <v>72</v>
-      </c>
-      <c r="J33" t="s" s="48">
+      <c r="K33" t="s" s="49">
         <v>78</v>
-      </c>
-      <c r="K33" t="s" s="49">
-        <v>79</v>
       </c>
       <c r="L33" s="0"/>
     </row>
@@ -2550,7 +2587,7 @@
         <v>31</v>
       </c>
       <c r="H34" s="52">
-        <v>15143.52</v>
+        <v>3812.55</v>
       </c>
       <c r="I34" s="53"/>
       <c r="J34" s="48"/>
@@ -2559,36 +2596,38 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="44">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B35" s="45">
-        <v>0000107035</v>
+        <v>0000107024</v>
       </c>
       <c r="C35" t="s" s="46">
+        <v>79</v>
+      </c>
+      <c r="D35" t="s" s="46">
+        <v>75</v>
+      </c>
+      <c r="E35" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F35" t="s" s="44">
         <v>80</v>
-      </c>
-      <c r="D35" t="s" s="46">
-        <v>81</v>
-      </c>
-      <c r="E35" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F35" t="s" s="44">
-        <v>70</v>
       </c>
       <c r="G35" s="51">
         <v>1</v>
       </c>
       <c r="H35" s="52">
-        <v>0</v>
+        <v>940.21</v>
       </c>
       <c r="I35" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J35" t="s" s="48">
-        <v>71</v>
-      </c>
-      <c r="K35" s="49"/>
+        <v>81</v>
+      </c>
+      <c r="K35" t="s" s="49">
+        <v>82</v>
+      </c>
       <c r="L35" s="0"/>
     </row>
     <row r="36">
@@ -2602,7 +2641,7 @@
         <v>31</v>
       </c>
       <c r="H36" s="52">
-        <v>0</v>
+        <v>940.21</v>
       </c>
       <c r="I36" s="53"/>
       <c r="J36" s="48"/>
@@ -2614,34 +2653,34 @@
         <v>42</v>
       </c>
       <c r="B37" s="45">
-        <v>0000107024</v>
+        <v>0000107025</v>
       </c>
       <c r="C37" t="s" s="46">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s" s="46">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E37" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F37" t="s" s="44">
+        <v>68</v>
+      </c>
+      <c r="G37" s="51">
+        <v>24</v>
+      </c>
+      <c r="H37" s="52">
+        <v>317.95</v>
+      </c>
+      <c r="I37" s="53">
+        <v>36</v>
+      </c>
+      <c r="J37" t="s" s="48">
         <v>69</v>
       </c>
-      <c r="F37" t="s" s="44">
-        <v>84</v>
-      </c>
-      <c r="G37" s="51">
-        <v>1</v>
-      </c>
-      <c r="H37" s="52">
-        <v>940.21</v>
-      </c>
-      <c r="I37" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J37" t="s" s="48">
+      <c r="K37" t="s" s="49">
         <v>85</v>
-      </c>
-      <c r="K37" t="s" s="49">
-        <v>86</v>
       </c>
       <c r="L37" s="0"/>
     </row>
@@ -2656,7 +2695,7 @@
         <v>31</v>
       </c>
       <c r="H38" s="52">
-        <v>940.21</v>
+        <v>7630.8</v>
       </c>
       <c r="I38" s="53"/>
       <c r="J38" s="48"/>
@@ -2665,36 +2704,38 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="44">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B39" s="45">
-        <v>0000107033</v>
+        <v>0000106778</v>
       </c>
       <c r="C39" t="s" s="46">
         <v>87</v>
       </c>
       <c r="D39" t="s" s="46">
+        <v>84</v>
+      </c>
+      <c r="E39" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F39" t="s" s="44">
         <v>88</v>
       </c>
-      <c r="E39" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F39" t="s" s="44">
-        <v>89</v>
-      </c>
       <c r="G39" s="51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H39" s="52">
-        <v>502.91</v>
+        <v>2250</v>
       </c>
       <c r="I39" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J39" t="s" s="48">
+        <v>89</v>
+      </c>
+      <c r="K39" t="s" s="49">
         <v>90</v>
       </c>
-      <c r="K39" s="49"/>
       <c r="L39" s="0"/>
     </row>
     <row r="40">
@@ -2708,7 +2749,7 @@
         <v>31</v>
       </c>
       <c r="H40" s="52">
-        <v>4023.28</v>
+        <v>11250</v>
       </c>
       <c r="I40" s="53"/>
       <c r="J40" s="48"/>
@@ -2717,37 +2758,37 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="44">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="B41" s="45">
-        <v>0000107025</v>
+        <v>0000106978</v>
       </c>
       <c r="C41" t="s" s="46">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s" s="46">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E41" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F41" t="s" s="44">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="G41" s="51">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="H41" s="52">
-        <v>317.95</v>
-      </c>
-      <c r="I41" s="53">
-        <v>36</v>
+        <v>75</v>
+      </c>
+      <c r="I41" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J41" t="s" s="48">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="49">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L41" s="0"/>
     </row>
@@ -2762,7 +2803,7 @@
         <v>31</v>
       </c>
       <c r="H42" s="52">
-        <v>7630.8</v>
+        <v>8550</v>
       </c>
       <c r="I42" s="53"/>
       <c r="J42" s="48"/>
@@ -2771,91 +2812,109 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="44">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B43" s="45">
-        <v>0000106778</v>
+        <v>0000107030</v>
       </c>
       <c r="C43" t="s" s="46">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s" s="46">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E43" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F43" t="s" s="44">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G43" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H43" s="52">
-        <v>2250</v>
+        <v>498.31</v>
       </c>
       <c r="I43" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J43" t="s" s="48">
+        <v>100</v>
+      </c>
+      <c r="K43" t="s" s="49">
+        <v>101</v>
+      </c>
+      <c r="L43" s="0"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="44">
+        <v>96</v>
+      </c>
+      <c r="B44" s="45">
+        <v>0000107030</v>
+      </c>
+      <c r="C44" t="s" s="46">
         <v>97</v>
       </c>
-      <c r="K43" t="s" s="49">
+      <c r="D44" t="s" s="46">
         <v>98</v>
       </c>
-      <c r="L43" s="0"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="44"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="44"/>
-      <c r="G44" t="s" s="51">
-        <v>31</v>
+      <c r="E44" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F44" t="s" s="44">
+        <v>102</v>
+      </c>
+      <c r="G44" s="51">
+        <v>1</v>
       </c>
       <c r="H44" s="52">
-        <v>11250</v>
-      </c>
-      <c r="I44" s="53"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="49"/>
+        <v>449.86</v>
+      </c>
+      <c r="I44" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J44" t="s" s="48">
+        <v>103</v>
+      </c>
+      <c r="K44" t="s" s="49">
+        <v>101</v>
+      </c>
       <c r="L44" s="0"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="44">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B45" s="45">
-        <v>0000106978</v>
+        <v>0000107030</v>
       </c>
       <c r="C45" t="s" s="46">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s" s="46">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F45" t="s" s="44">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G45" s="51">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="H45" s="52">
-        <v>75</v>
+        <v>588.28</v>
       </c>
       <c r="I45" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J45" t="s" s="48">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K45" t="s" s="49">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L45" s="0"/>
     </row>
@@ -2870,7 +2929,7 @@
         <v>31</v>
       </c>
       <c r="H46" s="52">
-        <v>8550</v>
+        <v>1536.45</v>
       </c>
       <c r="I46" s="53"/>
       <c r="J46" s="48"/>
@@ -2879,109 +2938,91 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="44">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B47" s="45">
-        <v>0000107030</v>
+        <v>0000106977</v>
       </c>
       <c r="C47" t="s" s="46">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s" s="46">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F47" t="s" s="44">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G47" s="51">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H47" s="52">
-        <v>498.31</v>
+        <v>563.43</v>
       </c>
       <c r="I47" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J47" t="s" s="48">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K47" t="s" s="49">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L47" s="0"/>
     </row>
     <row r="48">
-      <c r="A48" t="s" s="44">
-        <v>104</v>
-      </c>
-      <c r="B48" s="45">
-        <v>0000107030</v>
-      </c>
-      <c r="C48" t="s" s="46">
-        <v>105</v>
-      </c>
-      <c r="D48" t="s" s="46">
-        <v>106</v>
-      </c>
-      <c r="E48" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F48" t="s" s="44">
-        <v>110</v>
-      </c>
-      <c r="G48" s="51">
-        <v>1</v>
+      <c r="A48" s="44"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="44"/>
+      <c r="G48" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H48" s="52">
-        <v>449.86</v>
-      </c>
-      <c r="I48" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J48" t="s" s="48">
-        <v>111</v>
-      </c>
-      <c r="K48" t="s" s="49">
-        <v>109</v>
-      </c>
+        <v>5634.3</v>
+      </c>
+      <c r="I48" s="53"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="49"/>
       <c r="L48" s="0"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="44">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="B49" s="45">
-        <v>0000107030</v>
+        <v>0000106968</v>
       </c>
       <c r="C49" t="s" s="46">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D49" t="s" s="46">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E49" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F49" t="s" s="44">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G49" s="51">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="H49" s="52">
-        <v>588.28</v>
-      </c>
-      <c r="I49" t="s" s="53">
-        <v>18</v>
+        <v>375.19</v>
+      </c>
+      <c r="I49" s="53">
+        <v>87.5</v>
       </c>
       <c r="J49" t="s" s="48">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K49" t="s" s="49">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L49" s="0"/>
     </row>
@@ -2996,7 +3037,7 @@
         <v>31</v>
       </c>
       <c r="H50" s="52">
-        <v>1536.45</v>
+        <v>26263.3</v>
       </c>
       <c r="I50" s="53"/>
       <c r="J50" s="48"/>
@@ -3005,37 +3046,37 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="44">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="B51" s="45">
-        <v>0000106977</v>
+        <v>0000107018</v>
       </c>
       <c r="C51" t="s" s="46">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s" s="46">
+        <v>113</v>
+      </c>
+      <c r="E51" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F51" t="s" s="44">
+        <v>118</v>
+      </c>
+      <c r="G51" s="51">
+        <v>100</v>
+      </c>
+      <c r="H51" s="52">
+        <v>11.36</v>
+      </c>
+      <c r="I51" s="53">
+        <v>3.3</v>
+      </c>
+      <c r="J51" t="s" s="48">
+        <v>119</v>
+      </c>
+      <c r="K51" t="s" s="49">
         <v>116</v>
-      </c>
-      <c r="E51" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F51" t="s" s="44">
-        <v>117</v>
-      </c>
-      <c r="G51" s="51">
-        <v>10</v>
-      </c>
-      <c r="H51" s="52">
-        <v>563.43</v>
-      </c>
-      <c r="I51" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J51" t="s" s="48">
-        <v>118</v>
-      </c>
-      <c r="K51" t="s" s="49">
-        <v>119</v>
       </c>
       <c r="L51" s="0"/>
     </row>
@@ -3050,7 +3091,7 @@
         <v>31</v>
       </c>
       <c r="H52" s="52">
-        <v>5634.3</v>
+        <v>1136</v>
       </c>
       <c r="I52" s="53"/>
       <c r="J52" s="48"/>
@@ -3062,34 +3103,34 @@
         <v>42</v>
       </c>
       <c r="B53" s="45">
-        <v>0000106968</v>
+        <v>0000107038</v>
       </c>
       <c r="C53" t="s" s="46">
         <v>120</v>
       </c>
       <c r="D53" t="s" s="46">
+        <v>113</v>
+      </c>
+      <c r="E53" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F53" t="s" s="44">
         <v>121</v>
       </c>
-      <c r="E53" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F53" t="s" s="44">
+      <c r="G53" s="51">
+        <v>1</v>
+      </c>
+      <c r="H53" s="52">
+        <v>1838.23</v>
+      </c>
+      <c r="I53" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J53" t="s" s="48">
         <v>122</v>
       </c>
-      <c r="G53" s="51">
-        <v>70</v>
-      </c>
-      <c r="H53" s="52">
-        <v>375.19</v>
-      </c>
-      <c r="I53" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J53" t="s" s="48">
-        <v>123</v>
-      </c>
       <c r="K53" t="s" s="49">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="L53" s="0"/>
     </row>
@@ -3104,7 +3145,7 @@
         <v>31</v>
       </c>
       <c r="H54" s="52">
-        <v>26263.3</v>
+        <v>1838.23</v>
       </c>
       <c r="I54" s="53"/>
       <c r="J54" s="48"/>
@@ -3113,37 +3154,37 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="44">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="B55" s="45">
-        <v>0000107018</v>
+        <v>0000106990</v>
       </c>
       <c r="C55" t="s" s="46">
+        <v>124</v>
+      </c>
+      <c r="D55" t="s" s="46">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F55" t="s" s="44">
         <v>125</v>
       </c>
-      <c r="D55" t="s" s="46">
-        <v>121</v>
-      </c>
-      <c r="E55" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F55" t="s" s="44">
+      <c r="G55" s="51">
+        <v>504</v>
+      </c>
+      <c r="H55" s="52">
+        <v>22.84</v>
+      </c>
+      <c r="I55" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J55" t="s" s="48">
         <v>126</v>
       </c>
-      <c r="G55" s="51">
-        <v>100</v>
-      </c>
-      <c r="H55" s="52">
-        <v>11.36</v>
-      </c>
-      <c r="I55" s="53">
-        <v>3.3</v>
-      </c>
-      <c r="J55" t="s" s="48">
-        <v>127</v>
-      </c>
       <c r="K55" t="s" s="49">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="L55" s="0"/>
     </row>
@@ -3158,7 +3199,7 @@
         <v>31</v>
       </c>
       <c r="H56" s="52">
-        <v>1136</v>
+        <v>11511.36</v>
       </c>
       <c r="I56" s="53"/>
       <c r="J56" s="48"/>
@@ -3167,37 +3208,37 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B57" s="45">
+        <v>0000106998</v>
+      </c>
+      <c r="C57" t="s" s="46">
+        <v>74</v>
+      </c>
+      <c r="D57" t="s" s="46">
+        <v>127</v>
+      </c>
+      <c r="E57" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F57" t="s" s="44">
         <v>128</v>
       </c>
-      <c r="B57" s="45">
-        <v>0000106990</v>
-      </c>
-      <c r="C57" t="s" s="46">
-        <v>129</v>
-      </c>
-      <c r="D57" t="s" s="46">
-        <v>121</v>
-      </c>
-      <c r="E57" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F57" t="s" s="44">
-        <v>130</v>
-      </c>
       <c r="G57" s="51">
-        <v>504</v>
+        <v>50</v>
       </c>
       <c r="H57" s="52">
-        <v>22.84</v>
+        <v>235.23</v>
       </c>
       <c r="I57" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J57" t="s" s="48">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K57" t="s" s="49">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="L57" s="0"/>
     </row>
@@ -3212,7 +3253,7 @@
         <v>31</v>
       </c>
       <c r="H58" s="52">
-        <v>11511.36</v>
+        <v>11761.5</v>
       </c>
       <c r="I58" s="53"/>
       <c r="J58" s="48"/>
@@ -3221,73 +3262,73 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="44">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="B59" s="45">
-        <v>0000106998</v>
+        <v>0000107014</v>
       </c>
       <c r="C59" t="s" s="46">
+        <v>130</v>
+      </c>
+      <c r="D59" t="s" s="46">
+        <v>131</v>
+      </c>
+      <c r="E59" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F59" t="s" s="44">
         <v>132</v>
       </c>
-      <c r="D59" t="s" s="46">
-        <v>133</v>
-      </c>
-      <c r="E59" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F59" t="s" s="44">
-        <v>134</v>
-      </c>
       <c r="G59" s="51">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="H59" s="52">
-        <v>234.56</v>
+        <v>195.71</v>
       </c>
       <c r="I59" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J59" t="s" s="48">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K59" t="s" s="49">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L59" s="0"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="44">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="B60" s="45">
-        <v>0000106998</v>
+        <v>0000107014</v>
       </c>
       <c r="C60" t="s" s="46">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D60" t="s" s="46">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E60" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F60" t="s" s="44">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G60" s="51">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H60" s="52">
-        <v>253.45</v>
+        <v>286.99</v>
       </c>
       <c r="I60" s="53">
-        <v>7.5</v>
+        <v>225</v>
       </c>
       <c r="J60" t="s" s="48">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K60" t="s" s="49">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L60" s="0"/>
     </row>
@@ -3302,7 +3343,7 @@
         <v>31</v>
       </c>
       <c r="H61" s="52">
-        <v>15529.75</v>
+        <v>82188.96</v>
       </c>
       <c r="I61" s="53"/>
       <c r="J61" s="48"/>
@@ -3311,73 +3352,73 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="44">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="B62" s="45">
-        <v>0000107014</v>
+        <v>0000107012</v>
       </c>
       <c r="C62" t="s" s="46">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D62" t="s" s="46">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E62" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F62" t="s" s="44">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G62" s="51">
-        <v>156</v>
+        <v>7</v>
       </c>
       <c r="H62" s="52">
-        <v>195.71</v>
+        <v>622.67</v>
       </c>
       <c r="I62" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J62" t="s" s="48">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K62" t="s" s="49">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="L62" s="0"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="44">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="B63" s="45">
-        <v>0000107014</v>
+        <v>0000107012</v>
       </c>
       <c r="C63" t="s" s="46">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D63" t="s" s="46">
+        <v>131</v>
+      </c>
+      <c r="E63" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F63" t="s" s="44">
         <v>140</v>
       </c>
-      <c r="E63" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F63" t="s" s="44">
-        <v>144</v>
-      </c>
       <c r="G63" s="51">
-        <v>180</v>
+        <v>7</v>
       </c>
       <c r="H63" s="52">
-        <v>286.99</v>
-      </c>
-      <c r="I63" s="53">
-        <v>225</v>
+        <v>592.02</v>
+      </c>
+      <c r="I63" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J63" t="s" s="48">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K63" t="s" s="49">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="L63" s="0"/>
     </row>
@@ -3392,7 +3433,7 @@
         <v>31</v>
       </c>
       <c r="H64" s="52">
-        <v>82188.96</v>
+        <v>8502.83</v>
       </c>
       <c r="I64" s="53"/>
       <c r="J64" s="48"/>
@@ -3401,182 +3442,200 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="44">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="B65" s="45">
-        <v>0000107012</v>
+        <v>0000107011</v>
       </c>
       <c r="C65" t="s" s="46">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D65" t="s" s="46">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E65" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F65" t="s" s="44">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G65" s="51">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="H65" s="52">
-        <v>622.67</v>
+        <v>1191.28</v>
       </c>
       <c r="I65" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J65" t="s" s="48">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K65" t="s" s="49">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="L65" s="0"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="44">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="B66" s="45">
-        <v>0000107012</v>
+        <v>0000107011</v>
       </c>
       <c r="C66" t="s" s="46">
+        <v>143</v>
+      </c>
+      <c r="D66" t="s" s="46">
+        <v>131</v>
+      </c>
+      <c r="E66" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F66" t="s" s="44">
         <v>146</v>
       </c>
-      <c r="D66" t="s" s="46">
-        <v>140</v>
-      </c>
-      <c r="E66" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F66" t="s" s="44">
-        <v>149</v>
-      </c>
       <c r="G66" s="51">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H66" s="52">
-        <v>592.02</v>
+        <v>1872.05</v>
       </c>
       <c r="I66" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J66" t="s" s="48">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K66" t="s" s="49">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="L66" s="0"/>
     </row>
     <row r="67">
-      <c r="A67" s="44"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="46"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="44"/>
-      <c r="G67" t="s" s="51">
+      <c r="A67" t="s" s="44">
+        <v>142</v>
+      </c>
+      <c r="B67" s="45">
+        <v>0000107011</v>
+      </c>
+      <c r="C67" t="s" s="46">
+        <v>143</v>
+      </c>
+      <c r="D67" t="s" s="46">
+        <v>131</v>
+      </c>
+      <c r="E67" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F67" t="s" s="44">
+        <v>148</v>
+      </c>
+      <c r="G67" s="51">
+        <v>40</v>
+      </c>
+      <c r="H67" s="52">
+        <v>1074.38</v>
+      </c>
+      <c r="I67" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J67" t="s" s="48">
+        <v>149</v>
+      </c>
+      <c r="K67" t="s" s="49">
+        <v>47</v>
+      </c>
+      <c r="L67" s="0"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="44"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="46"/>
+      <c r="D68" s="46"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="44"/>
+      <c r="G68" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H67" s="52">
-        <v>8502.83</v>
-      </c>
-      <c r="I67" s="53"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="49"/>
-      <c r="L67" s="0"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="44">
-        <v>51</v>
-      </c>
-      <c r="B68" s="45">
-        <v>0000107011</v>
-      </c>
-      <c r="C68" t="s" s="46">
-        <v>52</v>
-      </c>
-      <c r="D68" t="s" s="46">
-        <v>140</v>
-      </c>
-      <c r="E68" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F68" t="s" s="44">
-        <v>151</v>
-      </c>
-      <c r="G68" s="51">
-        <v>72</v>
-      </c>
       <c r="H68" s="52">
-        <v>1182.43</v>
-      </c>
-      <c r="I68" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J68" t="s" s="48">
-        <v>152</v>
-      </c>
-      <c r="K68" t="s" s="49">
-        <v>47</v>
-      </c>
+        <v>137767.63</v>
+      </c>
+      <c r="I68" s="53"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="0"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="44">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B69" s="45">
-        <v>0000107011</v>
+        <v>0000107028</v>
       </c>
       <c r="C69" t="s" s="46">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D69" t="s" s="46">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E69" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F69" t="s" s="44">
+        <v>150</v>
+      </c>
+      <c r="G69" s="51">
+        <v>5</v>
+      </c>
+      <c r="H69" s="52">
+        <v>740.25</v>
+      </c>
+      <c r="I69" s="53">
+        <v>15</v>
+      </c>
+      <c r="J69" t="s" s="48">
+        <v>151</v>
+      </c>
+      <c r="K69" t="s" s="49">
+        <v>152</v>
+      </c>
+      <c r="L69" s="0"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B70" s="45">
+        <v>0000107028</v>
+      </c>
+      <c r="C70" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="D70" t="s" s="46">
+        <v>131</v>
+      </c>
+      <c r="E70" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F70" t="s" s="44">
         <v>153</v>
       </c>
-      <c r="G69" s="51">
-        <v>15</v>
-      </c>
-      <c r="H69" s="52">
-        <v>1858.15</v>
-      </c>
-      <c r="I69" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J69" t="s" s="48">
-        <v>154</v>
-      </c>
-      <c r="K69" t="s" s="49">
-        <v>47</v>
-      </c>
-      <c r="L69" s="0"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="44"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="44"/>
-      <c r="G70" t="s" s="51">
-        <v>31</v>
+      <c r="G70" s="51">
+        <v>28</v>
       </c>
       <c r="H70" s="52">
-        <v>113007.21</v>
-      </c>
-      <c r="I70" s="53"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="49"/>
+        <v>968.51</v>
+      </c>
+      <c r="I70" s="53">
+        <v>84</v>
+      </c>
+      <c r="J70" t="s" s="48">
+        <v>19</v>
+      </c>
+      <c r="K70" t="s" s="49">
+        <v>152</v>
+      </c>
       <c r="L70" s="0"/>
     </row>
     <row r="71">
@@ -3590,521 +3649,563 @@
         <v>43</v>
       </c>
       <c r="D71" t="s" s="46">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E71" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F71" t="s" s="44">
+        <v>154</v>
+      </c>
+      <c r="G71" s="51">
+        <v>44</v>
+      </c>
+      <c r="H71" s="52">
+        <v>626.12</v>
+      </c>
+      <c r="I71" s="53">
+        <v>132</v>
+      </c>
+      <c r="J71" t="s" s="48">
         <v>155</v>
       </c>
-      <c r="G71" s="51">
+      <c r="K71" t="s" s="49">
+        <v>152</v>
+      </c>
+      <c r="L71" s="0"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="44"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="47"/>
+      <c r="F72" t="s" s="44">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H72" s="52">
+        <v>58368.81</v>
+      </c>
+      <c r="I72" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s" s="48">
+        <v>18</v>
+      </c>
+      <c r="K72" s="49"/>
+      <c r="L72" s="0"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="44"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="46"/>
+      <c r="D73" s="46"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="G73" t="s" s="51">
+        <v>48</v>
+      </c>
+      <c r="H73" s="52">
+        <v>393836.45</v>
+      </c>
+      <c r="I73" s="53">
+        <v>662.3</v>
+      </c>
+      <c r="J73" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="K73" s="49"/>
+      <c r="L73" s="0"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B74" s="45">
+        <v>0000107036</v>
+      </c>
+      <c r="C74" t="s" s="46">
+        <v>156</v>
+      </c>
+      <c r="D74" t="s" s="46">
+        <v>157</v>
+      </c>
+      <c r="E74" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F74" t="s" s="44">
+        <v>158</v>
+      </c>
+      <c r="G74" s="51">
+        <v>10</v>
+      </c>
+      <c r="H74" s="52">
+        <v>467.16</v>
+      </c>
+      <c r="I74" s="53">
+        <v>10</v>
+      </c>
+      <c r="J74" t="s" s="48">
+        <v>159</v>
+      </c>
+      <c r="K74" t="s" s="49">
+        <v>160</v>
+      </c>
+      <c r="L74" s="0"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B75" s="45">
+        <v>0000107036</v>
+      </c>
+      <c r="C75" t="s" s="46">
+        <v>156</v>
+      </c>
+      <c r="D75" t="s" s="46">
+        <v>157</v>
+      </c>
+      <c r="E75" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F75" t="s" s="44">
+        <v>150</v>
+      </c>
+      <c r="G75" s="51">
         <v>5</v>
       </c>
-      <c r="H71" s="52">
-        <v>740.25</v>
-      </c>
-      <c r="I71" s="53">
+      <c r="H75" s="52">
+        <v>684.63</v>
+      </c>
+      <c r="I75" s="53">
         <v>15</v>
       </c>
-      <c r="J71" t="s" s="48">
-        <v>156</v>
-      </c>
-      <c r="K71" t="s" s="49">
-        <v>157</v>
-      </c>
-      <c r="L71" s="0"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B72" s="45">
-        <v>0000107028</v>
-      </c>
-      <c r="C72" t="s" s="46">
-        <v>43</v>
-      </c>
-      <c r="D72" t="s" s="46">
-        <v>140</v>
-      </c>
-      <c r="E72" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F72" t="s" s="44">
-        <v>158</v>
-      </c>
-      <c r="G72" s="51">
-        <v>28</v>
-      </c>
-      <c r="H72" s="52">
-        <v>968.51</v>
-      </c>
-      <c r="I72" s="53">
-        <v>84</v>
-      </c>
-      <c r="J72" t="s" s="48">
-        <v>19</v>
-      </c>
-      <c r="K72" t="s" s="49">
-        <v>157</v>
-      </c>
-      <c r="L72" s="0"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="44">
-        <v>13</v>
-      </c>
-      <c r="B73" s="45">
-        <v>0000107028</v>
-      </c>
-      <c r="C73" t="s" s="46">
-        <v>43</v>
-      </c>
-      <c r="D73" t="s" s="46">
-        <v>140</v>
-      </c>
-      <c r="E73" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F73" t="s" s="44">
-        <v>159</v>
-      </c>
-      <c r="G73" s="51">
-        <v>44</v>
-      </c>
-      <c r="H73" s="52">
-        <v>626.12</v>
-      </c>
-      <c r="I73" s="53">
-        <v>132</v>
-      </c>
-      <c r="J73" t="s" s="48">
+      <c r="J75" t="s" s="48">
+        <v>151</v>
+      </c>
+      <c r="K75" t="s" s="49">
         <v>160</v>
       </c>
-      <c r="K73" t="s" s="49">
-        <v>157</v>
-      </c>
-      <c r="L73" s="0"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="44"/>
-      <c r="B74" s="45"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="47"/>
-      <c r="F74" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G74" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H74" s="52">
-        <v>58368.81</v>
-      </c>
-      <c r="I74" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K74" s="49"/>
-      <c r="L74" s="0"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="44"/>
-      <c r="B75" s="45"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="G75" t="s" s="51">
-        <v>48</v>
-      </c>
-      <c r="H75" s="52">
-        <v>371216.78</v>
-      </c>
-      <c r="I75" s="53">
-        <v>662.3</v>
-      </c>
-      <c r="J75" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="K75" s="49"/>
       <c r="L75" s="0"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="44">
-        <v>161</v>
+        <v>13</v>
       </c>
       <c r="B76" s="45">
-        <v>0000107029</v>
+        <v>0000107036</v>
       </c>
       <c r="C76" t="s" s="46">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="D76" t="s" s="46">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F76" t="s" s="44">
         <v>163</v>
       </c>
       <c r="G76" s="51">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H76" s="52">
-        <v>518.96</v>
-      </c>
-      <c r="I76" t="s" s="53">
-        <v>18</v>
+        <v>636.30</v>
+      </c>
+      <c r="I76" s="53">
+        <v>30</v>
       </c>
       <c r="J76" t="s" s="48">
         <v>164</v>
       </c>
       <c r="K76" t="s" s="49">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L76" s="0"/>
     </row>
     <row r="77">
-      <c r="A77" s="44"/>
-      <c r="B77" s="45"/>
-      <c r="C77" s="46"/>
-      <c r="D77" s="46"/>
-      <c r="E77" s="47"/>
-      <c r="F77" s="44"/>
-      <c r="G77" t="s" s="51">
-        <v>31</v>
+      <c r="A77" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B77" s="45">
+        <v>0000107036</v>
+      </c>
+      <c r="C77" t="s" s="46">
+        <v>156</v>
+      </c>
+      <c r="D77" t="s" s="46">
+        <v>157</v>
+      </c>
+      <c r="E77" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F77" t="s" s="44">
+        <v>153</v>
+      </c>
+      <c r="G77" s="51">
+        <v>25</v>
       </c>
       <c r="H77" s="52">
-        <v>22834.24</v>
-      </c>
-      <c r="I77" s="53"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="49"/>
+        <v>797.39</v>
+      </c>
+      <c r="I77" s="53">
+        <v>75</v>
+      </c>
+      <c r="J77" t="s" s="48">
+        <v>19</v>
+      </c>
+      <c r="K77" t="s" s="49">
+        <v>160</v>
+      </c>
       <c r="L77" s="0"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="44">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B78" s="45">
-        <v>0000106967</v>
+        <v>0000107036</v>
       </c>
       <c r="C78" t="s" s="46">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="D78" t="s" s="46">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E78" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F78" t="s" s="44">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G78" s="51">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H78" s="52">
-        <v>666.84</v>
+        <v>434.94</v>
       </c>
       <c r="I78" s="53">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J78" t="s" s="48">
-        <v>170</v>
+        <v>22</v>
       </c>
       <c r="K78" t="s" s="49">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="L78" s="0"/>
     </row>
     <row r="79">
-      <c r="A79" s="44"/>
-      <c r="B79" s="45"/>
-      <c r="C79" s="46"/>
-      <c r="D79" s="46"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="44"/>
-      <c r="G79" t="s" s="51">
-        <v>31</v>
+      <c r="A79" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B79" s="45">
+        <v>0000107036</v>
+      </c>
+      <c r="C79" t="s" s="46">
+        <v>156</v>
+      </c>
+      <c r="D79" t="s" s="46">
+        <v>157</v>
+      </c>
+      <c r="E79" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F79" t="s" s="44">
+        <v>55</v>
+      </c>
+      <c r="G79" s="51">
+        <v>150</v>
       </c>
       <c r="H79" s="52">
-        <v>10669.44</v>
-      </c>
-      <c r="I79" s="53"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="49"/>
+        <v>442.99</v>
+      </c>
+      <c r="I79" s="53">
+        <v>150</v>
+      </c>
+      <c r="J79" t="s" s="48">
+        <v>25</v>
+      </c>
+      <c r="K79" t="s" s="49">
+        <v>160</v>
+      </c>
       <c r="L79" s="0"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B80" s="45">
+        <v>0000107036</v>
+      </c>
+      <c r="C80" t="s" s="46">
+        <v>156</v>
+      </c>
+      <c r="D80" t="s" s="46">
+        <v>157</v>
+      </c>
+      <c r="E80" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F80" t="s" s="44">
+        <v>154</v>
+      </c>
+      <c r="G80" s="51">
+        <v>120</v>
+      </c>
+      <c r="H80" s="52">
+        <v>652.41</v>
+      </c>
+      <c r="I80" s="53">
+        <v>360</v>
+      </c>
+      <c r="J80" t="s" s="48">
+        <v>155</v>
+      </c>
+      <c r="K80" t="s" s="49">
+        <v>160</v>
+      </c>
+      <c r="L80" s="0"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="44">
+        <v>13</v>
+      </c>
+      <c r="B81" s="45">
+        <v>0000107036</v>
+      </c>
+      <c r="C81" t="s" s="46">
+        <v>156</v>
+      </c>
+      <c r="D81" t="s" s="46">
+        <v>157</v>
+      </c>
+      <c r="E81" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F81" t="s" s="44">
+        <v>166</v>
+      </c>
+      <c r="G81" s="51">
+        <v>40</v>
+      </c>
+      <c r="H81" s="52">
+        <v>1022.92</v>
+      </c>
+      <c r="I81" s="53">
+        <v>40</v>
+      </c>
+      <c r="J81" t="s" s="48">
+        <v>167</v>
+      </c>
+      <c r="K81" t="s" s="49">
+        <v>160</v>
+      </c>
+      <c r="L81" s="0"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="44"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="46"/>
+      <c r="E82" s="47"/>
+      <c r="F82" s="44"/>
+      <c r="G82" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H82" s="52">
+        <v>241471.8</v>
+      </c>
+      <c r="I82" s="53"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="49"/>
+      <c r="L82" s="0"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="44">
+        <v>168</v>
+      </c>
+      <c r="B83" s="45">
+        <v>0000107029</v>
+      </c>
+      <c r="C83" t="s" s="46">
+        <v>97</v>
+      </c>
+      <c r="D83" t="s" s="46">
+        <v>169</v>
+      </c>
+      <c r="E83" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F83" t="s" s="44">
+        <v>170</v>
+      </c>
+      <c r="G83" s="51">
+        <v>44</v>
+      </c>
+      <c r="H83" s="52">
+        <v>518.96</v>
+      </c>
+      <c r="I83" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J83" t="s" s="48">
+        <v>171</v>
+      </c>
+      <c r="K83" t="s" s="49">
+        <v>172</v>
+      </c>
+      <c r="L83" s="0"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="44"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="46"/>
+      <c r="D84" s="46"/>
+      <c r="E84" s="47"/>
+      <c r="F84" s="44"/>
+      <c r="G84" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H84" s="52">
+        <v>22834.24</v>
+      </c>
+      <c r="I84" s="53"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="49"/>
+      <c r="L84" s="0"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="44">
         <v>42</v>
       </c>
-      <c r="B80" s="45">
-        <v>0000106986</v>
-      </c>
-      <c r="C80" t="s" s="46">
-        <v>172</v>
-      </c>
-      <c r="D80" t="s" s="46">
+      <c r="B85" s="45">
+        <v>0000106967</v>
+      </c>
+      <c r="C85" t="s" s="46">
+        <v>112</v>
+      </c>
+      <c r="D85" t="s" s="46">
         <v>173</v>
       </c>
-      <c r="E80" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F80" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G80" s="51">
+      <c r="E85" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F85" t="s" s="44">
+        <v>174</v>
+      </c>
+      <c r="G85" s="51">
+        <v>16</v>
+      </c>
+      <c r="H85" s="52">
+        <v>666.84</v>
+      </c>
+      <c r="I85" s="53">
         <v>48</v>
       </c>
-      <c r="H80" s="52">
-        <v>326.73</v>
-      </c>
-      <c r="I80" s="53">
-        <v>72</v>
-      </c>
-      <c r="J80" t="s" s="48">
-        <v>78</v>
-      </c>
-      <c r="K80" t="s" s="49">
-        <v>174</v>
-      </c>
-      <c r="L80" s="0"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="44"/>
-      <c r="B81" s="45"/>
-      <c r="C81" s="46"/>
-      <c r="D81" s="46"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="44"/>
-      <c r="G81" t="s" s="51">
+      <c r="J85" t="s" s="48">
+        <v>175</v>
+      </c>
+      <c r="K85" t="s" s="49">
+        <v>176</v>
+      </c>
+      <c r="L85" s="0"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="44"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="46"/>
+      <c r="D86" s="46"/>
+      <c r="E86" s="47"/>
+      <c r="F86" s="44"/>
+      <c r="G86" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H81" s="52">
-        <v>15683.04</v>
-      </c>
-      <c r="I81" s="53"/>
-      <c r="J81" s="48"/>
-      <c r="K81" s="49"/>
-      <c r="L81" s="0"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="44">
-        <v>175</v>
-      </c>
-      <c r="B82" s="45">
-        <v>0000107015</v>
-      </c>
-      <c r="C82" t="s" s="46">
-        <v>139</v>
-      </c>
-      <c r="D82" t="s" s="46">
-        <v>173</v>
-      </c>
-      <c r="E82" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F82" t="s" s="44">
-        <v>176</v>
-      </c>
-      <c r="G82" s="51">
-        <v>29</v>
-      </c>
-      <c r="H82" s="52">
-        <v>2144.54</v>
-      </c>
-      <c r="I82" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J82" t="s" s="48">
-        <v>177</v>
-      </c>
-      <c r="K82" t="s" s="49">
-        <v>178</v>
-      </c>
-      <c r="L82" s="0"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="44"/>
-      <c r="B83" s="45"/>
-      <c r="C83" s="46"/>
-      <c r="D83" s="46"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="44"/>
-      <c r="G83" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H83" s="52">
-        <v>62191.66</v>
-      </c>
-      <c r="I83" s="53"/>
-      <c r="J83" s="48"/>
-      <c r="K83" s="49"/>
-      <c r="L83" s="0"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="44">
-        <v>179</v>
-      </c>
-      <c r="B84" s="45">
-        <v>0000107031</v>
-      </c>
-      <c r="C84" t="s" s="46">
-        <v>180</v>
-      </c>
-      <c r="D84" t="s" s="46">
-        <v>181</v>
-      </c>
-      <c r="E84" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F84" t="s" s="44">
-        <v>182</v>
-      </c>
-      <c r="G84" s="51">
-        <v>20</v>
-      </c>
-      <c r="H84" s="52">
-        <v>22.60</v>
-      </c>
-      <c r="I84" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J84" t="s" s="48">
-        <v>183</v>
-      </c>
-      <c r="K84" t="s" s="49">
-        <v>184</v>
-      </c>
-      <c r="L84" s="0"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="44"/>
-      <c r="B85" s="45"/>
-      <c r="C85" s="46"/>
-      <c r="D85" s="46"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="44"/>
-      <c r="G85" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H85" s="52">
-        <v>452</v>
-      </c>
-      <c r="I85" s="53"/>
-      <c r="J85" s="48"/>
-      <c r="K85" s="49"/>
-      <c r="L85" s="0"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="44">
-        <v>185</v>
-      </c>
-      <c r="B86" s="45">
-        <v>0000107034</v>
-      </c>
-      <c r="C86" t="s" s="46">
-        <v>80</v>
-      </c>
-      <c r="D86" t="s" s="46">
-        <v>186</v>
-      </c>
-      <c r="E86" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F86" t="s" s="44">
-        <v>187</v>
-      </c>
-      <c r="G86" s="51">
-        <v>20</v>
-      </c>
       <c r="H86" s="52">
-        <v>210.91</v>
-      </c>
-      <c r="I86" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J86" t="s" s="48">
-        <v>135</v>
-      </c>
+        <v>10669.44</v>
+      </c>
+      <c r="I86" s="53"/>
+      <c r="J86" s="48"/>
       <c r="K86" s="49"/>
       <c r="L86" s="0"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="44">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="B87" s="45">
-        <v>0000107034</v>
+        <v>0000107039</v>
       </c>
       <c r="C87" t="s" s="46">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D87" t="s" s="46">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E87" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F87" t="s" s="44">
-        <v>188</v>
+        <v>76</v>
       </c>
       <c r="G87" s="51">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H87" s="52">
-        <v>228.47</v>
-      </c>
-      <c r="I87" t="s" s="53">
-        <v>18</v>
+        <v>249.78</v>
+      </c>
+      <c r="I87" s="53">
+        <v>7.5</v>
       </c>
       <c r="J87" t="s" s="48">
-        <v>189</v>
-      </c>
-      <c r="K87" s="49"/>
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="49">
+        <v>178</v>
+      </c>
       <c r="L87" s="0"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="44">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="B88" s="45">
-        <v>0000107034</v>
+        <v>0000107039</v>
       </c>
       <c r="C88" t="s" s="46">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D88" t="s" s="46">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E88" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F88" t="s" s="44">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G88" s="51">
         <v>20</v>
       </c>
       <c r="H88" s="52">
-        <v>339.90</v>
+        <v>34.58</v>
       </c>
       <c r="I88" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J88" t="s" s="48">
-        <v>191</v>
-      </c>
-      <c r="K88" s="49"/>
+        <v>180</v>
+      </c>
+      <c r="K88" t="s" s="49">
+        <v>178</v>
+      </c>
       <c r="L88" s="0"/>
     </row>
     <row r="89">
@@ -4118,7 +4219,7 @@
         <v>31</v>
       </c>
       <c r="H89" s="52">
-        <v>17870.3</v>
+        <v>4438.3</v>
       </c>
       <c r="I89" s="53"/>
       <c r="J89" s="48"/>
@@ -4130,34 +4231,34 @@
         <v>42</v>
       </c>
       <c r="B90" s="45">
-        <v>0000106996</v>
+        <v>0000106986</v>
       </c>
       <c r="C90" t="s" s="46">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="D90" t="s" s="46">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="E90" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F90" t="s" s="44">
+        <v>68</v>
+      </c>
+      <c r="G90" s="51">
+        <v>48</v>
+      </c>
+      <c r="H90" s="52">
+        <v>326.73</v>
+      </c>
+      <c r="I90" s="53">
+        <v>72</v>
+      </c>
+      <c r="J90" t="s" s="48">
         <v>69</v>
       </c>
-      <c r="F90" t="s" s="44">
-        <v>122</v>
-      </c>
-      <c r="G90" s="51">
-        <v>70</v>
-      </c>
-      <c r="H90" s="52">
-        <v>374.24</v>
-      </c>
-      <c r="I90" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J90" t="s" s="48">
-        <v>123</v>
-      </c>
       <c r="K90" t="s" s="49">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L90" s="0"/>
     </row>
@@ -4172,7 +4273,7 @@
         <v>31</v>
       </c>
       <c r="H91" s="52">
-        <v>26196.8</v>
+        <v>15683.04</v>
       </c>
       <c r="I91" s="53"/>
       <c r="J91" s="48"/>
@@ -4181,37 +4282,37 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="44">
-        <v>94</v>
+        <v>184</v>
       </c>
       <c r="B92" s="45">
-        <v>0000106778</v>
+        <v>0000107015</v>
       </c>
       <c r="C92" t="s" s="46">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="D92" t="s" s="46">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="E92" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F92" t="s" s="44">
-        <v>96</v>
+        <v>185</v>
       </c>
       <c r="G92" s="51">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H92" s="52">
-        <v>2250</v>
+        <v>2144.54</v>
       </c>
       <c r="I92" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J92" t="s" s="48">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="K92" t="s" s="49">
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="L92" s="0"/>
     </row>
@@ -4226,7 +4327,7 @@
         <v>31</v>
       </c>
       <c r="H93" s="52">
-        <v>11250</v>
+        <v>62191.66</v>
       </c>
       <c r="I93" s="53"/>
       <c r="J93" s="48"/>
@@ -4235,37 +4336,37 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="44">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="B94" s="45">
-        <v>0000107019</v>
+        <v>0000107031</v>
       </c>
       <c r="C94" t="s" s="46">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="D94" t="s" s="46">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E94" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F94" t="s" s="44">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="G94" s="51">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H94" s="52">
-        <v>11.36</v>
-      </c>
-      <c r="I94" s="53">
-        <v>3.3</v>
+        <v>22.60</v>
+      </c>
+      <c r="I94" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J94" t="s" s="48">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="K94" t="s" s="49">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L94" s="0"/>
     </row>
@@ -4280,7 +4381,7 @@
         <v>31</v>
       </c>
       <c r="H95" s="52">
-        <v>1136</v>
+        <v>452</v>
       </c>
       <c r="I95" s="53"/>
       <c r="J95" s="48"/>
@@ -4289,98 +4390,110 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="44">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="B96" s="45">
-        <v>0000106999</v>
+        <v>0000107034</v>
       </c>
       <c r="C96" t="s" s="46">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="D96" t="s" s="46">
+        <v>195</v>
+      </c>
+      <c r="E96" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F96" t="s" s="44">
         <v>196</v>
       </c>
-      <c r="E96" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F96" t="s" s="44">
+      <c r="G96" s="51">
+        <v>20</v>
+      </c>
+      <c r="H96" s="52">
+        <v>226.20</v>
+      </c>
+      <c r="I96" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J96" t="s" s="48">
+        <v>129</v>
+      </c>
+      <c r="K96" t="s" s="49">
         <v>197</v>
-      </c>
-      <c r="G96" s="51">
-        <v>25</v>
-      </c>
-      <c r="H96" s="52">
-        <v>240.32</v>
-      </c>
-      <c r="I96" s="53">
-        <v>12.5</v>
-      </c>
-      <c r="J96" t="s" s="48">
-        <v>198</v>
-      </c>
-      <c r="K96" t="s" s="49">
-        <v>199</v>
       </c>
       <c r="L96" s="0"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="44">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="B97" s="45">
-        <v>0000106999</v>
+        <v>0000107034</v>
       </c>
       <c r="C97" t="s" s="46">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="D97" t="s" s="46">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E97" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F97" t="s" s="44">
+        <v>198</v>
+      </c>
+      <c r="G97" s="51">
+        <v>30</v>
+      </c>
+      <c r="H97" s="52">
+        <v>243.77</v>
+      </c>
+      <c r="I97" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J97" t="s" s="48">
+        <v>199</v>
+      </c>
+      <c r="K97" t="s" s="49">
+        <v>197</v>
+      </c>
+      <c r="L97" s="0"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="44">
+        <v>194</v>
+      </c>
+      <c r="B98" s="45">
+        <v>0000107034</v>
+      </c>
+      <c r="C98" t="s" s="46">
+        <v>71</v>
+      </c>
+      <c r="D98" t="s" s="46">
+        <v>195</v>
+      </c>
+      <c r="E98" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F98" t="s" s="44">
         <v>200</v>
       </c>
-      <c r="G97" s="51">
-        <v>10</v>
-      </c>
-      <c r="H97" s="52">
-        <v>579.56</v>
-      </c>
-      <c r="I97" s="53">
-        <v>30</v>
-      </c>
-      <c r="J97" t="s" s="48">
+      <c r="G98" s="51">
+        <v>20</v>
+      </c>
+      <c r="H98" s="52">
+        <v>355.20</v>
+      </c>
+      <c r="I98" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J98" t="s" s="48">
         <v>201</v>
       </c>
-      <c r="K97" t="s" s="49">
-        <v>199</v>
-      </c>
-      <c r="L97" s="0"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="44"/>
-      <c r="B98" s="45"/>
-      <c r="C98" s="46"/>
-      <c r="D98" s="46"/>
-      <c r="E98" s="47"/>
-      <c r="F98" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G98" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H98" s="52">
-        <v>11803.6</v>
-      </c>
-      <c r="I98" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J98" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K98" s="49"/>
+      <c r="K98" t="s" s="49">
+        <v>197</v>
+      </c>
       <c r="L98" s="0"/>
     </row>
     <row r="99">
@@ -4389,129 +4502,123 @@
       <c r="C99" s="46"/>
       <c r="D99" s="46"/>
       <c r="E99" s="47"/>
-      <c r="F99" s="44" t="s">
-        <v>204</v>
-      </c>
+      <c r="F99" s="44"/>
       <c r="G99" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H99" s="52">
-        <v>180087.08</v>
-      </c>
-      <c r="I99" s="53">
-        <v>253.3</v>
-      </c>
-      <c r="J99" s="48" t="s">
-        <v>205</v>
-      </c>
+        <v>18941.1</v>
+      </c>
+      <c r="I99" s="53"/>
+      <c r="J99" s="48"/>
       <c r="K99" s="49"/>
       <c r="L99" s="0"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="44">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="B100" s="45">
-        <v>0000107021</v>
+        <v>0000107037</v>
       </c>
       <c r="C100" t="s" s="46">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="D100" t="s" s="46">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E100" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F100" t="s" s="44">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="G100" s="51">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H100" s="52">
-        <v>661.61</v>
-      </c>
-      <c r="I100" s="53">
-        <v>48</v>
+        <v>1684.35</v>
+      </c>
+      <c r="I100" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J100" t="s" s="48">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="K100" t="s" s="49">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L100" s="0"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="44">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="B101" s="45">
-        <v>0000107021</v>
+        <v>0000107037</v>
       </c>
       <c r="C101" t="s" s="46">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="D101" t="s" s="46">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E101" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F101" t="s" s="44">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="G101" s="51">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="H101" s="52">
-        <v>376.11</v>
-      </c>
-      <c r="I101" s="53">
-        <v>87.5</v>
+        <v>34.65</v>
+      </c>
+      <c r="I101" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J101" t="s" s="48">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="K101" t="s" s="49">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L101" s="0"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="44">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="B102" s="45">
-        <v>0000107021</v>
+        <v>0000107037</v>
       </c>
       <c r="C102" t="s" s="46">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="D102" t="s" s="46">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F102" t="s" s="44">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="G102" s="51">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H102" s="52">
-        <v>320.39</v>
-      </c>
-      <c r="I102" s="53">
-        <v>72</v>
+        <v>665.42</v>
+      </c>
+      <c r="I102" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J102" t="s" s="48">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="K102" t="s" s="49">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L102" s="0"/>
     </row>
@@ -4526,7 +4633,7 @@
         <v>31</v>
       </c>
       <c r="H103" s="52">
-        <v>52292.18</v>
+        <v>2384.42</v>
       </c>
       <c r="I103" s="53"/>
       <c r="J103" s="48"/>
@@ -4535,37 +4642,37 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="44">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="B104" s="45">
-        <v>0000106778</v>
+        <v>0000106996</v>
       </c>
       <c r="C104" t="s" s="46">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D104" t="s" s="46">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E104" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F104" t="s" s="44">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="G104" s="51">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="H104" s="52">
-        <v>2250</v>
-      </c>
-      <c r="I104" t="s" s="53">
-        <v>18</v>
+        <v>374.24</v>
+      </c>
+      <c r="I104" s="53">
+        <v>87.5</v>
       </c>
       <c r="J104" t="s" s="48">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="K104" t="s" s="49">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L104" s="0"/>
     </row>
@@ -4580,7 +4687,7 @@
         <v>31</v>
       </c>
       <c r="H105" s="52">
-        <v>4500</v>
+        <v>26196.8</v>
       </c>
       <c r="I105" s="53"/>
       <c r="J105" s="48"/>
@@ -4589,37 +4696,37 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="44">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="B106" s="45">
-        <v>0000106623</v>
+        <v>0000106778</v>
       </c>
       <c r="C106" t="s" s="46">
-        <v>207</v>
+        <v>87</v>
       </c>
       <c r="D106" t="s" s="46">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E106" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F106" t="s" s="44">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="G106" s="51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H106" s="52">
-        <v>269.86</v>
+        <v>2250</v>
       </c>
       <c r="I106" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J106" t="s" s="48">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="K106" t="s" s="49">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="L106" s="0"/>
     </row>
@@ -4634,7 +4741,7 @@
         <v>31</v>
       </c>
       <c r="H107" s="52">
-        <v>539.72</v>
+        <v>11250</v>
       </c>
       <c r="I107" s="53"/>
       <c r="J107" s="48"/>
@@ -4643,34 +4750,34 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="44">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="B108" s="45">
-        <v>0000107020</v>
+        <v>0000107040</v>
       </c>
       <c r="C108" t="s" s="46">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D108" t="s" s="46">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E108" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F108" t="s" s="44">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="G108" s="51">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H108" s="52">
-        <v>31.20</v>
-      </c>
-      <c r="I108" s="53">
-        <v>3.35</v>
+        <v>586.03</v>
+      </c>
+      <c r="I108" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J108" t="s" s="48">
-        <v>213</v>
+        <v>105</v>
       </c>
       <c r="K108" t="s" s="49">
         <v>214</v>
@@ -4679,34 +4786,34 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="44">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="B109" s="45">
-        <v>0000107020</v>
+        <v>0000107040</v>
       </c>
       <c r="C109" t="s" s="46">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D109" t="s" s="46">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E109" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F109" t="s" s="44">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="G109" s="51">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H109" s="52">
-        <v>11.36</v>
-      </c>
-      <c r="I109" s="53">
-        <v>3.3</v>
+        <v>958.33</v>
+      </c>
+      <c r="I109" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J109" t="s" s="48">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="K109" t="s" s="49">
         <v>214</v>
@@ -4714,141 +4821,147 @@
       <c r="L109" s="0"/>
     </row>
     <row r="110">
-      <c r="A110" s="44"/>
-      <c r="B110" s="45"/>
-      <c r="C110" s="46"/>
-      <c r="D110" s="46"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="44"/>
-      <c r="G110" t="s" s="51">
+      <c r="A110" t="s" s="44">
+        <v>96</v>
+      </c>
+      <c r="B110" s="45">
+        <v>0000107040</v>
+      </c>
+      <c r="C110" t="s" s="46">
+        <v>60</v>
+      </c>
+      <c r="D110" t="s" s="46">
+        <v>213</v>
+      </c>
+      <c r="E110" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F110" t="s" s="44">
+        <v>217</v>
+      </c>
+      <c r="G110" s="51">
+        <v>5</v>
+      </c>
+      <c r="H110" s="52">
+        <v>958.33</v>
+      </c>
+      <c r="I110" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J110" t="s" s="48">
+        <v>218</v>
+      </c>
+      <c r="K110" t="s" s="49">
+        <v>214</v>
+      </c>
+      <c r="L110" s="0"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="44"/>
+      <c r="B111" s="45"/>
+      <c r="C111" s="46"/>
+      <c r="D111" s="46"/>
+      <c r="E111" s="47"/>
+      <c r="F111" s="44"/>
+      <c r="G111" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H110" s="52">
-        <v>2696</v>
-      </c>
-      <c r="I110" s="53"/>
-      <c r="J110" s="48"/>
-      <c r="K110" s="49"/>
-      <c r="L110" s="0"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="44">
-        <v>215</v>
-      </c>
-      <c r="B111" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C111" t="s" s="46">
-        <v>216</v>
-      </c>
-      <c r="D111" t="s" s="46">
-        <v>211</v>
-      </c>
-      <c r="E111" t="s" s="47">
-        <v>217</v>
-      </c>
-      <c r="F111" t="s" s="44">
-        <v>218</v>
-      </c>
-      <c r="G111" s="51">
-        <v>1</v>
-      </c>
       <c r="H111" s="52">
-        <v>89.15</v>
-      </c>
-      <c r="I111" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J111" t="s" s="48">
-        <v>219</v>
-      </c>
+        <v>12513.45</v>
+      </c>
+      <c r="I111" s="53"/>
+      <c r="J111" s="48"/>
       <c r="K111" s="49"/>
       <c r="L111" s="0"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="44">
-        <v>215</v>
+        <v>42</v>
       </c>
       <c r="B112" s="45">
-        <v>0000106325</v>
+        <v>0000107019</v>
       </c>
       <c r="C112" t="s" s="46">
-        <v>216</v>
+        <v>117</v>
       </c>
       <c r="D112" t="s" s="46">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E112" t="s" s="47">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="F112" t="s" s="44">
+        <v>118</v>
+      </c>
+      <c r="G112" s="51">
+        <v>100</v>
+      </c>
+      <c r="H112" s="52">
+        <v>11.36</v>
+      </c>
+      <c r="I112" s="53">
+        <v>3.3</v>
+      </c>
+      <c r="J112" t="s" s="48">
+        <v>119</v>
+      </c>
+      <c r="K112" t="s" s="49">
         <v>220</v>
       </c>
-      <c r="G112" s="51">
-        <v>1</v>
-      </c>
-      <c r="H112" s="52">
-        <v>510.61</v>
-      </c>
-      <c r="I112" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J112" t="s" s="48">
-        <v>221</v>
-      </c>
-      <c r="K112" s="49"/>
       <c r="L112" s="0"/>
     </row>
     <row r="113">
-      <c r="A113" t="s" s="44">
-        <v>215</v>
-      </c>
-      <c r="B113" s="45">
-        <v>0000106325</v>
-      </c>
-      <c r="C113" t="s" s="46">
-        <v>216</v>
-      </c>
-      <c r="D113" t="s" s="46">
-        <v>211</v>
-      </c>
-      <c r="E113" t="s" s="47">
-        <v>217</v>
-      </c>
-      <c r="F113" t="s" s="44">
-        <v>222</v>
-      </c>
-      <c r="G113" s="51">
-        <v>1</v>
+      <c r="A113" s="44"/>
+      <c r="B113" s="45"/>
+      <c r="C113" s="46"/>
+      <c r="D113" s="46"/>
+      <c r="E113" s="47"/>
+      <c r="F113" s="44"/>
+      <c r="G113" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H113" s="52">
-        <v>0</v>
-      </c>
-      <c r="I113" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J113" t="s" s="48">
-        <v>223</v>
-      </c>
+        <v>1136</v>
+      </c>
+      <c r="I113" s="53"/>
+      <c r="J113" s="48"/>
       <c r="K113" s="49"/>
       <c r="L113" s="0"/>
     </row>
     <row r="114">
-      <c r="A114" s="44"/>
-      <c r="B114" s="45"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="46"/>
-      <c r="E114" s="47"/>
-      <c r="F114" s="44"/>
-      <c r="G114" t="s" s="51">
-        <v>31</v>
+      <c r="A114" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B114" s="45">
+        <v>0000106999</v>
+      </c>
+      <c r="C114" t="s" s="46">
+        <v>74</v>
+      </c>
+      <c r="D114" t="s" s="46">
+        <v>221</v>
+      </c>
+      <c r="E114" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F114" t="s" s="44">
+        <v>222</v>
+      </c>
+      <c r="G114" s="51">
+        <v>25</v>
       </c>
       <c r="H114" s="52">
-        <v>599.76</v>
-      </c>
-      <c r="I114" s="53"/>
-      <c r="J114" s="48"/>
-      <c r="K114" s="49"/>
+        <v>240.32</v>
+      </c>
+      <c r="I114" s="53">
+        <v>12.5</v>
+      </c>
+      <c r="J114" t="s" s="48">
+        <v>223</v>
+      </c>
+      <c r="K114" t="s" s="49">
+        <v>224</v>
+      </c>
       <c r="L114" s="0"/>
     </row>
     <row r="115">
@@ -4856,71 +4969,59 @@
         <v>42</v>
       </c>
       <c r="B115" s="45">
-        <v>0000107022</v>
+        <v>0000106999</v>
       </c>
       <c r="C115" t="s" s="46">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="D115" t="s" s="46">
+        <v>221</v>
+      </c>
+      <c r="E115" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F115" t="s" s="44">
+        <v>225</v>
+      </c>
+      <c r="G115" s="51">
+        <v>10</v>
+      </c>
+      <c r="H115" s="52">
+        <v>579.56</v>
+      </c>
+      <c r="I115" s="53">
+        <v>30</v>
+      </c>
+      <c r="J115" t="s" s="48">
+        <v>226</v>
+      </c>
+      <c r="K115" t="s" s="49">
         <v>224</v>
       </c>
-      <c r="E115" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F115" t="s" s="44">
-        <v>122</v>
-      </c>
-      <c r="G115" s="51">
-        <v>70</v>
-      </c>
-      <c r="H115" s="52">
-        <v>376.11</v>
-      </c>
-      <c r="I115" s="53">
-        <v>87.5</v>
-      </c>
-      <c r="J115" t="s" s="48">
-        <v>123</v>
-      </c>
-      <c r="K115" t="s" s="49">
-        <v>225</v>
-      </c>
       <c r="L115" s="0"/>
     </row>
     <row r="116">
-      <c r="A116" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B116" s="45">
-        <v>0000107022</v>
-      </c>
-      <c r="C116" t="s" s="46">
-        <v>125</v>
-      </c>
-      <c r="D116" t="s" s="46">
-        <v>224</v>
-      </c>
-      <c r="E116" t="s" s="47">
-        <v>69</v>
-      </c>
+      <c r="A116" s="44"/>
+      <c r="B116" s="45"/>
+      <c r="C116" s="46"/>
+      <c r="D116" s="46"/>
+      <c r="E116" s="47"/>
       <c r="F116" t="s" s="44">
-        <v>77</v>
-      </c>
-      <c r="G116" s="51">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="G116" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H116" s="52">
-        <v>320.39</v>
-      </c>
-      <c r="I116" s="53">
-        <v>72</v>
+        <v>11803.6</v>
+      </c>
+      <c r="I116" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J116" t="s" s="48">
-        <v>78</v>
-      </c>
-      <c r="K116" t="s" s="49">
-        <v>225</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K116" s="49"/>
       <c r="L116" s="0"/>
     </row>
     <row r="117">
@@ -4929,46 +5030,58 @@
       <c r="C117" s="46"/>
       <c r="D117" s="46"/>
       <c r="E117" s="47"/>
-      <c r="F117" t="s" s="44">
-        <v>18</v>
+      <c r="F117" s="44" t="s">
+        <v>229</v>
       </c>
       <c r="G117" t="s" s="51">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H117" s="52">
-        <v>41706.42</v>
-      </c>
-      <c r="I117" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" t="s" s="48">
-        <v>18</v>
+        <v>441965.85</v>
+      </c>
+      <c r="I117" s="53">
+        <v>960.8</v>
+      </c>
+      <c r="J117" s="48" t="s">
+        <v>230</v>
       </c>
       <c r="K117" s="49"/>
       <c r="L117" s="0"/>
     </row>
     <row r="118">
-      <c r="A118" s="44"/>
-      <c r="B118" s="45"/>
-      <c r="C118" s="46"/>
-      <c r="D118" s="46"/>
-      <c r="E118" s="47"/>
-      <c r="F118" s="44" t="s">
+      <c r="A118" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B118" s="45">
+        <v>0000107021</v>
+      </c>
+      <c r="C118" t="s" s="46">
+        <v>117</v>
+      </c>
+      <c r="D118" t="s" s="46">
+        <v>227</v>
+      </c>
+      <c r="E118" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F118" t="s" s="44">
+        <v>174</v>
+      </c>
+      <c r="G118" s="51">
+        <v>16</v>
+      </c>
+      <c r="H118" s="52">
+        <v>661.61</v>
+      </c>
+      <c r="I118" s="53">
+        <v>48</v>
+      </c>
+      <c r="J118" t="s" s="48">
+        <v>175</v>
+      </c>
+      <c r="K118" t="s" s="49">
         <v>228</v>
       </c>
-      <c r="G118" t="s" s="51">
-        <v>48</v>
-      </c>
-      <c r="H118" s="52">
-        <v>102334.08</v>
-      </c>
-      <c r="I118" s="53">
-        <v>373.65</v>
-      </c>
-      <c r="J118" s="48" t="s">
-        <v>229</v>
-      </c>
-      <c r="K118" s="49"/>
       <c r="L118" s="0"/>
     </row>
     <row r="119">
@@ -4976,59 +5089,71 @@
         <v>42</v>
       </c>
       <c r="B119" s="45">
-        <v>0000107026</v>
+        <v>0000107021</v>
       </c>
       <c r="C119" t="s" s="46">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="D119" t="s" s="46">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E119" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F119" t="s" s="44">
+        <v>114</v>
+      </c>
+      <c r="G119" s="51">
+        <v>70</v>
+      </c>
+      <c r="H119" s="52">
+        <v>376.11</v>
+      </c>
+      <c r="I119" s="53">
+        <v>87.5</v>
+      </c>
+      <c r="J119" t="s" s="48">
+        <v>115</v>
+      </c>
+      <c r="K119" t="s" s="49">
+        <v>228</v>
+      </c>
+      <c r="L119" s="0"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B120" s="45">
+        <v>0000107021</v>
+      </c>
+      <c r="C120" t="s" s="46">
+        <v>117</v>
+      </c>
+      <c r="D120" t="s" s="46">
+        <v>227</v>
+      </c>
+      <c r="E120" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F120" t="s" s="44">
+        <v>68</v>
+      </c>
+      <c r="G120" s="51">
+        <v>48</v>
+      </c>
+      <c r="H120" s="52">
+        <v>320.39</v>
+      </c>
+      <c r="I120" s="53">
+        <v>72</v>
+      </c>
+      <c r="J120" t="s" s="48">
         <v>69</v>
       </c>
-      <c r="F119" t="s" s="44">
-        <v>169</v>
-      </c>
-      <c r="G119" s="51">
-        <v>16</v>
-      </c>
-      <c r="H119" s="52">
-        <v>656.58</v>
-      </c>
-      <c r="I119" s="53">
-        <v>48</v>
-      </c>
-      <c r="J119" t="s" s="48">
-        <v>170</v>
-      </c>
-      <c r="K119" t="s" s="49">
-        <v>227</v>
-      </c>
-      <c r="L119" s="0"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="44"/>
-      <c r="B120" s="45"/>
-      <c r="C120" s="46"/>
-      <c r="D120" s="46"/>
-      <c r="E120" s="47"/>
-      <c r="F120" t="s" s="44">
-        <v>18</v>
-      </c>
-      <c r="G120" t="s" s="51">
-        <v>31</v>
-      </c>
-      <c r="H120" s="52">
-        <v>10505.28</v>
-      </c>
-      <c r="I120" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" t="s" s="48">
-        <v>18</v>
-      </c>
-      <c r="K120" s="49"/>
+      <c r="K120" t="s" s="49">
+        <v>228</v>
+      </c>
       <c r="L120" s="0"/>
     </row>
     <row r="121">
@@ -5037,56 +5162,52 @@
       <c r="C121" s="46"/>
       <c r="D121" s="46"/>
       <c r="E121" s="47"/>
-      <c r="F121" s="44" t="s">
-        <v>232</v>
-      </c>
+      <c r="F121" s="44"/>
       <c r="G121" t="s" s="51">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="H121" s="52">
-        <v>10505.28</v>
-      </c>
-      <c r="I121" s="53">
-        <v>48</v>
-      </c>
-      <c r="J121" s="48" t="s">
-        <v>233</v>
-      </c>
+        <v>52292.18</v>
+      </c>
+      <c r="I121" s="53"/>
+      <c r="J121" s="48"/>
       <c r="K121" s="49"/>
       <c r="L121" s="0"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="44">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="B122" s="45">
-        <v>0000106170</v>
+        <v>0000106778</v>
       </c>
       <c r="C122" t="s" s="46">
-        <v>230</v>
+        <v>87</v>
       </c>
       <c r="D122" t="s" s="46">
         <v>231</v>
       </c>
       <c r="E122" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F122" t="s" s="44">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G122" s="51">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H122" s="52">
-        <v>0</v>
-      </c>
-      <c r="I122" s="53">
-        <v>72</v>
+        <v>2250</v>
+      </c>
+      <c r="I122" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J122" t="s" s="48">
-        <v>78</v>
-      </c>
-      <c r="K122" s="49"/>
+        <v>89</v>
+      </c>
+      <c r="K122" t="s" s="49">
+        <v>90</v>
+      </c>
       <c r="L122" s="0"/>
     </row>
     <row r="123">
@@ -5100,7 +5221,7 @@
         <v>31</v>
       </c>
       <c r="H123" s="52">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="I123" s="53"/>
       <c r="J123" s="48"/>
@@ -5112,33 +5233,35 @@
         <v>42</v>
       </c>
       <c r="B124" s="45">
-        <v>0000106171</v>
+        <v>0000106623</v>
       </c>
       <c r="C124" t="s" s="46">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D124" t="s" s="46">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E124" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F124" t="s" s="44">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="G124" s="51">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="H124" s="52">
-        <v>0</v>
-      </c>
-      <c r="I124" s="53">
-        <v>87.5</v>
+        <v>269.86</v>
+      </c>
+      <c r="I124" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J124" t="s" s="48">
-        <v>123</v>
-      </c>
-      <c r="K124" s="49"/>
+        <v>235</v>
+      </c>
+      <c r="K124" t="s" s="49">
+        <v>47</v>
+      </c>
       <c r="L124" s="0"/>
     </row>
     <row r="125">
@@ -5152,7 +5275,7 @@
         <v>31</v>
       </c>
       <c r="H125" s="52">
-        <v>0</v>
+        <v>539.72</v>
       </c>
       <c r="I125" s="53"/>
       <c r="J125" s="48"/>
@@ -5164,213 +5287,209 @@
         <v>42</v>
       </c>
       <c r="B126" s="45">
-        <v>0000106172</v>
+        <v>0000107020</v>
       </c>
       <c r="C126" t="s" s="46">
-        <v>230</v>
+        <v>117</v>
       </c>
       <c r="D126" t="s" s="46">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E126" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F126" t="s" s="44">
-        <v>122</v>
+        <v>237</v>
       </c>
       <c r="G126" s="51">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H126" s="52">
-        <v>0</v>
+        <v>31.20</v>
       </c>
       <c r="I126" s="53">
-        <v>87.5</v>
+        <v>3.35</v>
       </c>
       <c r="J126" t="s" s="48">
-        <v>123</v>
-      </c>
-      <c r="K126" s="49"/>
+        <v>238</v>
+      </c>
+      <c r="K126" t="s" s="49">
+        <v>239</v>
+      </c>
       <c r="L126" s="0"/>
     </row>
     <row r="127">
-      <c r="A127" s="44"/>
-      <c r="B127" s="45"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="46"/>
-      <c r="E127" s="47"/>
-      <c r="F127" s="44"/>
-      <c r="G127" t="s" s="51">
+      <c r="A127" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B127" s="45">
+        <v>0000107020</v>
+      </c>
+      <c r="C127" t="s" s="46">
+        <v>117</v>
+      </c>
+      <c r="D127" t="s" s="46">
+        <v>236</v>
+      </c>
+      <c r="E127" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F127" t="s" s="44">
+        <v>118</v>
+      </c>
+      <c r="G127" s="51">
+        <v>100</v>
+      </c>
+      <c r="H127" s="52">
+        <v>11.36</v>
+      </c>
+      <c r="I127" s="53">
+        <v>3.3</v>
+      </c>
+      <c r="J127" t="s" s="48">
+        <v>119</v>
+      </c>
+      <c r="K127" t="s" s="49">
+        <v>239</v>
+      </c>
+      <c r="L127" s="0"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="44"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="46"/>
+      <c r="D128" s="46"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="44"/>
+      <c r="G128" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H127" s="52">
-        <v>0</v>
-      </c>
-      <c r="I127" s="53"/>
-      <c r="J127" s="48"/>
-      <c r="K127" s="49"/>
-      <c r="L127" s="0"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B128" s="45">
-        <v>0000106234</v>
-      </c>
-      <c r="C128" t="s" s="46">
-        <v>234</v>
-      </c>
-      <c r="D128" t="s" s="46">
-        <v>231</v>
-      </c>
-      <c r="E128" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F128" t="s" s="44">
-        <v>235</v>
-      </c>
-      <c r="G128" s="51">
-        <v>5</v>
-      </c>
       <c r="H128" s="52">
-        <v>0</v>
-      </c>
-      <c r="I128" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J128" t="s" s="48">
-        <v>236</v>
-      </c>
-      <c r="K128" t="s" s="49">
-        <v>237</v>
-      </c>
+        <v>2696</v>
+      </c>
+      <c r="I128" s="53"/>
+      <c r="J128" s="48"/>
+      <c r="K128" s="49"/>
       <c r="L128" s="0"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="44">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="B129" s="45">
-        <v>0000106234</v>
+        <v>0000106325</v>
       </c>
       <c r="C129" t="s" s="46">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D129" t="s" s="46">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E129" t="s" s="47">
-        <v>69</v>
+        <v>242</v>
       </c>
       <c r="F129" t="s" s="44">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G129" s="51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H129" s="52">
-        <v>0</v>
+        <v>89.15</v>
       </c>
       <c r="I129" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J129" t="s" s="48">
-        <v>239</v>
-      </c>
-      <c r="K129" t="s" s="49">
-        <v>237</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="K129" s="49"/>
       <c r="L129" s="0"/>
     </row>
     <row r="130">
-      <c r="A130" s="44"/>
-      <c r="B130" s="45"/>
-      <c r="C130" s="46"/>
-      <c r="D130" s="46"/>
-      <c r="E130" s="47"/>
-      <c r="F130" s="44"/>
-      <c r="G130" t="s" s="51">
-        <v>31</v>
+      <c r="A130" t="s" s="44">
+        <v>240</v>
+      </c>
+      <c r="B130" s="45">
+        <v>0000106325</v>
+      </c>
+      <c r="C130" t="s" s="46">
+        <v>241</v>
+      </c>
+      <c r="D130" t="s" s="46">
+        <v>236</v>
+      </c>
+      <c r="E130" t="s" s="47">
+        <v>242</v>
+      </c>
+      <c r="F130" t="s" s="44">
+        <v>245</v>
+      </c>
+      <c r="G130" s="51">
+        <v>1</v>
       </c>
       <c r="H130" s="52">
-        <v>0</v>
-      </c>
-      <c r="I130" s="53"/>
-      <c r="J130" s="48"/>
+        <v>510.61</v>
+      </c>
+      <c r="I130" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J130" t="s" s="48">
+        <v>246</v>
+      </c>
       <c r="K130" s="49"/>
       <c r="L130" s="0"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="44">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="B131" s="45">
-        <v>0000106644</v>
+        <v>0000106325</v>
       </c>
       <c r="C131" t="s" s="46">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D131" t="s" s="46">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E131" t="s" s="47">
-        <v>69</v>
+        <v>242</v>
       </c>
       <c r="F131" t="s" s="44">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="G131" s="51">
         <v>1</v>
       </c>
       <c r="H131" s="52">
-        <v>2132.20</v>
+        <v>0</v>
       </c>
       <c r="I131" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J131" t="s" s="48">
-        <v>242</v>
-      </c>
-      <c r="K131" t="s" s="49">
-        <v>243</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="K131" s="49"/>
       <c r="L131" s="0"/>
     </row>
     <row r="132">
-      <c r="A132" t="s" s="44">
-        <v>42</v>
-      </c>
-      <c r="B132" s="45">
-        <v>0000106644</v>
-      </c>
-      <c r="C132" t="s" s="46">
-        <v>240</v>
-      </c>
-      <c r="D132" t="s" s="46">
-        <v>231</v>
-      </c>
-      <c r="E132" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F132" t="s" s="44">
-        <v>244</v>
-      </c>
-      <c r="G132" s="51">
-        <v>1</v>
+      <c r="A132" s="44"/>
+      <c r="B132" s="45"/>
+      <c r="C132" s="46"/>
+      <c r="D132" s="46"/>
+      <c r="E132" s="47"/>
+      <c r="F132" s="44"/>
+      <c r="G132" t="s" s="51">
+        <v>31</v>
       </c>
       <c r="H132" s="52">
-        <v>1359.96</v>
-      </c>
-      <c r="I132" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J132" t="s" s="48">
-        <v>245</v>
-      </c>
-      <c r="K132" t="s" s="49">
-        <v>243</v>
-      </c>
+        <v>599.76</v>
+      </c>
+      <c r="I132" s="53"/>
+      <c r="J132" s="48"/>
+      <c r="K132" s="49"/>
       <c r="L132" s="0"/>
     </row>
     <row r="133">
@@ -5378,34 +5497,34 @@
         <v>42</v>
       </c>
       <c r="B133" s="45">
-        <v>0000106644</v>
+        <v>0000107022</v>
       </c>
       <c r="C133" t="s" s="46">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="D133" t="s" s="46">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E133" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F133" t="s" s="44">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="G133" s="51">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="H133" s="52">
-        <v>949.92</v>
-      </c>
-      <c r="I133" t="s" s="53">
-        <v>18</v>
+        <v>376.11</v>
+      </c>
+      <c r="I133" s="53">
+        <v>87.5</v>
       </c>
       <c r="J133" t="s" s="48">
-        <v>247</v>
+        <v>115</v>
       </c>
       <c r="K133" t="s" s="49">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L133" s="0"/>
     </row>
@@ -5414,34 +5533,34 @@
         <v>42</v>
       </c>
       <c r="B134" s="45">
-        <v>0000106644</v>
+        <v>0000107022</v>
       </c>
       <c r="C134" t="s" s="46">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="D134" t="s" s="46">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E134" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F134" t="s" s="44">
+        <v>68</v>
+      </c>
+      <c r="G134" s="51">
+        <v>48</v>
+      </c>
+      <c r="H134" s="52">
+        <v>320.39</v>
+      </c>
+      <c r="I134" s="53">
+        <v>72</v>
+      </c>
+      <c r="J134" t="s" s="48">
         <v>69</v>
       </c>
-      <c r="F134" t="s" s="44">
-        <v>248</v>
-      </c>
-      <c r="G134" s="51">
-        <v>1</v>
-      </c>
-      <c r="H134" s="52">
-        <v>531.68</v>
-      </c>
-      <c r="I134" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J134" t="s" s="48">
-        <v>249</v>
-      </c>
       <c r="K134" t="s" s="49">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L134" s="0"/>
     </row>
@@ -5451,102 +5570,104 @@
       <c r="C135" s="46"/>
       <c r="D135" s="46"/>
       <c r="E135" s="47"/>
-      <c r="F135" s="44"/>
+      <c r="F135" t="s" s="44">
+        <v>18</v>
+      </c>
       <c r="G135" t="s" s="51">
         <v>31</v>
       </c>
       <c r="H135" s="52">
-        <v>4973.76</v>
-      </c>
-      <c r="I135" s="53"/>
-      <c r="J135" s="48"/>
+        <v>41706.42</v>
+      </c>
+      <c r="I135" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" t="s" s="48">
+        <v>18</v>
+      </c>
       <c r="K135" s="49"/>
       <c r="L135" s="0"/>
     </row>
     <row r="136">
-      <c r="A136" t="s" s="44">
-        <v>250</v>
-      </c>
-      <c r="B136" s="45">
-        <v>0000106764</v>
-      </c>
-      <c r="C136" t="s" s="46">
+      <c r="A136" s="44"/>
+      <c r="B136" s="45"/>
+      <c r="C136" s="46"/>
+      <c r="D136" s="46"/>
+      <c r="E136" s="47"/>
+      <c r="F136" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="G136" t="s" s="51">
+        <v>48</v>
+      </c>
+      <c r="H136" s="52">
+        <v>102334.08</v>
+      </c>
+      <c r="I136" s="53">
+        <v>373.65</v>
+      </c>
+      <c r="J136" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="K136" s="49"/>
+      <c r="L136" s="0"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B137" s="45">
+        <v>0000107026</v>
+      </c>
+      <c r="C137" t="s" s="46">
+        <v>83</v>
+      </c>
+      <c r="D137" t="s" s="46">
         <v>251</v>
       </c>
-      <c r="D136" t="s" s="46">
-        <v>231</v>
-      </c>
-      <c r="E136" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F136" t="s" s="44">
+      <c r="E137" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F137" t="s" s="44">
+        <v>174</v>
+      </c>
+      <c r="G137" s="51">
+        <v>16</v>
+      </c>
+      <c r="H137" s="52">
+        <v>656.58</v>
+      </c>
+      <c r="I137" s="53">
+        <v>48</v>
+      </c>
+      <c r="J137" t="s" s="48">
+        <v>175</v>
+      </c>
+      <c r="K137" t="s" s="49">
         <v>252</v>
       </c>
-      <c r="G136" s="51">
-        <v>24</v>
-      </c>
-      <c r="H136" s="52">
-        <v>15</v>
-      </c>
-      <c r="I136" t="s" s="53">
+      <c r="L137" s="0"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="44"/>
+      <c r="B138" s="45"/>
+      <c r="C138" s="46"/>
+      <c r="D138" s="46"/>
+      <c r="E138" s="47"/>
+      <c r="F138" t="s" s="44">
         <v>18</v>
       </c>
-      <c r="J136" t="s" s="48">
-        <v>253</v>
-      </c>
-      <c r="K136" t="s" s="49">
-        <v>254</v>
-      </c>
-      <c r="L136" s="0"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="44"/>
-      <c r="B137" s="45"/>
-      <c r="C137" s="46"/>
-      <c r="D137" s="46"/>
-      <c r="E137" s="47"/>
-      <c r="F137" s="44"/>
-      <c r="G137" t="s" s="51">
+      <c r="G138" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H137" s="52">
-        <v>360</v>
-      </c>
-      <c r="I137" s="53"/>
-      <c r="J137" s="48"/>
-      <c r="K137" s="49"/>
-      <c r="L137" s="0"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="44">
-        <v>128</v>
-      </c>
-      <c r="B138" s="45">
-        <v>0000106173</v>
-      </c>
-      <c r="C138" t="s" s="46">
-        <v>230</v>
-      </c>
-      <c r="D138" t="s" s="46">
-        <v>231</v>
-      </c>
-      <c r="E138" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F138" t="s" s="44">
-        <v>144</v>
-      </c>
-      <c r="G138" s="51">
-        <v>180</v>
-      </c>
       <c r="H138" s="52">
-        <v>0</v>
-      </c>
-      <c r="I138" s="53">
-        <v>225</v>
+        <v>10505.28</v>
+      </c>
+      <c r="I138" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="J138" t="s" s="48">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="K138" s="49"/>
       <c r="L138" s="0"/>
@@ -5557,48 +5678,54 @@
       <c r="C139" s="46"/>
       <c r="D139" s="46"/>
       <c r="E139" s="47"/>
-      <c r="F139" s="44"/>
+      <c r="F139" s="44" t="s">
+        <v>257</v>
+      </c>
       <c r="G139" t="s" s="51">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H139" s="52">
-        <v>0</v>
-      </c>
-      <c r="I139" s="53"/>
-      <c r="J139" s="48"/>
+        <v>10505.28</v>
+      </c>
+      <c r="I139" s="53">
+        <v>48</v>
+      </c>
+      <c r="J139" s="48" t="s">
+        <v>258</v>
+      </c>
       <c r="K139" s="49"/>
       <c r="L139" s="0"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="44">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="B140" s="45">
-        <v>0000106174</v>
+        <v>0000106170</v>
       </c>
       <c r="C140" t="s" s="46">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="D140" t="s" s="46">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="E140" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F140" t="s" s="44">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="G140" s="51">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="H140" s="52">
         <v>0</v>
       </c>
       <c r="I140" s="53">
-        <v>225</v>
+        <v>72</v>
       </c>
       <c r="J140" t="s" s="48">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="K140" s="49"/>
       <c r="L140" s="0"/>
@@ -5623,34 +5750,34 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="44">
-        <v>179</v>
+        <v>42</v>
       </c>
       <c r="B142" s="45">
-        <v>0000106175</v>
+        <v>0000106171</v>
       </c>
       <c r="C142" t="s" s="46">
         <v>255</v>
       </c>
       <c r="D142" t="s" s="46">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="E142" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F142" t="s" s="44">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="G142" s="51">
-        <v>208</v>
+        <v>70</v>
       </c>
       <c r="H142" s="52">
-        <v>362.68</v>
+        <v>0</v>
       </c>
       <c r="I142" s="53">
-        <v>208</v>
+        <v>87.5</v>
       </c>
       <c r="J142" t="s" s="48">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="K142" s="49"/>
       <c r="L142" s="0"/>
@@ -5666,7 +5793,7 @@
         <v>31</v>
       </c>
       <c r="H143" s="52">
-        <v>75437.44</v>
+        <v>0</v>
       </c>
       <c r="I143" s="53"/>
       <c r="J143" s="48"/>
@@ -5675,34 +5802,34 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="44">
-        <v>179</v>
+        <v>42</v>
       </c>
       <c r="B144" s="45">
-        <v>0000106176</v>
+        <v>0000106172</v>
       </c>
       <c r="C144" t="s" s="46">
         <v>255</v>
       </c>
       <c r="D144" t="s" s="46">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="E144" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F144" t="s" s="44">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="G144" s="51">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="H144" s="52">
-        <v>509.41</v>
-      </c>
-      <c r="I144" t="s" s="53">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="I144" s="53">
+        <v>87.5</v>
       </c>
       <c r="J144" t="s" s="48">
-        <v>257</v>
+        <v>115</v>
       </c>
       <c r="K144" s="49"/>
       <c r="L144" s="0"/>
@@ -5718,7 +5845,7 @@
         <v>31</v>
       </c>
       <c r="H145" s="52">
-        <v>26489.32</v>
+        <v>0</v>
       </c>
       <c r="I145" s="53"/>
       <c r="J145" s="48"/>
@@ -5727,174 +5854,236 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="44">
-        <v>179</v>
+        <v>42</v>
       </c>
       <c r="B146" s="45">
-        <v>0000106178</v>
+        <v>0000106234</v>
       </c>
       <c r="C146" t="s" s="46">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D146" t="s" s="46">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="E146" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F146" t="s" s="44">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G146" s="51">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="H146" s="52">
-        <v>489.76</v>
+        <v>0</v>
       </c>
       <c r="I146" t="s" s="53">
         <v>18</v>
       </c>
       <c r="J146" t="s" s="48">
+        <v>261</v>
+      </c>
+      <c r="K146" t="s" s="49">
+        <v>262</v>
+      </c>
+      <c r="L146" s="0"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B147" s="45">
+        <v>0000106234</v>
+      </c>
+      <c r="C147" t="s" s="46">
         <v>259</v>
       </c>
-      <c r="K146" s="49"/>
-      <c r="L146" s="0"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="44"/>
-      <c r="B147" s="45"/>
-      <c r="C147" s="46"/>
-      <c r="D147" s="46"/>
-      <c r="E147" s="47"/>
-      <c r="F147" s="44"/>
-      <c r="G147" t="s" s="51">
+      <c r="D147" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E147" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F147" t="s" s="44">
+        <v>121</v>
+      </c>
+      <c r="G147" s="51">
+        <v>5</v>
+      </c>
+      <c r="H147" s="52">
+        <v>0</v>
+      </c>
+      <c r="I147" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J147" t="s" s="48">
+        <v>122</v>
+      </c>
+      <c r="K147" t="s" s="49">
+        <v>262</v>
+      </c>
+      <c r="L147" s="0"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="44"/>
+      <c r="B148" s="45"/>
+      <c r="C148" s="46"/>
+      <c r="D148" s="46"/>
+      <c r="E148" s="47"/>
+      <c r="F148" s="44"/>
+      <c r="G148" t="s" s="51">
         <v>31</v>
       </c>
-      <c r="H147" s="52">
-        <v>25467.52</v>
-      </c>
-      <c r="I147" s="53"/>
-      <c r="J147" s="48"/>
-      <c r="K147" s="49"/>
-      <c r="L147" s="0"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="s" s="44">
-        <v>179</v>
-      </c>
-      <c r="B148" s="45">
-        <v>0000106179</v>
-      </c>
-      <c r="C148" t="s" s="46">
-        <v>255</v>
-      </c>
-      <c r="D148" t="s" s="46">
-        <v>231</v>
-      </c>
-      <c r="E148" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="F148" t="s" s="44">
-        <v>260</v>
-      </c>
-      <c r="G148" s="51">
-        <v>52</v>
-      </c>
       <c r="H148" s="52">
-        <v>458.18</v>
-      </c>
-      <c r="I148" t="s" s="53">
-        <v>18</v>
-      </c>
-      <c r="J148" t="s" s="48">
-        <v>261</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I148" s="53"/>
+      <c r="J148" s="48"/>
       <c r="K148" s="49"/>
       <c r="L148" s="0"/>
     </row>
     <row r="149">
-      <c r="A149" s="44"/>
-      <c r="B149" s="45"/>
-      <c r="C149" s="46"/>
-      <c r="D149" s="46"/>
-      <c r="E149" s="47"/>
-      <c r="F149" s="44"/>
-      <c r="G149" t="s" s="51">
-        <v>31</v>
+      <c r="A149" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B149" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C149" t="s" s="46">
+        <v>263</v>
+      </c>
+      <c r="D149" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E149" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F149" t="s" s="44">
+        <v>264</v>
+      </c>
+      <c r="G149" s="51">
+        <v>1</v>
       </c>
       <c r="H149" s="52">
-        <v>23825.36</v>
-      </c>
-      <c r="I149" s="53"/>
-      <c r="J149" s="48"/>
-      <c r="K149" s="49"/>
+        <v>2132.20</v>
+      </c>
+      <c r="I149" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J149" t="s" s="48">
+        <v>265</v>
+      </c>
+      <c r="K149" t="s" s="49">
+        <v>266</v>
+      </c>
       <c r="L149" s="0"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="44">
-        <v>179</v>
+        <v>42</v>
       </c>
       <c r="B150" s="45">
-        <v>0000106180</v>
+        <v>0000106644</v>
       </c>
       <c r="C150" t="s" s="46">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D150" t="s" s="46">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="E150" t="s" s="47">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F150" t="s" s="44">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G150" s="51">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="H150" s="52">
-        <v>466.80</v>
-      </c>
-      <c r="I150" s="53">
-        <v>104</v>
+        <v>1359.96</v>
+      </c>
+      <c r="I150" t="s" s="53">
+        <v>18</v>
       </c>
       <c r="J150" t="s" s="48">
+        <v>268</v>
+      </c>
+      <c r="K150" t="s" s="49">
+        <v>266</v>
+      </c>
+      <c r="L150" s="0"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B151" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C151" t="s" s="46">
         <v>263</v>
       </c>
-      <c r="K150" t="s" s="49">
-        <v>237</v>
-      </c>
-      <c r="L150" s="0"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="44"/>
-      <c r="B151" s="45"/>
-      <c r="C151" s="46"/>
-      <c r="D151" s="46"/>
-      <c r="E151" s="47"/>
-      <c r="F151" s="44"/>
-      <c r="G151" t="s" s="51">
-        <v>31</v>
+      <c r="D151" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E151" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F151" t="s" s="44">
+        <v>269</v>
+      </c>
+      <c r="G151" s="51">
+        <v>1</v>
       </c>
       <c r="H151" s="52">
-        <v>48547.2</v>
-      </c>
-      <c r="I151" s="53"/>
-      <c r="J151" s="48"/>
-      <c r="K151" s="49"/>
+        <v>949.92</v>
+      </c>
+      <c r="I151" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J151" t="s" s="48">
+        <v>270</v>
+      </c>
+      <c r="K151" t="s" s="49">
+        <v>266</v>
+      </c>
       <c r="L151" s="0"/>
     </row>
     <row r="152">
-      <c r="A152" s="44"/>
-      <c r="B152" s="45"/>
-      <c r="C152" s="46"/>
-      <c r="D152" s="46"/>
-      <c r="E152" s="47"/>
-      <c r="F152" s="44"/>
-      <c r="G152" s="51"/>
-      <c r="H152" s="52"/>
-      <c r="I152" s="53"/>
-      <c r="J152" s="48"/>
-      <c r="K152" s="49"/>
+      <c r="A152" t="s" s="44">
+        <v>42</v>
+      </c>
+      <c r="B152" s="45">
+        <v>0000106644</v>
+      </c>
+      <c r="C152" t="s" s="46">
+        <v>263</v>
+      </c>
+      <c r="D152" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E152" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F152" t="s" s="44">
+        <v>271</v>
+      </c>
+      <c r="G152" s="51">
+        <v>1</v>
+      </c>
+      <c r="H152" s="52">
+        <v>531.68</v>
+      </c>
+      <c r="I152" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J152" t="s" s="48">
+        <v>272</v>
+      </c>
+      <c r="K152" t="s" s="49">
+        <v>266</v>
+      </c>
       <c r="L152" s="0"/>
     </row>
     <row r="153">
@@ -5908,236 +6097,426 @@
         <v>31</v>
       </c>
       <c r="H153" s="52">
-        <v>932389.07</v>
-      </c>
-      <c r="I153" s="53">
-        <v>1339.25</v>
-      </c>
+        <v>4973.76</v>
+      </c>
+      <c r="I153" s="53"/>
       <c r="J153" s="48"/>
       <c r="K153" s="49"/>
       <c r="L153" s="0"/>
     </row>
-    <row r="154" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="44"/>
-      <c r="B154" s="45"/>
-      <c r="C154" s="46"/>
-      <c r="D154" s="46"/>
-      <c r="E154" s="47"/>
-      <c r="F154" s="44"/>
-      <c r="G154" s="51"/>
-      <c r="H154" s="52"/>
-      <c r="I154" s="53"/>
-      <c r="J154" s="48"/>
+    <row r="154">
+      <c r="A154" t="s" s="44">
+        <v>123</v>
+      </c>
+      <c r="B154" s="45">
+        <v>0000106173</v>
+      </c>
+      <c r="C154" t="s" s="46">
+        <v>255</v>
+      </c>
+      <c r="D154" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E154" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F154" t="s" s="44">
+        <v>135</v>
+      </c>
+      <c r="G154" s="51">
+        <v>180</v>
+      </c>
+      <c r="H154" s="52">
+        <v>0</v>
+      </c>
+      <c r="I154" s="53">
+        <v>225</v>
+      </c>
+      <c r="J154" t="s" s="48">
+        <v>136</v>
+      </c>
       <c r="K154" s="49"/>
       <c r="L154" s="0"/>
     </row>
-    <row r="155" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="5"/>
-      <c r="B155" s="25"/>
-      <c r="C155" s="19"/>
-      <c r="D155" s="19"/>
-      <c r="E155" s="13"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="25"/>
-      <c r="H155" s="25"/>
-      <c r="I155" s="25"/>
-      <c r="J155" s="36"/>
-      <c r="K155" s="29"/>
-    </row>
-    <row r="156" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="5"/>
-      <c r="B156" s="25"/>
-      <c r="C156" s="19"/>
-      <c r="D156" s="19"/>
-      <c r="E156" s="13"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="25"/>
-      <c r="H156" s="25"/>
-      <c r="I156" s="25"/>
-      <c r="J156" s="36"/>
-      <c r="K156" s="29"/>
-    </row>
-    <row r="157" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="5"/>
-      <c r="B157" s="25"/>
-      <c r="C157" s="19"/>
-      <c r="D157" s="19"/>
-      <c r="E157" s="13"/>
-      <c r="F157" s="5"/>
-      <c r="G157" s="25"/>
-      <c r="H157" s="25"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="36"/>
-      <c r="K157" s="29"/>
-    </row>
-    <row r="158" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="5"/>
-      <c r="B158" s="25"/>
-      <c r="C158" s="19"/>
-      <c r="D158" s="19"/>
-      <c r="E158" s="13"/>
-      <c r="F158" s="5"/>
-      <c r="G158" s="25"/>
-      <c r="H158" s="25"/>
-      <c r="I158" s="25"/>
-      <c r="J158" s="36"/>
-      <c r="K158" s="29"/>
-    </row>
-    <row r="159" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="5"/>
-      <c r="B159" s="25"/>
-      <c r="C159" s="19"/>
-      <c r="D159" s="19"/>
-      <c r="E159" s="13"/>
-      <c r="F159" s="5"/>
-      <c r="G159" s="25"/>
-      <c r="H159" s="25"/>
-      <c r="I159" s="25"/>
-      <c r="J159" s="36"/>
-      <c r="K159" s="29"/>
-    </row>
-    <row r="160" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="5"/>
-      <c r="B160" s="25"/>
-      <c r="C160" s="19"/>
-      <c r="D160" s="19"/>
-      <c r="E160" s="13"/>
-      <c r="F160" s="5"/>
-      <c r="G160" s="25"/>
-      <c r="H160" s="25"/>
-      <c r="I160" s="25"/>
-      <c r="J160" s="36"/>
-      <c r="K160" s="29"/>
-    </row>
-    <row r="161" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="5"/>
-      <c r="B161" s="25"/>
-      <c r="C161" s="19"/>
-      <c r="D161" s="19"/>
-      <c r="E161" s="13"/>
-      <c r="F161" s="5"/>
-      <c r="G161" s="25"/>
-      <c r="H161" s="25"/>
-      <c r="I161" s="25"/>
-      <c r="J161" s="36"/>
-      <c r="K161" s="29"/>
-    </row>
-    <row r="162" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="5"/>
-      <c r="B162" s="25"/>
-      <c r="C162" s="19"/>
-      <c r="D162" s="19"/>
-      <c r="E162" s="13"/>
-      <c r="F162" s="5"/>
-      <c r="G162" s="25"/>
-      <c r="H162" s="25"/>
-      <c r="I162" s="25"/>
-      <c r="J162" s="36"/>
-      <c r="K162" s="29"/>
-    </row>
-    <row r="163" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="5"/>
-      <c r="B163" s="25"/>
-      <c r="C163" s="19"/>
-      <c r="D163" s="19"/>
-      <c r="E163" s="13"/>
-      <c r="F163" s="5"/>
-      <c r="G163" s="25"/>
-      <c r="H163" s="25"/>
-      <c r="I163" s="25"/>
-      <c r="J163" s="36"/>
-      <c r="K163" s="29"/>
-    </row>
-    <row r="164" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="5"/>
-      <c r="B164" s="25"/>
-      <c r="C164" s="19"/>
-      <c r="D164" s="19"/>
-      <c r="E164" s="13"/>
-      <c r="F164" s="5"/>
-      <c r="G164" s="25"/>
-      <c r="H164" s="25"/>
-      <c r="I164" s="25"/>
-      <c r="J164" s="36"/>
-      <c r="K164" s="29"/>
-    </row>
-    <row r="165" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="5"/>
-      <c r="B165" s="25"/>
-      <c r="C165" s="19"/>
-      <c r="D165" s="19"/>
-      <c r="E165" s="13"/>
-      <c r="F165" s="5"/>
-      <c r="G165" s="25"/>
-      <c r="H165" s="25"/>
-      <c r="I165" s="25"/>
-      <c r="J165" s="36"/>
-      <c r="K165" s="29"/>
-    </row>
-    <row r="166" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="5"/>
-      <c r="B166" s="25"/>
-      <c r="C166" s="19"/>
-      <c r="D166" s="19"/>
-      <c r="E166" s="13"/>
-      <c r="F166" s="5"/>
-      <c r="G166" s="25"/>
-      <c r="H166" s="25"/>
-      <c r="I166" s="25"/>
-      <c r="J166" s="36"/>
-      <c r="K166" s="29"/>
-    </row>
-    <row r="167" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="5"/>
-      <c r="B167" s="25"/>
-      <c r="C167" s="19"/>
-      <c r="D167" s="19"/>
-      <c r="E167" s="13"/>
-      <c r="F167" s="5"/>
-      <c r="G167" s="25"/>
-      <c r="H167" s="25"/>
-      <c r="I167" s="25"/>
-      <c r="J167" s="36"/>
-      <c r="K167" s="29"/>
-    </row>
-    <row r="168" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="5"/>
-      <c r="B168" s="25"/>
-      <c r="C168" s="19"/>
-      <c r="D168" s="19"/>
-      <c r="E168" s="13"/>
-      <c r="F168" s="5"/>
-      <c r="G168" s="25"/>
-      <c r="H168" s="25"/>
-      <c r="I168" s="25"/>
-      <c r="J168" s="36"/>
-      <c r="K168" s="29"/>
-    </row>
-    <row r="169" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="5"/>
-      <c r="B169" s="25"/>
-      <c r="C169" s="19"/>
-      <c r="D169" s="19"/>
-      <c r="E169" s="13"/>
-      <c r="F169" s="5"/>
-      <c r="G169" s="25"/>
-      <c r="H169" s="25"/>
-      <c r="I169" s="25"/>
-      <c r="J169" s="36"/>
-      <c r="K169" s="29"/>
+    <row r="155">
+      <c r="A155" s="44"/>
+      <c r="B155" s="45"/>
+      <c r="C155" s="46"/>
+      <c r="D155" s="46"/>
+      <c r="E155" s="47"/>
+      <c r="F155" s="44"/>
+      <c r="G155" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H155" s="52">
+        <v>0</v>
+      </c>
+      <c r="I155" s="53"/>
+      <c r="J155" s="48"/>
+      <c r="K155" s="49"/>
+      <c r="L155" s="0"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="44">
+        <v>123</v>
+      </c>
+      <c r="B156" s="45">
+        <v>0000106174</v>
+      </c>
+      <c r="C156" t="s" s="46">
+        <v>255</v>
+      </c>
+      <c r="D156" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E156" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F156" t="s" s="44">
+        <v>135</v>
+      </c>
+      <c r="G156" s="51">
+        <v>180</v>
+      </c>
+      <c r="H156" s="52">
+        <v>0</v>
+      </c>
+      <c r="I156" s="53">
+        <v>225</v>
+      </c>
+      <c r="J156" t="s" s="48">
+        <v>136</v>
+      </c>
+      <c r="K156" s="49"/>
+      <c r="L156" s="0"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="44"/>
+      <c r="B157" s="45"/>
+      <c r="C157" s="46"/>
+      <c r="D157" s="46"/>
+      <c r="E157" s="47"/>
+      <c r="F157" s="44"/>
+      <c r="G157" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H157" s="52">
+        <v>0</v>
+      </c>
+      <c r="I157" s="53"/>
+      <c r="J157" s="48"/>
+      <c r="K157" s="49"/>
+      <c r="L157" s="0"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="44">
+        <v>188</v>
+      </c>
+      <c r="B158" s="45">
+        <v>0000106175</v>
+      </c>
+      <c r="C158" t="s" s="46">
+        <v>273</v>
+      </c>
+      <c r="D158" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E158" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F158" t="s" s="44">
+        <v>56</v>
+      </c>
+      <c r="G158" s="51">
+        <v>208</v>
+      </c>
+      <c r="H158" s="52">
+        <v>362.68</v>
+      </c>
+      <c r="I158" s="53">
+        <v>208</v>
+      </c>
+      <c r="J158" t="s" s="48">
+        <v>57</v>
+      </c>
+      <c r="K158" s="49"/>
+      <c r="L158" s="0"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="44"/>
+      <c r="B159" s="45"/>
+      <c r="C159" s="46"/>
+      <c r="D159" s="46"/>
+      <c r="E159" s="47"/>
+      <c r="F159" s="44"/>
+      <c r="G159" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H159" s="52">
+        <v>75437.44</v>
+      </c>
+      <c r="I159" s="53"/>
+      <c r="J159" s="48"/>
+      <c r="K159" s="49"/>
+      <c r="L159" s="0"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="44">
+        <v>188</v>
+      </c>
+      <c r="B160" s="45">
+        <v>0000106176</v>
+      </c>
+      <c r="C160" t="s" s="46">
+        <v>273</v>
+      </c>
+      <c r="D160" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E160" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F160" t="s" s="44">
+        <v>274</v>
+      </c>
+      <c r="G160" s="51">
+        <v>52</v>
+      </c>
+      <c r="H160" s="52">
+        <v>509.41</v>
+      </c>
+      <c r="I160" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J160" t="s" s="48">
+        <v>275</v>
+      </c>
+      <c r="K160" s="49"/>
+      <c r="L160" s="0"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="44"/>
+      <c r="B161" s="45"/>
+      <c r="C161" s="46"/>
+      <c r="D161" s="46"/>
+      <c r="E161" s="47"/>
+      <c r="F161" s="44"/>
+      <c r="G161" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H161" s="52">
+        <v>26489.32</v>
+      </c>
+      <c r="I161" s="53"/>
+      <c r="J161" s="48"/>
+      <c r="K161" s="49"/>
+      <c r="L161" s="0"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="44">
+        <v>188</v>
+      </c>
+      <c r="B162" s="45">
+        <v>0000106178</v>
+      </c>
+      <c r="C162" t="s" s="46">
+        <v>273</v>
+      </c>
+      <c r="D162" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E162" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F162" t="s" s="44">
+        <v>276</v>
+      </c>
+      <c r="G162" s="51">
+        <v>52</v>
+      </c>
+      <c r="H162" s="52">
+        <v>489.76</v>
+      </c>
+      <c r="I162" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J162" t="s" s="48">
+        <v>277</v>
+      </c>
+      <c r="K162" s="49"/>
+      <c r="L162" s="0"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="44"/>
+      <c r="B163" s="45"/>
+      <c r="C163" s="46"/>
+      <c r="D163" s="46"/>
+      <c r="E163" s="47"/>
+      <c r="F163" s="44"/>
+      <c r="G163" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H163" s="52">
+        <v>25467.52</v>
+      </c>
+      <c r="I163" s="53"/>
+      <c r="J163" s="48"/>
+      <c r="K163" s="49"/>
+      <c r="L163" s="0"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="44">
+        <v>188</v>
+      </c>
+      <c r="B164" s="45">
+        <v>0000106179</v>
+      </c>
+      <c r="C164" t="s" s="46">
+        <v>273</v>
+      </c>
+      <c r="D164" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E164" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F164" t="s" s="44">
+        <v>278</v>
+      </c>
+      <c r="G164" s="51">
+        <v>52</v>
+      </c>
+      <c r="H164" s="52">
+        <v>458.18</v>
+      </c>
+      <c r="I164" t="s" s="53">
+        <v>18</v>
+      </c>
+      <c r="J164" t="s" s="48">
+        <v>279</v>
+      </c>
+      <c r="K164" s="49"/>
+      <c r="L164" s="0"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="44"/>
+      <c r="B165" s="45"/>
+      <c r="C165" s="46"/>
+      <c r="D165" s="46"/>
+      <c r="E165" s="47"/>
+      <c r="F165" s="44"/>
+      <c r="G165" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H165" s="52">
+        <v>23825.36</v>
+      </c>
+      <c r="I165" s="53"/>
+      <c r="J165" s="48"/>
+      <c r="K165" s="49"/>
+      <c r="L165" s="0"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="44">
+        <v>188</v>
+      </c>
+      <c r="B166" s="45">
+        <v>0000106180</v>
+      </c>
+      <c r="C166" t="s" s="46">
+        <v>273</v>
+      </c>
+      <c r="D166" t="s" s="46">
+        <v>256</v>
+      </c>
+      <c r="E166" t="s" s="47">
+        <v>73</v>
+      </c>
+      <c r="F166" t="s" s="44">
+        <v>280</v>
+      </c>
+      <c r="G166" s="51">
+        <v>104</v>
+      </c>
+      <c r="H166" s="52">
+        <v>466.80</v>
+      </c>
+      <c r="I166" s="53">
+        <v>104</v>
+      </c>
+      <c r="J166" t="s" s="48">
+        <v>281</v>
+      </c>
+      <c r="K166" t="s" s="49">
+        <v>262</v>
+      </c>
+      <c r="L166" s="0"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="44"/>
+      <c r="B167" s="45"/>
+      <c r="C167" s="46"/>
+      <c r="D167" s="46"/>
+      <c r="E167" s="47"/>
+      <c r="F167" s="44"/>
+      <c r="G167" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H167" s="52">
+        <v>48547.2</v>
+      </c>
+      <c r="I167" s="53"/>
+      <c r="J167" s="48"/>
+      <c r="K167" s="49"/>
+      <c r="L167" s="0"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="44"/>
+      <c r="B168" s="45"/>
+      <c r="C168" s="46"/>
+      <c r="D168" s="46"/>
+      <c r="E168" s="47"/>
+      <c r="F168" s="44"/>
+      <c r="G168" s="51"/>
+      <c r="H168" s="52"/>
+      <c r="I168" s="53"/>
+      <c r="J168" s="48"/>
+      <c r="K168" s="49"/>
+      <c r="L168" s="0"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="44"/>
+      <c r="B169" s="45"/>
+      <c r="C169" s="46"/>
+      <c r="D169" s="46"/>
+      <c r="E169" s="47"/>
+      <c r="F169" s="44"/>
+      <c r="G169" t="s" s="51">
+        <v>31</v>
+      </c>
+      <c r="H169" s="52">
+        <v>1153382.26</v>
+      </c>
+      <c r="I169" s="53">
+        <v>2046.75</v>
+      </c>
+      <c r="J169" s="48"/>
+      <c r="K169" s="49"/>
+      <c r="L169" s="0"/>
     </row>
     <row r="170" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="5"/>
-      <c r="B170" s="25"/>
-      <c r="C170" s="19"/>
-      <c r="D170" s="19"/>
-      <c r="E170" s="13"/>
-      <c r="F170" s="5"/>
-      <c r="G170" s="25"/>
-      <c r="H170" s="25"/>
-      <c r="I170" s="25"/>
-      <c r="J170" s="36"/>
-      <c r="K170" s="29"/>
+      <c r="A170" s="44"/>
+      <c r="B170" s="45"/>
+      <c r="C170" s="46"/>
+      <c r="D170" s="46"/>
+      <c r="E170" s="47"/>
+      <c r="F170" s="44"/>
+      <c r="G170" s="51"/>
+      <c r="H170" s="52"/>
+      <c r="I170" s="53"/>
+      <c r="J170" s="48"/>
+      <c r="K170" s="49"/>
+      <c r="L170" s="0"/>
     </row>
     <row r="171" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A171" s="5"/>
@@ -6191,7 +6570,7 @@
       <c r="J174" s="36"/>
       <c r="K174" s="29"/>
     </row>
-    <row r="175" x14ac:dyDescent="0.2">
+    <row r="175" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="25"/>
       <c r="C175" s="19"/>
@@ -6204,7 +6583,7 @@
       <c r="J175" s="36"/>
       <c r="K175" s="29"/>
     </row>
-    <row r="176" x14ac:dyDescent="0.2">
+    <row r="176" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="25"/>
       <c r="C176" s="19"/>
@@ -6217,7 +6596,7 @@
       <c r="J176" s="36"/>
       <c r="K176" s="29"/>
     </row>
-    <row r="177" x14ac:dyDescent="0.2">
+    <row r="177" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="25"/>
       <c r="C177" s="19"/>
@@ -6230,7 +6609,7 @@
       <c r="J177" s="36"/>
       <c r="K177" s="29"/>
     </row>
-    <row r="178" x14ac:dyDescent="0.2">
+    <row r="178" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="25"/>
       <c r="C178" s="19"/>
@@ -6243,7 +6622,7 @@
       <c r="J178" s="36"/>
       <c r="K178" s="29"/>
     </row>
-    <row r="179" x14ac:dyDescent="0.2">
+    <row r="179" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="25"/>
       <c r="C179" s="19"/>
@@ -6256,7 +6635,7 @@
       <c r="J179" s="36"/>
       <c r="K179" s="29"/>
     </row>
-    <row r="180" x14ac:dyDescent="0.2">
+    <row r="180" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="25"/>
       <c r="C180" s="19"/>
@@ -6269,7 +6648,7 @@
       <c r="J180" s="36"/>
       <c r="K180" s="29"/>
     </row>
-    <row r="181" x14ac:dyDescent="0.2">
+    <row r="181" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="25"/>
       <c r="C181" s="19"/>
@@ -6282,7 +6661,7 @@
       <c r="J181" s="36"/>
       <c r="K181" s="29"/>
     </row>
-    <row r="182" x14ac:dyDescent="0.2">
+    <row r="182" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="25"/>
       <c r="C182" s="19"/>
@@ -6295,7 +6674,7 @@
       <c r="J182" s="36"/>
       <c r="K182" s="29"/>
     </row>
-    <row r="183" x14ac:dyDescent="0.2">
+    <row r="183" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="25"/>
       <c r="C183" s="19"/>
@@ -6308,7 +6687,7 @@
       <c r="J183" s="36"/>
       <c r="K183" s="29"/>
     </row>
-    <row r="184" x14ac:dyDescent="0.2">
+    <row r="184" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A184" s="5"/>
       <c r="B184" s="25"/>
       <c r="C184" s="19"/>
@@ -6321,7 +6700,7 @@
       <c r="J184" s="36"/>
       <c r="K184" s="29"/>
     </row>
-    <row r="185" x14ac:dyDescent="0.2">
+    <row r="185" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="5"/>
       <c r="B185" s="25"/>
       <c r="C185" s="19"/>
@@ -6334,7 +6713,7 @@
       <c r="J185" s="36"/>
       <c r="K185" s="29"/>
     </row>
-    <row r="186" x14ac:dyDescent="0.2">
+    <row r="186" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A186" s="5"/>
       <c r="B186" s="25"/>
       <c r="C186" s="19"/>
@@ -6347,7 +6726,7 @@
       <c r="J186" s="36"/>
       <c r="K186" s="29"/>
     </row>
-    <row r="187" x14ac:dyDescent="0.2">
+    <row r="187" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A187" s="5"/>
       <c r="B187" s="25"/>
       <c r="C187" s="19"/>
@@ -6360,7 +6739,7 @@
       <c r="J187" s="36"/>
       <c r="K187" s="29"/>
     </row>
-    <row r="188" x14ac:dyDescent="0.2">
+    <row r="188" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A188" s="5"/>
       <c r="B188" s="25"/>
       <c r="C188" s="19"/>
@@ -6373,7 +6752,7 @@
       <c r="J188" s="36"/>
       <c r="K188" s="29"/>
     </row>
-    <row r="189" x14ac:dyDescent="0.2">
+    <row r="189" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A189" s="5"/>
       <c r="B189" s="25"/>
       <c r="C189" s="19"/>
@@ -6386,7 +6765,7 @@
       <c r="J189" s="36"/>
       <c r="K189" s="29"/>
     </row>
-    <row r="190" x14ac:dyDescent="0.2">
+    <row r="190" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="5"/>
       <c r="B190" s="25"/>
       <c r="C190" s="19"/>
@@ -6517,212 +6896,212 @@
       <c r="K199" s="29"/>
     </row>
     <row r="200" x14ac:dyDescent="0.2">
-      <c r="A200" s="6"/>
-      <c r="B200" s="33"/>
-      <c r="C200" s="20"/>
-      <c r="D200" s="20"/>
-      <c r="E200" s="14"/>
-      <c r="F200" s="6"/>
+      <c r="A200" s="5"/>
+      <c r="B200" s="25"/>
+      <c r="C200" s="19"/>
+      <c r="D200" s="19"/>
+      <c r="E200" s="13"/>
+      <c r="F200" s="5"/>
       <c r="G200" s="25"/>
       <c r="H200" s="25"/>
       <c r="I200" s="25"/>
       <c r="J200" s="36"/>
-      <c r="K200" s="30"/>
+      <c r="K200" s="29"/>
     </row>
     <row r="201" x14ac:dyDescent="0.2">
-      <c r="A201" s="6"/>
-      <c r="B201" s="33"/>
-      <c r="C201" s="20"/>
-      <c r="D201" s="20"/>
-      <c r="E201" s="14"/>
-      <c r="F201" s="6"/>
+      <c r="A201" s="5"/>
+      <c r="B201" s="25"/>
+      <c r="C201" s="19"/>
+      <c r="D201" s="19"/>
+      <c r="E201" s="13"/>
+      <c r="F201" s="5"/>
       <c r="G201" s="25"/>
       <c r="H201" s="25"/>
       <c r="I201" s="25"/>
       <c r="J201" s="36"/>
-      <c r="K201" s="30"/>
+      <c r="K201" s="29"/>
     </row>
     <row r="202" x14ac:dyDescent="0.2">
-      <c r="A202" s="6"/>
-      <c r="B202" s="33"/>
-      <c r="C202" s="20"/>
-      <c r="D202" s="20"/>
-      <c r="E202" s="14"/>
-      <c r="F202" s="6"/>
+      <c r="A202" s="5"/>
+      <c r="B202" s="25"/>
+      <c r="C202" s="19"/>
+      <c r="D202" s="19"/>
+      <c r="E202" s="13"/>
+      <c r="F202" s="5"/>
       <c r="G202" s="25"/>
       <c r="H202" s="25"/>
       <c r="I202" s="25"/>
       <c r="J202" s="36"/>
-      <c r="K202" s="30"/>
+      <c r="K202" s="29"/>
     </row>
     <row r="203" x14ac:dyDescent="0.2">
-      <c r="A203" s="6"/>
-      <c r="B203" s="33"/>
-      <c r="C203" s="20"/>
-      <c r="D203" s="20"/>
-      <c r="E203" s="14"/>
-      <c r="F203" s="6"/>
+      <c r="A203" s="5"/>
+      <c r="B203" s="25"/>
+      <c r="C203" s="19"/>
+      <c r="D203" s="19"/>
+      <c r="E203" s="13"/>
+      <c r="F203" s="5"/>
       <c r="G203" s="25"/>
       <c r="H203" s="25"/>
       <c r="I203" s="25"/>
       <c r="J203" s="36"/>
-      <c r="K203" s="30"/>
+      <c r="K203" s="29"/>
     </row>
     <row r="204" x14ac:dyDescent="0.2">
-      <c r="A204" s="6"/>
-      <c r="B204" s="33"/>
-      <c r="C204" s="20"/>
-      <c r="D204" s="20"/>
-      <c r="E204" s="14"/>
-      <c r="F204" s="6"/>
+      <c r="A204" s="5"/>
+      <c r="B204" s="25"/>
+      <c r="C204" s="19"/>
+      <c r="D204" s="19"/>
+      <c r="E204" s="13"/>
+      <c r="F204" s="5"/>
       <c r="G204" s="25"/>
       <c r="H204" s="25"/>
       <c r="I204" s="25"/>
       <c r="J204" s="36"/>
-      <c r="K204" s="30"/>
+      <c r="K204" s="29"/>
     </row>
     <row r="205" x14ac:dyDescent="0.2">
-      <c r="A205" s="6"/>
-      <c r="B205" s="33"/>
-      <c r="C205" s="20"/>
-      <c r="D205" s="20"/>
-      <c r="E205" s="14"/>
-      <c r="F205" s="6"/>
+      <c r="A205" s="5"/>
+      <c r="B205" s="25"/>
+      <c r="C205" s="19"/>
+      <c r="D205" s="19"/>
+      <c r="E205" s="13"/>
+      <c r="F205" s="5"/>
       <c r="G205" s="25"/>
       <c r="H205" s="25"/>
       <c r="I205" s="25"/>
       <c r="J205" s="36"/>
-      <c r="K205" s="30"/>
+      <c r="K205" s="29"/>
     </row>
     <row r="206" x14ac:dyDescent="0.2">
-      <c r="A206" s="6"/>
-      <c r="B206" s="33"/>
-      <c r="C206" s="20"/>
-      <c r="D206" s="20"/>
-      <c r="E206" s="14"/>
-      <c r="F206" s="6"/>
+      <c r="A206" s="5"/>
+      <c r="B206" s="25"/>
+      <c r="C206" s="19"/>
+      <c r="D206" s="19"/>
+      <c r="E206" s="13"/>
+      <c r="F206" s="5"/>
       <c r="G206" s="25"/>
       <c r="H206" s="25"/>
       <c r="I206" s="25"/>
       <c r="J206" s="36"/>
-      <c r="K206" s="30"/>
+      <c r="K206" s="29"/>
     </row>
     <row r="207" x14ac:dyDescent="0.2">
-      <c r="A207" s="6"/>
-      <c r="B207" s="33"/>
-      <c r="C207" s="20"/>
-      <c r="D207" s="20"/>
-      <c r="E207" s="14"/>
-      <c r="F207" s="6"/>
+      <c r="A207" s="5"/>
+      <c r="B207" s="25"/>
+      <c r="C207" s="19"/>
+      <c r="D207" s="19"/>
+      <c r="E207" s="13"/>
+      <c r="F207" s="5"/>
       <c r="G207" s="25"/>
       <c r="H207" s="25"/>
       <c r="I207" s="25"/>
       <c r="J207" s="36"/>
-      <c r="K207" s="30"/>
+      <c r="K207" s="29"/>
     </row>
     <row r="208" x14ac:dyDescent="0.2">
-      <c r="A208" s="6"/>
-      <c r="B208" s="33"/>
-      <c r="C208" s="20"/>
-      <c r="D208" s="20"/>
-      <c r="E208" s="14"/>
-      <c r="F208" s="6"/>
+      <c r="A208" s="5"/>
+      <c r="B208" s="25"/>
+      <c r="C208" s="19"/>
+      <c r="D208" s="19"/>
+      <c r="E208" s="13"/>
+      <c r="F208" s="5"/>
       <c r="G208" s="25"/>
       <c r="H208" s="25"/>
       <c r="I208" s="25"/>
       <c r="J208" s="36"/>
-      <c r="K208" s="30"/>
+      <c r="K208" s="29"/>
     </row>
     <row r="209" x14ac:dyDescent="0.2">
-      <c r="A209" s="6"/>
-      <c r="B209" s="33"/>
-      <c r="C209" s="20"/>
-      <c r="D209" s="20"/>
-      <c r="E209" s="14"/>
-      <c r="F209" s="6"/>
+      <c r="A209" s="5"/>
+      <c r="B209" s="25"/>
+      <c r="C209" s="19"/>
+      <c r="D209" s="19"/>
+      <c r="E209" s="13"/>
+      <c r="F209" s="5"/>
       <c r="G209" s="25"/>
       <c r="H209" s="25"/>
       <c r="I209" s="25"/>
       <c r="J209" s="36"/>
-      <c r="K209" s="30"/>
+      <c r="K209" s="29"/>
     </row>
     <row r="210" x14ac:dyDescent="0.2">
-      <c r="A210" s="6"/>
-      <c r="B210" s="33"/>
-      <c r="C210" s="20"/>
-      <c r="D210" s="20"/>
-      <c r="E210" s="14"/>
-      <c r="F210" s="6"/>
+      <c r="A210" s="5"/>
+      <c r="B210" s="25"/>
+      <c r="C210" s="19"/>
+      <c r="D210" s="19"/>
+      <c r="E210" s="13"/>
+      <c r="F210" s="5"/>
       <c r="G210" s="25"/>
       <c r="H210" s="25"/>
       <c r="I210" s="25"/>
       <c r="J210" s="36"/>
-      <c r="K210" s="30"/>
+      <c r="K210" s="29"/>
     </row>
     <row r="211" x14ac:dyDescent="0.2">
-      <c r="A211" s="6"/>
-      <c r="B211" s="33"/>
-      <c r="C211" s="20"/>
-      <c r="D211" s="20"/>
-      <c r="E211" s="14"/>
-      <c r="F211" s="6"/>
+      <c r="A211" s="5"/>
+      <c r="B211" s="25"/>
+      <c r="C211" s="19"/>
+      <c r="D211" s="19"/>
+      <c r="E211" s="13"/>
+      <c r="F211" s="5"/>
       <c r="G211" s="25"/>
       <c r="H211" s="25"/>
       <c r="I211" s="25"/>
       <c r="J211" s="36"/>
-      <c r="K211" s="30"/>
+      <c r="K211" s="29"/>
     </row>
     <row r="212" x14ac:dyDescent="0.2">
-      <c r="A212" s="6"/>
-      <c r="B212" s="33"/>
-      <c r="C212" s="20"/>
-      <c r="D212" s="20"/>
-      <c r="E212" s="14"/>
-      <c r="F212" s="6"/>
+      <c r="A212" s="5"/>
+      <c r="B212" s="25"/>
+      <c r="C212" s="19"/>
+      <c r="D212" s="19"/>
+      <c r="E212" s="13"/>
+      <c r="F212" s="5"/>
       <c r="G212" s="25"/>
       <c r="H212" s="25"/>
       <c r="I212" s="25"/>
       <c r="J212" s="36"/>
-      <c r="K212" s="30"/>
+      <c r="K212" s="29"/>
     </row>
     <row r="213" x14ac:dyDescent="0.2">
-      <c r="A213" s="6"/>
-      <c r="B213" s="33"/>
-      <c r="C213" s="20"/>
-      <c r="D213" s="20"/>
-      <c r="E213" s="14"/>
-      <c r="F213" s="6"/>
+      <c r="A213" s="5"/>
+      <c r="B213" s="25"/>
+      <c r="C213" s="19"/>
+      <c r="D213" s="19"/>
+      <c r="E213" s="13"/>
+      <c r="F213" s="5"/>
       <c r="G213" s="25"/>
       <c r="H213" s="25"/>
       <c r="I213" s="25"/>
       <c r="J213" s="36"/>
-      <c r="K213" s="30"/>
+      <c r="K213" s="29"/>
     </row>
     <row r="214" x14ac:dyDescent="0.2">
-      <c r="A214" s="6"/>
-      <c r="B214" s="33"/>
-      <c r="C214" s="20"/>
-      <c r="D214" s="20"/>
-      <c r="E214" s="14"/>
-      <c r="F214" s="6"/>
+      <c r="A214" s="5"/>
+      <c r="B214" s="25"/>
+      <c r="C214" s="19"/>
+      <c r="D214" s="19"/>
+      <c r="E214" s="13"/>
+      <c r="F214" s="5"/>
       <c r="G214" s="25"/>
       <c r="H214" s="25"/>
       <c r="I214" s="25"/>
       <c r="J214" s="36"/>
-      <c r="K214" s="30"/>
+      <c r="K214" s="29"/>
     </row>
     <row r="215" x14ac:dyDescent="0.2">
-      <c r="A215" s="6"/>
-      <c r="B215" s="33"/>
-      <c r="C215" s="20"/>
-      <c r="D215" s="20"/>
-      <c r="E215" s="14"/>
-      <c r="F215" s="6"/>
+      <c r="A215" s="5"/>
+      <c r="B215" s="25"/>
+      <c r="C215" s="19"/>
+      <c r="D215" s="19"/>
+      <c r="E215" s="13"/>
+      <c r="F215" s="5"/>
       <c r="G215" s="25"/>
       <c r="H215" s="25"/>
       <c r="I215" s="25"/>
       <c r="J215" s="36"/>
-      <c r="K215" s="30"/>
+      <c r="K215" s="29"/>
     </row>
     <row r="216" x14ac:dyDescent="0.2">
       <c r="A216" s="6"/>
@@ -15019,7 +15398,7 @@
       <c r="K853" s="30"/>
     </row>
     <row r="854" x14ac:dyDescent="0.2">
-      <c r="A854" s="8"/>
+      <c r="A854" s="6"/>
       <c r="B854" s="33"/>
       <c r="C854" s="20"/>
       <c r="D854" s="20"/>
@@ -15032,7 +15411,7 @@
       <c r="K854" s="30"/>
     </row>
     <row r="855" x14ac:dyDescent="0.2">
-      <c r="A855" s="8"/>
+      <c r="A855" s="6"/>
       <c r="B855" s="33"/>
       <c r="C855" s="20"/>
       <c r="D855" s="20"/>
@@ -15045,7 +15424,7 @@
       <c r="K855" s="30"/>
     </row>
     <row r="856" x14ac:dyDescent="0.2">
-      <c r="A856" s="8"/>
+      <c r="A856" s="6"/>
       <c r="B856" s="33"/>
       <c r="C856" s="20"/>
       <c r="D856" s="20"/>
@@ -15058,7 +15437,7 @@
       <c r="K856" s="30"/>
     </row>
     <row r="857" x14ac:dyDescent="0.2">
-      <c r="A857" s="8"/>
+      <c r="A857" s="6"/>
       <c r="B857" s="33"/>
       <c r="C857" s="20"/>
       <c r="D857" s="20"/>
@@ -15071,7 +15450,7 @@
       <c r="K857" s="30"/>
     </row>
     <row r="858" x14ac:dyDescent="0.2">
-      <c r="A858" s="8"/>
+      <c r="A858" s="6"/>
       <c r="B858" s="33"/>
       <c r="C858" s="20"/>
       <c r="D858" s="20"/>
@@ -15084,7 +15463,7 @@
       <c r="K858" s="30"/>
     </row>
     <row r="859" x14ac:dyDescent="0.2">
-      <c r="A859" s="8"/>
+      <c r="A859" s="6"/>
       <c r="B859" s="33"/>
       <c r="C859" s="20"/>
       <c r="D859" s="20"/>
@@ -15097,7 +15476,7 @@
       <c r="K859" s="30"/>
     </row>
     <row r="860" x14ac:dyDescent="0.2">
-      <c r="A860" s="8"/>
+      <c r="A860" s="6"/>
       <c r="B860" s="33"/>
       <c r="C860" s="20"/>
       <c r="D860" s="20"/>
@@ -15110,7 +15489,7 @@
       <c r="K860" s="30"/>
     </row>
     <row r="861" x14ac:dyDescent="0.2">
-      <c r="A861" s="8"/>
+      <c r="A861" s="6"/>
       <c r="B861" s="33"/>
       <c r="C861" s="20"/>
       <c r="D861" s="20"/>
@@ -15123,7 +15502,7 @@
       <c r="K861" s="30"/>
     </row>
     <row r="862" x14ac:dyDescent="0.2">
-      <c r="A862" s="8"/>
+      <c r="A862" s="6"/>
       <c r="B862" s="33"/>
       <c r="C862" s="20"/>
       <c r="D862" s="20"/>
@@ -15136,7 +15515,7 @@
       <c r="K862" s="30"/>
     </row>
     <row r="863" x14ac:dyDescent="0.2">
-      <c r="A863" s="8"/>
+      <c r="A863" s="6"/>
       <c r="B863" s="33"/>
       <c r="C863" s="20"/>
       <c r="D863" s="20"/>
@@ -15149,7 +15528,7 @@
       <c r="K863" s="30"/>
     </row>
     <row r="864" x14ac:dyDescent="0.2">
-      <c r="A864" s="8"/>
+      <c r="A864" s="6"/>
       <c r="B864" s="33"/>
       <c r="C864" s="20"/>
       <c r="D864" s="20"/>
@@ -15162,7 +15541,7 @@
       <c r="K864" s="30"/>
     </row>
     <row r="865" x14ac:dyDescent="0.2">
-      <c r="A865" s="8"/>
+      <c r="A865" s="6"/>
       <c r="B865" s="33"/>
       <c r="C865" s="20"/>
       <c r="D865" s="20"/>
@@ -15175,7 +15554,7 @@
       <c r="K865" s="30"/>
     </row>
     <row r="866" x14ac:dyDescent="0.2">
-      <c r="A866" s="8"/>
+      <c r="A866" s="6"/>
       <c r="B866" s="33"/>
       <c r="C866" s="20"/>
       <c r="D866" s="20"/>
@@ -15188,7 +15567,7 @@
       <c r="K866" s="30"/>
     </row>
     <row r="867" x14ac:dyDescent="0.2">
-      <c r="A867" s="8"/>
+      <c r="A867" s="6"/>
       <c r="B867" s="33"/>
       <c r="C867" s="20"/>
       <c r="D867" s="20"/>
@@ -15201,7 +15580,7 @@
       <c r="K867" s="30"/>
     </row>
     <row r="868" x14ac:dyDescent="0.2">
-      <c r="A868" s="8"/>
+      <c r="A868" s="6"/>
       <c r="B868" s="33"/>
       <c r="C868" s="20"/>
       <c r="D868" s="20"/>
@@ -15214,7 +15593,7 @@
       <c r="K868" s="30"/>
     </row>
     <row r="869" x14ac:dyDescent="0.2">
-      <c r="A869" s="8"/>
+      <c r="A869" s="6"/>
       <c r="B869" s="33"/>
       <c r="C869" s="20"/>
       <c r="D869" s="20"/>
@@ -16903,117 +17282,213 @@
       <c r="J998" s="36"/>
       <c r="K998" s="30"/>
     </row>
-    <row r="999" ht="15" x14ac:dyDescent="0.25">
-      <c r="A999" s="4"/>
-      <c r="G999" s="26"/>
-      <c r="H999" s="26"/>
-      <c r="I999" s="26"/>
-      <c r="J999" s="37"/>
-    </row>
-    <row r="1000" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1000" s="4"/>
-      <c r="G1000" s="26"/>
-      <c r="H1000" s="26"/>
-      <c r="I1000" s="26"/>
-      <c r="J1000" s="37"/>
-    </row>
-    <row r="1001" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1001" s="4"/>
-      <c r="G1001" s="26"/>
-      <c r="H1001" s="26"/>
-      <c r="I1001" s="26"/>
-      <c r="J1001" s="37"/>
-    </row>
-    <row r="1002" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1002" s="4"/>
-      <c r="G1002" s="26"/>
-      <c r="H1002" s="26"/>
-      <c r="I1002" s="26"/>
-      <c r="J1002" s="37"/>
-    </row>
-    <row r="1003" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1003" s="4"/>
-      <c r="G1003" s="26"/>
-      <c r="H1003" s="26"/>
-      <c r="I1003" s="26"/>
-      <c r="J1003" s="37"/>
-    </row>
-    <row r="1004" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1004" s="4"/>
-      <c r="G1004" s="26"/>
-      <c r="H1004" s="26"/>
-      <c r="I1004" s="26"/>
-      <c r="J1004" s="37"/>
-    </row>
-    <row r="1005" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1005" s="4"/>
-      <c r="G1005" s="26"/>
-      <c r="H1005" s="26"/>
-      <c r="I1005" s="26"/>
-      <c r="J1005" s="37"/>
-    </row>
-    <row r="1006" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1006" s="4"/>
-      <c r="G1006" s="26"/>
-      <c r="H1006" s="26"/>
-      <c r="I1006" s="26"/>
-      <c r="J1006" s="37"/>
-    </row>
-    <row r="1007" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1007" s="4"/>
-      <c r="G1007" s="26"/>
-      <c r="H1007" s="26"/>
-      <c r="I1007" s="26"/>
-      <c r="J1007" s="37"/>
-    </row>
-    <row r="1008" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1008" s="4"/>
-      <c r="G1008" s="26"/>
-      <c r="H1008" s="26"/>
-      <c r="I1008" s="26"/>
-      <c r="J1008" s="37"/>
-    </row>
-    <row r="1009" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1009" s="4"/>
-      <c r="G1009" s="26"/>
-      <c r="H1009" s="26"/>
-      <c r="I1009" s="26"/>
-      <c r="J1009" s="37"/>
-    </row>
-    <row r="1010" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1010" s="4"/>
-      <c r="G1010" s="26"/>
-      <c r="H1010" s="26"/>
-      <c r="I1010" s="26"/>
-      <c r="J1010" s="37"/>
-    </row>
-    <row r="1011" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1011" s="4"/>
-      <c r="G1011" s="26"/>
-      <c r="H1011" s="26"/>
-      <c r="I1011" s="26"/>
-      <c r="J1011" s="37"/>
-    </row>
-    <row r="1012" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1012" s="4"/>
-      <c r="G1012" s="26"/>
-      <c r="H1012" s="26"/>
-      <c r="I1012" s="26"/>
-      <c r="J1012" s="37"/>
-    </row>
-    <row r="1013" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1013" s="4"/>
-      <c r="G1013" s="26"/>
-      <c r="H1013" s="26"/>
-      <c r="I1013" s="26"/>
-      <c r="J1013" s="37"/>
-    </row>
-    <row r="1014" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1014" s="4"/>
-      <c r="G1014" s="26"/>
-      <c r="H1014" s="26"/>
-      <c r="I1014" s="26"/>
-      <c r="J1014" s="37"/>
+    <row r="999" x14ac:dyDescent="0.2">
+      <c r="A999" s="8"/>
+      <c r="B999" s="33"/>
+      <c r="C999" s="20"/>
+      <c r="D999" s="20"/>
+      <c r="E999" s="14"/>
+      <c r="F999" s="6"/>
+      <c r="G999" s="25"/>
+      <c r="H999" s="25"/>
+      <c r="I999" s="25"/>
+      <c r="J999" s="36"/>
+      <c r="K999" s="30"/>
+    </row>
+    <row r="1000" x14ac:dyDescent="0.2">
+      <c r="A1000" s="8"/>
+      <c r="B1000" s="33"/>
+      <c r="C1000" s="20"/>
+      <c r="D1000" s="20"/>
+      <c r="E1000" s="14"/>
+      <c r="F1000" s="6"/>
+      <c r="G1000" s="25"/>
+      <c r="H1000" s="25"/>
+      <c r="I1000" s="25"/>
+      <c r="J1000" s="36"/>
+      <c r="K1000" s="30"/>
+    </row>
+    <row r="1001" x14ac:dyDescent="0.2">
+      <c r="A1001" s="8"/>
+      <c r="B1001" s="33"/>
+      <c r="C1001" s="20"/>
+      <c r="D1001" s="20"/>
+      <c r="E1001" s="14"/>
+      <c r="F1001" s="6"/>
+      <c r="G1001" s="25"/>
+      <c r="H1001" s="25"/>
+      <c r="I1001" s="25"/>
+      <c r="J1001" s="36"/>
+      <c r="K1001" s="30"/>
+    </row>
+    <row r="1002" x14ac:dyDescent="0.2">
+      <c r="A1002" s="8"/>
+      <c r="B1002" s="33"/>
+      <c r="C1002" s="20"/>
+      <c r="D1002" s="20"/>
+      <c r="E1002" s="14"/>
+      <c r="F1002" s="6"/>
+      <c r="G1002" s="25"/>
+      <c r="H1002" s="25"/>
+      <c r="I1002" s="25"/>
+      <c r="J1002" s="36"/>
+      <c r="K1002" s="30"/>
+    </row>
+    <row r="1003" x14ac:dyDescent="0.2">
+      <c r="A1003" s="8"/>
+      <c r="B1003" s="33"/>
+      <c r="C1003" s="20"/>
+      <c r="D1003" s="20"/>
+      <c r="E1003" s="14"/>
+      <c r="F1003" s="6"/>
+      <c r="G1003" s="25"/>
+      <c r="H1003" s="25"/>
+      <c r="I1003" s="25"/>
+      <c r="J1003" s="36"/>
+      <c r="K1003" s="30"/>
+    </row>
+    <row r="1004" x14ac:dyDescent="0.2">
+      <c r="A1004" s="8"/>
+      <c r="B1004" s="33"/>
+      <c r="C1004" s="20"/>
+      <c r="D1004" s="20"/>
+      <c r="E1004" s="14"/>
+      <c r="F1004" s="6"/>
+      <c r="G1004" s="25"/>
+      <c r="H1004" s="25"/>
+      <c r="I1004" s="25"/>
+      <c r="J1004" s="36"/>
+      <c r="K1004" s="30"/>
+    </row>
+    <row r="1005" x14ac:dyDescent="0.2">
+      <c r="A1005" s="8"/>
+      <c r="B1005" s="33"/>
+      <c r="C1005" s="20"/>
+      <c r="D1005" s="20"/>
+      <c r="E1005" s="14"/>
+      <c r="F1005" s="6"/>
+      <c r="G1005" s="25"/>
+      <c r="H1005" s="25"/>
+      <c r="I1005" s="25"/>
+      <c r="J1005" s="36"/>
+      <c r="K1005" s="30"/>
+    </row>
+    <row r="1006" x14ac:dyDescent="0.2">
+      <c r="A1006" s="8"/>
+      <c r="B1006" s="33"/>
+      <c r="C1006" s="20"/>
+      <c r="D1006" s="20"/>
+      <c r="E1006" s="14"/>
+      <c r="F1006" s="6"/>
+      <c r="G1006" s="25"/>
+      <c r="H1006" s="25"/>
+      <c r="I1006" s="25"/>
+      <c r="J1006" s="36"/>
+      <c r="K1006" s="30"/>
+    </row>
+    <row r="1007" x14ac:dyDescent="0.2">
+      <c r="A1007" s="8"/>
+      <c r="B1007" s="33"/>
+      <c r="C1007" s="20"/>
+      <c r="D1007" s="20"/>
+      <c r="E1007" s="14"/>
+      <c r="F1007" s="6"/>
+      <c r="G1007" s="25"/>
+      <c r="H1007" s="25"/>
+      <c r="I1007" s="25"/>
+      <c r="J1007" s="36"/>
+      <c r="K1007" s="30"/>
+    </row>
+    <row r="1008" x14ac:dyDescent="0.2">
+      <c r="A1008" s="8"/>
+      <c r="B1008" s="33"/>
+      <c r="C1008" s="20"/>
+      <c r="D1008" s="20"/>
+      <c r="E1008" s="14"/>
+      <c r="F1008" s="6"/>
+      <c r="G1008" s="25"/>
+      <c r="H1008" s="25"/>
+      <c r="I1008" s="25"/>
+      <c r="J1008" s="36"/>
+      <c r="K1008" s="30"/>
+    </row>
+    <row r="1009" x14ac:dyDescent="0.2">
+      <c r="A1009" s="8"/>
+      <c r="B1009" s="33"/>
+      <c r="C1009" s="20"/>
+      <c r="D1009" s="20"/>
+      <c r="E1009" s="14"/>
+      <c r="F1009" s="6"/>
+      <c r="G1009" s="25"/>
+      <c r="H1009" s="25"/>
+      <c r="I1009" s="25"/>
+      <c r="J1009" s="36"/>
+      <c r="K1009" s="30"/>
+    </row>
+    <row r="1010" x14ac:dyDescent="0.2">
+      <c r="A1010" s="8"/>
+      <c r="B1010" s="33"/>
+      <c r="C1010" s="20"/>
+      <c r="D1010" s="20"/>
+      <c r="E1010" s="14"/>
+      <c r="F1010" s="6"/>
+      <c r="G1010" s="25"/>
+      <c r="H1010" s="25"/>
+      <c r="I1010" s="25"/>
+      <c r="J1010" s="36"/>
+      <c r="K1010" s="30"/>
+    </row>
+    <row r="1011" x14ac:dyDescent="0.2">
+      <c r="A1011" s="8"/>
+      <c r="B1011" s="33"/>
+      <c r="C1011" s="20"/>
+      <c r="D1011" s="20"/>
+      <c r="E1011" s="14"/>
+      <c r="F1011" s="6"/>
+      <c r="G1011" s="25"/>
+      <c r="H1011" s="25"/>
+      <c r="I1011" s="25"/>
+      <c r="J1011" s="36"/>
+      <c r="K1011" s="30"/>
+    </row>
+    <row r="1012" x14ac:dyDescent="0.2">
+      <c r="A1012" s="8"/>
+      <c r="B1012" s="33"/>
+      <c r="C1012" s="20"/>
+      <c r="D1012" s="20"/>
+      <c r="E1012" s="14"/>
+      <c r="F1012" s="6"/>
+      <c r="G1012" s="25"/>
+      <c r="H1012" s="25"/>
+      <c r="I1012" s="25"/>
+      <c r="J1012" s="36"/>
+      <c r="K1012" s="30"/>
+    </row>
+    <row r="1013" x14ac:dyDescent="0.2">
+      <c r="A1013" s="8"/>
+      <c r="B1013" s="33"/>
+      <c r="C1013" s="20"/>
+      <c r="D1013" s="20"/>
+      <c r="E1013" s="14"/>
+      <c r="F1013" s="6"/>
+      <c r="G1013" s="25"/>
+      <c r="H1013" s="25"/>
+      <c r="I1013" s="25"/>
+      <c r="J1013" s="36"/>
+      <c r="K1013" s="30"/>
+    </row>
+    <row r="1014" x14ac:dyDescent="0.2">
+      <c r="A1014" s="8"/>
+      <c r="B1014" s="33"/>
+      <c r="C1014" s="20"/>
+      <c r="D1014" s="20"/>
+      <c r="E1014" s="14"/>
+      <c r="F1014" s="6"/>
+      <c r="G1014" s="25"/>
+      <c r="H1014" s="25"/>
+      <c r="I1014" s="25"/>
+      <c r="J1014" s="36"/>
+      <c r="K1014" s="30"/>
     </row>
     <row r="1015" ht="15" x14ac:dyDescent="0.25">
       <c r="A1015" s="4"/>
@@ -20516,96 +20991,112 @@
       <c r="J1514" s="37"/>
     </row>
     <row r="1515" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1515" s="4"/>
       <c r="G1515" s="26"/>
       <c r="H1515" s="26"/>
       <c r="I1515" s="26"/>
       <c r="J1515" s="37"/>
     </row>
     <row r="1516" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1516" s="4"/>
       <c r="G1516" s="26"/>
       <c r="H1516" s="26"/>
       <c r="I1516" s="26"/>
       <c r="J1516" s="37"/>
     </row>
     <row r="1517" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1517" s="4"/>
       <c r="G1517" s="26"/>
       <c r="H1517" s="26"/>
       <c r="I1517" s="26"/>
       <c r="J1517" s="37"/>
     </row>
     <row r="1518" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1518" s="4"/>
       <c r="G1518" s="26"/>
       <c r="H1518" s="26"/>
       <c r="I1518" s="26"/>
       <c r="J1518" s="37"/>
     </row>
     <row r="1519" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1519" s="4"/>
       <c r="G1519" s="26"/>
       <c r="H1519" s="26"/>
       <c r="I1519" s="26"/>
       <c r="J1519" s="37"/>
     </row>
     <row r="1520" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1520" s="4"/>
       <c r="G1520" s="26"/>
       <c r="H1520" s="26"/>
       <c r="I1520" s="26"/>
       <c r="J1520" s="37"/>
     </row>
     <row r="1521" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1521" s="4"/>
       <c r="G1521" s="26"/>
       <c r="H1521" s="26"/>
       <c r="I1521" s="26"/>
       <c r="J1521" s="37"/>
     </row>
     <row r="1522" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1522" s="4"/>
       <c r="G1522" s="26"/>
       <c r="H1522" s="26"/>
       <c r="I1522" s="26"/>
       <c r="J1522" s="37"/>
     </row>
     <row r="1523" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1523" s="4"/>
       <c r="G1523" s="26"/>
       <c r="H1523" s="26"/>
       <c r="I1523" s="26"/>
       <c r="J1523" s="37"/>
     </row>
     <row r="1524" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1524" s="4"/>
       <c r="G1524" s="26"/>
       <c r="H1524" s="26"/>
       <c r="I1524" s="26"/>
       <c r="J1524" s="37"/>
     </row>
     <row r="1525" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1525" s="4"/>
       <c r="G1525" s="26"/>
       <c r="H1525" s="26"/>
       <c r="I1525" s="26"/>
       <c r="J1525" s="37"/>
     </row>
     <row r="1526" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1526" s="4"/>
       <c r="G1526" s="26"/>
       <c r="H1526" s="26"/>
       <c r="I1526" s="26"/>
       <c r="J1526" s="37"/>
     </row>
     <row r="1527" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1527" s="4"/>
       <c r="G1527" s="26"/>
       <c r="H1527" s="26"/>
       <c r="I1527" s="26"/>
       <c r="J1527" s="37"/>
     </row>
     <row r="1528" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1528" s="4"/>
       <c r="G1528" s="26"/>
       <c r="H1528" s="26"/>
       <c r="I1528" s="26"/>
       <c r="J1528" s="37"/>
     </row>
     <row r="1529" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1529" s="4"/>
       <c r="G1529" s="26"/>
       <c r="H1529" s="26"/>
       <c r="I1529" s="26"/>
       <c r="J1529" s="37"/>
     </row>
     <row r="1530" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1530" s="4"/>
       <c r="G1530" s="26"/>
       <c r="H1530" s="26"/>
       <c r="I1530" s="26"/>
@@ -54456,6 +54947,102 @@
       <c r="H7171" s="26"/>
       <c r="I7171" s="26"/>
       <c r="J7171" s="37"/>
+    </row>
+    <row r="7172" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7172" s="26"/>
+      <c r="H7172" s="26"/>
+      <c r="I7172" s="26"/>
+      <c r="J7172" s="37"/>
+    </row>
+    <row r="7173" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7173" s="26"/>
+      <c r="H7173" s="26"/>
+      <c r="I7173" s="26"/>
+      <c r="J7173" s="37"/>
+    </row>
+    <row r="7174" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7174" s="26"/>
+      <c r="H7174" s="26"/>
+      <c r="I7174" s="26"/>
+      <c r="J7174" s="37"/>
+    </row>
+    <row r="7175" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7175" s="26"/>
+      <c r="H7175" s="26"/>
+      <c r="I7175" s="26"/>
+      <c r="J7175" s="37"/>
+    </row>
+    <row r="7176" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7176" s="26"/>
+      <c r="H7176" s="26"/>
+      <c r="I7176" s="26"/>
+      <c r="J7176" s="37"/>
+    </row>
+    <row r="7177" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7177" s="26"/>
+      <c r="H7177" s="26"/>
+      <c r="I7177" s="26"/>
+      <c r="J7177" s="37"/>
+    </row>
+    <row r="7178" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7178" s="26"/>
+      <c r="H7178" s="26"/>
+      <c r="I7178" s="26"/>
+      <c r="J7178" s="37"/>
+    </row>
+    <row r="7179" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7179" s="26"/>
+      <c r="H7179" s="26"/>
+      <c r="I7179" s="26"/>
+      <c r="J7179" s="37"/>
+    </row>
+    <row r="7180" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7180" s="26"/>
+      <c r="H7180" s="26"/>
+      <c r="I7180" s="26"/>
+      <c r="J7180" s="37"/>
+    </row>
+    <row r="7181" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7181" s="26"/>
+      <c r="H7181" s="26"/>
+      <c r="I7181" s="26"/>
+      <c r="J7181" s="37"/>
+    </row>
+    <row r="7182" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7182" s="26"/>
+      <c r="H7182" s="26"/>
+      <c r="I7182" s="26"/>
+      <c r="J7182" s="37"/>
+    </row>
+    <row r="7183" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7183" s="26"/>
+      <c r="H7183" s="26"/>
+      <c r="I7183" s="26"/>
+      <c r="J7183" s="37"/>
+    </row>
+    <row r="7184" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7184" s="26"/>
+      <c r="H7184" s="26"/>
+      <c r="I7184" s="26"/>
+      <c r="J7184" s="37"/>
+    </row>
+    <row r="7185" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7185" s="26"/>
+      <c r="H7185" s="26"/>
+      <c r="I7185" s="26"/>
+      <c r="J7185" s="37"/>
+    </row>
+    <row r="7186" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7186" s="26"/>
+      <c r="H7186" s="26"/>
+      <c r="I7186" s="26"/>
+      <c r="J7186" s="37"/>
+    </row>
+    <row r="7187" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7187" s="26"/>
+      <c r="H7187" s="26"/>
+      <c r="I7187" s="26"/>
+      <c r="J7187" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">
